--- a/data/T3_leader_cleaned.xlsx
+++ b/data/T3_leader_cleaned.xlsx
@@ -88,241 +88,241 @@
     <t>SpanOfControl</t>
   </si>
   <si>
+    <t>C_L03</t>
+  </si>
+  <si>
+    <t>B_L21</t>
+  </si>
+  <si>
+    <t>B_L16</t>
+  </si>
+  <si>
+    <t>B_L25</t>
+  </si>
+  <si>
+    <t>A_L29</t>
+  </si>
+  <si>
+    <t>A_L23</t>
+  </si>
+  <si>
+    <t>B_L08</t>
+  </si>
+  <si>
+    <t>C_L07</t>
+  </si>
+  <si>
+    <t>C_L26</t>
+  </si>
+  <si>
+    <t>B_L09</t>
+  </si>
+  <si>
+    <t>B_L24</t>
+  </si>
+  <si>
+    <t>B_L13</t>
+  </si>
+  <si>
+    <t>A_L09</t>
+  </si>
+  <si>
+    <t>B_L18</t>
+  </si>
+  <si>
+    <t>B_L19</t>
+  </si>
+  <si>
+    <t>C_L22</t>
+  </si>
+  <si>
+    <t>A_L06</t>
+  </si>
+  <si>
+    <t>C_L05</t>
+  </si>
+  <si>
+    <t>B_L01</t>
+  </si>
+  <si>
+    <t>B_L02</t>
+  </si>
+  <si>
+    <t>B_L06</t>
+  </si>
+  <si>
+    <t>A_L07</t>
+  </si>
+  <si>
+    <t>C_L27</t>
+  </si>
+  <si>
+    <t>A_L01</t>
+  </si>
+  <si>
+    <t>B_L14</t>
+  </si>
+  <si>
+    <t>C_L13</t>
+  </si>
+  <si>
+    <t>B_L15</t>
+  </si>
+  <si>
+    <t>B_L26</t>
+  </si>
+  <si>
+    <t>A_L30</t>
+  </si>
+  <si>
+    <t>B_L17</t>
+  </si>
+  <si>
+    <t>B_L27</t>
+  </si>
+  <si>
+    <t>A_L17</t>
+  </si>
+  <si>
+    <t>A_L19</t>
+  </si>
+  <si>
+    <t>A_L15</t>
+  </si>
+  <si>
+    <t>A_L25</t>
+  </si>
+  <si>
+    <t>A_L08</t>
+  </si>
+  <si>
+    <t>C_L29</t>
+  </si>
+  <si>
+    <t>B_L10</t>
+  </si>
+  <si>
+    <t>C_L14</t>
+  </si>
+  <si>
     <t>C_L02</t>
   </si>
   <si>
-    <t>B_L21</t>
-  </si>
-  <si>
-    <t>B_L17</t>
-  </si>
-  <si>
-    <t>B_L24</t>
+    <t>A_L11</t>
+  </si>
+  <si>
+    <t>C_L30</t>
+  </si>
+  <si>
+    <t>A_L13</t>
+  </si>
+  <si>
+    <t>A_L04</t>
+  </si>
+  <si>
+    <t>A_L14</t>
+  </si>
+  <si>
+    <t>C_L20</t>
+  </si>
+  <si>
+    <t>C_L10</t>
+  </si>
+  <si>
+    <t>B_L04</t>
+  </si>
+  <si>
+    <t>C_L12</t>
+  </si>
+  <si>
+    <t>C_L21</t>
+  </si>
+  <si>
+    <t>C_L25</t>
+  </si>
+  <si>
+    <t>C_L09</t>
+  </si>
+  <si>
+    <t>B_L30</t>
+  </si>
+  <si>
+    <t>B_L29</t>
+  </si>
+  <si>
+    <t>A_L18</t>
+  </si>
+  <si>
+    <t>B_L28</t>
+  </si>
+  <si>
+    <t>C_L24</t>
+  </si>
+  <si>
+    <t>A_L12</t>
+  </si>
+  <si>
+    <t>C_L11</t>
+  </si>
+  <si>
+    <t>B_L05</t>
+  </si>
+  <si>
+    <t>A_L10</t>
+  </si>
+  <si>
+    <t>A_L20</t>
+  </si>
+  <si>
+    <t>B_L07</t>
+  </si>
+  <si>
+    <t>C_L16</t>
+  </si>
+  <si>
+    <t>B_L12</t>
+  </si>
+  <si>
+    <t>A_L16</t>
+  </si>
+  <si>
+    <t>A_L03</t>
+  </si>
+  <si>
+    <t>C_L06</t>
+  </si>
+  <si>
+    <t>C_L23</t>
+  </si>
+  <si>
+    <t>C_L19</t>
+  </si>
+  <si>
+    <t>A_L27</t>
+  </si>
+  <si>
+    <t>C_L04</t>
   </si>
   <si>
     <t>A_L28</t>
   </si>
   <si>
-    <t>A_L22</t>
-  </si>
-  <si>
-    <t>B_L09</t>
-  </si>
-  <si>
-    <t>C_L06</t>
-  </si>
-  <si>
-    <t>C_L25</t>
-  </si>
-  <si>
-    <t>B_L10</t>
-  </si>
-  <si>
-    <t>B_L23</t>
-  </si>
-  <si>
-    <t>B_L14</t>
-  </si>
-  <si>
-    <t>A_L09</t>
-  </si>
-  <si>
-    <t>B_L19</t>
-  </si>
-  <si>
-    <t>B_L20</t>
-  </si>
-  <si>
-    <t>C_L21</t>
+    <t>C_L28</t>
   </si>
   <si>
     <t>A_L05</t>
   </si>
   <si>
-    <t>C_L04</t>
-  </si>
-  <si>
-    <t>B_L01</t>
-  </si>
-  <si>
-    <t>B_L02</t>
-  </si>
-  <si>
-    <t>B_L07</t>
-  </si>
-  <si>
-    <t>A_L06</t>
-  </si>
-  <si>
-    <t>C_L26</t>
-  </si>
-  <si>
-    <t>A_L01</t>
-  </si>
-  <si>
-    <t>B_L15</t>
-  </si>
-  <si>
-    <t>C_L12</t>
-  </si>
-  <si>
-    <t>B_L16</t>
-  </si>
-  <si>
-    <t>B_L26</t>
-  </si>
-  <si>
-    <t>A_L30</t>
-  </si>
-  <si>
-    <t>B_L18</t>
-  </si>
-  <si>
-    <t>B_L27</t>
-  </si>
-  <si>
-    <t>A_L18</t>
-  </si>
-  <si>
-    <t>A_L20</t>
-  </si>
-  <si>
-    <t>A_L16</t>
+    <t>C_L08</t>
+  </si>
+  <si>
+    <t>B_L22</t>
+  </si>
+  <si>
+    <t>B_L11</t>
   </si>
   <si>
     <t>A_L24</t>
-  </si>
-  <si>
-    <t>A_L07</t>
-  </si>
-  <si>
-    <t>C_L29</t>
-  </si>
-  <si>
-    <t>B_L11</t>
-  </si>
-  <si>
-    <t>C_L13</t>
-  </si>
-  <si>
-    <t>C_L01</t>
-  </si>
-  <si>
-    <t>A_L12</t>
-  </si>
-  <si>
-    <t>C_L30</t>
-  </si>
-  <si>
-    <t>A_L14</t>
-  </si>
-  <si>
-    <t>A_L03</t>
-  </si>
-  <si>
-    <t>A_L15</t>
-  </si>
-  <si>
-    <t>C_L19</t>
-  </si>
-  <si>
-    <t>C_L09</t>
-  </si>
-  <si>
-    <t>B_L05</t>
-  </si>
-  <si>
-    <t>C_L11</t>
-  </si>
-  <si>
-    <t>C_L20</t>
-  </si>
-  <si>
-    <t>C_L24</t>
-  </si>
-  <si>
-    <t>C_L08</t>
-  </si>
-  <si>
-    <t>B_L30</t>
-  </si>
-  <si>
-    <t>B_L29</t>
-  </si>
-  <si>
-    <t>A_L19</t>
-  </si>
-  <si>
-    <t>B_L28</t>
-  </si>
-  <si>
-    <t>C_L23</t>
-  </si>
-  <si>
-    <t>A_L13</t>
-  </si>
-  <si>
-    <t>C_L10</t>
-  </si>
-  <si>
-    <t>B_L06</t>
-  </si>
-  <si>
-    <t>A_L11</t>
-  </si>
-  <si>
-    <t>A_L21</t>
-  </si>
-  <si>
-    <t>B_L08</t>
-  </si>
-  <si>
-    <t>C_L14</t>
-  </si>
-  <si>
-    <t>B_L13</t>
-  </si>
-  <si>
-    <t>A_L17</t>
-  </si>
-  <si>
-    <t>A_L02</t>
-  </si>
-  <si>
-    <t>C_L05</t>
-  </si>
-  <si>
-    <t>C_L22</t>
-  </si>
-  <si>
-    <t>C_L16</t>
-  </si>
-  <si>
-    <t>A_L25</t>
-  </si>
-  <si>
-    <t>C_L03</t>
-  </si>
-  <si>
-    <t>A_L27</t>
-  </si>
-  <si>
-    <t>C_L27</t>
-  </si>
-  <si>
-    <t>A_L04</t>
-  </si>
-  <si>
-    <t>C_L07</t>
-  </si>
-  <si>
-    <t>B_L22</t>
-  </si>
-  <si>
-    <t>B_L12</t>
-  </si>
-  <si>
-    <t>A_L23</t>
   </si>
   <si>
     <t>C</t>
@@ -777,49 +777,49 @@
         <v>103</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S2">
         <v>6</v>
@@ -872,28 +872,28 @@
         <v>3</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S3">
         <v>6</v>
@@ -925,49 +925,49 @@
         <v>104</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G4">
         <v>1</v>
       </c>
       <c r="H4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I4">
         <v>1</v>
       </c>
       <c r="J4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S4">
         <v>6</v>
@@ -999,49 +999,49 @@
         <v>104</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S5">
         <v>6</v>
@@ -1073,49 +1073,49 @@
         <v>105</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P6">
         <v>1</v>
       </c>
       <c r="Q6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S6">
         <v>6</v>
@@ -1147,49 +1147,49 @@
         <v>105</v>
       </c>
       <c r="D7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S7">
         <v>6</v>
@@ -1221,49 +1221,49 @@
         <v>104</v>
       </c>
       <c r="D8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S8">
         <v>6</v>
@@ -1295,31 +1295,31 @@
         <v>103</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M9">
         <v>5</v>
@@ -1328,16 +1328,16 @@
         <v>5</v>
       </c>
       <c r="O9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q9">
         <v>5</v>
       </c>
       <c r="R9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S9">
         <v>6</v>
@@ -1369,31 +1369,31 @@
         <v>103</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M10">
         <v>5</v>
@@ -1405,13 +1405,13 @@
         <v>5</v>
       </c>
       <c r="P10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S10">
         <v>6</v>
@@ -1467,16 +1467,16 @@
         <v>5</v>
       </c>
       <c r="L11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M11">
         <v>4</v>
       </c>
       <c r="N11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P11">
         <v>5</v>
@@ -1538,28 +1538,28 @@
         <v>2</v>
       </c>
       <c r="K12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S12">
         <v>6</v>
@@ -1591,37 +1591,37 @@
         <v>104</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K13">
         <v>5</v>
       </c>
       <c r="L13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O13">
         <v>5</v>
@@ -1633,7 +1633,7 @@
         <v>5</v>
       </c>
       <c r="R13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S13">
         <v>6</v>
@@ -1686,28 +1686,28 @@
         <v>2</v>
       </c>
       <c r="K14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S14">
         <v>6</v>
@@ -1813,49 +1813,49 @@
         <v>104</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J16">
         <v>1</v>
       </c>
       <c r="K16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S16">
         <v>6</v>
@@ -1887,25 +1887,25 @@
         <v>103</v>
       </c>
       <c r="D17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K17">
         <v>4</v>
@@ -1961,49 +1961,49 @@
         <v>105</v>
       </c>
       <c r="D18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F18">
         <v>1</v>
       </c>
       <c r="G18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S18">
         <v>6</v>
@@ -2041,43 +2041,43 @@
         <v>1</v>
       </c>
       <c r="F19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G19">
         <v>1</v>
       </c>
       <c r="H19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S19">
         <v>6</v>
@@ -2109,25 +2109,25 @@
         <v>104</v>
       </c>
       <c r="D20">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F20">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G20">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I20">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J20">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K20">
         <v>3</v>
@@ -2183,7 +2183,7 @@
         <v>104</v>
       </c>
       <c r="D21">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E21">
         <v>5</v>
@@ -2195,7 +2195,7 @@
         <v>5</v>
       </c>
       <c r="H21">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I21">
         <v>5</v>
@@ -2278,28 +2278,28 @@
         <v>1</v>
       </c>
       <c r="K22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L22">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N22">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S22">
         <v>6</v>
@@ -2334,46 +2334,46 @@
         <v>1</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K23">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L23">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M23">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N23">
         <v>5</v>
       </c>
       <c r="O23">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P23">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q23">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R23">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S23">
         <v>6</v>
@@ -2405,49 +2405,49 @@
         <v>103</v>
       </c>
       <c r="D24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E24">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H24">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I24">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S24">
         <v>6</v>
@@ -2553,7 +2553,7 @@
         <v>104</v>
       </c>
       <c r="D26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E26">
         <v>1</v>
@@ -2562,40 +2562,40 @@
         <v>1</v>
       </c>
       <c r="G26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K26">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L26">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q26">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S26">
         <v>6</v>
@@ -2627,49 +2627,49 @@
         <v>103</v>
       </c>
       <c r="D27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N27">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O27">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P27">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q27">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R27">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S27">
         <v>6</v>
@@ -2701,7 +2701,7 @@
         <v>104</v>
       </c>
       <c r="D28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28">
         <v>1</v>
@@ -2710,7 +2710,7 @@
         <v>1</v>
       </c>
       <c r="G28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H28">
         <v>1</v>
@@ -2722,13 +2722,13 @@
         <v>1</v>
       </c>
       <c r="K28">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L28">
         <v>5</v>
       </c>
       <c r="M28">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N28">
         <v>5</v>
@@ -2740,10 +2740,10 @@
         <v>5</v>
       </c>
       <c r="Q28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S28">
         <v>6</v>
@@ -2802,7 +2802,7 @@
         <v>5</v>
       </c>
       <c r="M29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N29">
         <v>4</v>
@@ -2811,13 +2811,13 @@
         <v>5</v>
       </c>
       <c r="P29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S29">
         <v>6</v>
@@ -2852,10 +2852,10 @@
         <v>1</v>
       </c>
       <c r="E30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -2867,31 +2867,31 @@
         <v>1</v>
       </c>
       <c r="J30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S30">
         <v>6</v>
@@ -3018,28 +3018,28 @@
         <v>1</v>
       </c>
       <c r="K32">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L32">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M32">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N32">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O32">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P32">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q32">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R32">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S32">
         <v>6</v>
@@ -3098,7 +3098,7 @@
         <v>5</v>
       </c>
       <c r="M33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N33">
         <v>5</v>
@@ -3113,7 +3113,7 @@
         <v>4</v>
       </c>
       <c r="R33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S33">
         <v>6</v>
@@ -3219,49 +3219,49 @@
         <v>105</v>
       </c>
       <c r="D35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E35">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F35">
         <v>1</v>
       </c>
       <c r="G35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K35">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L35">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P35">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q35">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S35">
         <v>6</v>
@@ -3536,28 +3536,28 @@
         <v>4</v>
       </c>
       <c r="K39">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L39">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N39">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O39">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S39">
         <v>6</v>
@@ -3589,31 +3589,31 @@
         <v>103</v>
       </c>
       <c r="D40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L40">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M40">
         <v>5</v>
@@ -3625,10 +3625,10 @@
         <v>5</v>
       </c>
       <c r="P40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q40">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R40">
         <v>5</v>
@@ -3663,43 +3663,43 @@
         <v>103</v>
       </c>
       <c r="D41">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E41">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F41">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G41">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H41">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I41">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J41">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K41">
         <v>5</v>
       </c>
       <c r="L41">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M41">
         <v>5</v>
       </c>
       <c r="N41">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O41">
         <v>5</v>
       </c>
       <c r="P41">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q41">
         <v>5</v>
@@ -3758,28 +3758,28 @@
         <v>3</v>
       </c>
       <c r="K42">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L42">
         <v>5</v>
       </c>
       <c r="M42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N42">
         <v>5</v>
       </c>
       <c r="O42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P42">
         <v>5</v>
       </c>
       <c r="Q42">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R42">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S42">
         <v>6</v>
@@ -3832,28 +3832,28 @@
         <v>3</v>
       </c>
       <c r="K43">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L43">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M43">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N43">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O43">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P43">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q43">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R43">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S43">
         <v>6</v>
@@ -3885,46 +3885,46 @@
         <v>105</v>
       </c>
       <c r="D44">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E44">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F44">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G44">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H44">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I44">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J44">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K44">
         <v>5</v>
       </c>
       <c r="L44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M44">
         <v>5</v>
       </c>
       <c r="N44">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O44">
         <v>5</v>
       </c>
       <c r="P44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R44">
         <v>5</v>
@@ -3980,16 +3980,16 @@
         <v>5</v>
       </c>
       <c r="L45">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M45">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N45">
         <v>5</v>
       </c>
       <c r="O45">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P45">
         <v>5</v>
@@ -3998,7 +3998,7 @@
         <v>5</v>
       </c>
       <c r="R45">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S45">
         <v>6</v>
@@ -4036,7 +4036,7 @@
         <v>1</v>
       </c>
       <c r="G46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H46">
         <v>1</v>
@@ -4048,28 +4048,28 @@
         <v>1</v>
       </c>
       <c r="K46">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L46">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M46">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N46">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O46">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P46">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q46">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R46">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S46">
         <v>6</v>
@@ -4107,7 +4107,7 @@
         <v>1</v>
       </c>
       <c r="F47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G47">
         <v>1</v>
@@ -4119,31 +4119,31 @@
         <v>1</v>
       </c>
       <c r="J47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K47">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L47">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M47">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N47">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O47">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P47">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q47">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R47">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S47">
         <v>6</v>
@@ -4196,28 +4196,28 @@
         <v>3</v>
       </c>
       <c r="K48">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L48">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M48">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N48">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O48">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P48">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q48">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R48">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S48">
         <v>6</v>
@@ -4249,49 +4249,49 @@
         <v>104</v>
       </c>
       <c r="D49">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E49">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F49">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G49">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H49">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I49">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J49">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K49">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L49">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M49">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N49">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O49">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P49">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Q49">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R49">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="S49">
         <v>6</v>
@@ -4400,46 +4400,46 @@
         <v>1</v>
       </c>
       <c r="E51">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F51">
         <v>1</v>
       </c>
       <c r="G51">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I51">
         <v>1</v>
       </c>
       <c r="J51">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L51">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M51">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N51">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O51">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P51">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R51">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S51">
         <v>6</v>
@@ -4492,28 +4492,28 @@
         <v>1</v>
       </c>
       <c r="K52">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L52">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M52">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N52">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O52">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P52">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q52">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R52">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S52">
         <v>6</v>
@@ -4569,7 +4569,7 @@
         <v>5</v>
       </c>
       <c r="L53">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M53">
         <v>5</v>
@@ -4578,16 +4578,16 @@
         <v>4</v>
       </c>
       <c r="O53">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P53">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q53">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R53">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S53">
         <v>6</v>
@@ -4788,28 +4788,28 @@
         <v>4</v>
       </c>
       <c r="K56">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L56">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M56">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N56">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O56">
         <v>5</v>
       </c>
       <c r="P56">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q56">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R56">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S56">
         <v>6</v>
@@ -4841,28 +4841,28 @@
         <v>104</v>
       </c>
       <c r="D57">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F57">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H57">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I57">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J57">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K57">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L57">
         <v>5</v>
@@ -4874,7 +4874,7 @@
         <v>5</v>
       </c>
       <c r="O57">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P57">
         <v>5</v>
@@ -4915,49 +4915,49 @@
         <v>103</v>
       </c>
       <c r="D58">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E58">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F58">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G58">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H58">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I58">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J58">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K58">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L58">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M58">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N58">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O58">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P58">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q58">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R58">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S58">
         <v>6</v>
@@ -4989,49 +4989,49 @@
         <v>105</v>
       </c>
       <c r="D59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G59">
         <v>1</v>
       </c>
       <c r="H59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I59">
         <v>1</v>
       </c>
       <c r="J59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K59">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L59">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M59">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N59">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O59">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P59">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q59">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R59">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S59">
         <v>6</v>
@@ -5063,28 +5063,28 @@
         <v>103</v>
       </c>
       <c r="D60">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F60">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G60">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H60">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I60">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J60">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K60">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L60">
         <v>5</v>
@@ -5137,49 +5137,49 @@
         <v>104</v>
       </c>
       <c r="D61">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E61">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F61">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G61">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H61">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I61">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J61">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K61">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L61">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M61">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N61">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O61">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P61">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q61">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R61">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S61">
         <v>6</v>
@@ -5211,34 +5211,34 @@
         <v>105</v>
       </c>
       <c r="D62">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E62">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F62">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G62">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H62">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I62">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J62">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K62">
         <v>5</v>
       </c>
       <c r="L62">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M62">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N62">
         <v>5</v>
@@ -5247,13 +5247,13 @@
         <v>5</v>
       </c>
       <c r="P62">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q62">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R62">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S62">
         <v>6</v>
@@ -5297,37 +5297,37 @@
         <v>1</v>
       </c>
       <c r="H63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I63">
         <v>1</v>
       </c>
       <c r="J63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K63">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L63">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M63">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N63">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O63">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P63">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q63">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R63">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S63">
         <v>6</v>
@@ -5383,10 +5383,10 @@
         <v>5</v>
       </c>
       <c r="L64">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M64">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N64">
         <v>5</v>
@@ -5398,10 +5398,10 @@
         <v>5</v>
       </c>
       <c r="Q64">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R64">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S64">
         <v>6</v>
@@ -5433,49 +5433,49 @@
         <v>103</v>
       </c>
       <c r="D65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E65">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F65">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G65">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H65">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J65">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K65">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L65">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M65">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N65">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O65">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P65">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q65">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R65">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S65">
         <v>6</v>
@@ -5507,49 +5507,49 @@
         <v>104</v>
       </c>
       <c r="D66">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E66">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F66">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G66">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H66">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I66">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J66">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K66">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L66">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M66">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N66">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O66">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P66">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q66">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R66">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S66">
         <v>6</v>
@@ -5581,28 +5581,28 @@
         <v>105</v>
       </c>
       <c r="D67">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E67">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F67">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G67">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H67">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I67">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J67">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K67">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L67">
         <v>5</v>
@@ -5655,34 +5655,34 @@
         <v>105</v>
       </c>
       <c r="D68">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E68">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F68">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G68">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H68">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I68">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J68">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K68">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L68">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M68">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N68">
         <v>5</v>
@@ -5694,10 +5694,10 @@
         <v>5</v>
       </c>
       <c r="Q68">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R68">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S68">
         <v>6</v>
@@ -5729,28 +5729,28 @@
         <v>103</v>
       </c>
       <c r="D69">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E69">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G69">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H69">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J69">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K69">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L69">
         <v>5</v>
@@ -5759,19 +5759,19 @@
         <v>5</v>
       </c>
       <c r="N69">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O69">
         <v>5</v>
       </c>
       <c r="P69">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q69">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R69">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S69">
         <v>6</v>
@@ -5803,49 +5803,49 @@
         <v>103</v>
       </c>
       <c r="D70">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E70">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F70">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G70">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H70">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I70">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J70">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K70">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L70">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M70">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N70">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P70">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q70">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R70">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S70">
         <v>6</v>
@@ -5901,7 +5901,7 @@
         <v>5</v>
       </c>
       <c r="L71">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M71">
         <v>5</v>
@@ -5916,10 +5916,10 @@
         <v>5</v>
       </c>
       <c r="Q71">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R71">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S71">
         <v>6</v>
@@ -5951,25 +5951,25 @@
         <v>105</v>
       </c>
       <c r="D72">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E72">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F72">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G72">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H72">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I72">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J72">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K72">
         <v>5</v>
@@ -5978,7 +5978,7 @@
         <v>5</v>
       </c>
       <c r="M72">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N72">
         <v>5</v>
@@ -6025,16 +6025,16 @@
         <v>103</v>
       </c>
       <c r="D73">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H73">
         <v>1</v>
@@ -6043,7 +6043,7 @@
         <v>1</v>
       </c>
       <c r="J73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K73">
         <v>5</v>
@@ -6052,22 +6052,22 @@
         <v>5</v>
       </c>
       <c r="M73">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N73">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O73">
         <v>5</v>
       </c>
       <c r="P73">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q73">
         <v>5</v>
       </c>
       <c r="R73">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S73">
         <v>6</v>
@@ -6120,7 +6120,7 @@
         <v>3</v>
       </c>
       <c r="K74">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L74">
         <v>4</v>
@@ -6321,49 +6321,49 @@
         <v>103</v>
       </c>
       <c r="D77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K77">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L77">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M77">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N77">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O77">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P77">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q77">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R77">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S77">
         <v>6</v>
@@ -6543,49 +6543,49 @@
         <v>105</v>
       </c>
       <c r="D80">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E80">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F80">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G80">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H80">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I80">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J80">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K80">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L80">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M80">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N80">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O80">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P80">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q80">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R80">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S80">
         <v>6</v>

--- a/data/T3_leader_cleaned.xlsx
+++ b/data/T3_leader_cleaned.xlsx
@@ -88,250 +88,250 @@
     <t>SpanOfControl</t>
   </si>
   <si>
+    <t>A_L14</t>
+  </si>
+  <si>
+    <t>A_L19</t>
+  </si>
+  <si>
+    <t>A_L08</t>
+  </si>
+  <si>
+    <t>B_L10</t>
+  </si>
+  <si>
+    <t>B_L05</t>
+  </si>
+  <si>
+    <t>C_L20</t>
+  </si>
+  <si>
+    <t>C_L26</t>
+  </si>
+  <si>
+    <t>A_L11</t>
+  </si>
+  <si>
+    <t>A_L10</t>
+  </si>
+  <si>
+    <t>B_L25</t>
+  </si>
+  <si>
+    <t>B_L23</t>
+  </si>
+  <si>
+    <t>C_L13</t>
+  </si>
+  <si>
+    <t>C_L02</t>
+  </si>
+  <si>
     <t>C_L03</t>
   </si>
   <si>
-    <t>B_L21</t>
+    <t>B_L08</t>
+  </si>
+  <si>
+    <t>B_L09</t>
+  </si>
+  <si>
+    <t>A_L25</t>
+  </si>
+  <si>
+    <t>C_L08</t>
+  </si>
+  <si>
+    <t>A_L15</t>
+  </si>
+  <si>
+    <t>C_L10</t>
+  </si>
+  <si>
+    <t>B_L04</t>
+  </si>
+  <si>
+    <t>C_L16</t>
+  </si>
+  <si>
+    <t>C_L22</t>
+  </si>
+  <si>
+    <t>A_L27</t>
+  </si>
+  <si>
+    <t>C_L19</t>
+  </si>
+  <si>
+    <t>C_L09</t>
+  </si>
+  <si>
+    <t>A_L18</t>
+  </si>
+  <si>
+    <t>A_L29</t>
+  </si>
+  <si>
+    <t>A_L26</t>
+  </si>
+  <si>
+    <t>A_L06</t>
+  </si>
+  <si>
+    <t>C_L25</t>
+  </si>
+  <si>
+    <t>A_L13</t>
+  </si>
+  <si>
+    <t>C_L29</t>
+  </si>
+  <si>
+    <t>B_L29</t>
+  </si>
+  <si>
+    <t>C_L12</t>
+  </si>
+  <si>
+    <t>B_L26</t>
+  </si>
+  <si>
+    <t>B_L30</t>
+  </si>
+  <si>
+    <t>C_L05</t>
+  </si>
+  <si>
+    <t>A_L20</t>
+  </si>
+  <si>
+    <t>C_L30</t>
+  </si>
+  <si>
+    <t>C_L28</t>
+  </si>
+  <si>
+    <t>B_L01</t>
+  </si>
+  <si>
+    <t>C_L18</t>
+  </si>
+  <si>
+    <t>C_L23</t>
+  </si>
+  <si>
+    <t>B_L03</t>
+  </si>
+  <si>
+    <t>C_L21</t>
+  </si>
+  <si>
+    <t>B_L11</t>
+  </si>
+  <si>
+    <t>A_L17</t>
+  </si>
+  <si>
+    <t>C_L04</t>
+  </si>
+  <si>
+    <t>B_L20</t>
+  </si>
+  <si>
+    <t>A_L09</t>
+  </si>
+  <si>
+    <t>B_L19</t>
+  </si>
+  <si>
+    <t>B_L02</t>
+  </si>
+  <si>
+    <t>B_L06</t>
+  </si>
+  <si>
+    <t>B_L24</t>
   </si>
   <si>
     <t>B_L16</t>
   </si>
   <si>
-    <t>B_L25</t>
-  </si>
-  <si>
-    <t>A_L29</t>
+    <t>A_L07</t>
+  </si>
+  <si>
+    <t>C_L17</t>
+  </si>
+  <si>
+    <t>C_L01</t>
+  </si>
+  <si>
+    <t>A_L02</t>
+  </si>
+  <si>
+    <t>C_L11</t>
+  </si>
+  <si>
+    <t>C_L14</t>
+  </si>
+  <si>
+    <t>A_L03</t>
+  </si>
+  <si>
+    <t>A_L24</t>
+  </si>
+  <si>
+    <t>A_L28</t>
+  </si>
+  <si>
+    <t>A_L16</t>
+  </si>
+  <si>
+    <t>B_L14</t>
+  </si>
+  <si>
+    <t>B_L22</t>
+  </si>
+  <si>
+    <t>A_L22</t>
+  </si>
+  <si>
+    <t>B_L12</t>
+  </si>
+  <si>
+    <t>C_L27</t>
+  </si>
+  <si>
+    <t>A_L12</t>
+  </si>
+  <si>
+    <t>B_L18</t>
+  </si>
+  <si>
+    <t>A_L21</t>
   </si>
   <si>
     <t>A_L23</t>
   </si>
   <si>
-    <t>B_L08</t>
-  </si>
-  <si>
-    <t>C_L07</t>
-  </si>
-  <si>
-    <t>C_L26</t>
-  </si>
-  <si>
-    <t>B_L09</t>
-  </si>
-  <si>
-    <t>B_L24</t>
-  </si>
-  <si>
-    <t>B_L13</t>
-  </si>
-  <si>
-    <t>A_L09</t>
-  </si>
-  <si>
-    <t>B_L18</t>
-  </si>
-  <si>
-    <t>B_L19</t>
-  </si>
-  <si>
-    <t>C_L22</t>
-  </si>
-  <si>
-    <t>A_L06</t>
-  </si>
-  <si>
-    <t>C_L05</t>
-  </si>
-  <si>
-    <t>B_L01</t>
-  </si>
-  <si>
-    <t>B_L02</t>
-  </si>
-  <si>
-    <t>B_L06</t>
-  </si>
-  <si>
-    <t>A_L07</t>
-  </si>
-  <si>
-    <t>C_L27</t>
-  </si>
-  <si>
     <t>A_L01</t>
   </si>
   <si>
-    <t>B_L14</t>
-  </si>
-  <si>
-    <t>C_L13</t>
-  </si>
-  <si>
-    <t>B_L15</t>
-  </si>
-  <si>
-    <t>B_L26</t>
-  </si>
-  <si>
-    <t>A_L30</t>
-  </si>
-  <si>
-    <t>B_L17</t>
-  </si>
-  <si>
-    <t>B_L27</t>
-  </si>
-  <si>
-    <t>A_L17</t>
-  </si>
-  <si>
-    <t>A_L19</t>
-  </si>
-  <si>
-    <t>A_L15</t>
-  </si>
-  <si>
-    <t>A_L25</t>
-  </si>
-  <si>
-    <t>A_L08</t>
-  </si>
-  <si>
-    <t>C_L29</t>
-  </si>
-  <si>
-    <t>B_L10</t>
-  </si>
-  <si>
-    <t>C_L14</t>
-  </si>
-  <si>
-    <t>C_L02</t>
-  </si>
-  <si>
-    <t>A_L11</t>
-  </si>
-  <si>
-    <t>C_L30</t>
-  </si>
-  <si>
-    <t>A_L13</t>
-  </si>
-  <si>
-    <t>A_L04</t>
-  </si>
-  <si>
-    <t>A_L14</t>
-  </si>
-  <si>
-    <t>C_L20</t>
-  </si>
-  <si>
-    <t>C_L10</t>
-  </si>
-  <si>
-    <t>B_L04</t>
-  </si>
-  <si>
-    <t>C_L12</t>
-  </si>
-  <si>
-    <t>C_L21</t>
-  </si>
-  <si>
-    <t>C_L25</t>
-  </si>
-  <si>
-    <t>C_L09</t>
-  </si>
-  <si>
-    <t>B_L30</t>
-  </si>
-  <si>
-    <t>B_L29</t>
-  </si>
-  <si>
-    <t>A_L18</t>
-  </si>
-  <si>
-    <t>B_L28</t>
-  </si>
-  <si>
     <t>C_L24</t>
   </si>
   <si>
-    <t>A_L12</t>
-  </si>
-  <si>
-    <t>C_L11</t>
-  </si>
-  <si>
-    <t>B_L05</t>
-  </si>
-  <si>
-    <t>A_L10</t>
-  </si>
-  <si>
-    <t>A_L20</t>
-  </si>
-  <si>
-    <t>B_L07</t>
-  </si>
-  <si>
-    <t>C_L16</t>
-  </si>
-  <si>
-    <t>B_L12</t>
-  </si>
-  <si>
-    <t>A_L16</t>
-  </si>
-  <si>
-    <t>A_L03</t>
-  </si>
-  <si>
     <t>C_L06</t>
   </si>
   <si>
-    <t>C_L23</t>
-  </si>
-  <si>
-    <t>C_L19</t>
-  </si>
-  <si>
-    <t>A_L27</t>
-  </si>
-  <si>
-    <t>C_L04</t>
-  </si>
-  <si>
-    <t>A_L28</t>
-  </si>
-  <si>
-    <t>C_L28</t>
-  </si>
-  <si>
     <t>A_L05</t>
   </si>
   <si>
-    <t>C_L08</t>
-  </si>
-  <si>
-    <t>B_L22</t>
-  </si>
-  <si>
-    <t>B_L11</t>
-  </si>
-  <si>
-    <t>A_L24</t>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
   </si>
   <si>
     <t>C</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>A</t>
   </si>
 </sst>
 </file>
@@ -777,64 +777,64 @@
         <v>103</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M2">
         <v>6</v>
       </c>
       <c r="N2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q2">
         <v>5</v>
       </c>
       <c r="R2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S2">
         <v>6</v>
       </c>
       <c r="T2">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="U2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W2">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="X2">
         <v>5</v>
@@ -848,67 +848,67 @@
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N3">
         <v>3</v>
       </c>
       <c r="O3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S3">
         <v>6</v>
       </c>
       <c r="T3">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="U3">
         <v>1</v>
       </c>
       <c r="V3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W3">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="X3">
         <v>5</v>
@@ -922,70 +922,70 @@
         <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M4">
         <v>6</v>
       </c>
       <c r="N4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S4">
         <v>6</v>
       </c>
       <c r="T4">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="U4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W4">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="X4">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:24">
@@ -999,55 +999,55 @@
         <v>104</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5">
         <v>3</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N5">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O5">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S5">
         <v>6</v>
       </c>
       <c r="T5">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="U5">
         <v>1</v>
@@ -1056,10 +1056,10 @@
         <v>3</v>
       </c>
       <c r="W5">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="X5">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:24">
@@ -1070,70 +1070,70 @@
         <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L6">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M6">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N6">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O6">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P6">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Q6">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="R6">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="S6">
         <v>6</v>
       </c>
       <c r="T6">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="U6">
         <v>1</v>
       </c>
       <c r="V6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X6">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:24">
@@ -1147,67 +1147,67 @@
         <v>105</v>
       </c>
       <c r="D7">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H7">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K7">
         <v>3</v>
       </c>
       <c r="L7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S7">
         <v>6</v>
       </c>
       <c r="T7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="U7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X7">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:24">
@@ -1218,70 +1218,70 @@
         <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I8">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K8">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L8">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M8">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N8">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O8">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="P8">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Q8">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R8">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="S8">
         <v>6</v>
       </c>
       <c r="T8">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="U8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W8">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="X8">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:24">
@@ -1295,31 +1295,31 @@
         <v>103</v>
       </c>
       <c r="D9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F9">
         <v>2</v>
       </c>
       <c r="G9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M9">
         <v>5</v>
@@ -1331,19 +1331,19 @@
         <v>6</v>
       </c>
       <c r="P9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q9">
         <v>5</v>
       </c>
       <c r="R9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S9">
         <v>6</v>
       </c>
       <c r="T9">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="U9">
         <v>2</v>
@@ -1352,7 +1352,7 @@
         <v>4</v>
       </c>
       <c r="W9">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="X9">
         <v>8</v>
@@ -1369,10 +1369,10 @@
         <v>103</v>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F10">
         <v>2</v>
@@ -1381,7 +1381,7 @@
         <v>2</v>
       </c>
       <c r="H10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I10">
         <v>2</v>
@@ -1390,25 +1390,25 @@
         <v>2</v>
       </c>
       <c r="K10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M10">
         <v>5</v>
       </c>
       <c r="N10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O10">
         <v>5</v>
       </c>
       <c r="P10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R10">
         <v>4</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="V10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="W10">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="X10">
         <v>4</v>
@@ -1443,10 +1443,10 @@
         <v>104</v>
       </c>
       <c r="D11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F11">
         <v>3</v>
@@ -1461,28 +1461,28 @@
         <v>3</v>
       </c>
       <c r="J11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M11">
         <v>4</v>
       </c>
       <c r="N11">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O11">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P11">
         <v>5</v>
       </c>
       <c r="Q11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R11">
         <v>5</v>
@@ -1491,19 +1491,19 @@
         <v>6</v>
       </c>
       <c r="T11">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="U11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W11">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="X11">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:24">
@@ -1517,67 +1517,67 @@
         <v>104</v>
       </c>
       <c r="D12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F12">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M12">
         <v>3</v>
       </c>
       <c r="N12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q12">
         <v>3</v>
       </c>
       <c r="R12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S12">
         <v>6</v>
       </c>
       <c r="T12">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="U12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W12">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="X12">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:24">
@@ -1588,7 +1588,7 @@
         <v>35</v>
       </c>
       <c r="C13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D13">
         <v>3</v>
@@ -1597,7 +1597,7 @@
         <v>3</v>
       </c>
       <c r="F13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G13">
         <v>3</v>
@@ -1609,49 +1609,49 @@
         <v>2</v>
       </c>
       <c r="J13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L13">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M13">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N13">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P13">
         <v>5</v>
       </c>
       <c r="Q13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S13">
         <v>6</v>
       </c>
       <c r="T13">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="U13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V13">
         <v>3</v>
       </c>
       <c r="W13">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="X13">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:24">
@@ -1665,67 +1665,67 @@
         <v>105</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K14">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L14">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Q14">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="R14">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="S14">
         <v>6</v>
       </c>
       <c r="T14">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="U14">
         <v>1</v>
       </c>
       <c r="V14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="W14">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="X14">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:24">
@@ -1736,70 +1736,70 @@
         <v>37</v>
       </c>
       <c r="C15" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I15">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K15">
         <v>5</v>
       </c>
       <c r="L15">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N15">
         <v>5</v>
       </c>
       <c r="O15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S15">
         <v>6</v>
       </c>
       <c r="T15">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="U15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W15">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="X15">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:24">
@@ -1813,67 +1813,67 @@
         <v>104</v>
       </c>
       <c r="D16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L16">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M16">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N16">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P16">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Q16">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R16">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S16">
         <v>6</v>
       </c>
       <c r="T16">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="U16">
         <v>1</v>
       </c>
       <c r="V16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W16">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="X16">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:24">
@@ -1884,46 +1884,46 @@
         <v>39</v>
       </c>
       <c r="C17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D17">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E17">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F17">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G17">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H17">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I17">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J17">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K17">
         <v>4</v>
       </c>
       <c r="L17">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q17">
         <v>4</v>
@@ -1935,19 +1935,19 @@
         <v>6</v>
       </c>
       <c r="T17">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="U17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V17">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W17">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="X17">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:24">
@@ -1958,28 +1958,28 @@
         <v>40</v>
       </c>
       <c r="C18" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D18">
         <v>2</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H18">
         <v>2</v>
       </c>
       <c r="I18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K18">
         <v>4</v>
@@ -1994,13 +1994,13 @@
         <v>4</v>
       </c>
       <c r="O18">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P18">
         <v>5</v>
       </c>
       <c r="Q18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R18">
         <v>5</v>
@@ -2009,19 +2009,19 @@
         <v>6</v>
       </c>
       <c r="T18">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="U18">
         <v>1</v>
       </c>
       <c r="V18">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W18">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="X18">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:24">
@@ -2032,70 +2032,70 @@
         <v>41</v>
       </c>
       <c r="C19" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H19">
         <v>2</v>
       </c>
       <c r="I19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K19">
         <v>5</v>
       </c>
       <c r="L19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M19">
         <v>5</v>
       </c>
       <c r="N19">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O19">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P19">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S19">
         <v>6</v>
       </c>
       <c r="T19">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="U19">
         <v>1</v>
       </c>
       <c r="V19">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W19">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="X19">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:24">
@@ -2106,34 +2106,34 @@
         <v>42</v>
       </c>
       <c r="C20" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D20">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G20">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H20">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M20">
         <v>3</v>
@@ -2145,10 +2145,10 @@
         <v>3</v>
       </c>
       <c r="P20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q20">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R20">
         <v>4</v>
@@ -2157,7 +2157,7 @@
         <v>6</v>
       </c>
       <c r="T20">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="U20">
         <v>1</v>
@@ -2166,10 +2166,10 @@
         <v>3</v>
       </c>
       <c r="W20">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="X20">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:24">
@@ -2180,70 +2180,70 @@
         <v>43</v>
       </c>
       <c r="C21" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D21">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E21">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F21">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G21">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I21">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J21">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K21">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L21">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M21">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N21">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O21">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P21">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q21">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R21">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S21">
         <v>6</v>
       </c>
       <c r="T21">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="U21">
         <v>1</v>
       </c>
       <c r="V21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W21">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="X21">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:24">
@@ -2260,64 +2260,64 @@
         <v>1</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H22">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J22">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K22">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L22">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M22">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N22">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O22">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="P22">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Q22">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R22">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="S22">
         <v>6</v>
       </c>
       <c r="T22">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="U22">
         <v>1</v>
       </c>
       <c r="V22">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W22">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="X22">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:24">
@@ -2334,64 +2334,64 @@
         <v>1</v>
       </c>
       <c r="E23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K23">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L23">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M23">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N23">
         <v>5</v>
       </c>
       <c r="O23">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P23">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q23">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R23">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S23">
         <v>6</v>
       </c>
       <c r="T23">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="U23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W23">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="X23">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:24">
@@ -2402,19 +2402,19 @@
         <v>46</v>
       </c>
       <c r="C24" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E24">
         <v>3</v>
       </c>
       <c r="F24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H24">
         <v>4</v>
@@ -2426,7 +2426,7 @@
         <v>2</v>
       </c>
       <c r="K24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L24">
         <v>4</v>
@@ -2438,13 +2438,13 @@
         <v>5</v>
       </c>
       <c r="O24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P24">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R24">
         <v>4</v>
@@ -2453,7 +2453,7 @@
         <v>6</v>
       </c>
       <c r="T24">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="U24">
         <v>2</v>
@@ -2462,10 +2462,10 @@
         <v>4</v>
       </c>
       <c r="W24">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="X24">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:24">
@@ -2476,22 +2476,22 @@
         <v>47</v>
       </c>
       <c r="C25" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D25">
         <v>2</v>
       </c>
       <c r="E25">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F25">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G25">
         <v>3</v>
       </c>
       <c r="H25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I25">
         <v>2</v>
@@ -2500,46 +2500,46 @@
         <v>2</v>
       </c>
       <c r="K25">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L25">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M25">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N25">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O25">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P25">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q25">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R25">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S25">
         <v>6</v>
       </c>
       <c r="T25">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="U25">
         <v>1</v>
       </c>
       <c r="V25">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W25">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X25">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:24">
@@ -2550,70 +2550,70 @@
         <v>48</v>
       </c>
       <c r="C26" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J26">
         <v>1</v>
       </c>
       <c r="K26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N26">
         <v>6</v>
       </c>
       <c r="O26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q26">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S26">
         <v>6</v>
       </c>
       <c r="T26">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="U26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V26">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W26">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="X26">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:24">
@@ -2624,70 +2624,70 @@
         <v>49</v>
       </c>
       <c r="C27" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D27">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E27">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F27">
         <v>2</v>
       </c>
       <c r="G27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I27">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J27">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K27">
         <v>4</v>
       </c>
       <c r="L27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M27">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N27">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O27">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P27">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q27">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R27">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S27">
         <v>6</v>
       </c>
       <c r="T27">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="U27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W27">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="X27">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:24">
@@ -2698,10 +2698,10 @@
         <v>50</v>
       </c>
       <c r="C28" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28">
         <v>1</v>
@@ -2710,7 +2710,7 @@
         <v>1</v>
       </c>
       <c r="G28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H28">
         <v>1</v>
@@ -2722,46 +2722,46 @@
         <v>1</v>
       </c>
       <c r="K28">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M28">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N28">
         <v>5</v>
       </c>
       <c r="O28">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q28">
         <v>6</v>
       </c>
       <c r="R28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S28">
         <v>6</v>
       </c>
       <c r="T28">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="U28">
         <v>1</v>
       </c>
       <c r="V28">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W28">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="X28">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29" spans="1:24">
@@ -2772,46 +2772,46 @@
         <v>51</v>
       </c>
       <c r="C29" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D29">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H29">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I29">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K29">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L29">
         <v>5</v>
       </c>
       <c r="M29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N29">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O29">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P29">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q29">
         <v>6</v>
@@ -2823,7 +2823,7 @@
         <v>6</v>
       </c>
       <c r="T29">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="U29">
         <v>2</v>
@@ -2832,10 +2832,10 @@
         <v>4</v>
       </c>
       <c r="W29">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="X29">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:24">
@@ -2846,10 +2846,10 @@
         <v>52</v>
       </c>
       <c r="C30" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30">
         <v>1</v>
@@ -2858,28 +2858,28 @@
         <v>1</v>
       </c>
       <c r="G30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H30">
         <v>1</v>
       </c>
       <c r="I30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L30">
         <v>6</v>
       </c>
       <c r="M30">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O30">
         <v>6</v>
@@ -2888,28 +2888,28 @@
         <v>6</v>
       </c>
       <c r="Q30">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R30">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S30">
         <v>6</v>
       </c>
       <c r="T30">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="U30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V30">
         <v>3</v>
       </c>
       <c r="W30">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="X30">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:24">
@@ -2920,70 +2920,70 @@
         <v>53</v>
       </c>
       <c r="C31" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D31">
         <v>2</v>
       </c>
       <c r="E31">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F31">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G31">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K31">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M31">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O31">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q31">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S31">
         <v>6</v>
       </c>
       <c r="T31">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="U31">
         <v>1</v>
       </c>
       <c r="V31">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W31">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="X31">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:24">
@@ -2994,70 +2994,70 @@
         <v>54</v>
       </c>
       <c r="C32" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K32">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L32">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M32">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N32">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O32">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="P32">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Q32">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R32">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="S32">
         <v>6</v>
       </c>
       <c r="T32">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="U32">
         <v>1</v>
       </c>
       <c r="V32">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W32">
         <v>17</v>
       </c>
       <c r="X32">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:24">
@@ -3068,10 +3068,10 @@
         <v>55</v>
       </c>
       <c r="C33" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D33">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E33">
         <v>3</v>
@@ -3080,31 +3080,31 @@
         <v>2</v>
       </c>
       <c r="G33">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I33">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J33">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K33">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L33">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M33">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N33">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P33">
         <v>5</v>
@@ -3113,25 +3113,25 @@
         <v>4</v>
       </c>
       <c r="R33">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S33">
         <v>6</v>
       </c>
       <c r="T33">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="U33">
         <v>1</v>
       </c>
       <c r="V33">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W33">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="X33">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:24">
@@ -3148,52 +3148,52 @@
         <v>2</v>
       </c>
       <c r="E34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F34">
         <v>2</v>
       </c>
       <c r="G34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I34">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M34">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P34">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Q34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S34">
         <v>6</v>
       </c>
       <c r="T34">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="U34">
         <v>1</v>
@@ -3202,7 +3202,7 @@
         <v>3</v>
       </c>
       <c r="W34">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="X34">
         <v>4</v>
@@ -3216,58 +3216,58 @@
         <v>57</v>
       </c>
       <c r="C35" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D35">
         <v>2</v>
       </c>
       <c r="E35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I35">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K35">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L35">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M35">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N35">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O35">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P35">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Q35">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="R35">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="S35">
         <v>6</v>
       </c>
       <c r="T35">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="U35">
         <v>1</v>
@@ -3276,7 +3276,7 @@
         <v>3</v>
       </c>
       <c r="W35">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X35">
         <v>5</v>
@@ -3293,43 +3293,43 @@
         <v>105</v>
       </c>
       <c r="D36">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E36">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G36">
         <v>3</v>
       </c>
       <c r="H36">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M36">
         <v>4</v>
       </c>
       <c r="N36">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O36">
         <v>4</v>
       </c>
       <c r="P36">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q36">
         <v>4</v>
@@ -3340,20 +3340,17 @@
       <c r="S36">
         <v>6</v>
       </c>
-      <c r="T36">
-        <v>39</v>
-      </c>
       <c r="U36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W36">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="X36">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:24">
@@ -3364,70 +3361,70 @@
         <v>59</v>
       </c>
       <c r="C37" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E37">
         <v>3</v>
       </c>
       <c r="F37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G37">
         <v>3</v>
       </c>
       <c r="H37">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J37">
         <v>3</v>
       </c>
       <c r="K37">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L37">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M37">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N37">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O37">
         <v>5</v>
       </c>
       <c r="P37">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q37">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R37">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S37">
         <v>6</v>
       </c>
       <c r="T37">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="U37">
         <v>1</v>
       </c>
       <c r="V37">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W37">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="X37">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:24">
@@ -3438,43 +3435,43 @@
         <v>60</v>
       </c>
       <c r="C38" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D38">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E38">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F38">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G38">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H38">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I38">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J38">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K38">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M38">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N38">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O38">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P38">
         <v>4</v>
@@ -3483,13 +3480,13 @@
         <v>4</v>
       </c>
       <c r="R38">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S38">
         <v>6</v>
       </c>
       <c r="T38">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="U38">
         <v>1</v>
@@ -3501,7 +3498,7 @@
         <v>11</v>
       </c>
       <c r="X38">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:24">
@@ -3512,58 +3509,58 @@
         <v>61</v>
       </c>
       <c r="C39" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D39">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F39">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G39">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H39">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I39">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J39">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M39">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N39">
         <v>5</v>
       </c>
       <c r="O39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P39">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q39">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R39">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S39">
         <v>6</v>
       </c>
       <c r="T39">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="U39">
         <v>1</v>
@@ -3572,10 +3569,10 @@
         <v>3</v>
       </c>
       <c r="W39">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="X39">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40" spans="1:24">
@@ -3589,13 +3586,13 @@
         <v>103</v>
       </c>
       <c r="D40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E40">
         <v>3</v>
       </c>
       <c r="F40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G40">
         <v>3</v>
@@ -3604,31 +3601,31 @@
         <v>4</v>
       </c>
       <c r="I40">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J40">
         <v>3</v>
       </c>
       <c r="K40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L40">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N40">
         <v>5</v>
       </c>
       <c r="O40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P40">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q40">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R40">
         <v>5</v>
@@ -3637,19 +3634,19 @@
         <v>6</v>
       </c>
       <c r="T40">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="U40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V40">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="W40">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="X40">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41" spans="1:24">
@@ -3660,34 +3657,34 @@
         <v>63</v>
       </c>
       <c r="C41" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D41">
         <v>4</v>
       </c>
       <c r="E41">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F41">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G41">
         <v>3</v>
       </c>
       <c r="H41">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I41">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J41">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K41">
         <v>5</v>
       </c>
       <c r="L41">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M41">
         <v>5</v>
@@ -3702,28 +3699,28 @@
         <v>4</v>
       </c>
       <c r="Q41">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R41">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S41">
         <v>6</v>
       </c>
       <c r="T41">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="U41">
         <v>1</v>
       </c>
       <c r="V41">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W41">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="X41">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42" spans="1:24">
@@ -3737,43 +3734,43 @@
         <v>105</v>
       </c>
       <c r="D42">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E42">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F42">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G42">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H42">
         <v>4</v>
       </c>
       <c r="I42">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J42">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K42">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L42">
         <v>5</v>
       </c>
       <c r="M42">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N42">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O42">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P42">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q42">
         <v>4</v>
@@ -3785,19 +3782,19 @@
         <v>6</v>
       </c>
       <c r="T42">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V42">
         <v>3</v>
       </c>
       <c r="W42">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="X42">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43" spans="1:24">
@@ -3808,58 +3805,58 @@
         <v>65</v>
       </c>
       <c r="C43" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D43">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E43">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F43">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G43">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H43">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I43">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J43">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K43">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L43">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M43">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N43">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P43">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q43">
         <v>5</v>
       </c>
       <c r="R43">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S43">
         <v>6</v>
       </c>
       <c r="T43">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="U43">
         <v>1</v>
@@ -3868,10 +3865,10 @@
         <v>4</v>
       </c>
       <c r="W43">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="X43">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44" spans="1:24">
@@ -3885,7 +3882,7 @@
         <v>105</v>
       </c>
       <c r="D44">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E44">
         <v>3</v>
@@ -3894,16 +3891,16 @@
         <v>4</v>
       </c>
       <c r="G44">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H44">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I44">
         <v>4</v>
       </c>
       <c r="J44">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K44">
         <v>5</v>
@@ -3912,26 +3909,29 @@
         <v>6</v>
       </c>
       <c r="M44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N44">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O44">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P44">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q44">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R44">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S44">
         <v>6</v>
       </c>
+      <c r="T44">
+        <v>36</v>
+      </c>
       <c r="U44">
         <v>1</v>
       </c>
@@ -3939,10 +3939,10 @@
         <v>3</v>
       </c>
       <c r="W44">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="X44">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:24">
@@ -3956,55 +3956,55 @@
         <v>105</v>
       </c>
       <c r="D45">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E45">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H45">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J45">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K45">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L45">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M45">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N45">
         <v>5</v>
       </c>
       <c r="O45">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P45">
         <v>5</v>
       </c>
       <c r="Q45">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R45">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S45">
         <v>6</v>
       </c>
       <c r="T45">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="U45">
         <v>1</v>
@@ -4012,8 +4012,8 @@
       <c r="V45">
         <v>3</v>
       </c>
-      <c r="X45">
-        <v>8</v>
+      <c r="W45">
+        <v>7</v>
       </c>
     </row>
     <row r="46" spans="1:24">
@@ -4024,7 +4024,7 @@
         <v>68</v>
       </c>
       <c r="C46" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D46">
         <v>1</v>
@@ -4033,10 +4033,10 @@
         <v>1</v>
       </c>
       <c r="F46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H46">
         <v>1</v>
@@ -4045,7 +4045,7 @@
         <v>1</v>
       </c>
       <c r="J46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K46">
         <v>7</v>
@@ -4054,7 +4054,7 @@
         <v>7</v>
       </c>
       <c r="M46">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N46">
         <v>7</v>
@@ -4066,28 +4066,28 @@
         <v>7</v>
       </c>
       <c r="Q46">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R46">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S46">
         <v>6</v>
       </c>
       <c r="T46">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="U46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V46">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="W46">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="X46">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:24">
@@ -4098,70 +4098,70 @@
         <v>69</v>
       </c>
       <c r="C47" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D47">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E47">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F47">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G47">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H47">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I47">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J47">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K47">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L47">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M47">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N47">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O47">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="P47">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Q47">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="R47">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="S47">
         <v>6</v>
       </c>
       <c r="T47">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="U47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V47">
         <v>3</v>
       </c>
       <c r="W47">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="X47">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48" spans="1:24">
@@ -4172,70 +4172,70 @@
         <v>70</v>
       </c>
       <c r="C48" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E48">
         <v>2</v>
       </c>
       <c r="F48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J48">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K48">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L48">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M48">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N48">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O48">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P48">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q48">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R48">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S48">
         <v>6</v>
       </c>
       <c r="T48">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="U48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V48">
         <v>4</v>
       </c>
       <c r="W48">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X48">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49" spans="1:24">
@@ -4246,58 +4246,58 @@
         <v>71</v>
       </c>
       <c r="C49" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D49">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E49">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G49">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H49">
         <v>2</v>
       </c>
       <c r="I49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J49">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K49">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L49">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M49">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N49">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O49">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P49">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Q49">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="R49">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="S49">
         <v>6</v>
       </c>
       <c r="T49">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="U49">
         <v>1</v>
@@ -4306,10 +4306,10 @@
         <v>3</v>
       </c>
       <c r="W49">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="X49">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50" spans="1:24">
@@ -4320,70 +4320,70 @@
         <v>72</v>
       </c>
       <c r="C50" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D50">
         <v>2</v>
       </c>
       <c r="E50">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F50">
         <v>2</v>
       </c>
       <c r="G50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H50">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I50">
         <v>3</v>
       </c>
       <c r="J50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K50">
         <v>5</v>
       </c>
       <c r="L50">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M50">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N50">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O50">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P50">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q50">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R50">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="S50">
         <v>6</v>
       </c>
       <c r="T50">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="U50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V50">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W50">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="X50">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51" spans="1:24">
@@ -4394,13 +4394,13 @@
         <v>73</v>
       </c>
       <c r="C51" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E51">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F51">
         <v>1</v>
@@ -4409,55 +4409,55 @@
         <v>3</v>
       </c>
       <c r="H51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L51">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O51">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P51">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q51">
         <v>4</v>
       </c>
       <c r="R51">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S51">
         <v>6</v>
       </c>
       <c r="T51">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="U51">
         <v>1</v>
       </c>
       <c r="V51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W51">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X51">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="52" spans="1:24">
@@ -4474,43 +4474,43 @@
         <v>2</v>
       </c>
       <c r="E52">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F52">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G52">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H52">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J52">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K52">
         <v>4</v>
       </c>
       <c r="L52">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M52">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N52">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O52">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P52">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q52">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R52">
         <v>4</v>
@@ -4519,19 +4519,19 @@
         <v>6</v>
       </c>
       <c r="T52">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="U52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V52">
         <v>2</v>
       </c>
       <c r="W52">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="X52">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53" spans="1:24">
@@ -4542,40 +4542,40 @@
         <v>75</v>
       </c>
       <c r="C53" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D53">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E53">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F53">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G53">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I53">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J53">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K53">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L53">
         <v>6</v>
       </c>
       <c r="M53">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N53">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O53">
         <v>6</v>
@@ -4587,13 +4587,13 @@
         <v>7</v>
       </c>
       <c r="R53">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S53">
         <v>6</v>
       </c>
       <c r="T53">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="U53">
         <v>1</v>
@@ -4602,10 +4602,10 @@
         <v>3</v>
       </c>
       <c r="W53">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="X53">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54" spans="1:24">
@@ -4619,25 +4619,25 @@
         <v>104</v>
       </c>
       <c r="D54">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E54">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F54">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G54">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H54">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I54">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J54">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K54">
         <v>5</v>
@@ -4646,19 +4646,19 @@
         <v>5</v>
       </c>
       <c r="M54">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N54">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O54">
         <v>5</v>
       </c>
       <c r="P54">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q54">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R54">
         <v>4</v>
@@ -4667,16 +4667,16 @@
         <v>6</v>
       </c>
       <c r="T54">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="U54">
         <v>2</v>
       </c>
       <c r="V54">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W54">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X54">
         <v>4</v>
@@ -4705,55 +4705,55 @@
         <v>2</v>
       </c>
       <c r="H55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I55">
         <v>2</v>
       </c>
       <c r="J55">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K55">
         <v>4</v>
       </c>
       <c r="L55">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M55">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N55">
         <v>5</v>
       </c>
       <c r="O55">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P55">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q55">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R55">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S55">
         <v>6</v>
       </c>
       <c r="T55">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="U55">
         <v>1</v>
       </c>
       <c r="V55">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W55">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X55">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56" spans="1:24">
@@ -4764,67 +4764,67 @@
         <v>78</v>
       </c>
       <c r="C56" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E56">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F56">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G56">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H56">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I56">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J56">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K56">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L56">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M56">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N56">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O56">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P56">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q56">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R56">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S56">
         <v>6</v>
       </c>
       <c r="T56">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="U56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V56">
         <v>3</v>
       </c>
       <c r="W56">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="X56">
         <v>6</v>
@@ -4841,7 +4841,7 @@
         <v>104</v>
       </c>
       <c r="D57">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E57">
         <v>2</v>
@@ -4850,19 +4850,19 @@
         <v>3</v>
       </c>
       <c r="G57">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I57">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J57">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K57">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L57">
         <v>5</v>
@@ -4874,7 +4874,7 @@
         <v>5</v>
       </c>
       <c r="O57">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P57">
         <v>5</v>
@@ -4883,25 +4883,25 @@
         <v>5</v>
       </c>
       <c r="R57">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S57">
         <v>6</v>
       </c>
       <c r="T57">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="U57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W57">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="X57">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="58" spans="1:24">
@@ -4915,37 +4915,37 @@
         <v>103</v>
       </c>
       <c r="D58">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E58">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F58">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G58">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H58">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I58">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J58">
         <v>3</v>
       </c>
       <c r="K58">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L58">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M58">
         <v>5</v>
       </c>
       <c r="N58">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O58">
         <v>5</v>
@@ -4954,28 +4954,28 @@
         <v>5</v>
       </c>
       <c r="Q58">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R58">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S58">
         <v>6</v>
       </c>
       <c r="T58">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="U58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V58">
         <v>4</v>
       </c>
       <c r="W58">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="X58">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59" spans="1:24">
@@ -5001,7 +5001,7 @@
         <v>1</v>
       </c>
       <c r="H59">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I59">
         <v>1</v>
@@ -5010,25 +5010,25 @@
         <v>1</v>
       </c>
       <c r="K59">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L59">
         <v>5</v>
       </c>
       <c r="M59">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N59">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O59">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P59">
         <v>5</v>
       </c>
       <c r="Q59">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R59">
         <v>5</v>
@@ -5037,7 +5037,7 @@
         <v>6</v>
       </c>
       <c r="T59">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="U59">
         <v>1</v>
@@ -5046,10 +5046,10 @@
         <v>2</v>
       </c>
       <c r="W59">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="X59">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60" spans="1:24">
@@ -5060,28 +5060,28 @@
         <v>82</v>
       </c>
       <c r="C60" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E60">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G60">
         <v>3</v>
       </c>
       <c r="H60">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I60">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K60">
         <v>6</v>
@@ -5093,10 +5093,10 @@
         <v>5</v>
       </c>
       <c r="N60">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O60">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P60">
         <v>5</v>
@@ -5111,19 +5111,19 @@
         <v>6</v>
       </c>
       <c r="T60">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="U60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V60">
         <v>4</v>
       </c>
       <c r="W60">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="X60">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="61" spans="1:24">
@@ -5134,70 +5134,70 @@
         <v>83</v>
       </c>
       <c r="C61" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E61">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F61">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G61">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J61">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K61">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L61">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M61">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N61">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O61">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P61">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q61">
         <v>4</v>
       </c>
       <c r="R61">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S61">
         <v>6</v>
       </c>
       <c r="T61">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="U61">
         <v>2</v>
       </c>
       <c r="V61">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W61">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X61">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="62" spans="1:24">
@@ -5211,40 +5211,40 @@
         <v>105</v>
       </c>
       <c r="D62">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E62">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F62">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G62">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H62">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I62">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J62">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K62">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L62">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M62">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N62">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O62">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P62">
         <v>4</v>
@@ -5259,19 +5259,19 @@
         <v>6</v>
       </c>
       <c r="T62">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="U62">
         <v>1</v>
       </c>
       <c r="V62">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W62">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="X62">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63" spans="1:24">
@@ -5285,67 +5285,67 @@
         <v>105</v>
       </c>
       <c r="D63">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E63">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F63">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G63">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H63">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I63">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J63">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K63">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L63">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M63">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N63">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O63">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P63">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Q63">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R63">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S63">
         <v>6</v>
       </c>
       <c r="T63">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="U63">
         <v>1</v>
       </c>
       <c r="V63">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W63">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="X63">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64" spans="1:24">
@@ -5356,52 +5356,52 @@
         <v>86</v>
       </c>
       <c r="C64" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D64">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E64">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H64">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I64">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K64">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L64">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M64">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N64">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O64">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P64">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q64">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="R64">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="S64">
         <v>6</v>
@@ -5410,13 +5410,13 @@
         <v>33</v>
       </c>
       <c r="U64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V64">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="W64">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="X64">
         <v>5</v>
@@ -5433,25 +5433,25 @@
         <v>103</v>
       </c>
       <c r="D65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E65">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F65">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G65">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H65">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J65">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K65">
         <v>5</v>
@@ -5460,37 +5460,37 @@
         <v>6</v>
       </c>
       <c r="M65">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N65">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O65">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P65">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q65">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R65">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S65">
         <v>6</v>
       </c>
       <c r="T65">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="U65">
         <v>1</v>
       </c>
       <c r="V65">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W65">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="X65">
         <v>4</v>
@@ -5504,31 +5504,31 @@
         <v>88</v>
       </c>
       <c r="C66" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D66">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G66">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I66">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K66">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L66">
         <v>6</v>
@@ -5537,16 +5537,16 @@
         <v>6</v>
       </c>
       <c r="N66">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O66">
         <v>6</v>
       </c>
       <c r="P66">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q66">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R66">
         <v>6</v>
@@ -5555,19 +5555,19 @@
         <v>6</v>
       </c>
       <c r="T66">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="U66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V66">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W66">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="X66">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="67" spans="1:24">
@@ -5578,70 +5578,70 @@
         <v>89</v>
       </c>
       <c r="C67" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D67">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F67">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G67">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I67">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J67">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K67">
         <v>6</v>
       </c>
       <c r="L67">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M67">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N67">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O67">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P67">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q67">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R67">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S67">
         <v>6</v>
       </c>
       <c r="T67">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="U67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V67">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W67">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="X67">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68" spans="1:24">
@@ -5652,22 +5652,22 @@
         <v>90</v>
       </c>
       <c r="C68" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D68">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E68">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F68">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G68">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H68">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I68">
         <v>3</v>
@@ -5679,19 +5679,19 @@
         <v>6</v>
       </c>
       <c r="L68">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M68">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N68">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O68">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P68">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q68">
         <v>6</v>
@@ -5703,19 +5703,16 @@
         <v>6</v>
       </c>
       <c r="T68">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="U68">
         <v>1</v>
       </c>
       <c r="V68">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W68">
-        <v>25</v>
-      </c>
-      <c r="X68">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="69" spans="1:24">
@@ -5726,49 +5723,49 @@
         <v>91</v>
       </c>
       <c r="C69" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D69">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E69">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F69">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G69">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H69">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I69">
         <v>2</v>
       </c>
       <c r="J69">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K69">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L69">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M69">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N69">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O69">
         <v>5</v>
       </c>
       <c r="P69">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q69">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R69">
         <v>4</v>
@@ -5777,19 +5774,19 @@
         <v>6</v>
       </c>
       <c r="T69">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="U69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V69">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W69">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="X69">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="70" spans="1:24">
@@ -5803,10 +5800,10 @@
         <v>103</v>
       </c>
       <c r="D70">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E70">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F70">
         <v>3</v>
@@ -5815,16 +5812,16 @@
         <v>3</v>
       </c>
       <c r="H70">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I70">
         <v>3</v>
       </c>
       <c r="J70">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K70">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L70">
         <v>5</v>
@@ -5833,37 +5830,37 @@
         <v>5</v>
       </c>
       <c r="N70">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O70">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P70">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q70">
         <v>5</v>
       </c>
       <c r="R70">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S70">
         <v>6</v>
       </c>
       <c r="T70">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="U70">
         <v>1</v>
       </c>
       <c r="V70">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W70">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="X70">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71" spans="1:24">
@@ -5874,46 +5871,46 @@
         <v>93</v>
       </c>
       <c r="C71" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D71">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E71">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F71">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G71">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H71">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I71">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J71">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K71">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L71">
         <v>6</v>
       </c>
       <c r="M71">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N71">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O71">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P71">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q71">
         <v>6</v>
@@ -5925,7 +5922,7 @@
         <v>6</v>
       </c>
       <c r="T71">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="U71">
         <v>2</v>
@@ -5934,10 +5931,10 @@
         <v>3</v>
       </c>
       <c r="W71">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="X71">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="72" spans="1:24">
@@ -5951,67 +5948,67 @@
         <v>105</v>
       </c>
       <c r="D72">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E72">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F72">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G72">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H72">
         <v>3</v>
       </c>
       <c r="I72">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J72">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K72">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L72">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M72">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N72">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O72">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P72">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q72">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R72">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S72">
         <v>6</v>
       </c>
       <c r="T72">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="U72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V72">
         <v>3</v>
       </c>
       <c r="W72">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="X72">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="73" spans="1:24">
@@ -6025,16 +6022,16 @@
         <v>103</v>
       </c>
       <c r="D73">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F73">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H73">
         <v>1</v>
@@ -6043,40 +6040,40 @@
         <v>1</v>
       </c>
       <c r="J73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K73">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L73">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M73">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N73">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O73">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P73">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Q73">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R73">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="S73">
         <v>6</v>
       </c>
       <c r="T73">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="U73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V73">
         <v>4</v>
@@ -6085,7 +6082,7 @@
         <v>16</v>
       </c>
       <c r="X73">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74" spans="1:24">
@@ -6096,22 +6093,22 @@
         <v>96</v>
       </c>
       <c r="C74" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E74">
         <v>4</v>
       </c>
       <c r="F74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H74">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I74">
         <v>4</v>
@@ -6120,25 +6117,25 @@
         <v>3</v>
       </c>
       <c r="K74">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L74">
         <v>4</v>
       </c>
       <c r="M74">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N74">
         <v>4</v>
       </c>
       <c r="O74">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q74">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R74">
         <v>4</v>
@@ -6147,19 +6144,19 @@
         <v>6</v>
       </c>
       <c r="T74">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="U74">
         <v>1</v>
       </c>
       <c r="V74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W74">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="X74">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="75" spans="1:24">
@@ -6173,64 +6170,64 @@
         <v>103</v>
       </c>
       <c r="D75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E75">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F75">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H75">
         <v>2</v>
       </c>
       <c r="I75">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J75">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K75">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L75">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M75">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N75">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O75">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P75">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q75">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R75">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S75">
         <v>6</v>
       </c>
       <c r="T75">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="U75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V75">
         <v>4</v>
       </c>
       <c r="W75">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="X75">
         <v>5</v>
@@ -6244,40 +6241,40 @@
         <v>98</v>
       </c>
       <c r="C76" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D76">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E76">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F76">
         <v>2</v>
       </c>
       <c r="G76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J76">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K76">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L76">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M76">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N76">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O76">
         <v>4</v>
@@ -6286,25 +6283,25 @@
         <v>5</v>
       </c>
       <c r="Q76">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R76">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S76">
         <v>6</v>
       </c>
       <c r="T76">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="U76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V76">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W76">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="X76">
         <v>6</v>
@@ -6321,67 +6318,67 @@
         <v>103</v>
       </c>
       <c r="D77">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E77">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G77">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K77">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L77">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M77">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N77">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O77">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P77">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q77">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R77">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="S77">
         <v>6</v>
       </c>
       <c r="T77">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="U77">
         <v>2</v>
       </c>
       <c r="V77">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W77">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="X77">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78" spans="1:24">
@@ -6392,70 +6389,70 @@
         <v>100</v>
       </c>
       <c r="C78" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D78">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E78">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F78">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G78">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H78">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I78">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J78">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K78">
         <v>3</v>
       </c>
       <c r="L78">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N78">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O78">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P78">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q78">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R78">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S78">
         <v>6</v>
       </c>
       <c r="T78">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="U78">
         <v>2</v>
       </c>
       <c r="V78">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W78">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="X78">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79" spans="1:24">
@@ -6466,28 +6463,28 @@
         <v>101</v>
       </c>
       <c r="C79" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D79">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E79">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F79">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G79">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I79">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J79">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K79">
         <v>4</v>
@@ -6496,37 +6493,37 @@
         <v>4</v>
       </c>
       <c r="M79">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N79">
         <v>5</v>
       </c>
       <c r="O79">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P79">
         <v>4</v>
       </c>
       <c r="Q79">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R79">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S79">
         <v>6</v>
       </c>
       <c r="T79">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="U79">
         <v>1</v>
       </c>
       <c r="V79">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W79">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="X79">
         <v>6</v>
@@ -6540,49 +6537,49 @@
         <v>102</v>
       </c>
       <c r="C80" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D80">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E80">
         <v>3</v>
       </c>
       <c r="F80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G80">
         <v>3</v>
       </c>
       <c r="H80">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I80">
         <v>3</v>
       </c>
       <c r="J80">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K80">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L80">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M80">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N80">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O80">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P80">
         <v>4</v>
       </c>
       <c r="Q80">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R80">
         <v>5</v>
@@ -6591,19 +6588,19 @@
         <v>6</v>
       </c>
       <c r="T80">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V80">
         <v>3</v>
       </c>
       <c r="W80">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X80">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/data/T3_leader_cleaned.xlsx
+++ b/data/T3_leader_cleaned.xlsx
@@ -100,229 +100,229 @@
     <t>B_L10</t>
   </si>
   <si>
+    <t>B_L06</t>
+  </si>
+  <si>
+    <t>C_L19</t>
+  </si>
+  <si>
+    <t>C_L25</t>
+  </si>
+  <si>
+    <t>A_L11</t>
+  </si>
+  <si>
+    <t>A_L10</t>
+  </si>
+  <si>
+    <t>B_L23</t>
+  </si>
+  <si>
+    <t>B_L21</t>
+  </si>
+  <si>
+    <t>C_L12</t>
+  </si>
+  <si>
+    <t>B_L29</t>
+  </si>
+  <si>
+    <t>C_L01</t>
+  </si>
+  <si>
+    <t>B_L08</t>
+  </si>
+  <si>
+    <t>B_L09</t>
+  </si>
+  <si>
+    <t>A_L26</t>
+  </si>
+  <si>
+    <t>C_L05</t>
+  </si>
+  <si>
+    <t>A_L15</t>
+  </si>
+  <si>
+    <t>C_L08</t>
+  </si>
+  <si>
     <t>B_L05</t>
   </si>
   <si>
+    <t>C_L14</t>
+  </si>
+  <si>
+    <t>C_L21</t>
+  </si>
+  <si>
+    <t>A_L28</t>
+  </si>
+  <si>
+    <t>C_L18</t>
+  </si>
+  <si>
+    <t>C_L07</t>
+  </si>
+  <si>
+    <t>A_L18</t>
+  </si>
+  <si>
+    <t>B_L01</t>
+  </si>
+  <si>
+    <t>A_L06</t>
+  </si>
+  <si>
+    <t>C_L24</t>
+  </si>
+  <si>
+    <t>A_L13</t>
+  </si>
+  <si>
+    <t>C_L29</t>
+  </si>
+  <si>
+    <t>B_L25</t>
+  </si>
+  <si>
+    <t>C_L11</t>
+  </si>
+  <si>
+    <t>B_L24</t>
+  </si>
+  <si>
+    <t>B_L26</t>
+  </si>
+  <si>
+    <t>C_L03</t>
+  </si>
+  <si>
+    <t>A_L20</t>
+  </si>
+  <si>
+    <t>C_L30</t>
+  </si>
+  <si>
+    <t>C_L28</t>
+  </si>
+  <si>
+    <t>B_L02</t>
+  </si>
+  <si>
+    <t>C_L17</t>
+  </si>
+  <si>
+    <t>C_L22</t>
+  </si>
+  <si>
+    <t>B_L04</t>
+  </si>
+  <si>
     <t>C_L20</t>
   </si>
   <si>
-    <t>C_L26</t>
-  </si>
-  <si>
-    <t>A_L11</t>
-  </si>
-  <si>
-    <t>A_L10</t>
-  </si>
-  <si>
-    <t>B_L25</t>
-  </si>
-  <si>
-    <t>B_L23</t>
+    <t>B_L11</t>
+  </si>
+  <si>
+    <t>A_L17</t>
+  </si>
+  <si>
+    <t>C_L02</t>
+  </si>
+  <si>
+    <t>B_L19</t>
+  </si>
+  <si>
+    <t>A_L09</t>
+  </si>
+  <si>
+    <t>B_L18</t>
+  </si>
+  <si>
+    <t>B_L03</t>
+  </si>
+  <si>
+    <t>B_L07</t>
+  </si>
+  <si>
+    <t>B_L22</t>
+  </si>
+  <si>
+    <t>B_L15</t>
+  </si>
+  <si>
+    <t>A_L07</t>
+  </si>
+  <si>
+    <t>C_L16</t>
+  </si>
+  <si>
+    <t>B_L27</t>
+  </si>
+  <si>
+    <t>A_L03</t>
+  </si>
+  <si>
+    <t>C_L10</t>
   </si>
   <si>
     <t>C_L13</t>
   </si>
   <si>
-    <t>C_L02</t>
-  </si>
-  <si>
-    <t>C_L03</t>
-  </si>
-  <si>
-    <t>B_L08</t>
-  </si>
-  <si>
-    <t>B_L09</t>
+    <t>A_L04</t>
   </si>
   <si>
     <t>A_L25</t>
   </si>
   <si>
-    <t>C_L08</t>
-  </si>
-  <si>
-    <t>A_L15</t>
-  </si>
-  <si>
-    <t>C_L10</t>
-  </si>
-  <si>
-    <t>B_L04</t>
-  </si>
-  <si>
-    <t>C_L16</t>
-  </si>
-  <si>
-    <t>C_L22</t>
+    <t>A_L29</t>
+  </si>
+  <si>
+    <t>A_L16</t>
+  </si>
+  <si>
+    <t>B_L14</t>
+  </si>
+  <si>
+    <t>B_L20</t>
+  </si>
+  <si>
+    <t>A_L22</t>
+  </si>
+  <si>
+    <t>B_L12</t>
+  </si>
+  <si>
+    <t>C_L27</t>
+  </si>
+  <si>
+    <t>A_L12</t>
+  </si>
+  <si>
+    <t>B_L16</t>
+  </si>
+  <si>
+    <t>A_L21</t>
+  </si>
+  <si>
+    <t>A_L24</t>
+  </si>
+  <si>
+    <t>A_L02</t>
+  </si>
+  <si>
+    <t>C_L23</t>
+  </si>
+  <si>
+    <t>C_L04</t>
+  </si>
+  <si>
+    <t>A_L05</t>
   </si>
   <si>
     <t>A_L27</t>
-  </si>
-  <si>
-    <t>C_L19</t>
-  </si>
-  <si>
-    <t>C_L09</t>
-  </si>
-  <si>
-    <t>A_L18</t>
-  </si>
-  <si>
-    <t>A_L29</t>
-  </si>
-  <si>
-    <t>A_L26</t>
-  </si>
-  <si>
-    <t>A_L06</t>
-  </si>
-  <si>
-    <t>C_L25</t>
-  </si>
-  <si>
-    <t>A_L13</t>
-  </si>
-  <si>
-    <t>C_L29</t>
-  </si>
-  <si>
-    <t>B_L29</t>
-  </si>
-  <si>
-    <t>C_L12</t>
-  </si>
-  <si>
-    <t>B_L26</t>
-  </si>
-  <si>
-    <t>B_L30</t>
-  </si>
-  <si>
-    <t>C_L05</t>
-  </si>
-  <si>
-    <t>A_L20</t>
-  </si>
-  <si>
-    <t>C_L30</t>
-  </si>
-  <si>
-    <t>C_L28</t>
-  </si>
-  <si>
-    <t>B_L01</t>
-  </si>
-  <si>
-    <t>C_L18</t>
-  </si>
-  <si>
-    <t>C_L23</t>
-  </si>
-  <si>
-    <t>B_L03</t>
-  </si>
-  <si>
-    <t>C_L21</t>
-  </si>
-  <si>
-    <t>B_L11</t>
-  </si>
-  <si>
-    <t>A_L17</t>
-  </si>
-  <si>
-    <t>C_L04</t>
-  </si>
-  <si>
-    <t>B_L20</t>
-  </si>
-  <si>
-    <t>A_L09</t>
-  </si>
-  <si>
-    <t>B_L19</t>
-  </si>
-  <si>
-    <t>B_L02</t>
-  </si>
-  <si>
-    <t>B_L06</t>
-  </si>
-  <si>
-    <t>B_L24</t>
-  </si>
-  <si>
-    <t>B_L16</t>
-  </si>
-  <si>
-    <t>A_L07</t>
-  </si>
-  <si>
-    <t>C_L17</t>
-  </si>
-  <si>
-    <t>C_L01</t>
-  </si>
-  <si>
-    <t>A_L02</t>
-  </si>
-  <si>
-    <t>C_L11</t>
-  </si>
-  <si>
-    <t>C_L14</t>
-  </si>
-  <si>
-    <t>A_L03</t>
-  </si>
-  <si>
-    <t>A_L24</t>
-  </si>
-  <si>
-    <t>A_L28</t>
-  </si>
-  <si>
-    <t>A_L16</t>
-  </si>
-  <si>
-    <t>B_L14</t>
-  </si>
-  <si>
-    <t>B_L22</t>
-  </si>
-  <si>
-    <t>A_L22</t>
-  </si>
-  <si>
-    <t>B_L12</t>
-  </si>
-  <si>
-    <t>C_L27</t>
-  </si>
-  <si>
-    <t>A_L12</t>
-  </si>
-  <si>
-    <t>B_L18</t>
-  </si>
-  <si>
-    <t>A_L21</t>
-  </si>
-  <si>
-    <t>A_L23</t>
-  </si>
-  <si>
-    <t>A_L01</t>
-  </si>
-  <si>
-    <t>C_L24</t>
-  </si>
-  <si>
-    <t>C_L06</t>
-  </si>
-  <si>
-    <t>A_L05</t>
   </si>
   <si>
     <t>A</t>
@@ -777,34 +777,34 @@
         <v>103</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K2">
         <v>6</v>
       </c>
       <c r="L2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N2">
         <v>5</v>
@@ -813,31 +813,31 @@
         <v>4</v>
       </c>
       <c r="P2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q2">
         <v>5</v>
       </c>
       <c r="R2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S2">
         <v>6</v>
       </c>
       <c r="T2">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="U2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="X2">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:24">
@@ -851,67 +851,67 @@
         <v>103</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L3">
         <v>4</v>
       </c>
       <c r="M3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="S3">
         <v>6</v>
       </c>
       <c r="T3">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="U3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W3">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="X3">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:24">
@@ -925,31 +925,31 @@
         <v>103</v>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M4">
         <v>6</v>
@@ -958,7 +958,7 @@
         <v>5</v>
       </c>
       <c r="O4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P4">
         <v>5</v>
@@ -973,16 +973,16 @@
         <v>6</v>
       </c>
       <c r="T4">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="U4">
         <v>1</v>
       </c>
       <c r="V4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="X4">
         <v>7</v>
@@ -999,13 +999,13 @@
         <v>104</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G5">
         <v>4</v>
@@ -1017,7 +1017,7 @@
         <v>4</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K5">
         <v>6</v>
@@ -1032,34 +1032,34 @@
         <v>7</v>
       </c>
       <c r="O5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S5">
         <v>6</v>
       </c>
       <c r="T5">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="U5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V5">
         <v>3</v>
       </c>
       <c r="W5">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="X5">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:24">
@@ -1079,7 +1079,7 @@
         <v>1</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -1088,52 +1088,52 @@
         <v>1</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L6">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N6">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O6">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="P6">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Q6">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R6">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="S6">
         <v>6</v>
       </c>
       <c r="T6">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="U6">
         <v>1</v>
       </c>
       <c r="V6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W6">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="X6">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:24">
@@ -1150,52 +1150,52 @@
         <v>2</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7">
         <v>1</v>
       </c>
       <c r="J7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K7">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S7">
         <v>6</v>
       </c>
       <c r="T7">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="U7">
         <v>1</v>
@@ -1204,7 +1204,7 @@
         <v>3</v>
       </c>
       <c r="W7">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="X7">
         <v>5</v>
@@ -1224,64 +1224,64 @@
         <v>4</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F8">
         <v>4</v>
       </c>
       <c r="G8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I8">
         <v>5</v>
       </c>
       <c r="J8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q8">
         <v>3</v>
       </c>
       <c r="R8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S8">
         <v>6</v>
       </c>
       <c r="T8">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="U8">
         <v>1</v>
       </c>
       <c r="V8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W8">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="X8">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:24">
@@ -1295,31 +1295,31 @@
         <v>103</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M9">
         <v>5</v>
@@ -1328,7 +1328,7 @@
         <v>5</v>
       </c>
       <c r="O9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P9">
         <v>5</v>
@@ -1337,7 +1337,7 @@
         <v>5</v>
       </c>
       <c r="R9">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="S9">
         <v>6</v>
@@ -1352,10 +1352,10 @@
         <v>4</v>
       </c>
       <c r="W9">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X9">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:24">
@@ -1369,34 +1369,34 @@
         <v>103</v>
       </c>
       <c r="D10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N10">
         <v>4</v>
@@ -1408,28 +1408,28 @@
         <v>5</v>
       </c>
       <c r="Q10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R10">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S10">
         <v>6</v>
       </c>
       <c r="T10">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="U10">
         <v>1</v>
       </c>
       <c r="V10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W10">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="X10">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:24">
@@ -1443,67 +1443,67 @@
         <v>104</v>
       </c>
       <c r="D11">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H11">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K11">
         <v>4</v>
       </c>
       <c r="L11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N11">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q11">
         <v>4</v>
       </c>
       <c r="R11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S11">
         <v>6</v>
       </c>
       <c r="T11">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="U11">
         <v>1</v>
       </c>
       <c r="V11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W11">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="X11">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:24">
@@ -1517,67 +1517,67 @@
         <v>104</v>
       </c>
       <c r="D12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E12">
         <v>3</v>
       </c>
       <c r="F12">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H12">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N12">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P12">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R12">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S12">
         <v>6</v>
       </c>
       <c r="T12">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="U12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W12">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="X12">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:24">
@@ -1591,67 +1591,67 @@
         <v>105</v>
       </c>
       <c r="D13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F13">
         <v>2</v>
       </c>
       <c r="G13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H13">
         <v>3</v>
       </c>
       <c r="I13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K13">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L13">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M13">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N13">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O13">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P13">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q13">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R13">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S13">
         <v>6</v>
       </c>
       <c r="T13">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="U13">
         <v>2</v>
       </c>
       <c r="V13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W13">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="X13">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:24">
@@ -1662,70 +1662,70 @@
         <v>36</v>
       </c>
       <c r="C14" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D14">
         <v>3</v>
       </c>
       <c r="E14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G14">
         <v>3</v>
       </c>
       <c r="H14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R14">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S14">
         <v>6</v>
       </c>
       <c r="T14">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="U14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V14">
         <v>2</v>
       </c>
       <c r="W14">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="X14">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:24">
@@ -1739,34 +1739,34 @@
         <v>105</v>
       </c>
       <c r="D15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K15">
         <v>5</v>
       </c>
       <c r="L15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N15">
         <v>5</v>
@@ -1778,28 +1778,28 @@
         <v>6</v>
       </c>
       <c r="Q15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S15">
         <v>6</v>
       </c>
       <c r="T15">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="U15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W15">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="X15">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:24">
@@ -1813,25 +1813,25 @@
         <v>104</v>
       </c>
       <c r="D16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I16">
         <v>1</v>
       </c>
       <c r="J16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K16">
         <v>5</v>
@@ -1843,37 +1843,37 @@
         <v>4</v>
       </c>
       <c r="N16">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O16">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P16">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q16">
         <v>5</v>
       </c>
       <c r="R16">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S16">
         <v>6</v>
       </c>
       <c r="T16">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="U16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V16">
         <v>3</v>
       </c>
       <c r="W16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X16">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:24">
@@ -1887,67 +1887,67 @@
         <v>104</v>
       </c>
       <c r="D17">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F17">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G17">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H17">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K17">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L17">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M17">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q17">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R17">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S17">
         <v>6</v>
       </c>
       <c r="T17">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="U17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W17">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="X17">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:24">
@@ -1961,46 +1961,46 @@
         <v>103</v>
       </c>
       <c r="D18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K18">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M18">
         <v>5</v>
       </c>
       <c r="N18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P18">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R18">
         <v>5</v>
@@ -2009,19 +2009,19 @@
         <v>6</v>
       </c>
       <c r="T18">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="U18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W18">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="X18">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:24">
@@ -2038,7 +2038,7 @@
         <v>2</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F19">
         <v>2</v>
@@ -2050,19 +2050,19 @@
         <v>2</v>
       </c>
       <c r="I19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L19">
         <v>4</v>
       </c>
       <c r="M19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N19">
         <v>4</v>
@@ -2071,31 +2071,31 @@
         <v>4</v>
       </c>
       <c r="P19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S19">
         <v>6</v>
       </c>
       <c r="T19">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="U19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W19">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="X19">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:24">
@@ -2109,64 +2109,64 @@
         <v>103</v>
       </c>
       <c r="D20">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E20">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F20">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G20">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H20">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I20">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J20">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K20">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L20">
         <v>3</v>
       </c>
       <c r="M20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P20">
         <v>3</v>
       </c>
       <c r="Q20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S20">
         <v>6</v>
       </c>
       <c r="T20">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="U20">
         <v>1</v>
       </c>
       <c r="V20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W20">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X20">
         <v>5</v>
@@ -2183,19 +2183,19 @@
         <v>105</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F21">
         <v>2</v>
       </c>
       <c r="G21">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I21">
         <v>3</v>
@@ -2207,7 +2207,7 @@
         <v>6</v>
       </c>
       <c r="L21">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M21">
         <v>5</v>
@@ -2216,13 +2216,13 @@
         <v>5</v>
       </c>
       <c r="O21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P21">
         <v>5</v>
       </c>
       <c r="Q21">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R21">
         <v>5</v>
@@ -2234,16 +2234,13 @@
         <v>46</v>
       </c>
       <c r="U21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W21">
         <v>17</v>
-      </c>
-      <c r="X21">
-        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:24">
@@ -2257,55 +2254,55 @@
         <v>104</v>
       </c>
       <c r="D22">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G22">
         <v>3</v>
       </c>
       <c r="H22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I22">
         <v>2</v>
       </c>
       <c r="J22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K22">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L22">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M22">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N22">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O22">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P22">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q22">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R22">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S22">
         <v>6</v>
       </c>
       <c r="T22">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="U22">
         <v>1</v>
@@ -2314,10 +2311,10 @@
         <v>3</v>
       </c>
       <c r="W22">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="X22">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:24">
@@ -2331,67 +2328,67 @@
         <v>105</v>
       </c>
       <c r="D23">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F23">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G23">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H23">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K23">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L23">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M23">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N23">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O23">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P23">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q23">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R23">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S23">
         <v>6</v>
       </c>
       <c r="T23">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="U23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W23">
         <v>1</v>
       </c>
       <c r="X23">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:24">
@@ -2408,19 +2405,19 @@
         <v>3</v>
       </c>
       <c r="E24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H24">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J24">
         <v>2</v>
@@ -2435,37 +2432,37 @@
         <v>4</v>
       </c>
       <c r="N24">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O24">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P24">
         <v>4</v>
       </c>
       <c r="Q24">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R24">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S24">
         <v>6</v>
       </c>
       <c r="T24">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="U24">
         <v>2</v>
       </c>
       <c r="V24">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W24">
         <v>1</v>
       </c>
       <c r="X24">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:24">
@@ -2479,34 +2476,34 @@
         <v>103</v>
       </c>
       <c r="D25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G25">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H25">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K25">
         <v>6</v>
       </c>
       <c r="L25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M25">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N25">
         <v>5</v>
@@ -2518,7 +2515,7 @@
         <v>5</v>
       </c>
       <c r="Q25">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R25">
         <v>6</v>
@@ -2527,19 +2524,19 @@
         <v>6</v>
       </c>
       <c r="T25">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U25">
         <v>1</v>
       </c>
       <c r="V25">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W25">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="X25">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:24">
@@ -2553,46 +2550,46 @@
         <v>105</v>
       </c>
       <c r="D26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E26">
         <v>3</v>
       </c>
       <c r="F26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H26">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K26">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L26">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R26">
         <v>5</v>
@@ -2601,19 +2598,19 @@
         <v>6</v>
       </c>
       <c r="T26">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="U26">
         <v>1</v>
       </c>
       <c r="V26">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W26">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="X26">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:24">
@@ -2627,37 +2624,37 @@
         <v>105</v>
       </c>
       <c r="D27">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E27">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G27">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H27">
         <v>3</v>
       </c>
       <c r="I27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J27">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K27">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L27">
         <v>3</v>
       </c>
       <c r="M27">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N27">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O27">
         <v>3</v>
@@ -2666,28 +2663,28 @@
         <v>3</v>
       </c>
       <c r="Q27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S27">
         <v>6</v>
       </c>
       <c r="T27">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="U27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V27">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W27">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="X27">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:24">
@@ -2701,67 +2698,67 @@
         <v>103</v>
       </c>
       <c r="D28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H28">
         <v>1</v>
       </c>
       <c r="I28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O28">
         <v>4</v>
       </c>
       <c r="P28">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q28">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R28">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S28">
         <v>6</v>
       </c>
       <c r="T28">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="U28">
         <v>1</v>
       </c>
       <c r="V28">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W28">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="X28">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:24">
@@ -2772,13 +2769,13 @@
         <v>51</v>
       </c>
       <c r="C29" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D29">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E29">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F29">
         <v>3</v>
@@ -2787,34 +2784,34 @@
         <v>3</v>
       </c>
       <c r="H29">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I29">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K29">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L29">
         <v>5</v>
       </c>
       <c r="M29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O29">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P29">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R29">
         <v>6</v>
@@ -2826,16 +2823,16 @@
         <v>40</v>
       </c>
       <c r="U29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V29">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W29">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X29">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:24">
@@ -2849,7 +2846,7 @@
         <v>103</v>
       </c>
       <c r="D30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E30">
         <v>1</v>
@@ -2858,58 +2855,58 @@
         <v>1</v>
       </c>
       <c r="G30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H30">
         <v>1</v>
       </c>
       <c r="I30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L30">
         <v>6</v>
       </c>
       <c r="M30">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R30">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="S30">
         <v>6</v>
       </c>
       <c r="T30">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="U30">
         <v>1</v>
       </c>
       <c r="V30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W30">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="X30">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31" spans="1:24">
@@ -2920,67 +2917,67 @@
         <v>53</v>
       </c>
       <c r="C31" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D31">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F31">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G31">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H31">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I31">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J31">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K31">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L31">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M31">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="N31">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O31">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P31">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q31">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="R31">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="S31">
         <v>6</v>
       </c>
       <c r="T31">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="U31">
         <v>1</v>
       </c>
       <c r="V31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W31">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="X31">
         <v>7</v>
@@ -2994,70 +2991,70 @@
         <v>54</v>
       </c>
       <c r="C32" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E32">
         <v>2</v>
       </c>
       <c r="F32">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J32">
         <v>2</v>
       </c>
       <c r="K32">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N32">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O32">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P32">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q32">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R32">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S32">
         <v>6</v>
       </c>
       <c r="T32">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="U32">
         <v>1</v>
       </c>
       <c r="V32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W32">
         <v>17</v>
       </c>
       <c r="X32">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:24">
@@ -3068,19 +3065,19 @@
         <v>55</v>
       </c>
       <c r="C33" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33">
         <v>3</v>
       </c>
       <c r="F33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H33">
         <v>2</v>
@@ -3089,22 +3086,22 @@
         <v>1</v>
       </c>
       <c r="J33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K33">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L33">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M33">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N33">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P33">
         <v>5</v>
@@ -3113,22 +3110,22 @@
         <v>4</v>
       </c>
       <c r="R33">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S33">
         <v>6</v>
       </c>
       <c r="T33">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="U33">
         <v>1</v>
       </c>
       <c r="V33">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W33">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="X33">
         <v>5</v>
@@ -3142,58 +3139,58 @@
         <v>56</v>
       </c>
       <c r="C34" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E34">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G34">
         <v>1</v>
       </c>
       <c r="H34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I34">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J34">
         <v>2</v>
       </c>
       <c r="K34">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L34">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M34">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N34">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O34">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="P34">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R34">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S34">
         <v>6</v>
       </c>
       <c r="T34">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="U34">
         <v>1</v>
@@ -3202,10 +3199,10 @@
         <v>3</v>
       </c>
       <c r="W34">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X34">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:24">
@@ -3216,19 +3213,19 @@
         <v>57</v>
       </c>
       <c r="C35" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E35">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H35">
         <v>2</v>
@@ -3240,7 +3237,7 @@
         <v>3</v>
       </c>
       <c r="K35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L35">
         <v>3</v>
@@ -3252,7 +3249,7 @@
         <v>3</v>
       </c>
       <c r="O35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P35">
         <v>3</v>
@@ -3261,25 +3258,25 @@
         <v>3</v>
       </c>
       <c r="R35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S35">
         <v>6</v>
       </c>
       <c r="T35">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="U35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W35">
         <v>9</v>
       </c>
       <c r="X35">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:24">
@@ -3290,13 +3287,13 @@
         <v>58</v>
       </c>
       <c r="C36" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F36">
         <v>2</v>
@@ -3305,7 +3302,7 @@
         <v>3</v>
       </c>
       <c r="H36">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I36">
         <v>2</v>
@@ -3314,43 +3311,46 @@
         <v>2</v>
       </c>
       <c r="K36">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L36">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M36">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N36">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O36">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P36">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q36">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R36">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S36">
         <v>6</v>
       </c>
+      <c r="T36">
+        <v>37</v>
+      </c>
       <c r="U36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V36">
         <v>3</v>
       </c>
       <c r="W36">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="X36">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:24">
@@ -3364,43 +3364,43 @@
         <v>104</v>
       </c>
       <c r="D37">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E37">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F37">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G37">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H37">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I37">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J37">
         <v>3</v>
       </c>
       <c r="K37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O37">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q37">
         <v>6</v>
@@ -3412,19 +3412,19 @@
         <v>6</v>
       </c>
       <c r="T37">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="U37">
         <v>1</v>
       </c>
       <c r="V37">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W37">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="X37">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38" spans="1:24">
@@ -3435,70 +3435,67 @@
         <v>60</v>
       </c>
       <c r="C38" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D38">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E38">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F38">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G38">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H38">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I38">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K38">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L38">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M38">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N38">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O38">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P38">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q38">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R38">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S38">
         <v>6</v>
       </c>
-      <c r="T38">
-        <v>41</v>
-      </c>
       <c r="U38">
         <v>1</v>
       </c>
       <c r="V38">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="W38">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="X38">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:24">
@@ -3509,16 +3506,16 @@
         <v>61</v>
       </c>
       <c r="C39" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D39">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E39">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G39">
         <v>2</v>
@@ -3527,40 +3524,40 @@
         <v>2</v>
       </c>
       <c r="I39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J39">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K39">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L39">
         <v>6</v>
       </c>
       <c r="M39">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N39">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O39">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P39">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q39">
         <v>4</v>
       </c>
       <c r="R39">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S39">
         <v>6</v>
       </c>
       <c r="T39">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="U39">
         <v>1</v>
@@ -3569,10 +3566,10 @@
         <v>3</v>
       </c>
       <c r="W39">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="X39">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:24">
@@ -3583,49 +3580,49 @@
         <v>62</v>
       </c>
       <c r="C40" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D40">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E40">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F40">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G40">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H40">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I40">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K40">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L40">
         <v>5</v>
       </c>
       <c r="M40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N40">
         <v>5</v>
       </c>
       <c r="O40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P40">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R40">
         <v>5</v>
@@ -3634,19 +3631,19 @@
         <v>6</v>
       </c>
       <c r="T40">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="U40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V40">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W40">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="X40">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41" spans="1:24">
@@ -3660,10 +3657,10 @@
         <v>105</v>
       </c>
       <c r="D41">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E41">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F41">
         <v>4</v>
@@ -3675,52 +3672,52 @@
         <v>3</v>
       </c>
       <c r="I41">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J41">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K41">
         <v>5</v>
       </c>
       <c r="L41">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M41">
         <v>5</v>
       </c>
       <c r="N41">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O41">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P41">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q41">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R41">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S41">
         <v>6</v>
       </c>
       <c r="T41">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="U41">
         <v>1</v>
       </c>
       <c r="V41">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W41">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="X41">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42" spans="1:24">
@@ -3731,58 +3728,58 @@
         <v>64</v>
       </c>
       <c r="C42" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D42">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E42">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F42">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G42">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H42">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I42">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J42">
         <v>4</v>
       </c>
       <c r="K42">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L42">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M42">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N42">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O42">
         <v>4</v>
       </c>
       <c r="P42">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q42">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R42">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S42">
         <v>6</v>
       </c>
       <c r="T42">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="U42">
         <v>1</v>
@@ -3791,10 +3788,10 @@
         <v>3</v>
       </c>
       <c r="W42">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="X42">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43" spans="1:24">
@@ -3805,70 +3802,70 @@
         <v>65</v>
       </c>
       <c r="C43" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H43">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J43">
         <v>1</v>
       </c>
       <c r="K43">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N43">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O43">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P43">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q43">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R43">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="S43">
         <v>6</v>
       </c>
       <c r="T43">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="U43">
         <v>1</v>
       </c>
       <c r="V43">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W43">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="X43">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44" spans="1:24">
@@ -3882,55 +3879,55 @@
         <v>105</v>
       </c>
       <c r="D44">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E44">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F44">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G44">
         <v>3</v>
       </c>
       <c r="H44">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I44">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J44">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K44">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L44">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M44">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N44">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O44">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P44">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q44">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R44">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S44">
         <v>6</v>
       </c>
       <c r="T44">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="U44">
         <v>1</v>
@@ -3939,10 +3936,10 @@
         <v>3</v>
       </c>
       <c r="W44">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="X44">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45" spans="1:24">
@@ -3953,31 +3950,31 @@
         <v>67</v>
       </c>
       <c r="C45" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D45">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E45">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F45">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G45">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H45">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I45">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J45">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K45">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L45">
         <v>5</v>
@@ -3986,7 +3983,7 @@
         <v>5</v>
       </c>
       <c r="N45">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O45">
         <v>4</v>
@@ -3995,25 +3992,28 @@
         <v>5</v>
       </c>
       <c r="Q45">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R45">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S45">
         <v>6</v>
       </c>
       <c r="T45">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="U45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W45">
-        <v>7</v>
+        <v>10</v>
+      </c>
+      <c r="X45">
+        <v>6</v>
       </c>
     </row>
     <row r="46" spans="1:24">
@@ -4024,31 +4024,31 @@
         <v>68</v>
       </c>
       <c r="C46" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D46">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E46">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F46">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G46">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H46">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I46">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K46">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L46">
         <v>7</v>
@@ -4060,13 +4060,13 @@
         <v>7</v>
       </c>
       <c r="O46">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P46">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q46">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R46">
         <v>6</v>
@@ -4081,13 +4081,13 @@
         <v>2</v>
       </c>
       <c r="V46">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W46">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="X46">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="47" spans="1:24">
@@ -4098,28 +4098,28 @@
         <v>69</v>
       </c>
       <c r="C47" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D47">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E47">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F47">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G47">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H47">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I47">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K47">
         <v>3</v>
@@ -4131,37 +4131,37 @@
         <v>3</v>
       </c>
       <c r="N47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O47">
         <v>4</v>
       </c>
       <c r="P47">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q47">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S47">
         <v>6</v>
       </c>
       <c r="T47">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="U47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W47">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="X47">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48" spans="1:24">
@@ -4172,43 +4172,43 @@
         <v>70</v>
       </c>
       <c r="C48" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D48">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F48">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G48">
         <v>3</v>
       </c>
       <c r="H48">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I48">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J48">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K48">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L48">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M48">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N48">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O48">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P48">
         <v>5</v>
@@ -4223,19 +4223,19 @@
         <v>6</v>
       </c>
       <c r="T48">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="U48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V48">
         <v>4</v>
       </c>
       <c r="W48">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="X48">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49" spans="1:24">
@@ -4246,28 +4246,28 @@
         <v>71</v>
       </c>
       <c r="C49" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D49">
         <v>4</v>
       </c>
       <c r="E49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H49">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I49">
         <v>4</v>
       </c>
       <c r="J49">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K49">
         <v>3</v>
@@ -4276,7 +4276,7 @@
         <v>2</v>
       </c>
       <c r="M49">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N49">
         <v>3</v>
@@ -4291,25 +4291,25 @@
         <v>2</v>
       </c>
       <c r="R49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S49">
         <v>6</v>
       </c>
       <c r="T49">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="U49">
         <v>1</v>
       </c>
       <c r="V49">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W49">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="X49">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50" spans="1:24">
@@ -4320,10 +4320,10 @@
         <v>72</v>
       </c>
       <c r="C50" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E50">
         <v>1</v>
@@ -4335,52 +4335,52 @@
         <v>1</v>
       </c>
       <c r="H50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I50">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J50">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K50">
         <v>5</v>
       </c>
       <c r="L50">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M50">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N50">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O50">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P50">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q50">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R50">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S50">
         <v>6</v>
       </c>
       <c r="T50">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="U50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V50">
         <v>3</v>
       </c>
       <c r="W50">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="X50">
         <v>4</v>
@@ -4394,7 +4394,7 @@
         <v>73</v>
       </c>
       <c r="C51" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D51">
         <v>2</v>
@@ -4403,13 +4403,13 @@
         <v>1</v>
       </c>
       <c r="F51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I51">
         <v>2</v>
@@ -4418,46 +4418,46 @@
         <v>2</v>
       </c>
       <c r="K51">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L51">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M51">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N51">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P51">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q51">
         <v>4</v>
       </c>
       <c r="R51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S51">
         <v>6</v>
       </c>
       <c r="T51">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="U51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V51">
         <v>4</v>
       </c>
       <c r="W51">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X51">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52" spans="1:24">
@@ -4468,25 +4468,25 @@
         <v>74</v>
       </c>
       <c r="C52" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D52">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E52">
         <v>3</v>
       </c>
       <c r="F52">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G52">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H52">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I52">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J52">
         <v>3</v>
@@ -4495,25 +4495,25 @@
         <v>4</v>
       </c>
       <c r="L52">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M52">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N52">
         <v>5</v>
       </c>
       <c r="O52">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P52">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q52">
         <v>4</v>
       </c>
       <c r="R52">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S52">
         <v>6</v>
@@ -4522,13 +4522,13 @@
         <v>36</v>
       </c>
       <c r="U52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V52">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W52">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="X52">
         <v>5</v>
@@ -4545,67 +4545,67 @@
         <v>104</v>
       </c>
       <c r="D53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F53">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H53">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I53">
         <v>1</v>
       </c>
       <c r="J53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K53">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L53">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M53">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N53">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O53">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="P53">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q53">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="R53">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="S53">
         <v>6</v>
       </c>
       <c r="T53">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="U53">
         <v>1</v>
       </c>
       <c r="V53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W53">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="X53">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54" spans="1:24">
@@ -4619,22 +4619,22 @@
         <v>104</v>
       </c>
       <c r="D54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E54">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F54">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G54">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H54">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I54">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J54">
         <v>2</v>
@@ -4643,31 +4643,31 @@
         <v>5</v>
       </c>
       <c r="L54">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M54">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N54">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O54">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P54">
         <v>5</v>
       </c>
       <c r="Q54">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R54">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S54">
         <v>6</v>
       </c>
       <c r="T54">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="U54">
         <v>2</v>
@@ -4676,10 +4676,10 @@
         <v>3</v>
       </c>
       <c r="W54">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="X54">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55" spans="1:24">
@@ -4693,25 +4693,25 @@
         <v>104</v>
       </c>
       <c r="D55">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E55">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F55">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G55">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H55">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I55">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J55">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K55">
         <v>4</v>
@@ -4720,40 +4720,40 @@
         <v>4</v>
       </c>
       <c r="M55">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N55">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O55">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P55">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q55">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="R55">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S55">
         <v>6</v>
       </c>
       <c r="T55">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="U55">
         <v>1</v>
       </c>
       <c r="V55">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W55">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="X55">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:24">
@@ -4767,55 +4767,55 @@
         <v>104</v>
       </c>
       <c r="D56">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G56">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H56">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I56">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J56">
         <v>2</v>
       </c>
       <c r="K56">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L56">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M56">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N56">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O56">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P56">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q56">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R56">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S56">
         <v>6</v>
       </c>
       <c r="T56">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="U56">
         <v>1</v>
@@ -4824,10 +4824,10 @@
         <v>3</v>
       </c>
       <c r="W56">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="X56">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:24">
@@ -4838,13 +4838,13 @@
         <v>79</v>
       </c>
       <c r="C57" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D57">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E57">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F57">
         <v>3</v>
@@ -4853,34 +4853,34 @@
         <v>3</v>
       </c>
       <c r="H57">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I57">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J57">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K57">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L57">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M57">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N57">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O57">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P57">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q57">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R57">
         <v>4</v>
@@ -4889,7 +4889,7 @@
         <v>6</v>
       </c>
       <c r="T57">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="U57">
         <v>1</v>
@@ -4898,10 +4898,10 @@
         <v>2</v>
       </c>
       <c r="W57">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="X57">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58" spans="1:24">
@@ -4912,70 +4912,70 @@
         <v>80</v>
       </c>
       <c r="C58" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D58">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E58">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F58">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G58">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H58">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I58">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J58">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K58">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L58">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M58">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N58">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O58">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P58">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q58">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R58">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S58">
         <v>6</v>
       </c>
       <c r="T58">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="U58">
         <v>1</v>
       </c>
       <c r="V58">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W58">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="X58">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59" spans="1:24">
@@ -4986,40 +4986,40 @@
         <v>81</v>
       </c>
       <c r="C59" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D59">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E59">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F59">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G59">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H59">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I59">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J59">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K59">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L59">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M59">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N59">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O59">
         <v>5</v>
@@ -5028,7 +5028,7 @@
         <v>5</v>
       </c>
       <c r="Q59">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R59">
         <v>5</v>
@@ -5036,17 +5036,14 @@
       <c r="S59">
         <v>6</v>
       </c>
-      <c r="T59">
-        <v>28</v>
-      </c>
       <c r="U59">
         <v>1</v>
       </c>
       <c r="V59">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W59">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="X59">
         <v>4</v>
@@ -5060,70 +5057,70 @@
         <v>82</v>
       </c>
       <c r="C60" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D60">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E60">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F60">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G60">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H60">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I60">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J60">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K60">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L60">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M60">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N60">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O60">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="P60">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q60">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R60">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S60">
         <v>6</v>
       </c>
       <c r="T60">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="U60">
         <v>2</v>
       </c>
       <c r="V60">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W60">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="X60">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61" spans="1:24">
@@ -5134,52 +5131,52 @@
         <v>83</v>
       </c>
       <c r="C61" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D61">
         <v>2</v>
       </c>
       <c r="E61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F61">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G61">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H61">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I61">
         <v>2</v>
       </c>
       <c r="J61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K61">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L61">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M61">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N61">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O61">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P61">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q61">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R61">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S61">
         <v>6</v>
@@ -5191,13 +5188,13 @@
         <v>2</v>
       </c>
       <c r="V61">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W61">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="X61">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62" spans="1:24">
@@ -5214,7 +5211,7 @@
         <v>3</v>
       </c>
       <c r="E62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F62">
         <v>3</v>
@@ -5229,49 +5226,49 @@
         <v>3</v>
       </c>
       <c r="J62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K62">
         <v>3</v>
       </c>
       <c r="L62">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M62">
         <v>3</v>
       </c>
       <c r="N62">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O62">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P62">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q62">
         <v>4</v>
       </c>
       <c r="R62">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S62">
         <v>6</v>
       </c>
       <c r="T62">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V62">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W62">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="X62">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63" spans="1:24">
@@ -5282,25 +5279,25 @@
         <v>85</v>
       </c>
       <c r="C63" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D63">
         <v>3</v>
       </c>
       <c r="E63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F63">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G63">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H63">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I63">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J63">
         <v>3</v>
@@ -5309,10 +5306,10 @@
         <v>5</v>
       </c>
       <c r="L63">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M63">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N63">
         <v>5</v>
@@ -5321,31 +5318,31 @@
         <v>5</v>
       </c>
       <c r="P63">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q63">
         <v>4</v>
       </c>
       <c r="R63">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S63">
         <v>6</v>
       </c>
       <c r="T63">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="U63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V63">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="W63">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X63">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64" spans="1:24">
@@ -5359,49 +5356,49 @@
         <v>103</v>
       </c>
       <c r="D64">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E64">
         <v>3</v>
       </c>
       <c r="F64">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G64">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H64">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I64">
         <v>3</v>
       </c>
       <c r="J64">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K64">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L64">
         <v>3</v>
       </c>
       <c r="M64">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N64">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O64">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P64">
         <v>3</v>
       </c>
       <c r="Q64">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R64">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S64">
         <v>6</v>
@@ -5410,16 +5407,16 @@
         <v>33</v>
       </c>
       <c r="U64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V64">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W64">
         <v>5</v>
       </c>
       <c r="X64">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65" spans="1:24">
@@ -5433,67 +5430,67 @@
         <v>103</v>
       </c>
       <c r="D65">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E65">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F65">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G65">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H65">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I65">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J65">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K65">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L65">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M65">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N65">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O65">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="P65">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Q65">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R65">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="S65">
         <v>6</v>
       </c>
       <c r="T65">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="U65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W65">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="X65">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="66" spans="1:24">
@@ -5513,7 +5510,7 @@
         <v>1</v>
       </c>
       <c r="F66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G66">
         <v>1</v>
@@ -5531,7 +5528,7 @@
         <v>7</v>
       </c>
       <c r="L66">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M66">
         <v>6</v>
@@ -5540,22 +5537,22 @@
         <v>7</v>
       </c>
       <c r="O66">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P66">
         <v>7</v>
       </c>
       <c r="Q66">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R66">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S66">
         <v>6</v>
       </c>
       <c r="T66">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="U66">
         <v>1</v>
@@ -5564,10 +5561,10 @@
         <v>3</v>
       </c>
       <c r="W66">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="X66">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67" spans="1:24">
@@ -5578,25 +5575,25 @@
         <v>89</v>
       </c>
       <c r="C67" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F67">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J67">
         <v>1</v>
@@ -5620,7 +5617,7 @@
         <v>7</v>
       </c>
       <c r="Q67">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R67">
         <v>6</v>
@@ -5629,19 +5626,19 @@
         <v>6</v>
       </c>
       <c r="T67">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="U67">
         <v>1</v>
       </c>
       <c r="V67">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W67">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="X67">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68" spans="1:24">
@@ -5655,64 +5652,67 @@
         <v>104</v>
       </c>
       <c r="D68">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E68">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F68">
         <v>3</v>
       </c>
       <c r="G68">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H68">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I68">
         <v>3</v>
       </c>
       <c r="J68">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K68">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L68">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M68">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N68">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O68">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="P68">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q68">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R68">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S68">
         <v>6</v>
       </c>
       <c r="T68">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="U68">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V68">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W68">
-        <v>11</v>
+        <v>8</v>
+      </c>
+      <c r="X68">
+        <v>8</v>
       </c>
     </row>
     <row r="69" spans="1:24">
@@ -5723,52 +5723,52 @@
         <v>91</v>
       </c>
       <c r="C69" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F69">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K69">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L69">
         <v>6</v>
       </c>
       <c r="M69">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N69">
         <v>5</v>
       </c>
       <c r="O69">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P69">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q69">
         <v>5</v>
       </c>
       <c r="R69">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S69">
         <v>6</v>
@@ -5783,10 +5783,10 @@
         <v>4</v>
       </c>
       <c r="W69">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="X69">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="70" spans="1:24">
@@ -5797,58 +5797,58 @@
         <v>92</v>
       </c>
       <c r="C70" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E70">
         <v>2</v>
       </c>
       <c r="F70">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G70">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I70">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J70">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K70">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L70">
         <v>5</v>
       </c>
       <c r="M70">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N70">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O70">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P70">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Q70">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R70">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S70">
         <v>6</v>
       </c>
       <c r="T70">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="U70">
         <v>1</v>
@@ -5857,10 +5857,10 @@
         <v>3</v>
       </c>
       <c r="W70">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="X70">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71" spans="1:24">
@@ -5871,49 +5871,49 @@
         <v>93</v>
       </c>
       <c r="C71" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D71">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E71">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F71">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G71">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H71">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I71">
         <v>3</v>
       </c>
       <c r="J71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K71">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L71">
         <v>6</v>
       </c>
       <c r="M71">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N71">
         <v>6</v>
       </c>
       <c r="O71">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P71">
         <v>7</v>
       </c>
       <c r="Q71">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R71">
         <v>6</v>
@@ -5922,16 +5922,16 @@
         <v>6</v>
       </c>
       <c r="T71">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="U71">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V71">
         <v>3</v>
       </c>
       <c r="W71">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="X71">
         <v>7</v>
@@ -5945,10 +5945,10 @@
         <v>94</v>
       </c>
       <c r="C72" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D72">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E72">
         <v>2</v>
@@ -5957,13 +5957,13 @@
         <v>1</v>
       </c>
       <c r="G72">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H72">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I72">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J72">
         <v>1</v>
@@ -5972,43 +5972,43 @@
         <v>7</v>
       </c>
       <c r="L72">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M72">
         <v>7</v>
       </c>
       <c r="N72">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O72">
         <v>7</v>
       </c>
       <c r="P72">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q72">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R72">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S72">
         <v>6</v>
       </c>
       <c r="T72">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="U72">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V72">
         <v>3</v>
       </c>
       <c r="W72">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="X72">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73" spans="1:24">
@@ -6019,7 +6019,7 @@
         <v>95</v>
       </c>
       <c r="C73" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D73">
         <v>1</v>
@@ -6028,10 +6028,10 @@
         <v>1</v>
       </c>
       <c r="F73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H73">
         <v>1</v>
@@ -6043,43 +6043,43 @@
         <v>1</v>
       </c>
       <c r="K73">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L73">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M73">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N73">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O73">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P73">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q73">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R73">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S73">
         <v>6</v>
       </c>
       <c r="T73">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="U73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V73">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W73">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="X73">
         <v>3</v>
@@ -6093,58 +6093,58 @@
         <v>96</v>
       </c>
       <c r="C74" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D74">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E74">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F74">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G74">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H74">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I74">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J74">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K74">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L74">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M74">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N74">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O74">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P74">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q74">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="R74">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="S74">
         <v>6</v>
       </c>
       <c r="T74">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="U74">
         <v>1</v>
@@ -6153,10 +6153,10 @@
         <v>4</v>
       </c>
       <c r="W74">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="X74">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75" spans="1:24">
@@ -6173,40 +6173,40 @@
         <v>2</v>
       </c>
       <c r="E75">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F75">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G75">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H75">
         <v>2</v>
       </c>
       <c r="I75">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J75">
         <v>3</v>
       </c>
       <c r="K75">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L75">
         <v>6</v>
       </c>
       <c r="M75">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N75">
         <v>6</v>
       </c>
       <c r="O75">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P75">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q75">
         <v>7</v>
@@ -6218,19 +6218,19 @@
         <v>6</v>
       </c>
       <c r="T75">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="U75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V75">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W75">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="X75">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76" spans="1:24">
@@ -6247,31 +6247,31 @@
         <v>3</v>
       </c>
       <c r="E76">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F76">
         <v>2</v>
       </c>
       <c r="G76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I76">
         <v>3</v>
       </c>
       <c r="J76">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K76">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L76">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M76">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N76">
         <v>4</v>
@@ -6283,7 +6283,7 @@
         <v>5</v>
       </c>
       <c r="Q76">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R76">
         <v>3</v>
@@ -6292,7 +6292,7 @@
         <v>6</v>
       </c>
       <c r="T76">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="U76">
         <v>1</v>
@@ -6301,7 +6301,7 @@
         <v>4</v>
       </c>
       <c r="W76">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="X76">
         <v>6</v>
@@ -6315,58 +6315,58 @@
         <v>99</v>
       </c>
       <c r="C77" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D77">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E77">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F77">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G77">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H77">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I77">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J77">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K77">
         <v>4</v>
       </c>
       <c r="L77">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M77">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N77">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O77">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P77">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q77">
         <v>3</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S77">
         <v>6</v>
       </c>
       <c r="T77">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="U77">
         <v>2</v>
@@ -6375,10 +6375,10 @@
         <v>3</v>
       </c>
       <c r="W77">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="X77">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78" spans="1:24">
@@ -6392,67 +6392,67 @@
         <v>105</v>
       </c>
       <c r="D78">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E78">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F78">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G78">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H78">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I78">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J78">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K78">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L78">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M78">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N78">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O78">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P78">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q78">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R78">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S78">
         <v>6</v>
       </c>
       <c r="T78">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="U78">
         <v>2</v>
       </c>
       <c r="V78">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W78">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="X78">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79" spans="1:24">
@@ -6463,52 +6463,52 @@
         <v>101</v>
       </c>
       <c r="C79" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D79">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E79">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F79">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G79">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H79">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I79">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J79">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K79">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L79">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M79">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N79">
         <v>5</v>
       </c>
       <c r="O79">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P79">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q79">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R79">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S79">
         <v>6</v>
@@ -6523,10 +6523,10 @@
         <v>3</v>
       </c>
       <c r="W79">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X79">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80" spans="1:24">
@@ -6540,16 +6540,16 @@
         <v>103</v>
       </c>
       <c r="D80">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E80">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F80">
         <v>1</v>
       </c>
       <c r="G80">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H80">
         <v>2</v>
@@ -6558,49 +6558,49 @@
         <v>3</v>
       </c>
       <c r="J80">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K80">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L80">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M80">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N80">
         <v>4</v>
       </c>
       <c r="O80">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P80">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q80">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R80">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S80">
         <v>6</v>
       </c>
       <c r="T80">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="U80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V80">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W80">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="X80">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/data/T3_leader_cleaned.xlsx
+++ b/data/T3_leader_cleaned.xlsx
@@ -76,241 +76,241 @@
     <t>SpanOfControl</t>
   </si>
   <si>
+    <t>A_L14</t>
+  </si>
+  <si>
+    <t>A_L20</t>
+  </si>
+  <si>
+    <t>A_L08</t>
+  </si>
+  <si>
+    <t>B_L10</t>
+  </si>
+  <si>
+    <t>B_L06</t>
+  </si>
+  <si>
+    <t>C_L18</t>
+  </si>
+  <si>
+    <t>C_L25</t>
+  </si>
+  <si>
+    <t>A_L11</t>
+  </si>
+  <si>
+    <t>A_L10</t>
+  </si>
+  <si>
+    <t>B_L23</t>
+  </si>
+  <si>
+    <t>B_L21</t>
+  </si>
+  <si>
+    <t>C_L10</t>
+  </si>
+  <si>
+    <t>B_L29</t>
+  </si>
+  <si>
+    <t>B_L30</t>
+  </si>
+  <si>
+    <t>B_L08</t>
+  </si>
+  <si>
+    <t>B_L09</t>
+  </si>
+  <si>
+    <t>A_L26</t>
+  </si>
+  <si>
+    <t>C_L04</t>
+  </si>
+  <si>
+    <t>A_L15</t>
+  </si>
+  <si>
+    <t>C_L07</t>
+  </si>
+  <si>
+    <t>B_L05</t>
+  </si>
+  <si>
+    <t>C_L12</t>
+  </si>
+  <si>
+    <t>C_L20</t>
+  </si>
+  <si>
+    <t>A_L28</t>
+  </si>
+  <si>
+    <t>C_L16</t>
+  </si>
+  <si>
+    <t>C_L06</t>
+  </si>
+  <si>
+    <t>A_L19</t>
+  </si>
+  <si>
+    <t>B_L01</t>
+  </si>
+  <si>
+    <t>C_L26</t>
+  </si>
+  <si>
+    <t>A_L06</t>
+  </si>
+  <si>
+    <t>C_L24</t>
+  </si>
+  <si>
     <t>A_L13</t>
   </si>
   <si>
-    <t>A_L19</t>
+    <t>C_L29</t>
+  </si>
+  <si>
+    <t>B_L25</t>
+  </si>
+  <si>
+    <t>C_L09</t>
+  </si>
+  <si>
+    <t>B_L24</t>
+  </si>
+  <si>
+    <t>B_L26</t>
+  </si>
+  <si>
+    <t>C_L02</t>
+  </si>
+  <si>
+    <t>A_L21</t>
+  </si>
+  <si>
+    <t>C_L30</t>
+  </si>
+  <si>
+    <t>C_L28</t>
+  </si>
+  <si>
+    <t>B_L02</t>
+  </si>
+  <si>
+    <t>C_L14</t>
+  </si>
+  <si>
+    <t>C_L21</t>
+  </si>
+  <si>
+    <t>B_L04</t>
+  </si>
+  <si>
+    <t>C_L19</t>
+  </si>
+  <si>
+    <t>B_L11</t>
+  </si>
+  <si>
+    <t>A_L18</t>
+  </si>
+  <si>
+    <t>C_L01</t>
+  </si>
+  <si>
+    <t>B_L19</t>
+  </si>
+  <si>
+    <t>A_L09</t>
+  </si>
+  <si>
+    <t>B_L18</t>
+  </si>
+  <si>
+    <t>B_L03</t>
+  </si>
+  <si>
+    <t>B_L07</t>
+  </si>
+  <si>
+    <t>B_L22</t>
+  </si>
+  <si>
+    <t>B_L15</t>
   </si>
   <si>
     <t>A_L07</t>
   </si>
   <si>
-    <t>B_L09</t>
-  </si>
-  <si>
-    <t>B_L05</t>
-  </si>
-  <si>
-    <t>C_L16</t>
-  </si>
-  <si>
-    <t>C_L24</t>
-  </si>
-  <si>
-    <t>A_L10</t>
-  </si>
-  <si>
-    <t>A_L09</t>
-  </si>
-  <si>
-    <t>B_L22</t>
+    <t>C_L13</t>
+  </si>
+  <si>
+    <t>B_L27</t>
+  </si>
+  <si>
+    <t>A_L02</t>
+  </si>
+  <si>
+    <t>C_L08</t>
+  </si>
+  <si>
+    <t>C_L11</t>
+  </si>
+  <si>
+    <t>A_L03</t>
+  </si>
+  <si>
+    <t>A_L25</t>
+  </si>
+  <si>
+    <t>A_L29</t>
+  </si>
+  <si>
+    <t>A_L16</t>
+  </si>
+  <si>
+    <t>B_L14</t>
   </si>
   <si>
     <t>B_L20</t>
   </si>
   <si>
-    <t>C_L09</t>
-  </si>
-  <si>
-    <t>B_L27</t>
-  </si>
-  <si>
-    <t>B_L29</t>
-  </si>
-  <si>
-    <t>B_L07</t>
-  </si>
-  <si>
-    <t>B_L08</t>
-  </si>
-  <si>
-    <t>A_L25</t>
+    <t>A_L23</t>
+  </si>
+  <si>
+    <t>B_L12</t>
+  </si>
+  <si>
+    <t>A_L12</t>
+  </si>
+  <si>
+    <t>B_L16</t>
+  </si>
+  <si>
+    <t>A_L22</t>
+  </si>
+  <si>
+    <t>A_L24</t>
+  </si>
+  <si>
+    <t>A_L01</t>
+  </si>
+  <si>
+    <t>C_L22</t>
   </si>
   <si>
     <t>C_L03</t>
   </si>
   <si>
-    <t>A_L14</t>
-  </si>
-  <si>
-    <t>C_L05</t>
-  </si>
-  <si>
-    <t>B_L04</t>
-  </si>
-  <si>
-    <t>C_L11</t>
-  </si>
-  <si>
-    <t>C_L18</t>
+    <t>A_L04</t>
   </si>
   <si>
     <t>A_L27</t>
-  </si>
-  <si>
-    <t>C_L14</t>
-  </si>
-  <si>
-    <t>C_L04</t>
-  </si>
-  <si>
-    <t>A_L18</t>
-  </si>
-  <si>
-    <t>A_L29</t>
-  </si>
-  <si>
-    <t>C_L26</t>
-  </si>
-  <si>
-    <t>A_L05</t>
-  </si>
-  <si>
-    <t>C_L22</t>
-  </si>
-  <si>
-    <t>A_L12</t>
-  </si>
-  <si>
-    <t>C_L28</t>
-  </si>
-  <si>
-    <t>B_L24</t>
-  </si>
-  <si>
-    <t>C_L08</t>
-  </si>
-  <si>
-    <t>B_L23</t>
-  </si>
-  <si>
-    <t>B_L25</t>
-  </si>
-  <si>
-    <t>C_L01</t>
-  </si>
-  <si>
-    <t>A_L20</t>
-  </si>
-  <si>
-    <t>C_L30</t>
-  </si>
-  <si>
-    <t>C_L27</t>
-  </si>
-  <si>
-    <t>B_L01</t>
-  </si>
-  <si>
-    <t>C_L13</t>
-  </si>
-  <si>
-    <t>C_L19</t>
-  </si>
-  <si>
-    <t>B_L03</t>
-  </si>
-  <si>
-    <t>C_L17</t>
-  </si>
-  <si>
-    <t>B_L10</t>
-  </si>
-  <si>
-    <t>A_L17</t>
-  </si>
-  <si>
-    <t>B_L30</t>
-  </si>
-  <si>
-    <t>B_L18</t>
-  </si>
-  <si>
-    <t>A_L08</t>
-  </si>
-  <si>
-    <t>B_L16</t>
-  </si>
-  <si>
-    <t>B_L02</t>
-  </si>
-  <si>
-    <t>B_L06</t>
-  </si>
-  <si>
-    <t>B_L21</t>
-  </si>
-  <si>
-    <t>B_L14</t>
-  </si>
-  <si>
-    <t>A_L06</t>
-  </si>
-  <si>
-    <t>C_L12</t>
-  </si>
-  <si>
-    <t>B_L26</t>
-  </si>
-  <si>
-    <t>A_L02</t>
-  </si>
-  <si>
-    <t>C_L07</t>
-  </si>
-  <si>
-    <t>C_L10</t>
-  </si>
-  <si>
-    <t>A_L03</t>
-  </si>
-  <si>
-    <t>A_L24</t>
-  </si>
-  <si>
-    <t>A_L28</t>
-  </si>
-  <si>
-    <t>A_L16</t>
-  </si>
-  <si>
-    <t>B_L12</t>
-  </si>
-  <si>
-    <t>B_L19</t>
-  </si>
-  <si>
-    <t>A_L22</t>
-  </si>
-  <si>
-    <t>B_L11</t>
-  </si>
-  <si>
-    <t>A_L11</t>
-  </si>
-  <si>
-    <t>B_L15</t>
-  </si>
-  <si>
-    <t>A_L21</t>
-  </si>
-  <si>
-    <t>A_L23</t>
-  </si>
-  <si>
-    <t>A_L01</t>
-  </si>
-  <si>
-    <t>C_L20</t>
-  </si>
-  <si>
-    <t>C_L02</t>
-  </si>
-  <si>
-    <t>A_L04</t>
-  </si>
-  <si>
-    <t>A_L26</t>
   </si>
   <si>
     <t>A</t>
@@ -830,22 +830,22 @@
         <v>2</v>
       </c>
       <c r="I3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O3">
         <v>6</v>
@@ -877,37 +877,37 @@
         <v>99</v>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O4">
         <v>6</v>
@@ -1007,31 +1007,31 @@
         <v>1</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O6">
         <v>6</v>
@@ -1078,22 +1078,22 @@
         <v>3</v>
       </c>
       <c r="I7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O7">
         <v>6</v>
@@ -1125,37 +1125,37 @@
         <v>101</v>
       </c>
       <c r="D8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O8">
         <v>6</v>
@@ -1249,37 +1249,37 @@
         <v>99</v>
       </c>
       <c r="D10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O10">
         <v>6</v>
@@ -1311,37 +1311,37 @@
         <v>100</v>
       </c>
       <c r="D11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O11">
         <v>6</v>
@@ -1435,37 +1435,37 @@
         <v>101</v>
       </c>
       <c r="D13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O13">
         <v>6</v>
@@ -1512,22 +1512,22 @@
         <v>4</v>
       </c>
       <c r="I14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O14">
         <v>6</v>
@@ -1621,19 +1621,19 @@
         <v>100</v>
       </c>
       <c r="D16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I16">
         <v>5</v>
@@ -1683,19 +1683,19 @@
         <v>100</v>
       </c>
       <c r="D17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I17">
         <v>4</v>
@@ -1745,37 +1745,37 @@
         <v>99</v>
       </c>
       <c r="D18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F18">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H18">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I18">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J18">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K18">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L18">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M18">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N18">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O18">
         <v>6</v>
@@ -1866,37 +1866,37 @@
         <v>99</v>
       </c>
       <c r="D20">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F20">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G20">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H20">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I20">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J20">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K20">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L20">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M20">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N20">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O20">
         <v>6</v>
@@ -1928,37 +1928,37 @@
         <v>101</v>
       </c>
       <c r="D21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I21">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N21">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O21">
         <v>6</v>
@@ -1990,37 +1990,37 @@
         <v>100</v>
       </c>
       <c r="D22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I22">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J22">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M22">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N22">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O22">
         <v>6</v>
@@ -2052,37 +2052,37 @@
         <v>101</v>
       </c>
       <c r="D23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E23">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K23">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M23">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N23">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O23">
         <v>6</v>
@@ -2173,37 +2173,37 @@
         <v>99</v>
       </c>
       <c r="D25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F25">
         <v>1</v>
       </c>
       <c r="G25">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H25">
         <v>1</v>
       </c>
       <c r="I25">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J25">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K25">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L25">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M25">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N25">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O25">
         <v>6</v>
@@ -2235,37 +2235,37 @@
         <v>101</v>
       </c>
       <c r="D26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I26">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J26">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K26">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L26">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M26">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N26">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O26">
         <v>6</v>
@@ -2359,7 +2359,7 @@
         <v>99</v>
       </c>
       <c r="D28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E28">
         <v>1</v>
@@ -2368,28 +2368,28 @@
         <v>1</v>
       </c>
       <c r="G28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I28">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J28">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L28">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M28">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N28">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O28">
         <v>6</v>
@@ -2418,40 +2418,40 @@
         <v>47</v>
       </c>
       <c r="C29" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D29">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E29">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F29">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G29">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H29">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I29">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J29">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O29">
         <v>6</v>
@@ -2545,37 +2545,37 @@
         <v>99</v>
       </c>
       <c r="D31">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E31">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F31">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G31">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H31">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J31">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K31">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L31">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M31">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N31">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O31">
         <v>6</v>
@@ -2607,37 +2607,37 @@
         <v>101</v>
       </c>
       <c r="D32">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F32">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G32">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I32">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J32">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K32">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L32">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M32">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N32">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O32">
         <v>6</v>
@@ -2669,37 +2669,37 @@
         <v>99</v>
       </c>
       <c r="D33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I33">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J33">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M33">
         <v>7</v>
       </c>
       <c r="N33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O33">
         <v>6</v>
@@ -2870,22 +2870,22 @@
         <v>1</v>
       </c>
       <c r="I36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O36">
         <v>6</v>
@@ -2917,37 +2917,37 @@
         <v>100</v>
       </c>
       <c r="D37">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E37">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F37">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G37">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H37">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I37">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J37">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K37">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L37">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M37">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N37">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O37">
         <v>6</v>
@@ -2994,22 +2994,22 @@
         <v>2</v>
       </c>
       <c r="I38">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K38">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M38">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O38">
         <v>6</v>
@@ -3041,37 +3041,37 @@
         <v>101</v>
       </c>
       <c r="D39">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E39">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F39">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G39">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H39">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I39">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J39">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K39">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L39">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M39">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N39">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O39">
         <v>6</v>
@@ -3103,37 +3103,37 @@
         <v>99</v>
       </c>
       <c r="D40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I40">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J40">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L40">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M40">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O40">
         <v>6</v>
@@ -3242,13 +3242,13 @@
         <v>2</v>
       </c>
       <c r="I42">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J42">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K42">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L42">
         <v>7</v>
@@ -3257,7 +3257,7 @@
         <v>7</v>
       </c>
       <c r="N42">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O42">
         <v>6</v>
@@ -3304,22 +3304,22 @@
         <v>2</v>
       </c>
       <c r="I43">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J43">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K43">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L43">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M43">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N43">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O43">
         <v>6</v>
@@ -3413,37 +3413,37 @@
         <v>101</v>
       </c>
       <c r="D45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I45">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J45">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K45">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L45">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M45">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N45">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O45">
         <v>6</v>
@@ -3661,37 +3661,37 @@
         <v>99</v>
       </c>
       <c r="D49">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E49">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F49">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G49">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H49">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I49">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J49">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K49">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L49">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M49">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N49">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O49">
         <v>6</v>
@@ -3720,7 +3720,7 @@
         <v>68</v>
       </c>
       <c r="C50" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D50">
         <v>1</v>
@@ -3738,22 +3738,22 @@
         <v>1</v>
       </c>
       <c r="I50">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J50">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K50">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L50">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M50">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N50">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O50">
         <v>6</v>
@@ -3788,31 +3788,31 @@
         <v>1</v>
       </c>
       <c r="F51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H51">
         <v>1</v>
       </c>
       <c r="I51">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J51">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K51">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L51">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M51">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N51">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O51">
         <v>6</v>
@@ -3844,37 +3844,37 @@
         <v>99</v>
       </c>
       <c r="D52">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E52">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I52">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J52">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K52">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L52">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M52">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N52">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O52">
         <v>6</v>
@@ -3909,34 +3909,34 @@
         <v>1</v>
       </c>
       <c r="E53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F53">
         <v>1</v>
       </c>
       <c r="G53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H53">
         <v>1</v>
       </c>
       <c r="I53">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J53">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K53">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L53">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M53">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N53">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O53">
         <v>6</v>
@@ -4154,19 +4154,19 @@
         <v>100</v>
       </c>
       <c r="D57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E57">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F57">
         <v>1</v>
       </c>
       <c r="G57">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I57">
         <v>6</v>
@@ -4216,37 +4216,37 @@
         <v>99</v>
       </c>
       <c r="D58">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E58">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F58">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G58">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H58">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I58">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J58">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K58">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L58">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M58">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N58">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O58">
         <v>6</v>
@@ -4293,22 +4293,22 @@
         <v>3</v>
       </c>
       <c r="I59">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J59">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K59">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L59">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M59">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N59">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O59">
         <v>6</v>
@@ -4340,19 +4340,19 @@
         <v>100</v>
       </c>
       <c r="D60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I60">
         <v>6</v>
@@ -4464,37 +4464,37 @@
         <v>101</v>
       </c>
       <c r="D62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F62">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I62">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J62">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K62">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L62">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M62">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N62">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O62">
         <v>6</v>
@@ -4526,37 +4526,37 @@
         <v>101</v>
       </c>
       <c r="D63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I63">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J63">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K63">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L63">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M63">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N63">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O63">
         <v>6</v>
@@ -4650,37 +4650,37 @@
         <v>99</v>
       </c>
       <c r="D65">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E65">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F65">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G65">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H65">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I65">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J65">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K65">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L65">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M65">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N65">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O65">
         <v>6</v>
@@ -4712,37 +4712,37 @@
         <v>99</v>
       </c>
       <c r="D66">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E66">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F66">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G66">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H66">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I66">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J66">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K66">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L66">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M66">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N66">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O66">
         <v>6</v>
@@ -4898,37 +4898,37 @@
         <v>100</v>
       </c>
       <c r="D69">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E69">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F69">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G69">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H69">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I69">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J69">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K69">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L69">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M69">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N69">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O69">
         <v>6</v>
@@ -5022,37 +5022,37 @@
         <v>100</v>
       </c>
       <c r="D71">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E71">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F71">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G71">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H71">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I71">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J71">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K71">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L71">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M71">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N71">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O71">
         <v>6</v>
@@ -5084,37 +5084,37 @@
         <v>99</v>
       </c>
       <c r="D72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F72">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G72">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H72">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I72">
         <v>7</v>
       </c>
       <c r="J72">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K72">
         <v>7</v>
       </c>
       <c r="L72">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M72">
         <v>7</v>
       </c>
       <c r="N72">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O72">
         <v>6</v>
@@ -5146,22 +5146,22 @@
         <v>100</v>
       </c>
       <c r="D73">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E73">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G73">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H73">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I73">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J73">
         <v>7</v>
@@ -5170,10 +5170,10 @@
         <v>7</v>
       </c>
       <c r="L73">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M73">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N73">
         <v>7</v>
@@ -5208,19 +5208,19 @@
         <v>99</v>
       </c>
       <c r="D74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I74">
         <v>4</v>
@@ -5270,37 +5270,37 @@
         <v>99</v>
       </c>
       <c r="D75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I75">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J75">
         <v>7</v>
       </c>
       <c r="K75">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L75">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M75">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N75">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O75">
         <v>6</v>
@@ -5456,37 +5456,37 @@
         <v>101</v>
       </c>
       <c r="D78">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E78">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F78">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G78">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H78">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I78">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J78">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K78">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L78">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M78">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N78">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O78">
         <v>6</v>
@@ -5580,7 +5580,7 @@
         <v>99</v>
       </c>
       <c r="D80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E80">
         <v>1</v>
@@ -5595,22 +5595,22 @@
         <v>1</v>
       </c>
       <c r="I80">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J80">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K80">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L80">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M80">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N80">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O80">
         <v>6</v>

--- a/data/T3_leader_cleaned.xlsx
+++ b/data/T3_leader_cleaned.xlsx
@@ -76,241 +76,241 @@
     <t>SpanOfControl</t>
   </si>
   <si>
+    <t>A_L13</t>
+  </si>
+  <si>
+    <t>A_L19</t>
+  </si>
+  <si>
+    <t>A_L07</t>
+  </si>
+  <si>
+    <t>B_L08</t>
+  </si>
+  <si>
+    <t>B_L04</t>
+  </si>
+  <si>
+    <t>C_L19</t>
+  </si>
+  <si>
+    <t>C_L26</t>
+  </si>
+  <si>
+    <t>A_L10</t>
+  </si>
+  <si>
+    <t>A_L09</t>
+  </si>
+  <si>
+    <t>B_L21</t>
+  </si>
+  <si>
+    <t>B_L19</t>
+  </si>
+  <si>
+    <t>C_L11</t>
+  </si>
+  <si>
+    <t>B_L30</t>
+  </si>
+  <si>
+    <t>C_L01</t>
+  </si>
+  <si>
+    <t>B_L06</t>
+  </si>
+  <si>
+    <t>B_L07</t>
+  </si>
+  <si>
+    <t>A_L25</t>
+  </si>
+  <si>
+    <t>C_L05</t>
+  </si>
+  <si>
     <t>A_L14</t>
   </si>
   <si>
+    <t>C_L07</t>
+  </si>
+  <si>
+    <t>B_L03</t>
+  </si>
+  <si>
+    <t>C_L15</t>
+  </si>
+  <si>
+    <t>C_L21</t>
+  </si>
+  <si>
+    <t>A_L27</t>
+  </si>
+  <si>
+    <t>C_L18</t>
+  </si>
+  <si>
+    <t>C_L06</t>
+  </si>
+  <si>
+    <t>A_L18</t>
+  </si>
+  <si>
+    <t>A_L29</t>
+  </si>
+  <si>
+    <t>A_L05</t>
+  </si>
+  <si>
+    <t>C_L25</t>
+  </si>
+  <si>
+    <t>A_L12</t>
+  </si>
+  <si>
+    <t>C_L29</t>
+  </si>
+  <si>
+    <t>B_L23</t>
+  </si>
+  <si>
+    <t>C_L10</t>
+  </si>
+  <si>
+    <t>B_L22</t>
+  </si>
+  <si>
+    <t>B_L26</t>
+  </si>
+  <si>
+    <t>C_L03</t>
+  </si>
+  <si>
     <t>A_L20</t>
   </si>
   <si>
+    <t>C_L30</t>
+  </si>
+  <si>
+    <t>C_L28</t>
+  </si>
+  <si>
+    <t>A_L30</t>
+  </si>
+  <si>
+    <t>C_L17</t>
+  </si>
+  <si>
+    <t>C_L23</t>
+  </si>
+  <si>
+    <t>B_L02</t>
+  </si>
+  <si>
+    <t>C_L20</t>
+  </si>
+  <si>
+    <t>B_L09</t>
+  </si>
+  <si>
+    <t>A_L17</t>
+  </si>
+  <si>
+    <t>C_L02</t>
+  </si>
+  <si>
+    <t>B_L16</t>
+  </si>
+  <si>
     <t>A_L08</t>
   </si>
   <si>
+    <t>B_L15</t>
+  </si>
+  <si>
+    <t>B_L01</t>
+  </si>
+  <si>
+    <t>B_L05</t>
+  </si>
+  <si>
+    <t>B_L20</t>
+  </si>
+  <si>
+    <t>B_L13</t>
+  </si>
+  <si>
+    <t>A_L06</t>
+  </si>
+  <si>
+    <t>C_L16</t>
+  </si>
+  <si>
+    <t>B_L29</t>
+  </si>
+  <si>
+    <t>A_L02</t>
+  </si>
+  <si>
+    <t>C_L09</t>
+  </si>
+  <si>
+    <t>C_L14</t>
+  </si>
+  <si>
+    <t>A_L03</t>
+  </si>
+  <si>
+    <t>A_L24</t>
+  </si>
+  <si>
+    <t>A_L28</t>
+  </si>
+  <si>
+    <t>A_L16</t>
+  </si>
+  <si>
+    <t>B_L12</t>
+  </si>
+  <si>
+    <t>B_L18</t>
+  </si>
+  <si>
+    <t>A_L22</t>
+  </si>
+  <si>
     <t>B_L10</t>
   </si>
   <si>
-    <t>B_L06</t>
-  </si>
-  <si>
-    <t>C_L18</t>
-  </si>
-  <si>
-    <t>C_L25</t>
+    <t>C_L27</t>
   </si>
   <si>
     <t>A_L11</t>
   </si>
   <si>
-    <t>A_L10</t>
-  </si>
-  <si>
-    <t>B_L23</t>
-  </si>
-  <si>
-    <t>B_L21</t>
-  </si>
-  <si>
-    <t>C_L10</t>
-  </si>
-  <si>
-    <t>B_L29</t>
-  </si>
-  <si>
-    <t>B_L30</t>
-  </si>
-  <si>
-    <t>B_L08</t>
-  </si>
-  <si>
-    <t>B_L09</t>
+    <t>B_L14</t>
+  </si>
+  <si>
+    <t>A_L21</t>
+  </si>
+  <si>
+    <t>A_L23</t>
+  </si>
+  <si>
+    <t>A_L01</t>
+  </si>
+  <si>
+    <t>C_L24</t>
+  </si>
+  <si>
+    <t>C_L04</t>
+  </si>
+  <si>
+    <t>A_L04</t>
   </si>
   <si>
     <t>A_L26</t>
-  </si>
-  <si>
-    <t>C_L04</t>
-  </si>
-  <si>
-    <t>A_L15</t>
-  </si>
-  <si>
-    <t>C_L07</t>
-  </si>
-  <si>
-    <t>B_L05</t>
-  </si>
-  <si>
-    <t>C_L12</t>
-  </si>
-  <si>
-    <t>C_L20</t>
-  </si>
-  <si>
-    <t>A_L28</t>
-  </si>
-  <si>
-    <t>C_L16</t>
-  </si>
-  <si>
-    <t>C_L06</t>
-  </si>
-  <si>
-    <t>A_L19</t>
-  </si>
-  <si>
-    <t>B_L01</t>
-  </si>
-  <si>
-    <t>C_L26</t>
-  </si>
-  <si>
-    <t>A_L06</t>
-  </si>
-  <si>
-    <t>C_L24</t>
-  </si>
-  <si>
-    <t>A_L13</t>
-  </si>
-  <si>
-    <t>C_L29</t>
-  </si>
-  <si>
-    <t>B_L25</t>
-  </si>
-  <si>
-    <t>C_L09</t>
-  </si>
-  <si>
-    <t>B_L24</t>
-  </si>
-  <si>
-    <t>B_L26</t>
-  </si>
-  <si>
-    <t>C_L02</t>
-  </si>
-  <si>
-    <t>A_L21</t>
-  </si>
-  <si>
-    <t>C_L30</t>
-  </si>
-  <si>
-    <t>C_L28</t>
-  </si>
-  <si>
-    <t>B_L02</t>
-  </si>
-  <si>
-    <t>C_L14</t>
-  </si>
-  <si>
-    <t>C_L21</t>
-  </si>
-  <si>
-    <t>B_L04</t>
-  </si>
-  <si>
-    <t>C_L19</t>
-  </si>
-  <si>
-    <t>B_L11</t>
-  </si>
-  <si>
-    <t>A_L18</t>
-  </si>
-  <si>
-    <t>C_L01</t>
-  </si>
-  <si>
-    <t>B_L19</t>
-  </si>
-  <si>
-    <t>A_L09</t>
-  </si>
-  <si>
-    <t>B_L18</t>
-  </si>
-  <si>
-    <t>B_L03</t>
-  </si>
-  <si>
-    <t>B_L07</t>
-  </si>
-  <si>
-    <t>B_L22</t>
-  </si>
-  <si>
-    <t>B_L15</t>
-  </si>
-  <si>
-    <t>A_L07</t>
-  </si>
-  <si>
-    <t>C_L13</t>
-  </si>
-  <si>
-    <t>B_L27</t>
-  </si>
-  <si>
-    <t>A_L02</t>
-  </si>
-  <si>
-    <t>C_L08</t>
-  </si>
-  <si>
-    <t>C_L11</t>
-  </si>
-  <si>
-    <t>A_L03</t>
-  </si>
-  <si>
-    <t>A_L25</t>
-  </si>
-  <si>
-    <t>A_L29</t>
-  </si>
-  <si>
-    <t>A_L16</t>
-  </si>
-  <si>
-    <t>B_L14</t>
-  </si>
-  <si>
-    <t>B_L20</t>
-  </si>
-  <si>
-    <t>A_L23</t>
-  </si>
-  <si>
-    <t>B_L12</t>
-  </si>
-  <si>
-    <t>A_L12</t>
-  </si>
-  <si>
-    <t>B_L16</t>
-  </si>
-  <si>
-    <t>A_L22</t>
-  </si>
-  <si>
-    <t>A_L24</t>
-  </si>
-  <si>
-    <t>A_L01</t>
-  </si>
-  <si>
-    <t>C_L22</t>
-  </si>
-  <si>
-    <t>C_L03</t>
-  </si>
-  <si>
-    <t>A_L04</t>
-  </si>
-  <si>
-    <t>A_L27</t>
   </si>
   <si>
     <t>A</t>
@@ -756,7 +756,7 @@
         <v>2</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F2">
         <v>3</v>
@@ -765,43 +765,43 @@
         <v>2</v>
       </c>
       <c r="H2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K2">
         <v>6</v>
       </c>
       <c r="L2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M2">
         <v>6</v>
       </c>
       <c r="N2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O2">
         <v>6</v>
       </c>
       <c r="P2">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="Q2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S2">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T2">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -818,19 +818,19 @@
         <v>3</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G3">
         <v>3</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J3">
         <v>7</v>
@@ -839,31 +839,31 @@
         <v>7</v>
       </c>
       <c r="L3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M3">
         <v>7</v>
       </c>
       <c r="N3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O3">
         <v>6</v>
       </c>
       <c r="P3">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="Q3">
         <v>2</v>
       </c>
       <c r="R3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T3">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -877,55 +877,55 @@
         <v>99</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4">
         <v>3</v>
       </c>
       <c r="I4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O4">
         <v>6</v>
       </c>
       <c r="P4">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Q4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R4">
         <v>3</v>
       </c>
       <c r="S4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T4">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -939,55 +939,52 @@
         <v>100</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O5">
         <v>6</v>
       </c>
       <c r="P5">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="Q5">
         <v>2</v>
       </c>
       <c r="R5">
-        <v>2</v>
-      </c>
-      <c r="S5">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T5">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -1001,52 +998,52 @@
         <v>100</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K6">
         <v>5</v>
       </c>
       <c r="L6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O6">
         <v>6</v>
       </c>
       <c r="P6">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="Q6">
         <v>1</v>
       </c>
       <c r="R6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S6">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="T6">
         <v>7</v>
@@ -1063,55 +1060,52 @@
         <v>101</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L7">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O7">
         <v>6</v>
       </c>
       <c r="P7">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="Q7">
         <v>2</v>
       </c>
       <c r="R7">
-        <v>3</v>
-      </c>
-      <c r="S7">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T7">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -1128,40 +1122,40 @@
         <v>3</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F8">
         <v>3</v>
       </c>
       <c r="G8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K8">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L8">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O8">
         <v>6</v>
       </c>
       <c r="P8">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="Q8">
         <v>1</v>
@@ -1170,10 +1164,10 @@
         <v>3</v>
       </c>
       <c r="S8">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T8">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -1190,16 +1184,16 @@
         <v>2</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I9">
         <v>5</v>
@@ -1208,34 +1202,34 @@
         <v>6</v>
       </c>
       <c r="K9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L9">
         <v>6</v>
       </c>
       <c r="M9">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O9">
         <v>6</v>
       </c>
       <c r="P9">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="Q9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S9">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="T9">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -1255,19 +1249,19 @@
         <v>4</v>
       </c>
       <c r="F10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H10">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I10">
         <v>5</v>
       </c>
       <c r="J10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K10">
         <v>5</v>
@@ -1276,7 +1270,7 @@
         <v>5</v>
       </c>
       <c r="M10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N10">
         <v>4</v>
@@ -1285,19 +1279,19 @@
         <v>6</v>
       </c>
       <c r="P10">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="Q10">
         <v>1</v>
       </c>
       <c r="R10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S10">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="T10">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -1311,43 +1305,43 @@
         <v>100</v>
       </c>
       <c r="D11">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E11">
         <v>5</v>
       </c>
       <c r="F11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J11">
         <v>3</v>
       </c>
       <c r="K11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M11">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O11">
         <v>6</v>
       </c>
       <c r="P11">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="Q11">
         <v>1</v>
@@ -1356,10 +1350,10 @@
         <v>3</v>
       </c>
       <c r="S11">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="T11">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -1373,34 +1367,34 @@
         <v>100</v>
       </c>
       <c r="D12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L12">
         <v>5</v>
       </c>
       <c r="M12">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N12">
         <v>5</v>
@@ -1409,19 +1403,19 @@
         <v>6</v>
       </c>
       <c r="P12">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="Q12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S12">
         <v>12</v>
       </c>
       <c r="T12">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -1435,52 +1429,52 @@
         <v>101</v>
       </c>
       <c r="D13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J13">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O13">
         <v>6</v>
       </c>
       <c r="P13">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Q13">
         <v>1</v>
       </c>
       <c r="R13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T13">
         <v>6</v>
@@ -1497,43 +1491,43 @@
         <v>100</v>
       </c>
       <c r="D14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E14">
         <v>3</v>
       </c>
       <c r="F14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I14">
         <v>4</v>
       </c>
       <c r="J14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M14">
         <v>4</v>
       </c>
       <c r="N14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O14">
         <v>6</v>
       </c>
       <c r="P14">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="Q14">
         <v>1</v>
@@ -1542,10 +1536,10 @@
         <v>3</v>
       </c>
       <c r="S14">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T14">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -1556,58 +1550,58 @@
         <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I15">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J15">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L15">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O15">
         <v>6</v>
       </c>
       <c r="P15">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="Q15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S15">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="T15">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -1621,43 +1615,43 @@
         <v>100</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F16">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H16">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I16">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J16">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K16">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L16">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M16">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N16">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O16">
         <v>6</v>
       </c>
       <c r="P16">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="Q16">
         <v>2</v>
@@ -1666,10 +1660,10 @@
         <v>3</v>
       </c>
       <c r="S16">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="T16">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:20">
@@ -1683,55 +1677,55 @@
         <v>100</v>
       </c>
       <c r="D17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E17">
         <v>3</v>
       </c>
       <c r="F17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I17">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J17">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K17">
         <v>5</v>
       </c>
       <c r="L17">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M17">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N17">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O17">
         <v>6</v>
       </c>
       <c r="P17">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="Q17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R17">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S17">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="T17">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:20">
@@ -1745,34 +1739,34 @@
         <v>99</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G18">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H18">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I18">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J18">
         <v>4</v>
       </c>
       <c r="K18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L18">
         <v>4</v>
       </c>
       <c r="M18">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N18">
         <v>4</v>
@@ -1781,19 +1775,19 @@
         <v>6</v>
       </c>
       <c r="P18">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="Q18">
         <v>1</v>
       </c>
       <c r="R18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S18">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="T18">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:20">
@@ -1807,52 +1801,55 @@
         <v>101</v>
       </c>
       <c r="D19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L19">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M19">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N19">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O19">
         <v>6</v>
       </c>
+      <c r="P19">
+        <v>28</v>
+      </c>
       <c r="Q19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R19">
         <v>3</v>
       </c>
       <c r="S19">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="T19">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:20">
@@ -1866,13 +1863,13 @@
         <v>99</v>
       </c>
       <c r="D20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F20">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G20">
         <v>5</v>
@@ -1881,37 +1878,37 @@
         <v>5</v>
       </c>
       <c r="I20">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J20">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K20">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L20">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M20">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N20">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O20">
         <v>6</v>
       </c>
       <c r="P20">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="Q20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R20">
         <v>3</v>
       </c>
       <c r="S20">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="T20">
         <v>4</v>
@@ -1928,43 +1925,43 @@
         <v>101</v>
       </c>
       <c r="D21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E21">
         <v>3</v>
       </c>
       <c r="F21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H21">
         <v>3</v>
       </c>
       <c r="I21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K21">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L21">
         <v>3</v>
       </c>
       <c r="M21">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O21">
         <v>6</v>
       </c>
       <c r="P21">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="Q21">
         <v>1</v>
@@ -1973,10 +1970,10 @@
         <v>3</v>
       </c>
       <c r="S21">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T21">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:20">
@@ -1990,34 +1987,34 @@
         <v>100</v>
       </c>
       <c r="D22">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G22">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I22">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J22">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K22">
         <v>4</v>
       </c>
       <c r="L22">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M22">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N22">
         <v>5</v>
@@ -2026,19 +2023,19 @@
         <v>6</v>
       </c>
       <c r="P22">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="Q22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R22">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S22">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T22">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:20">
@@ -2052,46 +2049,46 @@
         <v>101</v>
       </c>
       <c r="D23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F23">
         <v>3</v>
       </c>
       <c r="G23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I23">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K23">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L23">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M23">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N23">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O23">
         <v>6</v>
       </c>
       <c r="P23">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R23">
         <v>3</v>
@@ -2120,46 +2117,49 @@
         <v>2</v>
       </c>
       <c r="F24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H24">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I24">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J24">
         <v>5</v>
       </c>
       <c r="K24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M24">
         <v>4</v>
       </c>
       <c r="N24">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O24">
         <v>6</v>
       </c>
       <c r="P24">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="Q24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R24">
         <v>3</v>
       </c>
       <c r="S24">
-        <v>20</v>
+        <v>7</v>
+      </c>
+      <c r="T24">
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:20">
@@ -2173,34 +2173,34 @@
         <v>99</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I25">
         <v>6</v>
       </c>
       <c r="J25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K25">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L25">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N25">
         <v>6</v>
@@ -2209,7 +2209,7 @@
         <v>6</v>
       </c>
       <c r="P25">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="Q25">
         <v>2</v>
@@ -2218,10 +2218,10 @@
         <v>4</v>
       </c>
       <c r="S25">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T25">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:20">
@@ -2235,10 +2235,10 @@
         <v>101</v>
       </c>
       <c r="D26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F26">
         <v>1</v>
@@ -2250,40 +2250,40 @@
         <v>1</v>
       </c>
       <c r="I26">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J26">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K26">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M26">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N26">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O26">
         <v>6</v>
       </c>
       <c r="P26">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="Q26">
         <v>1</v>
       </c>
       <c r="R26">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S26">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="T26">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:20">
@@ -2297,10 +2297,10 @@
         <v>101</v>
       </c>
       <c r="D27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F27">
         <v>2</v>
@@ -2309,7 +2309,7 @@
         <v>2</v>
       </c>
       <c r="H27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I27">
         <v>4</v>
@@ -2333,19 +2333,19 @@
         <v>6</v>
       </c>
       <c r="P27">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="Q27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R27">
         <v>3</v>
       </c>
       <c r="S27">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="T27">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:20">
@@ -2359,55 +2359,55 @@
         <v>99</v>
       </c>
       <c r="D28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28">
         <v>2</v>
       </c>
       <c r="H28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I28">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J28">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K28">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L28">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M28">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N28">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O28">
         <v>6</v>
       </c>
       <c r="P28">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="Q28">
         <v>1</v>
       </c>
       <c r="R28">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S28">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T28">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:20">
@@ -2418,37 +2418,37 @@
         <v>47</v>
       </c>
       <c r="C29" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D29">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G29">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I29">
         <v>5</v>
       </c>
       <c r="J29">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K29">
         <v>4</v>
       </c>
       <c r="L29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M29">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N29">
         <v>4</v>
@@ -2457,19 +2457,16 @@
         <v>6</v>
       </c>
       <c r="P29">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="Q29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R29">
         <v>3</v>
       </c>
-      <c r="S29">
-        <v>4</v>
-      </c>
       <c r="T29">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:20">
@@ -2480,7 +2477,7 @@
         <v>48</v>
       </c>
       <c r="C30" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D30">
         <v>4</v>
@@ -2489,46 +2486,46 @@
         <v>3</v>
       </c>
       <c r="F30">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G30">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H30">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I30">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J30">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K30">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L30">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M30">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N30">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O30">
         <v>6</v>
       </c>
       <c r="P30">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="Q30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R30">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S30">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T30">
         <v>5</v>
@@ -2542,7 +2539,7 @@
         <v>49</v>
       </c>
       <c r="C31" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D31">
         <v>1</v>
@@ -2551,37 +2548,37 @@
         <v>1</v>
       </c>
       <c r="F31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I31">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J31">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K31">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L31">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M31">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N31">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O31">
         <v>6</v>
       </c>
       <c r="P31">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="Q31">
         <v>2</v>
@@ -2590,10 +2587,10 @@
         <v>4</v>
       </c>
       <c r="S31">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="T31">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:20">
@@ -2604,55 +2601,55 @@
         <v>50</v>
       </c>
       <c r="C32" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D32">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E32">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F32">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G32">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H32">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I32">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J32">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K32">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L32">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M32">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N32">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O32">
         <v>6</v>
       </c>
       <c r="P32">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q32">
         <v>1</v>
       </c>
       <c r="R32">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S32">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T32">
         <v>4</v>
@@ -2666,7 +2663,7 @@
         <v>51</v>
       </c>
       <c r="C33" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D33">
         <v>3</v>
@@ -2681,37 +2678,37 @@
         <v>3</v>
       </c>
       <c r="H33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I33">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K33">
         <v>6</v>
       </c>
       <c r="L33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O33">
         <v>6</v>
       </c>
       <c r="P33">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="Q33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R33">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S33">
         <v>20</v>
@@ -2728,34 +2725,34 @@
         <v>52</v>
       </c>
       <c r="C34" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D34">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E34">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F34">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M34">
         <v>7</v>
@@ -2767,19 +2764,19 @@
         <v>6</v>
       </c>
       <c r="P34">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="Q34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R34">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S34">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="T34">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:20">
@@ -2790,58 +2787,58 @@
         <v>53</v>
       </c>
       <c r="C35" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E35">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F35">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I35">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K35">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M35">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N35">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O35">
         <v>6</v>
       </c>
       <c r="P35">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="Q35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R35">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S35">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="T35">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:20">
@@ -2852,58 +2849,58 @@
         <v>54</v>
       </c>
       <c r="C36" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D36">
         <v>1</v>
       </c>
       <c r="E36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F36">
         <v>1</v>
       </c>
       <c r="G36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H36">
         <v>1</v>
       </c>
       <c r="I36">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J36">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K36">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L36">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M36">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N36">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O36">
         <v>6</v>
       </c>
       <c r="P36">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="Q36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R36">
         <v>3</v>
       </c>
       <c r="S36">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T36">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:20">
@@ -2917,37 +2914,37 @@
         <v>100</v>
       </c>
       <c r="D37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E37">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F37">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G37">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H37">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I37">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J37">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K37">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M37">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N37">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O37">
         <v>6</v>
@@ -2956,16 +2953,16 @@
         <v>45</v>
       </c>
       <c r="Q37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R37">
         <v>4</v>
       </c>
       <c r="S37">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="T37">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:20">
@@ -2976,7 +2973,7 @@
         <v>56</v>
       </c>
       <c r="C38" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D38">
         <v>2</v>
@@ -2994,13 +2991,13 @@
         <v>2</v>
       </c>
       <c r="I38">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J38">
         <v>6</v>
       </c>
       <c r="K38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L38">
         <v>6</v>
@@ -3009,25 +3006,25 @@
         <v>5</v>
       </c>
       <c r="N38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O38">
         <v>6</v>
       </c>
       <c r="P38">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="Q38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R38">
         <v>3</v>
       </c>
       <c r="S38">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T38">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:20">
@@ -3038,55 +3035,55 @@
         <v>57</v>
       </c>
       <c r="C39" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D39">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E39">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F39">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G39">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H39">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I39">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J39">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K39">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L39">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M39">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N39">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O39">
         <v>6</v>
       </c>
       <c r="P39">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="Q39">
         <v>1</v>
       </c>
       <c r="R39">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S39">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="T39">
         <v>5</v>
@@ -3100,37 +3097,37 @@
         <v>58</v>
       </c>
       <c r="C40" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F40">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G40">
         <v>3</v>
       </c>
       <c r="H40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I40">
         <v>4</v>
       </c>
       <c r="J40">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K40">
         <v>5</v>
       </c>
       <c r="L40">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M40">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N40">
         <v>5</v>
@@ -3139,16 +3136,16 @@
         <v>6</v>
       </c>
       <c r="P40">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="Q40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S40">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T40">
         <v>5</v>
@@ -3165,22 +3162,22 @@
         <v>101</v>
       </c>
       <c r="D41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G41">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J41">
         <v>6</v>
@@ -3210,7 +3207,7 @@
         <v>3</v>
       </c>
       <c r="S41">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T41">
         <v>5</v>
@@ -3224,58 +3221,58 @@
         <v>60</v>
       </c>
       <c r="C42" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E42">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F42">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G42">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I42">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J42">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K42">
         <v>5</v>
       </c>
       <c r="L42">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M42">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N42">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O42">
         <v>6</v>
       </c>
       <c r="P42">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="Q42">
         <v>1</v>
       </c>
       <c r="R42">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S42">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="T42">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43" spans="1:20">
@@ -3286,46 +3283,46 @@
         <v>61</v>
       </c>
       <c r="C43" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D43">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G43">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H43">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I43">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J43">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K43">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L43">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M43">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N43">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O43">
         <v>6</v>
       </c>
       <c r="P43">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Q43">
         <v>1</v>
@@ -3334,10 +3331,10 @@
         <v>4</v>
       </c>
       <c r="S43">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="T43">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44" spans="1:20">
@@ -3357,25 +3354,25 @@
         <v>3</v>
       </c>
       <c r="F44">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G44">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H44">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I44">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J44">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K44">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L44">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M44">
         <v>4</v>
@@ -3387,19 +3384,19 @@
         <v>6</v>
       </c>
       <c r="P44">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="Q44">
         <v>1</v>
       </c>
       <c r="R44">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S44">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="T44">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45" spans="1:20">
@@ -3410,37 +3407,37 @@
         <v>63</v>
       </c>
       <c r="C45" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D45">
         <v>3</v>
       </c>
       <c r="E45">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F45">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H45">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I45">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J45">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K45">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L45">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M45">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N45">
         <v>5</v>
@@ -3449,19 +3446,19 @@
         <v>6</v>
       </c>
       <c r="P45">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="Q45">
         <v>2</v>
       </c>
       <c r="R45">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S45">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="T45">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46" spans="1:20">
@@ -3472,58 +3469,58 @@
         <v>64</v>
       </c>
       <c r="C46" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E46">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H46">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I46">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J46">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K46">
         <v>5</v>
       </c>
       <c r="L46">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M46">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N46">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O46">
         <v>6</v>
       </c>
       <c r="P46">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="Q46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R46">
         <v>3</v>
       </c>
       <c r="S46">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="T46">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47" spans="1:20">
@@ -3534,58 +3531,58 @@
         <v>65</v>
       </c>
       <c r="C47" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E47">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F47">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G47">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H47">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I47">
         <v>5</v>
       </c>
       <c r="J47">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K47">
         <v>5</v>
       </c>
       <c r="L47">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M47">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N47">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O47">
         <v>6</v>
       </c>
       <c r="P47">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="Q47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R47">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S47">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T47">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48" spans="1:20">
@@ -3596,58 +3593,58 @@
         <v>66</v>
       </c>
       <c r="C48" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D48">
         <v>3</v>
       </c>
       <c r="E48">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H48">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I48">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J48">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K48">
         <v>6</v>
       </c>
       <c r="L48">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M48">
         <v>5</v>
       </c>
       <c r="N48">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O48">
         <v>6</v>
       </c>
       <c r="P48">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="Q48">
         <v>1</v>
       </c>
       <c r="R48">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S48">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="T48">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49" spans="1:20">
@@ -3658,40 +3655,40 @@
         <v>67</v>
       </c>
       <c r="C49" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D49">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E49">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H49">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I49">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J49">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K49">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L49">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M49">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N49">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O49">
         <v>6</v>
@@ -3706,10 +3703,10 @@
         <v>4</v>
       </c>
       <c r="S49">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T49">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50" spans="1:20">
@@ -3720,55 +3717,58 @@
         <v>68</v>
       </c>
       <c r="C50" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D50">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E50">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F50">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G50">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H50">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I50">
         <v>4</v>
       </c>
       <c r="J50">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K50">
         <v>4</v>
       </c>
       <c r="L50">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M50">
         <v>4</v>
       </c>
       <c r="N50">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O50">
         <v>6</v>
       </c>
       <c r="P50">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="Q50">
         <v>1</v>
       </c>
       <c r="R50">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S50">
-        <v>16</v>
+        <v>11</v>
+      </c>
+      <c r="T50">
+        <v>4</v>
       </c>
     </row>
     <row r="51" spans="1:20">
@@ -3779,46 +3779,46 @@
         <v>69</v>
       </c>
       <c r="C51" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D51">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E51">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G51">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H51">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I51">
         <v>6</v>
       </c>
       <c r="J51">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K51">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L51">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M51">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N51">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O51">
         <v>6</v>
       </c>
       <c r="P51">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="Q51">
         <v>2</v>
@@ -3827,10 +3827,10 @@
         <v>3</v>
       </c>
       <c r="S51">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="T51">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52" spans="1:20">
@@ -3841,58 +3841,58 @@
         <v>70</v>
       </c>
       <c r="C52" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D52">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E52">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H52">
         <v>2</v>
       </c>
       <c r="I52">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J52">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K52">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L52">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M52">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N52">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O52">
         <v>6</v>
       </c>
       <c r="P52">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="Q52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R52">
         <v>3</v>
       </c>
       <c r="S52">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="T52">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53" spans="1:20">
@@ -3906,19 +3906,19 @@
         <v>100</v>
       </c>
       <c r="D53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H53">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I53">
         <v>5</v>
@@ -3927,34 +3927,34 @@
         <v>5</v>
       </c>
       <c r="K53">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L53">
         <v>5</v>
       </c>
       <c r="M53">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N53">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O53">
         <v>6</v>
       </c>
       <c r="P53">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="Q53">
         <v>1</v>
       </c>
       <c r="R53">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S53">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T53">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54" spans="1:20">
@@ -3968,22 +3968,22 @@
         <v>100</v>
       </c>
       <c r="D54">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E54">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F54">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G54">
         <v>3</v>
       </c>
       <c r="H54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I54">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J54">
         <v>5</v>
@@ -3995,28 +3995,28 @@
         <v>5</v>
       </c>
       <c r="M54">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N54">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O54">
         <v>6</v>
       </c>
       <c r="P54">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="Q54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R54">
         <v>3</v>
       </c>
       <c r="S54">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="T54">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55" spans="1:20">
@@ -4036,37 +4036,37 @@
         <v>4</v>
       </c>
       <c r="F55">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G55">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H55">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I55">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J55">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K55">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L55">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M55">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N55">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O55">
         <v>6</v>
       </c>
       <c r="P55">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="Q55">
         <v>1</v>
@@ -4075,10 +4075,10 @@
         <v>3</v>
       </c>
       <c r="S55">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="T55">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56" spans="1:20">
@@ -4092,25 +4092,25 @@
         <v>100</v>
       </c>
       <c r="D56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E56">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F56">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G56">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H56">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I56">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J56">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K56">
         <v>4</v>
@@ -4119,28 +4119,28 @@
         <v>4</v>
       </c>
       <c r="M56">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N56">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O56">
         <v>6</v>
       </c>
       <c r="P56">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="Q56">
         <v>1</v>
       </c>
       <c r="R56">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S56">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T56">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="57" spans="1:20">
@@ -4151,28 +4151,28 @@
         <v>75</v>
       </c>
       <c r="C57" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E57">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F57">
         <v>1</v>
       </c>
       <c r="G57">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I57">
         <v>6</v>
       </c>
       <c r="J57">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K57">
         <v>7</v>
@@ -4181,28 +4181,28 @@
         <v>7</v>
       </c>
       <c r="M57">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N57">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O57">
         <v>6</v>
       </c>
       <c r="P57">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="Q57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R57">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S57">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T57">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58" spans="1:20">
@@ -4213,25 +4213,25 @@
         <v>76</v>
       </c>
       <c r="C58" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D58">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E58">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F58">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G58">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H58">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I58">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J58">
         <v>4</v>
@@ -4243,28 +4243,28 @@
         <v>4</v>
       </c>
       <c r="M58">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N58">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O58">
         <v>6</v>
       </c>
       <c r="P58">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R58">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S58">
         <v>5</v>
       </c>
       <c r="T58">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59" spans="1:20">
@@ -4275,46 +4275,46 @@
         <v>77</v>
       </c>
       <c r="C59" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D59">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E59">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F59">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G59">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H59">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I59">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J59">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K59">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L59">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M59">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N59">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O59">
         <v>6</v>
       </c>
       <c r="P59">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="Q59">
         <v>2</v>
@@ -4323,10 +4323,10 @@
         <v>3</v>
       </c>
       <c r="S59">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="T59">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60" spans="1:20">
@@ -4337,19 +4337,19 @@
         <v>78</v>
       </c>
       <c r="C60" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D60">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E60">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F60">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G60">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H60">
         <v>2</v>
@@ -4358,37 +4358,37 @@
         <v>6</v>
       </c>
       <c r="J60">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K60">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L60">
         <v>6</v>
       </c>
       <c r="M60">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N60">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O60">
         <v>6</v>
       </c>
       <c r="P60">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="Q60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R60">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S60">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="T60">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="61" spans="1:20">
@@ -4399,58 +4399,58 @@
         <v>79</v>
       </c>
       <c r="C61" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D61">
         <v>2</v>
       </c>
       <c r="E61">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G61">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H61">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I61">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J61">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K61">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L61">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M61">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N61">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O61">
         <v>6</v>
       </c>
       <c r="P61">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="Q61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R61">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S61">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="T61">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62" spans="1:20">
@@ -4464,52 +4464,52 @@
         <v>101</v>
       </c>
       <c r="D62">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F62">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G62">
         <v>2</v>
       </c>
       <c r="H62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I62">
         <v>5</v>
       </c>
       <c r="J62">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K62">
         <v>4</v>
       </c>
       <c r="L62">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M62">
         <v>5</v>
       </c>
       <c r="N62">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O62">
         <v>6</v>
       </c>
       <c r="P62">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="Q62">
         <v>1</v>
       </c>
       <c r="R62">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S62">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="T62">
         <v>4</v>
@@ -4523,16 +4523,16 @@
         <v>81</v>
       </c>
       <c r="C63" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D63">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G63">
         <v>2</v>
@@ -4550,31 +4550,31 @@
         <v>5</v>
       </c>
       <c r="L63">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M63">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N63">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O63">
         <v>6</v>
       </c>
       <c r="P63">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="Q63">
         <v>1</v>
       </c>
       <c r="R63">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S63">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="T63">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64" spans="1:20">
@@ -4588,7 +4588,7 @@
         <v>99</v>
       </c>
       <c r="D64">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E64">
         <v>3</v>
@@ -4597,46 +4597,46 @@
         <v>2</v>
       </c>
       <c r="G64">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H64">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I64">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J64">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K64">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L64">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M64">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N64">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O64">
         <v>6</v>
       </c>
       <c r="P64">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="Q64">
         <v>1</v>
       </c>
       <c r="R64">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S64">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="T64">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65" spans="1:20">
@@ -4650,55 +4650,55 @@
         <v>99</v>
       </c>
       <c r="D65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E65">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F65">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G65">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H65">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I65">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J65">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K65">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L65">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M65">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N65">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O65">
         <v>6</v>
       </c>
       <c r="P65">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="Q65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R65">
         <v>3</v>
       </c>
       <c r="S65">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T65">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="66" spans="1:20">
@@ -4712,55 +4712,55 @@
         <v>99</v>
       </c>
       <c r="D66">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E66">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F66">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G66">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H66">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I66">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J66">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K66">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L66">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M66">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N66">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O66">
         <v>6</v>
       </c>
       <c r="P66">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="Q66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R66">
         <v>3</v>
       </c>
       <c r="S66">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="T66">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="67" spans="1:20">
@@ -4771,55 +4771,55 @@
         <v>85</v>
       </c>
       <c r="C67" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D67">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E67">
         <v>1</v>
       </c>
       <c r="F67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H67">
         <v>2</v>
       </c>
       <c r="I67">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J67">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K67">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L67">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M67">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N67">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O67">
         <v>6</v>
       </c>
       <c r="P67">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="Q67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R67">
         <v>4</v>
       </c>
       <c r="S67">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="T67">
         <v>3</v>
@@ -4836,55 +4836,55 @@
         <v>100</v>
       </c>
       <c r="D68">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E68">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F68">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G68">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H68">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I68">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J68">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K68">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L68">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M68">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N68">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O68">
         <v>6</v>
       </c>
       <c r="P68">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="Q68">
         <v>1</v>
       </c>
       <c r="R68">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S68">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T68">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69" spans="1:20">
@@ -4895,13 +4895,13 @@
         <v>87</v>
       </c>
       <c r="C69" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D69">
         <v>3</v>
       </c>
       <c r="E69">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F69">
         <v>3</v>
@@ -4919,34 +4919,34 @@
         <v>4</v>
       </c>
       <c r="K69">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L69">
         <v>5</v>
       </c>
       <c r="M69">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N69">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O69">
         <v>6</v>
       </c>
       <c r="P69">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="Q69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R69">
         <v>3</v>
       </c>
       <c r="S69">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="T69">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70" spans="1:20">
@@ -4957,10 +4957,10 @@
         <v>88</v>
       </c>
       <c r="C70" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E70">
         <v>2</v>
@@ -4969,25 +4969,25 @@
         <v>1</v>
       </c>
       <c r="G70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I70">
         <v>4</v>
       </c>
       <c r="J70">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K70">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L70">
         <v>5</v>
       </c>
       <c r="M70">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N70">
         <v>4</v>
@@ -5008,7 +5008,7 @@
         <v>16</v>
       </c>
       <c r="T70">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="71" spans="1:20">
@@ -5019,58 +5019,58 @@
         <v>89</v>
       </c>
       <c r="C71" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D71">
         <v>1</v>
       </c>
       <c r="E71">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F71">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G71">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H71">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I71">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J71">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K71">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L71">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M71">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N71">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O71">
         <v>6</v>
       </c>
       <c r="P71">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="Q71">
         <v>1</v>
       </c>
       <c r="R71">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S71">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="T71">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:20">
@@ -5084,46 +5084,46 @@
         <v>99</v>
       </c>
       <c r="D72">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E72">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F72">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G72">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H72">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I72">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J72">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K72">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L72">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M72">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N72">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O72">
         <v>6</v>
       </c>
       <c r="P72">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Q72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R72">
         <v>3</v>
@@ -5132,7 +5132,7 @@
         <v>15</v>
       </c>
       <c r="T72">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73" spans="1:20">
@@ -5152,49 +5152,49 @@
         <v>2</v>
       </c>
       <c r="F73">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G73">
         <v>2</v>
       </c>
       <c r="H73">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I73">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J73">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K73">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L73">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M73">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N73">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O73">
         <v>6</v>
       </c>
       <c r="P73">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="Q73">
         <v>1</v>
       </c>
       <c r="R73">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S73">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="T73">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="74" spans="1:20">
@@ -5211,52 +5211,52 @@
         <v>4</v>
       </c>
       <c r="E74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G74">
         <v>3</v>
       </c>
       <c r="H74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I74">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J74">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K74">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L74">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M74">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N74">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O74">
         <v>6</v>
       </c>
       <c r="P74">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="Q74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S74">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="T74">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75" spans="1:20">
@@ -5273,52 +5273,52 @@
         <v>2</v>
       </c>
       <c r="E75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G75">
         <v>2</v>
       </c>
       <c r="H75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I75">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J75">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K75">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L75">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M75">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N75">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O75">
         <v>6</v>
       </c>
       <c r="P75">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="Q75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R75">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S75">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="T75">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76" spans="1:20">
@@ -5332,13 +5332,13 @@
         <v>99</v>
       </c>
       <c r="D76">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E76">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G76">
         <v>3</v>
@@ -5347,28 +5347,28 @@
         <v>3</v>
       </c>
       <c r="I76">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J76">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K76">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L76">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M76">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N76">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O76">
         <v>6</v>
       </c>
       <c r="P76">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="Q76">
         <v>1</v>
@@ -5377,7 +5377,7 @@
         <v>4</v>
       </c>
       <c r="S76">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="T76">
         <v>5</v>
@@ -5394,55 +5394,55 @@
         <v>101</v>
       </c>
       <c r="D77">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E77">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F77">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G77">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I77">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J77">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K77">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L77">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M77">
         <v>6</v>
       </c>
       <c r="N77">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O77">
         <v>6</v>
       </c>
       <c r="P77">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="Q77">
         <v>1</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S77">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="T77">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78" spans="1:20">
@@ -5456,13 +5456,13 @@
         <v>101</v>
       </c>
       <c r="D78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E78">
         <v>1</v>
       </c>
       <c r="F78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G78">
         <v>1</v>
@@ -5471,40 +5471,40 @@
         <v>1</v>
       </c>
       <c r="I78">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J78">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K78">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L78">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M78">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N78">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O78">
         <v>6</v>
       </c>
       <c r="P78">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="Q78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R78">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S78">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="T78">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79" spans="1:20">
@@ -5518,16 +5518,16 @@
         <v>99</v>
       </c>
       <c r="D79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G79">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H79">
         <v>1</v>
@@ -5536,37 +5536,37 @@
         <v>6</v>
       </c>
       <c r="J79">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K79">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L79">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M79">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N79">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O79">
         <v>6</v>
       </c>
       <c r="P79">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="Q79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R79">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S79">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="T79">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80" spans="1:20">
@@ -5580,7 +5580,7 @@
         <v>99</v>
       </c>
       <c r="D80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E80">
         <v>1</v>
@@ -5595,40 +5595,40 @@
         <v>1</v>
       </c>
       <c r="I80">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J80">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K80">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L80">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M80">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N80">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O80">
         <v>6</v>
       </c>
       <c r="P80">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="Q80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R80">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S80">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="T80">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/data/T3_leader_cleaned.xlsx
+++ b/data/T3_leader_cleaned.xlsx
@@ -76,241 +76,241 @@
     <t>SpanOfControl</t>
   </si>
   <si>
+    <t>A_L14</t>
+  </si>
+  <si>
+    <t>A_L19</t>
+  </si>
+  <si>
+    <t>A_L07</t>
+  </si>
+  <si>
+    <t>B_L09</t>
+  </si>
+  <si>
+    <t>B_L05</t>
+  </si>
+  <si>
+    <t>C_L19</t>
+  </si>
+  <si>
+    <t>C_L26</t>
+  </si>
+  <si>
+    <t>A_L11</t>
+  </si>
+  <si>
+    <t>A_L09</t>
+  </si>
+  <si>
+    <t>B_L23</t>
+  </si>
+  <si>
+    <t>B_L21</t>
+  </si>
+  <si>
+    <t>C_L13</t>
+  </si>
+  <si>
+    <t>B_L29</t>
+  </si>
+  <si>
+    <t>B_L30</t>
+  </si>
+  <si>
+    <t>B_L07</t>
+  </si>
+  <si>
+    <t>B_L08</t>
+  </si>
+  <si>
+    <t>A_L26</t>
+  </si>
+  <si>
+    <t>C_L07</t>
+  </si>
+  <si>
+    <t>A_L15</t>
+  </si>
+  <si>
+    <t>C_L10</t>
+  </si>
+  <si>
+    <t>B_L04</t>
+  </si>
+  <si>
+    <t>C_L15</t>
+  </si>
+  <si>
+    <t>C_L21</t>
+  </si>
+  <si>
+    <t>A_L28</t>
+  </si>
+  <si>
+    <t>C_L18</t>
+  </si>
+  <si>
+    <t>C_L09</t>
+  </si>
+  <si>
+    <t>A_L18</t>
+  </si>
+  <si>
+    <t>A_L30</t>
+  </si>
+  <si>
+    <t>A_L05</t>
+  </si>
+  <si>
+    <t>C_L25</t>
+  </si>
+  <si>
     <t>A_L13</t>
   </si>
   <si>
-    <t>A_L19</t>
-  </si>
-  <si>
-    <t>A_L07</t>
-  </si>
-  <si>
-    <t>B_L08</t>
-  </si>
-  <si>
-    <t>B_L04</t>
-  </si>
-  <si>
-    <t>C_L19</t>
-  </si>
-  <si>
-    <t>C_L26</t>
-  </si>
-  <si>
-    <t>A_L10</t>
-  </si>
-  <si>
-    <t>A_L09</t>
-  </si>
-  <si>
-    <t>B_L21</t>
-  </si>
-  <si>
-    <t>B_L19</t>
+    <t>C_L29</t>
+  </si>
+  <si>
+    <t>B_L26</t>
+  </si>
+  <si>
+    <t>C_L12</t>
+  </si>
+  <si>
+    <t>B_L24</t>
+  </si>
+  <si>
+    <t>B_L27</t>
+  </si>
+  <si>
+    <t>C_L04</t>
+  </si>
+  <si>
+    <t>A_L20</t>
+  </si>
+  <si>
+    <t>C_L30</t>
+  </si>
+  <si>
+    <t>C_L28</t>
+  </si>
+  <si>
+    <t>B_L01</t>
+  </si>
+  <si>
+    <t>C_L17</t>
+  </si>
+  <si>
+    <t>C_L23</t>
+  </si>
+  <si>
+    <t>B_L03</t>
+  </si>
+  <si>
+    <t>C_L20</t>
+  </si>
+  <si>
+    <t>B_L10</t>
+  </si>
+  <si>
+    <t>A_L17</t>
+  </si>
+  <si>
+    <t>C_L01</t>
+  </si>
+  <si>
+    <t>B_L18</t>
+  </si>
+  <si>
+    <t>A_L08</t>
+  </si>
+  <si>
+    <t>B_L16</t>
+  </si>
+  <si>
+    <t>B_L02</t>
+  </si>
+  <si>
+    <t>B_L06</t>
+  </si>
+  <si>
+    <t>B_L22</t>
+  </si>
+  <si>
+    <t>B_L14</t>
+  </si>
+  <si>
+    <t>A_L06</t>
+  </si>
+  <si>
+    <t>C_L16</t>
+  </si>
+  <si>
+    <t>B_L28</t>
+  </si>
+  <si>
+    <t>A_L02</t>
   </si>
   <si>
     <t>C_L11</t>
   </si>
   <si>
-    <t>B_L30</t>
-  </si>
-  <si>
-    <t>C_L01</t>
-  </si>
-  <si>
-    <t>B_L06</t>
-  </si>
-  <si>
-    <t>B_L07</t>
+    <t>C_L14</t>
+  </si>
+  <si>
+    <t>A_L03</t>
   </si>
   <si>
     <t>A_L25</t>
   </si>
   <si>
-    <t>C_L05</t>
-  </si>
-  <si>
-    <t>A_L14</t>
-  </si>
-  <si>
-    <t>C_L07</t>
-  </si>
-  <si>
-    <t>B_L03</t>
-  </si>
-  <si>
-    <t>C_L15</t>
-  </si>
-  <si>
-    <t>C_L21</t>
+    <t>A_L29</t>
+  </si>
+  <si>
+    <t>A_L16</t>
+  </si>
+  <si>
+    <t>B_L13</t>
+  </si>
+  <si>
+    <t>B_L20</t>
+  </si>
+  <si>
+    <t>A_L23</t>
+  </si>
+  <si>
+    <t>B_L12</t>
+  </si>
+  <si>
+    <t>C_L27</t>
+  </si>
+  <si>
+    <t>A_L12</t>
+  </si>
+  <si>
+    <t>B_L15</t>
+  </si>
+  <si>
+    <t>A_L21</t>
+  </si>
+  <si>
+    <t>A_L24</t>
+  </si>
+  <si>
+    <t>A_L01</t>
+  </si>
+  <si>
+    <t>C_L24</t>
+  </si>
+  <si>
+    <t>C_L06</t>
+  </si>
+  <si>
+    <t>A_L04</t>
   </si>
   <si>
     <t>A_L27</t>
-  </si>
-  <si>
-    <t>C_L18</t>
-  </si>
-  <si>
-    <t>C_L06</t>
-  </si>
-  <si>
-    <t>A_L18</t>
-  </si>
-  <si>
-    <t>A_L29</t>
-  </si>
-  <si>
-    <t>A_L05</t>
-  </si>
-  <si>
-    <t>C_L25</t>
-  </si>
-  <si>
-    <t>A_L12</t>
-  </si>
-  <si>
-    <t>C_L29</t>
-  </si>
-  <si>
-    <t>B_L23</t>
-  </si>
-  <si>
-    <t>C_L10</t>
-  </si>
-  <si>
-    <t>B_L22</t>
-  </si>
-  <si>
-    <t>B_L26</t>
-  </si>
-  <si>
-    <t>C_L03</t>
-  </si>
-  <si>
-    <t>A_L20</t>
-  </si>
-  <si>
-    <t>C_L30</t>
-  </si>
-  <si>
-    <t>C_L28</t>
-  </si>
-  <si>
-    <t>A_L30</t>
-  </si>
-  <si>
-    <t>C_L17</t>
-  </si>
-  <si>
-    <t>C_L23</t>
-  </si>
-  <si>
-    <t>B_L02</t>
-  </si>
-  <si>
-    <t>C_L20</t>
-  </si>
-  <si>
-    <t>B_L09</t>
-  </si>
-  <si>
-    <t>A_L17</t>
-  </si>
-  <si>
-    <t>C_L02</t>
-  </si>
-  <si>
-    <t>B_L16</t>
-  </si>
-  <si>
-    <t>A_L08</t>
-  </si>
-  <si>
-    <t>B_L15</t>
-  </si>
-  <si>
-    <t>B_L01</t>
-  </si>
-  <si>
-    <t>B_L05</t>
-  </si>
-  <si>
-    <t>B_L20</t>
-  </si>
-  <si>
-    <t>B_L13</t>
-  </si>
-  <si>
-    <t>A_L06</t>
-  </si>
-  <si>
-    <t>C_L16</t>
-  </si>
-  <si>
-    <t>B_L29</t>
-  </si>
-  <si>
-    <t>A_L02</t>
-  </si>
-  <si>
-    <t>C_L09</t>
-  </si>
-  <si>
-    <t>C_L14</t>
-  </si>
-  <si>
-    <t>A_L03</t>
-  </si>
-  <si>
-    <t>A_L24</t>
-  </si>
-  <si>
-    <t>A_L28</t>
-  </si>
-  <si>
-    <t>A_L16</t>
-  </si>
-  <si>
-    <t>B_L12</t>
-  </si>
-  <si>
-    <t>B_L18</t>
-  </si>
-  <si>
-    <t>A_L22</t>
-  </si>
-  <si>
-    <t>B_L10</t>
-  </si>
-  <si>
-    <t>C_L27</t>
-  </si>
-  <si>
-    <t>A_L11</t>
-  </si>
-  <si>
-    <t>B_L14</t>
-  </si>
-  <si>
-    <t>A_L21</t>
-  </si>
-  <si>
-    <t>A_L23</t>
-  </si>
-  <si>
-    <t>A_L01</t>
-  </si>
-  <si>
-    <t>C_L24</t>
-  </si>
-  <si>
-    <t>C_L04</t>
-  </si>
-  <si>
-    <t>A_L04</t>
-  </si>
-  <si>
-    <t>A_L26</t>
   </si>
   <si>
     <t>A</t>
@@ -753,7 +753,7 @@
         <v>99</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2">
         <v>2</v>
@@ -762,46 +762,43 @@
         <v>3</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O2">
         <v>6</v>
       </c>
-      <c r="P2">
-        <v>47</v>
-      </c>
       <c r="Q2">
         <v>2</v>
       </c>
       <c r="R2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S2">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="T2">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -815,52 +812,52 @@
         <v>99</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O3">
         <v>6</v>
       </c>
       <c r="P3">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="Q3">
         <v>2</v>
       </c>
       <c r="R3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S3">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="T3">
         <v>7</v>
@@ -877,10 +874,10 @@
         <v>99</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4">
         <v>4</v>
@@ -892,40 +889,40 @@
         <v>3</v>
       </c>
       <c r="I4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O4">
         <v>6</v>
       </c>
       <c r="P4">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="Q4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R4">
         <v>3</v>
       </c>
       <c r="S4">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="T4">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -939,52 +936,55 @@
         <v>100</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5">
         <v>2</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O5">
         <v>6</v>
       </c>
       <c r="P5">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="Q5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R5">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="S5">
+        <v>12</v>
       </c>
       <c r="T5">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -998,43 +998,43 @@
         <v>100</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K6">
         <v>5</v>
       </c>
       <c r="L6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O6">
         <v>6</v>
       </c>
       <c r="P6">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="Q6">
         <v>1</v>
@@ -1043,10 +1043,10 @@
         <v>4</v>
       </c>
       <c r="S6">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T6">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -1060,31 +1060,31 @@
         <v>101</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K7">
         <v>6</v>
       </c>
       <c r="L7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M7">
         <v>6</v>
@@ -1096,16 +1096,19 @@
         <v>6</v>
       </c>
       <c r="P7">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="Q7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R7">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="S7">
+        <v>7</v>
       </c>
       <c r="T7">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -1119,34 +1122,34 @@
         <v>101</v>
       </c>
       <c r="D8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I8">
         <v>3</v>
       </c>
       <c r="J8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N8">
         <v>3</v>
@@ -1155,19 +1158,19 @@
         <v>6</v>
       </c>
       <c r="P8">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="Q8">
         <v>1</v>
       </c>
       <c r="R8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -1181,55 +1184,55 @@
         <v>99</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M9">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N9">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O9">
         <v>6</v>
       </c>
       <c r="P9">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="Q9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R9">
         <v>3</v>
       </c>
       <c r="S9">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="T9">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -1252,46 +1255,46 @@
         <v>4</v>
       </c>
       <c r="G10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J10">
         <v>5</v>
       </c>
       <c r="K10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L10">
         <v>5</v>
       </c>
       <c r="M10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O10">
         <v>6</v>
       </c>
       <c r="P10">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="Q10">
         <v>1</v>
       </c>
       <c r="R10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S10">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="T10">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -1305,52 +1308,52 @@
         <v>100</v>
       </c>
       <c r="D11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E11">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F11">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G11">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I11">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J11">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K11">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M11">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N11">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O11">
         <v>6</v>
       </c>
       <c r="P11">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="Q11">
         <v>1</v>
       </c>
       <c r="R11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S11">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="T11">
         <v>6</v>
@@ -1367,19 +1370,19 @@
         <v>100</v>
       </c>
       <c r="D12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E12">
         <v>4</v>
       </c>
       <c r="F12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I12">
         <v>5</v>
@@ -1388,13 +1391,13 @@
         <v>4</v>
       </c>
       <c r="K12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N12">
         <v>5</v>
@@ -1403,19 +1406,19 @@
         <v>6</v>
       </c>
       <c r="P12">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="Q12">
         <v>1</v>
       </c>
       <c r="R12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S12">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T12">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -1429,55 +1432,55 @@
         <v>101</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I13">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K13">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L13">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M13">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N13">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O13">
         <v>6</v>
       </c>
       <c r="P13">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Q13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S13">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T13">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -1491,43 +1494,43 @@
         <v>100</v>
       </c>
       <c r="D14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O14">
         <v>6</v>
       </c>
       <c r="P14">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="Q14">
         <v>1</v>
@@ -1536,7 +1539,7 @@
         <v>3</v>
       </c>
       <c r="S14">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T14">
         <v>4</v>
@@ -1550,58 +1553,58 @@
         <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15">
         <v>2</v>
       </c>
       <c r="H15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I15">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J15">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O15">
         <v>6</v>
       </c>
       <c r="P15">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Q15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T15">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -1615,55 +1618,55 @@
         <v>100</v>
       </c>
       <c r="D16">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E16">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F16">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G16">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I16">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J16">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K16">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L16">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M16">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="N16">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O16">
         <v>6</v>
       </c>
       <c r="P16">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="Q16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S16">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="T16">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:20">
@@ -1677,55 +1680,55 @@
         <v>100</v>
       </c>
       <c r="D17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17">
         <v>3</v>
       </c>
       <c r="F17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L17">
         <v>7</v>
       </c>
       <c r="M17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O17">
         <v>6</v>
       </c>
       <c r="P17">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="Q17">
         <v>2</v>
       </c>
       <c r="R17">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S17">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="T17">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:20">
@@ -1739,55 +1742,55 @@
         <v>99</v>
       </c>
       <c r="D18">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E18">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F18">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G18">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H18">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I18">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J18">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L18">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M18">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N18">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O18">
         <v>6</v>
       </c>
       <c r="P18">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="Q18">
         <v>1</v>
       </c>
       <c r="R18">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S18">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="T18">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:20">
@@ -1801,19 +1804,19 @@
         <v>101</v>
       </c>
       <c r="D19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E19">
         <v>2</v>
       </c>
       <c r="F19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I19">
         <v>5</v>
@@ -1822,22 +1825,22 @@
         <v>5</v>
       </c>
       <c r="K19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M19">
         <v>5</v>
       </c>
       <c r="N19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O19">
         <v>6</v>
       </c>
       <c r="P19">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="Q19">
         <v>2</v>
@@ -1846,10 +1849,10 @@
         <v>3</v>
       </c>
       <c r="S19">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T19">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:20">
@@ -1863,52 +1866,52 @@
         <v>99</v>
       </c>
       <c r="D20">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E20">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F20">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G20">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H20">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I20">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J20">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K20">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M20">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N20">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O20">
         <v>6</v>
       </c>
       <c r="P20">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="Q20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S20">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="T20">
         <v>4</v>
@@ -1925,7 +1928,7 @@
         <v>101</v>
       </c>
       <c r="D21">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E21">
         <v>3</v>
@@ -1934,46 +1937,46 @@
         <v>3</v>
       </c>
       <c r="G21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H21">
         <v>3</v>
       </c>
       <c r="I21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J21">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K21">
         <v>5</v>
       </c>
       <c r="L21">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M21">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N21">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O21">
         <v>6</v>
       </c>
       <c r="P21">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="Q21">
         <v>1</v>
       </c>
       <c r="R21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S21">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="T21">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:20">
@@ -1987,25 +1990,25 @@
         <v>100</v>
       </c>
       <c r="D22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G22">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H22">
         <v>3</v>
       </c>
       <c r="I22">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J22">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K22">
         <v>4</v>
@@ -2014,7 +2017,7 @@
         <v>4</v>
       </c>
       <c r="M22">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N22">
         <v>5</v>
@@ -2023,19 +2026,19 @@
         <v>6</v>
       </c>
       <c r="P22">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="Q22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R22">
         <v>3</v>
       </c>
       <c r="S22">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="T22">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:20">
@@ -2049,43 +2052,43 @@
         <v>101</v>
       </c>
       <c r="D23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I23">
         <v>4</v>
       </c>
       <c r="J23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L23">
         <v>3</v>
       </c>
       <c r="M23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O23">
         <v>6</v>
       </c>
       <c r="P23">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="Q23">
         <v>2</v>
@@ -2094,10 +2097,10 @@
         <v>3</v>
       </c>
       <c r="S23">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="T23">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:20">
@@ -2111,28 +2114,28 @@
         <v>101</v>
       </c>
       <c r="D24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E24">
         <v>2</v>
       </c>
       <c r="F24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H24">
         <v>2</v>
       </c>
       <c r="I24">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J24">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L24">
         <v>5</v>
@@ -2147,19 +2150,19 @@
         <v>6</v>
       </c>
       <c r="P24">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="Q24">
         <v>2</v>
       </c>
       <c r="R24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S24">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T24">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:20">
@@ -2176,13 +2179,13 @@
         <v>3</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F25">
         <v>3</v>
       </c>
       <c r="G25">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H25">
         <v>3</v>
@@ -2191,16 +2194,16 @@
         <v>6</v>
       </c>
       <c r="J25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K25">
         <v>5</v>
       </c>
       <c r="L25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N25">
         <v>6</v>
@@ -2218,10 +2221,10 @@
         <v>4</v>
       </c>
       <c r="S25">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T25">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26" spans="1:20">
@@ -2235,13 +2238,13 @@
         <v>101</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E26">
         <v>1</v>
       </c>
       <c r="F26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -2250,10 +2253,10 @@
         <v>1</v>
       </c>
       <c r="I26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J26">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K26">
         <v>5</v>
@@ -2265,25 +2268,25 @@
         <v>5</v>
       </c>
       <c r="N26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O26">
         <v>6</v>
       </c>
       <c r="P26">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="Q26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R26">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S26">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T26">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:20">
@@ -2297,22 +2300,22 @@
         <v>101</v>
       </c>
       <c r="D27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E27">
         <v>3</v>
       </c>
       <c r="F27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G27">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J27">
         <v>3</v>
@@ -2333,19 +2336,19 @@
         <v>6</v>
       </c>
       <c r="P27">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="Q27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R27">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S27">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="T27">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:20">
@@ -2359,19 +2362,19 @@
         <v>99</v>
       </c>
       <c r="D28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I28">
         <v>7</v>
@@ -2380,34 +2383,34 @@
         <v>7</v>
       </c>
       <c r="K28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M28">
         <v>6</v>
       </c>
       <c r="N28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O28">
         <v>6</v>
       </c>
       <c r="P28">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Q28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R28">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S28">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T28">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:20">
@@ -2421,7 +2424,7 @@
         <v>99</v>
       </c>
       <c r="D29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E29">
         <v>4</v>
@@ -2430,10 +2433,10 @@
         <v>4</v>
       </c>
       <c r="G29">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H29">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I29">
         <v>5</v>
@@ -2445,10 +2448,10 @@
         <v>4</v>
       </c>
       <c r="L29">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M29">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N29">
         <v>4</v>
@@ -2457,7 +2460,7 @@
         <v>6</v>
       </c>
       <c r="P29">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="Q29">
         <v>2</v>
@@ -2465,8 +2468,11 @@
       <c r="R29">
         <v>3</v>
       </c>
+      <c r="S29">
+        <v>28</v>
+      </c>
       <c r="T29">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:20">
@@ -2486,46 +2492,46 @@
         <v>3</v>
       </c>
       <c r="F30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G30">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I30">
         <v>5</v>
       </c>
       <c r="J30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L30">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M30">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N30">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O30">
         <v>6</v>
       </c>
       <c r="P30">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="Q30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S30">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="T30">
         <v>5</v>
@@ -2545,40 +2551,40 @@
         <v>1</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F31">
         <v>2</v>
       </c>
       <c r="G31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I31">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J31">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K31">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L31">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M31">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N31">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O31">
         <v>6</v>
       </c>
       <c r="P31">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="Q31">
         <v>2</v>
@@ -2587,10 +2593,10 @@
         <v>4</v>
       </c>
       <c r="S31">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="T31">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:20">
@@ -2604,52 +2610,52 @@
         <v>99</v>
       </c>
       <c r="D32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F32">
         <v>1</v>
       </c>
       <c r="G32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H32">
         <v>1</v>
       </c>
       <c r="I32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J32">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K32">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L32">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M32">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O32">
         <v>6</v>
       </c>
       <c r="P32">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="Q32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R32">
         <v>3</v>
       </c>
       <c r="S32">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="T32">
         <v>4</v>
@@ -2666,55 +2672,55 @@
         <v>101</v>
       </c>
       <c r="D33">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E33">
         <v>2</v>
       </c>
       <c r="F33">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L33">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M33">
         <v>6</v>
       </c>
       <c r="N33">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O33">
         <v>6</v>
       </c>
       <c r="P33">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="Q33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R33">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S33">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T33">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:20">
@@ -2728,7 +2734,7 @@
         <v>100</v>
       </c>
       <c r="D34">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E34">
         <v>3</v>
@@ -2743,40 +2749,40 @@
         <v>3</v>
       </c>
       <c r="I34">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J34">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K34">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L34">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M34">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N34">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O34">
         <v>6</v>
       </c>
       <c r="P34">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="Q34">
         <v>1</v>
       </c>
       <c r="R34">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S34">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="T34">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:20">
@@ -2790,34 +2796,34 @@
         <v>101</v>
       </c>
       <c r="D35">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E35">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F35">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G35">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H35">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J35">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K35">
         <v>4</v>
       </c>
       <c r="L35">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M35">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N35">
         <v>4</v>
@@ -2826,19 +2832,19 @@
         <v>6</v>
       </c>
       <c r="P35">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="Q35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R35">
         <v>3</v>
       </c>
       <c r="S35">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T35">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36" spans="1:20">
@@ -2852,7 +2858,7 @@
         <v>100</v>
       </c>
       <c r="D36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E36">
         <v>1</v>
@@ -2861,7 +2867,7 @@
         <v>1</v>
       </c>
       <c r="G36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H36">
         <v>1</v>
@@ -2870,7 +2876,7 @@
         <v>5</v>
       </c>
       <c r="J36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K36">
         <v>6</v>
@@ -2879,10 +2885,10 @@
         <v>4</v>
       </c>
       <c r="M36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O36">
         <v>6</v>
@@ -2891,16 +2897,16 @@
         <v>33</v>
       </c>
       <c r="Q36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R36">
         <v>3</v>
       </c>
       <c r="S36">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T36">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:20">
@@ -2914,13 +2920,13 @@
         <v>100</v>
       </c>
       <c r="D37">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E37">
         <v>4</v>
       </c>
       <c r="F37">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G37">
         <v>4</v>
@@ -2929,28 +2935,28 @@
         <v>4</v>
       </c>
       <c r="I37">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J37">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K37">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L37">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M37">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N37">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O37">
         <v>6</v>
       </c>
       <c r="P37">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="Q37">
         <v>1</v>
@@ -2959,10 +2965,10 @@
         <v>4</v>
       </c>
       <c r="S37">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="T37">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38" spans="1:20">
@@ -2976,43 +2982,43 @@
         <v>101</v>
       </c>
       <c r="D38">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G38">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H38">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I38">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J38">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K38">
         <v>6</v>
       </c>
       <c r="L38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N38">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O38">
         <v>6</v>
       </c>
       <c r="P38">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q38">
         <v>1</v>
@@ -3021,10 +3027,10 @@
         <v>3</v>
       </c>
       <c r="S38">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="T38">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:20">
@@ -3053,10 +3059,10 @@
         <v>1</v>
       </c>
       <c r="I39">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J39">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K39">
         <v>6</v>
@@ -3074,19 +3080,19 @@
         <v>6</v>
       </c>
       <c r="P39">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="Q39">
         <v>1</v>
       </c>
       <c r="R39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S39">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="T39">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:20">
@@ -3106,25 +3112,25 @@
         <v>2</v>
       </c>
       <c r="F40">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I40">
         <v>4</v>
       </c>
       <c r="J40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K40">
         <v>5</v>
       </c>
       <c r="L40">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M40">
         <v>5</v>
@@ -3136,16 +3142,16 @@
         <v>6</v>
       </c>
       <c r="P40">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="Q40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R40">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S40">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="T40">
         <v>5</v>
@@ -3162,7 +3168,7 @@
         <v>101</v>
       </c>
       <c r="D41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E41">
         <v>2</v>
@@ -3171,7 +3177,7 @@
         <v>2</v>
       </c>
       <c r="G41">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H41">
         <v>2</v>
@@ -3180,25 +3186,25 @@
         <v>5</v>
       </c>
       <c r="J41">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K41">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L41">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M41">
         <v>6</v>
       </c>
       <c r="N41">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O41">
         <v>6</v>
       </c>
       <c r="P41">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="Q41">
         <v>2</v>
@@ -3207,10 +3213,10 @@
         <v>3</v>
       </c>
       <c r="S41">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T41">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42" spans="1:20">
@@ -3221,58 +3227,58 @@
         <v>60</v>
       </c>
       <c r="C42" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D42">
         <v>3</v>
       </c>
       <c r="E42">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F42">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G42">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H42">
         <v>3</v>
       </c>
       <c r="I42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J42">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L42">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M42">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N42">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O42">
         <v>6</v>
       </c>
       <c r="P42">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="Q42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R42">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S42">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="T42">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43" spans="1:20">
@@ -3289,7 +3295,7 @@
         <v>3</v>
       </c>
       <c r="E43">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F43">
         <v>2</v>
@@ -3298,43 +3304,43 @@
         <v>3</v>
       </c>
       <c r="H43">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I43">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J43">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K43">
         <v>5</v>
       </c>
       <c r="L43">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M43">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N43">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O43">
         <v>6</v>
       </c>
       <c r="P43">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="Q43">
         <v>1</v>
       </c>
       <c r="R43">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S43">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="T43">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44" spans="1:20">
@@ -3351,16 +3357,16 @@
         <v>3</v>
       </c>
       <c r="E44">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F44">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G44">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H44">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I44">
         <v>4</v>
@@ -3369,7 +3375,7 @@
         <v>3</v>
       </c>
       <c r="K44">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L44">
         <v>3</v>
@@ -3378,13 +3384,13 @@
         <v>4</v>
       </c>
       <c r="N44">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O44">
         <v>6</v>
       </c>
       <c r="P44">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="Q44">
         <v>1</v>
@@ -3393,10 +3399,10 @@
         <v>4</v>
       </c>
       <c r="S44">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="T44">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45" spans="1:20">
@@ -3410,28 +3416,28 @@
         <v>100</v>
       </c>
       <c r="D45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E45">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F45">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G45">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H45">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K45">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L45">
         <v>5</v>
@@ -3440,13 +3446,13 @@
         <v>4</v>
       </c>
       <c r="N45">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O45">
         <v>6</v>
       </c>
       <c r="P45">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="Q45">
         <v>2</v>
@@ -3455,10 +3461,10 @@
         <v>3</v>
       </c>
       <c r="S45">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T45">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46" spans="1:20">
@@ -3475,7 +3481,7 @@
         <v>2</v>
       </c>
       <c r="E46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F46">
         <v>2</v>
@@ -3484,25 +3490,25 @@
         <v>2</v>
       </c>
       <c r="H46">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I46">
         <v>4</v>
       </c>
       <c r="J46">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K46">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L46">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M46">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N46">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O46">
         <v>6</v>
@@ -3514,13 +3520,13 @@
         <v>1</v>
       </c>
       <c r="R46">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S46">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T46">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47" spans="1:20">
@@ -3534,43 +3540,43 @@
         <v>100</v>
       </c>
       <c r="D47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E47">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F47">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G47">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H47">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I47">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J47">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K47">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L47">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M47">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N47">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O47">
         <v>6</v>
       </c>
       <c r="P47">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="Q47">
         <v>1</v>
@@ -3579,10 +3585,10 @@
         <v>3</v>
       </c>
       <c r="S47">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T47">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48" spans="1:20">
@@ -3596,52 +3602,49 @@
         <v>99</v>
       </c>
       <c r="D48">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E48">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H48">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I48">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J48">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K48">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L48">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M48">
         <v>5</v>
       </c>
       <c r="N48">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O48">
         <v>6</v>
       </c>
-      <c r="P48">
-        <v>53</v>
-      </c>
       <c r="Q48">
         <v>1</v>
       </c>
       <c r="R48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S48">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="T48">
         <v>4</v>
@@ -3658,55 +3661,55 @@
         <v>101</v>
       </c>
       <c r="D49">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E49">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F49">
         <v>3</v>
       </c>
       <c r="G49">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H49">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I49">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J49">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K49">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L49">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M49">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O49">
         <v>6</v>
       </c>
       <c r="P49">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="Q49">
         <v>2</v>
       </c>
       <c r="R49">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S49">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="T49">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50" spans="1:20">
@@ -3720,55 +3723,55 @@
         <v>100</v>
       </c>
       <c r="D50">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E50">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F50">
         <v>4</v>
       </c>
       <c r="G50">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H50">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I50">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J50">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K50">
         <v>4</v>
       </c>
       <c r="L50">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M50">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N50">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O50">
         <v>6</v>
       </c>
       <c r="P50">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="Q50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R50">
         <v>3</v>
       </c>
       <c r="S50">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="T50">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51" spans="1:20">
@@ -3782,55 +3785,55 @@
         <v>99</v>
       </c>
       <c r="D51">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E51">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F51">
         <v>2</v>
       </c>
       <c r="G51">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H51">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I51">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J51">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K51">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L51">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M51">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N51">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O51">
         <v>6</v>
       </c>
       <c r="P51">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="Q51">
         <v>2</v>
       </c>
       <c r="R51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S51">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="T51">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52" spans="1:20">
@@ -3844,16 +3847,16 @@
         <v>100</v>
       </c>
       <c r="D52">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E52">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F52">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H52">
         <v>2</v>
@@ -3865,22 +3868,22 @@
         <v>4</v>
       </c>
       <c r="K52">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L52">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M52">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N52">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O52">
         <v>6</v>
       </c>
       <c r="P52">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="Q52">
         <v>1</v>
@@ -3889,7 +3892,7 @@
         <v>3</v>
       </c>
       <c r="S52">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52">
         <v>4</v>
@@ -3906,19 +3909,19 @@
         <v>100</v>
       </c>
       <c r="D53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E53">
         <v>1</v>
       </c>
       <c r="F53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I53">
         <v>5</v>
@@ -3930,19 +3933,19 @@
         <v>5</v>
       </c>
       <c r="L53">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M53">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N53">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O53">
         <v>6</v>
       </c>
       <c r="P53">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="Q53">
         <v>1</v>
@@ -3951,10 +3954,10 @@
         <v>4</v>
       </c>
       <c r="S53">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T53">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54" spans="1:20">
@@ -3968,7 +3971,7 @@
         <v>100</v>
       </c>
       <c r="D54">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E54">
         <v>4</v>
@@ -3980,40 +3983,40 @@
         <v>3</v>
       </c>
       <c r="H54">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I54">
         <v>4</v>
       </c>
       <c r="J54">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K54">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L54">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M54">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N54">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O54">
         <v>6</v>
       </c>
       <c r="P54">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="Q54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R54">
         <v>3</v>
       </c>
       <c r="S54">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T54">
         <v>6</v>
@@ -4030,43 +4033,43 @@
         <v>100</v>
       </c>
       <c r="D55">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E55">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F55">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G55">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H55">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I55">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J55">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K55">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L55">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M55">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N55">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O55">
         <v>6</v>
       </c>
       <c r="P55">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="Q55">
         <v>1</v>
@@ -4075,10 +4078,10 @@
         <v>3</v>
       </c>
       <c r="S55">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="T55">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56" spans="1:20">
@@ -4092,55 +4095,55 @@
         <v>100</v>
       </c>
       <c r="D56">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E56">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F56">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I56">
         <v>4</v>
       </c>
       <c r="J56">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K56">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L56">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M56">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N56">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O56">
         <v>6</v>
       </c>
       <c r="P56">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="Q56">
         <v>1</v>
       </c>
       <c r="R56">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S56">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="T56">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57" spans="1:20">
@@ -4169,40 +4172,40 @@
         <v>1</v>
       </c>
       <c r="I57">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J57">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K57">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L57">
         <v>7</v>
       </c>
       <c r="M57">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N57">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O57">
         <v>6</v>
       </c>
       <c r="P57">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="Q57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R57">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S57">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T57">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58" spans="1:20">
@@ -4216,28 +4219,28 @@
         <v>101</v>
       </c>
       <c r="D58">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E58">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F58">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G58">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H58">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I58">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J58">
         <v>4</v>
       </c>
       <c r="K58">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L58">
         <v>4</v>
@@ -4246,25 +4249,25 @@
         <v>5</v>
       </c>
       <c r="N58">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O58">
         <v>6</v>
       </c>
       <c r="P58">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Q58">
         <v>2</v>
       </c>
       <c r="R58">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S58">
         <v>5</v>
       </c>
       <c r="T58">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59" spans="1:20">
@@ -4278,55 +4281,55 @@
         <v>100</v>
       </c>
       <c r="D59">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E59">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F59">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G59">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H59">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I59">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J59">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K59">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L59">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M59">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N59">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O59">
         <v>6</v>
       </c>
       <c r="P59">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="Q59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R59">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S59">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="T59">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="60" spans="1:20">
@@ -4340,7 +4343,7 @@
         <v>99</v>
       </c>
       <c r="D60">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E60">
         <v>4</v>
@@ -4352,43 +4355,43 @@
         <v>3</v>
       </c>
       <c r="H60">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I60">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J60">
         <v>5</v>
       </c>
       <c r="K60">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L60">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M60">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N60">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O60">
         <v>6</v>
       </c>
       <c r="P60">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="Q60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R60">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S60">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="T60">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61" spans="1:20">
@@ -4402,55 +4405,52 @@
         <v>101</v>
       </c>
       <c r="D61">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E61">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F61">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G61">
         <v>3</v>
       </c>
       <c r="H61">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I61">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J61">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K61">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L61">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M61">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N61">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O61">
         <v>6</v>
       </c>
-      <c r="P61">
-        <v>44</v>
-      </c>
       <c r="Q61">
         <v>1</v>
       </c>
       <c r="R61">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S61">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="T61">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62" spans="1:20">
@@ -4464,22 +4464,22 @@
         <v>101</v>
       </c>
       <c r="D62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G62">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H62">
         <v>1</v>
       </c>
       <c r="I62">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J62">
         <v>5</v>
@@ -4488,31 +4488,31 @@
         <v>4</v>
       </c>
       <c r="L62">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M62">
         <v>5</v>
       </c>
       <c r="N62">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O62">
         <v>6</v>
       </c>
       <c r="P62">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="Q62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R62">
         <v>3</v>
       </c>
       <c r="S62">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="T62">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="63" spans="1:20">
@@ -4526,19 +4526,19 @@
         <v>99</v>
       </c>
       <c r="D63">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E63">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I63">
         <v>4</v>
@@ -4547,13 +4547,13 @@
         <v>5</v>
       </c>
       <c r="K63">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L63">
         <v>5</v>
       </c>
       <c r="M63">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N63">
         <v>5</v>
@@ -4562,19 +4562,19 @@
         <v>6</v>
       </c>
       <c r="P63">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="Q63">
         <v>1</v>
       </c>
       <c r="R63">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S63">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="T63">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="64" spans="1:20">
@@ -4588,55 +4588,55 @@
         <v>99</v>
       </c>
       <c r="D64">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E64">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F64">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G64">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H64">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I64">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J64">
         <v>5</v>
       </c>
       <c r="K64">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L64">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M64">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N64">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O64">
         <v>6</v>
       </c>
       <c r="P64">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R64">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S64">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T64">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65" spans="1:20">
@@ -4653,52 +4653,52 @@
         <v>2</v>
       </c>
       <c r="E65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G65">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I65">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J65">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K65">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L65">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M65">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N65">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O65">
         <v>6</v>
       </c>
       <c r="P65">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q65">
         <v>1</v>
       </c>
       <c r="R65">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S65">
+        <v>9</v>
+      </c>
+      <c r="T65">
         <v>8</v>
-      </c>
-      <c r="T65">
-        <v>6</v>
       </c>
     </row>
     <row r="66" spans="1:20">
@@ -4712,13 +4712,13 @@
         <v>99</v>
       </c>
       <c r="D66">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E66">
         <v>1</v>
       </c>
       <c r="F66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G66">
         <v>1</v>
@@ -4733,13 +4733,13 @@
         <v>6</v>
       </c>
       <c r="K66">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L66">
         <v>6</v>
       </c>
       <c r="M66">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N66">
         <v>5</v>
@@ -4748,19 +4748,19 @@
         <v>6</v>
       </c>
       <c r="P66">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="Q66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R66">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S66">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="T66">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67" spans="1:20">
@@ -4774,25 +4774,25 @@
         <v>100</v>
       </c>
       <c r="D67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E67">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F67">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G67">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H67">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I67">
         <v>4</v>
       </c>
       <c r="J67">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K67">
         <v>4</v>
@@ -4801,7 +4801,7 @@
         <v>4</v>
       </c>
       <c r="M67">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N67">
         <v>4</v>
@@ -4810,7 +4810,7 @@
         <v>6</v>
       </c>
       <c r="P67">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="Q67">
         <v>2</v>
@@ -4819,10 +4819,10 @@
         <v>4</v>
       </c>
       <c r="S67">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="T67">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68" spans="1:20">
@@ -4845,43 +4845,43 @@
         <v>3</v>
       </c>
       <c r="G68">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H68">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I68">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J68">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K68">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L68">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M68">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N68">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O68">
         <v>6</v>
       </c>
       <c r="P68">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q68">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R68">
         <v>3</v>
       </c>
       <c r="S68">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="T68">
         <v>5</v>
@@ -4898,10 +4898,10 @@
         <v>99</v>
       </c>
       <c r="D69">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E69">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F69">
         <v>3</v>
@@ -4910,43 +4910,43 @@
         <v>4</v>
       </c>
       <c r="H69">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I69">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J69">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K69">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L69">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M69">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N69">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O69">
         <v>6</v>
       </c>
       <c r="P69">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="Q69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R69">
         <v>3</v>
       </c>
       <c r="S69">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="T69">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:20">
@@ -4960,55 +4960,55 @@
         <v>100</v>
       </c>
       <c r="D70">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E70">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F70">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I70">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J70">
         <v>3</v>
       </c>
       <c r="K70">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L70">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M70">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N70">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O70">
         <v>6</v>
       </c>
       <c r="P70">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="Q70">
         <v>1</v>
       </c>
       <c r="R70">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S70">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="T70">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="71" spans="1:20">
@@ -5022,43 +5022,43 @@
         <v>101</v>
       </c>
       <c r="D71">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E71">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F71">
         <v>2</v>
       </c>
       <c r="G71">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H71">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I71">
         <v>4</v>
       </c>
       <c r="J71">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K71">
         <v>4</v>
       </c>
       <c r="L71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M71">
         <v>5</v>
       </c>
       <c r="N71">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O71">
         <v>6</v>
       </c>
       <c r="P71">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="Q71">
         <v>1</v>
@@ -5067,10 +5067,10 @@
         <v>3</v>
       </c>
       <c r="S71">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="T71">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="72" spans="1:20">
@@ -5084,52 +5084,52 @@
         <v>99</v>
       </c>
       <c r="D72">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E72">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F72">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G72">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H72">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I72">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J72">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K72">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L72">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M72">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N72">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O72">
         <v>6</v>
       </c>
       <c r="P72">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q72">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R72">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S72">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="T72">
         <v>6</v>
@@ -5146,55 +5146,55 @@
         <v>100</v>
       </c>
       <c r="D73">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F73">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H73">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I73">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J73">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K73">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L73">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M73">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N73">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O73">
         <v>6</v>
       </c>
       <c r="P73">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="Q73">
         <v>1</v>
       </c>
       <c r="R73">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S73">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="T73">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74" spans="1:20">
@@ -5208,52 +5208,52 @@
         <v>99</v>
       </c>
       <c r="D74">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E74">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F74">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G74">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H74">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I74">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J74">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K74">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L74">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M74">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N74">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O74">
         <v>6</v>
       </c>
       <c r="P74">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="Q74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S74">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="T74">
         <v>5</v>
@@ -5270,7 +5270,7 @@
         <v>99</v>
       </c>
       <c r="D75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E75">
         <v>2</v>
@@ -5279,46 +5279,46 @@
         <v>1</v>
       </c>
       <c r="G75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H75">
         <v>1</v>
       </c>
       <c r="I75">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J75">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K75">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L75">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M75">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N75">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O75">
         <v>6</v>
       </c>
       <c r="P75">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="Q75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R75">
         <v>4</v>
       </c>
       <c r="S75">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="T75">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76" spans="1:20">
@@ -5332,52 +5332,52 @@
         <v>99</v>
       </c>
       <c r="D76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G76">
         <v>3</v>
       </c>
       <c r="H76">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I76">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J76">
         <v>5</v>
       </c>
       <c r="K76">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L76">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M76">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N76">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O76">
         <v>6</v>
       </c>
       <c r="P76">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="Q76">
         <v>1</v>
       </c>
       <c r="R76">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S76">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="T76">
         <v>5</v>
@@ -5400,13 +5400,13 @@
         <v>3</v>
       </c>
       <c r="F77">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G77">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H77">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I77">
         <v>4</v>
@@ -5418,10 +5418,10 @@
         <v>4</v>
       </c>
       <c r="L77">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M77">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N77">
         <v>4</v>
@@ -5436,7 +5436,7 @@
         <v>1</v>
       </c>
       <c r="R77">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S77">
         <v>13</v>
@@ -5456,55 +5456,55 @@
         <v>101</v>
       </c>
       <c r="D78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E78">
         <v>1</v>
       </c>
       <c r="F78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I78">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J78">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K78">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L78">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M78">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N78">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O78">
         <v>6</v>
       </c>
       <c r="P78">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="Q78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R78">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S78">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T78">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="79" spans="1:20">
@@ -5518,7 +5518,7 @@
         <v>99</v>
       </c>
       <c r="D79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E79">
         <v>1</v>
@@ -5533,40 +5533,40 @@
         <v>1</v>
       </c>
       <c r="I79">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J79">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K79">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L79">
         <v>6</v>
       </c>
       <c r="M79">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N79">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O79">
         <v>6</v>
       </c>
       <c r="P79">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R79">
         <v>3</v>
       </c>
       <c r="S79">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T79">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80" spans="1:20">
@@ -5580,55 +5580,55 @@
         <v>99</v>
       </c>
       <c r="D80">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E80">
         <v>1</v>
       </c>
       <c r="F80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I80">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J80">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K80">
         <v>7</v>
       </c>
       <c r="L80">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M80">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N80">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O80">
         <v>6</v>
       </c>
       <c r="P80">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="Q80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R80">
         <v>3</v>
       </c>
       <c r="S80">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="T80">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/data/T3_leader_cleaned.xlsx
+++ b/data/T3_leader_cleaned.xlsx
@@ -82,232 +82,232 @@
     <t>LeaderJobLevel</t>
   </si>
   <si>
+    <t>A_L14</t>
+  </si>
+  <si>
+    <t>A_L21</t>
+  </si>
+  <si>
+    <t>A_L08</t>
+  </si>
+  <si>
+    <t>B_L14</t>
+  </si>
+  <si>
+    <t>B_L08</t>
+  </si>
+  <si>
+    <t>C_L19</t>
+  </si>
+  <si>
+    <t>C_L25</t>
+  </si>
+  <si>
+    <t>A_L11</t>
+  </si>
+  <si>
+    <t>A_L10</t>
+  </si>
+  <si>
+    <t>B_L26</t>
+  </si>
+  <si>
+    <t>B_L24</t>
+  </si>
+  <si>
+    <t>C_L12</t>
+  </si>
+  <si>
+    <t>C_L02</t>
+  </si>
+  <si>
+    <t>C_L03</t>
+  </si>
+  <si>
+    <t>B_L10</t>
+  </si>
+  <si>
+    <t>B_L12</t>
+  </si>
+  <si>
+    <t>A_L28</t>
+  </si>
+  <si>
+    <t>C_L07</t>
+  </si>
+  <si>
     <t>A_L15</t>
   </si>
   <si>
-    <t>A_L21</t>
-  </si>
-  <si>
-    <t>A_L08</t>
-  </si>
-  <si>
-    <t>B_L14</t>
+    <t>C_L09</t>
+  </si>
+  <si>
+    <t>B_L07</t>
+  </si>
+  <si>
+    <t>C_L14</t>
+  </si>
+  <si>
+    <t>C_L21</t>
+  </si>
+  <si>
+    <t>B_L01</t>
+  </si>
+  <si>
+    <t>C_L18</t>
+  </si>
+  <si>
+    <t>C_L08</t>
+  </si>
+  <si>
+    <t>A_L18</t>
+  </si>
+  <si>
+    <t>B_L03</t>
   </si>
   <si>
     <t>B_L09</t>
   </si>
   <si>
+    <t>A_L06</t>
+  </si>
+  <si>
+    <t>C_L24</t>
+  </si>
+  <si>
+    <t>A_L13</t>
+  </si>
+  <si>
+    <t>C_L29</t>
+  </si>
+  <si>
+    <t>B_L29</t>
+  </si>
+  <si>
+    <t>C_L11</t>
+  </si>
+  <si>
+    <t>B_L27</t>
+  </si>
+  <si>
+    <t>B_L30</t>
+  </si>
+  <si>
+    <t>C_L05</t>
+  </si>
+  <si>
+    <t>A_L22</t>
+  </si>
+  <si>
+    <t>C_L30</t>
+  </si>
+  <si>
+    <t>C_L28</t>
+  </si>
+  <si>
+    <t>B_L04</t>
+  </si>
+  <si>
+    <t>C_L17</t>
+  </si>
+  <si>
+    <t>C_L22</t>
+  </si>
+  <si>
+    <t>B_L06</t>
+  </si>
+  <si>
     <t>C_L20</t>
   </si>
   <si>
+    <t>B_L15</t>
+  </si>
+  <si>
+    <t>A_L17</t>
+  </si>
+  <si>
+    <t>C_L04</t>
+  </si>
+  <si>
+    <t>B_L22</t>
+  </si>
+  <si>
+    <t>A_L09</t>
+  </si>
+  <si>
+    <t>B_L21</t>
+  </si>
+  <si>
+    <t>B_L05</t>
+  </si>
+  <si>
+    <t>B_L25</t>
+  </si>
+  <si>
+    <t>B_L19</t>
+  </si>
+  <si>
+    <t>A_L07</t>
+  </si>
+  <si>
+    <t>C_L16</t>
+  </si>
+  <si>
+    <t>C_L01</t>
+  </si>
+  <si>
+    <t>A_L02</t>
+  </si>
+  <si>
+    <t>C_L10</t>
+  </si>
+  <si>
+    <t>C_L13</t>
+  </si>
+  <si>
+    <t>A_L04</t>
+  </si>
+  <si>
+    <t>A_L27</t>
+  </si>
+  <si>
+    <t>B_L02</t>
+  </si>
+  <si>
+    <t>A_L16</t>
+  </si>
+  <si>
+    <t>B_L18</t>
+  </si>
+  <si>
+    <t>B_L23</t>
+  </si>
+  <si>
+    <t>A_L25</t>
+  </si>
+  <si>
+    <t>B_L16</t>
+  </si>
+  <si>
     <t>C_L26</t>
   </si>
   <si>
-    <t>A_L11</t>
-  </si>
-  <si>
-    <t>A_L10</t>
-  </si>
-  <si>
-    <t>B_L26</t>
-  </si>
-  <si>
-    <t>B_L24</t>
-  </si>
-  <si>
-    <t>C_L13</t>
-  </si>
-  <si>
-    <t>C_L02</t>
-  </si>
-  <si>
-    <t>C_L03</t>
-  </si>
-  <si>
-    <t>B_L11</t>
-  </si>
-  <si>
-    <t>B_L12</t>
-  </si>
-  <si>
-    <t>A_L28</t>
-  </si>
-  <si>
-    <t>C_L07</t>
-  </si>
-  <si>
-    <t>A_L16</t>
-  </si>
-  <si>
-    <t>C_L10</t>
-  </si>
-  <si>
-    <t>B_L08</t>
-  </si>
-  <si>
-    <t>C_L16</t>
-  </si>
-  <si>
-    <t>C_L22</t>
-  </si>
-  <si>
-    <t>B_L01</t>
-  </si>
-  <si>
-    <t>C_L19</t>
-  </si>
-  <si>
-    <t>C_L08</t>
-  </si>
-  <si>
-    <t>A_L20</t>
-  </si>
-  <si>
-    <t>B_L03</t>
-  </si>
-  <si>
-    <t>A_L06</t>
-  </si>
-  <si>
-    <t>C_L25</t>
-  </si>
-  <si>
-    <t>A_L14</t>
-  </si>
-  <si>
-    <t>C_L29</t>
-  </si>
-  <si>
-    <t>B_L29</t>
-  </si>
-  <si>
-    <t>C_L12</t>
-  </si>
-  <si>
-    <t>B_L27</t>
-  </si>
-  <si>
-    <t>B_L30</t>
-  </si>
-  <si>
-    <t>C_L05</t>
-  </si>
-  <si>
-    <t>A_L22</t>
-  </si>
-  <si>
-    <t>C_L30</t>
-  </si>
-  <si>
-    <t>C_L28</t>
-  </si>
-  <si>
-    <t>B_L04</t>
-  </si>
-  <si>
-    <t>C_L18</t>
+    <t>A_L12</t>
+  </si>
+  <si>
+    <t>B_L20</t>
+  </si>
+  <si>
+    <t>A_L23</t>
+  </si>
+  <si>
+    <t>A_L26</t>
+  </si>
+  <si>
+    <t>A_L01</t>
   </si>
   <si>
     <t>C_L23</t>
-  </si>
-  <si>
-    <t>B_L06</t>
-  </si>
-  <si>
-    <t>C_L21</t>
-  </si>
-  <si>
-    <t>B_L15</t>
-  </si>
-  <si>
-    <t>A_L19</t>
-  </si>
-  <si>
-    <t>C_L04</t>
-  </si>
-  <si>
-    <t>B_L22</t>
-  </si>
-  <si>
-    <t>A_L09</t>
-  </si>
-  <si>
-    <t>B_L21</t>
-  </si>
-  <si>
-    <t>B_L05</t>
-  </si>
-  <si>
-    <t>B_L10</t>
-  </si>
-  <si>
-    <t>B_L25</t>
-  </si>
-  <si>
-    <t>B_L19</t>
-  </si>
-  <si>
-    <t>A_L07</t>
-  </si>
-  <si>
-    <t>C_L17</t>
-  </si>
-  <si>
-    <t>C_L01</t>
-  </si>
-  <si>
-    <t>A_L02</t>
-  </si>
-  <si>
-    <t>C_L11</t>
-  </si>
-  <si>
-    <t>C_L14</t>
-  </si>
-  <si>
-    <t>A_L03</t>
-  </si>
-  <si>
-    <t>A_L27</t>
-  </si>
-  <si>
-    <t>B_L02</t>
-  </si>
-  <si>
-    <t>A_L17</t>
-  </si>
-  <si>
-    <t>B_L18</t>
-  </si>
-  <si>
-    <t>B_L23</t>
-  </si>
-  <si>
-    <t>A_L24</t>
-  </si>
-  <si>
-    <t>B_L16</t>
-  </si>
-  <si>
-    <t>C_L27</t>
-  </si>
-  <si>
-    <t>A_L13</t>
-  </si>
-  <si>
-    <t>B_L20</t>
-  </si>
-  <si>
-    <t>A_L23</t>
-  </si>
-  <si>
-    <t>A_L26</t>
-  </si>
-  <si>
-    <t>A_L01</t>
-  </si>
-  <si>
-    <t>C_L24</t>
   </si>
   <si>
     <t>C_L06</t>
@@ -765,61 +765,61 @@
         <v>101</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I2">
         <v>4</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K2">
         <v>4</v>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O2">
         <v>6</v>
       </c>
       <c r="P2">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="Q2">
         <v>1</v>
       </c>
       <c r="R2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S2">
-        <v>6.7</v>
+        <v>6</v>
       </c>
       <c r="T2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -833,13 +833,13 @@
         <v>101</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G3">
         <v>3</v>
@@ -848,46 +848,46 @@
         <v>2</v>
       </c>
       <c r="I3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O3">
         <v>6</v>
       </c>
       <c r="P3">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="Q3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S3">
-        <v>3.7</v>
+        <v>11.5</v>
       </c>
       <c r="T3">
         <v>3</v>
       </c>
       <c r="U3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -913,49 +913,49 @@
         <v>1</v>
       </c>
       <c r="H4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O4">
         <v>6</v>
       </c>
       <c r="P4">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="Q4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R4">
         <v>3</v>
       </c>
       <c r="S4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U4">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="V4">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -969,13 +969,13 @@
         <v>102</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -984,46 +984,46 @@
         <v>3</v>
       </c>
       <c r="I5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O5">
         <v>6</v>
       </c>
       <c r="P5">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="Q5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S5">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="T5">
         <v>6</v>
       </c>
       <c r="U5">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="V5">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -1037,37 +1037,37 @@
         <v>102</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M6">
         <v>6</v>
       </c>
       <c r="N6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O6">
         <v>6</v>
@@ -1079,16 +1079,16 @@
         <v>1</v>
       </c>
       <c r="R6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S6">
-        <v>6.1</v>
+        <v>2.4</v>
       </c>
       <c r="T6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U6">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V6">
         <v>3</v>
@@ -1105,61 +1105,61 @@
         <v>103</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K7">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L7">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N7">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O7">
         <v>6</v>
       </c>
       <c r="P7">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="Q7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R7">
         <v>3</v>
       </c>
       <c r="S7">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="T7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U7">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="V7">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -1173,61 +1173,61 @@
         <v>103</v>
       </c>
       <c r="D8">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E8">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G8">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H8">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I8">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O8">
         <v>6</v>
       </c>
       <c r="P8">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="Q8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R8">
         <v>3</v>
       </c>
       <c r="S8">
-        <v>4.7</v>
+        <v>9</v>
       </c>
       <c r="T8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U8">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="V8">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -1241,43 +1241,43 @@
         <v>101</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H9">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I9">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K9">
         <v>5</v>
       </c>
       <c r="L9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O9">
         <v>6</v>
       </c>
       <c r="P9">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="Q9">
         <v>1</v>
@@ -1286,16 +1286,16 @@
         <v>4</v>
       </c>
       <c r="S9">
-        <v>5.6</v>
+        <v>2.7</v>
       </c>
       <c r="T9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U9">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="V9">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1309,61 +1309,58 @@
         <v>101</v>
       </c>
       <c r="D10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I10">
         <v>5</v>
       </c>
       <c r="J10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K10">
         <v>5</v>
       </c>
       <c r="L10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M10">
         <v>5</v>
       </c>
       <c r="N10">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O10">
         <v>6</v>
       </c>
-      <c r="P10">
-        <v>43</v>
-      </c>
       <c r="Q10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S10">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="T10">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U10">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="V10">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1377,31 +1374,31 @@
         <v>102</v>
       </c>
       <c r="D11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F11">
         <v>2</v>
       </c>
       <c r="G11">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M11">
         <v>6</v>
@@ -1413,25 +1410,25 @@
         <v>6</v>
       </c>
       <c r="P11">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="Q11">
         <v>1</v>
       </c>
       <c r="R11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S11">
-        <v>4.1</v>
+        <v>6.4</v>
       </c>
       <c r="T11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U11">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="V11">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1445,58 +1442,58 @@
         <v>102</v>
       </c>
       <c r="D12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H12">
         <v>2</v>
       </c>
       <c r="I12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J12">
         <v>5</v>
       </c>
       <c r="K12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O12">
         <v>6</v>
       </c>
       <c r="P12">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="Q12">
         <v>2</v>
       </c>
       <c r="R12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S12">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="T12">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U12">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="V12">
         <v>3</v>
@@ -1513,61 +1510,61 @@
         <v>103</v>
       </c>
       <c r="D13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="F13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G13">
         <v>2</v>
       </c>
       <c r="H13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K13">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L13">
         <v>4</v>
       </c>
       <c r="M13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O13">
         <v>6</v>
       </c>
       <c r="P13">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="Q13">
         <v>1</v>
       </c>
       <c r="R13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S13">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="T13">
         <v>6</v>
       </c>
       <c r="U13">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="V13">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -1581,7 +1578,7 @@
         <v>103</v>
       </c>
       <c r="D14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E14">
         <v>5</v>
@@ -1590,52 +1587,52 @@
         <v>4</v>
       </c>
       <c r="G14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I14">
         <v>2</v>
       </c>
       <c r="J14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L14">
         <v>3</v>
       </c>
       <c r="M14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O14">
         <v>6</v>
       </c>
       <c r="P14">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="Q14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R14">
         <v>3</v>
       </c>
       <c r="S14">
-        <v>3.4</v>
+        <v>5.7</v>
       </c>
       <c r="T14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U14">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V14">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1649,10 +1646,10 @@
         <v>103</v>
       </c>
       <c r="D15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F15">
         <v>2</v>
@@ -1664,43 +1661,46 @@
         <v>2</v>
       </c>
       <c r="I15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K15">
         <v>5</v>
       </c>
       <c r="L15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M15">
         <v>5</v>
       </c>
       <c r="N15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O15">
         <v>6</v>
       </c>
       <c r="P15">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="Q15">
         <v>1</v>
       </c>
       <c r="R15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S15">
-        <v>2.6</v>
+        <v>7.4</v>
+      </c>
+      <c r="T15">
+        <v>6</v>
       </c>
       <c r="U15">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="V15">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -1714,10 +1714,10 @@
         <v>102</v>
       </c>
       <c r="D16">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F16">
         <v>3</v>
@@ -1732,40 +1732,40 @@
         <v>5</v>
       </c>
       <c r="J16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L16">
         <v>5</v>
       </c>
       <c r="M16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N16">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O16">
         <v>6</v>
       </c>
       <c r="P16">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="Q16">
         <v>2</v>
       </c>
       <c r="R16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S16">
-        <v>13.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="T16">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U16">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="V16">
         <v>4</v>
@@ -1782,7 +1782,7 @@
         <v>102</v>
       </c>
       <c r="D17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17">
         <v>2</v>
@@ -1791,49 +1791,49 @@
         <v>2</v>
       </c>
       <c r="G17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J17">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K17">
         <v>6</v>
       </c>
       <c r="L17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M17">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O17">
         <v>6</v>
       </c>
       <c r="P17">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="Q17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S17">
-        <v>4.9</v>
+        <v>6.3</v>
       </c>
       <c r="T17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U17">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="V17">
         <v>3</v>
@@ -1856,7 +1856,7 @@
         <v>1</v>
       </c>
       <c r="F18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1865,28 +1865,28 @@
         <v>1</v>
       </c>
       <c r="I18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J18">
         <v>5</v>
       </c>
       <c r="K18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M18">
         <v>6</v>
       </c>
       <c r="N18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O18">
         <v>6</v>
       </c>
       <c r="P18">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="Q18">
         <v>1</v>
@@ -1895,16 +1895,16 @@
         <v>4</v>
       </c>
       <c r="S18">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="T18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U18">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="V18">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -1918,37 +1918,37 @@
         <v>103</v>
       </c>
       <c r="D19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E19">
         <v>3</v>
       </c>
       <c r="F19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G19">
         <v>3</v>
       </c>
       <c r="H19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K19">
         <v>4</v>
       </c>
       <c r="L19">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N19">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O19">
         <v>6</v>
@@ -1957,19 +1957,19 @@
         <v>45</v>
       </c>
       <c r="Q19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S19">
-        <v>4.9</v>
+        <v>8</v>
       </c>
       <c r="T19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U19">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="V19">
         <v>4</v>
@@ -1986,58 +1986,58 @@
         <v>101</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F20">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G20">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H20">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I20">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J20">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K20">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L20">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M20">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N20">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O20">
         <v>6</v>
       </c>
       <c r="P20">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="Q20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S20">
-        <v>1.2</v>
+        <v>5.6</v>
       </c>
       <c r="T20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U20">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="V20">
         <v>3</v>
@@ -2057,10 +2057,10 @@
         <v>2</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G21">
         <v>2</v>
@@ -2069,46 +2069,46 @@
         <v>2</v>
       </c>
       <c r="I21">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L21">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N21">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O21">
         <v>6</v>
       </c>
       <c r="P21">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="Q21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R21">
         <v>3</v>
       </c>
       <c r="S21">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="T21">
         <v>6</v>
       </c>
       <c r="U21">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="V21">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -2125,55 +2125,55 @@
         <v>2</v>
       </c>
       <c r="E22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G22">
         <v>2</v>
       </c>
       <c r="H22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I22">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J22">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K22">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L22">
         <v>5</v>
       </c>
       <c r="M22">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N22">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O22">
         <v>6</v>
       </c>
       <c r="P22">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="Q22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R22">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S22">
-        <v>2.6</v>
+        <v>5.5</v>
       </c>
       <c r="T22">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U22">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="V22">
         <v>3</v>
@@ -2190,10 +2190,10 @@
         <v>103</v>
       </c>
       <c r="D23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F23">
         <v>3</v>
@@ -2202,49 +2202,49 @@
         <v>3</v>
       </c>
       <c r="H23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I23">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K23">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L23">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M23">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O23">
         <v>6</v>
       </c>
       <c r="P23">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="Q23">
         <v>1</v>
       </c>
       <c r="R23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S23">
-        <v>8.1</v>
+        <v>4.4</v>
       </c>
       <c r="T23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U23">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="V23">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -2261,25 +2261,25 @@
         <v>2</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G24">
         <v>2</v>
       </c>
       <c r="H24">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I24">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J24">
         <v>5</v>
       </c>
       <c r="K24">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L24">
         <v>4</v>
@@ -2288,7 +2288,7 @@
         <v>4</v>
       </c>
       <c r="N24">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O24">
         <v>6</v>
@@ -2303,13 +2303,16 @@
         <v>3</v>
       </c>
       <c r="S24">
-        <v>5.4</v>
+        <v>1.5</v>
+      </c>
+      <c r="T24">
+        <v>7</v>
       </c>
       <c r="U24">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="V24">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -2323,34 +2326,34 @@
         <v>102</v>
       </c>
       <c r="D25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F25">
         <v>1</v>
       </c>
       <c r="G25">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H25">
         <v>1</v>
       </c>
       <c r="I25">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J25">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K25">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L25">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M25">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N25">
         <v>4</v>
@@ -2359,25 +2362,25 @@
         <v>6</v>
       </c>
       <c r="P25">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="Q25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R25">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S25">
-        <v>7.7</v>
+        <v>11.9</v>
       </c>
       <c r="T25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U25">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="V25">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -2391,10 +2394,10 @@
         <v>103</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26">
         <v>1</v>
@@ -2403,10 +2406,10 @@
         <v>1</v>
       </c>
       <c r="H26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J26">
         <v>5</v>
@@ -2427,22 +2430,22 @@
         <v>6</v>
       </c>
       <c r="P26">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="Q26">
         <v>1</v>
       </c>
       <c r="R26">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S26">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="T26">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U26">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="V26">
         <v>4</v>
@@ -2462,7 +2465,7 @@
         <v>3</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F27">
         <v>3</v>
@@ -2474,43 +2477,43 @@
         <v>3</v>
       </c>
       <c r="I27">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J27">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L27">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M27">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N27">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O27">
         <v>6</v>
       </c>
       <c r="P27">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="Q27">
         <v>1</v>
       </c>
       <c r="R27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S27">
-        <v>8.9</v>
+        <v>3.8</v>
       </c>
       <c r="T27">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U27">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="V27">
         <v>4</v>
@@ -2530,58 +2533,58 @@
         <v>2</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F28">
         <v>1</v>
       </c>
       <c r="G28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I28">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J28">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L28">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M28">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N28">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O28">
         <v>6</v>
       </c>
       <c r="P28">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R28">
         <v>3</v>
       </c>
       <c r="S28">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T28">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U28">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="V28">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -2595,61 +2598,61 @@
         <v>102</v>
       </c>
       <c r="D29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I29">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J29">
         <v>5</v>
       </c>
       <c r="K29">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L29">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M29">
         <v>4</v>
       </c>
       <c r="N29">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O29">
         <v>6</v>
       </c>
       <c r="P29">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="Q29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R29">
         <v>3</v>
       </c>
       <c r="S29">
-        <v>3.8</v>
+        <v>5.2</v>
       </c>
       <c r="T29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U29">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="V29">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30" spans="1:22">
@@ -2660,64 +2663,64 @@
         <v>50</v>
       </c>
       <c r="C30" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F30">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G30">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H30">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L30">
         <v>6</v>
       </c>
       <c r="M30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O30">
         <v>6</v>
       </c>
       <c r="P30">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="Q30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R30">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S30">
-        <v>8.4</v>
+        <v>6.5</v>
       </c>
       <c r="T30">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="U30">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="V30">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:22">
@@ -2728,7 +2731,7 @@
         <v>51</v>
       </c>
       <c r="C31" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D31">
         <v>2</v>
@@ -2737,55 +2740,55 @@
         <v>2</v>
       </c>
       <c r="F31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I31">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J31">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L31">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M31">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N31">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O31">
         <v>6</v>
       </c>
       <c r="P31">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="Q31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R31">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S31">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="T31">
         <v>4</v>
       </c>
       <c r="U31">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V31">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:22">
@@ -2796,13 +2799,13 @@
         <v>52</v>
       </c>
       <c r="C32" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D32">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F32">
         <v>3</v>
@@ -2814,43 +2817,43 @@
         <v>3</v>
       </c>
       <c r="I32">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J32">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K32">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L32">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M32">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N32">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O32">
         <v>6</v>
       </c>
       <c r="P32">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="Q32">
         <v>1</v>
       </c>
       <c r="R32">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S32">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="T32">
         <v>5</v>
       </c>
       <c r="U32">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="V32">
         <v>3</v>
@@ -2864,7 +2867,7 @@
         <v>53</v>
       </c>
       <c r="C33" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D33">
         <v>2</v>
@@ -2873,7 +2876,7 @@
         <v>1</v>
       </c>
       <c r="F33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G33">
         <v>2</v>
@@ -2882,13 +2885,13 @@
         <v>2</v>
       </c>
       <c r="I33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J33">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L33">
         <v>7</v>
@@ -2903,22 +2906,22 @@
         <v>6</v>
       </c>
       <c r="P33">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Q33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R33">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S33">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="T33">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="V33">
         <v>4</v>
@@ -2932,31 +2935,31 @@
         <v>54</v>
       </c>
       <c r="C34" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D34">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E34">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G34">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H34">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I34">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J34">
         <v>6</v>
       </c>
       <c r="K34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L34">
         <v>6</v>
@@ -2965,28 +2968,28 @@
         <v>6</v>
       </c>
       <c r="N34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O34">
         <v>6</v>
       </c>
       <c r="P34">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Q34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R34">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S34">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="T34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U34">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="V34">
         <v>3</v>
@@ -3000,22 +3003,22 @@
         <v>55</v>
       </c>
       <c r="C35" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D35">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E35">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F35">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H35">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I35">
         <v>4</v>
@@ -3024,13 +3027,13 @@
         <v>4</v>
       </c>
       <c r="K35">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L35">
         <v>4</v>
       </c>
       <c r="M35">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N35">
         <v>5</v>
@@ -3048,16 +3051,16 @@
         <v>3</v>
       </c>
       <c r="S35">
-        <v>4.4</v>
+        <v>1.8</v>
       </c>
       <c r="T35">
         <v>6</v>
       </c>
       <c r="U35">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="V35">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:22">
@@ -3068,64 +3071,64 @@
         <v>56</v>
       </c>
       <c r="C36" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G36">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I36">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J36">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K36">
         <v>3</v>
       </c>
       <c r="L36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M36">
         <v>3</v>
       </c>
       <c r="N36">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O36">
         <v>6</v>
       </c>
       <c r="P36">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S36">
-        <v>8.5</v>
+        <v>2.6</v>
       </c>
       <c r="T36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U36">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="V36">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37" spans="1:22">
@@ -3139,61 +3142,61 @@
         <v>102</v>
       </c>
       <c r="D37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E37">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F37">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I37">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J37">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K37">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L37">
         <v>5</v>
       </c>
       <c r="M37">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O37">
         <v>6</v>
       </c>
       <c r="P37">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="Q37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R37">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S37">
-        <v>2.1</v>
+        <v>3.6</v>
       </c>
       <c r="T37">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U37">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V37">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38" spans="1:22">
@@ -3204,61 +3207,61 @@
         <v>58</v>
       </c>
       <c r="C38" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D38">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E38">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F38">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G38">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H38">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I38">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J38">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K38">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L38">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M38">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N38">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O38">
         <v>6</v>
       </c>
       <c r="P38">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="Q38">
         <v>1</v>
       </c>
       <c r="R38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S38">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="T38">
         <v>5</v>
       </c>
       <c r="U38">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="V38">
         <v>4</v>
@@ -3272,37 +3275,37 @@
         <v>59</v>
       </c>
       <c r="C39" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D39">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E39">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F39">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H39">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I39">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J39">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K39">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L39">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N39">
         <v>4</v>
@@ -3311,25 +3314,25 @@
         <v>6</v>
       </c>
       <c r="P39">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="Q39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R39">
         <v>3</v>
       </c>
       <c r="S39">
-        <v>2.8</v>
+        <v>6.3</v>
       </c>
       <c r="T39">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U39">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="V39">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40" spans="1:22">
@@ -3340,61 +3343,61 @@
         <v>60</v>
       </c>
       <c r="C40" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E40">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I40">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J40">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K40">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L40">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M40">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N40">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O40">
         <v>6</v>
       </c>
       <c r="P40">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="Q40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S40">
-        <v>4.4</v>
+        <v>1.8</v>
       </c>
       <c r="T40">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U40">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="V40">
         <v>3</v>
@@ -3411,55 +3414,55 @@
         <v>103</v>
       </c>
       <c r="D41">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E41">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F41">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G41">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H41">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I41">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K41">
         <v>6</v>
       </c>
       <c r="L41">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M41">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N41">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O41">
         <v>6</v>
       </c>
       <c r="P41">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="Q41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R41">
         <v>5</v>
       </c>
       <c r="S41">
-        <v>10.2</v>
+        <v>2.9</v>
       </c>
       <c r="T41">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U41">
         <v>13</v>
@@ -3476,40 +3479,40 @@
         <v>62</v>
       </c>
       <c r="C42" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G42">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H42">
         <v>2</v>
       </c>
       <c r="I42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J42">
         <v>5</v>
       </c>
       <c r="K42">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L42">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M42">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N42">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O42">
         <v>6</v>
@@ -3524,16 +3527,16 @@
         <v>4</v>
       </c>
       <c r="S42">
-        <v>5.9</v>
+        <v>3.3</v>
       </c>
       <c r="T42">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U42">
         <v>14</v>
       </c>
       <c r="V42">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43" spans="1:22">
@@ -3544,28 +3547,28 @@
         <v>63</v>
       </c>
       <c r="C43" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H43">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I43">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J43">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K43">
         <v>6</v>
@@ -3574,34 +3577,34 @@
         <v>5</v>
       </c>
       <c r="M43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O43">
         <v>6</v>
       </c>
       <c r="P43">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="Q43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R43">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S43">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="T43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U43">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="V43">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44" spans="1:22">
@@ -3615,19 +3618,19 @@
         <v>103</v>
       </c>
       <c r="D44">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E44">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F44">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H44">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I44">
         <v>5</v>
@@ -3636,13 +3639,13 @@
         <v>5</v>
       </c>
       <c r="K44">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M44">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N44">
         <v>4</v>
@@ -3651,25 +3654,25 @@
         <v>6</v>
       </c>
       <c r="P44">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="Q44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R44">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S44">
-        <v>6.5</v>
+        <v>7.9</v>
       </c>
       <c r="T44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U44">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V44">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45" spans="1:22">
@@ -3680,37 +3683,37 @@
         <v>65</v>
       </c>
       <c r="C45" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D45">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E45">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F45">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G45">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H45">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I45">
         <v>6</v>
       </c>
       <c r="J45">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K45">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L45">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M45">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N45">
         <v>7</v>
@@ -3719,22 +3722,22 @@
         <v>6</v>
       </c>
       <c r="P45">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="Q45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R45">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S45">
-        <v>5.7</v>
+        <v>2.6</v>
       </c>
       <c r="T45">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U45">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="V45">
         <v>3</v>
@@ -3748,10 +3751,10 @@
         <v>66</v>
       </c>
       <c r="C46" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E46">
         <v>3</v>
@@ -3763,10 +3766,10 @@
         <v>3</v>
       </c>
       <c r="H46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I46">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J46">
         <v>3</v>
@@ -3775,37 +3778,37 @@
         <v>3</v>
       </c>
       <c r="L46">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M46">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N46">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O46">
         <v>6</v>
       </c>
       <c r="P46">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="Q46">
         <v>2</v>
       </c>
       <c r="R46">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S46">
-        <v>12.7</v>
+        <v>6.4</v>
       </c>
       <c r="T46">
         <v>6</v>
       </c>
       <c r="U46">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="V46">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:22">
@@ -3816,64 +3819,64 @@
         <v>67</v>
       </c>
       <c r="C47" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D47">
         <v>3</v>
       </c>
       <c r="E47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I47">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J47">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K47">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L47">
         <v>4</v>
       </c>
       <c r="M47">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N47">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O47">
         <v>6</v>
       </c>
       <c r="P47">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q47">
         <v>1</v>
       </c>
       <c r="R47">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S47">
-        <v>10.6</v>
+        <v>5.7</v>
       </c>
       <c r="T47">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U47">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="V47">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48" spans="1:22">
@@ -3884,64 +3887,64 @@
         <v>68</v>
       </c>
       <c r="C48" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G48">
         <v>2</v>
       </c>
       <c r="H48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I48">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J48">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K48">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L48">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M48">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N48">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O48">
         <v>6</v>
       </c>
       <c r="P48">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="Q48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R48">
         <v>4</v>
       </c>
       <c r="S48">
-        <v>6.7</v>
+        <v>3.6</v>
       </c>
       <c r="T48">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U48">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V48">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49" spans="1:22">
@@ -3952,40 +3955,40 @@
         <v>69</v>
       </c>
       <c r="C49" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D49">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E49">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F49">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G49">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H49">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I49">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J49">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K49">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L49">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M49">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N49">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O49">
         <v>6</v>
@@ -3994,19 +3997,19 @@
         <v>43</v>
       </c>
       <c r="Q49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R49">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S49">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="T49">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U49">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="V49">
         <v>4</v>
@@ -4020,7 +4023,7 @@
         <v>70</v>
       </c>
       <c r="C50" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D50">
         <v>1</v>
@@ -4029,25 +4032,25 @@
         <v>1</v>
       </c>
       <c r="F50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H50">
         <v>1</v>
       </c>
       <c r="I50">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J50">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K50">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L50">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M50">
         <v>4</v>
@@ -4059,7 +4062,7 @@
         <v>6</v>
       </c>
       <c r="P50">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="Q50">
         <v>2</v>
@@ -4068,16 +4071,16 @@
         <v>3</v>
       </c>
       <c r="S50">
-        <v>6.2</v>
+        <v>2.2</v>
       </c>
       <c r="T50">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U50">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="V50">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51" spans="1:22">
@@ -4088,46 +4091,46 @@
         <v>71</v>
       </c>
       <c r="C51" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E51">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F51">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G51">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H51">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I51">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J51">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K51">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L51">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M51">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N51">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O51">
         <v>6</v>
       </c>
       <c r="P51">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="Q51">
         <v>2</v>
@@ -4136,10 +4139,10 @@
         <v>3</v>
       </c>
       <c r="S51">
-        <v>4.5</v>
+        <v>7.2</v>
       </c>
       <c r="T51">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U51">
         <v>9</v>
@@ -4156,22 +4159,22 @@
         <v>72</v>
       </c>
       <c r="C52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D52">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E52">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F52">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G52">
         <v>2</v>
       </c>
       <c r="H52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I52">
         <v>5</v>
@@ -4180,40 +4183,40 @@
         <v>5</v>
       </c>
       <c r="K52">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L52">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M52">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N52">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O52">
         <v>6</v>
       </c>
       <c r="P52">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="Q52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R52">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S52">
-        <v>9.6</v>
+        <v>6.8</v>
       </c>
       <c r="T52">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U52">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="V52">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53" spans="1:22">
@@ -4227,43 +4230,43 @@
         <v>102</v>
       </c>
       <c r="D53">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F53">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G53">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I53">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J53">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K53">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L53">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M53">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N53">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O53">
         <v>6</v>
       </c>
       <c r="P53">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="Q53">
         <v>1</v>
@@ -4272,16 +4275,16 @@
         <v>3</v>
       </c>
       <c r="S53">
-        <v>10.3</v>
+        <v>5</v>
       </c>
       <c r="T53">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U53">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="V53">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54" spans="1:22">
@@ -4295,58 +4298,58 @@
         <v>102</v>
       </c>
       <c r="D54">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E54">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G54">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H54">
         <v>2</v>
       </c>
       <c r="I54">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J54">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K54">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L54">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M54">
         <v>6</v>
       </c>
       <c r="N54">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O54">
         <v>6</v>
       </c>
       <c r="P54">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="Q54">
         <v>1</v>
       </c>
       <c r="R54">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S54">
-        <v>3.9</v>
+        <v>7.3</v>
       </c>
       <c r="T54">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U54">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="V54">
         <v>3</v>
@@ -4363,58 +4366,58 @@
         <v>102</v>
       </c>
       <c r="D55">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E55">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F55">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G55">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H55">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I55">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J55">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K55">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L55">
         <v>4</v>
       </c>
       <c r="M55">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N55">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O55">
         <v>6</v>
       </c>
       <c r="P55">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="Q55">
         <v>1</v>
       </c>
       <c r="R55">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S55">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="T55">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U55">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="V55">
         <v>4</v>
@@ -4431,13 +4434,13 @@
         <v>102</v>
       </c>
       <c r="D56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E56">
         <v>2</v>
       </c>
       <c r="F56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G56">
         <v>2</v>
@@ -4446,43 +4449,43 @@
         <v>1</v>
       </c>
       <c r="I56">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J56">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K56">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L56">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M56">
         <v>5</v>
       </c>
       <c r="N56">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O56">
         <v>6</v>
       </c>
       <c r="P56">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="Q56">
         <v>1</v>
       </c>
       <c r="R56">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S56">
-        <v>6.6</v>
+        <v>11.5</v>
       </c>
       <c r="T56">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="U56">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="V56">
         <v>4</v>
@@ -4499,34 +4502,34 @@
         <v>101</v>
       </c>
       <c r="D57">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E57">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F57">
         <v>4</v>
       </c>
       <c r="G57">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H57">
         <v>4</v>
       </c>
       <c r="I57">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J57">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K57">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L57">
         <v>4</v>
       </c>
       <c r="M57">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N57">
         <v>4</v>
@@ -4535,25 +4538,25 @@
         <v>6</v>
       </c>
       <c r="P57">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="Q57">
         <v>1</v>
       </c>
       <c r="R57">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S57">
-        <v>7</v>
+        <v>2.3</v>
       </c>
       <c r="T57">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="U57">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="V57">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="58" spans="1:22">
@@ -4567,28 +4570,28 @@
         <v>103</v>
       </c>
       <c r="D58">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E58">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F58">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G58">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H58">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I58">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J58">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K58">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L58">
         <v>5</v>
@@ -4603,22 +4606,22 @@
         <v>6</v>
       </c>
       <c r="P58">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q58">
         <v>2</v>
       </c>
       <c r="R58">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S58">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="T58">
         <v>6</v>
       </c>
       <c r="U58">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="V58">
         <v>4</v>
@@ -4635,43 +4638,43 @@
         <v>103</v>
       </c>
       <c r="D59">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E59">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F59">
         <v>3</v>
       </c>
       <c r="G59">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H59">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I59">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J59">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K59">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L59">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M59">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N59">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O59">
         <v>6</v>
       </c>
       <c r="P59">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="Q59">
         <v>1</v>
@@ -4679,14 +4682,11 @@
       <c r="R59">
         <v>3</v>
       </c>
-      <c r="S59">
-        <v>3.9</v>
-      </c>
       <c r="T59">
         <v>4</v>
       </c>
       <c r="U59">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="V59">
         <v>3</v>
@@ -4706,55 +4706,55 @@
         <v>2</v>
       </c>
       <c r="E60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G60">
         <v>2</v>
       </c>
       <c r="H60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I60">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J60">
         <v>6</v>
       </c>
       <c r="K60">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L60">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M60">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N60">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O60">
         <v>6</v>
       </c>
       <c r="P60">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="Q60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R60">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S60">
-        <v>9.4</v>
+        <v>10.6</v>
       </c>
       <c r="T60">
         <v>4</v>
       </c>
       <c r="U60">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="V60">
         <v>3</v>
@@ -4777,7 +4777,7 @@
         <v>2</v>
       </c>
       <c r="F61">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G61">
         <v>2</v>
@@ -4789,40 +4789,40 @@
         <v>4</v>
       </c>
       <c r="J61">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K61">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L61">
         <v>4</v>
       </c>
       <c r="M61">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N61">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O61">
         <v>6</v>
       </c>
       <c r="P61">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="Q61">
         <v>1</v>
       </c>
       <c r="R61">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S61">
-        <v>2.2</v>
+        <v>5.6</v>
       </c>
       <c r="T61">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U61">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="V61">
         <v>3</v>
@@ -4839,61 +4839,61 @@
         <v>103</v>
       </c>
       <c r="D62">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E62">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F62">
         <v>2</v>
       </c>
       <c r="G62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I62">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J62">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K62">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L62">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M62">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N62">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O62">
         <v>6</v>
       </c>
       <c r="P62">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q62">
         <v>1</v>
       </c>
       <c r="R62">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S62">
-        <v>6.4</v>
+        <v>9.9</v>
       </c>
       <c r="T62">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U62">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="V62">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63" spans="1:22">
@@ -4907,61 +4907,61 @@
         <v>101</v>
       </c>
       <c r="D63">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E63">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F63">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G63">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H63">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I63">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J63">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K63">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L63">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M63">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N63">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O63">
         <v>6</v>
       </c>
       <c r="P63">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="Q63">
         <v>1</v>
       </c>
       <c r="R63">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S63">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="T63">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U63">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="V63">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64" spans="1:22">
@@ -4975,7 +4975,7 @@
         <v>101</v>
       </c>
       <c r="D64">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E64">
         <v>3</v>
@@ -4993,40 +4993,43 @@
         <v>5</v>
       </c>
       <c r="J64">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K64">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L64">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M64">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N64">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O64">
         <v>6</v>
       </c>
+      <c r="P64">
+        <v>37</v>
+      </c>
       <c r="Q64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R64">
         <v>3</v>
       </c>
       <c r="S64">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="T64">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="U64">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="V64">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65" spans="1:22">
@@ -5043,13 +5046,13 @@
         <v>3</v>
       </c>
       <c r="E65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H65">
         <v>3</v>
@@ -5061,13 +5064,13 @@
         <v>6</v>
       </c>
       <c r="K65">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L65">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M65">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N65">
         <v>5</v>
@@ -5076,25 +5079,25 @@
         <v>6</v>
       </c>
       <c r="P65">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="Q65">
         <v>2</v>
       </c>
       <c r="R65">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S65">
-        <v>7.9</v>
+        <v>6.4</v>
       </c>
       <c r="T65">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U65">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="V65">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66" spans="1:22">
@@ -5108,58 +5111,58 @@
         <v>101</v>
       </c>
       <c r="D66">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E66">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F66">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G66">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H66">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I66">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J66">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K66">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L66">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M66">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N66">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O66">
         <v>6</v>
       </c>
       <c r="P66">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="Q66">
         <v>1</v>
       </c>
       <c r="R66">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S66">
-        <v>7.5</v>
+        <v>5.1</v>
       </c>
       <c r="T66">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U66">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="V66">
         <v>3</v>
@@ -5176,61 +5179,61 @@
         <v>102</v>
       </c>
       <c r="D67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E67">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G67">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H67">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I67">
         <v>4</v>
       </c>
       <c r="J67">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K67">
         <v>4</v>
       </c>
       <c r="L67">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M67">
         <v>3</v>
       </c>
       <c r="N67">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O67">
         <v>6</v>
       </c>
       <c r="P67">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="Q67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R67">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S67">
-        <v>3.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="T67">
         <v>6</v>
       </c>
       <c r="U67">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="V67">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68" spans="1:22">
@@ -5253,49 +5256,49 @@
         <v>5</v>
       </c>
       <c r="G68">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H68">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I68">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J68">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K68">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L68">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M68">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N68">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O68">
         <v>6</v>
       </c>
       <c r="P68">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Q68">
         <v>1</v>
       </c>
       <c r="R68">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S68">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="T68">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U68">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="V68">
         <v>3</v>
@@ -5312,43 +5315,43 @@
         <v>101</v>
       </c>
       <c r="D69">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E69">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F69">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G69">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H69">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I69">
         <v>5</v>
       </c>
       <c r="J69">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K69">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L69">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M69">
         <v>5</v>
       </c>
       <c r="N69">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O69">
         <v>6</v>
       </c>
       <c r="P69">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="Q69">
         <v>1</v>
@@ -5357,16 +5360,16 @@
         <v>4</v>
       </c>
       <c r="S69">
-        <v>7.5</v>
+        <v>3.4</v>
       </c>
       <c r="T69">
         <v>3</v>
       </c>
       <c r="U69">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="V69">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:22">
@@ -5380,7 +5383,7 @@
         <v>102</v>
       </c>
       <c r="D70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E70">
         <v>1</v>
@@ -5395,46 +5398,46 @@
         <v>1</v>
       </c>
       <c r="I70">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J70">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K70">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L70">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M70">
         <v>6</v>
       </c>
       <c r="N70">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O70">
         <v>6</v>
       </c>
       <c r="P70">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="Q70">
         <v>1</v>
       </c>
       <c r="R70">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S70">
-        <v>12</v>
+        <v>4.6</v>
       </c>
       <c r="T70">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U70">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="V70">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71" spans="1:22">
@@ -5448,61 +5451,61 @@
         <v>103</v>
       </c>
       <c r="D71">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E71">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F71">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G71">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H71">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I71">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J71">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K71">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L71">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M71">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N71">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O71">
         <v>6</v>
       </c>
       <c r="P71">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Q71">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R71">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S71">
-        <v>3</v>
+        <v>5.8</v>
       </c>
       <c r="T71">
         <v>5</v>
       </c>
       <c r="U71">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="V71">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72" spans="1:22">
@@ -5516,43 +5519,43 @@
         <v>101</v>
       </c>
       <c r="D72">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E72">
         <v>2</v>
       </c>
       <c r="F72">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G72">
         <v>3</v>
       </c>
       <c r="H72">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I72">
         <v>7</v>
       </c>
       <c r="J72">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K72">
         <v>7</v>
       </c>
       <c r="L72">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M72">
         <v>7</v>
       </c>
       <c r="N72">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O72">
         <v>6</v>
       </c>
       <c r="P72">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="Q72">
         <v>2</v>
@@ -5561,16 +5564,16 @@
         <v>3</v>
       </c>
       <c r="S72">
-        <v>3.4</v>
+        <v>6.9</v>
       </c>
       <c r="T72">
         <v>5</v>
       </c>
       <c r="U72">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V72">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73" spans="1:22">
@@ -5584,61 +5587,61 @@
         <v>102</v>
       </c>
       <c r="D73">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E73">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F73">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G73">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H73">
         <v>3</v>
       </c>
       <c r="I73">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J73">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K73">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L73">
         <v>6</v>
       </c>
       <c r="M73">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N73">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O73">
         <v>6</v>
       </c>
       <c r="P73">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="Q73">
         <v>1</v>
       </c>
       <c r="R73">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S73">
-        <v>7.6</v>
+        <v>6.5</v>
       </c>
       <c r="T73">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U73">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="V73">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74" spans="1:22">
@@ -5652,10 +5655,10 @@
         <v>101</v>
       </c>
       <c r="D74">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F74">
         <v>1</v>
@@ -5667,43 +5670,43 @@
         <v>2</v>
       </c>
       <c r="I74">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J74">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K74">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L74">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M74">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N74">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O74">
         <v>6</v>
       </c>
       <c r="P74">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="Q74">
         <v>2</v>
       </c>
       <c r="R74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S74">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="T74">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U74">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="V74">
         <v>4</v>
@@ -5720,61 +5723,61 @@
         <v>101</v>
       </c>
       <c r="D75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E75">
         <v>1</v>
       </c>
       <c r="F75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I75">
         <v>7</v>
       </c>
       <c r="J75">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K75">
         <v>5</v>
       </c>
       <c r="L75">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M75">
         <v>6</v>
       </c>
       <c r="N75">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O75">
         <v>6</v>
       </c>
       <c r="P75">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="Q75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R75">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S75">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="T75">
         <v>5</v>
       </c>
       <c r="U75">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="V75">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76" spans="1:22">
@@ -5791,55 +5794,55 @@
         <v>3</v>
       </c>
       <c r="E76">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F76">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G76">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H76">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I76">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L76">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M76">
         <v>3</v>
       </c>
       <c r="N76">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O76">
         <v>6</v>
       </c>
       <c r="P76">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q76">
         <v>1</v>
       </c>
       <c r="R76">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S76">
-        <v>5.1</v>
+        <v>18</v>
       </c>
       <c r="T76">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U76">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="V76">
         <v>3</v>
@@ -5856,16 +5859,16 @@
         <v>103</v>
       </c>
       <c r="D77">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E77">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F77">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G77">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H77">
         <v>3</v>
@@ -5874,25 +5877,25 @@
         <v>4</v>
       </c>
       <c r="J77">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K77">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L77">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M77">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N77">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O77">
         <v>6</v>
       </c>
       <c r="P77">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="Q77">
         <v>1</v>
@@ -5901,16 +5904,16 @@
         <v>3</v>
       </c>
       <c r="S77">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="T77">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U77">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V77">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78" spans="1:22">
@@ -5924,34 +5927,34 @@
         <v>103</v>
       </c>
       <c r="D78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E78">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F78">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G78">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H78">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I78">
         <v>7</v>
       </c>
       <c r="J78">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K78">
         <v>7</v>
       </c>
       <c r="L78">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M78">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N78">
         <v>6</v>
@@ -5960,25 +5963,25 @@
         <v>6</v>
       </c>
       <c r="P78">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="Q78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R78">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S78">
-        <v>10</v>
+        <v>3.1</v>
       </c>
       <c r="T78">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U78">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="V78">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79" spans="1:22">
@@ -5992,7 +5995,7 @@
         <v>101</v>
       </c>
       <c r="D79">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E79">
         <v>3</v>
@@ -6001,52 +6004,52 @@
         <v>3</v>
       </c>
       <c r="G79">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H79">
         <v>2</v>
       </c>
       <c r="I79">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J79">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K79">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L79">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M79">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N79">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O79">
         <v>6</v>
       </c>
       <c r="P79">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="Q79">
         <v>1</v>
       </c>
       <c r="R79">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S79">
-        <v>9.1</v>
+        <v>8.4</v>
       </c>
       <c r="T79">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U79">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="V79">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80" spans="1:22">
@@ -6060,52 +6063,49 @@
         <v>101</v>
       </c>
       <c r="D80">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E80">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F80">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G80">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H80">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I80">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J80">
         <v>4</v>
       </c>
       <c r="K80">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L80">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M80">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N80">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O80">
         <v>6</v>
       </c>
       <c r="P80">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="Q80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R80">
-        <v>2</v>
-      </c>
-      <c r="S80">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="T80">
         <v>5</v>
@@ -6114,7 +6114,7 @@
         <v>22</v>
       </c>
       <c r="V80">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/data/T3_leader_cleaned.xlsx
+++ b/data/T3_leader_cleaned.xlsx
@@ -82,241 +82,241 @@
     <t>LeaderJobLevel</t>
   </si>
   <si>
-    <t>A_L14</t>
+    <t>A_L13</t>
+  </si>
+  <si>
+    <t>A_L19</t>
+  </si>
+  <si>
+    <t>A_L07</t>
+  </si>
+  <si>
+    <t>B_L10</t>
+  </si>
+  <si>
+    <t>B_L06</t>
+  </si>
+  <si>
+    <t>C_L19</t>
+  </si>
+  <si>
+    <t>C_L25</t>
+  </si>
+  <si>
+    <t>A_L10</t>
+  </si>
+  <si>
+    <t>A_L09</t>
+  </si>
+  <si>
+    <t>B_L25</t>
+  </si>
+  <si>
+    <t>B_L23</t>
+  </si>
+  <si>
+    <t>C_L11</t>
+  </si>
+  <si>
+    <t>C_L01</t>
+  </si>
+  <si>
+    <t>C_L02</t>
+  </si>
+  <si>
+    <t>B_L08</t>
+  </si>
+  <si>
+    <t>B_L09</t>
+  </si>
+  <si>
+    <t>A_L25</t>
+  </si>
+  <si>
+    <t>C_L06</t>
+  </si>
+  <si>
+    <t>A_L15</t>
+  </si>
+  <si>
+    <t>C_L08</t>
+  </si>
+  <si>
+    <t>B_L05</t>
+  </si>
+  <si>
+    <t>C_L13</t>
+  </si>
+  <si>
+    <t>C_L21</t>
+  </si>
+  <si>
+    <t>A_L27</t>
+  </si>
+  <si>
+    <t>C_L18</t>
+  </si>
+  <si>
+    <t>C_L07</t>
+  </si>
+  <si>
+    <t>A_L18</t>
+  </si>
+  <si>
+    <t>A_L29</t>
+  </si>
+  <si>
+    <t>B_L07</t>
+  </si>
+  <si>
+    <t>A_L05</t>
+  </si>
+  <si>
+    <t>C_L24</t>
+  </si>
+  <si>
+    <t>A_L12</t>
+  </si>
+  <si>
+    <t>C_L29</t>
+  </si>
+  <si>
+    <t>B_L27</t>
+  </si>
+  <si>
+    <t>C_L10</t>
+  </si>
+  <si>
+    <t>B_L26</t>
+  </si>
+  <si>
+    <t>B_L29</t>
+  </si>
+  <si>
+    <t>C_L04</t>
+  </si>
+  <si>
+    <t>A_L20</t>
+  </si>
+  <si>
+    <t>C_L30</t>
+  </si>
+  <si>
+    <t>C_L28</t>
+  </si>
+  <si>
+    <t>B_L01</t>
+  </si>
+  <si>
+    <t>C_L16</t>
+  </si>
+  <si>
+    <t>C_L22</t>
+  </si>
+  <si>
+    <t>B_L04</t>
+  </si>
+  <si>
+    <t>C_L20</t>
+  </si>
+  <si>
+    <t>B_L11</t>
+  </si>
+  <si>
+    <t>A_L17</t>
+  </si>
+  <si>
+    <t>C_L03</t>
+  </si>
+  <si>
+    <t>B_L21</t>
+  </si>
+  <si>
+    <t>A_L08</t>
+  </si>
+  <si>
+    <t>B_L20</t>
+  </si>
+  <si>
+    <t>B_L03</t>
+  </si>
+  <si>
+    <t>B_L24</t>
+  </si>
+  <si>
+    <t>B_L18</t>
+  </si>
+  <si>
+    <t>A_L06</t>
+  </si>
+  <si>
+    <t>C_L14</t>
+  </si>
+  <si>
+    <t>B_L30</t>
+  </si>
+  <si>
+    <t>A_L02</t>
+  </si>
+  <si>
+    <t>C_L09</t>
+  </si>
+  <si>
+    <t>C_L12</t>
+  </si>
+  <si>
+    <t>A_L03</t>
+  </si>
+  <si>
+    <t>A_L24</t>
+  </si>
+  <si>
+    <t>A_L28</t>
+  </si>
+  <si>
+    <t>A_L16</t>
+  </si>
+  <si>
+    <t>B_L16</t>
+  </si>
+  <si>
+    <t>B_L22</t>
+  </si>
+  <si>
+    <t>A_L22</t>
+  </si>
+  <si>
+    <t>B_L12</t>
+  </si>
+  <si>
+    <t>C_L26</t>
+  </si>
+  <si>
+    <t>A_L11</t>
+  </si>
+  <si>
+    <t>B_L19</t>
   </si>
   <si>
     <t>A_L21</t>
   </si>
   <si>
-    <t>A_L08</t>
-  </si>
-  <si>
-    <t>B_L14</t>
-  </si>
-  <si>
-    <t>B_L08</t>
-  </si>
-  <si>
-    <t>C_L19</t>
-  </si>
-  <si>
-    <t>C_L25</t>
-  </si>
-  <si>
-    <t>A_L11</t>
-  </si>
-  <si>
-    <t>A_L10</t>
-  </si>
-  <si>
-    <t>B_L26</t>
-  </si>
-  <si>
-    <t>B_L24</t>
-  </si>
-  <si>
-    <t>C_L12</t>
-  </si>
-  <si>
-    <t>C_L02</t>
-  </si>
-  <si>
-    <t>C_L03</t>
-  </si>
-  <si>
-    <t>B_L10</t>
-  </si>
-  <si>
-    <t>B_L12</t>
-  </si>
-  <si>
-    <t>A_L28</t>
-  </si>
-  <si>
-    <t>C_L07</t>
-  </si>
-  <si>
-    <t>A_L15</t>
-  </si>
-  <si>
-    <t>C_L09</t>
-  </si>
-  <si>
-    <t>B_L07</t>
-  </si>
-  <si>
-    <t>C_L14</t>
-  </si>
-  <si>
-    <t>C_L21</t>
-  </si>
-  <si>
-    <t>B_L01</t>
-  </si>
-  <si>
-    <t>C_L18</t>
-  </si>
-  <si>
-    <t>C_L08</t>
-  </si>
-  <si>
-    <t>A_L18</t>
-  </si>
-  <si>
-    <t>B_L03</t>
-  </si>
-  <si>
-    <t>B_L09</t>
-  </si>
-  <si>
-    <t>A_L06</t>
-  </si>
-  <si>
-    <t>C_L24</t>
-  </si>
-  <si>
-    <t>A_L13</t>
-  </si>
-  <si>
-    <t>C_L29</t>
-  </si>
-  <si>
-    <t>B_L29</t>
-  </si>
-  <si>
-    <t>C_L11</t>
-  </si>
-  <si>
-    <t>B_L27</t>
-  </si>
-  <si>
-    <t>B_L30</t>
+    <t>A_L23</t>
+  </si>
+  <si>
+    <t>A_L01</t>
+  </si>
+  <si>
+    <t>C_L23</t>
   </si>
   <si>
     <t>C_L05</t>
   </si>
   <si>
-    <t>A_L22</t>
-  </si>
-  <si>
-    <t>C_L30</t>
-  </si>
-  <si>
-    <t>C_L28</t>
-  </si>
-  <si>
-    <t>B_L04</t>
-  </si>
-  <si>
-    <t>C_L17</t>
-  </si>
-  <si>
-    <t>C_L22</t>
-  </si>
-  <si>
-    <t>B_L06</t>
-  </si>
-  <si>
-    <t>C_L20</t>
-  </si>
-  <si>
-    <t>B_L15</t>
-  </si>
-  <si>
-    <t>A_L17</t>
-  </si>
-  <si>
-    <t>C_L04</t>
-  </si>
-  <si>
-    <t>B_L22</t>
-  </si>
-  <si>
-    <t>A_L09</t>
-  </si>
-  <si>
-    <t>B_L21</t>
-  </si>
-  <si>
-    <t>B_L05</t>
-  </si>
-  <si>
-    <t>B_L25</t>
-  </si>
-  <si>
-    <t>B_L19</t>
-  </si>
-  <si>
-    <t>A_L07</t>
-  </si>
-  <si>
-    <t>C_L16</t>
-  </si>
-  <si>
-    <t>C_L01</t>
-  </si>
-  <si>
-    <t>A_L02</t>
-  </si>
-  <si>
-    <t>C_L10</t>
-  </si>
-  <si>
-    <t>C_L13</t>
-  </si>
-  <si>
     <t>A_L04</t>
   </si>
   <si>
-    <t>A_L27</t>
-  </si>
-  <si>
-    <t>B_L02</t>
-  </si>
-  <si>
-    <t>A_L16</t>
-  </si>
-  <si>
-    <t>B_L18</t>
-  </si>
-  <si>
-    <t>B_L23</t>
-  </si>
-  <si>
-    <t>A_L25</t>
-  </si>
-  <si>
-    <t>B_L16</t>
-  </si>
-  <si>
-    <t>C_L26</t>
-  </si>
-  <si>
-    <t>A_L12</t>
-  </si>
-  <si>
-    <t>B_L20</t>
-  </si>
-  <si>
-    <t>A_L23</t>
-  </si>
-  <si>
     <t>A_L26</t>
-  </si>
-  <si>
-    <t>A_L01</t>
-  </si>
-  <si>
-    <t>C_L23</t>
-  </si>
-  <si>
-    <t>C_L06</t>
-  </si>
-  <si>
-    <t>A_L05</t>
-  </si>
-  <si>
-    <t>A_L29</t>
   </si>
   <si>
     <t>A</t>
@@ -848,22 +848,22 @@
         <v>2</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O3">
         <v>6</v>
@@ -901,37 +901,37 @@
         <v>101</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O4">
         <v>6</v>
@@ -984,22 +984,22 @@
         <v>3</v>
       </c>
       <c r="I5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O5">
         <v>6</v>
@@ -1309,19 +1309,19 @@
         <v>101</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I10">
         <v>5</v>
@@ -1389,22 +1389,22 @@
         <v>2</v>
       </c>
       <c r="I11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O11">
         <v>6</v>
@@ -1442,37 +1442,37 @@
         <v>102</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H12">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I12">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J12">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L12">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N12">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O12">
         <v>6</v>
@@ -1525,22 +1525,22 @@
         <v>3</v>
       </c>
       <c r="I13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O13">
         <v>6</v>
@@ -1578,37 +1578,37 @@
         <v>103</v>
       </c>
       <c r="D14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O14">
         <v>6</v>
@@ -1646,37 +1646,37 @@
         <v>103</v>
       </c>
       <c r="D15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I15">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J15">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K15">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L15">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M15">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N15">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O15">
         <v>6</v>
@@ -1714,19 +1714,19 @@
         <v>102</v>
       </c>
       <c r="D16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I16">
         <v>5</v>
@@ -1782,37 +1782,37 @@
         <v>102</v>
       </c>
       <c r="D17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O17">
         <v>6</v>
@@ -1850,37 +1850,37 @@
         <v>101</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G18">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H18">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I18">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J18">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K18">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L18">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M18">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N18">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O18">
         <v>6</v>
@@ -1918,37 +1918,37 @@
         <v>103</v>
       </c>
       <c r="D19">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H19">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J19">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K19">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L19">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M19">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N19">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O19">
         <v>6</v>
@@ -2054,37 +2054,37 @@
         <v>103</v>
       </c>
       <c r="D21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O21">
         <v>6</v>
@@ -2122,37 +2122,37 @@
         <v>102</v>
       </c>
       <c r="D22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22">
         <v>1</v>
       </c>
       <c r="F22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M22">
         <v>7</v>
       </c>
       <c r="N22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O22">
         <v>6</v>
@@ -2190,19 +2190,19 @@
         <v>103</v>
       </c>
       <c r="D23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I23">
         <v>4</v>
@@ -2323,7 +2323,7 @@
         <v>45</v>
       </c>
       <c r="C25" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -2462,37 +2462,37 @@
         <v>103</v>
       </c>
       <c r="D27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I27">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L27">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M27">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N27">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O27">
         <v>6</v>
@@ -2595,40 +2595,40 @@
         <v>49</v>
       </c>
       <c r="C29" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I29">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J29">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L29">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M29">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N29">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O29">
         <v>6</v>
@@ -2734,37 +2734,37 @@
         <v>101</v>
       </c>
       <c r="D31">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E31">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H31">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J31">
         <v>7</v>
       </c>
       <c r="K31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O31">
         <v>6</v>
@@ -2870,25 +2870,25 @@
         <v>101</v>
       </c>
       <c r="D33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E33">
         <v>1</v>
       </c>
       <c r="F33">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J33">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K33">
         <v>7</v>
@@ -2900,7 +2900,7 @@
         <v>7</v>
       </c>
       <c r="N33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O33">
         <v>6</v>
@@ -3021,22 +3021,22 @@
         <v>4</v>
       </c>
       <c r="I35">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J35">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L35">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O35">
         <v>6</v>
@@ -3074,37 +3074,37 @@
         <v>103</v>
       </c>
       <c r="D36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J36">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K36">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L36">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M36">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N36">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O36">
         <v>6</v>
@@ -3142,19 +3142,19 @@
         <v>102</v>
       </c>
       <c r="D37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I37">
         <v>5</v>
@@ -3287,28 +3287,28 @@
         <v>1</v>
       </c>
       <c r="G39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H39">
         <v>1</v>
       </c>
       <c r="I39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M39">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N39">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O39">
         <v>6</v>
@@ -3346,37 +3346,37 @@
         <v>101</v>
       </c>
       <c r="D40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J40">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K40">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L40">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N40">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O40">
         <v>6</v>
@@ -3899,28 +3899,28 @@
         <v>1</v>
       </c>
       <c r="G48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H48">
         <v>1</v>
       </c>
       <c r="I48">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K48">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L48">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M48">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N48">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O48">
         <v>6</v>
@@ -3958,19 +3958,19 @@
         <v>101</v>
       </c>
       <c r="D49">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E49">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F49">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G49">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H49">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I49">
         <v>4</v>
@@ -4162,37 +4162,37 @@
         <v>101</v>
       </c>
       <c r="D52">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E52">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F52">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I52">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J52">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K52">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L52">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M52">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N52">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O52">
         <v>6</v>
@@ -4245,22 +4245,22 @@
         <v>2</v>
       </c>
       <c r="I53">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J53">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K53">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L53">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M53">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N53">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O53">
         <v>6</v>
@@ -4298,37 +4298,37 @@
         <v>102</v>
       </c>
       <c r="D54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G54">
         <v>1</v>
       </c>
       <c r="H54">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I54">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J54">
         <v>7</v>
       </c>
       <c r="K54">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L54">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M54">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N54">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O54">
         <v>6</v>
@@ -4434,37 +4434,37 @@
         <v>102</v>
       </c>
       <c r="D56">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E56">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F56">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G56">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H56">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I56">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J56">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K56">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L56">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M56">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N56">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O56">
         <v>6</v>
@@ -4502,37 +4502,37 @@
         <v>101</v>
       </c>
       <c r="D57">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E57">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F57">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G57">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H57">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I57">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J57">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K57">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L57">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M57">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N57">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O57">
         <v>6</v>
@@ -4570,37 +4570,37 @@
         <v>103</v>
       </c>
       <c r="D58">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E58">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F58">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G58">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H58">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I58">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J58">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K58">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L58">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M58">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N58">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O58">
         <v>6</v>
@@ -4635,7 +4635,7 @@
         <v>79</v>
       </c>
       <c r="C59" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D59">
         <v>3</v>
@@ -4653,22 +4653,22 @@
         <v>2</v>
       </c>
       <c r="I59">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J59">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K59">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L59">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M59">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N59">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O59">
         <v>6</v>
@@ -4771,19 +4771,19 @@
         <v>103</v>
       </c>
       <c r="D61">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E61">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G61">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H61">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I61">
         <v>4</v>
@@ -4839,19 +4839,19 @@
         <v>103</v>
       </c>
       <c r="D62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I62">
         <v>7</v>
@@ -4907,37 +4907,37 @@
         <v>101</v>
       </c>
       <c r="D63">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E63">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F63">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G63">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H63">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I63">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J63">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K63">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L63">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M63">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N63">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O63">
         <v>6</v>
@@ -4975,37 +4975,37 @@
         <v>101</v>
       </c>
       <c r="D64">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E64">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F64">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G64">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H64">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I64">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J64">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K64">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L64">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M64">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N64">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O64">
         <v>6</v>
@@ -5040,40 +5040,40 @@
         <v>85</v>
       </c>
       <c r="C65" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D65">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E65">
         <v>1</v>
       </c>
       <c r="F65">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G65">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H65">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I65">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J65">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K65">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L65">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M65">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N65">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O65">
         <v>6</v>
@@ -5194,22 +5194,22 @@
         <v>1</v>
       </c>
       <c r="I67">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J67">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K67">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L67">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M67">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N67">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O67">
         <v>6</v>
@@ -5247,37 +5247,37 @@
         <v>102</v>
       </c>
       <c r="D68">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E68">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F68">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G68">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H68">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I68">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J68">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K68">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L68">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M68">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N68">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O68">
         <v>6</v>
@@ -5315,37 +5315,37 @@
         <v>101</v>
       </c>
       <c r="D69">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E69">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F69">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G69">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H69">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I69">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J69">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K69">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L69">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M69">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N69">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O69">
         <v>6</v>
@@ -5519,37 +5519,37 @@
         <v>101</v>
       </c>
       <c r="D72">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E72">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F72">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G72">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H72">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I72">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J72">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K72">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L72">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M72">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N72">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O72">
         <v>6</v>
@@ -5587,37 +5587,37 @@
         <v>102</v>
       </c>
       <c r="D73">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F73">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H73">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I73">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J73">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K73">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L73">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M73">
         <v>7</v>
       </c>
       <c r="N73">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O73">
         <v>6</v>
@@ -5655,19 +5655,19 @@
         <v>101</v>
       </c>
       <c r="D74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E74">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F74">
         <v>1</v>
       </c>
       <c r="G74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I74">
         <v>3</v>
@@ -5723,37 +5723,37 @@
         <v>101</v>
       </c>
       <c r="D75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E75">
         <v>1</v>
       </c>
       <c r="F75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G75">
         <v>1</v>
       </c>
       <c r="H75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I75">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J75">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K75">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L75">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M75">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N75">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O75">
         <v>6</v>
@@ -5874,22 +5874,22 @@
         <v>3</v>
       </c>
       <c r="I77">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J77">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K77">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L77">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M77">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N77">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O77">
         <v>6</v>
@@ -5927,19 +5927,19 @@
         <v>103</v>
       </c>
       <c r="D78">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E78">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F78">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G78">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H78">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I78">
         <v>7</v>
@@ -5995,37 +5995,37 @@
         <v>101</v>
       </c>
       <c r="D79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E79">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F79">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I79">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J79">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K79">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L79">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M79">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N79">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O79">
         <v>6</v>
@@ -6063,37 +6063,37 @@
         <v>101</v>
       </c>
       <c r="D80">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E80">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F80">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G80">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H80">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I80">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J80">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K80">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L80">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M80">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N80">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O80">
         <v>6</v>

--- a/data/T3_leader_cleaned.xlsx
+++ b/data/T3_leader_cleaned.xlsx
@@ -85,229 +85,229 @@
     <t>A_L13</t>
   </si>
   <si>
+    <t>A_L18</t>
+  </si>
+  <si>
+    <t>A_L07</t>
+  </si>
+  <si>
+    <t>B_L11</t>
+  </si>
+  <si>
+    <t>B_L05</t>
+  </si>
+  <si>
+    <t>C_L20</t>
+  </si>
+  <si>
+    <t>C_L26</t>
+  </si>
+  <si>
+    <t>A_L10</t>
+  </si>
+  <si>
+    <t>A_L09</t>
+  </si>
+  <si>
+    <t>B_L24</t>
+  </si>
+  <si>
+    <t>B_L22</t>
+  </si>
+  <si>
+    <t>C_L12</t>
+  </si>
+  <si>
+    <t>C_L01</t>
+  </si>
+  <si>
+    <t>C_L02</t>
+  </si>
+  <si>
+    <t>B_L08</t>
+  </si>
+  <si>
+    <t>B_L10</t>
+  </si>
+  <si>
+    <t>A_L25</t>
+  </si>
+  <si>
+    <t>C_L06</t>
+  </si>
+  <si>
+    <t>A_L14</t>
+  </si>
+  <si>
+    <t>C_L09</t>
+  </si>
+  <si>
+    <t>B_L04</t>
+  </si>
+  <si>
+    <t>C_L14</t>
+  </si>
+  <si>
+    <t>C_L22</t>
+  </si>
+  <si>
+    <t>A_L27</t>
+  </si>
+  <si>
+    <t>C_L19</t>
+  </si>
+  <si>
+    <t>C_L07</t>
+  </si>
+  <si>
+    <t>A_L17</t>
+  </si>
+  <si>
+    <t>A_L29</t>
+  </si>
+  <si>
+    <t>A_L05</t>
+  </si>
+  <si>
+    <t>C_L25</t>
+  </si>
+  <si>
+    <t>A_L12</t>
+  </si>
+  <si>
+    <t>C_L29</t>
+  </si>
+  <si>
+    <t>B_L27</t>
+  </si>
+  <si>
+    <t>C_L11</t>
+  </si>
+  <si>
+    <t>B_L25</t>
+  </si>
+  <si>
+    <t>B_L29</t>
+  </si>
+  <si>
+    <t>C_L04</t>
+  </si>
+  <si>
     <t>A_L19</t>
   </si>
   <si>
-    <t>A_L07</t>
-  </si>
-  <si>
-    <t>B_L10</t>
-  </si>
-  <si>
-    <t>B_L06</t>
-  </si>
-  <si>
-    <t>C_L19</t>
-  </si>
-  <si>
-    <t>C_L25</t>
-  </si>
-  <si>
-    <t>A_L10</t>
-  </si>
-  <si>
-    <t>A_L09</t>
-  </si>
-  <si>
-    <t>B_L25</t>
+    <t>C_L30</t>
+  </si>
+  <si>
+    <t>C_L28</t>
+  </si>
+  <si>
+    <t>B_L01</t>
+  </si>
+  <si>
+    <t>C_L18</t>
+  </si>
+  <si>
+    <t>C_L23</t>
+  </si>
+  <si>
+    <t>B_L03</t>
+  </si>
+  <si>
+    <t>C_L21</t>
+  </si>
+  <si>
+    <t>B_L12</t>
+  </si>
+  <si>
+    <t>A_L16</t>
+  </si>
+  <si>
+    <t>C_L03</t>
+  </si>
+  <si>
+    <t>B_L20</t>
+  </si>
+  <si>
+    <t>A_L08</t>
+  </si>
+  <si>
+    <t>B_L19</t>
+  </si>
+  <si>
+    <t>B_L02</t>
+  </si>
+  <si>
+    <t>B_L07</t>
   </si>
   <si>
     <t>B_L23</t>
   </si>
   <si>
-    <t>C_L11</t>
-  </si>
-  <si>
-    <t>C_L01</t>
-  </si>
-  <si>
-    <t>C_L02</t>
-  </si>
-  <si>
-    <t>B_L08</t>
-  </si>
-  <si>
-    <t>B_L09</t>
-  </si>
-  <si>
-    <t>A_L25</t>
-  </si>
-  <si>
-    <t>C_L06</t>
+    <t>B_L16</t>
+  </si>
+  <si>
+    <t>A_L06</t>
+  </si>
+  <si>
+    <t>C_L17</t>
+  </si>
+  <si>
+    <t>B_L30</t>
+  </si>
+  <si>
+    <t>A_L02</t>
+  </si>
+  <si>
+    <t>C_L10</t>
+  </si>
+  <si>
+    <t>C_L13</t>
+  </si>
+  <si>
+    <t>A_L03</t>
+  </si>
+  <si>
+    <t>A_L24</t>
+  </si>
+  <si>
+    <t>A_L28</t>
   </si>
   <si>
     <t>A_L15</t>
   </si>
   <si>
-    <t>C_L08</t>
-  </si>
-  <si>
-    <t>B_L05</t>
-  </si>
-  <si>
-    <t>C_L13</t>
-  </si>
-  <si>
-    <t>C_L21</t>
-  </si>
-  <si>
-    <t>A_L27</t>
-  </si>
-  <si>
-    <t>C_L18</t>
-  </si>
-  <si>
-    <t>C_L07</t>
-  </si>
-  <si>
-    <t>A_L18</t>
-  </si>
-  <si>
-    <t>A_L29</t>
-  </si>
-  <si>
-    <t>B_L07</t>
-  </si>
-  <si>
-    <t>A_L05</t>
+    <t>B_L15</t>
+  </si>
+  <si>
+    <t>B_L21</t>
+  </si>
+  <si>
+    <t>A_L21</t>
+  </si>
+  <si>
+    <t>B_L14</t>
+  </si>
+  <si>
+    <t>C_L27</t>
+  </si>
+  <si>
+    <t>A_L11</t>
+  </si>
+  <si>
+    <t>B_L18</t>
+  </si>
+  <si>
+    <t>A_L20</t>
+  </si>
+  <si>
+    <t>A_L22</t>
+  </si>
+  <si>
+    <t>A_L01</t>
   </si>
   <si>
     <t>C_L24</t>
-  </si>
-  <si>
-    <t>A_L12</t>
-  </si>
-  <si>
-    <t>C_L29</t>
-  </si>
-  <si>
-    <t>B_L27</t>
-  </si>
-  <si>
-    <t>C_L10</t>
-  </si>
-  <si>
-    <t>B_L26</t>
-  </si>
-  <si>
-    <t>B_L29</t>
-  </si>
-  <si>
-    <t>C_L04</t>
-  </si>
-  <si>
-    <t>A_L20</t>
-  </si>
-  <si>
-    <t>C_L30</t>
-  </si>
-  <si>
-    <t>C_L28</t>
-  </si>
-  <si>
-    <t>B_L01</t>
-  </si>
-  <si>
-    <t>C_L16</t>
-  </si>
-  <si>
-    <t>C_L22</t>
-  </si>
-  <si>
-    <t>B_L04</t>
-  </si>
-  <si>
-    <t>C_L20</t>
-  </si>
-  <si>
-    <t>B_L11</t>
-  </si>
-  <si>
-    <t>A_L17</t>
-  </si>
-  <si>
-    <t>C_L03</t>
-  </si>
-  <si>
-    <t>B_L21</t>
-  </si>
-  <si>
-    <t>A_L08</t>
-  </si>
-  <si>
-    <t>B_L20</t>
-  </si>
-  <si>
-    <t>B_L03</t>
-  </si>
-  <si>
-    <t>B_L24</t>
-  </si>
-  <si>
-    <t>B_L18</t>
-  </si>
-  <si>
-    <t>A_L06</t>
-  </si>
-  <si>
-    <t>C_L14</t>
-  </si>
-  <si>
-    <t>B_L30</t>
-  </si>
-  <si>
-    <t>A_L02</t>
-  </si>
-  <si>
-    <t>C_L09</t>
-  </si>
-  <si>
-    <t>C_L12</t>
-  </si>
-  <si>
-    <t>A_L03</t>
-  </si>
-  <si>
-    <t>A_L24</t>
-  </si>
-  <si>
-    <t>A_L28</t>
-  </si>
-  <si>
-    <t>A_L16</t>
-  </si>
-  <si>
-    <t>B_L16</t>
-  </si>
-  <si>
-    <t>B_L22</t>
-  </si>
-  <si>
-    <t>A_L22</t>
-  </si>
-  <si>
-    <t>B_L12</t>
-  </si>
-  <si>
-    <t>C_L26</t>
-  </si>
-  <si>
-    <t>A_L11</t>
-  </si>
-  <si>
-    <t>B_L19</t>
-  </si>
-  <si>
-    <t>A_L21</t>
-  </si>
-  <si>
-    <t>A_L23</t>
-  </si>
-  <si>
-    <t>A_L01</t>
-  </si>
-  <si>
-    <t>C_L23</t>
   </si>
   <si>
     <t>C_L05</t>
@@ -765,34 +765,34 @@
         <v>101</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L2">
         <v>5</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N2">
         <v>5</v>
@@ -801,25 +801,25 @@
         <v>6</v>
       </c>
       <c r="P2">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="Q2">
         <v>1</v>
       </c>
       <c r="R2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S2">
-        <v>6</v>
+        <v>6.7</v>
       </c>
       <c r="T2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -833,61 +833,61 @@
         <v>101</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <v>3</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="N3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O3">
         <v>6</v>
       </c>
       <c r="P3">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="Q3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S3">
-        <v>11.5</v>
+        <v>3.7</v>
       </c>
       <c r="T3">
         <v>3</v>
       </c>
       <c r="U3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="V3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -901,10 +901,10 @@
         <v>101</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4">
         <v>2</v>
@@ -913,49 +913,49 @@
         <v>3</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O4">
         <v>6</v>
       </c>
       <c r="P4">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="Q4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R4">
         <v>3</v>
       </c>
       <c r="S4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U4">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="V4">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -972,58 +972,58 @@
         <v>2</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O5">
         <v>6</v>
       </c>
       <c r="P5">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="Q5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S5">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="T5">
         <v>6</v>
       </c>
       <c r="U5">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="V5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -1037,7 +1037,7 @@
         <v>102</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1058,13 +1058,13 @@
         <v>6</v>
       </c>
       <c r="K6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N6">
         <v>7</v>
@@ -1079,16 +1079,16 @@
         <v>1</v>
       </c>
       <c r="R6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S6">
-        <v>2.4</v>
+        <v>6.1</v>
       </c>
       <c r="T6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V6">
         <v>3</v>
@@ -1105,61 +1105,61 @@
         <v>103</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K7">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L7">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N7">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O7">
         <v>6</v>
       </c>
       <c r="P7">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="Q7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R7">
         <v>3</v>
       </c>
       <c r="S7">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="T7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U7">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="V7">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -1173,61 +1173,61 @@
         <v>103</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G8">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H8">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I8">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K8">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L8">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O8">
         <v>6</v>
       </c>
       <c r="P8">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="Q8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R8">
         <v>3</v>
       </c>
       <c r="S8">
-        <v>9</v>
+        <v>4.7</v>
       </c>
       <c r="T8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U8">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="V8">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -1241,43 +1241,43 @@
         <v>101</v>
       </c>
       <c r="D9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E9">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F9">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H9">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I9">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J9">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K9">
         <v>5</v>
       </c>
       <c r="L9">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O9">
         <v>6</v>
       </c>
       <c r="P9">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="Q9">
         <v>1</v>
@@ -1286,16 +1286,16 @@
         <v>4</v>
       </c>
       <c r="S9">
-        <v>2.7</v>
+        <v>5.6</v>
       </c>
       <c r="T9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U9">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="V9">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1309,58 +1309,61 @@
         <v>101</v>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L10">
         <v>4</v>
       </c>
       <c r="M10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N10">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O10">
         <v>6</v>
       </c>
+      <c r="P10">
+        <v>43</v>
+      </c>
       <c r="Q10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S10">
-        <v>2.6</v>
+        <v>4.5</v>
       </c>
       <c r="T10">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="U10">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="V10">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1374,25 +1377,25 @@
         <v>102</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F11">
         <v>2</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I11">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J11">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K11">
         <v>6</v>
@@ -1401,34 +1404,34 @@
         <v>6</v>
       </c>
       <c r="M11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O11">
         <v>6</v>
       </c>
       <c r="P11">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="Q11">
         <v>1</v>
       </c>
       <c r="R11">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S11">
-        <v>6.4</v>
+        <v>4.1</v>
       </c>
       <c r="T11">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U11">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="V11">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1445,55 +1448,55 @@
         <v>3</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G12">
         <v>3</v>
       </c>
       <c r="H12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I12">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K12">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M12">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O12">
         <v>6</v>
       </c>
       <c r="P12">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="Q12">
         <v>2</v>
       </c>
       <c r="R12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S12">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="T12">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U12">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="V12">
         <v>3</v>
@@ -1510,61 +1513,61 @@
         <v>103</v>
       </c>
       <c r="D13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="F13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G13">
         <v>2</v>
       </c>
       <c r="H13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I13">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J13">
         <v>3</v>
       </c>
       <c r="K13">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L13">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M13">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O13">
         <v>6</v>
       </c>
       <c r="P13">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="Q13">
         <v>1</v>
       </c>
       <c r="R13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S13">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="T13">
         <v>6</v>
       </c>
       <c r="U13">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="V13">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -1578,7 +1581,7 @@
         <v>103</v>
       </c>
       <c r="D14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E14">
         <v>3</v>
@@ -1587,52 +1590,52 @@
         <v>2</v>
       </c>
       <c r="G14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I14">
         <v>4</v>
       </c>
       <c r="J14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L14">
         <v>5</v>
       </c>
       <c r="M14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O14">
         <v>6</v>
       </c>
       <c r="P14">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Q14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R14">
         <v>3</v>
       </c>
       <c r="S14">
-        <v>5.7</v>
+        <v>3.4</v>
       </c>
       <c r="T14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U14">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="V14">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1646,10 +1649,10 @@
         <v>103</v>
       </c>
       <c r="D15">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F15">
         <v>4</v>
@@ -1661,46 +1664,43 @@
         <v>4</v>
       </c>
       <c r="I15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K15">
         <v>2</v>
       </c>
       <c r="L15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M15">
         <v>2</v>
       </c>
       <c r="N15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O15">
         <v>6</v>
       </c>
       <c r="P15">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="Q15">
         <v>1</v>
       </c>
       <c r="R15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S15">
-        <v>7.4</v>
-      </c>
-      <c r="T15">
-        <v>6</v>
+        <v>2.6</v>
       </c>
       <c r="U15">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="V15">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -1714,10 +1714,10 @@
         <v>102</v>
       </c>
       <c r="D16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F16">
         <v>2</v>
@@ -1732,40 +1732,40 @@
         <v>5</v>
       </c>
       <c r="J16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L16">
         <v>5</v>
       </c>
       <c r="M16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N16">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O16">
         <v>6</v>
       </c>
       <c r="P16">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="Q16">
         <v>2</v>
       </c>
       <c r="R16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S16">
-        <v>9.199999999999999</v>
+        <v>13.8</v>
       </c>
       <c r="T16">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U16">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="V16">
         <v>4</v>
@@ -1782,7 +1782,7 @@
         <v>102</v>
       </c>
       <c r="D17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -1791,49 +1791,49 @@
         <v>3</v>
       </c>
       <c r="G17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I17">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J17">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K17">
         <v>5</v>
       </c>
       <c r="L17">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M17">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N17">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O17">
         <v>6</v>
       </c>
       <c r="P17">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="Q17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S17">
-        <v>6.3</v>
+        <v>4.9</v>
       </c>
       <c r="T17">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U17">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="V17">
         <v>3</v>
@@ -1853,40 +1853,40 @@
         <v>3</v>
       </c>
       <c r="E18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F18">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H18">
         <v>4</v>
       </c>
       <c r="I18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J18">
         <v>2</v>
       </c>
       <c r="K18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L18">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M18">
         <v>3</v>
       </c>
       <c r="N18">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O18">
         <v>6</v>
       </c>
       <c r="P18">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q18">
         <v>1</v>
@@ -1895,16 +1895,16 @@
         <v>4</v>
       </c>
       <c r="S18">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="T18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U18">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="V18">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -1918,7 +1918,7 @@
         <v>103</v>
       </c>
       <c r="D19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -1930,25 +1930,25 @@
         <v>1</v>
       </c>
       <c r="H19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J19">
         <v>6</v>
       </c>
       <c r="K19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M19">
         <v>7</v>
       </c>
       <c r="N19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O19">
         <v>6</v>
@@ -1957,19 +1957,19 @@
         <v>45</v>
       </c>
       <c r="Q19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S19">
-        <v>8</v>
+        <v>4.9</v>
       </c>
       <c r="T19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U19">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="V19">
         <v>4</v>
@@ -1986,58 +1986,58 @@
         <v>101</v>
       </c>
       <c r="D20">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E20">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F20">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H20">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I20">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J20">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O20">
         <v>6</v>
       </c>
       <c r="P20">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="Q20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S20">
-        <v>5.6</v>
+        <v>1.2</v>
       </c>
       <c r="T20">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U20">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="V20">
         <v>3</v>
@@ -2054,34 +2054,34 @@
         <v>103</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G21">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H21">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I21">
         <v>4</v>
       </c>
       <c r="J21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L21">
         <v>3</v>
       </c>
       <c r="M21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N21">
         <v>4</v>
@@ -2090,25 +2090,25 @@
         <v>6</v>
       </c>
       <c r="P21">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="Q21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R21">
         <v>3</v>
       </c>
       <c r="S21">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="T21">
         <v>6</v>
       </c>
       <c r="U21">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="V21">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -2122,58 +2122,58 @@
         <v>102</v>
       </c>
       <c r="D22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H22">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I22">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J22">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K22">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M22">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N22">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O22">
         <v>6</v>
       </c>
       <c r="P22">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="Q22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S22">
-        <v>5.5</v>
+        <v>2.6</v>
       </c>
       <c r="T22">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U22">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="V22">
         <v>3</v>
@@ -2190,61 +2190,61 @@
         <v>103</v>
       </c>
       <c r="D23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I23">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J23">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K23">
         <v>4</v>
       </c>
       <c r="L23">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M23">
         <v>4</v>
       </c>
       <c r="N23">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O23">
         <v>6</v>
       </c>
       <c r="P23">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="Q23">
         <v>1</v>
       </c>
       <c r="R23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S23">
-        <v>4.4</v>
+        <v>8.1</v>
       </c>
       <c r="T23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U23">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="V23">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -2261,25 +2261,25 @@
         <v>2</v>
       </c>
       <c r="E24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F24">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G24">
         <v>2</v>
       </c>
       <c r="H24">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I24">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J24">
         <v>5</v>
       </c>
       <c r="K24">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L24">
         <v>4</v>
@@ -2288,7 +2288,7 @@
         <v>4</v>
       </c>
       <c r="N24">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O24">
         <v>6</v>
@@ -2303,16 +2303,13 @@
         <v>3</v>
       </c>
       <c r="S24">
-        <v>1.5</v>
-      </c>
-      <c r="T24">
-        <v>7</v>
+        <v>5.4</v>
       </c>
       <c r="U24">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="V24">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -2326,34 +2323,34 @@
         <v>101</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25">
         <v>1</v>
       </c>
       <c r="G25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H25">
         <v>1</v>
       </c>
       <c r="I25">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J25">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K25">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L25">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M25">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N25">
         <v>4</v>
@@ -2362,25 +2359,25 @@
         <v>6</v>
       </c>
       <c r="P25">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="Q25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R25">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S25">
-        <v>11.9</v>
+        <v>7.7</v>
       </c>
       <c r="T25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U25">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="V25">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -2394,10 +2391,10 @@
         <v>103</v>
       </c>
       <c r="D26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F26">
         <v>1</v>
@@ -2406,10 +2403,10 @@
         <v>1</v>
       </c>
       <c r="H26">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I26">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J26">
         <v>5</v>
@@ -2430,22 +2427,22 @@
         <v>6</v>
       </c>
       <c r="P26">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Q26">
         <v>1</v>
       </c>
       <c r="R26">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S26">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="T26">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U26">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="V26">
         <v>4</v>
@@ -2465,7 +2462,7 @@
         <v>4</v>
       </c>
       <c r="E27">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F27">
         <v>4</v>
@@ -2477,43 +2474,43 @@
         <v>4</v>
       </c>
       <c r="I27">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J27">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L27">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M27">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N27">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O27">
         <v>6</v>
       </c>
       <c r="P27">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="Q27">
         <v>1</v>
       </c>
       <c r="R27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S27">
-        <v>3.8</v>
+        <v>8.9</v>
       </c>
       <c r="T27">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U27">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="V27">
         <v>4</v>
@@ -2530,61 +2527,61 @@
         <v>101</v>
       </c>
       <c r="D28">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E28">
         <v>2</v>
       </c>
       <c r="F28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H28">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I28">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J28">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K28">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L28">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M28">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N28">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O28">
         <v>6</v>
       </c>
       <c r="P28">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Q28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R28">
         <v>3</v>
       </c>
       <c r="S28">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T28">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U28">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="V28">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -2598,61 +2595,61 @@
         <v>101</v>
       </c>
       <c r="D29">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E29">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F29">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G29">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H29">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J29">
         <v>4</v>
       </c>
       <c r="K29">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L29">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M29">
         <v>3</v>
       </c>
       <c r="N29">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O29">
         <v>6</v>
       </c>
       <c r="P29">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="Q29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R29">
         <v>3</v>
       </c>
       <c r="S29">
-        <v>5.2</v>
+        <v>3.8</v>
       </c>
       <c r="T29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U29">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="V29">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:22">
@@ -2663,64 +2660,64 @@
         <v>50</v>
       </c>
       <c r="C30" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E30">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F30">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G30">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H30">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J30">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K30">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L30">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M30">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N30">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O30">
         <v>6</v>
       </c>
       <c r="P30">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="Q30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R30">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S30">
-        <v>6.5</v>
+        <v>8.4</v>
       </c>
       <c r="T30">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U30">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="V30">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31" spans="1:22">
@@ -2731,64 +2728,64 @@
         <v>51</v>
       </c>
       <c r="C31" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D31">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E31">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H31">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J31">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K31">
         <v>6</v>
       </c>
       <c r="L31">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N31">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O31">
         <v>6</v>
       </c>
       <c r="P31">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="Q31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S31">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="T31">
         <v>4</v>
       </c>
       <c r="U31">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V31">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:22">
@@ -2799,61 +2796,61 @@
         <v>52</v>
       </c>
       <c r="C32" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D32">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E32">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F32">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G32">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H32">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I32">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J32">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K32">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L32">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M32">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N32">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O32">
         <v>6</v>
       </c>
       <c r="P32">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="Q32">
         <v>1</v>
       </c>
       <c r="R32">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S32">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="T32">
         <v>5</v>
       </c>
       <c r="U32">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="V32">
         <v>3</v>
@@ -2867,10 +2864,10 @@
         <v>53</v>
       </c>
       <c r="C33" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33">
         <v>1</v>
@@ -2879,10 +2876,10 @@
         <v>1</v>
       </c>
       <c r="G33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I33">
         <v>7</v>
@@ -2891,7 +2888,7 @@
         <v>7</v>
       </c>
       <c r="K33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L33">
         <v>7</v>
@@ -2900,28 +2897,28 @@
         <v>7</v>
       </c>
       <c r="N33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O33">
         <v>6</v>
       </c>
       <c r="P33">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Q33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R33">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S33">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="T33">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U33">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="V33">
         <v>4</v>
@@ -2935,31 +2932,31 @@
         <v>54</v>
       </c>
       <c r="C34" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34">
         <v>1</v>
       </c>
       <c r="G34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H34">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J34">
         <v>6</v>
       </c>
       <c r="K34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L34">
         <v>6</v>
@@ -2968,28 +2965,28 @@
         <v>6</v>
       </c>
       <c r="N34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O34">
         <v>6</v>
       </c>
       <c r="P34">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="Q34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R34">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S34">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="T34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U34">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="V34">
         <v>3</v>
@@ -3003,40 +3000,40 @@
         <v>55</v>
       </c>
       <c r="C35" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D35">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E35">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F35">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G35">
         <v>3</v>
       </c>
       <c r="H35">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I35">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J35">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K35">
         <v>4</v>
       </c>
       <c r="L35">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M35">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N35">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O35">
         <v>6</v>
@@ -3051,16 +3048,16 @@
         <v>3</v>
       </c>
       <c r="S35">
-        <v>1.8</v>
+        <v>4.4</v>
       </c>
       <c r="T35">
         <v>6</v>
       </c>
       <c r="U35">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="V35">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:22">
@@ -3071,16 +3068,16 @@
         <v>56</v>
       </c>
       <c r="C36" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D36">
         <v>2</v>
       </c>
       <c r="E36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G36">
         <v>3</v>
@@ -3089,46 +3086,46 @@
         <v>1</v>
       </c>
       <c r="I36">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J36">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L36">
         <v>4</v>
       </c>
       <c r="M36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N36">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O36">
         <v>6</v>
       </c>
       <c r="P36">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R36">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S36">
-        <v>2.6</v>
+        <v>8.5</v>
       </c>
       <c r="T36">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U36">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="V36">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:22">
@@ -3142,7 +3139,7 @@
         <v>102</v>
       </c>
       <c r="D37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E37">
         <v>2</v>
@@ -3151,22 +3148,22 @@
         <v>3</v>
       </c>
       <c r="G37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I37">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J37">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K37">
         <v>5</v>
       </c>
       <c r="L37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M37">
         <v>5</v>
@@ -3178,25 +3175,25 @@
         <v>6</v>
       </c>
       <c r="P37">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="Q37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R37">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S37">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="T37">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U37">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="V37">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38" spans="1:22">
@@ -3207,61 +3204,61 @@
         <v>58</v>
       </c>
       <c r="C38" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D38">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E38">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F38">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G38">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H38">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I38">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J38">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K38">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L38">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M38">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N38">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O38">
         <v>6</v>
       </c>
       <c r="P38">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="Q38">
         <v>1</v>
       </c>
       <c r="R38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S38">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="T38">
         <v>5</v>
       </c>
       <c r="U38">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="V38">
         <v>4</v>
@@ -3275,37 +3272,37 @@
         <v>59</v>
       </c>
       <c r="C39" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D39">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E39">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F39">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G39">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H39">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I39">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J39">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K39">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L39">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M39">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N39">
         <v>5</v>
@@ -3314,25 +3311,25 @@
         <v>6</v>
       </c>
       <c r="P39">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="Q39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R39">
         <v>3</v>
       </c>
       <c r="S39">
-        <v>6.3</v>
+        <v>2.8</v>
       </c>
       <c r="T39">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U39">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="V39">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40" spans="1:22">
@@ -3343,13 +3340,13 @@
         <v>60</v>
       </c>
       <c r="C40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D40">
         <v>1</v>
       </c>
       <c r="E40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F40">
         <v>1</v>
@@ -3361,43 +3358,43 @@
         <v>1</v>
       </c>
       <c r="I40">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M40">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O40">
         <v>6</v>
       </c>
       <c r="P40">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="Q40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R40">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S40">
-        <v>1.8</v>
+        <v>4.4</v>
       </c>
       <c r="T40">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U40">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="V40">
         <v>3</v>
@@ -3414,55 +3411,55 @@
         <v>103</v>
       </c>
       <c r="D41">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E41">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F41">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G41">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H41">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I41">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K41">
         <v>6</v>
       </c>
       <c r="L41">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M41">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N41">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O41">
         <v>6</v>
       </c>
       <c r="P41">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="Q41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R41">
         <v>5</v>
       </c>
       <c r="S41">
-        <v>2.9</v>
+        <v>10.2</v>
       </c>
       <c r="T41">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U41">
         <v>13</v>
@@ -3479,40 +3476,40 @@
         <v>62</v>
       </c>
       <c r="C42" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G42">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H42">
         <v>2</v>
       </c>
       <c r="I42">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J42">
         <v>5</v>
       </c>
       <c r="K42">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L42">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M42">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N42">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O42">
         <v>6</v>
@@ -3527,16 +3524,16 @@
         <v>4</v>
       </c>
       <c r="S42">
-        <v>3.3</v>
+        <v>5.9</v>
       </c>
       <c r="T42">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U42">
         <v>14</v>
       </c>
       <c r="V42">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:22">
@@ -3547,28 +3544,28 @@
         <v>63</v>
       </c>
       <c r="C43" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H43">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I43">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J43">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K43">
         <v>6</v>
@@ -3577,34 +3574,34 @@
         <v>5</v>
       </c>
       <c r="M43">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N43">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O43">
         <v>6</v>
       </c>
       <c r="P43">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="Q43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R43">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S43">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="T43">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U43">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="V43">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44" spans="1:22">
@@ -3618,19 +3615,19 @@
         <v>103</v>
       </c>
       <c r="D44">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E44">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F44">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H44">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I44">
         <v>5</v>
@@ -3639,13 +3636,13 @@
         <v>5</v>
       </c>
       <c r="K44">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L44">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M44">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N44">
         <v>4</v>
@@ -3654,25 +3651,25 @@
         <v>6</v>
       </c>
       <c r="P44">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="Q44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R44">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S44">
-        <v>7.9</v>
+        <v>6.5</v>
       </c>
       <c r="T44">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U44">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="V44">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45" spans="1:22">
@@ -3683,37 +3680,37 @@
         <v>65</v>
       </c>
       <c r="C45" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E45">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F45">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H45">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I45">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J45">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K45">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L45">
         <v>6</v>
       </c>
       <c r="M45">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N45">
         <v>7</v>
@@ -3722,22 +3719,22 @@
         <v>6</v>
       </c>
       <c r="P45">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="Q45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S45">
-        <v>2.6</v>
+        <v>5.7</v>
       </c>
       <c r="T45">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U45">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="V45">
         <v>3</v>
@@ -3751,10 +3748,10 @@
         <v>66</v>
       </c>
       <c r="C46" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E46">
         <v>3</v>
@@ -3766,49 +3763,49 @@
         <v>3</v>
       </c>
       <c r="H46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I46">
         <v>4</v>
       </c>
       <c r="J46">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K46">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L46">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M46">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N46">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O46">
         <v>6</v>
       </c>
       <c r="P46">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="Q46">
         <v>2</v>
       </c>
       <c r="R46">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S46">
-        <v>6.4</v>
+        <v>12</v>
       </c>
       <c r="T46">
         <v>6</v>
       </c>
       <c r="U46">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="V46">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47" spans="1:22">
@@ -3819,64 +3816,64 @@
         <v>67</v>
       </c>
       <c r="C47" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E47">
         <v>2</v>
       </c>
       <c r="F47">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G47">
         <v>2</v>
       </c>
       <c r="H47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I47">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J47">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K47">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L47">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M47">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N47">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O47">
         <v>6</v>
       </c>
       <c r="P47">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="Q47">
         <v>1</v>
       </c>
       <c r="R47">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S47">
-        <v>5.7</v>
+        <v>10.6</v>
       </c>
       <c r="T47">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U47">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="V47">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48" spans="1:22">
@@ -3887,7 +3884,7 @@
         <v>68</v>
       </c>
       <c r="C48" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D48">
         <v>1</v>
@@ -3899,52 +3896,52 @@
         <v>1</v>
       </c>
       <c r="G48">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H48">
         <v>1</v>
       </c>
       <c r="I48">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J48">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K48">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L48">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M48">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N48">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O48">
         <v>6</v>
       </c>
       <c r="P48">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="Q48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R48">
         <v>4</v>
       </c>
       <c r="S48">
-        <v>3.6</v>
+        <v>6.7</v>
       </c>
       <c r="T48">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U48">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="V48">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:22">
@@ -3955,40 +3952,40 @@
         <v>69</v>
       </c>
       <c r="C49" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E49">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I49">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J49">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K49">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L49">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M49">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N49">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O49">
         <v>6</v>
@@ -3997,19 +3994,19 @@
         <v>43</v>
       </c>
       <c r="Q49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S49">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="T49">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U49">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="V49">
         <v>4</v>
@@ -4023,7 +4020,7 @@
         <v>70</v>
       </c>
       <c r="C50" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D50">
         <v>1</v>
@@ -4032,25 +4029,25 @@
         <v>1</v>
       </c>
       <c r="F50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H50">
         <v>1</v>
       </c>
       <c r="I50">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J50">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K50">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L50">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M50">
         <v>4</v>
@@ -4062,7 +4059,7 @@
         <v>6</v>
       </c>
       <c r="P50">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="Q50">
         <v>2</v>
@@ -4071,16 +4068,16 @@
         <v>3</v>
       </c>
       <c r="S50">
-        <v>2.2</v>
+        <v>6.2</v>
       </c>
       <c r="T50">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U50">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="V50">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51" spans="1:22">
@@ -4091,37 +4088,37 @@
         <v>71</v>
       </c>
       <c r="C51" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D51">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E51">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F51">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G51">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H51">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I51">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J51">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K51">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N51">
         <v>5</v>
@@ -4130,7 +4127,7 @@
         <v>6</v>
       </c>
       <c r="P51">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="Q51">
         <v>2</v>
@@ -4139,10 +4136,10 @@
         <v>3</v>
       </c>
       <c r="S51">
-        <v>7.2</v>
+        <v>4.5</v>
       </c>
       <c r="T51">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U51">
         <v>9</v>
@@ -4159,16 +4156,16 @@
         <v>72</v>
       </c>
       <c r="C52" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D52">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F52">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G52">
         <v>1</v>
@@ -4177,19 +4174,19 @@
         <v>1</v>
       </c>
       <c r="I52">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J52">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K52">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L52">
         <v>6</v>
       </c>
       <c r="M52">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N52">
         <v>6</v>
@@ -4198,25 +4195,25 @@
         <v>6</v>
       </c>
       <c r="P52">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="Q52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R52">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S52">
-        <v>6.8</v>
+        <v>9.6</v>
       </c>
       <c r="T52">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U52">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="V52">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53" spans="1:22">
@@ -4230,43 +4227,43 @@
         <v>102</v>
       </c>
       <c r="D53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G53">
         <v>3</v>
       </c>
       <c r="H53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I53">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J53">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K53">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L53">
         <v>5</v>
       </c>
       <c r="M53">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N53">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O53">
         <v>6</v>
       </c>
       <c r="P53">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="Q53">
         <v>1</v>
@@ -4275,16 +4272,16 @@
         <v>3</v>
       </c>
       <c r="S53">
-        <v>5</v>
+        <v>10.3</v>
       </c>
       <c r="T53">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U53">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="V53">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54" spans="1:22">
@@ -4298,58 +4295,58 @@
         <v>102</v>
       </c>
       <c r="D54">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E54">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F54">
         <v>2</v>
       </c>
       <c r="G54">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I54">
         <v>6</v>
       </c>
       <c r="J54">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K54">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L54">
         <v>6</v>
       </c>
       <c r="M54">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N54">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O54">
         <v>6</v>
       </c>
       <c r="P54">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="Q54">
         <v>1</v>
       </c>
       <c r="R54">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S54">
-        <v>7.3</v>
+        <v>3.9</v>
       </c>
       <c r="T54">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U54">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="V54">
         <v>3</v>
@@ -4366,58 +4363,58 @@
         <v>102</v>
       </c>
       <c r="D55">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E55">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F55">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G55">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H55">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I55">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J55">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K55">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L55">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M55">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N55">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O55">
         <v>6</v>
       </c>
       <c r="P55">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="Q55">
         <v>1</v>
       </c>
       <c r="R55">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S55">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="T55">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U55">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="V55">
         <v>4</v>
@@ -4434,58 +4431,58 @@
         <v>102</v>
       </c>
       <c r="D56">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E56">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F56">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G56">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H56">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I56">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J56">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K56">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L56">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M56">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N56">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O56">
         <v>6</v>
       </c>
       <c r="P56">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="Q56">
         <v>1</v>
       </c>
       <c r="R56">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S56">
-        <v>11.5</v>
+        <v>6.6</v>
       </c>
       <c r="T56">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="U56">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="V56">
         <v>4</v>
@@ -4505,13 +4502,13 @@
         <v>1</v>
       </c>
       <c r="E57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F57">
         <v>1</v>
       </c>
       <c r="G57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H57">
         <v>1</v>
@@ -4529,7 +4526,7 @@
         <v>7</v>
       </c>
       <c r="M57">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N57">
         <v>7</v>
@@ -4538,25 +4535,25 @@
         <v>6</v>
       </c>
       <c r="P57">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="Q57">
         <v>1</v>
       </c>
       <c r="R57">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S57">
-        <v>2.3</v>
+        <v>7</v>
       </c>
       <c r="T57">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U57">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="V57">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58" spans="1:22">
@@ -4570,58 +4567,58 @@
         <v>103</v>
       </c>
       <c r="D58">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E58">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F58">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G58">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H58">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I58">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J58">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K58">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L58">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M58">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N58">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O58">
         <v>6</v>
       </c>
       <c r="P58">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q58">
         <v>2</v>
       </c>
       <c r="R58">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S58">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="T58">
         <v>6</v>
       </c>
       <c r="U58">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="V58">
         <v>4</v>
@@ -4641,40 +4638,40 @@
         <v>3</v>
       </c>
       <c r="E59">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F59">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G59">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H59">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I59">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J59">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K59">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L59">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M59">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N59">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O59">
         <v>6</v>
       </c>
       <c r="P59">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="Q59">
         <v>1</v>
@@ -4682,11 +4679,14 @@
       <c r="R59">
         <v>3</v>
       </c>
+      <c r="S59">
+        <v>3.9</v>
+      </c>
       <c r="T59">
         <v>4</v>
       </c>
       <c r="U59">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="V59">
         <v>3</v>
@@ -4706,55 +4706,55 @@
         <v>2</v>
       </c>
       <c r="E60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G60">
         <v>2</v>
       </c>
       <c r="H60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I60">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J60">
         <v>6</v>
       </c>
       <c r="K60">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L60">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M60">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N60">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O60">
         <v>6</v>
       </c>
       <c r="P60">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="Q60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R60">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S60">
-        <v>10.6</v>
+        <v>9.4</v>
       </c>
       <c r="T60">
         <v>4</v>
       </c>
       <c r="U60">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="V60">
         <v>3</v>
@@ -4771,58 +4771,58 @@
         <v>103</v>
       </c>
       <c r="D61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F61">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I61">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J61">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K61">
         <v>4</v>
       </c>
       <c r="L61">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M61">
         <v>5</v>
       </c>
       <c r="N61">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O61">
         <v>6</v>
       </c>
       <c r="P61">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="Q61">
         <v>1</v>
       </c>
       <c r="R61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S61">
-        <v>5.6</v>
+        <v>2.2</v>
       </c>
       <c r="T61">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U61">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="V61">
         <v>3</v>
@@ -4839,13 +4839,13 @@
         <v>103</v>
       </c>
       <c r="D62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G62">
         <v>1</v>
@@ -4854,46 +4854,46 @@
         <v>1</v>
       </c>
       <c r="I62">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J62">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K62">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L62">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M62">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N62">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O62">
         <v>6</v>
       </c>
       <c r="P62">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Q62">
         <v>1</v>
       </c>
       <c r="R62">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S62">
-        <v>9.9</v>
+        <v>6.4</v>
       </c>
       <c r="T62">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U62">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="V62">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63" spans="1:22">
@@ -4910,58 +4910,58 @@
         <v>4</v>
       </c>
       <c r="E63">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F63">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G63">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H63">
         <v>4</v>
       </c>
       <c r="I63">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J63">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K63">
         <v>3</v>
       </c>
       <c r="L63">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M63">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N63">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O63">
         <v>6</v>
       </c>
       <c r="P63">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="Q63">
         <v>1</v>
       </c>
       <c r="R63">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S63">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="T63">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U63">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="V63">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64" spans="1:22">
@@ -4975,7 +4975,7 @@
         <v>101</v>
       </c>
       <c r="D64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E64">
         <v>2</v>
@@ -4993,43 +4993,40 @@
         <v>6</v>
       </c>
       <c r="J64">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K64">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L64">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M64">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N64">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O64">
         <v>6</v>
       </c>
-      <c r="P64">
-        <v>37</v>
-      </c>
       <c r="Q64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R64">
         <v>3</v>
       </c>
       <c r="S64">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="T64">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="U64">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="V64">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65" spans="1:22">
@@ -5064,13 +5061,13 @@
         <v>7</v>
       </c>
       <c r="K65">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L65">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M65">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N65">
         <v>7</v>
@@ -5079,25 +5076,25 @@
         <v>6</v>
       </c>
       <c r="P65">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="Q65">
         <v>2</v>
       </c>
       <c r="R65">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S65">
-        <v>6.4</v>
+        <v>7.9</v>
       </c>
       <c r="T65">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U65">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="V65">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66" spans="1:22">
@@ -5111,58 +5108,58 @@
         <v>101</v>
       </c>
       <c r="D66">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E66">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F66">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G66">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H66">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I66">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J66">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K66">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L66">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M66">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N66">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O66">
         <v>6</v>
       </c>
       <c r="P66">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="Q66">
         <v>1</v>
       </c>
       <c r="R66">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S66">
-        <v>5.1</v>
+        <v>7.5</v>
       </c>
       <c r="T66">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U66">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="V66">
         <v>3</v>
@@ -5182,58 +5179,58 @@
         <v>1</v>
       </c>
       <c r="E67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F67">
         <v>1</v>
       </c>
       <c r="G67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I67">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J67">
         <v>5</v>
       </c>
       <c r="K67">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L67">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M67">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N67">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O67">
         <v>6</v>
       </c>
       <c r="P67">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="Q67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R67">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S67">
-        <v>9.199999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="T67">
         <v>6</v>
       </c>
       <c r="U67">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="V67">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68" spans="1:22">
@@ -5256,49 +5253,49 @@
         <v>3</v>
       </c>
       <c r="G68">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H68">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I68">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J68">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K68">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L68">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M68">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N68">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O68">
         <v>6</v>
       </c>
       <c r="P68">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q68">
         <v>1</v>
       </c>
       <c r="R68">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S68">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="T68">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U68">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="V68">
         <v>3</v>
@@ -5321,37 +5318,37 @@
         <v>2</v>
       </c>
       <c r="F69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G69">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H69">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I69">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J69">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K69">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L69">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M69">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N69">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O69">
         <v>6</v>
       </c>
       <c r="P69">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="Q69">
         <v>1</v>
@@ -5360,16 +5357,16 @@
         <v>4</v>
       </c>
       <c r="S69">
-        <v>3.4</v>
+        <v>7.5</v>
       </c>
       <c r="T69">
         <v>3</v>
       </c>
       <c r="U69">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V69">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70" spans="1:22">
@@ -5383,7 +5380,7 @@
         <v>102</v>
       </c>
       <c r="D70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E70">
         <v>1</v>
@@ -5398,46 +5395,46 @@
         <v>1</v>
       </c>
       <c r="I70">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J70">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K70">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L70">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M70">
         <v>6</v>
       </c>
       <c r="N70">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O70">
         <v>6</v>
       </c>
       <c r="P70">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="Q70">
         <v>1</v>
       </c>
       <c r="R70">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S70">
-        <v>4.6</v>
+        <v>12</v>
       </c>
       <c r="T70">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U70">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="V70">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:22">
@@ -5451,61 +5448,61 @@
         <v>103</v>
       </c>
       <c r="D71">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E71">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F71">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G71">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H71">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I71">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J71">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K71">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L71">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M71">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N71">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O71">
         <v>6</v>
       </c>
       <c r="P71">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q71">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R71">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S71">
-        <v>5.8</v>
+        <v>3</v>
       </c>
       <c r="T71">
         <v>5</v>
       </c>
       <c r="U71">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="V71">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72" spans="1:22">
@@ -5519,34 +5516,34 @@
         <v>101</v>
       </c>
       <c r="D72">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E72">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F72">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G72">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H72">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I72">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J72">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K72">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L72">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M72">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N72">
         <v>5</v>
@@ -5555,7 +5552,7 @@
         <v>6</v>
       </c>
       <c r="P72">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="Q72">
         <v>2</v>
@@ -5564,16 +5561,16 @@
         <v>3</v>
       </c>
       <c r="S72">
-        <v>6.9</v>
+        <v>3.4</v>
       </c>
       <c r="T72">
         <v>5</v>
       </c>
       <c r="U72">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="V72">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73" spans="1:22">
@@ -5587,34 +5584,34 @@
         <v>102</v>
       </c>
       <c r="D73">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E73">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F73">
         <v>2</v>
       </c>
       <c r="G73">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H73">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I73">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J73">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K73">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L73">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M73">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N73">
         <v>6</v>
@@ -5623,25 +5620,25 @@
         <v>6</v>
       </c>
       <c r="P73">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="Q73">
         <v>1</v>
       </c>
       <c r="R73">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S73">
-        <v>6.5</v>
+        <v>7.6</v>
       </c>
       <c r="T73">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U73">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="V73">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74" spans="1:22">
@@ -5655,7 +5652,7 @@
         <v>101</v>
       </c>
       <c r="D74">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E74">
         <v>2</v>
@@ -5664,49 +5661,49 @@
         <v>1</v>
       </c>
       <c r="G74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I74">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J74">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K74">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L74">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M74">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N74">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O74">
         <v>6</v>
       </c>
       <c r="P74">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="Q74">
         <v>2</v>
       </c>
       <c r="R74">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S74">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="T74">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U74">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="V74">
         <v>4</v>
@@ -5723,61 +5720,61 @@
         <v>101</v>
       </c>
       <c r="D75">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F75">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G75">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H75">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I75">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J75">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K75">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L75">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M75">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N75">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O75">
         <v>6</v>
       </c>
       <c r="P75">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="Q75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R75">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S75">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="T75">
         <v>5</v>
       </c>
       <c r="U75">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="V75">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76" spans="1:22">
@@ -5794,55 +5791,55 @@
         <v>3</v>
       </c>
       <c r="E76">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F76">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G76">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H76">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I76">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L76">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M76">
         <v>3</v>
       </c>
       <c r="N76">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O76">
         <v>6</v>
       </c>
       <c r="P76">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q76">
         <v>1</v>
       </c>
       <c r="R76">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S76">
-        <v>18</v>
+        <v>5.1</v>
       </c>
       <c r="T76">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U76">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="V76">
         <v>3</v>
@@ -5859,25 +5856,25 @@
         <v>103</v>
       </c>
       <c r="D77">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E77">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F77">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G77">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H77">
         <v>3</v>
       </c>
       <c r="I77">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J77">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K77">
         <v>4</v>
@@ -5889,13 +5886,13 @@
         <v>4</v>
       </c>
       <c r="N77">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O77">
         <v>6</v>
       </c>
       <c r="P77">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="Q77">
         <v>1</v>
@@ -5904,16 +5901,16 @@
         <v>3</v>
       </c>
       <c r="S77">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="T77">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U77">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V77">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78" spans="1:22">
@@ -5927,34 +5924,34 @@
         <v>103</v>
       </c>
       <c r="D78">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E78">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F78">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G78">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H78">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I78">
         <v>7</v>
       </c>
       <c r="J78">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K78">
         <v>7</v>
       </c>
       <c r="L78">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M78">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N78">
         <v>6</v>
@@ -5963,25 +5960,25 @@
         <v>6</v>
       </c>
       <c r="P78">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="Q78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R78">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S78">
-        <v>3.1</v>
+        <v>10</v>
       </c>
       <c r="T78">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U78">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="V78">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79" spans="1:22">
@@ -5995,7 +5992,7 @@
         <v>101</v>
       </c>
       <c r="D79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E79">
         <v>2</v>
@@ -6004,52 +6001,52 @@
         <v>2</v>
       </c>
       <c r="G79">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H79">
         <v>1</v>
       </c>
       <c r="I79">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J79">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K79">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L79">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M79">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N79">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O79">
         <v>6</v>
       </c>
       <c r="P79">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="Q79">
         <v>1</v>
       </c>
       <c r="R79">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S79">
-        <v>8.4</v>
+        <v>9.1</v>
       </c>
       <c r="T79">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U79">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="V79">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80" spans="1:22">
@@ -6063,49 +6060,52 @@
         <v>101</v>
       </c>
       <c r="D80">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E80">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F80">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G80">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H80">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I80">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J80">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K80">
         <v>6</v>
       </c>
       <c r="L80">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M80">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N80">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O80">
         <v>6</v>
       </c>
       <c r="P80">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="Q80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R80">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="S80">
+        <v>5.3</v>
       </c>
       <c r="T80">
         <v>5</v>
@@ -6114,7 +6114,7 @@
         <v>22</v>
       </c>
       <c r="V80">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/data/T3_leader_cleaned.xlsx
+++ b/data/T3_leader_cleaned.xlsx
@@ -82,241 +82,241 @@
     <t>LeaderJobLevel</t>
   </si>
   <si>
+    <t>A_L14</t>
+  </si>
+  <si>
+    <t>A_L19</t>
+  </si>
+  <si>
+    <t>A_L08</t>
+  </si>
+  <si>
+    <t>B_L11</t>
+  </si>
+  <si>
+    <t>B_L07</t>
+  </si>
+  <si>
+    <t>C_L18</t>
+  </si>
+  <si>
+    <t>C_L26</t>
+  </si>
+  <si>
+    <t>A_L11</t>
+  </si>
+  <si>
+    <t>A_L10</t>
+  </si>
+  <si>
+    <t>B_L24</t>
+  </si>
+  <si>
+    <t>B_L22</t>
+  </si>
+  <si>
+    <t>C_L11</t>
+  </si>
+  <si>
+    <t>B_L30</t>
+  </si>
+  <si>
+    <t>C_L01</t>
+  </si>
+  <si>
+    <t>B_L09</t>
+  </si>
+  <si>
+    <t>B_L10</t>
+  </si>
+  <si>
+    <t>A_L26</t>
+  </si>
+  <si>
+    <t>C_L06</t>
+  </si>
+  <si>
+    <t>A_L15</t>
+  </si>
+  <si>
+    <t>C_L08</t>
+  </si>
+  <si>
+    <t>B_L06</t>
+  </si>
+  <si>
+    <t>C_L13</t>
+  </si>
+  <si>
+    <t>C_L21</t>
+  </si>
+  <si>
+    <t>A_L28</t>
+  </si>
+  <si>
+    <t>C_L17</t>
+  </si>
+  <si>
+    <t>C_L07</t>
+  </si>
+  <si>
+    <t>A_L18</t>
+  </si>
+  <si>
+    <t>B_L01</t>
+  </si>
+  <si>
+    <t>B_L08</t>
+  </si>
+  <si>
+    <t>A_L06</t>
+  </si>
+  <si>
+    <t>C_L25</t>
+  </si>
+  <si>
     <t>A_L13</t>
   </si>
   <si>
-    <t>A_L18</t>
+    <t>C_L29</t>
+  </si>
+  <si>
+    <t>B_L26</t>
+  </si>
+  <si>
+    <t>C_L10</t>
+  </si>
+  <si>
+    <t>B_L25</t>
+  </si>
+  <si>
+    <t>B_L27</t>
+  </si>
+  <si>
+    <t>C_L03</t>
+  </si>
+  <si>
+    <t>A_L21</t>
+  </si>
+  <si>
+    <t>C_L30</t>
+  </si>
+  <si>
+    <t>C_L28</t>
+  </si>
+  <si>
+    <t>B_L02</t>
+  </si>
+  <si>
+    <t>C_L16</t>
+  </si>
+  <si>
+    <t>C_L22</t>
+  </si>
+  <si>
+    <t>B_L04</t>
+  </si>
+  <si>
+    <t>C_L20</t>
+  </si>
+  <si>
+    <t>B_L12</t>
+  </si>
+  <si>
+    <t>A_L17</t>
+  </si>
+  <si>
+    <t>C_L02</t>
+  </si>
+  <si>
+    <t>B_L20</t>
+  </si>
+  <si>
+    <t>A_L09</t>
+  </si>
+  <si>
+    <t>B_L19</t>
+  </si>
+  <si>
+    <t>B_L03</t>
+  </si>
+  <si>
+    <t>B_L23</t>
+  </si>
+  <si>
+    <t>B_L16</t>
   </si>
   <si>
     <t>A_L07</t>
   </si>
   <si>
-    <t>B_L11</t>
-  </si>
-  <si>
-    <t>B_L05</t>
-  </si>
-  <si>
-    <t>C_L20</t>
-  </si>
-  <si>
-    <t>C_L26</t>
-  </si>
-  <si>
-    <t>A_L10</t>
-  </si>
-  <si>
-    <t>A_L09</t>
-  </si>
-  <si>
-    <t>B_L24</t>
-  </si>
-  <si>
-    <t>B_L22</t>
+    <t>C_L14</t>
+  </si>
+  <si>
+    <t>B_L29</t>
+  </si>
+  <si>
+    <t>A_L03</t>
+  </si>
+  <si>
+    <t>C_L09</t>
   </si>
   <si>
     <t>C_L12</t>
   </si>
   <si>
-    <t>C_L01</t>
-  </si>
-  <si>
-    <t>C_L02</t>
-  </si>
-  <si>
-    <t>B_L08</t>
-  </si>
-  <si>
-    <t>B_L10</t>
+    <t>A_L04</t>
   </si>
   <si>
     <t>A_L25</t>
   </si>
   <si>
-    <t>C_L06</t>
-  </si>
-  <si>
-    <t>A_L14</t>
-  </si>
-  <si>
-    <t>C_L09</t>
-  </si>
-  <si>
-    <t>B_L04</t>
-  </si>
-  <si>
-    <t>C_L14</t>
-  </si>
-  <si>
-    <t>C_L22</t>
+    <t>A_L29</t>
+  </si>
+  <si>
+    <t>A_L16</t>
+  </si>
+  <si>
+    <t>B_L15</t>
+  </si>
+  <si>
+    <t>B_L21</t>
+  </si>
+  <si>
+    <t>A_L23</t>
+  </si>
+  <si>
+    <t>B_L14</t>
+  </si>
+  <si>
+    <t>C_L27</t>
+  </si>
+  <si>
+    <t>A_L12</t>
+  </si>
+  <si>
+    <t>B_L18</t>
+  </si>
+  <si>
+    <t>A_L22</t>
+  </si>
+  <si>
+    <t>A_L24</t>
+  </si>
+  <si>
+    <t>A_L01</t>
+  </si>
+  <si>
+    <t>C_L24</t>
+  </si>
+  <si>
+    <t>C_L05</t>
+  </si>
+  <si>
+    <t>A_L05</t>
   </si>
   <si>
     <t>A_L27</t>
-  </si>
-  <si>
-    <t>C_L19</t>
-  </si>
-  <si>
-    <t>C_L07</t>
-  </si>
-  <si>
-    <t>A_L17</t>
-  </si>
-  <si>
-    <t>A_L29</t>
-  </si>
-  <si>
-    <t>A_L05</t>
-  </si>
-  <si>
-    <t>C_L25</t>
-  </si>
-  <si>
-    <t>A_L12</t>
-  </si>
-  <si>
-    <t>C_L29</t>
-  </si>
-  <si>
-    <t>B_L27</t>
-  </si>
-  <si>
-    <t>C_L11</t>
-  </si>
-  <si>
-    <t>B_L25</t>
-  </si>
-  <si>
-    <t>B_L29</t>
-  </si>
-  <si>
-    <t>C_L04</t>
-  </si>
-  <si>
-    <t>A_L19</t>
-  </si>
-  <si>
-    <t>C_L30</t>
-  </si>
-  <si>
-    <t>C_L28</t>
-  </si>
-  <si>
-    <t>B_L01</t>
-  </si>
-  <si>
-    <t>C_L18</t>
-  </si>
-  <si>
-    <t>C_L23</t>
-  </si>
-  <si>
-    <t>B_L03</t>
-  </si>
-  <si>
-    <t>C_L21</t>
-  </si>
-  <si>
-    <t>B_L12</t>
-  </si>
-  <si>
-    <t>A_L16</t>
-  </si>
-  <si>
-    <t>C_L03</t>
-  </si>
-  <si>
-    <t>B_L20</t>
-  </si>
-  <si>
-    <t>A_L08</t>
-  </si>
-  <si>
-    <t>B_L19</t>
-  </si>
-  <si>
-    <t>B_L02</t>
-  </si>
-  <si>
-    <t>B_L07</t>
-  </si>
-  <si>
-    <t>B_L23</t>
-  </si>
-  <si>
-    <t>B_L16</t>
-  </si>
-  <si>
-    <t>A_L06</t>
-  </si>
-  <si>
-    <t>C_L17</t>
-  </si>
-  <si>
-    <t>B_L30</t>
-  </si>
-  <si>
-    <t>A_L02</t>
-  </si>
-  <si>
-    <t>C_L10</t>
-  </si>
-  <si>
-    <t>C_L13</t>
-  </si>
-  <si>
-    <t>A_L03</t>
-  </si>
-  <si>
-    <t>A_L24</t>
-  </si>
-  <si>
-    <t>A_L28</t>
-  </si>
-  <si>
-    <t>A_L15</t>
-  </si>
-  <si>
-    <t>B_L15</t>
-  </si>
-  <si>
-    <t>B_L21</t>
-  </si>
-  <si>
-    <t>A_L21</t>
-  </si>
-  <si>
-    <t>B_L14</t>
-  </si>
-  <si>
-    <t>C_L27</t>
-  </si>
-  <si>
-    <t>A_L11</t>
-  </si>
-  <si>
-    <t>B_L18</t>
-  </si>
-  <si>
-    <t>A_L20</t>
-  </si>
-  <si>
-    <t>A_L22</t>
-  </si>
-  <si>
-    <t>A_L01</t>
-  </si>
-  <si>
-    <t>C_L24</t>
-  </si>
-  <si>
-    <t>C_L05</t>
-  </si>
-  <si>
-    <t>A_L04</t>
-  </si>
-  <si>
-    <t>A_L26</t>
   </si>
   <si>
     <t>A</t>
@@ -765,61 +765,61 @@
         <v>101</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O2">
         <v>6</v>
       </c>
       <c r="P2">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="Q2">
         <v>1</v>
       </c>
       <c r="R2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S2">
-        <v>6.7</v>
+        <v>6</v>
       </c>
       <c r="T2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -833,61 +833,61 @@
         <v>101</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F3">
         <v>3</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="N3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O3">
         <v>6</v>
       </c>
       <c r="P3">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="Q3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S3">
-        <v>3.7</v>
+        <v>11.5</v>
       </c>
       <c r="T3">
         <v>3</v>
       </c>
       <c r="U3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -901,25 +901,25 @@
         <v>101</v>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K4">
         <v>4</v>
@@ -928,34 +928,34 @@
         <v>4</v>
       </c>
       <c r="M4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O4">
         <v>6</v>
       </c>
       <c r="P4">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="Q4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R4">
         <v>3</v>
       </c>
       <c r="S4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U4">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="V4">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -969,13 +969,13 @@
         <v>102</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G5">
         <v>3</v>
@@ -984,46 +984,46 @@
         <v>4</v>
       </c>
       <c r="I5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O5">
         <v>6</v>
       </c>
       <c r="P5">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="Q5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S5">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="T5">
         <v>6</v>
       </c>
       <c r="U5">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="V5">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -1037,19 +1037,19 @@
         <v>102</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6">
         <v>6</v>
@@ -1058,13 +1058,13 @@
         <v>6</v>
       </c>
       <c r="K6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N6">
         <v>7</v>
@@ -1079,16 +1079,16 @@
         <v>1</v>
       </c>
       <c r="R6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S6">
-        <v>6.1</v>
+        <v>2.4</v>
       </c>
       <c r="T6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U6">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V6">
         <v>3</v>
@@ -1117,49 +1117,49 @@
         <v>2</v>
       </c>
       <c r="H7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K7">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L7">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N7">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O7">
         <v>6</v>
       </c>
       <c r="P7">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="Q7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R7">
         <v>3</v>
       </c>
       <c r="S7">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="T7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U7">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="V7">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -1173,61 +1173,61 @@
         <v>103</v>
       </c>
       <c r="D8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O8">
         <v>6</v>
       </c>
       <c r="P8">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="Q8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R8">
         <v>3</v>
       </c>
       <c r="S8">
-        <v>4.7</v>
+        <v>9</v>
       </c>
       <c r="T8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U8">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="V8">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -1241,43 +1241,43 @@
         <v>101</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I9">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K9">
         <v>5</v>
       </c>
       <c r="L9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O9">
         <v>6</v>
       </c>
       <c r="P9">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="Q9">
         <v>1</v>
@@ -1286,16 +1286,16 @@
         <v>4</v>
       </c>
       <c r="S9">
-        <v>5.6</v>
+        <v>2.7</v>
       </c>
       <c r="T9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U9">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="V9">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1309,61 +1309,58 @@
         <v>101</v>
       </c>
       <c r="D10">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E10">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L10">
         <v>4</v>
       </c>
       <c r="M10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N10">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O10">
         <v>6</v>
       </c>
-      <c r="P10">
-        <v>43</v>
-      </c>
       <c r="Q10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S10">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="T10">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U10">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="V10">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1377,25 +1374,25 @@
         <v>102</v>
       </c>
       <c r="D11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F11">
         <v>2</v>
       </c>
       <c r="G11">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K11">
         <v>6</v>
@@ -1404,34 +1401,34 @@
         <v>6</v>
       </c>
       <c r="M11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O11">
         <v>6</v>
       </c>
       <c r="P11">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="Q11">
         <v>1</v>
       </c>
       <c r="R11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S11">
-        <v>4.1</v>
+        <v>6.4</v>
       </c>
       <c r="T11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U11">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="V11">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1445,58 +1442,58 @@
         <v>102</v>
       </c>
       <c r="D12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F12">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I12">
         <v>6</v>
       </c>
       <c r="J12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K12">
         <v>5</v>
       </c>
       <c r="L12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M12">
         <v>5</v>
       </c>
       <c r="N12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O12">
         <v>6</v>
       </c>
       <c r="P12">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="Q12">
         <v>2</v>
       </c>
       <c r="R12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S12">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="T12">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U12">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="V12">
         <v>3</v>
@@ -1513,34 +1510,34 @@
         <v>103</v>
       </c>
       <c r="D13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="F13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G13">
         <v>2</v>
       </c>
       <c r="H13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I13">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K13">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M13">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N13">
         <v>5</v>
@@ -1549,25 +1546,25 @@
         <v>6</v>
       </c>
       <c r="P13">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="Q13">
         <v>1</v>
       </c>
       <c r="R13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S13">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="T13">
         <v>6</v>
       </c>
       <c r="U13">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="V13">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -1578,10 +1575,10 @@
         <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E14">
         <v>3</v>
@@ -1590,52 +1587,52 @@
         <v>2</v>
       </c>
       <c r="G14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I14">
         <v>4</v>
       </c>
       <c r="J14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L14">
         <v>5</v>
       </c>
       <c r="M14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O14">
         <v>6</v>
       </c>
       <c r="P14">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="Q14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R14">
         <v>3</v>
       </c>
       <c r="S14">
-        <v>3.4</v>
+        <v>5.7</v>
       </c>
       <c r="T14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U14">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V14">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1649,58 +1646,61 @@
         <v>103</v>
       </c>
       <c r="D15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E15">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L15">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N15">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O15">
         <v>6</v>
       </c>
       <c r="P15">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="Q15">
         <v>1</v>
       </c>
       <c r="R15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S15">
-        <v>2.6</v>
+        <v>7.4</v>
+      </c>
+      <c r="T15">
+        <v>6</v>
       </c>
       <c r="U15">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="V15">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -1714,58 +1714,58 @@
         <v>102</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I16">
         <v>5</v>
       </c>
       <c r="J16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L16">
         <v>5</v>
       </c>
       <c r="M16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N16">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O16">
         <v>6</v>
       </c>
       <c r="P16">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="Q16">
         <v>2</v>
       </c>
       <c r="R16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S16">
-        <v>13.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="T16">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U16">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="V16">
         <v>4</v>
@@ -1782,7 +1782,7 @@
         <v>102</v>
       </c>
       <c r="D17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -1791,49 +1791,49 @@
         <v>3</v>
       </c>
       <c r="G17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J17">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K17">
         <v>5</v>
       </c>
       <c r="L17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M17">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O17">
         <v>6</v>
       </c>
       <c r="P17">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="Q17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S17">
-        <v>4.9</v>
+        <v>6.3</v>
       </c>
       <c r="T17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U17">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="V17">
         <v>3</v>
@@ -1850,43 +1850,43 @@
         <v>101</v>
       </c>
       <c r="D18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F18">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H18">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J18">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K18">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L18">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M18">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N18">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O18">
         <v>6</v>
       </c>
       <c r="P18">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="Q18">
         <v>1</v>
@@ -1895,16 +1895,16 @@
         <v>4</v>
       </c>
       <c r="S18">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="T18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U18">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="V18">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -1918,7 +1918,7 @@
         <v>103</v>
       </c>
       <c r="D19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -1930,25 +1930,25 @@
         <v>1</v>
       </c>
       <c r="H19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J19">
         <v>6</v>
       </c>
       <c r="K19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M19">
         <v>7</v>
       </c>
       <c r="N19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O19">
         <v>6</v>
@@ -1957,19 +1957,19 @@
         <v>45</v>
       </c>
       <c r="Q19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S19">
-        <v>4.9</v>
+        <v>8</v>
       </c>
       <c r="T19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U19">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="V19">
         <v>4</v>
@@ -1986,58 +1986,58 @@
         <v>101</v>
       </c>
       <c r="D20">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F20">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H20">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I20">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J20">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O20">
         <v>6</v>
       </c>
       <c r="P20">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="Q20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S20">
-        <v>1.2</v>
+        <v>5.6</v>
       </c>
       <c r="T20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U20">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="V20">
         <v>3</v>
@@ -2054,34 +2054,34 @@
         <v>103</v>
       </c>
       <c r="D21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I21">
         <v>4</v>
       </c>
       <c r="J21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L21">
         <v>3</v>
       </c>
       <c r="M21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N21">
         <v>4</v>
@@ -2090,25 +2090,25 @@
         <v>6</v>
       </c>
       <c r="P21">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="Q21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R21">
         <v>3</v>
       </c>
       <c r="S21">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="T21">
         <v>6</v>
       </c>
       <c r="U21">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="V21">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -2122,58 +2122,58 @@
         <v>102</v>
       </c>
       <c r="D22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I22">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J22">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K22">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L22">
         <v>5</v>
       </c>
       <c r="M22">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N22">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O22">
         <v>6</v>
       </c>
       <c r="P22">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="Q22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R22">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S22">
-        <v>2.6</v>
+        <v>5.5</v>
       </c>
       <c r="T22">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U22">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="V22">
         <v>3</v>
@@ -2190,61 +2190,61 @@
         <v>103</v>
       </c>
       <c r="D23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E23">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I23">
         <v>5</v>
       </c>
       <c r="J23">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K23">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L23">
         <v>5</v>
       </c>
       <c r="M23">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N23">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O23">
         <v>6</v>
       </c>
       <c r="P23">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="Q23">
         <v>1</v>
       </c>
       <c r="R23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S23">
-        <v>8.1</v>
+        <v>4.4</v>
       </c>
       <c r="T23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U23">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="V23">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -2261,34 +2261,34 @@
         <v>2</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G24">
         <v>2</v>
       </c>
       <c r="H24">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I24">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K24">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N24">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O24">
         <v>6</v>
@@ -2303,13 +2303,16 @@
         <v>3</v>
       </c>
       <c r="S24">
-        <v>5.4</v>
+        <v>1.5</v>
+      </c>
+      <c r="T24">
+        <v>7</v>
       </c>
       <c r="U24">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="V24">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -2323,61 +2326,61 @@
         <v>101</v>
       </c>
       <c r="D25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F25">
         <v>1</v>
       </c>
       <c r="G25">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H25">
         <v>1</v>
       </c>
       <c r="I25">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J25">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M25">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N25">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O25">
         <v>6</v>
       </c>
       <c r="P25">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="Q25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R25">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S25">
-        <v>7.7</v>
+        <v>11.9</v>
       </c>
       <c r="T25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U25">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="V25">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -2403,46 +2406,46 @@
         <v>1</v>
       </c>
       <c r="H26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I26">
         <v>5</v>
       </c>
       <c r="J26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O26">
         <v>6</v>
       </c>
       <c r="P26">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="Q26">
         <v>1</v>
       </c>
       <c r="R26">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S26">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="T26">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U26">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="V26">
         <v>4</v>
@@ -2462,7 +2465,7 @@
         <v>4</v>
       </c>
       <c r="E27">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F27">
         <v>4</v>
@@ -2474,43 +2477,43 @@
         <v>4</v>
       </c>
       <c r="I27">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J27">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L27">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M27">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N27">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O27">
         <v>6</v>
       </c>
       <c r="P27">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="Q27">
         <v>1</v>
       </c>
       <c r="R27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S27">
-        <v>8.9</v>
+        <v>3.8</v>
       </c>
       <c r="T27">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U27">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="V27">
         <v>4</v>
@@ -2527,61 +2530,61 @@
         <v>101</v>
       </c>
       <c r="D28">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E28">
         <v>2</v>
       </c>
       <c r="F28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H28">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I28">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J28">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K28">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L28">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M28">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N28">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O28">
         <v>6</v>
       </c>
       <c r="P28">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R28">
         <v>3</v>
       </c>
       <c r="S28">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T28">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U28">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="V28">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -2592,64 +2595,64 @@
         <v>49</v>
       </c>
       <c r="C29" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D29">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E29">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F29">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G29">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H29">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I29">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J29">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K29">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L29">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M29">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N29">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O29">
         <v>6</v>
       </c>
       <c r="P29">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="Q29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R29">
         <v>3</v>
       </c>
       <c r="S29">
-        <v>3.8</v>
+        <v>5.2</v>
       </c>
       <c r="T29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U29">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="V29">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30" spans="1:22">
@@ -2660,64 +2663,64 @@
         <v>50</v>
       </c>
       <c r="C30" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D30">
         <v>2</v>
       </c>
       <c r="E30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G30">
         <v>3</v>
       </c>
       <c r="H30">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J30">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K30">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L30">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M30">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N30">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O30">
         <v>6</v>
       </c>
       <c r="P30">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="Q30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R30">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S30">
-        <v>8.4</v>
+        <v>6.5</v>
       </c>
       <c r="T30">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="U30">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="V30">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:22">
@@ -2728,64 +2731,64 @@
         <v>51</v>
       </c>
       <c r="C31" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H31">
         <v>1</v>
       </c>
       <c r="I31">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J31">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L31">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M31">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N31">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O31">
         <v>6</v>
       </c>
       <c r="P31">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="Q31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R31">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S31">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="T31">
         <v>4</v>
       </c>
       <c r="U31">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V31">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:22">
@@ -2796,13 +2799,13 @@
         <v>52</v>
       </c>
       <c r="C32" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F32">
         <v>1</v>
@@ -2814,43 +2817,43 @@
         <v>1</v>
       </c>
       <c r="I32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M32">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N32">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O32">
         <v>6</v>
       </c>
       <c r="P32">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="Q32">
         <v>1</v>
       </c>
       <c r="R32">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S32">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="T32">
         <v>5</v>
       </c>
       <c r="U32">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="V32">
         <v>3</v>
@@ -2864,7 +2867,7 @@
         <v>53</v>
       </c>
       <c r="C33" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D33">
         <v>2</v>
@@ -2873,7 +2876,7 @@
         <v>1</v>
       </c>
       <c r="F33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G33">
         <v>2</v>
@@ -2882,13 +2885,13 @@
         <v>2</v>
       </c>
       <c r="I33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J33">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L33">
         <v>7</v>
@@ -2903,22 +2906,22 @@
         <v>6</v>
       </c>
       <c r="P33">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Q33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R33">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S33">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="T33">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="V33">
         <v>4</v>
@@ -2932,31 +2935,31 @@
         <v>54</v>
       </c>
       <c r="C34" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F34">
         <v>1</v>
       </c>
       <c r="G34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H34">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I34">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J34">
         <v>6</v>
       </c>
       <c r="K34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L34">
         <v>6</v>
@@ -2965,28 +2968,28 @@
         <v>6</v>
       </c>
       <c r="N34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O34">
         <v>6</v>
       </c>
       <c r="P34">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Q34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R34">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S34">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="T34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U34">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="V34">
         <v>3</v>
@@ -3000,40 +3003,40 @@
         <v>55</v>
       </c>
       <c r="C35" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D35">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F35">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G35">
         <v>3</v>
       </c>
       <c r="H35">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K35">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M35">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N35">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O35">
         <v>6</v>
@@ -3048,16 +3051,16 @@
         <v>3</v>
       </c>
       <c r="S35">
-        <v>4.4</v>
+        <v>1.8</v>
       </c>
       <c r="T35">
         <v>6</v>
       </c>
       <c r="U35">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="V35">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:22">
@@ -3068,64 +3071,64 @@
         <v>56</v>
       </c>
       <c r="C36" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H36">
         <v>1</v>
       </c>
       <c r="I36">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J36">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K36">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L36">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M36">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N36">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O36">
         <v>6</v>
       </c>
       <c r="P36">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S36">
-        <v>8.5</v>
+        <v>2.6</v>
       </c>
       <c r="T36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U36">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="V36">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37" spans="1:22">
@@ -3139,7 +3142,7 @@
         <v>102</v>
       </c>
       <c r="D37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E37">
         <v>2</v>
@@ -3148,22 +3151,22 @@
         <v>3</v>
       </c>
       <c r="G37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I37">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J37">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K37">
         <v>5</v>
       </c>
       <c r="L37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M37">
         <v>5</v>
@@ -3175,25 +3178,25 @@
         <v>6</v>
       </c>
       <c r="P37">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="Q37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R37">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S37">
-        <v>2.1</v>
+        <v>3.6</v>
       </c>
       <c r="T37">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U37">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V37">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38" spans="1:22">
@@ -3204,61 +3207,61 @@
         <v>58</v>
       </c>
       <c r="C38" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D38">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E38">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F38">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G38">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H38">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I38">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K38">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L38">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N38">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O38">
         <v>6</v>
       </c>
       <c r="P38">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="Q38">
         <v>1</v>
       </c>
       <c r="R38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S38">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="T38">
         <v>5</v>
       </c>
       <c r="U38">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="V38">
         <v>4</v>
@@ -3272,37 +3275,37 @@
         <v>59</v>
       </c>
       <c r="C39" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D39">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E39">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F39">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G39">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H39">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I39">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J39">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L39">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M39">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N39">
         <v>5</v>
@@ -3311,25 +3314,25 @@
         <v>6</v>
       </c>
       <c r="P39">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="Q39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R39">
         <v>3</v>
       </c>
       <c r="S39">
-        <v>2.8</v>
+        <v>6.3</v>
       </c>
       <c r="T39">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U39">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="V39">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40" spans="1:22">
@@ -3340,7 +3343,7 @@
         <v>60</v>
       </c>
       <c r="C40" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D40">
         <v>1</v>
@@ -3358,43 +3361,43 @@
         <v>1</v>
       </c>
       <c r="I40">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M40">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O40">
         <v>6</v>
       </c>
       <c r="P40">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="Q40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S40">
-        <v>4.4</v>
+        <v>1.8</v>
       </c>
       <c r="T40">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U40">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="V40">
         <v>3</v>
@@ -3411,55 +3414,55 @@
         <v>103</v>
       </c>
       <c r="D41">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E41">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F41">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G41">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H41">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I41">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J41">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L41">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M41">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N41">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O41">
         <v>6</v>
       </c>
       <c r="P41">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="Q41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R41">
         <v>5</v>
       </c>
       <c r="S41">
-        <v>10.2</v>
+        <v>2.9</v>
       </c>
       <c r="T41">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U41">
         <v>13</v>
@@ -3476,40 +3479,40 @@
         <v>62</v>
       </c>
       <c r="C42" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G42">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H42">
         <v>2</v>
       </c>
       <c r="I42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J42">
         <v>5</v>
       </c>
       <c r="K42">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L42">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M42">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N42">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O42">
         <v>6</v>
@@ -3524,16 +3527,16 @@
         <v>4</v>
       </c>
       <c r="S42">
-        <v>5.9</v>
+        <v>3.3</v>
       </c>
       <c r="T42">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U42">
         <v>14</v>
       </c>
       <c r="V42">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43" spans="1:22">
@@ -3544,64 +3547,64 @@
         <v>63</v>
       </c>
       <c r="C43" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H43">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I43">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J43">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K43">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M43">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N43">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O43">
         <v>6</v>
       </c>
       <c r="P43">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="Q43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R43">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S43">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="T43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U43">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="V43">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44" spans="1:22">
@@ -3615,19 +3618,19 @@
         <v>103</v>
       </c>
       <c r="D44">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E44">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F44">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H44">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I44">
         <v>5</v>
@@ -3636,13 +3639,13 @@
         <v>5</v>
       </c>
       <c r="K44">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M44">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N44">
         <v>4</v>
@@ -3651,25 +3654,25 @@
         <v>6</v>
       </c>
       <c r="P44">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="Q44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R44">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S44">
-        <v>6.5</v>
+        <v>7.9</v>
       </c>
       <c r="T44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U44">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V44">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45" spans="1:22">
@@ -3680,37 +3683,37 @@
         <v>65</v>
       </c>
       <c r="C45" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D45">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E45">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F45">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G45">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H45">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I45">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J45">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K45">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L45">
         <v>6</v>
       </c>
       <c r="M45">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N45">
         <v>7</v>
@@ -3719,22 +3722,22 @@
         <v>6</v>
       </c>
       <c r="P45">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="Q45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R45">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S45">
-        <v>5.7</v>
+        <v>2.6</v>
       </c>
       <c r="T45">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U45">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="V45">
         <v>3</v>
@@ -3748,10 +3751,10 @@
         <v>66</v>
       </c>
       <c r="C46" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E46">
         <v>3</v>
@@ -3763,49 +3766,49 @@
         <v>3</v>
       </c>
       <c r="H46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I46">
         <v>4</v>
       </c>
       <c r="J46">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K46">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L46">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M46">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N46">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O46">
         <v>6</v>
       </c>
       <c r="P46">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="Q46">
         <v>2</v>
       </c>
       <c r="R46">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S46">
-        <v>12</v>
+        <v>6.4</v>
       </c>
       <c r="T46">
         <v>6</v>
       </c>
       <c r="U46">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="V46">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:22">
@@ -3816,64 +3819,64 @@
         <v>67</v>
       </c>
       <c r="C47" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E47">
         <v>2</v>
       </c>
       <c r="F47">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G47">
         <v>2</v>
       </c>
       <c r="H47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I47">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J47">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K47">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L47">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M47">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N47">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O47">
         <v>6</v>
       </c>
       <c r="P47">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q47">
         <v>1</v>
       </c>
       <c r="R47">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S47">
-        <v>10.6</v>
+        <v>5.7</v>
       </c>
       <c r="T47">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U47">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="V47">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48" spans="1:22">
@@ -3884,7 +3887,7 @@
         <v>68</v>
       </c>
       <c r="C48" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D48">
         <v>1</v>
@@ -3896,52 +3899,52 @@
         <v>1</v>
       </c>
       <c r="G48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H48">
         <v>1</v>
       </c>
       <c r="I48">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J48">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K48">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L48">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M48">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N48">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O48">
         <v>6</v>
       </c>
       <c r="P48">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="Q48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R48">
         <v>4</v>
       </c>
       <c r="S48">
-        <v>6.7</v>
+        <v>3.6</v>
       </c>
       <c r="T48">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U48">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V48">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49" spans="1:22">
@@ -3952,22 +3955,22 @@
         <v>69</v>
       </c>
       <c r="C49" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I49">
         <v>5</v>
@@ -3979,13 +3982,13 @@
         <v>5</v>
       </c>
       <c r="L49">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M49">
         <v>5</v>
       </c>
       <c r="N49">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O49">
         <v>6</v>
@@ -3994,19 +3997,19 @@
         <v>43</v>
       </c>
       <c r="Q49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R49">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S49">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="T49">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U49">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="V49">
         <v>4</v>
@@ -4020,46 +4023,46 @@
         <v>70</v>
       </c>
       <c r="C50" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D50">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E50">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F50">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G50">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H50">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I50">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J50">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K50">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L50">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M50">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N50">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O50">
         <v>6</v>
       </c>
       <c r="P50">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="Q50">
         <v>2</v>
@@ -4068,16 +4071,16 @@
         <v>3</v>
       </c>
       <c r="S50">
-        <v>6.2</v>
+        <v>2.2</v>
       </c>
       <c r="T50">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U50">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="V50">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51" spans="1:22">
@@ -4088,37 +4091,37 @@
         <v>71</v>
       </c>
       <c r="C51" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D51">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E51">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F51">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G51">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H51">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K51">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N51">
         <v>5</v>
@@ -4127,7 +4130,7 @@
         <v>6</v>
       </c>
       <c r="P51">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="Q51">
         <v>2</v>
@@ -4136,10 +4139,10 @@
         <v>3</v>
       </c>
       <c r="S51">
-        <v>4.5</v>
+        <v>7.2</v>
       </c>
       <c r="T51">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U51">
         <v>9</v>
@@ -4156,16 +4159,16 @@
         <v>72</v>
       </c>
       <c r="C52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D52">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F52">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G52">
         <v>1</v>
@@ -4174,46 +4177,46 @@
         <v>1</v>
       </c>
       <c r="I52">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J52">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K52">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L52">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M52">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N52">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O52">
         <v>6</v>
       </c>
       <c r="P52">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="Q52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R52">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S52">
-        <v>9.6</v>
+        <v>6.8</v>
       </c>
       <c r="T52">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U52">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="V52">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53" spans="1:22">
@@ -4227,19 +4230,19 @@
         <v>102</v>
       </c>
       <c r="D53">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F53">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G53">
         <v>3</v>
       </c>
       <c r="H53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I53">
         <v>6</v>
@@ -4251,19 +4254,19 @@
         <v>5</v>
       </c>
       <c r="L53">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M53">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N53">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O53">
         <v>6</v>
       </c>
       <c r="P53">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="Q53">
         <v>1</v>
@@ -4272,16 +4275,16 @@
         <v>3</v>
       </c>
       <c r="S53">
-        <v>10.3</v>
+        <v>5</v>
       </c>
       <c r="T53">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U53">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="V53">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54" spans="1:22">
@@ -4295,58 +4298,58 @@
         <v>102</v>
       </c>
       <c r="D54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E54">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F54">
         <v>2</v>
       </c>
       <c r="G54">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H54">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I54">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J54">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K54">
         <v>5</v>
       </c>
       <c r="L54">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M54">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N54">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O54">
         <v>6</v>
       </c>
       <c r="P54">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="Q54">
         <v>1</v>
       </c>
       <c r="R54">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S54">
-        <v>3.9</v>
+        <v>7.3</v>
       </c>
       <c r="T54">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U54">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="V54">
         <v>3</v>
@@ -4363,10 +4366,10 @@
         <v>102</v>
       </c>
       <c r="D55">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E55">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F55">
         <v>5</v>
@@ -4375,46 +4378,46 @@
         <v>5</v>
       </c>
       <c r="H55">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I55">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J55">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K55">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L55">
         <v>2</v>
       </c>
       <c r="M55">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N55">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O55">
         <v>6</v>
       </c>
       <c r="P55">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="Q55">
         <v>1</v>
       </c>
       <c r="R55">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S55">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="T55">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U55">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="V55">
         <v>4</v>
@@ -4431,13 +4434,13 @@
         <v>102</v>
       </c>
       <c r="D56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E56">
         <v>2</v>
       </c>
       <c r="F56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G56">
         <v>2</v>
@@ -4446,43 +4449,43 @@
         <v>1</v>
       </c>
       <c r="I56">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J56">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K56">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L56">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M56">
         <v>5</v>
       </c>
       <c r="N56">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O56">
         <v>6</v>
       </c>
       <c r="P56">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="Q56">
         <v>1</v>
       </c>
       <c r="R56">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S56">
-        <v>6.6</v>
+        <v>11.5</v>
       </c>
       <c r="T56">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="U56">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="V56">
         <v>4</v>
@@ -4499,61 +4502,61 @@
         <v>101</v>
       </c>
       <c r="D57">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E57">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F57">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G57">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H57">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I57">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J57">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K57">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L57">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M57">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N57">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O57">
         <v>6</v>
       </c>
       <c r="P57">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="Q57">
         <v>1</v>
       </c>
       <c r="R57">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S57">
-        <v>7</v>
+        <v>2.3</v>
       </c>
       <c r="T57">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="U57">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="V57">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="58" spans="1:22">
@@ -4567,58 +4570,58 @@
         <v>103</v>
       </c>
       <c r="D58">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E58">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F58">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G58">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H58">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I58">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J58">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K58">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L58">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M58">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N58">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O58">
         <v>6</v>
       </c>
       <c r="P58">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q58">
         <v>2</v>
       </c>
       <c r="R58">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S58">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="T58">
         <v>6</v>
       </c>
       <c r="U58">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="V58">
         <v>4</v>
@@ -4635,43 +4638,43 @@
         <v>102</v>
       </c>
       <c r="D59">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E59">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F59">
         <v>4</v>
       </c>
       <c r="G59">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H59">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I59">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J59">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K59">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L59">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M59">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N59">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O59">
         <v>6</v>
       </c>
       <c r="P59">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="Q59">
         <v>1</v>
@@ -4679,14 +4682,11 @@
       <c r="R59">
         <v>3</v>
       </c>
-      <c r="S59">
-        <v>3.9</v>
-      </c>
       <c r="T59">
         <v>4</v>
       </c>
       <c r="U59">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="V59">
         <v>3</v>
@@ -4703,58 +4703,58 @@
         <v>101</v>
       </c>
       <c r="D60">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E60">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F60">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G60">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H60">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I60">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J60">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K60">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L60">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M60">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N60">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O60">
         <v>6</v>
       </c>
       <c r="P60">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="Q60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R60">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S60">
-        <v>9.4</v>
+        <v>10.6</v>
       </c>
       <c r="T60">
         <v>4</v>
       </c>
       <c r="U60">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="V60">
         <v>3</v>
@@ -4771,58 +4771,58 @@
         <v>103</v>
       </c>
       <c r="D61">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E61">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F61">
         <v>3</v>
       </c>
       <c r="G61">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H61">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I61">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J61">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K61">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L61">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M61">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N61">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O61">
         <v>6</v>
       </c>
       <c r="P61">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="Q61">
         <v>1</v>
       </c>
       <c r="R61">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S61">
-        <v>2.2</v>
+        <v>5.6</v>
       </c>
       <c r="T61">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U61">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="V61">
         <v>3</v>
@@ -4839,61 +4839,61 @@
         <v>103</v>
       </c>
       <c r="D62">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E62">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F62">
         <v>2</v>
       </c>
       <c r="G62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I62">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J62">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K62">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L62">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M62">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N62">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O62">
         <v>6</v>
       </c>
       <c r="P62">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q62">
         <v>1</v>
       </c>
       <c r="R62">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S62">
-        <v>6.4</v>
+        <v>9.9</v>
       </c>
       <c r="T62">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U62">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="V62">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63" spans="1:22">
@@ -4907,61 +4907,61 @@
         <v>101</v>
       </c>
       <c r="D63">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E63">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F63">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G63">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H63">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I63">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J63">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K63">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L63">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M63">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N63">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O63">
         <v>6</v>
       </c>
       <c r="P63">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="Q63">
         <v>1</v>
       </c>
       <c r="R63">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S63">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="T63">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U63">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="V63">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64" spans="1:22">
@@ -4975,58 +4975,61 @@
         <v>101</v>
       </c>
       <c r="D64">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E64">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F64">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G64">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H64">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I64">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J64">
         <v>5</v>
       </c>
       <c r="K64">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L64">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M64">
         <v>5</v>
       </c>
       <c r="N64">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O64">
         <v>6</v>
       </c>
+      <c r="P64">
+        <v>37</v>
+      </c>
       <c r="Q64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R64">
         <v>3</v>
       </c>
       <c r="S64">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="T64">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="U64">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="V64">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65" spans="1:22">
@@ -5040,61 +5043,61 @@
         <v>101</v>
       </c>
       <c r="D65">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F65">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G65">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H65">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I65">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J65">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K65">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L65">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M65">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N65">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O65">
         <v>6</v>
       </c>
       <c r="P65">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="Q65">
         <v>2</v>
       </c>
       <c r="R65">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S65">
-        <v>7.9</v>
+        <v>6.4</v>
       </c>
       <c r="T65">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U65">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="V65">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66" spans="1:22">
@@ -5108,58 +5111,58 @@
         <v>101</v>
       </c>
       <c r="D66">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E66">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F66">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G66">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H66">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I66">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J66">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K66">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L66">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M66">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N66">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O66">
         <v>6</v>
       </c>
       <c r="P66">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="Q66">
         <v>1</v>
       </c>
       <c r="R66">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S66">
-        <v>7.5</v>
+        <v>5.1</v>
       </c>
       <c r="T66">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U66">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="V66">
         <v>3</v>
@@ -5179,58 +5182,58 @@
         <v>1</v>
       </c>
       <c r="E67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F67">
         <v>1</v>
       </c>
       <c r="G67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I67">
         <v>5</v>
       </c>
       <c r="J67">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K67">
         <v>5</v>
       </c>
       <c r="L67">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M67">
         <v>4</v>
       </c>
       <c r="N67">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O67">
         <v>6</v>
       </c>
       <c r="P67">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="Q67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R67">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S67">
-        <v>3.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="T67">
         <v>6</v>
       </c>
       <c r="U67">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="V67">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68" spans="1:22">
@@ -5253,49 +5256,49 @@
         <v>3</v>
       </c>
       <c r="G68">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H68">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I68">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J68">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K68">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L68">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M68">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N68">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O68">
         <v>6</v>
       </c>
       <c r="P68">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Q68">
         <v>1</v>
       </c>
       <c r="R68">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S68">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="T68">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U68">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="V68">
         <v>3</v>
@@ -5318,37 +5321,37 @@
         <v>2</v>
       </c>
       <c r="F69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G69">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H69">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I69">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J69">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K69">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L69">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M69">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N69">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O69">
         <v>6</v>
       </c>
       <c r="P69">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="Q69">
         <v>1</v>
@@ -5357,16 +5360,16 @@
         <v>4</v>
       </c>
       <c r="S69">
-        <v>7.5</v>
+        <v>3.4</v>
       </c>
       <c r="T69">
         <v>3</v>
       </c>
       <c r="U69">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="V69">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:22">
@@ -5380,7 +5383,7 @@
         <v>102</v>
       </c>
       <c r="D70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E70">
         <v>1</v>
@@ -5395,46 +5398,46 @@
         <v>1</v>
       </c>
       <c r="I70">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J70">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K70">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L70">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M70">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N70">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O70">
         <v>6</v>
       </c>
       <c r="P70">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="Q70">
         <v>1</v>
       </c>
       <c r="R70">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S70">
-        <v>12</v>
+        <v>4.6</v>
       </c>
       <c r="T70">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U70">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="V70">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71" spans="1:22">
@@ -5457,19 +5460,19 @@
         <v>1</v>
       </c>
       <c r="G71">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H71">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I71">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J71">
         <v>5</v>
       </c>
       <c r="K71">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L71">
         <v>6</v>
@@ -5484,25 +5487,25 @@
         <v>6</v>
       </c>
       <c r="P71">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Q71">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R71">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S71">
-        <v>3</v>
+        <v>5.8</v>
       </c>
       <c r="T71">
         <v>5</v>
       </c>
       <c r="U71">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="V71">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72" spans="1:22">
@@ -5516,43 +5519,43 @@
         <v>101</v>
       </c>
       <c r="D72">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E72">
         <v>2</v>
       </c>
       <c r="F72">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G72">
         <v>3</v>
       </c>
       <c r="H72">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I72">
         <v>7</v>
       </c>
       <c r="J72">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K72">
         <v>7</v>
       </c>
       <c r="L72">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M72">
         <v>7</v>
       </c>
       <c r="N72">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O72">
         <v>6</v>
       </c>
       <c r="P72">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="Q72">
         <v>2</v>
@@ -5561,16 +5564,16 @@
         <v>3</v>
       </c>
       <c r="S72">
-        <v>3.4</v>
+        <v>6.9</v>
       </c>
       <c r="T72">
         <v>5</v>
       </c>
       <c r="U72">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V72">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73" spans="1:22">
@@ -5590,55 +5593,55 @@
         <v>3</v>
       </c>
       <c r="F73">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G73">
         <v>3</v>
       </c>
       <c r="H73">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I73">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J73">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K73">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L73">
         <v>5</v>
       </c>
       <c r="M73">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N73">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O73">
         <v>6</v>
       </c>
       <c r="P73">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="Q73">
         <v>1</v>
       </c>
       <c r="R73">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S73">
-        <v>7.6</v>
+        <v>6.5</v>
       </c>
       <c r="T73">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U73">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="V73">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74" spans="1:22">
@@ -5655,55 +5658,55 @@
         <v>3</v>
       </c>
       <c r="E74">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I74">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J74">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K74">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L74">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M74">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N74">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O74">
         <v>6</v>
       </c>
       <c r="P74">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="Q74">
         <v>2</v>
       </c>
       <c r="R74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S74">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="T74">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U74">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="V74">
         <v>4</v>
@@ -5720,61 +5723,61 @@
         <v>101</v>
       </c>
       <c r="D75">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F75">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G75">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H75">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I75">
         <v>6</v>
       </c>
       <c r="J75">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K75">
         <v>4</v>
       </c>
       <c r="L75">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M75">
         <v>5</v>
       </c>
       <c r="N75">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O75">
         <v>6</v>
       </c>
       <c r="P75">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="Q75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R75">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S75">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="T75">
         <v>5</v>
       </c>
       <c r="U75">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="V75">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76" spans="1:22">
@@ -5791,19 +5794,19 @@
         <v>3</v>
       </c>
       <c r="E76">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F76">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G76">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H76">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I76">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J76">
         <v>3</v>
@@ -5815,7 +5818,7 @@
         <v>4</v>
       </c>
       <c r="M76">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N76">
         <v>4</v>
@@ -5824,22 +5827,22 @@
         <v>6</v>
       </c>
       <c r="P76">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q76">
         <v>1</v>
       </c>
       <c r="R76">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S76">
-        <v>5.1</v>
+        <v>18</v>
       </c>
       <c r="T76">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U76">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="V76">
         <v>3</v>
@@ -5856,43 +5859,43 @@
         <v>103</v>
       </c>
       <c r="D77">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E77">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F77">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G77">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H77">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I77">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J77">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K77">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L77">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M77">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N77">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O77">
         <v>6</v>
       </c>
       <c r="P77">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="Q77">
         <v>1</v>
@@ -5901,16 +5904,16 @@
         <v>3</v>
       </c>
       <c r="S77">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="T77">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U77">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V77">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78" spans="1:22">
@@ -5924,34 +5927,34 @@
         <v>103</v>
       </c>
       <c r="D78">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E78">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F78">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G78">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H78">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I78">
         <v>7</v>
       </c>
       <c r="J78">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K78">
         <v>7</v>
       </c>
       <c r="L78">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M78">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N78">
         <v>6</v>
@@ -5960,25 +5963,25 @@
         <v>6</v>
       </c>
       <c r="P78">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="Q78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R78">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S78">
-        <v>10</v>
+        <v>3.1</v>
       </c>
       <c r="T78">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U78">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="V78">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79" spans="1:22">
@@ -5995,58 +5998,58 @@
         <v>2</v>
       </c>
       <c r="E79">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F79">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G79">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I79">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J79">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K79">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L79">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M79">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N79">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O79">
         <v>6</v>
       </c>
       <c r="P79">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="Q79">
         <v>1</v>
       </c>
       <c r="R79">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S79">
-        <v>9.1</v>
+        <v>8.4</v>
       </c>
       <c r="T79">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U79">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="V79">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80" spans="1:22">
@@ -6060,52 +6063,49 @@
         <v>101</v>
       </c>
       <c r="D80">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E80">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F80">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G80">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H80">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I80">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J80">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K80">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L80">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M80">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N80">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O80">
         <v>6</v>
       </c>
       <c r="P80">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="Q80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R80">
-        <v>2</v>
-      </c>
-      <c r="S80">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="T80">
         <v>5</v>
@@ -6114,7 +6114,7 @@
         <v>22</v>
       </c>
       <c r="V80">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/data/T3_leader_cleaned.xlsx
+++ b/data/T3_leader_cleaned.xlsx
@@ -82,241 +82,241 @@
     <t>LeaderJobLevel</t>
   </si>
   <si>
+    <t>A_L15</t>
+  </si>
+  <si>
+    <t>A_L20</t>
+  </si>
+  <si>
+    <t>A_L09</t>
+  </si>
+  <si>
+    <t>B_L11</t>
+  </si>
+  <si>
+    <t>B_L07</t>
+  </si>
+  <si>
+    <t>C_L19</t>
+  </si>
+  <si>
+    <t>C_L25</t>
+  </si>
+  <si>
+    <t>A_L12</t>
+  </si>
+  <si>
+    <t>A_L11</t>
+  </si>
+  <si>
+    <t>B_L25</t>
+  </si>
+  <si>
+    <t>B_L22</t>
+  </si>
+  <si>
+    <t>C_L11</t>
+  </si>
+  <si>
+    <t>C_L01</t>
+  </si>
+  <si>
+    <t>C_L02</t>
+  </si>
+  <si>
+    <t>B_L09</t>
+  </si>
+  <si>
+    <t>B_L10</t>
+  </si>
+  <si>
+    <t>A_L26</t>
+  </si>
+  <si>
+    <t>C_L06</t>
+  </si>
+  <si>
+    <t>A_L16</t>
+  </si>
+  <si>
+    <t>C_L08</t>
+  </si>
+  <si>
+    <t>B_L06</t>
+  </si>
+  <si>
+    <t>C_L14</t>
+  </si>
+  <si>
+    <t>C_L21</t>
+  </si>
+  <si>
+    <t>A_L29</t>
+  </si>
+  <si>
+    <t>C_L18</t>
+  </si>
+  <si>
+    <t>C_L07</t>
+  </si>
+  <si>
+    <t>A_L19</t>
+  </si>
+  <si>
+    <t>B_L02</t>
+  </si>
+  <si>
+    <t>A_L06</t>
+  </si>
+  <si>
+    <t>C_L24</t>
+  </si>
+  <si>
     <t>A_L14</t>
   </si>
   <si>
-    <t>A_L19</t>
+    <t>C_L29</t>
+  </si>
+  <si>
+    <t>B_L27</t>
+  </si>
+  <si>
+    <t>C_L10</t>
+  </si>
+  <si>
+    <t>B_L26</t>
+  </si>
+  <si>
+    <t>B_L29</t>
+  </si>
+  <si>
+    <t>C_L04</t>
+  </si>
+  <si>
+    <t>A_L21</t>
+  </si>
+  <si>
+    <t>C_L30</t>
+  </si>
+  <si>
+    <t>C_L28</t>
+  </si>
+  <si>
+    <t>B_L03</t>
+  </si>
+  <si>
+    <t>C_L17</t>
+  </si>
+  <si>
+    <t>C_L22</t>
+  </si>
+  <si>
+    <t>B_L05</t>
+  </si>
+  <si>
+    <t>C_L20</t>
+  </si>
+  <si>
+    <t>B_L12</t>
+  </si>
+  <si>
+    <t>A_L18</t>
+  </si>
+  <si>
+    <t>C_L03</t>
+  </si>
+  <si>
+    <t>B_L20</t>
+  </si>
+  <si>
+    <t>A_L10</t>
+  </si>
+  <si>
+    <t>B_L19</t>
+  </si>
+  <si>
+    <t>B_L04</t>
+  </si>
+  <si>
+    <t>B_L08</t>
+  </si>
+  <si>
+    <t>B_L23</t>
+  </si>
+  <si>
+    <t>B_L16</t>
   </si>
   <si>
     <t>A_L08</t>
   </si>
   <si>
-    <t>B_L11</t>
-  </si>
-  <si>
-    <t>B_L07</t>
-  </si>
-  <si>
-    <t>C_L18</t>
+    <t>C_L16</t>
+  </si>
+  <si>
+    <t>B_L30</t>
+  </si>
+  <si>
+    <t>A_L03</t>
+  </si>
+  <si>
+    <t>C_L09</t>
+  </si>
+  <si>
+    <t>C_L13</t>
+  </si>
+  <si>
+    <t>A_L04</t>
+  </si>
+  <si>
+    <t>A_L25</t>
+  </si>
+  <si>
+    <t>B_L01</t>
+  </si>
+  <si>
+    <t>A_L17</t>
+  </si>
+  <si>
+    <t>B_L15</t>
+  </si>
+  <si>
+    <t>B_L21</t>
+  </si>
+  <si>
+    <t>A_L23</t>
+  </si>
+  <si>
+    <t>B_L14</t>
   </si>
   <si>
     <t>C_L26</t>
   </si>
   <si>
-    <t>A_L11</t>
-  </si>
-  <si>
-    <t>A_L10</t>
-  </si>
-  <si>
-    <t>B_L24</t>
-  </si>
-  <si>
-    <t>B_L22</t>
-  </si>
-  <si>
-    <t>C_L11</t>
-  </si>
-  <si>
-    <t>B_L30</t>
-  </si>
-  <si>
-    <t>C_L01</t>
-  </si>
-  <si>
-    <t>B_L09</t>
-  </si>
-  <si>
-    <t>B_L10</t>
-  </si>
-  <si>
-    <t>A_L26</t>
-  </si>
-  <si>
-    <t>C_L06</t>
-  </si>
-  <si>
-    <t>A_L15</t>
-  </si>
-  <si>
-    <t>C_L08</t>
-  </si>
-  <si>
-    <t>B_L06</t>
-  </si>
-  <si>
-    <t>C_L13</t>
-  </si>
-  <si>
-    <t>C_L21</t>
+    <t>A_L13</t>
+  </si>
+  <si>
+    <t>B_L18</t>
+  </si>
+  <si>
+    <t>A_L22</t>
+  </si>
+  <si>
+    <t>A_L24</t>
+  </si>
+  <si>
+    <t>A_L01</t>
+  </si>
+  <si>
+    <t>C_L23</t>
+  </si>
+  <si>
+    <t>C_L05</t>
+  </si>
+  <si>
+    <t>A_L05</t>
   </si>
   <si>
     <t>A_L28</t>
-  </si>
-  <si>
-    <t>C_L17</t>
-  </si>
-  <si>
-    <t>C_L07</t>
-  </si>
-  <si>
-    <t>A_L18</t>
-  </si>
-  <si>
-    <t>B_L01</t>
-  </si>
-  <si>
-    <t>B_L08</t>
-  </si>
-  <si>
-    <t>A_L06</t>
-  </si>
-  <si>
-    <t>C_L25</t>
-  </si>
-  <si>
-    <t>A_L13</t>
-  </si>
-  <si>
-    <t>C_L29</t>
-  </si>
-  <si>
-    <t>B_L26</t>
-  </si>
-  <si>
-    <t>C_L10</t>
-  </si>
-  <si>
-    <t>B_L25</t>
-  </si>
-  <si>
-    <t>B_L27</t>
-  </si>
-  <si>
-    <t>C_L03</t>
-  </si>
-  <si>
-    <t>A_L21</t>
-  </si>
-  <si>
-    <t>C_L30</t>
-  </si>
-  <si>
-    <t>C_L28</t>
-  </si>
-  <si>
-    <t>B_L02</t>
-  </si>
-  <si>
-    <t>C_L16</t>
-  </si>
-  <si>
-    <t>C_L22</t>
-  </si>
-  <si>
-    <t>B_L04</t>
-  </si>
-  <si>
-    <t>C_L20</t>
-  </si>
-  <si>
-    <t>B_L12</t>
-  </si>
-  <si>
-    <t>A_L17</t>
-  </si>
-  <si>
-    <t>C_L02</t>
-  </si>
-  <si>
-    <t>B_L20</t>
-  </si>
-  <si>
-    <t>A_L09</t>
-  </si>
-  <si>
-    <t>B_L19</t>
-  </si>
-  <si>
-    <t>B_L03</t>
-  </si>
-  <si>
-    <t>B_L23</t>
-  </si>
-  <si>
-    <t>B_L16</t>
-  </si>
-  <si>
-    <t>A_L07</t>
-  </si>
-  <si>
-    <t>C_L14</t>
-  </si>
-  <si>
-    <t>B_L29</t>
-  </si>
-  <si>
-    <t>A_L03</t>
-  </si>
-  <si>
-    <t>C_L09</t>
-  </si>
-  <si>
-    <t>C_L12</t>
-  </si>
-  <si>
-    <t>A_L04</t>
-  </si>
-  <si>
-    <t>A_L25</t>
-  </si>
-  <si>
-    <t>A_L29</t>
-  </si>
-  <si>
-    <t>A_L16</t>
-  </si>
-  <si>
-    <t>B_L15</t>
-  </si>
-  <si>
-    <t>B_L21</t>
-  </si>
-  <si>
-    <t>A_L23</t>
-  </si>
-  <si>
-    <t>B_L14</t>
-  </si>
-  <si>
-    <t>C_L27</t>
-  </si>
-  <si>
-    <t>A_L12</t>
-  </si>
-  <si>
-    <t>B_L18</t>
-  </si>
-  <si>
-    <t>A_L22</t>
-  </si>
-  <si>
-    <t>A_L24</t>
-  </si>
-  <si>
-    <t>A_L01</t>
-  </si>
-  <si>
-    <t>C_L24</t>
-  </si>
-  <si>
-    <t>C_L05</t>
-  </si>
-  <si>
-    <t>A_L05</t>
-  </si>
-  <si>
-    <t>A_L27</t>
   </si>
   <si>
     <t>A</t>
@@ -765,61 +765,61 @@
         <v>101</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J2">
         <v>3</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M2">
         <v>4</v>
       </c>
       <c r="N2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O2">
         <v>6</v>
       </c>
       <c r="P2">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="Q2">
         <v>1</v>
       </c>
       <c r="R2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S2">
-        <v>6</v>
+        <v>6.7</v>
       </c>
       <c r="T2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -833,61 +833,61 @@
         <v>101</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <v>3</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O3">
         <v>6</v>
       </c>
       <c r="P3">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="Q3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S3">
-        <v>11.5</v>
+        <v>3.7</v>
       </c>
       <c r="T3">
         <v>3</v>
       </c>
       <c r="U3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="V3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -901,25 +901,25 @@
         <v>101</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K4">
         <v>4</v>
@@ -928,34 +928,34 @@
         <v>4</v>
       </c>
       <c r="M4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O4">
         <v>6</v>
       </c>
       <c r="P4">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="Q4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R4">
         <v>3</v>
       </c>
       <c r="S4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U4">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="V4">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -969,13 +969,13 @@
         <v>102</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G5">
         <v>3</v>
@@ -984,46 +984,46 @@
         <v>4</v>
       </c>
       <c r="I5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O5">
         <v>6</v>
       </c>
       <c r="P5">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="Q5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S5">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="T5">
         <v>6</v>
       </c>
       <c r="U5">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="V5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -1037,7 +1037,7 @@
         <v>102</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1052,22 +1052,22 @@
         <v>2</v>
       </c>
       <c r="I6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M6">
         <v>6</v>
       </c>
       <c r="N6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O6">
         <v>6</v>
@@ -1079,16 +1079,16 @@
         <v>1</v>
       </c>
       <c r="R6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S6">
-        <v>2.4</v>
+        <v>6.1</v>
       </c>
       <c r="T6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V6">
         <v>3</v>
@@ -1105,16 +1105,16 @@
         <v>103</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H7">
         <v>2</v>
@@ -1123,43 +1123,43 @@
         <v>6</v>
       </c>
       <c r="J7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L7">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M7">
         <v>6</v>
       </c>
       <c r="N7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O7">
         <v>6</v>
       </c>
       <c r="P7">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="Q7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R7">
         <v>3</v>
       </c>
       <c r="S7">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="T7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U7">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="V7">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -1173,61 +1173,61 @@
         <v>103</v>
       </c>
       <c r="D8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O8">
         <v>6</v>
       </c>
       <c r="P8">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="Q8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R8">
         <v>3</v>
       </c>
       <c r="S8">
-        <v>9</v>
+        <v>4.7</v>
       </c>
       <c r="T8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U8">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="V8">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -1241,43 +1241,43 @@
         <v>101</v>
       </c>
       <c r="D9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I9">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J9">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L9">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O9">
         <v>6</v>
       </c>
       <c r="P9">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="Q9">
         <v>1</v>
@@ -1286,16 +1286,16 @@
         <v>4</v>
       </c>
       <c r="S9">
-        <v>2.7</v>
+        <v>5.6</v>
       </c>
       <c r="T9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U9">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="V9">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1309,58 +1309,61 @@
         <v>101</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I10">
         <v>5</v>
       </c>
       <c r="J10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K10">
         <v>5</v>
       </c>
       <c r="L10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M10">
         <v>5</v>
       </c>
       <c r="N10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O10">
         <v>6</v>
       </c>
+      <c r="P10">
+        <v>43</v>
+      </c>
       <c r="Q10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S10">
-        <v>2.6</v>
+        <v>4.5</v>
       </c>
       <c r="T10">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="U10">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="V10">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1374,25 +1377,25 @@
         <v>102</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F11">
         <v>2</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I11">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J11">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K11">
         <v>6</v>
@@ -1401,34 +1404,34 @@
         <v>6</v>
       </c>
       <c r="M11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O11">
         <v>6</v>
       </c>
       <c r="P11">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="Q11">
         <v>1</v>
       </c>
       <c r="R11">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S11">
-        <v>6.4</v>
+        <v>4.1</v>
       </c>
       <c r="T11">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U11">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="V11">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1442,58 +1445,58 @@
         <v>102</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H12">
         <v>2</v>
       </c>
       <c r="I12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J12">
         <v>6</v>
       </c>
       <c r="K12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O12">
         <v>6</v>
       </c>
       <c r="P12">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="Q12">
         <v>2</v>
       </c>
       <c r="R12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S12">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="T12">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U12">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="V12">
         <v>3</v>
@@ -1510,34 +1513,34 @@
         <v>103</v>
       </c>
       <c r="D13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="F13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G13">
         <v>2</v>
       </c>
       <c r="H13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I13">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K13">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M13">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N13">
         <v>5</v>
@@ -1546,25 +1549,25 @@
         <v>6</v>
       </c>
       <c r="P13">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="Q13">
         <v>1</v>
       </c>
       <c r="R13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S13">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="T13">
         <v>6</v>
       </c>
       <c r="U13">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="V13">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -1575,10 +1578,10 @@
         <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E14">
         <v>3</v>
@@ -1587,52 +1590,52 @@
         <v>2</v>
       </c>
       <c r="G14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I14">
         <v>4</v>
       </c>
       <c r="J14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L14">
         <v>5</v>
       </c>
       <c r="M14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O14">
         <v>6</v>
       </c>
       <c r="P14">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Q14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R14">
         <v>3</v>
       </c>
       <c r="S14">
-        <v>5.7</v>
+        <v>3.4</v>
       </c>
       <c r="T14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U14">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="V14">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1646,61 +1649,58 @@
         <v>103</v>
       </c>
       <c r="D15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L15">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N15">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O15">
         <v>6</v>
       </c>
       <c r="P15">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="Q15">
         <v>1</v>
       </c>
       <c r="R15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S15">
-        <v>7.4</v>
-      </c>
-      <c r="T15">
-        <v>6</v>
+        <v>2.6</v>
       </c>
       <c r="U15">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="V15">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -1714,10 +1714,10 @@
         <v>102</v>
       </c>
       <c r="D16">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E16">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F16">
         <v>3</v>
@@ -1732,40 +1732,40 @@
         <v>5</v>
       </c>
       <c r="J16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L16">
         <v>5</v>
       </c>
       <c r="M16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N16">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O16">
         <v>6</v>
       </c>
       <c r="P16">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="Q16">
         <v>2</v>
       </c>
       <c r="R16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S16">
-        <v>9.199999999999999</v>
+        <v>13.8</v>
       </c>
       <c r="T16">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U16">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="V16">
         <v>4</v>
@@ -1782,58 +1782,58 @@
         <v>102</v>
       </c>
       <c r="D17">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G17">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H17">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I17">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J17">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K17">
         <v>5</v>
       </c>
       <c r="L17">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M17">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N17">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O17">
         <v>6</v>
       </c>
       <c r="P17">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="Q17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S17">
-        <v>6.3</v>
+        <v>4.9</v>
       </c>
       <c r="T17">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U17">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="V17">
         <v>3</v>
@@ -1853,40 +1853,40 @@
         <v>1</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H18">
         <v>2</v>
       </c>
       <c r="I18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J18">
         <v>4</v>
       </c>
       <c r="K18">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L18">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M18">
         <v>5</v>
       </c>
       <c r="N18">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O18">
         <v>6</v>
       </c>
       <c r="P18">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q18">
         <v>1</v>
@@ -1895,16 +1895,16 @@
         <v>4</v>
       </c>
       <c r="S18">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="T18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U18">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="V18">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -1918,7 +1918,7 @@
         <v>103</v>
       </c>
       <c r="D19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -1930,22 +1930,22 @@
         <v>1</v>
       </c>
       <c r="H19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I19">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K19">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L19">
         <v>6</v>
       </c>
       <c r="M19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N19">
         <v>6</v>
@@ -1957,19 +1957,19 @@
         <v>45</v>
       </c>
       <c r="Q19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S19">
-        <v>8</v>
+        <v>4.9</v>
       </c>
       <c r="T19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U19">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="V19">
         <v>4</v>
@@ -1986,58 +1986,58 @@
         <v>101</v>
       </c>
       <c r="D20">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E20">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F20">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G20">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H20">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I20">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J20">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K20">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L20">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M20">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N20">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O20">
         <v>6</v>
       </c>
       <c r="P20">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="Q20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S20">
-        <v>5.6</v>
+        <v>1.2</v>
       </c>
       <c r="T20">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U20">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="V20">
         <v>3</v>
@@ -2054,22 +2054,22 @@
         <v>103</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21">
         <v>2</v>
       </c>
       <c r="F21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I21">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J21">
         <v>4</v>
@@ -2078,37 +2078,37 @@
         <v>4</v>
       </c>
       <c r="L21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M21">
         <v>3</v>
       </c>
       <c r="N21">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O21">
         <v>6</v>
       </c>
       <c r="P21">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="Q21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R21">
         <v>3</v>
       </c>
       <c r="S21">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="T21">
         <v>6</v>
       </c>
       <c r="U21">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="V21">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -2125,55 +2125,55 @@
         <v>1</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22">
         <v>1</v>
       </c>
       <c r="H22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I22">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J22">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K22">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L22">
         <v>5</v>
       </c>
       <c r="M22">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N22">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O22">
         <v>6</v>
       </c>
       <c r="P22">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="Q22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S22">
-        <v>5.5</v>
+        <v>2.6</v>
       </c>
       <c r="T22">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U22">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="V22">
         <v>3</v>
@@ -2190,61 +2190,61 @@
         <v>103</v>
       </c>
       <c r="D23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I23">
         <v>5</v>
       </c>
       <c r="J23">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K23">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L23">
         <v>5</v>
       </c>
       <c r="M23">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N23">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O23">
         <v>6</v>
       </c>
       <c r="P23">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="Q23">
         <v>1</v>
       </c>
       <c r="R23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S23">
-        <v>4.4</v>
+        <v>8.1</v>
       </c>
       <c r="T23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U23">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="V23">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -2261,34 +2261,34 @@
         <v>2</v>
       </c>
       <c r="E24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F24">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G24">
         <v>2</v>
       </c>
       <c r="H24">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I24">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K24">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L24">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M24">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N24">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O24">
         <v>6</v>
@@ -2303,16 +2303,13 @@
         <v>3</v>
       </c>
       <c r="S24">
-        <v>1.5</v>
-      </c>
-      <c r="T24">
-        <v>7</v>
+        <v>5.4</v>
       </c>
       <c r="U24">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="V24">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -2326,61 +2323,61 @@
         <v>101</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G25">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I25">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J25">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K25">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L25">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M25">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N25">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O25">
         <v>6</v>
       </c>
       <c r="P25">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="Q25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R25">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S25">
-        <v>11.9</v>
+        <v>7.7</v>
       </c>
       <c r="T25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U25">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="V25">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -2394,10 +2391,10 @@
         <v>103</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26">
         <v>1</v>
@@ -2406,46 +2403,46 @@
         <v>1</v>
       </c>
       <c r="H26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J26">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K26">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L26">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M26">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N26">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O26">
         <v>6</v>
       </c>
       <c r="P26">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Q26">
         <v>1</v>
       </c>
       <c r="R26">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S26">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="T26">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U26">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="V26">
         <v>4</v>
@@ -2465,7 +2462,7 @@
         <v>4</v>
       </c>
       <c r="E27">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F27">
         <v>4</v>
@@ -2477,43 +2474,43 @@
         <v>4</v>
       </c>
       <c r="I27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J27">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K27">
         <v>3</v>
       </c>
       <c r="L27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N27">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O27">
         <v>6</v>
       </c>
       <c r="P27">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="Q27">
         <v>1</v>
       </c>
       <c r="R27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S27">
-        <v>3.8</v>
+        <v>8.9</v>
       </c>
       <c r="T27">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U27">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="V27">
         <v>4</v>
@@ -2530,10 +2527,10 @@
         <v>101</v>
       </c>
       <c r="D28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F28">
         <v>1</v>
@@ -2542,49 +2539,49 @@
         <v>2</v>
       </c>
       <c r="H28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I28">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J28">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K28">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L28">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M28">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N28">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O28">
         <v>6</v>
       </c>
       <c r="P28">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Q28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R28">
         <v>3</v>
       </c>
       <c r="S28">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T28">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U28">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="V28">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -2598,61 +2595,61 @@
         <v>102</v>
       </c>
       <c r="D29">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F29">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G29">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H29">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I29">
         <v>5</v>
       </c>
       <c r="J29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K29">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L29">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M29">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N29">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O29">
         <v>6</v>
       </c>
       <c r="P29">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="Q29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R29">
         <v>3</v>
       </c>
       <c r="S29">
-        <v>5.2</v>
+        <v>3.8</v>
       </c>
       <c r="T29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U29">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="V29">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:22">
@@ -2663,22 +2660,22 @@
         <v>50</v>
       </c>
       <c r="C30" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E30">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F30">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H30">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I30">
         <v>7</v>
@@ -2690,7 +2687,7 @@
         <v>7</v>
       </c>
       <c r="L30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M30">
         <v>7</v>
@@ -2702,25 +2699,25 @@
         <v>6</v>
       </c>
       <c r="P30">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="Q30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R30">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S30">
-        <v>6.5</v>
+        <v>8.4</v>
       </c>
       <c r="T30">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U30">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="V30">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31" spans="1:22">
@@ -2731,64 +2728,64 @@
         <v>51</v>
       </c>
       <c r="C31" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D31">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F31">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G31">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I31">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J31">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K31">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L31">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M31">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N31">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O31">
         <v>6</v>
       </c>
       <c r="P31">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="Q31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S31">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="T31">
         <v>4</v>
       </c>
       <c r="U31">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V31">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:22">
@@ -2799,37 +2796,37 @@
         <v>52</v>
       </c>
       <c r="C32" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D32">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F32">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G32">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H32">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I32">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J32">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N32">
         <v>5</v>
@@ -2838,22 +2835,22 @@
         <v>6</v>
       </c>
       <c r="P32">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="Q32">
         <v>1</v>
       </c>
       <c r="R32">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S32">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="T32">
         <v>5</v>
       </c>
       <c r="U32">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="V32">
         <v>3</v>
@@ -2867,31 +2864,31 @@
         <v>53</v>
       </c>
       <c r="C33" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E33">
         <v>1</v>
       </c>
       <c r="F33">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J33">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L33">
         <v>7</v>
@@ -2906,22 +2903,22 @@
         <v>6</v>
       </c>
       <c r="P33">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Q33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R33">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S33">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="T33">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U33">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="V33">
         <v>4</v>
@@ -2935,7 +2932,7 @@
         <v>54</v>
       </c>
       <c r="C34" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D34">
         <v>1</v>
@@ -2950,16 +2947,16 @@
         <v>1</v>
       </c>
       <c r="H34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J34">
         <v>6</v>
       </c>
       <c r="K34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L34">
         <v>6</v>
@@ -2968,28 +2965,28 @@
         <v>6</v>
       </c>
       <c r="N34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O34">
         <v>6</v>
       </c>
       <c r="P34">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="Q34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R34">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S34">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="T34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U34">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="V34">
         <v>3</v>
@@ -3003,40 +3000,40 @@
         <v>55</v>
       </c>
       <c r="C35" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D35">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E35">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F35">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G35">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H35">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I35">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J35">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K35">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L35">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M35">
         <v>5</v>
       </c>
       <c r="N35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O35">
         <v>6</v>
@@ -3051,16 +3048,16 @@
         <v>3</v>
       </c>
       <c r="S35">
-        <v>1.8</v>
+        <v>4.4</v>
       </c>
       <c r="T35">
         <v>6</v>
       </c>
       <c r="U35">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="V35">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:22">
@@ -3071,64 +3068,64 @@
         <v>56</v>
       </c>
       <c r="C36" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H36">
         <v>1</v>
       </c>
       <c r="I36">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J36">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K36">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M36">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N36">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O36">
         <v>6</v>
       </c>
       <c r="P36">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R36">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S36">
-        <v>2.6</v>
+        <v>8.5</v>
       </c>
       <c r="T36">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U36">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="V36">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:22">
@@ -3145,10 +3142,10 @@
         <v>3</v>
       </c>
       <c r="E37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F37">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G37">
         <v>3</v>
@@ -3157,46 +3154,46 @@
         <v>3</v>
       </c>
       <c r="I37">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J37">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K37">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L37">
         <v>5</v>
       </c>
       <c r="M37">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O37">
         <v>6</v>
       </c>
       <c r="P37">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="Q37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R37">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S37">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="T37">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U37">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="V37">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38" spans="1:22">
@@ -3207,61 +3204,61 @@
         <v>58</v>
       </c>
       <c r="C38" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G38">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K38">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L38">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N38">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O38">
         <v>6</v>
       </c>
       <c r="P38">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="Q38">
         <v>1</v>
       </c>
       <c r="R38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S38">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="T38">
         <v>5</v>
       </c>
       <c r="U38">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="V38">
         <v>4</v>
@@ -3275,37 +3272,37 @@
         <v>59</v>
       </c>
       <c r="C39" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F39">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I39">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J39">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K39">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L39">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M39">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N39">
         <v>5</v>
@@ -3314,25 +3311,25 @@
         <v>6</v>
       </c>
       <c r="P39">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="Q39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R39">
         <v>3</v>
       </c>
       <c r="S39">
-        <v>6.3</v>
+        <v>2.8</v>
       </c>
       <c r="T39">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U39">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="V39">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40" spans="1:22">
@@ -3343,25 +3340,25 @@
         <v>60</v>
       </c>
       <c r="C40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I40">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J40">
         <v>5</v>
@@ -3373,7 +3370,7 @@
         <v>5</v>
       </c>
       <c r="M40">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N40">
         <v>5</v>
@@ -3382,22 +3379,22 @@
         <v>6</v>
       </c>
       <c r="P40">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="Q40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R40">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S40">
-        <v>1.8</v>
+        <v>4.4</v>
       </c>
       <c r="T40">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U40">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="V40">
         <v>3</v>
@@ -3414,55 +3411,55 @@
         <v>103</v>
       </c>
       <c r="D41">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E41">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F41">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G41">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H41">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I41">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J41">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L41">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M41">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N41">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O41">
         <v>6</v>
       </c>
       <c r="P41">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="Q41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R41">
         <v>5</v>
       </c>
       <c r="S41">
-        <v>2.9</v>
+        <v>10.2</v>
       </c>
       <c r="T41">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U41">
         <v>13</v>
@@ -3479,40 +3476,40 @@
         <v>62</v>
       </c>
       <c r="C42" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G42">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H42">
         <v>2</v>
       </c>
       <c r="I42">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J42">
         <v>5</v>
       </c>
       <c r="K42">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L42">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M42">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N42">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O42">
         <v>6</v>
@@ -3527,16 +3524,16 @@
         <v>4</v>
       </c>
       <c r="S42">
-        <v>3.3</v>
+        <v>5.9</v>
       </c>
       <c r="T42">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U42">
         <v>14</v>
       </c>
       <c r="V42">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:22">
@@ -3547,7 +3544,7 @@
         <v>63</v>
       </c>
       <c r="C43" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D43">
         <v>1</v>
@@ -3562,10 +3559,10 @@
         <v>1</v>
       </c>
       <c r="H43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I43">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J43">
         <v>7</v>
@@ -3577,34 +3574,34 @@
         <v>6</v>
       </c>
       <c r="M43">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N43">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O43">
         <v>6</v>
       </c>
       <c r="P43">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="Q43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R43">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S43">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="T43">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U43">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="V43">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44" spans="1:22">
@@ -3618,19 +3615,19 @@
         <v>103</v>
       </c>
       <c r="D44">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E44">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F44">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H44">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I44">
         <v>5</v>
@@ -3639,13 +3636,13 @@
         <v>5</v>
       </c>
       <c r="K44">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L44">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M44">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N44">
         <v>4</v>
@@ -3654,25 +3651,25 @@
         <v>6</v>
       </c>
       <c r="P44">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="Q44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R44">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S44">
-        <v>7.9</v>
+        <v>6.5</v>
       </c>
       <c r="T44">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U44">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="V44">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45" spans="1:22">
@@ -3683,37 +3680,37 @@
         <v>65</v>
       </c>
       <c r="C45" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E45">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F45">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H45">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I45">
         <v>6</v>
       </c>
       <c r="J45">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K45">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L45">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M45">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N45">
         <v>7</v>
@@ -3722,22 +3719,22 @@
         <v>6</v>
       </c>
       <c r="P45">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="Q45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S45">
-        <v>2.6</v>
+        <v>5.7</v>
       </c>
       <c r="T45">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U45">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="V45">
         <v>3</v>
@@ -3751,10 +3748,10 @@
         <v>66</v>
       </c>
       <c r="C46" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E46">
         <v>3</v>
@@ -3766,49 +3763,49 @@
         <v>3</v>
       </c>
       <c r="H46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I46">
         <v>4</v>
       </c>
       <c r="J46">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K46">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L46">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M46">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N46">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O46">
         <v>6</v>
       </c>
       <c r="P46">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="Q46">
         <v>2</v>
       </c>
       <c r="R46">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S46">
-        <v>6.4</v>
+        <v>12</v>
       </c>
       <c r="T46">
         <v>6</v>
       </c>
       <c r="U46">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="V46">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47" spans="1:22">
@@ -3819,64 +3816,64 @@
         <v>67</v>
       </c>
       <c r="C47" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E47">
         <v>2</v>
       </c>
       <c r="F47">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G47">
         <v>2</v>
       </c>
       <c r="H47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I47">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J47">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K47">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L47">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M47">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N47">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O47">
         <v>6</v>
       </c>
       <c r="P47">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="Q47">
         <v>1</v>
       </c>
       <c r="R47">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S47">
-        <v>5.7</v>
+        <v>10.6</v>
       </c>
       <c r="T47">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U47">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="V47">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48" spans="1:22">
@@ -3887,64 +3884,64 @@
         <v>68</v>
       </c>
       <c r="C48" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G48">
         <v>2</v>
       </c>
       <c r="H48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I48">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J48">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K48">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L48">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M48">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N48">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O48">
         <v>6</v>
       </c>
       <c r="P48">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="Q48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R48">
         <v>4</v>
       </c>
       <c r="S48">
-        <v>3.6</v>
+        <v>6.7</v>
       </c>
       <c r="T48">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U48">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="V48">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:22">
@@ -3955,22 +3952,22 @@
         <v>69</v>
       </c>
       <c r="C49" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E49">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I49">
         <v>5</v>
@@ -3982,13 +3979,13 @@
         <v>5</v>
       </c>
       <c r="L49">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M49">
         <v>5</v>
       </c>
       <c r="N49">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O49">
         <v>6</v>
@@ -3997,19 +3994,19 @@
         <v>43</v>
       </c>
       <c r="Q49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S49">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="T49">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U49">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="V49">
         <v>4</v>
@@ -4023,46 +4020,46 @@
         <v>70</v>
       </c>
       <c r="C50" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D50">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E50">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F50">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G50">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H50">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I50">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J50">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K50">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L50">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M50">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N50">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O50">
         <v>6</v>
       </c>
       <c r="P50">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="Q50">
         <v>2</v>
@@ -4071,16 +4068,16 @@
         <v>3</v>
       </c>
       <c r="S50">
-        <v>2.2</v>
+        <v>6.2</v>
       </c>
       <c r="T50">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U50">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="V50">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51" spans="1:22">
@@ -4091,46 +4088,46 @@
         <v>71</v>
       </c>
       <c r="C51" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E51">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F51">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G51">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H51">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I51">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J51">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K51">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L51">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M51">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N51">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O51">
         <v>6</v>
       </c>
       <c r="P51">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="Q51">
         <v>2</v>
@@ -4139,10 +4136,10 @@
         <v>3</v>
       </c>
       <c r="S51">
-        <v>7.2</v>
+        <v>4.5</v>
       </c>
       <c r="T51">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U51">
         <v>9</v>
@@ -4159,64 +4156,64 @@
         <v>72</v>
       </c>
       <c r="C52" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D52">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E52">
         <v>2</v>
       </c>
       <c r="F52">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H52">
         <v>1</v>
       </c>
       <c r="I52">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J52">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K52">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L52">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M52">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N52">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O52">
         <v>6</v>
       </c>
       <c r="P52">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="Q52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R52">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S52">
-        <v>6.8</v>
+        <v>9.6</v>
       </c>
       <c r="T52">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U52">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="V52">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53" spans="1:22">
@@ -4230,19 +4227,19 @@
         <v>102</v>
       </c>
       <c r="D53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G53">
         <v>3</v>
       </c>
       <c r="H53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I53">
         <v>6</v>
@@ -4254,19 +4251,19 @@
         <v>5</v>
       </c>
       <c r="L53">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M53">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N53">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O53">
         <v>6</v>
       </c>
       <c r="P53">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="Q53">
         <v>1</v>
@@ -4275,16 +4272,16 @@
         <v>3</v>
       </c>
       <c r="S53">
-        <v>5</v>
+        <v>10.3</v>
       </c>
       <c r="T53">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U53">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="V53">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54" spans="1:22">
@@ -4301,55 +4298,55 @@
         <v>2</v>
       </c>
       <c r="E54">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H54">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I54">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J54">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K54">
         <v>5</v>
       </c>
       <c r="L54">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M54">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N54">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O54">
         <v>6</v>
       </c>
       <c r="P54">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="Q54">
         <v>1</v>
       </c>
       <c r="R54">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S54">
-        <v>7.3</v>
+        <v>3.9</v>
       </c>
       <c r="T54">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U54">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="V54">
         <v>3</v>
@@ -4369,55 +4366,55 @@
         <v>4</v>
       </c>
       <c r="E55">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F55">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G55">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H55">
         <v>5</v>
       </c>
       <c r="I55">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J55">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K55">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L55">
         <v>2</v>
       </c>
       <c r="M55">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N55">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O55">
         <v>6</v>
       </c>
       <c r="P55">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="Q55">
         <v>1</v>
       </c>
       <c r="R55">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S55">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="T55">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U55">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="V55">
         <v>4</v>
@@ -4437,55 +4434,55 @@
         <v>2</v>
       </c>
       <c r="E56">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G56">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I56">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J56">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K56">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L56">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M56">
         <v>5</v>
       </c>
       <c r="N56">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O56">
         <v>6</v>
       </c>
       <c r="P56">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="Q56">
         <v>1</v>
       </c>
       <c r="R56">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S56">
-        <v>11.5</v>
+        <v>6.6</v>
       </c>
       <c r="T56">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="U56">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="V56">
         <v>4</v>
@@ -4505,58 +4502,58 @@
         <v>3</v>
       </c>
       <c r="E57">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F57">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G57">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H57">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I57">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J57">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K57">
         <v>6</v>
       </c>
       <c r="L57">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M57">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N57">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O57">
         <v>6</v>
       </c>
       <c r="P57">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="Q57">
         <v>1</v>
       </c>
       <c r="R57">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S57">
-        <v>2.3</v>
+        <v>7</v>
       </c>
       <c r="T57">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U57">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="V57">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58" spans="1:22">
@@ -4573,55 +4570,55 @@
         <v>4</v>
       </c>
       <c r="E58">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F58">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G58">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H58">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I58">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J58">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K58">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L58">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M58">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N58">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O58">
         <v>6</v>
       </c>
       <c r="P58">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q58">
         <v>2</v>
       </c>
       <c r="R58">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S58">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="T58">
         <v>6</v>
       </c>
       <c r="U58">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="V58">
         <v>4</v>
@@ -4638,13 +4635,13 @@
         <v>102</v>
       </c>
       <c r="D59">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E59">
         <v>3</v>
       </c>
       <c r="F59">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G59">
         <v>3</v>
@@ -4653,28 +4650,28 @@
         <v>3</v>
       </c>
       <c r="I59">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J59">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K59">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L59">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M59">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N59">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O59">
         <v>6</v>
       </c>
       <c r="P59">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="Q59">
         <v>1</v>
@@ -4682,11 +4679,14 @@
       <c r="R59">
         <v>3</v>
       </c>
+      <c r="S59">
+        <v>3.9</v>
+      </c>
       <c r="T59">
         <v>4</v>
       </c>
       <c r="U59">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="V59">
         <v>3</v>
@@ -4706,55 +4706,55 @@
         <v>3</v>
       </c>
       <c r="E60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G60">
         <v>3</v>
       </c>
       <c r="H60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I60">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J60">
         <v>5</v>
       </c>
       <c r="K60">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L60">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M60">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N60">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O60">
         <v>6</v>
       </c>
       <c r="P60">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="Q60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R60">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S60">
-        <v>10.6</v>
+        <v>9.4</v>
       </c>
       <c r="T60">
         <v>4</v>
       </c>
       <c r="U60">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="V60">
         <v>3</v>
@@ -4771,58 +4771,58 @@
         <v>103</v>
       </c>
       <c r="D61">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E61">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F61">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G61">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H61">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I61">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J61">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K61">
         <v>3</v>
       </c>
       <c r="L61">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M61">
         <v>4</v>
       </c>
       <c r="N61">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O61">
         <v>6</v>
       </c>
       <c r="P61">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="Q61">
         <v>1</v>
       </c>
       <c r="R61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S61">
-        <v>5.6</v>
+        <v>2.2</v>
       </c>
       <c r="T61">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U61">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="V61">
         <v>3</v>
@@ -4839,61 +4839,61 @@
         <v>103</v>
       </c>
       <c r="D62">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E62">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F62">
         <v>2</v>
       </c>
       <c r="G62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I62">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J62">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K62">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L62">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M62">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N62">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O62">
         <v>6</v>
       </c>
       <c r="P62">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Q62">
         <v>1</v>
       </c>
       <c r="R62">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S62">
-        <v>9.9</v>
+        <v>6.4</v>
       </c>
       <c r="T62">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U62">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="V62">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63" spans="1:22">
@@ -4916,7 +4916,7 @@
         <v>1</v>
       </c>
       <c r="G63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H63">
         <v>1</v>
@@ -4925,43 +4925,43 @@
         <v>6</v>
       </c>
       <c r="J63">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K63">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L63">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M63">
         <v>7</v>
       </c>
       <c r="N63">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O63">
         <v>6</v>
       </c>
       <c r="P63">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="Q63">
         <v>1</v>
       </c>
       <c r="R63">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S63">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="T63">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U63">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="V63">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64" spans="1:22">
@@ -4975,7 +4975,7 @@
         <v>101</v>
       </c>
       <c r="D64">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E64">
         <v>4</v>
@@ -4993,43 +4993,40 @@
         <v>4</v>
       </c>
       <c r="J64">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K64">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L64">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M64">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N64">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O64">
         <v>6</v>
       </c>
-      <c r="P64">
-        <v>37</v>
-      </c>
       <c r="Q64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R64">
         <v>3</v>
       </c>
       <c r="S64">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="T64">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="U64">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="V64">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65" spans="1:22">
@@ -5040,64 +5037,64 @@
         <v>85</v>
       </c>
       <c r="C65" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D65">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F65">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G65">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H65">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I65">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J65">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K65">
         <v>5</v>
       </c>
       <c r="L65">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M65">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N65">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O65">
         <v>6</v>
       </c>
       <c r="P65">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="Q65">
         <v>2</v>
       </c>
       <c r="R65">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S65">
-        <v>6.4</v>
+        <v>7.9</v>
       </c>
       <c r="T65">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U65">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="V65">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66" spans="1:22">
@@ -5111,19 +5108,19 @@
         <v>101</v>
       </c>
       <c r="D66">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E66">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F66">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G66">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H66">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I66">
         <v>6</v>
@@ -5135,34 +5132,34 @@
         <v>5</v>
       </c>
       <c r="L66">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M66">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N66">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O66">
         <v>6</v>
       </c>
       <c r="P66">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="Q66">
         <v>1</v>
       </c>
       <c r="R66">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S66">
-        <v>5.1</v>
+        <v>7.5</v>
       </c>
       <c r="T66">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U66">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="V66">
         <v>3</v>
@@ -5182,58 +5179,58 @@
         <v>1</v>
       </c>
       <c r="E67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F67">
         <v>1</v>
       </c>
       <c r="G67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I67">
         <v>5</v>
       </c>
       <c r="J67">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K67">
         <v>5</v>
       </c>
       <c r="L67">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M67">
         <v>4</v>
       </c>
       <c r="N67">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O67">
         <v>6</v>
       </c>
       <c r="P67">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="Q67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R67">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S67">
-        <v>9.199999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="T67">
         <v>6</v>
       </c>
       <c r="U67">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="V67">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68" spans="1:22">
@@ -5256,49 +5253,49 @@
         <v>3</v>
       </c>
       <c r="G68">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H68">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I68">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J68">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K68">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L68">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M68">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N68">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O68">
         <v>6</v>
       </c>
       <c r="P68">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q68">
         <v>1</v>
       </c>
       <c r="R68">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S68">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="T68">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U68">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="V68">
         <v>3</v>
@@ -5321,37 +5318,37 @@
         <v>2</v>
       </c>
       <c r="F69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G69">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H69">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I69">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J69">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K69">
         <v>5</v>
       </c>
       <c r="L69">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M69">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N69">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O69">
         <v>6</v>
       </c>
       <c r="P69">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="Q69">
         <v>1</v>
@@ -5360,16 +5357,16 @@
         <v>4</v>
       </c>
       <c r="S69">
-        <v>3.4</v>
+        <v>7.5</v>
       </c>
       <c r="T69">
         <v>3</v>
       </c>
       <c r="U69">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V69">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70" spans="1:22">
@@ -5395,49 +5392,49 @@
         <v>1</v>
       </c>
       <c r="H70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I70">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J70">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K70">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L70">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M70">
         <v>5</v>
       </c>
       <c r="N70">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O70">
         <v>6</v>
       </c>
       <c r="P70">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="Q70">
         <v>1</v>
       </c>
       <c r="R70">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S70">
-        <v>4.6</v>
+        <v>12</v>
       </c>
       <c r="T70">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U70">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="V70">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:22">
@@ -5451,61 +5448,61 @@
         <v>103</v>
       </c>
       <c r="D71">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E71">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F71">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G71">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H71">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I71">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J71">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K71">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L71">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M71">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N71">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O71">
         <v>6</v>
       </c>
       <c r="P71">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q71">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R71">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S71">
-        <v>5.8</v>
+        <v>3</v>
       </c>
       <c r="T71">
         <v>5</v>
       </c>
       <c r="U71">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="V71">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72" spans="1:22">
@@ -5519,43 +5516,43 @@
         <v>101</v>
       </c>
       <c r="D72">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E72">
         <v>2</v>
       </c>
       <c r="F72">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G72">
         <v>3</v>
       </c>
       <c r="H72">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I72">
         <v>7</v>
       </c>
       <c r="J72">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K72">
         <v>7</v>
       </c>
       <c r="L72">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M72">
         <v>7</v>
       </c>
       <c r="N72">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O72">
         <v>6</v>
       </c>
       <c r="P72">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="Q72">
         <v>2</v>
@@ -5564,16 +5561,16 @@
         <v>3</v>
       </c>
       <c r="S72">
-        <v>6.9</v>
+        <v>3.4</v>
       </c>
       <c r="T72">
         <v>5</v>
       </c>
       <c r="U72">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="V72">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73" spans="1:22">
@@ -5593,55 +5590,55 @@
         <v>3</v>
       </c>
       <c r="F73">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G73">
         <v>3</v>
       </c>
       <c r="H73">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I73">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J73">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K73">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L73">
         <v>5</v>
       </c>
       <c r="M73">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N73">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O73">
         <v>6</v>
       </c>
       <c r="P73">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="Q73">
         <v>1</v>
       </c>
       <c r="R73">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S73">
-        <v>6.5</v>
+        <v>7.6</v>
       </c>
       <c r="T73">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U73">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="V73">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74" spans="1:22">
@@ -5655,10 +5652,10 @@
         <v>101</v>
       </c>
       <c r="D74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E74">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F74">
         <v>2</v>
@@ -5670,43 +5667,43 @@
         <v>3</v>
       </c>
       <c r="I74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L74">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M74">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N74">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O74">
         <v>6</v>
       </c>
       <c r="P74">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="Q74">
         <v>2</v>
       </c>
       <c r="R74">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S74">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="T74">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U74">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="V74">
         <v>4</v>
@@ -5723,61 +5720,61 @@
         <v>101</v>
       </c>
       <c r="D75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E75">
         <v>1</v>
       </c>
       <c r="F75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I75">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J75">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K75">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L75">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M75">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N75">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O75">
         <v>6</v>
       </c>
       <c r="P75">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="Q75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R75">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S75">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="T75">
         <v>5</v>
       </c>
       <c r="U75">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="V75">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76" spans="1:22">
@@ -5794,19 +5791,19 @@
         <v>3</v>
       </c>
       <c r="E76">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F76">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G76">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H76">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I76">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J76">
         <v>3</v>
@@ -5818,7 +5815,7 @@
         <v>4</v>
       </c>
       <c r="M76">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N76">
         <v>4</v>
@@ -5827,22 +5824,22 @@
         <v>6</v>
       </c>
       <c r="P76">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q76">
         <v>1</v>
       </c>
       <c r="R76">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S76">
-        <v>18</v>
+        <v>5.1</v>
       </c>
       <c r="T76">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U76">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="V76">
         <v>3</v>
@@ -5859,43 +5856,43 @@
         <v>103</v>
       </c>
       <c r="D77">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E77">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F77">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G77">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H77">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I77">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J77">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K77">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L77">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M77">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N77">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O77">
         <v>6</v>
       </c>
       <c r="P77">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="Q77">
         <v>1</v>
@@ -5904,16 +5901,16 @@
         <v>3</v>
       </c>
       <c r="S77">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="T77">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U77">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V77">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78" spans="1:22">
@@ -5927,34 +5924,34 @@
         <v>103</v>
       </c>
       <c r="D78">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E78">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F78">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G78">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H78">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I78">
         <v>7</v>
       </c>
       <c r="J78">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K78">
         <v>7</v>
       </c>
       <c r="L78">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M78">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N78">
         <v>6</v>
@@ -5963,25 +5960,25 @@
         <v>6</v>
       </c>
       <c r="P78">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="Q78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R78">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S78">
-        <v>3.1</v>
+        <v>10</v>
       </c>
       <c r="T78">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U78">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="V78">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79" spans="1:22">
@@ -5995,7 +5992,7 @@
         <v>101</v>
       </c>
       <c r="D79">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E79">
         <v>3</v>
@@ -6004,52 +6001,52 @@
         <v>3</v>
       </c>
       <c r="G79">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H79">
         <v>2</v>
       </c>
       <c r="I79">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J79">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K79">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L79">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M79">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N79">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O79">
         <v>6</v>
       </c>
       <c r="P79">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="Q79">
         <v>1</v>
       </c>
       <c r="R79">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S79">
-        <v>8.4</v>
+        <v>9.1</v>
       </c>
       <c r="T79">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U79">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="V79">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80" spans="1:22">
@@ -6063,49 +6060,52 @@
         <v>101</v>
       </c>
       <c r="D80">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E80">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F80">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G80">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H80">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I80">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J80">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K80">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L80">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M80">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N80">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O80">
         <v>6</v>
       </c>
       <c r="P80">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="Q80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R80">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="S80">
+        <v>5.3</v>
       </c>
       <c r="T80">
         <v>5</v>
@@ -6114,7 +6114,7 @@
         <v>22</v>
       </c>
       <c r="V80">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/data/T3_leader_cleaned.xlsx
+++ b/data/T3_leader_cleaned.xlsx
@@ -82,241 +82,241 @@
     <t>LeaderJobLevel</t>
   </si>
   <si>
+    <t>A_L15</t>
+  </si>
+  <si>
+    <t>A_L20</t>
+  </si>
+  <si>
+    <t>A_L09</t>
+  </si>
+  <si>
+    <t>B_L11</t>
+  </si>
+  <si>
+    <t>B_L07</t>
+  </si>
+  <si>
+    <t>C_L19</t>
+  </si>
+  <si>
+    <t>C_L25</t>
+  </si>
+  <si>
+    <t>A_L12</t>
+  </si>
+  <si>
+    <t>A_L11</t>
+  </si>
+  <si>
+    <t>B_L25</t>
+  </si>
+  <si>
+    <t>B_L22</t>
+  </si>
+  <si>
+    <t>C_L11</t>
+  </si>
+  <si>
+    <t>C_L01</t>
+  </si>
+  <si>
+    <t>C_L02</t>
+  </si>
+  <si>
+    <t>B_L09</t>
+  </si>
+  <si>
+    <t>B_L10</t>
+  </si>
+  <si>
+    <t>A_L26</t>
+  </si>
+  <si>
+    <t>C_L06</t>
+  </si>
+  <si>
+    <t>A_L16</t>
+  </si>
+  <si>
+    <t>C_L08</t>
+  </si>
+  <si>
+    <t>B_L06</t>
+  </si>
+  <si>
+    <t>C_L14</t>
+  </si>
+  <si>
+    <t>C_L21</t>
+  </si>
+  <si>
+    <t>A_L29</t>
+  </si>
+  <si>
+    <t>C_L18</t>
+  </si>
+  <si>
+    <t>C_L07</t>
+  </si>
+  <si>
+    <t>A_L19</t>
+  </si>
+  <si>
+    <t>B_L02</t>
+  </si>
+  <si>
+    <t>A_L06</t>
+  </si>
+  <si>
+    <t>C_L24</t>
+  </si>
+  <si>
+    <t>A_L14</t>
+  </si>
+  <si>
+    <t>C_L29</t>
+  </si>
+  <si>
+    <t>B_L27</t>
+  </si>
+  <si>
+    <t>C_L10</t>
+  </si>
+  <si>
+    <t>B_L26</t>
+  </si>
+  <si>
+    <t>B_L29</t>
+  </si>
+  <si>
+    <t>C_L04</t>
+  </si>
+  <si>
+    <t>A_L21</t>
+  </si>
+  <si>
+    <t>C_L30</t>
+  </si>
+  <si>
+    <t>C_L28</t>
+  </si>
+  <si>
+    <t>B_L03</t>
+  </si>
+  <si>
+    <t>C_L17</t>
+  </si>
+  <si>
+    <t>C_L22</t>
+  </si>
+  <si>
+    <t>B_L05</t>
+  </si>
+  <si>
+    <t>C_L20</t>
+  </si>
+  <si>
+    <t>B_L12</t>
+  </si>
+  <si>
+    <t>A_L18</t>
+  </si>
+  <si>
+    <t>C_L03</t>
+  </si>
+  <si>
+    <t>B_L20</t>
+  </si>
+  <si>
+    <t>A_L10</t>
+  </si>
+  <si>
+    <t>B_L19</t>
+  </si>
+  <si>
+    <t>B_L04</t>
+  </si>
+  <si>
+    <t>B_L08</t>
+  </si>
+  <si>
+    <t>B_L23</t>
+  </si>
+  <si>
+    <t>B_L16</t>
+  </si>
+  <si>
+    <t>A_L08</t>
+  </si>
+  <si>
+    <t>C_L16</t>
+  </si>
+  <si>
+    <t>B_L30</t>
+  </si>
+  <si>
+    <t>A_L03</t>
+  </si>
+  <si>
+    <t>C_L09</t>
+  </si>
+  <si>
+    <t>C_L13</t>
+  </si>
+  <si>
+    <t>A_L04</t>
+  </si>
+  <si>
+    <t>A_L25</t>
+  </si>
+  <si>
+    <t>B_L01</t>
+  </si>
+  <si>
+    <t>A_L17</t>
+  </si>
+  <si>
+    <t>B_L15</t>
+  </si>
+  <si>
+    <t>B_L21</t>
+  </si>
+  <si>
+    <t>A_L23</t>
+  </si>
+  <si>
+    <t>B_L14</t>
+  </si>
+  <si>
+    <t>C_L26</t>
+  </si>
+  <si>
     <t>A_L13</t>
   </si>
   <si>
-    <t>A_L19</t>
-  </si>
-  <si>
-    <t>A_L07</t>
-  </si>
-  <si>
-    <t>B_L10</t>
-  </si>
-  <si>
-    <t>B_L06</t>
-  </si>
-  <si>
-    <t>C_L19</t>
-  </si>
-  <si>
-    <t>C_L25</t>
-  </si>
-  <si>
-    <t>A_L10</t>
-  </si>
-  <si>
-    <t>A_L09</t>
-  </si>
-  <si>
-    <t>B_L25</t>
-  </si>
-  <si>
-    <t>B_L23</t>
-  </si>
-  <si>
-    <t>C_L11</t>
-  </si>
-  <si>
-    <t>C_L01</t>
-  </si>
-  <si>
-    <t>C_L02</t>
-  </si>
-  <si>
-    <t>B_L08</t>
-  </si>
-  <si>
-    <t>B_L09</t>
-  </si>
-  <si>
-    <t>A_L25</t>
-  </si>
-  <si>
-    <t>C_L06</t>
-  </si>
-  <si>
-    <t>A_L15</t>
-  </si>
-  <si>
-    <t>C_L08</t>
-  </si>
-  <si>
-    <t>B_L05</t>
-  </si>
-  <si>
-    <t>C_L13</t>
-  </si>
-  <si>
-    <t>C_L21</t>
-  </si>
-  <si>
-    <t>A_L27</t>
-  </si>
-  <si>
-    <t>C_L18</t>
-  </si>
-  <si>
-    <t>C_L07</t>
-  </si>
-  <si>
-    <t>A_L18</t>
-  </si>
-  <si>
-    <t>A_L29</t>
-  </si>
-  <si>
-    <t>B_L07</t>
+    <t>B_L18</t>
+  </si>
+  <si>
+    <t>A_L22</t>
+  </si>
+  <si>
+    <t>A_L24</t>
+  </si>
+  <si>
+    <t>A_L01</t>
+  </si>
+  <si>
+    <t>C_L23</t>
+  </si>
+  <si>
+    <t>C_L05</t>
   </si>
   <si>
     <t>A_L05</t>
   </si>
   <si>
-    <t>C_L24</t>
-  </si>
-  <si>
-    <t>A_L12</t>
-  </si>
-  <si>
-    <t>C_L29</t>
-  </si>
-  <si>
-    <t>B_L27</t>
-  </si>
-  <si>
-    <t>C_L10</t>
-  </si>
-  <si>
-    <t>B_L26</t>
-  </si>
-  <si>
-    <t>B_L29</t>
-  </si>
-  <si>
-    <t>C_L04</t>
-  </si>
-  <si>
-    <t>A_L20</t>
-  </si>
-  <si>
-    <t>C_L30</t>
-  </si>
-  <si>
-    <t>C_L28</t>
-  </si>
-  <si>
-    <t>B_L01</t>
-  </si>
-  <si>
-    <t>C_L16</t>
-  </si>
-  <si>
-    <t>C_L22</t>
-  </si>
-  <si>
-    <t>B_L04</t>
-  </si>
-  <si>
-    <t>C_L20</t>
-  </si>
-  <si>
-    <t>B_L11</t>
-  </si>
-  <si>
-    <t>A_L17</t>
-  </si>
-  <si>
-    <t>C_L03</t>
-  </si>
-  <si>
-    <t>B_L21</t>
-  </si>
-  <si>
-    <t>A_L08</t>
-  </si>
-  <si>
-    <t>B_L20</t>
-  </si>
-  <si>
-    <t>B_L03</t>
-  </si>
-  <si>
-    <t>B_L24</t>
-  </si>
-  <si>
-    <t>B_L18</t>
-  </si>
-  <si>
-    <t>A_L06</t>
-  </si>
-  <si>
-    <t>C_L14</t>
-  </si>
-  <si>
-    <t>B_L30</t>
-  </si>
-  <si>
-    <t>A_L02</t>
-  </si>
-  <si>
-    <t>C_L09</t>
-  </si>
-  <si>
-    <t>C_L12</t>
-  </si>
-  <si>
-    <t>A_L03</t>
-  </si>
-  <si>
-    <t>A_L24</t>
-  </si>
-  <si>
     <t>A_L28</t>
-  </si>
-  <si>
-    <t>A_L16</t>
-  </si>
-  <si>
-    <t>B_L16</t>
-  </si>
-  <si>
-    <t>B_L22</t>
-  </si>
-  <si>
-    <t>A_L22</t>
-  </si>
-  <si>
-    <t>B_L12</t>
-  </si>
-  <si>
-    <t>C_L26</t>
-  </si>
-  <si>
-    <t>A_L11</t>
-  </si>
-  <si>
-    <t>B_L19</t>
-  </si>
-  <si>
-    <t>A_L21</t>
-  </si>
-  <si>
-    <t>A_L23</t>
-  </si>
-  <si>
-    <t>A_L01</t>
-  </si>
-  <si>
-    <t>C_L23</t>
-  </si>
-  <si>
-    <t>C_L05</t>
-  </si>
-  <si>
-    <t>A_L04</t>
-  </si>
-  <si>
-    <t>A_L26</t>
   </si>
   <si>
     <t>A</t>
@@ -765,61 +765,61 @@
         <v>101</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I2">
         <v>4</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K2">
         <v>4</v>
       </c>
       <c r="L2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O2">
         <v>6</v>
       </c>
       <c r="P2">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="Q2">
         <v>1</v>
       </c>
       <c r="R2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S2">
-        <v>6</v>
+        <v>6.7</v>
       </c>
       <c r="T2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -833,61 +833,61 @@
         <v>101</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <v>3</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="N3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O3">
         <v>6</v>
       </c>
       <c r="P3">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="Q3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S3">
-        <v>11.5</v>
+        <v>3.7</v>
       </c>
       <c r="T3">
         <v>3</v>
       </c>
       <c r="U3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="V3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -901,10 +901,10 @@
         <v>101</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4">
         <v>2</v>
@@ -913,49 +913,49 @@
         <v>3</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O4">
         <v>6</v>
       </c>
       <c r="P4">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="Q4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R4">
         <v>3</v>
       </c>
       <c r="S4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U4">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="V4">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -972,58 +972,58 @@
         <v>2</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O5">
         <v>6</v>
       </c>
       <c r="P5">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="Q5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S5">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="T5">
         <v>6</v>
       </c>
       <c r="U5">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="V5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -1037,37 +1037,37 @@
         <v>102</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M6">
         <v>6</v>
       </c>
       <c r="N6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O6">
         <v>6</v>
@@ -1079,16 +1079,16 @@
         <v>1</v>
       </c>
       <c r="R6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S6">
-        <v>2.4</v>
+        <v>6.1</v>
       </c>
       <c r="T6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V6">
         <v>3</v>
@@ -1117,49 +1117,49 @@
         <v>1</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L7">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O7">
         <v>6</v>
       </c>
       <c r="P7">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="Q7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R7">
         <v>3</v>
       </c>
       <c r="S7">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="T7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U7">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="V7">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -1176,19 +1176,19 @@
         <v>2</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H8">
         <v>4</v>
       </c>
       <c r="I8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J8">
         <v>4</v>
@@ -1209,25 +1209,25 @@
         <v>6</v>
       </c>
       <c r="P8">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="Q8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R8">
         <v>3</v>
       </c>
       <c r="S8">
-        <v>9</v>
+        <v>4.7</v>
       </c>
       <c r="T8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U8">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="V8">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -1241,43 +1241,43 @@
         <v>101</v>
       </c>
       <c r="D9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E9">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F9">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H9">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I9">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J9">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L9">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O9">
         <v>6</v>
       </c>
       <c r="P9">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="Q9">
         <v>1</v>
@@ -1286,16 +1286,16 @@
         <v>4</v>
       </c>
       <c r="S9">
-        <v>2.7</v>
+        <v>5.6</v>
       </c>
       <c r="T9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U9">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="V9">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1309,58 +1309,61 @@
         <v>101</v>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F10">
         <v>3</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I10">
         <v>5</v>
       </c>
       <c r="J10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K10">
         <v>5</v>
       </c>
       <c r="L10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M10">
         <v>5</v>
       </c>
       <c r="N10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O10">
         <v>6</v>
       </c>
+      <c r="P10">
+        <v>43</v>
+      </c>
       <c r="Q10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S10">
-        <v>2.6</v>
+        <v>4.5</v>
       </c>
       <c r="T10">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="U10">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="V10">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1374,25 +1377,25 @@
         <v>102</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F11">
         <v>2</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I11">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J11">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K11">
         <v>6</v>
@@ -1401,34 +1404,34 @@
         <v>6</v>
       </c>
       <c r="M11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O11">
         <v>6</v>
       </c>
       <c r="P11">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="Q11">
         <v>1</v>
       </c>
       <c r="R11">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S11">
-        <v>6.4</v>
+        <v>4.1</v>
       </c>
       <c r="T11">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U11">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="V11">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1442,7 +1445,7 @@
         <v>102</v>
       </c>
       <c r="D12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -1451,49 +1454,49 @@
         <v>3</v>
       </c>
       <c r="G12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I12">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J12">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K12">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L12">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M12">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N12">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O12">
         <v>6</v>
       </c>
       <c r="P12">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="Q12">
         <v>2</v>
       </c>
       <c r="R12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S12">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="T12">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U12">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="V12">
         <v>3</v>
@@ -1510,61 +1513,61 @@
         <v>103</v>
       </c>
       <c r="D13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="F13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G13">
         <v>2</v>
       </c>
       <c r="H13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I13">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J13">
         <v>3</v>
       </c>
       <c r="K13">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L13">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M13">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O13">
         <v>6</v>
       </c>
       <c r="P13">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="Q13">
         <v>1</v>
       </c>
       <c r="R13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S13">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="T13">
         <v>6</v>
       </c>
       <c r="U13">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="V13">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -1578,7 +1581,7 @@
         <v>103</v>
       </c>
       <c r="D14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E14">
         <v>3</v>
@@ -1587,52 +1590,52 @@
         <v>2</v>
       </c>
       <c r="G14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I14">
         <v>4</v>
       </c>
       <c r="J14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L14">
         <v>5</v>
       </c>
       <c r="M14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O14">
         <v>6</v>
       </c>
       <c r="P14">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Q14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R14">
         <v>3</v>
       </c>
       <c r="S14">
-        <v>5.7</v>
+        <v>3.4</v>
       </c>
       <c r="T14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U14">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="V14">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1646,61 +1649,58 @@
         <v>103</v>
       </c>
       <c r="D15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E15">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K15">
         <v>2</v>
       </c>
       <c r="L15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M15">
         <v>2</v>
       </c>
       <c r="N15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O15">
         <v>6</v>
       </c>
       <c r="P15">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="Q15">
         <v>1</v>
       </c>
       <c r="R15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S15">
-        <v>7.4</v>
-      </c>
-      <c r="T15">
-        <v>6</v>
+        <v>2.6</v>
       </c>
       <c r="U15">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="V15">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -1714,58 +1714,58 @@
         <v>102</v>
       </c>
       <c r="D16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I16">
         <v>5</v>
       </c>
       <c r="J16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L16">
         <v>5</v>
       </c>
       <c r="M16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N16">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O16">
         <v>6</v>
       </c>
       <c r="P16">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="Q16">
         <v>2</v>
       </c>
       <c r="R16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S16">
-        <v>9.199999999999999</v>
+        <v>13.8</v>
       </c>
       <c r="T16">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U16">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="V16">
         <v>4</v>
@@ -1782,58 +1782,58 @@
         <v>102</v>
       </c>
       <c r="D17">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G17">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H17">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I17">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J17">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K17">
         <v>5</v>
       </c>
       <c r="L17">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M17">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N17">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O17">
         <v>6</v>
       </c>
       <c r="P17">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="Q17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S17">
-        <v>6.3</v>
+        <v>4.9</v>
       </c>
       <c r="T17">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U17">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="V17">
         <v>3</v>
@@ -1850,34 +1850,34 @@
         <v>101</v>
       </c>
       <c r="D18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E18">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F18">
         <v>3</v>
       </c>
       <c r="G18">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H18">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I18">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J18">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L18">
         <v>4</v>
       </c>
       <c r="M18">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N18">
         <v>4</v>
@@ -1886,7 +1886,7 @@
         <v>6</v>
       </c>
       <c r="P18">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q18">
         <v>1</v>
@@ -1895,16 +1895,16 @@
         <v>4</v>
       </c>
       <c r="S18">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="T18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U18">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="V18">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -1918,7 +1918,7 @@
         <v>103</v>
       </c>
       <c r="D19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -1930,22 +1930,22 @@
         <v>1</v>
       </c>
       <c r="H19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I19">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K19">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L19">
         <v>6</v>
       </c>
       <c r="M19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N19">
         <v>6</v>
@@ -1957,19 +1957,19 @@
         <v>45</v>
       </c>
       <c r="Q19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S19">
-        <v>8</v>
+        <v>4.9</v>
       </c>
       <c r="T19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U19">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="V19">
         <v>4</v>
@@ -1986,58 +1986,58 @@
         <v>101</v>
       </c>
       <c r="D20">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E20">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F20">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G20">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H20">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I20">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J20">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K20">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L20">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M20">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N20">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O20">
         <v>6</v>
       </c>
       <c r="P20">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="Q20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S20">
-        <v>5.6</v>
+        <v>1.2</v>
       </c>
       <c r="T20">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U20">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="V20">
         <v>3</v>
@@ -2054,22 +2054,22 @@
         <v>103</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21">
         <v>2</v>
       </c>
       <c r="F21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I21">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J21">
         <v>4</v>
@@ -2078,37 +2078,37 @@
         <v>4</v>
       </c>
       <c r="L21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M21">
         <v>3</v>
       </c>
       <c r="N21">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O21">
         <v>6</v>
       </c>
       <c r="P21">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="Q21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R21">
         <v>3</v>
       </c>
       <c r="S21">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="T21">
         <v>6</v>
       </c>
       <c r="U21">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="V21">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -2125,55 +2125,55 @@
         <v>1</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22">
         <v>1</v>
       </c>
       <c r="H22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I22">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J22">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K22">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M22">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N22">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O22">
         <v>6</v>
       </c>
       <c r="P22">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="Q22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S22">
-        <v>5.5</v>
+        <v>2.6</v>
       </c>
       <c r="T22">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U22">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="V22">
         <v>3</v>
@@ -2190,61 +2190,61 @@
         <v>103</v>
       </c>
       <c r="D23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I23">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J23">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K23">
         <v>4</v>
       </c>
       <c r="L23">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M23">
         <v>4</v>
       </c>
       <c r="N23">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O23">
         <v>6</v>
       </c>
       <c r="P23">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="Q23">
         <v>1</v>
       </c>
       <c r="R23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S23">
-        <v>4.4</v>
+        <v>8.1</v>
       </c>
       <c r="T23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U23">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="V23">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -2261,25 +2261,25 @@
         <v>2</v>
       </c>
       <c r="E24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F24">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G24">
         <v>2</v>
       </c>
       <c r="H24">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I24">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J24">
         <v>5</v>
       </c>
       <c r="K24">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L24">
         <v>4</v>
@@ -2288,7 +2288,7 @@
         <v>4</v>
       </c>
       <c r="N24">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O24">
         <v>6</v>
@@ -2303,16 +2303,13 @@
         <v>3</v>
       </c>
       <c r="S24">
-        <v>1.5</v>
-      </c>
-      <c r="T24">
-        <v>7</v>
+        <v>5.4</v>
       </c>
       <c r="U24">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="V24">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -2326,61 +2323,61 @@
         <v>101</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G25">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I25">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J25">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K25">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L25">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M25">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N25">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O25">
         <v>6</v>
       </c>
       <c r="P25">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="Q25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R25">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S25">
-        <v>11.9</v>
+        <v>7.7</v>
       </c>
       <c r="T25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U25">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="V25">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -2406,46 +2403,46 @@
         <v>1</v>
       </c>
       <c r="H26">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I26">
         <v>4</v>
       </c>
       <c r="J26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O26">
         <v>6</v>
       </c>
       <c r="P26">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Q26">
         <v>1</v>
       </c>
       <c r="R26">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S26">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="T26">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U26">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="V26">
         <v>4</v>
@@ -2465,7 +2462,7 @@
         <v>4</v>
       </c>
       <c r="E27">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F27">
         <v>4</v>
@@ -2477,43 +2474,43 @@
         <v>4</v>
       </c>
       <c r="I27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J27">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K27">
         <v>3</v>
       </c>
       <c r="L27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N27">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O27">
         <v>6</v>
       </c>
       <c r="P27">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="Q27">
         <v>1</v>
       </c>
       <c r="R27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S27">
-        <v>3.8</v>
+        <v>8.9</v>
       </c>
       <c r="T27">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U27">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="V27">
         <v>4</v>
@@ -2530,10 +2527,10 @@
         <v>101</v>
       </c>
       <c r="D28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F28">
         <v>1</v>
@@ -2542,49 +2539,49 @@
         <v>2</v>
       </c>
       <c r="H28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I28">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J28">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K28">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L28">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M28">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N28">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O28">
         <v>6</v>
       </c>
       <c r="P28">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Q28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R28">
         <v>3</v>
       </c>
       <c r="S28">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T28">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U28">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="V28">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -2595,37 +2592,37 @@
         <v>49</v>
       </c>
       <c r="C29" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D29">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E29">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F29">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G29">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H29">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I29">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J29">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K29">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L29">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N29">
         <v>4</v>
@@ -2634,25 +2631,25 @@
         <v>6</v>
       </c>
       <c r="P29">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="Q29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R29">
         <v>3</v>
       </c>
       <c r="S29">
-        <v>5.2</v>
+        <v>3.8</v>
       </c>
       <c r="T29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U29">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="V29">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:22">
@@ -2663,64 +2660,64 @@
         <v>50</v>
       </c>
       <c r="C30" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D30">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E30">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F30">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G30">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H30">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L30">
         <v>6</v>
       </c>
       <c r="M30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O30">
         <v>6</v>
       </c>
       <c r="P30">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="Q30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R30">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S30">
-        <v>6.5</v>
+        <v>8.4</v>
       </c>
       <c r="T30">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U30">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="V30">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31" spans="1:22">
@@ -2731,7 +2728,7 @@
         <v>51</v>
       </c>
       <c r="C31" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D31">
         <v>4</v>
@@ -2740,55 +2737,55 @@
         <v>4</v>
       </c>
       <c r="F31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H31">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I31">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J31">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K31">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L31">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M31">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N31">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O31">
         <v>6</v>
       </c>
       <c r="P31">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="Q31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S31">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="T31">
         <v>4</v>
       </c>
       <c r="U31">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V31">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:22">
@@ -2799,22 +2796,22 @@
         <v>52</v>
       </c>
       <c r="C32" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D32">
         <v>4</v>
       </c>
       <c r="E32">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F32">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G32">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H32">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I32">
         <v>3</v>
@@ -2823,37 +2820,37 @@
         <v>4</v>
       </c>
       <c r="K32">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L32">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M32">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N32">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O32">
         <v>6</v>
       </c>
       <c r="P32">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="Q32">
         <v>1</v>
       </c>
       <c r="R32">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S32">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="T32">
         <v>5</v>
       </c>
       <c r="U32">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="V32">
         <v>3</v>
@@ -2867,7 +2864,7 @@
         <v>53</v>
       </c>
       <c r="C33" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D33">
         <v>1</v>
@@ -2891,7 +2888,7 @@
         <v>7</v>
       </c>
       <c r="K33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L33">
         <v>7</v>
@@ -2900,28 +2897,28 @@
         <v>7</v>
       </c>
       <c r="N33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O33">
         <v>6</v>
       </c>
       <c r="P33">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Q33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R33">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S33">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="T33">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U33">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="V33">
         <v>4</v>
@@ -2935,7 +2932,7 @@
         <v>54</v>
       </c>
       <c r="C34" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D34">
         <v>1</v>
@@ -2950,16 +2947,16 @@
         <v>1</v>
       </c>
       <c r="H34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J34">
         <v>6</v>
       </c>
       <c r="K34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L34">
         <v>6</v>
@@ -2968,28 +2965,28 @@
         <v>6</v>
       </c>
       <c r="N34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O34">
         <v>6</v>
       </c>
       <c r="P34">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="Q34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R34">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S34">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="T34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U34">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="V34">
         <v>3</v>
@@ -3003,22 +3000,22 @@
         <v>55</v>
       </c>
       <c r="C35" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D35">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E35">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F35">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G35">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H35">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I35">
         <v>5</v>
@@ -3027,13 +3024,13 @@
         <v>5</v>
       </c>
       <c r="K35">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L35">
         <v>5</v>
       </c>
       <c r="M35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N35">
         <v>6</v>
@@ -3051,16 +3048,16 @@
         <v>3</v>
       </c>
       <c r="S35">
-        <v>1.8</v>
+        <v>4.4</v>
       </c>
       <c r="T35">
         <v>6</v>
       </c>
       <c r="U35">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="V35">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:22">
@@ -3071,16 +3068,16 @@
         <v>56</v>
       </c>
       <c r="C36" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D36">
         <v>2</v>
       </c>
       <c r="E36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G36">
         <v>3</v>
@@ -3089,46 +3086,46 @@
         <v>1</v>
       </c>
       <c r="I36">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J36">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L36">
         <v>4</v>
       </c>
       <c r="M36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N36">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O36">
         <v>6</v>
       </c>
       <c r="P36">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R36">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S36">
-        <v>2.6</v>
+        <v>8.5</v>
       </c>
       <c r="T36">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U36">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="V36">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:22">
@@ -3145,10 +3142,10 @@
         <v>3</v>
       </c>
       <c r="E37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F37">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G37">
         <v>3</v>
@@ -3157,46 +3154,46 @@
         <v>3</v>
       </c>
       <c r="I37">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J37">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K37">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L37">
         <v>5</v>
       </c>
       <c r="M37">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O37">
         <v>6</v>
       </c>
       <c r="P37">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="Q37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R37">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S37">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="T37">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U37">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="V37">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38" spans="1:22">
@@ -3207,61 +3204,61 @@
         <v>58</v>
       </c>
       <c r="C38" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D38">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E38">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F38">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G38">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H38">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I38">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J38">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K38">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L38">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M38">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N38">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O38">
         <v>6</v>
       </c>
       <c r="P38">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="Q38">
         <v>1</v>
       </c>
       <c r="R38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S38">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="T38">
         <v>5</v>
       </c>
       <c r="U38">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="V38">
         <v>4</v>
@@ -3275,37 +3272,37 @@
         <v>59</v>
       </c>
       <c r="C39" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F39">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I39">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J39">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K39">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L39">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M39">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N39">
         <v>5</v>
@@ -3314,25 +3311,25 @@
         <v>6</v>
       </c>
       <c r="P39">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="Q39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R39">
         <v>3</v>
       </c>
       <c r="S39">
-        <v>6.3</v>
+        <v>2.8</v>
       </c>
       <c r="T39">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U39">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="V39">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40" spans="1:22">
@@ -3343,25 +3340,25 @@
         <v>60</v>
       </c>
       <c r="C40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E40">
         <v>2</v>
       </c>
       <c r="F40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I40">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J40">
         <v>5</v>
@@ -3373,7 +3370,7 @@
         <v>5</v>
       </c>
       <c r="M40">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N40">
         <v>5</v>
@@ -3382,22 +3379,22 @@
         <v>6</v>
       </c>
       <c r="P40">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="Q40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R40">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S40">
-        <v>1.8</v>
+        <v>4.4</v>
       </c>
       <c r="T40">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U40">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="V40">
         <v>3</v>
@@ -3414,55 +3411,55 @@
         <v>103</v>
       </c>
       <c r="D41">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E41">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F41">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G41">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H41">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I41">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K41">
         <v>6</v>
       </c>
       <c r="L41">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M41">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N41">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O41">
         <v>6</v>
       </c>
       <c r="P41">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="Q41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R41">
         <v>5</v>
       </c>
       <c r="S41">
-        <v>2.9</v>
+        <v>10.2</v>
       </c>
       <c r="T41">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U41">
         <v>13</v>
@@ -3479,40 +3476,40 @@
         <v>62</v>
       </c>
       <c r="C42" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G42">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H42">
         <v>2</v>
       </c>
       <c r="I42">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J42">
         <v>5</v>
       </c>
       <c r="K42">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L42">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M42">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N42">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O42">
         <v>6</v>
@@ -3527,16 +3524,16 @@
         <v>4</v>
       </c>
       <c r="S42">
-        <v>3.3</v>
+        <v>5.9</v>
       </c>
       <c r="T42">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U42">
         <v>14</v>
       </c>
       <c r="V42">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:22">
@@ -3547,7 +3544,7 @@
         <v>63</v>
       </c>
       <c r="C43" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D43">
         <v>1</v>
@@ -3571,10 +3568,10 @@
         <v>7</v>
       </c>
       <c r="K43">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M43">
         <v>6</v>
@@ -3586,25 +3583,25 @@
         <v>6</v>
       </c>
       <c r="P43">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="Q43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R43">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S43">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="T43">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U43">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="V43">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44" spans="1:22">
@@ -3618,19 +3615,19 @@
         <v>103</v>
       </c>
       <c r="D44">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E44">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F44">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H44">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I44">
         <v>5</v>
@@ -3639,13 +3636,13 @@
         <v>5</v>
       </c>
       <c r="K44">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L44">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M44">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N44">
         <v>4</v>
@@ -3654,25 +3651,25 @@
         <v>6</v>
       </c>
       <c r="P44">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="Q44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R44">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S44">
-        <v>7.9</v>
+        <v>6.5</v>
       </c>
       <c r="T44">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U44">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="V44">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45" spans="1:22">
@@ -3683,37 +3680,37 @@
         <v>65</v>
       </c>
       <c r="C45" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E45">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F45">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H45">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I45">
         <v>6</v>
       </c>
       <c r="J45">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K45">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L45">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M45">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N45">
         <v>7</v>
@@ -3722,22 +3719,22 @@
         <v>6</v>
       </c>
       <c r="P45">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="Q45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S45">
-        <v>2.6</v>
+        <v>5.7</v>
       </c>
       <c r="T45">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U45">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="V45">
         <v>3</v>
@@ -3751,10 +3748,10 @@
         <v>66</v>
       </c>
       <c r="C46" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E46">
         <v>3</v>
@@ -3766,49 +3763,49 @@
         <v>3</v>
       </c>
       <c r="H46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I46">
         <v>4</v>
       </c>
       <c r="J46">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K46">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L46">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M46">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N46">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O46">
         <v>6</v>
       </c>
       <c r="P46">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="Q46">
         <v>2</v>
       </c>
       <c r="R46">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S46">
-        <v>6.4</v>
+        <v>12</v>
       </c>
       <c r="T46">
         <v>6</v>
       </c>
       <c r="U46">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="V46">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47" spans="1:22">
@@ -3819,64 +3816,64 @@
         <v>67</v>
       </c>
       <c r="C47" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E47">
         <v>2</v>
       </c>
       <c r="F47">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G47">
         <v>2</v>
       </c>
       <c r="H47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I47">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J47">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K47">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L47">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M47">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N47">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O47">
         <v>6</v>
       </c>
       <c r="P47">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="Q47">
         <v>1</v>
       </c>
       <c r="R47">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S47">
-        <v>5.7</v>
+        <v>10.6</v>
       </c>
       <c r="T47">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U47">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="V47">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48" spans="1:22">
@@ -3887,64 +3884,64 @@
         <v>68</v>
       </c>
       <c r="C48" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I48">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J48">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K48">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L48">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M48">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N48">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O48">
         <v>6</v>
       </c>
       <c r="P48">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="Q48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R48">
         <v>4</v>
       </c>
       <c r="S48">
-        <v>3.6</v>
+        <v>6.7</v>
       </c>
       <c r="T48">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U48">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="V48">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:22">
@@ -3955,40 +3952,40 @@
         <v>69</v>
       </c>
       <c r="C49" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E49">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I49">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J49">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K49">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L49">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M49">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N49">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O49">
         <v>6</v>
@@ -3997,19 +3994,19 @@
         <v>43</v>
       </c>
       <c r="Q49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S49">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="T49">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U49">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="V49">
         <v>4</v>
@@ -4023,7 +4020,7 @@
         <v>70</v>
       </c>
       <c r="C50" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D50">
         <v>1</v>
@@ -4032,25 +4029,25 @@
         <v>1</v>
       </c>
       <c r="F50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H50">
         <v>1</v>
       </c>
       <c r="I50">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J50">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K50">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L50">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M50">
         <v>4</v>
@@ -4062,7 +4059,7 @@
         <v>6</v>
       </c>
       <c r="P50">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="Q50">
         <v>2</v>
@@ -4071,16 +4068,16 @@
         <v>3</v>
       </c>
       <c r="S50">
-        <v>2.2</v>
+        <v>6.2</v>
       </c>
       <c r="T50">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U50">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="V50">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51" spans="1:22">
@@ -4091,46 +4088,46 @@
         <v>71</v>
       </c>
       <c r="C51" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E51">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F51">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G51">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H51">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I51">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J51">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K51">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L51">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M51">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N51">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O51">
         <v>6</v>
       </c>
       <c r="P51">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="Q51">
         <v>2</v>
@@ -4139,10 +4136,10 @@
         <v>3</v>
       </c>
       <c r="S51">
-        <v>7.2</v>
+        <v>4.5</v>
       </c>
       <c r="T51">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U51">
         <v>9</v>
@@ -4159,37 +4156,37 @@
         <v>72</v>
       </c>
       <c r="C52" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D52">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E52">
         <v>2</v>
       </c>
       <c r="F52">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H52">
         <v>1</v>
       </c>
       <c r="I52">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J52">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K52">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L52">
         <v>6</v>
       </c>
       <c r="M52">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N52">
         <v>6</v>
@@ -4198,25 +4195,25 @@
         <v>6</v>
       </c>
       <c r="P52">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="Q52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R52">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S52">
-        <v>6.8</v>
+        <v>9.6</v>
       </c>
       <c r="T52">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U52">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="V52">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53" spans="1:22">
@@ -4230,43 +4227,43 @@
         <v>102</v>
       </c>
       <c r="D53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G53">
         <v>3</v>
       </c>
       <c r="H53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I53">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J53">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K53">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L53">
         <v>5</v>
       </c>
       <c r="M53">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N53">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O53">
         <v>6</v>
       </c>
       <c r="P53">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="Q53">
         <v>1</v>
@@ -4275,16 +4272,16 @@
         <v>3</v>
       </c>
       <c r="S53">
-        <v>5</v>
+        <v>10.3</v>
       </c>
       <c r="T53">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U53">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="V53">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54" spans="1:22">
@@ -4301,55 +4298,55 @@
         <v>2</v>
       </c>
       <c r="E54">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H54">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I54">
         <v>6</v>
       </c>
       <c r="J54">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K54">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L54">
         <v>6</v>
       </c>
       <c r="M54">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N54">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O54">
         <v>6</v>
       </c>
       <c r="P54">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="Q54">
         <v>1</v>
       </c>
       <c r="R54">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S54">
-        <v>7.3</v>
+        <v>3.9</v>
       </c>
       <c r="T54">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U54">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="V54">
         <v>3</v>
@@ -4366,58 +4363,58 @@
         <v>102</v>
       </c>
       <c r="D55">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E55">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F55">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G55">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H55">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I55">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J55">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K55">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L55">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M55">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N55">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O55">
         <v>6</v>
       </c>
       <c r="P55">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="Q55">
         <v>1</v>
       </c>
       <c r="R55">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S55">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="T55">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U55">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="V55">
         <v>4</v>
@@ -4434,58 +4431,58 @@
         <v>102</v>
       </c>
       <c r="D56">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E56">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F56">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G56">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I56">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J56">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K56">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L56">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M56">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N56">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O56">
         <v>6</v>
       </c>
       <c r="P56">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="Q56">
         <v>1</v>
       </c>
       <c r="R56">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S56">
-        <v>11.5</v>
+        <v>6.6</v>
       </c>
       <c r="T56">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="U56">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="V56">
         <v>4</v>
@@ -4502,61 +4499,61 @@
         <v>101</v>
       </c>
       <c r="D57">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E57">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F57">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G57">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H57">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I57">
         <v>7</v>
       </c>
       <c r="J57">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K57">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L57">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M57">
         <v>6</v>
       </c>
       <c r="N57">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O57">
         <v>6</v>
       </c>
       <c r="P57">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="Q57">
         <v>1</v>
       </c>
       <c r="R57">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S57">
-        <v>2.3</v>
+        <v>7</v>
       </c>
       <c r="T57">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U57">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="V57">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58" spans="1:22">
@@ -4573,55 +4570,55 @@
         <v>4</v>
       </c>
       <c r="E58">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F58">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G58">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H58">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I58">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J58">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K58">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L58">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M58">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N58">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O58">
         <v>6</v>
       </c>
       <c r="P58">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q58">
         <v>2</v>
       </c>
       <c r="R58">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S58">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="T58">
         <v>6</v>
       </c>
       <c r="U58">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="V58">
         <v>4</v>
@@ -4638,43 +4635,43 @@
         <v>102</v>
       </c>
       <c r="D59">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E59">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F59">
         <v>3</v>
       </c>
       <c r="G59">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H59">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I59">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J59">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K59">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L59">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M59">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N59">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O59">
         <v>6</v>
       </c>
       <c r="P59">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="Q59">
         <v>1</v>
@@ -4682,11 +4679,14 @@
       <c r="R59">
         <v>3</v>
       </c>
+      <c r="S59">
+        <v>3.9</v>
+      </c>
       <c r="T59">
         <v>4</v>
       </c>
       <c r="U59">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="V59">
         <v>3</v>
@@ -4703,7 +4703,7 @@
         <v>101</v>
       </c>
       <c r="D60">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E60">
         <v>2</v>
@@ -4712,7 +4712,7 @@
         <v>2</v>
       </c>
       <c r="G60">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H60">
         <v>2</v>
@@ -4721,7 +4721,7 @@
         <v>5</v>
       </c>
       <c r="J60">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K60">
         <v>4</v>
@@ -4730,31 +4730,31 @@
         <v>4</v>
       </c>
       <c r="M60">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N60">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O60">
         <v>6</v>
       </c>
       <c r="P60">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="Q60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R60">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S60">
-        <v>10.6</v>
+        <v>9.4</v>
       </c>
       <c r="T60">
         <v>4</v>
       </c>
       <c r="U60">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="V60">
         <v>3</v>
@@ -4777,7 +4777,7 @@
         <v>3</v>
       </c>
       <c r="F61">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G61">
         <v>3</v>
@@ -4789,40 +4789,40 @@
         <v>4</v>
       </c>
       <c r="J61">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K61">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L61">
         <v>4</v>
       </c>
       <c r="M61">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N61">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O61">
         <v>6</v>
       </c>
       <c r="P61">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="Q61">
         <v>1</v>
       </c>
       <c r="R61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S61">
-        <v>5.6</v>
+        <v>2.2</v>
       </c>
       <c r="T61">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U61">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="V61">
         <v>3</v>
@@ -4839,13 +4839,13 @@
         <v>103</v>
       </c>
       <c r="D62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G62">
         <v>1</v>
@@ -4854,46 +4854,46 @@
         <v>1</v>
       </c>
       <c r="I62">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J62">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K62">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L62">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M62">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N62">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O62">
         <v>6</v>
       </c>
       <c r="P62">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Q62">
         <v>1</v>
       </c>
       <c r="R62">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S62">
-        <v>9.9</v>
+        <v>6.4</v>
       </c>
       <c r="T62">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U62">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="V62">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63" spans="1:22">
@@ -4907,61 +4907,61 @@
         <v>101</v>
       </c>
       <c r="D63">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E63">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F63">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G63">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H63">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I63">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J63">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K63">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L63">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M63">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N63">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O63">
         <v>6</v>
       </c>
       <c r="P63">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="Q63">
         <v>1</v>
       </c>
       <c r="R63">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S63">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="T63">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U63">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="V63">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64" spans="1:22">
@@ -4975,61 +4975,58 @@
         <v>101</v>
       </c>
       <c r="D64">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E64">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F64">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G64">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H64">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I64">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J64">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K64">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L64">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M64">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N64">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O64">
         <v>6</v>
       </c>
-      <c r="P64">
-        <v>37</v>
-      </c>
       <c r="Q64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R64">
         <v>3</v>
       </c>
       <c r="S64">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="T64">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="U64">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="V64">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65" spans="1:22">
@@ -5040,10 +5037,10 @@
         <v>85</v>
       </c>
       <c r="C65" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E65">
         <v>1</v>
@@ -5055,49 +5052,49 @@
         <v>1</v>
       </c>
       <c r="H65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I65">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J65">
         <v>7</v>
       </c>
       <c r="K65">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L65">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M65">
         <v>6</v>
       </c>
       <c r="N65">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O65">
         <v>6</v>
       </c>
       <c r="P65">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="Q65">
         <v>2</v>
       </c>
       <c r="R65">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S65">
-        <v>6.4</v>
+        <v>7.9</v>
       </c>
       <c r="T65">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U65">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="V65">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66" spans="1:22">
@@ -5111,58 +5108,58 @@
         <v>101</v>
       </c>
       <c r="D66">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E66">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F66">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G66">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H66">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I66">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J66">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K66">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L66">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M66">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N66">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O66">
         <v>6</v>
       </c>
       <c r="P66">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="Q66">
         <v>1</v>
       </c>
       <c r="R66">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S66">
-        <v>5.1</v>
+        <v>7.5</v>
       </c>
       <c r="T66">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U66">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="V66">
         <v>3</v>
@@ -5182,58 +5179,58 @@
         <v>1</v>
       </c>
       <c r="E67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F67">
         <v>1</v>
       </c>
       <c r="G67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I67">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J67">
         <v>5</v>
       </c>
       <c r="K67">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L67">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M67">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N67">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O67">
         <v>6</v>
       </c>
       <c r="P67">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="Q67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R67">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S67">
-        <v>9.199999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="T67">
         <v>6</v>
       </c>
       <c r="U67">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="V67">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68" spans="1:22">
@@ -5256,49 +5253,49 @@
         <v>3</v>
       </c>
       <c r="G68">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H68">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I68">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J68">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K68">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L68">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M68">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N68">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O68">
         <v>6</v>
       </c>
       <c r="P68">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q68">
         <v>1</v>
       </c>
       <c r="R68">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S68">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="T68">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U68">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="V68">
         <v>3</v>
@@ -5321,37 +5318,37 @@
         <v>2</v>
       </c>
       <c r="F69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G69">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H69">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I69">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J69">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K69">
         <v>5</v>
       </c>
       <c r="L69">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M69">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N69">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O69">
         <v>6</v>
       </c>
       <c r="P69">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="Q69">
         <v>1</v>
@@ -5360,16 +5357,16 @@
         <v>4</v>
       </c>
       <c r="S69">
-        <v>3.4</v>
+        <v>7.5</v>
       </c>
       <c r="T69">
         <v>3</v>
       </c>
       <c r="U69">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V69">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70" spans="1:22">
@@ -5395,22 +5392,22 @@
         <v>1</v>
       </c>
       <c r="H70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I70">
         <v>5</v>
       </c>
       <c r="J70">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K70">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L70">
         <v>5</v>
       </c>
       <c r="M70">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N70">
         <v>5</v>
@@ -5419,25 +5416,25 @@
         <v>6</v>
       </c>
       <c r="P70">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="Q70">
         <v>1</v>
       </c>
       <c r="R70">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S70">
-        <v>4.6</v>
+        <v>12</v>
       </c>
       <c r="T70">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U70">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="V70">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:22">
@@ -5451,28 +5448,28 @@
         <v>103</v>
       </c>
       <c r="D71">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F71">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G71">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H71">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I71">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J71">
         <v>1</v>
       </c>
       <c r="K71">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L71">
         <v>2</v>
@@ -5487,25 +5484,25 @@
         <v>6</v>
       </c>
       <c r="P71">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q71">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R71">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S71">
-        <v>5.8</v>
+        <v>3</v>
       </c>
       <c r="T71">
         <v>5</v>
       </c>
       <c r="U71">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="V71">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72" spans="1:22">
@@ -5519,34 +5516,34 @@
         <v>101</v>
       </c>
       <c r="D72">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E72">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F72">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G72">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H72">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I72">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J72">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K72">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L72">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M72">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N72">
         <v>5</v>
@@ -5555,7 +5552,7 @@
         <v>6</v>
       </c>
       <c r="P72">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="Q72">
         <v>2</v>
@@ -5564,16 +5561,16 @@
         <v>3</v>
       </c>
       <c r="S72">
-        <v>6.9</v>
+        <v>3.4</v>
       </c>
       <c r="T72">
         <v>5</v>
       </c>
       <c r="U72">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="V72">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73" spans="1:22">
@@ -5587,34 +5584,34 @@
         <v>102</v>
       </c>
       <c r="D73">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E73">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F73">
         <v>2</v>
       </c>
       <c r="G73">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H73">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I73">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J73">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K73">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L73">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M73">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N73">
         <v>6</v>
@@ -5623,25 +5620,25 @@
         <v>6</v>
       </c>
       <c r="P73">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="Q73">
         <v>1</v>
       </c>
       <c r="R73">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S73">
-        <v>6.5</v>
+        <v>7.6</v>
       </c>
       <c r="T73">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U73">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="V73">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74" spans="1:22">
@@ -5655,19 +5652,19 @@
         <v>101</v>
       </c>
       <c r="D74">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G74">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H74">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I74">
         <v>3</v>
@@ -5679,34 +5676,34 @@
         <v>3</v>
       </c>
       <c r="L74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N74">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O74">
         <v>6</v>
       </c>
       <c r="P74">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="Q74">
         <v>2</v>
       </c>
       <c r="R74">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S74">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="T74">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U74">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="V74">
         <v>4</v>
@@ -5732,52 +5729,52 @@
         <v>2</v>
       </c>
       <c r="G75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H75">
         <v>2</v>
       </c>
       <c r="I75">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J75">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K75">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L75">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M75">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N75">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O75">
         <v>6</v>
       </c>
       <c r="P75">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="Q75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R75">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S75">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="T75">
         <v>5</v>
       </c>
       <c r="U75">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="V75">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76" spans="1:22">
@@ -5794,55 +5791,55 @@
         <v>3</v>
       </c>
       <c r="E76">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F76">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G76">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H76">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I76">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L76">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M76">
         <v>3</v>
       </c>
       <c r="N76">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O76">
         <v>6</v>
       </c>
       <c r="P76">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q76">
         <v>1</v>
       </c>
       <c r="R76">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S76">
-        <v>18</v>
+        <v>5.1</v>
       </c>
       <c r="T76">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U76">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="V76">
         <v>3</v>
@@ -5871,31 +5868,31 @@
         <v>2</v>
       </c>
       <c r="H77">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I77">
         <v>5</v>
       </c>
       <c r="J77">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K77">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L77">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M77">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N77">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O77">
         <v>6</v>
       </c>
       <c r="P77">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="Q77">
         <v>1</v>
@@ -5904,16 +5901,16 @@
         <v>3</v>
       </c>
       <c r="S77">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="T77">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U77">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V77">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78" spans="1:22">
@@ -5927,34 +5924,34 @@
         <v>103</v>
       </c>
       <c r="D78">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E78">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F78">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G78">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H78">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I78">
         <v>7</v>
       </c>
       <c r="J78">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K78">
         <v>7</v>
       </c>
       <c r="L78">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M78">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N78">
         <v>6</v>
@@ -5963,25 +5960,25 @@
         <v>6</v>
       </c>
       <c r="P78">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="Q78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R78">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S78">
-        <v>3.1</v>
+        <v>10</v>
       </c>
       <c r="T78">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U78">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="V78">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79" spans="1:22">
@@ -5995,31 +5992,31 @@
         <v>101</v>
       </c>
       <c r="D79">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E79">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F79">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G79">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I79">
         <v>5</v>
       </c>
       <c r="J79">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K79">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L79">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M79">
         <v>6</v>
@@ -6031,25 +6028,25 @@
         <v>6</v>
       </c>
       <c r="P79">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="Q79">
         <v>1</v>
       </c>
       <c r="R79">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S79">
-        <v>8.4</v>
+        <v>9.1</v>
       </c>
       <c r="T79">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U79">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="V79">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80" spans="1:22">
@@ -6063,49 +6060,52 @@
         <v>101</v>
       </c>
       <c r="D80">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E80">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F80">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G80">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H80">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I80">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J80">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K80">
         <v>6</v>
       </c>
       <c r="L80">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M80">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N80">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O80">
         <v>6</v>
       </c>
       <c r="P80">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="Q80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R80">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="S80">
+        <v>5.3</v>
       </c>
       <c r="T80">
         <v>5</v>
@@ -6114,7 +6114,7 @@
         <v>22</v>
       </c>
       <c r="V80">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/data/T3_leader_cleaned.xlsx
+++ b/data/T3_leader_cleaned.xlsx
@@ -88,235 +88,235 @@
     <t>A_L20</t>
   </si>
   <si>
+    <t>A_L08</t>
+  </si>
+  <si>
+    <t>B_L10</t>
+  </si>
+  <si>
+    <t>B_L06</t>
+  </si>
+  <si>
+    <t>C_L19</t>
+  </si>
+  <si>
+    <t>C_L26</t>
+  </si>
+  <si>
+    <t>A_L11</t>
+  </si>
+  <si>
+    <t>A_L10</t>
+  </si>
+  <si>
+    <t>B_L24</t>
+  </si>
+  <si>
+    <t>B_L22</t>
+  </si>
+  <si>
+    <t>C_L12</t>
+  </si>
+  <si>
+    <t>C_L01</t>
+  </si>
+  <si>
+    <t>C_L02</t>
+  </si>
+  <si>
+    <t>B_L08</t>
+  </si>
+  <si>
+    <t>B_L09</t>
+  </si>
+  <si>
+    <t>A_L26</t>
+  </si>
+  <si>
+    <t>C_L06</t>
+  </si>
+  <si>
+    <t>A_L16</t>
+  </si>
+  <si>
+    <t>C_L08</t>
+  </si>
+  <si>
+    <t>B_L05</t>
+  </si>
+  <si>
+    <t>C_L14</t>
+  </si>
+  <si>
+    <t>C_L21</t>
+  </si>
+  <si>
+    <t>A_L28</t>
+  </si>
+  <si>
+    <t>C_L18</t>
+  </si>
+  <si>
+    <t>C_L07</t>
+  </si>
+  <si>
+    <t>A_L19</t>
+  </si>
+  <si>
+    <t>B_L01</t>
+  </si>
+  <si>
+    <t>A_L06</t>
+  </si>
+  <si>
+    <t>C_L25</t>
+  </si>
+  <si>
+    <t>A_L14</t>
+  </si>
+  <si>
+    <t>C_L29</t>
+  </si>
+  <si>
+    <t>B_L26</t>
+  </si>
+  <si>
+    <t>C_L11</t>
+  </si>
+  <si>
+    <t>B_L25</t>
+  </si>
+  <si>
+    <t>B_L29</t>
+  </si>
+  <si>
+    <t>C_L04</t>
+  </si>
+  <si>
+    <t>A_L21</t>
+  </si>
+  <si>
+    <t>C_L30</t>
+  </si>
+  <si>
+    <t>C_L28</t>
+  </si>
+  <si>
+    <t>B_L02</t>
+  </si>
+  <si>
+    <t>C_L17</t>
+  </si>
+  <si>
+    <t>C_L22</t>
+  </si>
+  <si>
+    <t>B_L04</t>
+  </si>
+  <si>
+    <t>C_L20</t>
+  </si>
+  <si>
+    <t>B_L11</t>
+  </si>
+  <si>
+    <t>A_L18</t>
+  </si>
+  <si>
+    <t>C_L03</t>
+  </si>
+  <si>
+    <t>B_L20</t>
+  </si>
+  <si>
     <t>A_L09</t>
   </si>
   <si>
-    <t>B_L11</t>
+    <t>B_L18</t>
+  </si>
+  <si>
+    <t>B_L03</t>
   </si>
   <si>
     <t>B_L07</t>
   </si>
   <si>
-    <t>C_L19</t>
-  </si>
-  <si>
-    <t>C_L25</t>
-  </si>
-  <si>
-    <t>A_L12</t>
-  </si>
-  <si>
-    <t>A_L11</t>
-  </si>
-  <si>
-    <t>B_L25</t>
-  </si>
-  <si>
-    <t>B_L22</t>
-  </si>
-  <si>
-    <t>C_L11</t>
-  </si>
-  <si>
-    <t>C_L01</t>
-  </si>
-  <si>
-    <t>C_L02</t>
-  </si>
-  <si>
-    <t>B_L09</t>
-  </si>
-  <si>
-    <t>B_L10</t>
-  </si>
-  <si>
-    <t>A_L26</t>
-  </si>
-  <si>
-    <t>C_L06</t>
-  </si>
-  <si>
-    <t>A_L16</t>
-  </si>
-  <si>
-    <t>C_L08</t>
-  </si>
-  <si>
-    <t>B_L06</t>
-  </si>
-  <si>
-    <t>C_L14</t>
-  </si>
-  <si>
-    <t>C_L21</t>
+    <t>B_L23</t>
+  </si>
+  <si>
+    <t>B_L15</t>
+  </si>
+  <si>
+    <t>A_L07</t>
+  </si>
+  <si>
+    <t>C_L16</t>
+  </si>
+  <si>
+    <t>B_L30</t>
+  </si>
+  <si>
+    <t>A_L02</t>
+  </si>
+  <si>
+    <t>C_L10</t>
+  </si>
+  <si>
+    <t>C_L13</t>
+  </si>
+  <si>
+    <t>A_L03</t>
+  </si>
+  <si>
+    <t>A_L25</t>
   </si>
   <si>
     <t>A_L29</t>
   </si>
   <si>
-    <t>C_L18</t>
-  </si>
-  <si>
-    <t>C_L07</t>
-  </si>
-  <si>
-    <t>A_L19</t>
-  </si>
-  <si>
-    <t>B_L02</t>
-  </si>
-  <si>
-    <t>A_L06</t>
-  </si>
-  <si>
-    <t>C_L24</t>
-  </si>
-  <si>
-    <t>A_L14</t>
-  </si>
-  <si>
-    <t>C_L29</t>
-  </si>
-  <si>
-    <t>B_L27</t>
-  </si>
-  <si>
-    <t>C_L10</t>
-  </si>
-  <si>
-    <t>B_L26</t>
-  </si>
-  <si>
-    <t>B_L29</t>
-  </si>
-  <si>
-    <t>C_L04</t>
-  </si>
-  <si>
-    <t>A_L21</t>
-  </si>
-  <si>
-    <t>C_L30</t>
-  </si>
-  <si>
-    <t>C_L28</t>
-  </si>
-  <si>
-    <t>B_L03</t>
-  </si>
-  <si>
-    <t>C_L17</t>
-  </si>
-  <si>
-    <t>C_L22</t>
-  </si>
-  <si>
-    <t>B_L05</t>
-  </si>
-  <si>
-    <t>C_L20</t>
+    <t>A_L17</t>
+  </si>
+  <si>
+    <t>B_L14</t>
+  </si>
+  <si>
+    <t>B_L21</t>
+  </si>
+  <si>
+    <t>A_L23</t>
   </si>
   <si>
     <t>B_L12</t>
   </si>
   <si>
-    <t>A_L18</t>
-  </si>
-  <si>
-    <t>C_L03</t>
-  </si>
-  <si>
-    <t>B_L20</t>
-  </si>
-  <si>
-    <t>A_L10</t>
-  </si>
-  <si>
-    <t>B_L19</t>
-  </si>
-  <si>
-    <t>B_L04</t>
-  </si>
-  <si>
-    <t>B_L08</t>
-  </si>
-  <si>
-    <t>B_L23</t>
+    <t>C_L27</t>
+  </si>
+  <si>
+    <t>A_L13</t>
   </si>
   <si>
     <t>B_L16</t>
   </si>
   <si>
-    <t>A_L08</t>
-  </si>
-  <si>
-    <t>C_L16</t>
-  </si>
-  <si>
-    <t>B_L30</t>
-  </si>
-  <si>
-    <t>A_L03</t>
-  </si>
-  <si>
-    <t>C_L09</t>
-  </si>
-  <si>
-    <t>C_L13</t>
+    <t>A_L22</t>
+  </si>
+  <si>
+    <t>A_L24</t>
+  </si>
+  <si>
+    <t>A_L01</t>
+  </si>
+  <si>
+    <t>C_L23</t>
+  </si>
+  <si>
+    <t>C_L05</t>
   </si>
   <si>
     <t>A_L04</t>
   </si>
   <si>
-    <t>A_L25</t>
-  </si>
-  <si>
-    <t>B_L01</t>
-  </si>
-  <si>
-    <t>A_L17</t>
-  </si>
-  <si>
-    <t>B_L15</t>
-  </si>
-  <si>
-    <t>B_L21</t>
-  </si>
-  <si>
-    <t>A_L23</t>
-  </si>
-  <si>
-    <t>B_L14</t>
-  </si>
-  <si>
-    <t>C_L26</t>
-  </si>
-  <si>
-    <t>A_L13</t>
-  </si>
-  <si>
-    <t>B_L18</t>
-  </si>
-  <si>
-    <t>A_L22</t>
-  </si>
-  <si>
-    <t>A_L24</t>
-  </si>
-  <si>
-    <t>A_L01</t>
-  </si>
-  <si>
-    <t>C_L23</t>
-  </si>
-  <si>
-    <t>C_L05</t>
-  </si>
-  <si>
-    <t>A_L05</t>
-  </si>
-  <si>
-    <t>A_L28</t>
+    <t>A_L27</t>
   </si>
   <si>
     <t>A</t>
@@ -768,13 +768,13 @@
         <v>4</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H2">
         <v>5</v>
@@ -789,13 +789,13 @@
         <v>4</v>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O2">
         <v>6</v>
@@ -833,7 +833,7 @@
         <v>101</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -842,16 +842,16 @@
         <v>3</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K3">
         <v>7</v>
@@ -863,7 +863,7 @@
         <v>7</v>
       </c>
       <c r="N3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O3">
         <v>6</v>
@@ -904,34 +904,34 @@
         <v>3</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O4">
         <v>6</v>
@@ -969,13 +969,13 @@
         <v>102</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G5">
         <v>3</v>
@@ -987,13 +987,13 @@
         <v>3</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K5">
         <v>3</v>
       </c>
       <c r="L5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M5">
         <v>2</v>
@@ -1046,25 +1046,25 @@
         <v>2</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6">
         <v>2</v>
       </c>
       <c r="I6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J6">
         <v>5</v>
       </c>
       <c r="K6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L6">
         <v>5</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N6">
         <v>6</v>
@@ -1120,10 +1120,10 @@
         <v>2</v>
       </c>
       <c r="I7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K7">
         <v>5</v>
@@ -1132,7 +1132,7 @@
         <v>4</v>
       </c>
       <c r="M7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N7">
         <v>5</v>
@@ -1173,37 +1173,37 @@
         <v>103</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G8">
         <v>3</v>
       </c>
       <c r="H8">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O8">
         <v>6</v>
@@ -1241,37 +1241,37 @@
         <v>101</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9">
         <v>1</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I9">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J9">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K9">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L9">
         <v>7</v>
       </c>
       <c r="M9">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N9">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O9">
         <v>6</v>
@@ -1312,7 +1312,7 @@
         <v>4</v>
       </c>
       <c r="E10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F10">
         <v>3</v>
@@ -1321,25 +1321,25 @@
         <v>3</v>
       </c>
       <c r="H10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I10">
         <v>5</v>
       </c>
       <c r="J10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L10">
         <v>5</v>
       </c>
       <c r="M10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O10">
         <v>6</v>
@@ -1383,31 +1383,31 @@
         <v>3</v>
       </c>
       <c r="F11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H11">
         <v>3</v>
       </c>
       <c r="I11">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J11">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K11">
         <v>6</v>
       </c>
       <c r="L11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O11">
         <v>6</v>
@@ -1445,34 +1445,34 @@
         <v>102</v>
       </c>
       <c r="D12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12">
         <v>2</v>
       </c>
       <c r="F12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I12">
         <v>7</v>
       </c>
       <c r="J12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K12">
         <v>6</v>
       </c>
       <c r="L12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N12">
         <v>6</v>
@@ -1513,37 +1513,37 @@
         <v>103</v>
       </c>
       <c r="D13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="F13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G13">
         <v>2</v>
       </c>
       <c r="H13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J13">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L13">
         <v>5</v>
       </c>
       <c r="M13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N13">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O13">
         <v>6</v>
@@ -1590,19 +1590,19 @@
         <v>2</v>
       </c>
       <c r="G14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I14">
         <v>4</v>
       </c>
       <c r="J14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L14">
         <v>5</v>
@@ -1649,7 +1649,7 @@
         <v>103</v>
       </c>
       <c r="D15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E15">
         <v>7</v>
@@ -1667,10 +1667,10 @@
         <v>1</v>
       </c>
       <c r="J15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L15">
         <v>1</v>
@@ -1679,7 +1679,7 @@
         <v>2</v>
       </c>
       <c r="N15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O15">
         <v>6</v>
@@ -1714,37 +1714,37 @@
         <v>102</v>
       </c>
       <c r="D16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H16">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I16">
         <v>5</v>
       </c>
       <c r="J16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L16">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M16">
         <v>5</v>
       </c>
       <c r="N16">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O16">
         <v>6</v>
@@ -1782,10 +1782,10 @@
         <v>102</v>
       </c>
       <c r="D17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F17">
         <v>4</v>
@@ -1797,22 +1797,22 @@
         <v>4</v>
       </c>
       <c r="I17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K17">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L17">
         <v>4</v>
       </c>
       <c r="M17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O17">
         <v>6</v>
@@ -1856,25 +1856,25 @@
         <v>1</v>
       </c>
       <c r="F18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G18">
         <v>1</v>
       </c>
       <c r="H18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J18">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K18">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M18">
         <v>5</v>
@@ -1933,22 +1933,22 @@
         <v>1</v>
       </c>
       <c r="I19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J19">
         <v>5</v>
       </c>
       <c r="K19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O19">
         <v>6</v>
@@ -1998,25 +1998,25 @@
         <v>1</v>
       </c>
       <c r="H20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I20">
         <v>7</v>
       </c>
       <c r="J20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K20">
         <v>6</v>
       </c>
       <c r="L20">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O20">
         <v>6</v>
@@ -2054,19 +2054,19 @@
         <v>103</v>
       </c>
       <c r="D21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F21">
         <v>1</v>
       </c>
       <c r="G21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I21">
         <v>5</v>
@@ -2078,13 +2078,13 @@
         <v>4</v>
       </c>
       <c r="L21">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N21">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O21">
         <v>6</v>
@@ -2128,7 +2128,7 @@
         <v>2</v>
       </c>
       <c r="F22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -2137,22 +2137,22 @@
         <v>2</v>
       </c>
       <c r="I22">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J22">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K22">
         <v>3</v>
       </c>
       <c r="L22">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M22">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N22">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O22">
         <v>6</v>
@@ -2190,34 +2190,34 @@
         <v>103</v>
       </c>
       <c r="D23">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F23">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K23">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L23">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M23">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N23">
         <v>4</v>
@@ -2258,37 +2258,37 @@
         <v>103</v>
       </c>
       <c r="D24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E24">
         <v>2</v>
       </c>
       <c r="F24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G24">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H24">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J24">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K24">
         <v>3</v>
       </c>
       <c r="L24">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M24">
         <v>4</v>
       </c>
       <c r="N24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O24">
         <v>6</v>
@@ -2323,37 +2323,37 @@
         <v>101</v>
       </c>
       <c r="D25">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E25">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G25">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I25">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J25">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K25">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L25">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M25">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N25">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O25">
         <v>6</v>
@@ -2391,34 +2391,34 @@
         <v>103</v>
       </c>
       <c r="D26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F26">
         <v>1</v>
       </c>
       <c r="G26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I26">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J26">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K26">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M26">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N26">
         <v>4</v>
@@ -2459,19 +2459,19 @@
         <v>103</v>
       </c>
       <c r="D27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E27">
         <v>2</v>
       </c>
       <c r="F27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G27">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I27">
         <v>3</v>
@@ -2480,16 +2480,16 @@
         <v>2</v>
       </c>
       <c r="K27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M27">
         <v>3</v>
       </c>
       <c r="N27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O27">
         <v>6</v>
@@ -2527,7 +2527,7 @@
         <v>101</v>
       </c>
       <c r="D28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E28">
         <v>1</v>
@@ -2539,25 +2539,25 @@
         <v>2</v>
       </c>
       <c r="H28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I28">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J28">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K28">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L28">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M28">
         <v>4</v>
       </c>
       <c r="N28">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O28">
         <v>6</v>
@@ -2601,31 +2601,31 @@
         <v>4</v>
       </c>
       <c r="F29">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G29">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H29">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J29">
         <v>5</v>
       </c>
       <c r="K29">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M29">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N29">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O29">
         <v>6</v>
@@ -2672,25 +2672,25 @@
         <v>1</v>
       </c>
       <c r="G30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I30">
         <v>7</v>
       </c>
       <c r="J30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N30">
         <v>7</v>
@@ -2731,37 +2731,37 @@
         <v>103</v>
       </c>
       <c r="D31">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E31">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F31">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G31">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H31">
         <v>3</v>
       </c>
       <c r="I31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J31">
         <v>2</v>
       </c>
       <c r="K31">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L31">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M31">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O31">
         <v>6</v>
@@ -2802,31 +2802,31 @@
         <v>4</v>
       </c>
       <c r="E32">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F32">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G32">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H32">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I32">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J32">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K32">
         <v>5</v>
       </c>
       <c r="L32">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N32">
         <v>5</v>
@@ -2867,37 +2867,37 @@
         <v>103</v>
       </c>
       <c r="D33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33">
         <v>1</v>
       </c>
       <c r="F33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H33">
         <v>1</v>
       </c>
       <c r="I33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J33">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K33">
         <v>6</v>
       </c>
       <c r="L33">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O33">
         <v>6</v>
@@ -2935,37 +2935,37 @@
         <v>102</v>
       </c>
       <c r="D34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E34">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G34">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I34">
         <v>7</v>
       </c>
       <c r="J34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K34">
         <v>6</v>
       </c>
       <c r="L34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M34">
         <v>6</v>
       </c>
       <c r="N34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O34">
         <v>6</v>
@@ -3006,34 +3006,34 @@
         <v>1</v>
       </c>
       <c r="E35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F35">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I35">
         <v>5</v>
       </c>
       <c r="J35">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K35">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L35">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M35">
         <v>5</v>
       </c>
       <c r="N35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O35">
         <v>6</v>
@@ -3074,7 +3074,7 @@
         <v>2</v>
       </c>
       <c r="E36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F36">
         <v>2</v>
@@ -3083,7 +3083,7 @@
         <v>3</v>
       </c>
       <c r="H36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I36">
         <v>3</v>
@@ -3092,16 +3092,16 @@
         <v>2</v>
       </c>
       <c r="K36">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M36">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N36">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O36">
         <v>6</v>
@@ -3139,37 +3139,37 @@
         <v>102</v>
       </c>
       <c r="D37">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F37">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G37">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H37">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J37">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K37">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L37">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M37">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O37">
         <v>6</v>
@@ -3210,7 +3210,7 @@
         <v>2</v>
       </c>
       <c r="E38">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F38">
         <v>2</v>
@@ -3219,19 +3219,19 @@
         <v>1</v>
       </c>
       <c r="H38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I38">
         <v>6</v>
       </c>
       <c r="J38">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M38">
         <v>7</v>
@@ -3281,31 +3281,31 @@
         <v>2</v>
       </c>
       <c r="F39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G39">
         <v>2</v>
       </c>
       <c r="H39">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I39">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J39">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K39">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L39">
         <v>3</v>
       </c>
       <c r="M39">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N39">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O39">
         <v>6</v>
@@ -3343,37 +3343,37 @@
         <v>103</v>
       </c>
       <c r="D40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H40">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K40">
         <v>5</v>
       </c>
       <c r="L40">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M40">
         <v>5</v>
       </c>
       <c r="N40">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O40">
         <v>6</v>
@@ -3411,13 +3411,13 @@
         <v>103</v>
       </c>
       <c r="D41">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E41">
         <v>2</v>
       </c>
       <c r="F41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G41">
         <v>2</v>
@@ -3426,13 +3426,13 @@
         <v>3</v>
       </c>
       <c r="I41">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L41">
         <v>7</v>
@@ -3441,7 +3441,7 @@
         <v>7</v>
       </c>
       <c r="N41">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O41">
         <v>6</v>
@@ -3485,31 +3485,31 @@
         <v>1</v>
       </c>
       <c r="F42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G42">
         <v>1</v>
       </c>
       <c r="H42">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J42">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K42">
         <v>3</v>
       </c>
       <c r="L42">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M42">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N42">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O42">
         <v>6</v>
@@ -3550,7 +3550,7 @@
         <v>1</v>
       </c>
       <c r="E43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F43">
         <v>1</v>
@@ -3559,25 +3559,25 @@
         <v>1</v>
       </c>
       <c r="H43">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J43">
         <v>7</v>
       </c>
       <c r="K43">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L43">
         <v>6</v>
       </c>
       <c r="M43">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N43">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O43">
         <v>6</v>
@@ -3615,13 +3615,13 @@
         <v>103</v>
       </c>
       <c r="D44">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E44">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F44">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G44">
         <v>2</v>
@@ -3630,7 +3630,7 @@
         <v>3</v>
       </c>
       <c r="I44">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J44">
         <v>5</v>
@@ -3639,10 +3639,10 @@
         <v>4</v>
       </c>
       <c r="L44">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M44">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N44">
         <v>4</v>
@@ -3683,7 +3683,7 @@
         <v>102</v>
       </c>
       <c r="D45">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E45">
         <v>4</v>
@@ -3692,22 +3692,22 @@
         <v>3</v>
       </c>
       <c r="G45">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H45">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I45">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J45">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K45">
         <v>6</v>
       </c>
       <c r="L45">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M45">
         <v>6</v>
@@ -3751,37 +3751,37 @@
         <v>103</v>
       </c>
       <c r="D46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E46">
         <v>3</v>
       </c>
       <c r="F46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G46">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H46">
         <v>3</v>
       </c>
       <c r="I46">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J46">
         <v>4</v>
       </c>
       <c r="K46">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L46">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M46">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N46">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O46">
         <v>6</v>
@@ -3822,22 +3822,22 @@
         <v>2</v>
       </c>
       <c r="E47">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H47">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I47">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J47">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K47">
         <v>7</v>
@@ -3890,16 +3890,16 @@
         <v>2</v>
       </c>
       <c r="E48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G48">
         <v>2</v>
       </c>
       <c r="H48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I48">
         <v>7</v>
@@ -3973,19 +3973,19 @@
         <v>5</v>
       </c>
       <c r="J49">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K49">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L49">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M49">
         <v>5</v>
       </c>
       <c r="N49">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O49">
         <v>6</v>
@@ -4032,28 +4032,28 @@
         <v>2</v>
       </c>
       <c r="G50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H50">
         <v>1</v>
       </c>
       <c r="I50">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J50">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K50">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L50">
         <v>5</v>
       </c>
       <c r="M50">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O50">
         <v>6</v>
@@ -4097,10 +4097,10 @@
         <v>2</v>
       </c>
       <c r="F51">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H51">
         <v>1</v>
@@ -4112,13 +4112,13 @@
         <v>1</v>
       </c>
       <c r="K51">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L51">
         <v>2</v>
       </c>
       <c r="M51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N51">
         <v>3</v>
@@ -4159,34 +4159,34 @@
         <v>102</v>
       </c>
       <c r="D52">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E52">
         <v>2</v>
       </c>
       <c r="F52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G52">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H52">
         <v>1</v>
       </c>
       <c r="I52">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J52">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K52">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L52">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M52">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N52">
         <v>6</v>
@@ -4227,28 +4227,28 @@
         <v>102</v>
       </c>
       <c r="D53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E53">
         <v>1</v>
       </c>
       <c r="F53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G53">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I53">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J53">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K53">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L53">
         <v>5</v>
@@ -4295,34 +4295,34 @@
         <v>102</v>
       </c>
       <c r="D54">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E54">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F54">
         <v>1</v>
       </c>
       <c r="G54">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I54">
         <v>6</v>
       </c>
       <c r="J54">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K54">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L54">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M54">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N54">
         <v>7</v>
@@ -4363,19 +4363,19 @@
         <v>102</v>
       </c>
       <c r="D55">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E55">
         <v>5</v>
       </c>
       <c r="F55">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G55">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H55">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I55">
         <v>1</v>
@@ -4387,10 +4387,10 @@
         <v>2</v>
       </c>
       <c r="L55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M55">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N55">
         <v>2</v>
@@ -4431,10 +4431,10 @@
         <v>102</v>
       </c>
       <c r="D56">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F56">
         <v>1</v>
@@ -4446,16 +4446,16 @@
         <v>2</v>
       </c>
       <c r="I56">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J56">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K56">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L56">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M56">
         <v>5</v>
@@ -4499,10 +4499,10 @@
         <v>101</v>
       </c>
       <c r="D57">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E57">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F57">
         <v>3</v>
@@ -4511,25 +4511,25 @@
         <v>3</v>
       </c>
       <c r="H57">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I57">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J57">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K57">
         <v>6</v>
       </c>
       <c r="L57">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M57">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N57">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O57">
         <v>6</v>
@@ -4567,7 +4567,7 @@
         <v>103</v>
       </c>
       <c r="D58">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E58">
         <v>1</v>
@@ -4576,22 +4576,22 @@
         <v>3</v>
       </c>
       <c r="G58">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H58">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I58">
         <v>4</v>
       </c>
       <c r="J58">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K58">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L58">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M58">
         <v>5</v>
@@ -4635,25 +4635,25 @@
         <v>102</v>
       </c>
       <c r="D59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E59">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F59">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G59">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H59">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I59">
         <v>6</v>
       </c>
       <c r="J59">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K59">
         <v>6</v>
@@ -4662,10 +4662,10 @@
         <v>6</v>
       </c>
       <c r="M59">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N59">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O59">
         <v>6</v>
@@ -4703,37 +4703,37 @@
         <v>101</v>
       </c>
       <c r="D60">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F60">
         <v>2</v>
       </c>
       <c r="G60">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I60">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J60">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K60">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L60">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M60">
         <v>6</v>
       </c>
       <c r="N60">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O60">
         <v>6</v>
@@ -4771,37 +4771,37 @@
         <v>103</v>
       </c>
       <c r="D61">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F61">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I61">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J61">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K61">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L61">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M61">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N61">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O61">
         <v>6</v>
@@ -4839,7 +4839,7 @@
         <v>103</v>
       </c>
       <c r="D62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E62">
         <v>1</v>
@@ -4851,25 +4851,25 @@
         <v>1</v>
       </c>
       <c r="H62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I62">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J62">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K62">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L62">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M62">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N62">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O62">
         <v>6</v>
@@ -4907,37 +4907,37 @@
         <v>101</v>
       </c>
       <c r="D63">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E63">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F63">
         <v>1</v>
       </c>
       <c r="G63">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H63">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I63">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J63">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K63">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L63">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M63">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N63">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O63">
         <v>6</v>
@@ -4975,34 +4975,34 @@
         <v>101</v>
       </c>
       <c r="D64">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E64">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F64">
         <v>4</v>
       </c>
       <c r="G64">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H64">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I64">
         <v>4</v>
       </c>
       <c r="J64">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K64">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L64">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M64">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N64">
         <v>4</v>
@@ -5037,40 +5037,40 @@
         <v>85</v>
       </c>
       <c r="C65" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D65">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E65">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F65">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H65">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I65">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J65">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K65">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L65">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M65">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N65">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O65">
         <v>6</v>
@@ -5111,34 +5111,34 @@
         <v>5</v>
       </c>
       <c r="E66">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F66">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G66">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H66">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I66">
         <v>6</v>
       </c>
       <c r="J66">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K66">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L66">
         <v>5</v>
       </c>
       <c r="M66">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N66">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O66">
         <v>6</v>
@@ -5179,34 +5179,34 @@
         <v>1</v>
       </c>
       <c r="E67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G67">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H67">
         <v>2</v>
       </c>
       <c r="I67">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J67">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K67">
         <v>5</v>
       </c>
       <c r="L67">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M67">
         <v>4</v>
       </c>
       <c r="N67">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O67">
         <v>6</v>
@@ -5247,31 +5247,31 @@
         <v>3</v>
       </c>
       <c r="E68">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F68">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G68">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H68">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I68">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J68">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K68">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L68">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M68">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N68">
         <v>4</v>
@@ -5315,34 +5315,34 @@
         <v>2</v>
       </c>
       <c r="E69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F69">
         <v>1</v>
       </c>
       <c r="G69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H69">
         <v>2</v>
       </c>
       <c r="I69">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J69">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K69">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L69">
         <v>4</v>
       </c>
       <c r="M69">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N69">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O69">
         <v>6</v>
@@ -5392,22 +5392,22 @@
         <v>1</v>
       </c>
       <c r="H70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I70">
         <v>5</v>
       </c>
       <c r="J70">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K70">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L70">
         <v>5</v>
       </c>
       <c r="M70">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N70">
         <v>5</v>
@@ -5448,37 +5448,37 @@
         <v>103</v>
       </c>
       <c r="D71">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E71">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F71">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G71">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H71">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I71">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J71">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K71">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L71">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M71">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N71">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O71">
         <v>6</v>
@@ -5516,31 +5516,31 @@
         <v>101</v>
       </c>
       <c r="D72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E72">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F72">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G72">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H72">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I72">
         <v>7</v>
       </c>
       <c r="J72">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K72">
         <v>7</v>
       </c>
       <c r="L72">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M72">
         <v>7</v>
@@ -5587,34 +5587,34 @@
         <v>4</v>
       </c>
       <c r="E73">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G73">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H73">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I73">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J73">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K73">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L73">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M73">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N73">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O73">
         <v>6</v>
@@ -5652,10 +5652,10 @@
         <v>101</v>
       </c>
       <c r="D74">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E74">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F74">
         <v>2</v>
@@ -5664,25 +5664,25 @@
         <v>3</v>
       </c>
       <c r="H74">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J74">
         <v>4</v>
       </c>
       <c r="K74">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L74">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M74">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N74">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O74">
         <v>6</v>
@@ -5720,7 +5720,7 @@
         <v>101</v>
       </c>
       <c r="D75">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E75">
         <v>1</v>
@@ -5729,7 +5729,7 @@
         <v>2</v>
       </c>
       <c r="G75">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H75">
         <v>2</v>
@@ -5788,37 +5788,37 @@
         <v>101</v>
       </c>
       <c r="D76">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E76">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F76">
         <v>3</v>
       </c>
       <c r="G76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I76">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J76">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K76">
         <v>3</v>
       </c>
       <c r="L76">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M76">
         <v>3</v>
       </c>
       <c r="N76">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O76">
         <v>6</v>
@@ -5856,28 +5856,28 @@
         <v>103</v>
       </c>
       <c r="D77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E77">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F77">
         <v>3</v>
       </c>
       <c r="G77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I77">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J77">
         <v>6</v>
       </c>
       <c r="K77">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L77">
         <v>6</v>
@@ -5886,7 +5886,7 @@
         <v>5</v>
       </c>
       <c r="N77">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O77">
         <v>6</v>
@@ -5930,10 +5930,10 @@
         <v>1</v>
       </c>
       <c r="F78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G78">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H78">
         <v>1</v>
@@ -5942,19 +5942,19 @@
         <v>7</v>
       </c>
       <c r="J78">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K78">
         <v>7</v>
       </c>
       <c r="L78">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M78">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N78">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O78">
         <v>6</v>
@@ -5992,37 +5992,37 @@
         <v>101</v>
       </c>
       <c r="D79">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E79">
         <v>3</v>
       </c>
       <c r="F79">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G79">
         <v>4</v>
       </c>
       <c r="H79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I79">
         <v>5</v>
       </c>
       <c r="J79">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K79">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L79">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M79">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N79">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O79">
         <v>6</v>
@@ -6060,37 +6060,37 @@
         <v>101</v>
       </c>
       <c r="D80">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E80">
         <v>1</v>
       </c>
       <c r="F80">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G80">
         <v>1</v>
       </c>
       <c r="H80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I80">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J80">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K80">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L80">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M80">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N80">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O80">
         <v>6</v>

--- a/data/T3_leader_cleaned.xlsx
+++ b/data/T3_leader_cleaned.xlsx
@@ -82,235 +82,235 @@
     <t>LeaderJobLevel</t>
   </si>
   <si>
+    <t>A_L13</t>
+  </si>
+  <si>
+    <t>A_L18</t>
+  </si>
+  <si>
+    <t>A_L07</t>
+  </si>
+  <si>
+    <t>B_L10</t>
+  </si>
+  <si>
+    <t>B_L06</t>
+  </si>
+  <si>
+    <t>C_L18</t>
+  </si>
+  <si>
+    <t>C_L26</t>
+  </si>
+  <si>
+    <t>A_L10</t>
+  </si>
+  <si>
+    <t>A_L09</t>
+  </si>
+  <si>
+    <t>B_L24</t>
+  </si>
+  <si>
+    <t>B_L22</t>
+  </si>
+  <si>
+    <t>C_L11</t>
+  </si>
+  <si>
+    <t>B_L30</t>
+  </si>
+  <si>
+    <t>C_L01</t>
+  </si>
+  <si>
+    <t>B_L08</t>
+  </si>
+  <si>
+    <t>B_L09</t>
+  </si>
+  <si>
+    <t>A_L26</t>
+  </si>
+  <si>
+    <t>C_L06</t>
+  </si>
+  <si>
+    <t>A_L14</t>
+  </si>
+  <si>
+    <t>C_L08</t>
+  </si>
+  <si>
+    <t>B_L05</t>
+  </si>
+  <si>
+    <t>C_L13</t>
+  </si>
+  <si>
+    <t>C_L22</t>
+  </si>
+  <si>
+    <t>A_L28</t>
+  </si>
+  <si>
+    <t>C_L17</t>
+  </si>
+  <si>
+    <t>C_L07</t>
+  </si>
+  <si>
+    <t>A_L17</t>
+  </si>
+  <si>
+    <t>B_L01</t>
+  </si>
+  <si>
+    <t>C_L21</t>
+  </si>
+  <si>
+    <t>A_L05</t>
+  </si>
+  <si>
+    <t>C_L25</t>
+  </si>
+  <si>
+    <t>A_L12</t>
+  </si>
+  <si>
+    <t>C_L29</t>
+  </si>
+  <si>
+    <t>B_L26</t>
+  </si>
+  <si>
+    <t>C_L10</t>
+  </si>
+  <si>
+    <t>B_L25</t>
+  </si>
+  <si>
+    <t>B_L27</t>
+  </si>
+  <si>
+    <t>C_L03</t>
+  </si>
+  <si>
+    <t>A_L19</t>
+  </si>
+  <si>
+    <t>C_L30</t>
+  </si>
+  <si>
+    <t>C_L28</t>
+  </si>
+  <si>
+    <t>B_L02</t>
+  </si>
+  <si>
+    <t>C_L16</t>
+  </si>
+  <si>
+    <t>C_L23</t>
+  </si>
+  <si>
+    <t>B_L04</t>
+  </si>
+  <si>
+    <t>B_L11</t>
+  </si>
+  <si>
+    <t>A_L16</t>
+  </si>
+  <si>
+    <t>C_L02</t>
+  </si>
+  <si>
+    <t>B_L20</t>
+  </si>
+  <si>
+    <t>A_L08</t>
+  </si>
+  <si>
+    <t>B_L19</t>
+  </si>
+  <si>
+    <t>B_L03</t>
+  </si>
+  <si>
+    <t>B_L07</t>
+  </si>
+  <si>
+    <t>B_L23</t>
+  </si>
+  <si>
+    <t>B_L16</t>
+  </si>
+  <si>
+    <t>A_L06</t>
+  </si>
+  <si>
+    <t>C_L14</t>
+  </si>
+  <si>
+    <t>B_L29</t>
+  </si>
+  <si>
+    <t>A_L02</t>
+  </si>
+  <si>
+    <t>C_L09</t>
+  </si>
+  <si>
+    <t>C_L12</t>
+  </si>
+  <si>
+    <t>A_L03</t>
+  </si>
+  <si>
+    <t>A_L25</t>
+  </si>
+  <si>
+    <t>A_L29</t>
+  </si>
+  <si>
     <t>A_L15</t>
   </si>
   <si>
-    <t>A_L20</t>
-  </si>
-  <si>
-    <t>A_L08</t>
-  </si>
-  <si>
-    <t>B_L10</t>
-  </si>
-  <si>
-    <t>B_L06</t>
-  </si>
-  <si>
-    <t>C_L19</t>
-  </si>
-  <si>
-    <t>C_L26</t>
+    <t>B_L14</t>
+  </si>
+  <si>
+    <t>B_L21</t>
+  </si>
+  <si>
+    <t>A_L23</t>
+  </si>
+  <si>
+    <t>B_L12</t>
+  </si>
+  <si>
+    <t>C_L27</t>
   </si>
   <si>
     <t>A_L11</t>
   </si>
   <si>
-    <t>A_L10</t>
-  </si>
-  <si>
-    <t>B_L24</t>
-  </si>
-  <si>
-    <t>B_L22</t>
-  </si>
-  <si>
-    <t>C_L12</t>
-  </si>
-  <si>
-    <t>C_L01</t>
-  </si>
-  <si>
-    <t>C_L02</t>
-  </si>
-  <si>
-    <t>B_L08</t>
-  </si>
-  <si>
-    <t>B_L09</t>
-  </si>
-  <si>
-    <t>A_L26</t>
-  </si>
-  <si>
-    <t>C_L06</t>
-  </si>
-  <si>
-    <t>A_L16</t>
-  </si>
-  <si>
-    <t>C_L08</t>
-  </si>
-  <si>
-    <t>B_L05</t>
-  </si>
-  <si>
-    <t>C_L14</t>
-  </si>
-  <si>
-    <t>C_L21</t>
-  </si>
-  <si>
-    <t>A_L28</t>
-  </si>
-  <si>
-    <t>C_L18</t>
-  </si>
-  <si>
-    <t>C_L07</t>
-  </si>
-  <si>
-    <t>A_L19</t>
-  </si>
-  <si>
-    <t>B_L01</t>
-  </si>
-  <si>
-    <t>A_L06</t>
-  </si>
-  <si>
-    <t>C_L25</t>
-  </si>
-  <si>
-    <t>A_L14</t>
-  </si>
-  <si>
-    <t>C_L29</t>
-  </si>
-  <si>
-    <t>B_L26</t>
-  </si>
-  <si>
-    <t>C_L11</t>
-  </si>
-  <si>
-    <t>B_L25</t>
-  </si>
-  <si>
-    <t>B_L29</t>
+    <t>B_L18</t>
+  </si>
+  <si>
+    <t>A_L22</t>
+  </si>
+  <si>
+    <t>A_L24</t>
+  </si>
+  <si>
+    <t>A_L01</t>
+  </si>
+  <si>
+    <t>C_L24</t>
   </si>
   <si>
     <t>C_L04</t>
-  </si>
-  <si>
-    <t>A_L21</t>
-  </si>
-  <si>
-    <t>C_L30</t>
-  </si>
-  <si>
-    <t>C_L28</t>
-  </si>
-  <si>
-    <t>B_L02</t>
-  </si>
-  <si>
-    <t>C_L17</t>
-  </si>
-  <si>
-    <t>C_L22</t>
-  </si>
-  <si>
-    <t>B_L04</t>
-  </si>
-  <si>
-    <t>C_L20</t>
-  </si>
-  <si>
-    <t>B_L11</t>
-  </si>
-  <si>
-    <t>A_L18</t>
-  </si>
-  <si>
-    <t>C_L03</t>
-  </si>
-  <si>
-    <t>B_L20</t>
-  </si>
-  <si>
-    <t>A_L09</t>
-  </si>
-  <si>
-    <t>B_L18</t>
-  </si>
-  <si>
-    <t>B_L03</t>
-  </si>
-  <si>
-    <t>B_L07</t>
-  </si>
-  <si>
-    <t>B_L23</t>
-  </si>
-  <si>
-    <t>B_L15</t>
-  </si>
-  <si>
-    <t>A_L07</t>
-  </si>
-  <si>
-    <t>C_L16</t>
-  </si>
-  <si>
-    <t>B_L30</t>
-  </si>
-  <si>
-    <t>A_L02</t>
-  </si>
-  <si>
-    <t>C_L10</t>
-  </si>
-  <si>
-    <t>C_L13</t>
-  </si>
-  <si>
-    <t>A_L03</t>
-  </si>
-  <si>
-    <t>A_L25</t>
-  </si>
-  <si>
-    <t>A_L29</t>
-  </si>
-  <si>
-    <t>A_L17</t>
-  </si>
-  <si>
-    <t>B_L14</t>
-  </si>
-  <si>
-    <t>B_L21</t>
-  </si>
-  <si>
-    <t>A_L23</t>
-  </si>
-  <si>
-    <t>B_L12</t>
-  </si>
-  <si>
-    <t>C_L27</t>
-  </si>
-  <si>
-    <t>A_L13</t>
-  </si>
-  <si>
-    <t>B_L16</t>
-  </si>
-  <si>
-    <t>A_L22</t>
-  </si>
-  <si>
-    <t>A_L24</t>
-  </si>
-  <si>
-    <t>A_L01</t>
-  </si>
-  <si>
-    <t>C_L23</t>
-  </si>
-  <si>
-    <t>C_L05</t>
   </si>
   <si>
     <t>A_L04</t>
@@ -765,37 +765,37 @@
         <v>101</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O2">
         <v>6</v>
@@ -804,19 +804,19 @@
         <v>37</v>
       </c>
       <c r="Q2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S2">
-        <v>6.7</v>
+        <v>5.4</v>
       </c>
       <c r="T2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U2">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="V2">
         <v>4</v>
@@ -833,34 +833,34 @@
         <v>101</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3">
         <v>7</v>
       </c>
       <c r="J3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K3">
         <v>7</v>
       </c>
       <c r="L3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N3">
         <v>7</v>
@@ -869,25 +869,25 @@
         <v>6</v>
       </c>
       <c r="P3">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="Q3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S3">
-        <v>3.7</v>
+        <v>7.8</v>
       </c>
       <c r="T3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="U3">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="V3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -901,34 +901,34 @@
         <v>101</v>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H4">
         <v>3</v>
       </c>
       <c r="I4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K4">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L4">
         <v>5</v>
       </c>
       <c r="M4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N4">
         <v>5</v>
@@ -937,22 +937,22 @@
         <v>6</v>
       </c>
       <c r="P4">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="Q4">
         <v>2</v>
       </c>
       <c r="R4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S4">
-        <v>3</v>
+        <v>5.2</v>
       </c>
       <c r="T4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U4">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="V4">
         <v>4</v>
@@ -972,19 +972,19 @@
         <v>3</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G5">
         <v>3</v>
       </c>
       <c r="H5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J5">
         <v>4</v>
@@ -993,34 +993,34 @@
         <v>3</v>
       </c>
       <c r="L5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O5">
         <v>6</v>
       </c>
       <c r="P5">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="Q5">
         <v>2</v>
       </c>
       <c r="R5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S5">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U5">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="V5">
         <v>3</v>
@@ -1037,28 +1037,28 @@
         <v>102</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J6">
         <v>5</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L6">
         <v>5</v>
@@ -1067,28 +1067,28 @@
         <v>5</v>
       </c>
       <c r="N6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O6">
         <v>6</v>
       </c>
       <c r="P6">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="Q6">
         <v>1</v>
       </c>
       <c r="R6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S6">
-        <v>6.1</v>
+        <v>7.5</v>
       </c>
       <c r="T6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U6">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="V6">
         <v>3</v>
@@ -1105,43 +1105,43 @@
         <v>103</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J7">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O7">
         <v>6</v>
       </c>
       <c r="P7">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="Q7">
         <v>2</v>
@@ -1150,16 +1150,16 @@
         <v>3</v>
       </c>
       <c r="S7">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="T7">
         <v>5</v>
       </c>
       <c r="U7">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="V7">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -1173,61 +1173,61 @@
         <v>103</v>
       </c>
       <c r="D8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E8">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H8">
         <v>6</v>
       </c>
       <c r="I8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J8">
         <v>1</v>
       </c>
       <c r="K8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M8">
         <v>1</v>
       </c>
       <c r="N8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O8">
         <v>6</v>
       </c>
       <c r="P8">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="Q8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R8">
         <v>3</v>
       </c>
       <c r="S8">
-        <v>4.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="T8">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U8">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="V8">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -1241,16 +1241,16 @@
         <v>101</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H9">
         <v>4</v>
@@ -1262,40 +1262,40 @@
         <v>4</v>
       </c>
       <c r="K9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L9">
         <v>7</v>
       </c>
       <c r="M9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O9">
         <v>6</v>
       </c>
       <c r="P9">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="Q9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R9">
         <v>4</v>
       </c>
       <c r="S9">
-        <v>5.6</v>
+        <v>7.9</v>
       </c>
       <c r="T9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U9">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V9">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1309,58 +1309,58 @@
         <v>101</v>
       </c>
       <c r="D10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M10">
         <v>4</v>
       </c>
       <c r="N10">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O10">
         <v>6</v>
       </c>
       <c r="P10">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="Q10">
         <v>1</v>
       </c>
       <c r="R10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S10">
-        <v>4.5</v>
+        <v>6.9</v>
       </c>
       <c r="T10">
         <v>4</v>
       </c>
       <c r="U10">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="V10">
         <v>3</v>
@@ -1377,34 +1377,34 @@
         <v>102</v>
       </c>
       <c r="D11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F11">
         <v>1</v>
       </c>
       <c r="G11">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J11">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M11">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N11">
         <v>6</v>
@@ -1413,22 +1413,22 @@
         <v>6</v>
       </c>
       <c r="P11">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="Q11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S11">
-        <v>4.1</v>
+        <v>6.8</v>
       </c>
       <c r="T11">
         <v>5</v>
       </c>
       <c r="U11">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="V11">
         <v>4</v>
@@ -1445,58 +1445,58 @@
         <v>102</v>
       </c>
       <c r="D12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G12">
         <v>1</v>
       </c>
       <c r="H12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K12">
         <v>6</v>
       </c>
       <c r="L12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M12">
         <v>5</v>
       </c>
       <c r="N12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O12">
         <v>6</v>
       </c>
       <c r="P12">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="Q12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S12">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="T12">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="U12">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V12">
         <v>3</v>
@@ -1516,31 +1516,31 @@
         <v>2</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I13">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J13">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K13">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M13">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N13">
         <v>3</v>
@@ -1549,22 +1549,22 @@
         <v>6</v>
       </c>
       <c r="P13">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="Q13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S13">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="T13">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U13">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="V13">
         <v>3</v>
@@ -1578,46 +1578,46 @@
         <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O14">
         <v>6</v>
       </c>
       <c r="P14">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="Q14">
         <v>1</v>
@@ -1626,16 +1626,16 @@
         <v>3</v>
       </c>
       <c r="S14">
-        <v>3.4</v>
+        <v>6</v>
       </c>
       <c r="T14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="U14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V14">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1649,55 +1649,55 @@
         <v>103</v>
       </c>
       <c r="D15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E15">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F15">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G15">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L15">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M15">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="N15">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O15">
         <v>6</v>
       </c>
       <c r="P15">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="Q15">
         <v>1</v>
       </c>
       <c r="R15">
-        <v>4</v>
-      </c>
-      <c r="S15">
-        <v>2.6</v>
+        <v>5</v>
+      </c>
+      <c r="T15">
+        <v>5</v>
       </c>
       <c r="U15">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="V15">
         <v>2</v>
@@ -1714,28 +1714,28 @@
         <v>102</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16">
         <v>1</v>
       </c>
       <c r="F16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H16">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I16">
         <v>5</v>
       </c>
       <c r="J16">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L16">
         <v>4</v>
@@ -1744,31 +1744,31 @@
         <v>5</v>
       </c>
       <c r="N16">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O16">
         <v>6</v>
       </c>
       <c r="P16">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="Q16">
         <v>2</v>
       </c>
       <c r="R16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S16">
-        <v>13.8</v>
+        <v>2.1</v>
       </c>
       <c r="T16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U16">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="V16">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -1782,37 +1782,37 @@
         <v>102</v>
       </c>
       <c r="D17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E17">
         <v>3</v>
       </c>
       <c r="F17">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G17">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I17">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J17">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L17">
         <v>4</v>
       </c>
       <c r="M17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O17">
         <v>6</v>
@@ -1824,16 +1824,16 @@
         <v>1</v>
       </c>
       <c r="R17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S17">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="T17">
         <v>5</v>
       </c>
       <c r="U17">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="V17">
         <v>3</v>
@@ -1850,10 +1850,10 @@
         <v>101</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18">
         <v>2</v>
@@ -1862,7 +1862,7 @@
         <v>1</v>
       </c>
       <c r="H18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I18">
         <v>7</v>
@@ -1880,31 +1880,31 @@
         <v>5</v>
       </c>
       <c r="N18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O18">
         <v>6</v>
       </c>
       <c r="P18">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="Q18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S18">
-        <v>3.8</v>
+        <v>1.6</v>
       </c>
       <c r="T18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U18">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="V18">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -1918,16 +1918,16 @@
         <v>103</v>
       </c>
       <c r="D19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G19">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H19">
         <v>1</v>
@@ -1936,10 +1936,10 @@
         <v>7</v>
       </c>
       <c r="J19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L19">
         <v>7</v>
@@ -1954,25 +1954,25 @@
         <v>6</v>
       </c>
       <c r="P19">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="Q19">
         <v>1</v>
       </c>
       <c r="R19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S19">
-        <v>4.9</v>
+        <v>11.5</v>
       </c>
       <c r="T19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U19">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="V19">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -1986,58 +1986,58 @@
         <v>101</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F20">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G20">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H20">
         <v>2</v>
       </c>
       <c r="I20">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K20">
         <v>6</v>
       </c>
       <c r="L20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M20">
         <v>5</v>
       </c>
       <c r="N20">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O20">
         <v>6</v>
       </c>
       <c r="P20">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="Q20">
         <v>1</v>
       </c>
       <c r="R20">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S20">
-        <v>1.2</v>
+        <v>3.8</v>
       </c>
       <c r="T20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U20">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="V20">
         <v>3</v>
@@ -2054,61 +2054,61 @@
         <v>103</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21">
         <v>1</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G21">
         <v>3</v>
       </c>
       <c r="H21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I21">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K21">
         <v>4</v>
       </c>
       <c r="L21">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M21">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O21">
         <v>6</v>
       </c>
       <c r="P21">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="Q21">
         <v>1</v>
       </c>
       <c r="R21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S21">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="T21">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U21">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="V21">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H22">
         <v>2</v>
@@ -2143,22 +2143,22 @@
         <v>7</v>
       </c>
       <c r="K22">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L22">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M22">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N22">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O22">
         <v>6</v>
       </c>
       <c r="P22">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="Q22">
         <v>1</v>
@@ -2167,13 +2167,13 @@
         <v>4</v>
       </c>
       <c r="S22">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="T22">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U22">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="V22">
         <v>3</v>
@@ -2190,43 +2190,43 @@
         <v>103</v>
       </c>
       <c r="D23">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E23">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F23">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G23">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H23">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J23">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L23">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N23">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O23">
         <v>6</v>
       </c>
       <c r="P23">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="Q23">
         <v>1</v>
@@ -2235,13 +2235,13 @@
         <v>3</v>
       </c>
       <c r="S23">
-        <v>8.1</v>
+        <v>4.1</v>
       </c>
       <c r="T23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U23">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="V23">
         <v>2</v>
@@ -2258,58 +2258,61 @@
         <v>103</v>
       </c>
       <c r="D24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E24">
         <v>2</v>
       </c>
       <c r="F24">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G24">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I24">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J24">
         <v>7</v>
       </c>
       <c r="K24">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L24">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M24">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N24">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O24">
         <v>6</v>
       </c>
       <c r="P24">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="Q24">
         <v>1</v>
       </c>
       <c r="R24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S24">
-        <v>5.4</v>
+        <v>6.4</v>
+      </c>
+      <c r="T24">
+        <v>5</v>
       </c>
       <c r="U24">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="V24">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -2323,10 +2326,10 @@
         <v>101</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25">
         <v>1</v>
@@ -2341,43 +2344,43 @@
         <v>6</v>
       </c>
       <c r="J25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K25">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L25">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N25">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O25">
         <v>6</v>
       </c>
       <c r="P25">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="Q25">
         <v>2</v>
       </c>
       <c r="R25">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S25">
-        <v>7.7</v>
+        <v>5.9</v>
       </c>
       <c r="T25">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U25">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="V25">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -2397,37 +2400,37 @@
         <v>1</v>
       </c>
       <c r="F26">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G26">
         <v>2</v>
       </c>
       <c r="H26">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J26">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K26">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N26">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O26">
         <v>6</v>
       </c>
       <c r="P26">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="Q26">
         <v>1</v>
@@ -2436,13 +2439,13 @@
         <v>4</v>
       </c>
       <c r="S26">
-        <v>3.6</v>
+        <v>5.2</v>
       </c>
       <c r="T26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U26">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V26">
         <v>4</v>
@@ -2459,22 +2462,22 @@
         <v>103</v>
       </c>
       <c r="D27">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E27">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G27">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H27">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J27">
         <v>2</v>
@@ -2486,7 +2489,7 @@
         <v>2</v>
       </c>
       <c r="M27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N27">
         <v>3</v>
@@ -2495,25 +2498,25 @@
         <v>6</v>
       </c>
       <c r="P27">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="Q27">
         <v>1</v>
       </c>
       <c r="R27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S27">
-        <v>8.9</v>
+        <v>1.8</v>
       </c>
       <c r="T27">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="U27">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="V27">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -2527,10 +2530,10 @@
         <v>101</v>
       </c>
       <c r="D28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F28">
         <v>1</v>
@@ -2542,43 +2545,43 @@
         <v>2</v>
       </c>
       <c r="I28">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K28">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L28">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M28">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N28">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O28">
         <v>6</v>
       </c>
       <c r="P28">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="Q28">
         <v>1</v>
       </c>
       <c r="R28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S28">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="T28">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U28">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="V28">
         <v>4</v>
@@ -2595,61 +2598,61 @@
         <v>102</v>
       </c>
       <c r="D29">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E29">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F29">
         <v>3</v>
       </c>
       <c r="G29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J29">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K29">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L29">
         <v>4</v>
       </c>
       <c r="M29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O29">
         <v>6</v>
       </c>
       <c r="P29">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R29">
         <v>3</v>
       </c>
       <c r="S29">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="T29">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U29">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="V29">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30" spans="1:22">
@@ -2660,7 +2663,7 @@
         <v>50</v>
       </c>
       <c r="C30" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D30">
         <v>1</v>
@@ -2669,55 +2672,55 @@
         <v>1</v>
       </c>
       <c r="F30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I30">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J30">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L30">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M30">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N30">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O30">
         <v>6</v>
       </c>
       <c r="P30">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="Q30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R30">
         <v>4</v>
       </c>
       <c r="S30">
-        <v>8.4</v>
+        <v>7.3</v>
       </c>
       <c r="T30">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="U30">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="V30">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:22">
@@ -2728,7 +2731,7 @@
         <v>51</v>
       </c>
       <c r="C31" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D31">
         <v>1</v>
@@ -2737,31 +2740,31 @@
         <v>1</v>
       </c>
       <c r="F31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K31">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L31">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M31">
         <v>4</v>
       </c>
       <c r="N31">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O31">
         <v>6</v>
@@ -2773,19 +2776,19 @@
         <v>1</v>
       </c>
       <c r="R31">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S31">
-        <v>2.6</v>
+        <v>7.5</v>
       </c>
       <c r="T31">
         <v>4</v>
       </c>
       <c r="U31">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="V31">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:22">
@@ -2796,10 +2799,10 @@
         <v>52</v>
       </c>
       <c r="C32" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D32">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E32">
         <v>1</v>
@@ -2811,46 +2814,46 @@
         <v>2</v>
       </c>
       <c r="H32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I32">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K32">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L32">
         <v>7</v>
       </c>
       <c r="M32">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N32">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O32">
         <v>6</v>
       </c>
       <c r="P32">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="Q32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R32">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S32">
-        <v>5.2</v>
+        <v>6.5</v>
       </c>
       <c r="T32">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U32">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="V32">
         <v>3</v>
@@ -2864,64 +2867,64 @@
         <v>53</v>
       </c>
       <c r="C33" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33">
         <v>2</v>
       </c>
       <c r="G33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H33">
         <v>1</v>
       </c>
       <c r="I33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J33">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L33">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N33">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O33">
         <v>6</v>
       </c>
       <c r="P33">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="Q33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R33">
         <v>3</v>
       </c>
       <c r="S33">
-        <v>4.1</v>
+        <v>2.7</v>
       </c>
       <c r="T33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U33">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="V33">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:22">
@@ -2932,61 +2935,61 @@
         <v>54</v>
       </c>
       <c r="C34" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E34">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F34">
         <v>2</v>
       </c>
       <c r="G34">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H34">
         <v>3</v>
       </c>
       <c r="I34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O34">
         <v>6</v>
       </c>
       <c r="P34">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="Q34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R34">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S34">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="T34">
         <v>6</v>
       </c>
       <c r="U34">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="V34">
         <v>3</v>
@@ -3000,64 +3003,64 @@
         <v>55</v>
       </c>
       <c r="C35" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D35">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E35">
         <v>2</v>
       </c>
       <c r="F35">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G35">
         <v>2</v>
       </c>
       <c r="H35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I35">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J35">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K35">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L35">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M35">
         <v>5</v>
       </c>
       <c r="N35">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O35">
         <v>6</v>
       </c>
       <c r="P35">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="Q35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R35">
         <v>3</v>
       </c>
       <c r="S35">
-        <v>4.4</v>
+        <v>2.7</v>
       </c>
       <c r="T35">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U35">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="V35">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36" spans="1:22">
@@ -3068,64 +3071,64 @@
         <v>56</v>
       </c>
       <c r="C36" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G36">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I36">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J36">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K36">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L36">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M36">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N36">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O36">
         <v>6</v>
       </c>
       <c r="P36">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="Q36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S36">
-        <v>8.5</v>
+        <v>5.2</v>
       </c>
       <c r="T36">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U36">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V36">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:22">
@@ -3139,61 +3142,61 @@
         <v>102</v>
       </c>
       <c r="D37">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F37">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G37">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H37">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I37">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J37">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K37">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L37">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M37">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N37">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O37">
         <v>6</v>
       </c>
       <c r="P37">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="Q37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R37">
         <v>3</v>
       </c>
       <c r="S37">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="T37">
         <v>6</v>
       </c>
       <c r="U37">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="V37">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38" spans="1:22">
@@ -3204,64 +3207,64 @@
         <v>58</v>
       </c>
       <c r="C38" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D38">
         <v>2</v>
       </c>
       <c r="E38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F38">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G38">
         <v>1</v>
       </c>
       <c r="H38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I38">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J38">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K38">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L38">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M38">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N38">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O38">
         <v>6</v>
       </c>
       <c r="P38">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="Q38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S38">
-        <v>3</v>
+        <v>6.9</v>
       </c>
       <c r="T38">
         <v>5</v>
       </c>
       <c r="U38">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="V38">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:22">
@@ -3272,37 +3275,37 @@
         <v>59</v>
       </c>
       <c r="C39" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F39">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H39">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J39">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K39">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L39">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N39">
         <v>7</v>
@@ -3311,22 +3314,22 @@
         <v>6</v>
       </c>
       <c r="P39">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="Q39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R39">
         <v>3</v>
       </c>
       <c r="S39">
-        <v>2.8</v>
+        <v>6.6</v>
       </c>
       <c r="T39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U39">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="V39">
         <v>4</v>
@@ -3340,61 +3343,61 @@
         <v>60</v>
       </c>
       <c r="C40" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E40">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F40">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G40">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H40">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I40">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K40">
         <v>5</v>
       </c>
       <c r="L40">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M40">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N40">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O40">
         <v>6</v>
       </c>
       <c r="P40">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="Q40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R40">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S40">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="T40">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U40">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="V40">
         <v>3</v>
@@ -3411,58 +3414,58 @@
         <v>103</v>
       </c>
       <c r="D41">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E41">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F41">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G41">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H41">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I41">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J41">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K41">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L41">
         <v>7</v>
       </c>
       <c r="M41">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N41">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O41">
         <v>6</v>
       </c>
       <c r="P41">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="Q41">
         <v>1</v>
       </c>
       <c r="R41">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S41">
-        <v>10.2</v>
+        <v>4.6</v>
       </c>
       <c r="T41">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="U41">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="V41">
         <v>4</v>
@@ -3476,46 +3479,46 @@
         <v>62</v>
       </c>
       <c r="C42" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D42">
         <v>1</v>
       </c>
       <c r="E42">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F42">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G42">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H42">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I42">
         <v>6</v>
       </c>
       <c r="J42">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K42">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L42">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M42">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N42">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O42">
         <v>6</v>
       </c>
       <c r="P42">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="Q42">
         <v>1</v>
@@ -3524,16 +3527,16 @@
         <v>4</v>
       </c>
       <c r="S42">
-        <v>5.9</v>
+        <v>2.8</v>
       </c>
       <c r="T42">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U42">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V42">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43" spans="1:22">
@@ -3544,64 +3547,64 @@
         <v>63</v>
       </c>
       <c r="C43" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D43">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E43">
         <v>2</v>
       </c>
       <c r="F43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G43">
         <v>1</v>
       </c>
       <c r="H43">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I43">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J43">
         <v>7</v>
       </c>
       <c r="K43">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L43">
         <v>6</v>
       </c>
       <c r="M43">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N43">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O43">
         <v>6</v>
       </c>
       <c r="P43">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="Q43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R43">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S43">
-        <v>2.1</v>
+        <v>4.9</v>
       </c>
       <c r="T43">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U43">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="V43">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44" spans="1:22">
@@ -3615,16 +3618,16 @@
         <v>103</v>
       </c>
       <c r="D44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G44">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H44">
         <v>3</v>
@@ -3633,25 +3636,25 @@
         <v>7</v>
       </c>
       <c r="J44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K44">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L44">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M44">
         <v>5</v>
       </c>
       <c r="N44">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O44">
         <v>6</v>
       </c>
       <c r="P44">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="Q44">
         <v>2</v>
@@ -3660,16 +3663,16 @@
         <v>5</v>
       </c>
       <c r="S44">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="T44">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U44">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="V44">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45" spans="1:22">
@@ -3680,64 +3683,64 @@
         <v>65</v>
       </c>
       <c r="C45" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D45">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E45">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F45">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G45">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H45">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I45">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J45">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K45">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L45">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M45">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N45">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O45">
         <v>6</v>
       </c>
       <c r="P45">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="Q45">
         <v>2</v>
       </c>
       <c r="R45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S45">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="T45">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U45">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V45">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46" spans="1:22">
@@ -3748,13 +3751,13 @@
         <v>66</v>
       </c>
       <c r="C46" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E46">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F46">
         <v>3</v>
@@ -3763,49 +3766,49 @@
         <v>4</v>
       </c>
       <c r="H46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I46">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J46">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K46">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L46">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M46">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O46">
         <v>6</v>
       </c>
       <c r="P46">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="Q46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R46">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S46">
-        <v>12</v>
+        <v>3.9</v>
       </c>
       <c r="T46">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U46">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="V46">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:22">
@@ -3819,10 +3822,10 @@
         <v>102</v>
       </c>
       <c r="D47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E47">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F47">
         <v>2</v>
@@ -3831,46 +3834,46 @@
         <v>3</v>
       </c>
       <c r="H47">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I47">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J47">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K47">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L47">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M47">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N47">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O47">
         <v>6</v>
       </c>
       <c r="P47">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="Q47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R47">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S47">
-        <v>10.6</v>
+        <v>4.2</v>
       </c>
       <c r="T47">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U47">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="V47">
         <v>3</v>
@@ -3887,16 +3890,16 @@
         <v>101</v>
       </c>
       <c r="D48">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F48">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H48">
         <v>1</v>
@@ -3905,10 +3908,10 @@
         <v>7</v>
       </c>
       <c r="J48">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K48">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L48">
         <v>7</v>
@@ -3917,28 +3920,25 @@
         <v>7</v>
       </c>
       <c r="N48">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O48">
         <v>6</v>
       </c>
       <c r="P48">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="Q48">
         <v>2</v>
       </c>
       <c r="R48">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S48">
-        <v>6.7</v>
-      </c>
-      <c r="T48">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U48">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="V48">
         <v>3</v>
@@ -3955,34 +3955,34 @@
         <v>103</v>
       </c>
       <c r="D49">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F49">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G49">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H49">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I49">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J49">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K49">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L49">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M49">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N49">
         <v>5</v>
@@ -3991,25 +3991,25 @@
         <v>6</v>
       </c>
       <c r="P49">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="Q49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R49">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S49">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="T49">
         <v>4</v>
       </c>
       <c r="U49">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="V49">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50" spans="1:22">
@@ -4023,10 +4023,10 @@
         <v>102</v>
       </c>
       <c r="D50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E50">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F50">
         <v>2</v>
@@ -4038,46 +4038,46 @@
         <v>1</v>
       </c>
       <c r="I50">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J50">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K50">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L50">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M50">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N50">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O50">
         <v>6</v>
       </c>
       <c r="P50">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R50">
         <v>3</v>
       </c>
       <c r="S50">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="T50">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U50">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="V50">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51" spans="1:22">
@@ -4091,55 +4091,55 @@
         <v>101</v>
       </c>
       <c r="D51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F51">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H51">
         <v>1</v>
       </c>
       <c r="I51">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J51">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K51">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L51">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M51">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N51">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O51">
         <v>6</v>
       </c>
       <c r="P51">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="Q51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S51">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="T51">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U51">
         <v>9</v>
@@ -4159,43 +4159,43 @@
         <v>102</v>
       </c>
       <c r="D52">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E52">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F52">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G52">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H52">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I52">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J52">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K52">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L52">
         <v>5</v>
       </c>
       <c r="M52">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N52">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O52">
         <v>6</v>
       </c>
       <c r="P52">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="Q52">
         <v>1</v>
@@ -4204,13 +4204,13 @@
         <v>3</v>
       </c>
       <c r="S52">
-        <v>9.6</v>
+        <v>3.4</v>
       </c>
       <c r="T52">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U52">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="V52">
         <v>3</v>
@@ -4227,61 +4227,61 @@
         <v>102</v>
       </c>
       <c r="D53">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G53">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H53">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I53">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J53">
         <v>4</v>
       </c>
       <c r="K53">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L53">
         <v>5</v>
       </c>
       <c r="M53">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N53">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O53">
         <v>6</v>
       </c>
       <c r="P53">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="Q53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R53">
         <v>3</v>
       </c>
       <c r="S53">
-        <v>10.3</v>
+        <v>7.9</v>
       </c>
       <c r="T53">
+        <v>6</v>
+      </c>
+      <c r="U53">
         <v>8</v>
       </c>
-      <c r="U53">
-        <v>17</v>
-      </c>
       <c r="V53">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54" spans="1:22">
@@ -4295,61 +4295,61 @@
         <v>102</v>
       </c>
       <c r="D54">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E54">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F54">
         <v>1</v>
       </c>
       <c r="G54">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I54">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J54">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K54">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L54">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M54">
         <v>5</v>
       </c>
       <c r="N54">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O54">
         <v>6</v>
       </c>
       <c r="P54">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="Q54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R54">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S54">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="T54">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U54">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V54">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55" spans="1:22">
@@ -4363,43 +4363,43 @@
         <v>102</v>
       </c>
       <c r="D55">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E55">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F55">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G55">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H55">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J55">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K55">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L55">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M55">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N55">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O55">
         <v>6</v>
       </c>
       <c r="P55">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="Q55">
         <v>1</v>
@@ -4408,13 +4408,10 @@
         <v>3</v>
       </c>
       <c r="S55">
-        <v>3.3</v>
-      </c>
-      <c r="T55">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="U55">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="V55">
         <v>4</v>
@@ -4431,34 +4428,34 @@
         <v>102</v>
       </c>
       <c r="D56">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G56">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H56">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I56">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J56">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K56">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L56">
         <v>6</v>
       </c>
       <c r="M56">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N56">
         <v>7</v>
@@ -4467,25 +4464,25 @@
         <v>6</v>
       </c>
       <c r="P56">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="Q56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R56">
         <v>3</v>
       </c>
       <c r="S56">
-        <v>6.6</v>
+        <v>2.8</v>
       </c>
       <c r="T56">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U56">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="V56">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57" spans="1:22">
@@ -4499,61 +4496,61 @@
         <v>101</v>
       </c>
       <c r="D57">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E57">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F57">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G57">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H57">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I57">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J57">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K57">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L57">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M57">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N57">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O57">
         <v>6</v>
       </c>
       <c r="P57">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="Q57">
         <v>1</v>
       </c>
       <c r="R57">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S57">
-        <v>7</v>
+        <v>3.2</v>
       </c>
       <c r="T57">
         <v>8</v>
       </c>
       <c r="U57">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="V57">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58" spans="1:22">
@@ -4567,61 +4564,61 @@
         <v>103</v>
       </c>
       <c r="D58">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F58">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G58">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H58">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I58">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J58">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K58">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L58">
         <v>3</v>
       </c>
       <c r="M58">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N58">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O58">
         <v>6</v>
       </c>
       <c r="P58">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="Q58">
         <v>2</v>
       </c>
       <c r="R58">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S58">
-        <v>3</v>
+        <v>11.9</v>
       </c>
       <c r="T58">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U58">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="V58">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59" spans="1:22">
@@ -4635,43 +4632,43 @@
         <v>102</v>
       </c>
       <c r="D59">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E59">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F59">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G59">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H59">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I59">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J59">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K59">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L59">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M59">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N59">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O59">
         <v>6</v>
       </c>
       <c r="P59">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="Q59">
         <v>1</v>
@@ -4680,16 +4677,16 @@
         <v>3</v>
       </c>
       <c r="S59">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="T59">
         <v>4</v>
       </c>
       <c r="U59">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="V59">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60" spans="1:22">
@@ -4703,31 +4700,31 @@
         <v>101</v>
       </c>
       <c r="D60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F60">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G60">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H60">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I60">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J60">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K60">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L60">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M60">
         <v>6</v>
@@ -4739,7 +4736,7 @@
         <v>6</v>
       </c>
       <c r="P60">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="Q60">
         <v>2</v>
@@ -4748,16 +4745,16 @@
         <v>3</v>
       </c>
       <c r="S60">
-        <v>9.4</v>
+        <v>3.2</v>
       </c>
       <c r="T60">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U60">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="V60">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61" spans="1:22">
@@ -4771,58 +4768,58 @@
         <v>103</v>
       </c>
       <c r="D61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E61">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F61">
         <v>3</v>
       </c>
       <c r="G61">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H61">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I61">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J61">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K61">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L61">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M61">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N61">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O61">
         <v>6</v>
       </c>
       <c r="P61">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="Q61">
         <v>1</v>
       </c>
       <c r="R61">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S61">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="T61">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U61">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V61">
         <v>3</v>
@@ -4839,22 +4836,22 @@
         <v>103</v>
       </c>
       <c r="D62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E62">
         <v>1</v>
       </c>
       <c r="F62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I62">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J62">
         <v>7</v>
@@ -4863,7 +4860,7 @@
         <v>7</v>
       </c>
       <c r="L62">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M62">
         <v>7</v>
@@ -4875,25 +4872,25 @@
         <v>6</v>
       </c>
       <c r="P62">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="Q62">
         <v>1</v>
       </c>
       <c r="R62">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S62">
-        <v>6.4</v>
+        <v>3.6</v>
       </c>
       <c r="T62">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U62">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="V62">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63" spans="1:22">
@@ -4910,31 +4907,31 @@
         <v>3</v>
       </c>
       <c r="E63">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F63">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G63">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I63">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J63">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K63">
         <v>4</v>
       </c>
       <c r="L63">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M63">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N63">
         <v>2</v>
@@ -4949,19 +4946,19 @@
         <v>1</v>
       </c>
       <c r="R63">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S63">
-        <v>3.6</v>
+        <v>9.1</v>
       </c>
       <c r="T63">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U63">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="V63">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64" spans="1:22">
@@ -4978,55 +4975,58 @@
         <v>4</v>
       </c>
       <c r="E64">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F64">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G64">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H64">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I64">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J64">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K64">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L64">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M64">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N64">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O64">
         <v>6</v>
       </c>
+      <c r="P64">
+        <v>33</v>
+      </c>
       <c r="Q64">
         <v>2</v>
       </c>
       <c r="R64">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S64">
-        <v>2.9</v>
+        <v>8</v>
       </c>
       <c r="T64">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U64">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="V64">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65" spans="1:22">
@@ -5040,61 +5040,61 @@
         <v>101</v>
       </c>
       <c r="D65">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E65">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F65">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H65">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I65">
         <v>3</v>
       </c>
       <c r="J65">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K65">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L65">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M65">
         <v>4</v>
       </c>
       <c r="N65">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O65">
         <v>6</v>
       </c>
       <c r="P65">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="Q65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R65">
         <v>3</v>
       </c>
       <c r="S65">
-        <v>7.9</v>
+        <v>2.7</v>
       </c>
       <c r="T65">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U65">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V65">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66" spans="1:22">
@@ -5108,58 +5108,58 @@
         <v>101</v>
       </c>
       <c r="D66">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E66">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F66">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G66">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H66">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I66">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J66">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K66">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L66">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M66">
         <v>4</v>
       </c>
       <c r="N66">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O66">
         <v>6</v>
       </c>
       <c r="P66">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="Q66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R66">
         <v>4</v>
       </c>
       <c r="S66">
-        <v>7.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="T66">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="U66">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="V66">
         <v>3</v>
@@ -5176,7 +5176,7 @@
         <v>102</v>
       </c>
       <c r="D67">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E67">
         <v>1</v>
@@ -5185,49 +5185,49 @@
         <v>2</v>
       </c>
       <c r="G67">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H67">
         <v>2</v>
       </c>
       <c r="I67">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J67">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K67">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L67">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M67">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N67">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O67">
         <v>6</v>
       </c>
       <c r="P67">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="Q67">
         <v>1</v>
       </c>
       <c r="R67">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S67">
-        <v>3.6</v>
+        <v>8</v>
       </c>
       <c r="T67">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U67">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="V67">
         <v>4</v>
@@ -5244,34 +5244,34 @@
         <v>102</v>
       </c>
       <c r="D68">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E68">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F68">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G68">
         <v>3</v>
       </c>
       <c r="H68">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I68">
         <v>4</v>
       </c>
       <c r="J68">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K68">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L68">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M68">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N68">
         <v>4</v>
@@ -5280,22 +5280,22 @@
         <v>6</v>
       </c>
       <c r="P68">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="Q68">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R68">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S68">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="T68">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U68">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="V68">
         <v>3</v>
@@ -5315,31 +5315,31 @@
         <v>2</v>
       </c>
       <c r="E69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F69">
         <v>1</v>
       </c>
       <c r="G69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H69">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I69">
         <v>5</v>
       </c>
       <c r="J69">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K69">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L69">
         <v>4</v>
       </c>
       <c r="M69">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N69">
         <v>4</v>
@@ -5348,22 +5348,22 @@
         <v>6</v>
       </c>
       <c r="P69">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="Q69">
         <v>1</v>
       </c>
       <c r="R69">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S69">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="T69">
         <v>3</v>
       </c>
       <c r="U69">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="V69">
         <v>3</v>
@@ -5380,61 +5380,61 @@
         <v>102</v>
       </c>
       <c r="D70">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F70">
         <v>1</v>
       </c>
       <c r="G70">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H70">
         <v>1</v>
       </c>
       <c r="I70">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J70">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K70">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L70">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M70">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N70">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O70">
         <v>6</v>
       </c>
       <c r="P70">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="Q70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R70">
         <v>5</v>
       </c>
       <c r="S70">
-        <v>12</v>
+        <v>2.1</v>
       </c>
       <c r="T70">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U70">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="V70">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71" spans="1:22">
@@ -5448,7 +5448,7 @@
         <v>103</v>
       </c>
       <c r="D71">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E71">
         <v>1</v>
@@ -5460,22 +5460,22 @@
         <v>1</v>
       </c>
       <c r="H71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I71">
         <v>4</v>
       </c>
       <c r="J71">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K71">
         <v>6</v>
       </c>
       <c r="L71">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M71">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N71">
         <v>5</v>
@@ -5484,22 +5484,22 @@
         <v>6</v>
       </c>
       <c r="P71">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Q71">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R71">
         <v>4</v>
       </c>
       <c r="S71">
-        <v>3</v>
+        <v>6.3</v>
       </c>
       <c r="T71">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U71">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V71">
         <v>3</v>
@@ -5522,31 +5522,31 @@
         <v>3</v>
       </c>
       <c r="F72">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G72">
         <v>2</v>
       </c>
       <c r="H72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I72">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J72">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K72">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L72">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M72">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N72">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O72">
         <v>6</v>
@@ -5555,22 +5555,22 @@
         <v>44</v>
       </c>
       <c r="Q72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R72">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S72">
-        <v>3.4</v>
+        <v>5.4</v>
       </c>
       <c r="T72">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U72">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="V72">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:22">
@@ -5584,58 +5584,58 @@
         <v>102</v>
       </c>
       <c r="D73">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E73">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F73">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G73">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H73">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I73">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J73">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K73">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L73">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M73">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N73">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O73">
         <v>6</v>
       </c>
       <c r="P73">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="Q73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R73">
         <v>3</v>
       </c>
       <c r="S73">
-        <v>7.6</v>
+        <v>10.6</v>
       </c>
       <c r="T73">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U73">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="V73">
         <v>3</v>
@@ -5652,58 +5652,58 @@
         <v>101</v>
       </c>
       <c r="D74">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F74">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H74">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I74">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J74">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K74">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L74">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M74">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N74">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O74">
         <v>6</v>
       </c>
       <c r="P74">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="Q74">
         <v>2</v>
       </c>
       <c r="R74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S74">
-        <v>2.2</v>
+        <v>3.7</v>
       </c>
       <c r="T74">
         <v>3</v>
       </c>
       <c r="U74">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="V74">
         <v>4</v>
@@ -5720,61 +5720,61 @@
         <v>101</v>
       </c>
       <c r="D75">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G75">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H75">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I75">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J75">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K75">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L75">
         <v>7</v>
       </c>
       <c r="M75">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N75">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O75">
         <v>6</v>
       </c>
       <c r="P75">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="Q75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R75">
         <v>3</v>
       </c>
       <c r="S75">
-        <v>5.1</v>
+        <v>2.2</v>
       </c>
       <c r="T75">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U75">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V75">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76" spans="1:22">
@@ -5788,58 +5788,58 @@
         <v>101</v>
       </c>
       <c r="D76">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E76">
         <v>3</v>
       </c>
       <c r="F76">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G76">
         <v>2</v>
       </c>
       <c r="H76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I76">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J76">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K76">
         <v>3</v>
       </c>
       <c r="L76">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M76">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N76">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O76">
         <v>6</v>
       </c>
       <c r="P76">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="Q76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R76">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>5.1</v>
+        <v>8.5</v>
       </c>
       <c r="T76">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U76">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="V76">
         <v>3</v>
@@ -5856,58 +5856,58 @@
         <v>103</v>
       </c>
       <c r="D77">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E77">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F77">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G77">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H77">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I77">
         <v>4</v>
       </c>
       <c r="J77">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K77">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L77">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M77">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N77">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O77">
         <v>6</v>
       </c>
       <c r="P77">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="Q77">
         <v>1</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S77">
-        <v>3.7</v>
+        <v>2.4</v>
       </c>
       <c r="T77">
         <v>5</v>
       </c>
       <c r="U77">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="V77">
         <v>4</v>
@@ -5930,25 +5930,25 @@
         <v>1</v>
       </c>
       <c r="F78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G78">
         <v>3</v>
       </c>
       <c r="H78">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I78">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J78">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K78">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L78">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M78">
         <v>6</v>
@@ -5960,25 +5960,25 @@
         <v>6</v>
       </c>
       <c r="P78">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="Q78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R78">
         <v>4</v>
       </c>
       <c r="S78">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T78">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U78">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="V78">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79" spans="1:22">
@@ -5992,52 +5992,52 @@
         <v>101</v>
       </c>
       <c r="D79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E79">
         <v>3</v>
       </c>
       <c r="F79">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G79">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H79">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I79">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J79">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K79">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L79">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M79">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N79">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O79">
         <v>6</v>
       </c>
       <c r="P79">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="Q79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R79">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S79">
-        <v>9.1</v>
+        <v>6.1</v>
       </c>
       <c r="T79">
         <v>7</v>
@@ -6046,7 +6046,7 @@
         <v>10</v>
       </c>
       <c r="V79">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80" spans="1:22">
@@ -6060,22 +6060,22 @@
         <v>101</v>
       </c>
       <c r="D80">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E80">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F80">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G80">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H80">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I80">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J80">
         <v>5</v>
@@ -6084,37 +6084,37 @@
         <v>4</v>
       </c>
       <c r="L80">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M80">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N80">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O80">
         <v>6</v>
       </c>
       <c r="P80">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="Q80">
         <v>1</v>
       </c>
       <c r="R80">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S80">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="T80">
         <v>5</v>
       </c>
       <c r="U80">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="V80">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/data/T3_leader_cleaned.xlsx
+++ b/data/T3_leader_cleaned.xlsx
@@ -82,241 +82,241 @@
     <t>LeaderJobLevel</t>
   </si>
   <si>
+    <t>A_L14</t>
+  </si>
+  <si>
+    <t>A_L20</t>
+  </si>
+  <si>
+    <t>A_L08</t>
+  </si>
+  <si>
+    <t>B_L11</t>
+  </si>
+  <si>
+    <t>B_L07</t>
+  </si>
+  <si>
+    <t>C_L20</t>
+  </si>
+  <si>
+    <t>C_L26</t>
+  </si>
+  <si>
+    <t>A_L11</t>
+  </si>
+  <si>
+    <t>A_L10</t>
+  </si>
+  <si>
+    <t>B_L26</t>
+  </si>
+  <si>
+    <t>B_L24</t>
+  </si>
+  <si>
+    <t>C_L13</t>
+  </si>
+  <si>
+    <t>C_L02</t>
+  </si>
+  <si>
+    <t>C_L03</t>
+  </si>
+  <si>
+    <t>B_L09</t>
+  </si>
+  <si>
+    <t>B_L10</t>
+  </si>
+  <si>
+    <t>A_L26</t>
+  </si>
+  <si>
+    <t>C_L08</t>
+  </si>
+  <si>
+    <t>A_L16</t>
+  </si>
+  <si>
+    <t>C_L10</t>
+  </si>
+  <si>
+    <t>B_L06</t>
+  </si>
+  <si>
+    <t>C_L16</t>
+  </si>
+  <si>
+    <t>C_L22</t>
+  </si>
+  <si>
+    <t>A_L29</t>
+  </si>
+  <si>
+    <t>C_L19</t>
+  </si>
+  <si>
+    <t>C_L09</t>
+  </si>
+  <si>
+    <t>A_L19</t>
+  </si>
+  <si>
+    <t>B_L02</t>
+  </si>
+  <si>
+    <t>A_L05</t>
+  </si>
+  <si>
+    <t>C_L25</t>
+  </si>
+  <si>
     <t>A_L13</t>
   </si>
   <si>
+    <t>C_L29</t>
+  </si>
+  <si>
+    <t>B_L29</t>
+  </si>
+  <si>
+    <t>C_L12</t>
+  </si>
+  <si>
+    <t>B_L27</t>
+  </si>
+  <si>
+    <t>B_L30</t>
+  </si>
+  <si>
+    <t>C_L06</t>
+  </si>
+  <si>
+    <t>A_L21</t>
+  </si>
+  <si>
+    <t>C_L30</t>
+  </si>
+  <si>
+    <t>C_L28</t>
+  </si>
+  <si>
+    <t>B_L03</t>
+  </si>
+  <si>
+    <t>C_L18</t>
+  </si>
+  <si>
+    <t>C_L23</t>
+  </si>
+  <si>
+    <t>B_L05</t>
+  </si>
+  <si>
+    <t>C_L21</t>
+  </si>
+  <si>
+    <t>B_L12</t>
+  </si>
+  <si>
     <t>A_L18</t>
   </si>
   <si>
+    <t>C_L05</t>
+  </si>
+  <si>
+    <t>B_L20</t>
+  </si>
+  <si>
+    <t>A_L09</t>
+  </si>
+  <si>
+    <t>B_L19</t>
+  </si>
+  <si>
+    <t>B_L04</t>
+  </si>
+  <si>
+    <t>B_L08</t>
+  </si>
+  <si>
+    <t>B_L25</t>
+  </si>
+  <si>
+    <t>B_L16</t>
+  </si>
+  <si>
     <t>A_L07</t>
   </si>
   <si>
-    <t>B_L10</t>
-  </si>
-  <si>
-    <t>B_L06</t>
-  </si>
-  <si>
-    <t>C_L18</t>
-  </si>
-  <si>
-    <t>C_L26</t>
-  </si>
-  <si>
-    <t>A_L10</t>
-  </si>
-  <si>
-    <t>A_L09</t>
-  </si>
-  <si>
-    <t>B_L24</t>
-  </si>
-  <si>
-    <t>B_L22</t>
+    <t>C_L17</t>
+  </si>
+  <si>
+    <t>C_L01</t>
+  </si>
+  <si>
+    <t>A_L02</t>
   </si>
   <si>
     <t>C_L11</t>
   </si>
   <si>
-    <t>B_L30</t>
-  </si>
-  <si>
-    <t>C_L01</t>
-  </si>
-  <si>
-    <t>B_L08</t>
-  </si>
-  <si>
-    <t>B_L09</t>
-  </si>
-  <si>
-    <t>A_L26</t>
-  </si>
-  <si>
-    <t>C_L06</t>
-  </si>
-  <si>
-    <t>A_L14</t>
-  </si>
-  <si>
-    <t>C_L08</t>
-  </si>
-  <si>
-    <t>B_L05</t>
-  </si>
-  <si>
-    <t>C_L13</t>
-  </si>
-  <si>
-    <t>C_L22</t>
+    <t>C_L14</t>
+  </si>
+  <si>
+    <t>A_L03</t>
+  </si>
+  <si>
+    <t>A_L25</t>
+  </si>
+  <si>
+    <t>B_L01</t>
+  </si>
+  <si>
+    <t>A_L17</t>
+  </si>
+  <si>
+    <t>B_L15</t>
+  </si>
+  <si>
+    <t>B_L21</t>
+  </si>
+  <si>
+    <t>A_L23</t>
+  </si>
+  <si>
+    <t>B_L14</t>
+  </si>
+  <si>
+    <t>C_L27</t>
+  </si>
+  <si>
+    <t>A_L12</t>
+  </si>
+  <si>
+    <t>B_L18</t>
+  </si>
+  <si>
+    <t>A_L22</t>
+  </si>
+  <si>
+    <t>A_L24</t>
+  </si>
+  <si>
+    <t>A_L01</t>
+  </si>
+  <si>
+    <t>C_L24</t>
+  </si>
+  <si>
+    <t>C_L07</t>
+  </si>
+  <si>
+    <t>A_L04</t>
   </si>
   <si>
     <t>A_L28</t>
-  </si>
-  <si>
-    <t>C_L17</t>
-  </si>
-  <si>
-    <t>C_L07</t>
-  </si>
-  <si>
-    <t>A_L17</t>
-  </si>
-  <si>
-    <t>B_L01</t>
-  </si>
-  <si>
-    <t>C_L21</t>
-  </si>
-  <si>
-    <t>A_L05</t>
-  </si>
-  <si>
-    <t>C_L25</t>
-  </si>
-  <si>
-    <t>A_L12</t>
-  </si>
-  <si>
-    <t>C_L29</t>
-  </si>
-  <si>
-    <t>B_L26</t>
-  </si>
-  <si>
-    <t>C_L10</t>
-  </si>
-  <si>
-    <t>B_L25</t>
-  </si>
-  <si>
-    <t>B_L27</t>
-  </si>
-  <si>
-    <t>C_L03</t>
-  </si>
-  <si>
-    <t>A_L19</t>
-  </si>
-  <si>
-    <t>C_L30</t>
-  </si>
-  <si>
-    <t>C_L28</t>
-  </si>
-  <si>
-    <t>B_L02</t>
-  </si>
-  <si>
-    <t>C_L16</t>
-  </si>
-  <si>
-    <t>C_L23</t>
-  </si>
-  <si>
-    <t>B_L04</t>
-  </si>
-  <si>
-    <t>B_L11</t>
-  </si>
-  <si>
-    <t>A_L16</t>
-  </si>
-  <si>
-    <t>C_L02</t>
-  </si>
-  <si>
-    <t>B_L20</t>
-  </si>
-  <si>
-    <t>A_L08</t>
-  </si>
-  <si>
-    <t>B_L19</t>
-  </si>
-  <si>
-    <t>B_L03</t>
-  </si>
-  <si>
-    <t>B_L07</t>
-  </si>
-  <si>
-    <t>B_L23</t>
-  </si>
-  <si>
-    <t>B_L16</t>
-  </si>
-  <si>
-    <t>A_L06</t>
-  </si>
-  <si>
-    <t>C_L14</t>
-  </si>
-  <si>
-    <t>B_L29</t>
-  </si>
-  <si>
-    <t>A_L02</t>
-  </si>
-  <si>
-    <t>C_L09</t>
-  </si>
-  <si>
-    <t>C_L12</t>
-  </si>
-  <si>
-    <t>A_L03</t>
-  </si>
-  <si>
-    <t>A_L25</t>
-  </si>
-  <si>
-    <t>A_L29</t>
-  </si>
-  <si>
-    <t>A_L15</t>
-  </si>
-  <si>
-    <t>B_L14</t>
-  </si>
-  <si>
-    <t>B_L21</t>
-  </si>
-  <si>
-    <t>A_L23</t>
-  </si>
-  <si>
-    <t>B_L12</t>
-  </si>
-  <si>
-    <t>C_L27</t>
-  </si>
-  <si>
-    <t>A_L11</t>
-  </si>
-  <si>
-    <t>B_L18</t>
-  </si>
-  <si>
-    <t>A_L22</t>
-  </si>
-  <si>
-    <t>A_L24</t>
-  </si>
-  <si>
-    <t>A_L01</t>
-  </si>
-  <si>
-    <t>C_L24</t>
-  </si>
-  <si>
-    <t>C_L04</t>
-  </si>
-  <si>
-    <t>A_L04</t>
-  </si>
-  <si>
-    <t>A_L27</t>
   </si>
   <si>
     <t>A</t>
@@ -765,43 +765,43 @@
         <v>101</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O2">
         <v>6</v>
       </c>
       <c r="P2">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="Q2">
         <v>2</v>
@@ -810,16 +810,16 @@
         <v>3</v>
       </c>
       <c r="S2">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="T2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U2">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="V2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -833,7 +833,7 @@
         <v>101</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -842,25 +842,25 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3">
         <v>7</v>
       </c>
       <c r="J3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K3">
         <v>7</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N3">
         <v>7</v>
@@ -869,7 +869,7 @@
         <v>6</v>
       </c>
       <c r="P3">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="Q3">
         <v>1</v>
@@ -878,16 +878,16 @@
         <v>3</v>
       </c>
       <c r="S3">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="T3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U3">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="V3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -901,13 +901,13 @@
         <v>101</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G4">
         <v>3</v>
@@ -916,19 +916,19 @@
         <v>3</v>
       </c>
       <c r="I4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K4">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M4">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N4">
         <v>5</v>
@@ -937,7 +937,7 @@
         <v>6</v>
       </c>
       <c r="P4">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="Q4">
         <v>2</v>
@@ -946,16 +946,16 @@
         <v>4</v>
       </c>
       <c r="S4">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="T4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U4">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="V4">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -972,55 +972,55 @@
         <v>3</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G5">
         <v>3</v>
       </c>
       <c r="H5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I5">
         <v>5</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K5">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O5">
         <v>6</v>
       </c>
       <c r="P5">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="Q5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S5">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="T5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U5">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="V5">
         <v>3</v>
@@ -1040,58 +1040,58 @@
         <v>2</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G6">
         <v>3</v>
       </c>
       <c r="H6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O6">
         <v>6</v>
       </c>
       <c r="P6">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q6">
         <v>1</v>
       </c>
       <c r="R6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S6">
-        <v>7.5</v>
+        <v>7.9</v>
       </c>
       <c r="T6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U6">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="V6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -1105,49 +1105,49 @@
         <v>103</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N7">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O7">
         <v>6</v>
       </c>
       <c r="P7">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Q7">
         <v>2</v>
       </c>
       <c r="R7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S7">
         <v>4</v>
@@ -1156,10 +1156,10 @@
         <v>5</v>
       </c>
       <c r="U7">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="V7">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -1173,61 +1173,61 @@
         <v>103</v>
       </c>
       <c r="D8">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I8">
         <v>1</v>
       </c>
       <c r="J8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L8">
         <v>1</v>
       </c>
       <c r="M8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O8">
         <v>6</v>
       </c>
       <c r="P8">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="Q8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S8">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="T8">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U8">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="V8">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -1241,34 +1241,34 @@
         <v>101</v>
       </c>
       <c r="D9">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E9">
         <v>2</v>
       </c>
       <c r="F9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H9">
         <v>4</v>
       </c>
       <c r="I9">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J9">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K9">
         <v>5</v>
       </c>
       <c r="L9">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N9">
         <v>4</v>
@@ -1277,22 +1277,22 @@
         <v>6</v>
       </c>
       <c r="P9">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="Q9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S9">
-        <v>7.9</v>
+        <v>6</v>
       </c>
       <c r="T9">
         <v>6</v>
       </c>
       <c r="U9">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="V9">
         <v>3</v>
@@ -1312,55 +1312,55 @@
         <v>3</v>
       </c>
       <c r="E10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H10">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J10">
         <v>5</v>
       </c>
       <c r="K10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L10">
         <v>6</v>
       </c>
       <c r="M10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N10">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O10">
         <v>6</v>
       </c>
       <c r="P10">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="Q10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R10">
         <v>3</v>
       </c>
       <c r="S10">
-        <v>6.9</v>
+        <v>12.9</v>
       </c>
       <c r="T10">
         <v>4</v>
       </c>
       <c r="U10">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="V10">
         <v>3</v>
@@ -1377,28 +1377,28 @@
         <v>102</v>
       </c>
       <c r="D11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I11">
         <v>5</v>
       </c>
       <c r="J11">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L11">
         <v>4</v>
@@ -1407,31 +1407,31 @@
         <v>4</v>
       </c>
       <c r="N11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O11">
         <v>6</v>
       </c>
       <c r="P11">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="Q11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S11">
-        <v>6.8</v>
+        <v>4.8</v>
       </c>
       <c r="T11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U11">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="V11">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1445,37 +1445,37 @@
         <v>102</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F12">
         <v>1</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H12">
         <v>2</v>
       </c>
       <c r="I12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J12">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K12">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M12">
         <v>5</v>
       </c>
       <c r="N12">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O12">
         <v>6</v>
@@ -1487,13 +1487,13 @@
         <v>1</v>
       </c>
       <c r="R12">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S12">
         <v>2.3</v>
       </c>
       <c r="T12">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="U12">
         <v>14</v>
@@ -1516,40 +1516,40 @@
         <v>2</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G13">
         <v>3</v>
       </c>
       <c r="H13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I13">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J13">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K13">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L13">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M13">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="N13">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O13">
         <v>6</v>
       </c>
       <c r="P13">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="Q13">
         <v>2</v>
@@ -1558,16 +1558,16 @@
         <v>3</v>
       </c>
       <c r="S13">
-        <v>3.5</v>
+        <v>8.4</v>
       </c>
       <c r="T13">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U13">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V13">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -1578,37 +1578,37 @@
         <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D14">
         <v>3</v>
       </c>
       <c r="E14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H14">
         <v>4</v>
       </c>
       <c r="I14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N14">
         <v>5</v>
@@ -1617,7 +1617,7 @@
         <v>6</v>
       </c>
       <c r="P14">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="Q14">
         <v>1</v>
@@ -1626,16 +1626,16 @@
         <v>3</v>
       </c>
       <c r="S14">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U14">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="V14">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1655,52 +1655,55 @@
         <v>1</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K15">
         <v>5</v>
       </c>
       <c r="L15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N15">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O15">
         <v>6</v>
       </c>
       <c r="P15">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="Q15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R15">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="S15">
+        <v>4.2</v>
       </c>
       <c r="T15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U15">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="V15">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -1714,31 +1717,31 @@
         <v>102</v>
       </c>
       <c r="D16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G16">
         <v>3</v>
       </c>
       <c r="H16">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L16">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M16">
         <v>5</v>
@@ -1750,25 +1753,25 @@
         <v>6</v>
       </c>
       <c r="P16">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="Q16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S16">
-        <v>2.1</v>
+        <v>4.3</v>
       </c>
       <c r="T16">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U16">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="V16">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -1782,61 +1785,61 @@
         <v>102</v>
       </c>
       <c r="D17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G17">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H17">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I17">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J17">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K17">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L17">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M17">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O17">
         <v>6</v>
       </c>
       <c r="P17">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="Q17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S17">
-        <v>4.5</v>
+        <v>1.2</v>
       </c>
       <c r="T17">
         <v>5</v>
       </c>
       <c r="U17">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="V17">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -1850,34 +1853,34 @@
         <v>101</v>
       </c>
       <c r="D18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I18">
         <v>7</v>
       </c>
       <c r="J18">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K18">
         <v>6</v>
       </c>
       <c r="L18">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N18">
         <v>5</v>
@@ -1886,7 +1889,7 @@
         <v>6</v>
       </c>
       <c r="P18">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q18">
         <v>2</v>
@@ -1895,10 +1898,10 @@
         <v>3</v>
       </c>
       <c r="S18">
-        <v>1.6</v>
+        <v>6</v>
       </c>
       <c r="T18">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U18">
         <v>19</v>
@@ -1918,7 +1921,7 @@
         <v>103</v>
       </c>
       <c r="D19">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E19">
         <v>3</v>
@@ -1927,34 +1930,34 @@
         <v>2</v>
       </c>
       <c r="G19">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I19">
         <v>7</v>
       </c>
       <c r="J19">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K19">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L19">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O19">
         <v>6</v>
       </c>
       <c r="P19">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Q19">
         <v>1</v>
@@ -1963,13 +1966,13 @@
         <v>4</v>
       </c>
       <c r="S19">
-        <v>11.5</v>
+        <v>8.9</v>
       </c>
       <c r="T19">
         <v>4</v>
       </c>
       <c r="U19">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="V19">
         <v>3</v>
@@ -1986,22 +1989,22 @@
         <v>101</v>
       </c>
       <c r="D20">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F20">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G20">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H20">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I20">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J20">
         <v>7</v>
@@ -2010,28 +2013,28 @@
         <v>6</v>
       </c>
       <c r="L20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M20">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N20">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O20">
         <v>6</v>
       </c>
       <c r="P20">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="Q20">
         <v>1</v>
       </c>
       <c r="R20">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S20">
-        <v>3.8</v>
+        <v>6.8</v>
       </c>
       <c r="T20">
         <v>5</v>
@@ -2060,55 +2063,55 @@
         <v>1</v>
       </c>
       <c r="F21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G21">
         <v>3</v>
       </c>
       <c r="H21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K21">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L21">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N21">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O21">
         <v>6</v>
       </c>
       <c r="P21">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="Q21">
         <v>1</v>
       </c>
       <c r="R21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S21">
-        <v>2.6</v>
+        <v>15.1</v>
       </c>
       <c r="T21">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U21">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="V21">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -2125,55 +2128,55 @@
         <v>1</v>
       </c>
       <c r="E22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I22">
         <v>5</v>
       </c>
       <c r="J22">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L22">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N22">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O22">
         <v>6</v>
       </c>
       <c r="P22">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Q22">
         <v>1</v>
       </c>
       <c r="R22">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S22">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="T22">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U22">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="V22">
         <v>3</v>
@@ -2190,31 +2193,31 @@
         <v>103</v>
       </c>
       <c r="D23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E23">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G23">
         <v>5</v>
       </c>
       <c r="H23">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I23">
         <v>7</v>
       </c>
       <c r="J23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K23">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L23">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M23">
         <v>7</v>
@@ -2226,25 +2229,25 @@
         <v>6</v>
       </c>
       <c r="P23">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Q23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R23">
         <v>3</v>
       </c>
       <c r="S23">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T23">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U23">
         <v>14</v>
       </c>
       <c r="V23">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -2258,37 +2261,37 @@
         <v>103</v>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F24">
         <v>2</v>
       </c>
       <c r="G24">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I24">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J24">
         <v>7</v>
       </c>
       <c r="K24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L24">
         <v>6</v>
       </c>
       <c r="M24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O24">
         <v>6</v>
@@ -2297,22 +2300,22 @@
         <v>37</v>
       </c>
       <c r="Q24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R24">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S24">
-        <v>6.4</v>
+        <v>3.2</v>
       </c>
       <c r="T24">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U24">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="V24">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -2332,52 +2335,52 @@
         <v>2</v>
       </c>
       <c r="F25">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G25">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H25">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I25">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J25">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K25">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L25">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M25">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N25">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O25">
         <v>6</v>
       </c>
       <c r="P25">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="Q25">
         <v>2</v>
       </c>
       <c r="R25">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S25">
-        <v>5.9</v>
+        <v>9</v>
       </c>
       <c r="T25">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U25">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="V25">
         <v>3</v>
@@ -2397,31 +2400,31 @@
         <v>1</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F26">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H26">
         <v>1</v>
       </c>
       <c r="I26">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K26">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L26">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M26">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N26">
         <v>5</v>
@@ -2430,25 +2433,25 @@
         <v>6</v>
       </c>
       <c r="P26">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="Q26">
         <v>1</v>
       </c>
       <c r="R26">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S26">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="T26">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U26">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="V26">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -2462,43 +2465,43 @@
         <v>103</v>
       </c>
       <c r="D27">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H27">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I27">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J27">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K27">
         <v>4</v>
       </c>
       <c r="L27">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M27">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O27">
         <v>6</v>
       </c>
       <c r="P27">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="Q27">
         <v>1</v>
@@ -2507,16 +2510,16 @@
         <v>2</v>
       </c>
       <c r="S27">
-        <v>1.8</v>
+        <v>4.6</v>
       </c>
       <c r="T27">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="U27">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="V27">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -2530,7 +2533,7 @@
         <v>101</v>
       </c>
       <c r="D28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E28">
         <v>3</v>
@@ -2539,13 +2542,13 @@
         <v>1</v>
       </c>
       <c r="G28">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I28">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J28">
         <v>6</v>
@@ -2554,34 +2557,34 @@
         <v>4</v>
       </c>
       <c r="L28">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M28">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O28">
         <v>6</v>
       </c>
       <c r="P28">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="Q28">
         <v>1</v>
       </c>
       <c r="R28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S28">
-        <v>5.9</v>
+        <v>8.4</v>
       </c>
       <c r="T28">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U28">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="V28">
         <v>4</v>
@@ -2598,37 +2601,37 @@
         <v>102</v>
       </c>
       <c r="D29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F29">
         <v>3</v>
       </c>
       <c r="G29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H29">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I29">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J29">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K29">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L29">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M29">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O29">
         <v>6</v>
@@ -2637,22 +2640,22 @@
         <v>45</v>
       </c>
       <c r="Q29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R29">
         <v>3</v>
       </c>
       <c r="S29">
-        <v>2.3</v>
+        <v>4.8</v>
       </c>
       <c r="T29">
         <v>4</v>
       </c>
       <c r="U29">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="V29">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:22">
@@ -2663,61 +2666,61 @@
         <v>50</v>
       </c>
       <c r="C30" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D30">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F30">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H30">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I30">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J30">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K30">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M30">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N30">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O30">
         <v>6</v>
       </c>
       <c r="P30">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="Q30">
         <v>1</v>
       </c>
       <c r="R30">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S30">
-        <v>7.3</v>
+        <v>5.7</v>
       </c>
       <c r="T30">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U30">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="V30">
         <v>3</v>
@@ -2731,37 +2734,37 @@
         <v>51</v>
       </c>
       <c r="C31" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F31">
         <v>1</v>
       </c>
       <c r="G31">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I31">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J31">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K31">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L31">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M31">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N31">
         <v>5</v>
@@ -2770,22 +2773,22 @@
         <v>6</v>
       </c>
       <c r="P31">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="Q31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S31">
-        <v>7.5</v>
+        <v>2.2</v>
       </c>
       <c r="T31">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U31">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="V31">
         <v>2</v>
@@ -2799,19 +2802,19 @@
         <v>52</v>
       </c>
       <c r="C32" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F32">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H32">
         <v>2</v>
@@ -2823,37 +2826,37 @@
         <v>7</v>
       </c>
       <c r="K32">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M32">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N32">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O32">
         <v>6</v>
       </c>
       <c r="P32">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="Q32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R32">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S32">
-        <v>6.5</v>
+        <v>3.3</v>
       </c>
       <c r="T32">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U32">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="V32">
         <v>3</v>
@@ -2867,13 +2870,13 @@
         <v>53</v>
       </c>
       <c r="C33" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F33">
         <v>2</v>
@@ -2885,43 +2888,43 @@
         <v>1</v>
       </c>
       <c r="I33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J33">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K33">
         <v>7</v>
       </c>
       <c r="L33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M33">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N33">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O33">
         <v>6</v>
       </c>
       <c r="P33">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="Q33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R33">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S33">
-        <v>2.7</v>
+        <v>5.1</v>
       </c>
       <c r="T33">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U33">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="V33">
         <v>3</v>
@@ -2935,46 +2938,46 @@
         <v>54</v>
       </c>
       <c r="C34" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F34">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G34">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H34">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I34">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J34">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K34">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M34">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N34">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O34">
         <v>6</v>
       </c>
       <c r="P34">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Q34">
         <v>2</v>
@@ -2983,16 +2986,16 @@
         <v>3</v>
       </c>
       <c r="S34">
-        <v>3.6</v>
+        <v>1.7</v>
       </c>
       <c r="T34">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U34">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="V34">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35" spans="1:22">
@@ -3003,34 +3006,34 @@
         <v>55</v>
       </c>
       <c r="C35" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E35">
         <v>2</v>
       </c>
       <c r="F35">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J35">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M35">
         <v>5</v>
@@ -3042,25 +3045,25 @@
         <v>6</v>
       </c>
       <c r="P35">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="Q35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S35">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="T35">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U35">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="V35">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:22">
@@ -3071,64 +3074,64 @@
         <v>56</v>
       </c>
       <c r="C36" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D36">
         <v>3</v>
       </c>
       <c r="E36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F36">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G36">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H36">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I36">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J36">
         <v>7</v>
       </c>
       <c r="K36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L36">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M36">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N36">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O36">
         <v>6</v>
       </c>
       <c r="P36">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="Q36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R36">
         <v>3</v>
       </c>
       <c r="S36">
-        <v>5.2</v>
+        <v>3.4</v>
       </c>
       <c r="T36">
         <v>5</v>
       </c>
       <c r="U36">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="V36">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:22">
@@ -3145,13 +3148,13 @@
         <v>1</v>
       </c>
       <c r="E37">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H37">
         <v>2</v>
@@ -3160,43 +3163,43 @@
         <v>4</v>
       </c>
       <c r="J37">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K37">
         <v>7</v>
       </c>
       <c r="L37">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M37">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N37">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O37">
         <v>6</v>
       </c>
       <c r="P37">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R37">
         <v>3</v>
       </c>
       <c r="S37">
-        <v>2.6</v>
+        <v>4.5</v>
       </c>
       <c r="T37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U37">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="V37">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38" spans="1:22">
@@ -3207,64 +3210,64 @@
         <v>58</v>
       </c>
       <c r="C38" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E38">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F38">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G38">
         <v>1</v>
       </c>
       <c r="H38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I38">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J38">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L38">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M38">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N38">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O38">
         <v>6</v>
       </c>
       <c r="P38">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="Q38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S38">
-        <v>6.9</v>
+        <v>2.6</v>
       </c>
       <c r="T38">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U38">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="V38">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39" spans="1:22">
@@ -3275,46 +3278,46 @@
         <v>59</v>
       </c>
       <c r="C39" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E39">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F39">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G39">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I39">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J39">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K39">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L39">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M39">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N39">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O39">
         <v>6</v>
       </c>
       <c r="P39">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="Q39">
         <v>1</v>
@@ -3323,16 +3326,16 @@
         <v>3</v>
       </c>
       <c r="S39">
-        <v>6.6</v>
+        <v>2.4</v>
       </c>
       <c r="T39">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U39">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="V39">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40" spans="1:22">
@@ -3343,10 +3346,10 @@
         <v>60</v>
       </c>
       <c r="C40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D40">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E40">
         <v>5</v>
@@ -3355,7 +3358,7 @@
         <v>4</v>
       </c>
       <c r="G40">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H40">
         <v>3</v>
@@ -3364,43 +3367,43 @@
         <v>3</v>
       </c>
       <c r="J40">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K40">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L40">
         <v>3</v>
       </c>
       <c r="M40">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N40">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O40">
         <v>6</v>
       </c>
       <c r="P40">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="Q40">
         <v>1</v>
       </c>
       <c r="R40">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S40">
-        <v>3.1</v>
+        <v>13.7</v>
       </c>
       <c r="T40">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U40">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V40">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41" spans="1:22">
@@ -3414,58 +3417,58 @@
         <v>103</v>
       </c>
       <c r="D41">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E41">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F41">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G41">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H41">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I41">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J41">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K41">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L41">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N41">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O41">
         <v>6</v>
       </c>
       <c r="P41">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="Q41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R41">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S41">
-        <v>4.6</v>
+        <v>2.6</v>
       </c>
       <c r="T41">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U41">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="V41">
         <v>4</v>
@@ -3479,16 +3482,16 @@
         <v>62</v>
       </c>
       <c r="C42" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E42">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F42">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G42">
         <v>3</v>
@@ -3497,28 +3500,28 @@
         <v>2</v>
       </c>
       <c r="I42">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J42">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K42">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L42">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M42">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N42">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O42">
         <v>6</v>
       </c>
       <c r="P42">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="Q42">
         <v>1</v>
@@ -3527,16 +3530,16 @@
         <v>4</v>
       </c>
       <c r="S42">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="T42">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U42">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="V42">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43" spans="1:22">
@@ -3547,19 +3550,19 @@
         <v>63</v>
       </c>
       <c r="C43" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D43">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E43">
         <v>2</v>
       </c>
       <c r="F43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G43">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H43">
         <v>2</v>
@@ -3571,40 +3574,40 @@
         <v>7</v>
       </c>
       <c r="K43">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L43">
         <v>6</v>
       </c>
       <c r="M43">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N43">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O43">
         <v>6</v>
       </c>
       <c r="P43">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="Q43">
         <v>2</v>
       </c>
       <c r="R43">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S43">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="T43">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U43">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="V43">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44" spans="1:22">
@@ -3618,13 +3621,13 @@
         <v>103</v>
       </c>
       <c r="D44">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E44">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F44">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G44">
         <v>3</v>
@@ -3633,43 +3636,43 @@
         <v>3</v>
       </c>
       <c r="I44">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J44">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K44">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L44">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M44">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N44">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O44">
         <v>6</v>
       </c>
       <c r="P44">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="Q44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R44">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S44">
-        <v>6.4</v>
+        <v>5</v>
       </c>
       <c r="T44">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U44">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="V44">
         <v>3</v>
@@ -3683,64 +3686,64 @@
         <v>65</v>
       </c>
       <c r="C45" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D45">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G45">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H45">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I45">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J45">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K45">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L45">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M45">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N45">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O45">
         <v>6</v>
       </c>
       <c r="P45">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="Q45">
         <v>2</v>
       </c>
       <c r="R45">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S45">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="T45">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U45">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="V45">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46" spans="1:22">
@@ -3751,64 +3754,61 @@
         <v>66</v>
       </c>
       <c r="C46" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D46">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E46">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F46">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G46">
         <v>4</v>
       </c>
       <c r="H46">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I46">
         <v>4</v>
       </c>
       <c r="J46">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K46">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L46">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M46">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N46">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O46">
         <v>6</v>
       </c>
       <c r="P46">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="Q46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R46">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S46">
-        <v>3.9</v>
-      </c>
-      <c r="T46">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U46">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="V46">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47" spans="1:22">
@@ -3825,55 +3825,55 @@
         <v>1</v>
       </c>
       <c r="E47">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G47">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H47">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I47">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J47">
         <v>6</v>
       </c>
       <c r="K47">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L47">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M47">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N47">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O47">
         <v>6</v>
       </c>
       <c r="P47">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="Q47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R47">
         <v>3</v>
       </c>
       <c r="S47">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="T47">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U47">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="V47">
         <v>3</v>
@@ -3890,34 +3890,34 @@
         <v>101</v>
       </c>
       <c r="D48">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F48">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G48">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I48">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J48">
         <v>6</v>
       </c>
       <c r="K48">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L48">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M48">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N48">
         <v>5</v>
@@ -3926,22 +3926,25 @@
         <v>6</v>
       </c>
       <c r="P48">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="Q48">
         <v>2</v>
       </c>
       <c r="R48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S48">
-        <v>6</v>
+        <v>2.9</v>
+      </c>
+      <c r="T48">
+        <v>4</v>
       </c>
       <c r="U48">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="V48">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49" spans="1:22">
@@ -3958,58 +3961,58 @@
         <v>3</v>
       </c>
       <c r="E49">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F49">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G49">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H49">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K49">
         <v>4</v>
       </c>
       <c r="L49">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M49">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N49">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O49">
         <v>6</v>
       </c>
       <c r="P49">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="Q49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S49">
-        <v>5.1</v>
+        <v>8</v>
       </c>
       <c r="T49">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U49">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="V49">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50" spans="1:22">
@@ -4023,19 +4026,19 @@
         <v>102</v>
       </c>
       <c r="D50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E50">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F50">
         <v>2</v>
       </c>
       <c r="G50">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I50">
         <v>7</v>
@@ -4044,22 +4047,22 @@
         <v>7</v>
       </c>
       <c r="K50">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L50">
         <v>7</v>
       </c>
       <c r="M50">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N50">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O50">
         <v>6</v>
       </c>
       <c r="P50">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Q50">
         <v>1</v>
@@ -4068,13 +4071,13 @@
         <v>3</v>
       </c>
       <c r="S50">
-        <v>8.4</v>
+        <v>6</v>
       </c>
       <c r="T50">
         <v>4</v>
       </c>
       <c r="U50">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="V50">
         <v>3</v>
@@ -4091,34 +4094,34 @@
         <v>101</v>
       </c>
       <c r="D51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E51">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H51">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I51">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J51">
         <v>6</v>
       </c>
       <c r="K51">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L51">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M51">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N51">
         <v>7</v>
@@ -4127,25 +4130,25 @@
         <v>6</v>
       </c>
       <c r="P51">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="Q51">
         <v>1</v>
       </c>
       <c r="R51">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S51">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="T51">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U51">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="V51">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52" spans="1:22">
@@ -4159,28 +4162,28 @@
         <v>102</v>
       </c>
       <c r="D52">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E52">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F52">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G52">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H52">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I52">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J52">
         <v>5</v>
       </c>
       <c r="K52">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L52">
         <v>5</v>
@@ -4189,13 +4192,13 @@
         <v>5</v>
       </c>
       <c r="N52">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O52">
         <v>6</v>
       </c>
       <c r="P52">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="Q52">
         <v>1</v>
@@ -4204,16 +4207,16 @@
         <v>3</v>
       </c>
       <c r="S52">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="T52">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U52">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="V52">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53" spans="1:22">
@@ -4227,31 +4230,31 @@
         <v>102</v>
       </c>
       <c r="D53">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E53">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F53">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G53">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H53">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I53">
         <v>5</v>
       </c>
       <c r="J53">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K53">
         <v>5</v>
       </c>
       <c r="L53">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M53">
         <v>4</v>
@@ -4263,25 +4266,25 @@
         <v>6</v>
       </c>
       <c r="P53">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="Q53">
         <v>2</v>
       </c>
       <c r="R53">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S53">
-        <v>7.9</v>
+        <v>2.9</v>
       </c>
       <c r="T53">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U53">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="V53">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54" spans="1:22">
@@ -4295,61 +4298,61 @@
         <v>102</v>
       </c>
       <c r="D54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E54">
         <v>1</v>
       </c>
       <c r="F54">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H54">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I54">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J54">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K54">
         <v>6</v>
       </c>
       <c r="L54">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M54">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N54">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O54">
         <v>6</v>
       </c>
       <c r="P54">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="Q54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R54">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S54">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T54">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U54">
         <v>19</v>
       </c>
       <c r="V54">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55" spans="1:22">
@@ -4363,55 +4366,58 @@
         <v>102</v>
       </c>
       <c r="D55">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E55">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G55">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H55">
         <v>3</v>
       </c>
       <c r="I55">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J55">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K55">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L55">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M55">
         <v>3</v>
       </c>
       <c r="N55">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O55">
         <v>6</v>
       </c>
       <c r="P55">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="Q55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R55">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S55">
-        <v>2</v>
+        <v>8.5</v>
+      </c>
+      <c r="T55">
+        <v>6</v>
       </c>
       <c r="U55">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="V55">
         <v>4</v>
@@ -4428,13 +4434,13 @@
         <v>102</v>
       </c>
       <c r="D56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E56">
         <v>1</v>
       </c>
       <c r="F56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G56">
         <v>1</v>
@@ -4443,46 +4449,43 @@
         <v>3</v>
       </c>
       <c r="I56">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J56">
         <v>6</v>
       </c>
       <c r="K56">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L56">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M56">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N56">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O56">
         <v>6</v>
       </c>
-      <c r="P56">
-        <v>41</v>
-      </c>
       <c r="Q56">
         <v>2</v>
       </c>
       <c r="R56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S56">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="T56">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U56">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="V56">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57" spans="1:22">
@@ -4496,61 +4499,61 @@
         <v>101</v>
       </c>
       <c r="D57">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E57">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F57">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G57">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H57">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I57">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J57">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K57">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L57">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M57">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N57">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O57">
         <v>6</v>
       </c>
       <c r="P57">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="Q57">
         <v>1</v>
       </c>
       <c r="R57">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S57">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="T57">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="U57">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="V57">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58" spans="1:22">
@@ -4564,61 +4567,61 @@
         <v>103</v>
       </c>
       <c r="D58">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F58">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G58">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H58">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I58">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J58">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K58">
         <v>5</v>
       </c>
       <c r="L58">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M58">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N58">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O58">
         <v>6</v>
       </c>
       <c r="P58">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="Q58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R58">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S58">
-        <v>11.9</v>
+        <v>3.7</v>
       </c>
       <c r="T58">
         <v>8</v>
       </c>
       <c r="U58">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="V58">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59" spans="1:22">
@@ -4629,46 +4632,46 @@
         <v>79</v>
       </c>
       <c r="C59" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D59">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E59">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F59">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G59">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H59">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I59">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J59">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K59">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L59">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M59">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N59">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O59">
         <v>6</v>
       </c>
       <c r="P59">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="Q59">
         <v>1</v>
@@ -4677,16 +4680,16 @@
         <v>3</v>
       </c>
       <c r="S59">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="T59">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U59">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="V59">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60" spans="1:22">
@@ -4703,31 +4706,31 @@
         <v>2</v>
       </c>
       <c r="E60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F60">
         <v>4</v>
       </c>
       <c r="G60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H60">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I60">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J60">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K60">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L60">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M60">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N60">
         <v>7</v>
@@ -4739,22 +4742,22 @@
         <v>36</v>
       </c>
       <c r="Q60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R60">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S60">
-        <v>3.2</v>
+        <v>5.9</v>
       </c>
       <c r="T60">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U60">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="V60">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:22">
@@ -4768,61 +4771,61 @@
         <v>103</v>
       </c>
       <c r="D61">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E61">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F61">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G61">
         <v>3</v>
       </c>
       <c r="H61">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I61">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J61">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K61">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L61">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M61">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N61">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O61">
         <v>6</v>
       </c>
       <c r="P61">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="Q61">
         <v>1</v>
       </c>
       <c r="R61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S61">
-        <v>3.4</v>
+        <v>7.7</v>
       </c>
       <c r="T61">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="U61">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="V61">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62" spans="1:22">
@@ -4836,58 +4839,58 @@
         <v>103</v>
       </c>
       <c r="D62">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E62">
         <v>1</v>
       </c>
       <c r="F62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G62">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H62">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I62">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J62">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K62">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L62">
         <v>4</v>
       </c>
       <c r="M62">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N62">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O62">
         <v>6</v>
       </c>
       <c r="P62">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="Q62">
         <v>1</v>
       </c>
       <c r="R62">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S62">
-        <v>3.6</v>
+        <v>6</v>
       </c>
       <c r="T62">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U62">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="V62">
         <v>4</v>
@@ -4904,31 +4907,31 @@
         <v>101</v>
       </c>
       <c r="D63">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E63">
         <v>4</v>
       </c>
       <c r="F63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G63">
         <v>3</v>
       </c>
       <c r="H63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I63">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J63">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K63">
         <v>4</v>
       </c>
       <c r="L63">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M63">
         <v>3</v>
@@ -4940,25 +4943,25 @@
         <v>6</v>
       </c>
       <c r="P63">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="Q63">
         <v>1</v>
       </c>
       <c r="R63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S63">
-        <v>9.1</v>
+        <v>3.1</v>
       </c>
       <c r="T63">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U63">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="V63">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64" spans="1:22">
@@ -4972,61 +4975,61 @@
         <v>101</v>
       </c>
       <c r="D64">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E64">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F64">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G64">
         <v>4</v>
       </c>
       <c r="H64">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I64">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J64">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K64">
         <v>3</v>
       </c>
       <c r="L64">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M64">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N64">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O64">
         <v>6</v>
       </c>
       <c r="P64">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="Q64">
         <v>2</v>
       </c>
       <c r="R64">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S64">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="T64">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U64">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V64">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65" spans="1:22">
@@ -5037,37 +5040,37 @@
         <v>85</v>
       </c>
       <c r="C65" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D65">
         <v>1</v>
       </c>
       <c r="E65">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F65">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G65">
         <v>3</v>
       </c>
       <c r="H65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J65">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K65">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L65">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M65">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N65">
         <v>5</v>
@@ -5076,7 +5079,7 @@
         <v>6</v>
       </c>
       <c r="P65">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="Q65">
         <v>1</v>
@@ -5085,16 +5088,16 @@
         <v>3</v>
       </c>
       <c r="S65">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="T65">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U65">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="V65">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66" spans="1:22">
@@ -5108,34 +5111,34 @@
         <v>101</v>
       </c>
       <c r="D66">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E66">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F66">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G66">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H66">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I66">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J66">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K66">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L66">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M66">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N66">
         <v>3</v>
@@ -5144,22 +5147,22 @@
         <v>6</v>
       </c>
       <c r="P66">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="Q66">
         <v>2</v>
       </c>
       <c r="R66">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S66">
-        <v>8.800000000000001</v>
+        <v>1.9</v>
       </c>
       <c r="T66">
         <v>7</v>
       </c>
       <c r="U66">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="V66">
         <v>3</v>
@@ -5176,61 +5179,61 @@
         <v>102</v>
       </c>
       <c r="D67">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E67">
         <v>1</v>
       </c>
       <c r="F67">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G67">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H67">
         <v>2</v>
       </c>
       <c r="I67">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J67">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K67">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L67">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M67">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N67">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O67">
         <v>6</v>
       </c>
       <c r="P67">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="Q67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R67">
         <v>3</v>
       </c>
       <c r="S67">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="T67">
         <v>7</v>
       </c>
       <c r="U67">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="V67">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68" spans="1:22">
@@ -5244,61 +5247,61 @@
         <v>102</v>
       </c>
       <c r="D68">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E68">
         <v>1</v>
       </c>
       <c r="F68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G68">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H68">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I68">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J68">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K68">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L68">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M68">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N68">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O68">
         <v>6</v>
       </c>
       <c r="P68">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="Q68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R68">
         <v>4</v>
       </c>
       <c r="S68">
-        <v>3.8</v>
+        <v>6.6</v>
       </c>
       <c r="T68">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U68">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="V68">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69" spans="1:22">
@@ -5312,61 +5315,61 @@
         <v>101</v>
       </c>
       <c r="D69">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E69">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F69">
         <v>1</v>
       </c>
       <c r="G69">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H69">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I69">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J69">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K69">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L69">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M69">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N69">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O69">
         <v>6</v>
       </c>
       <c r="P69">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="Q69">
         <v>1</v>
       </c>
       <c r="R69">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S69">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="T69">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="U69">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="V69">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70" spans="1:22">
@@ -5380,31 +5383,31 @@
         <v>102</v>
       </c>
       <c r="D70">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F70">
         <v>1</v>
       </c>
       <c r="G70">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I70">
         <v>6</v>
       </c>
       <c r="J70">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K70">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L70">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M70">
         <v>5</v>
@@ -5416,25 +5419,25 @@
         <v>6</v>
       </c>
       <c r="P70">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="Q70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R70">
         <v>5</v>
       </c>
       <c r="S70">
-        <v>2.1</v>
+        <v>13.9</v>
       </c>
       <c r="T70">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U70">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="V70">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="71" spans="1:22">
@@ -5451,7 +5454,7 @@
         <v>1</v>
       </c>
       <c r="E71">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F71">
         <v>1</v>
@@ -5460,46 +5463,46 @@
         <v>1</v>
       </c>
       <c r="H71">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I71">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J71">
         <v>7</v>
       </c>
       <c r="K71">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L71">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M71">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N71">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O71">
         <v>6</v>
       </c>
       <c r="P71">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="Q71">
         <v>1</v>
       </c>
       <c r="R71">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S71">
-        <v>6.3</v>
+        <v>4.4</v>
       </c>
       <c r="T71">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U71">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="V71">
         <v>3</v>
@@ -5519,58 +5522,58 @@
         <v>1</v>
       </c>
       <c r="E72">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F72">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H72">
         <v>1</v>
       </c>
       <c r="I72">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J72">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K72">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L72">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M72">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N72">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O72">
         <v>6</v>
       </c>
       <c r="P72">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Q72">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R72">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S72">
-        <v>5.4</v>
+        <v>2.9</v>
       </c>
       <c r="T72">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U72">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="V72">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73" spans="1:22">
@@ -5587,58 +5590,55 @@
         <v>5</v>
       </c>
       <c r="E73">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F73">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G73">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H73">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I73">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J73">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K73">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L73">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M73">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N73">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O73">
         <v>6</v>
       </c>
       <c r="P73">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="Q73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R73">
         <v>3</v>
       </c>
-      <c r="S73">
-        <v>10.6</v>
-      </c>
       <c r="T73">
         <v>4</v>
       </c>
       <c r="U73">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="V73">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74" spans="1:22">
@@ -5655,58 +5655,58 @@
         <v>2</v>
       </c>
       <c r="E74">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F74">
         <v>4</v>
       </c>
       <c r="G74">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H74">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I74">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J74">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K74">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L74">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M74">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O74">
         <v>6</v>
       </c>
       <c r="P74">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="Q74">
         <v>2</v>
       </c>
       <c r="R74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S74">
-        <v>3.7</v>
+        <v>8</v>
       </c>
       <c r="T74">
         <v>3</v>
       </c>
       <c r="U74">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="V74">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75" spans="1:22">
@@ -5720,10 +5720,10 @@
         <v>101</v>
       </c>
       <c r="D75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F75">
         <v>1</v>
@@ -5741,22 +5741,22 @@
         <v>6</v>
       </c>
       <c r="K75">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L75">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M75">
         <v>4</v>
       </c>
       <c r="N75">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O75">
         <v>6</v>
       </c>
       <c r="P75">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="Q75">
         <v>1</v>
@@ -5765,16 +5765,16 @@
         <v>3</v>
       </c>
       <c r="S75">
-        <v>2.2</v>
+        <v>11</v>
       </c>
       <c r="T75">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U75">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="V75">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76" spans="1:22">
@@ -5788,52 +5788,52 @@
         <v>101</v>
       </c>
       <c r="D76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F76">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G76">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J76">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K76">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L76">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M76">
         <v>5</v>
       </c>
       <c r="N76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O76">
         <v>6</v>
       </c>
       <c r="P76">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="Q76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S76">
-        <v>8.5</v>
+        <v>4.7</v>
       </c>
       <c r="T76">
         <v>6</v>
@@ -5856,43 +5856,43 @@
         <v>103</v>
       </c>
       <c r="D77">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E77">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F77">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G77">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H77">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I77">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J77">
         <v>3</v>
       </c>
       <c r="K77">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L77">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M77">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N77">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O77">
         <v>6</v>
       </c>
       <c r="P77">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="Q77">
         <v>1</v>
@@ -5901,13 +5901,13 @@
         <v>2</v>
       </c>
       <c r="S77">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="T77">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U77">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V77">
         <v>4</v>
@@ -5924,25 +5924,25 @@
         <v>103</v>
       </c>
       <c r="D78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F78">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G78">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H78">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I78">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J78">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K78">
         <v>3</v>
@@ -5951,34 +5951,34 @@
         <v>7</v>
       </c>
       <c r="M78">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N78">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O78">
         <v>6</v>
       </c>
       <c r="P78">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R78">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S78">
-        <v>15</v>
+        <v>4.7</v>
       </c>
       <c r="T78">
         <v>5</v>
       </c>
       <c r="U78">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="V78">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79" spans="1:22">
@@ -5992,22 +5992,22 @@
         <v>101</v>
       </c>
       <c r="D79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E79">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F79">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G79">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H79">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I79">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J79">
         <v>4</v>
@@ -6016,37 +6016,37 @@
         <v>5</v>
       </c>
       <c r="L79">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M79">
         <v>5</v>
       </c>
       <c r="N79">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O79">
         <v>6</v>
       </c>
       <c r="P79">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Q79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R79">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S79">
-        <v>6.1</v>
+        <v>4.9</v>
       </c>
       <c r="T79">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U79">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="V79">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80" spans="1:22">
@@ -6060,34 +6060,34 @@
         <v>101</v>
       </c>
       <c r="D80">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E80">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F80">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G80">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H80">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I80">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J80">
         <v>5</v>
       </c>
       <c r="K80">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L80">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M80">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N80">
         <v>7</v>
@@ -6096,25 +6096,25 @@
         <v>6</v>
       </c>
       <c r="P80">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="Q80">
         <v>1</v>
       </c>
       <c r="R80">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S80">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="T80">
         <v>5</v>
       </c>
       <c r="U80">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="V80">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/data/T3_leader_cleaned.xlsx
+++ b/data/T3_leader_cleaned.xlsx
@@ -82,241 +82,241 @@
     <t>LeaderJobLevel</t>
   </si>
   <si>
+    <t>A_L13</t>
+  </si>
+  <si>
+    <t>A_L18</t>
+  </si>
+  <si>
+    <t>A_L07</t>
+  </si>
+  <si>
+    <t>B_L11</t>
+  </si>
+  <si>
+    <t>B_L07</t>
+  </si>
+  <si>
+    <t>C_L19</t>
+  </si>
+  <si>
+    <t>C_L26</t>
+  </si>
+  <si>
+    <t>A_L10</t>
+  </si>
+  <si>
+    <t>A_L09</t>
+  </si>
+  <si>
+    <t>B_L26</t>
+  </si>
+  <si>
+    <t>B_L24</t>
+  </si>
+  <si>
+    <t>C_L12</t>
+  </si>
+  <si>
+    <t>C_L02</t>
+  </si>
+  <si>
+    <t>C_L03</t>
+  </si>
+  <si>
+    <t>B_L09</t>
+  </si>
+  <si>
+    <t>B_L10</t>
+  </si>
+  <si>
+    <t>A_L25</t>
+  </si>
+  <si>
+    <t>C_L07</t>
+  </si>
+  <si>
     <t>A_L14</t>
   </si>
   <si>
+    <t>C_L09</t>
+  </si>
+  <si>
+    <t>B_L06</t>
+  </si>
+  <si>
+    <t>C_L14</t>
+  </si>
+  <si>
+    <t>C_L21</t>
+  </si>
+  <si>
+    <t>A_L28</t>
+  </si>
+  <si>
+    <t>C_L18</t>
+  </si>
+  <si>
+    <t>C_L08</t>
+  </si>
+  <si>
+    <t>A_L17</t>
+  </si>
+  <si>
+    <t>B_L01</t>
+  </si>
+  <si>
+    <t>A_L05</t>
+  </si>
+  <si>
+    <t>C_L25</t>
+  </si>
+  <si>
+    <t>A_L12</t>
+  </si>
+  <si>
+    <t>C_L29</t>
+  </si>
+  <si>
+    <t>B_L29</t>
+  </si>
+  <si>
+    <t>C_L11</t>
+  </si>
+  <si>
+    <t>B_L27</t>
+  </si>
+  <si>
+    <t>B_L30</t>
+  </si>
+  <si>
+    <t>C_L05</t>
+  </si>
+  <si>
+    <t>A_L19</t>
+  </si>
+  <si>
+    <t>C_L30</t>
+  </si>
+  <si>
+    <t>C_L28</t>
+  </si>
+  <si>
+    <t>B_L02</t>
+  </si>
+  <si>
+    <t>C_L17</t>
+  </si>
+  <si>
+    <t>C_L22</t>
+  </si>
+  <si>
+    <t>B_L05</t>
+  </si>
+  <si>
+    <t>C_L20</t>
+  </si>
+  <si>
+    <t>B_L12</t>
+  </si>
+  <si>
+    <t>A_L16</t>
+  </si>
+  <si>
+    <t>C_L04</t>
+  </si>
+  <si>
+    <t>B_L21</t>
+  </si>
+  <si>
+    <t>A_L08</t>
+  </si>
+  <si>
+    <t>B_L19</t>
+  </si>
+  <si>
+    <t>B_L04</t>
+  </si>
+  <si>
+    <t>B_L08</t>
+  </si>
+  <si>
+    <t>B_L25</t>
+  </si>
+  <si>
+    <t>B_L16</t>
+  </si>
+  <si>
+    <t>A_L06</t>
+  </si>
+  <si>
+    <t>C_L16</t>
+  </si>
+  <si>
+    <t>C_L01</t>
+  </si>
+  <si>
+    <t>A_L02</t>
+  </si>
+  <si>
+    <t>C_L10</t>
+  </si>
+  <si>
+    <t>C_L13</t>
+  </si>
+  <si>
+    <t>A_L03</t>
+  </si>
+  <si>
+    <t>A_L24</t>
+  </si>
+  <si>
+    <t>A_L29</t>
+  </si>
+  <si>
+    <t>A_L15</t>
+  </si>
+  <si>
+    <t>B_L15</t>
+  </si>
+  <si>
+    <t>B_L23</t>
+  </si>
+  <si>
+    <t>A_L21</t>
+  </si>
+  <si>
+    <t>B_L14</t>
+  </si>
+  <si>
+    <t>C_L27</t>
+  </si>
+  <si>
+    <t>A_L11</t>
+  </si>
+  <si>
+    <t>B_L18</t>
+  </si>
+  <si>
     <t>A_L20</t>
   </si>
   <si>
-    <t>A_L08</t>
-  </si>
-  <si>
-    <t>B_L11</t>
-  </si>
-  <si>
-    <t>B_L07</t>
-  </si>
-  <si>
-    <t>C_L20</t>
-  </si>
-  <si>
-    <t>C_L26</t>
-  </si>
-  <si>
-    <t>A_L11</t>
-  </si>
-  <si>
-    <t>A_L10</t>
-  </si>
-  <si>
-    <t>B_L26</t>
-  </si>
-  <si>
-    <t>B_L24</t>
-  </si>
-  <si>
-    <t>C_L13</t>
-  </si>
-  <si>
-    <t>C_L02</t>
-  </si>
-  <si>
-    <t>C_L03</t>
-  </si>
-  <si>
-    <t>B_L09</t>
-  </si>
-  <si>
-    <t>B_L10</t>
+    <t>A_L23</t>
+  </si>
+  <si>
+    <t>A_L01</t>
+  </si>
+  <si>
+    <t>C_L23</t>
+  </si>
+  <si>
+    <t>C_L06</t>
+  </si>
+  <si>
+    <t>A_L04</t>
   </si>
   <si>
     <t>A_L26</t>
-  </si>
-  <si>
-    <t>C_L08</t>
-  </si>
-  <si>
-    <t>A_L16</t>
-  </si>
-  <si>
-    <t>C_L10</t>
-  </si>
-  <si>
-    <t>B_L06</t>
-  </si>
-  <si>
-    <t>C_L16</t>
-  </si>
-  <si>
-    <t>C_L22</t>
-  </si>
-  <si>
-    <t>A_L29</t>
-  </si>
-  <si>
-    <t>C_L19</t>
-  </si>
-  <si>
-    <t>C_L09</t>
-  </si>
-  <si>
-    <t>A_L19</t>
-  </si>
-  <si>
-    <t>B_L02</t>
-  </si>
-  <si>
-    <t>A_L05</t>
-  </si>
-  <si>
-    <t>C_L25</t>
-  </si>
-  <si>
-    <t>A_L13</t>
-  </si>
-  <si>
-    <t>C_L29</t>
-  </si>
-  <si>
-    <t>B_L29</t>
-  </si>
-  <si>
-    <t>C_L12</t>
-  </si>
-  <si>
-    <t>B_L27</t>
-  </si>
-  <si>
-    <t>B_L30</t>
-  </si>
-  <si>
-    <t>C_L06</t>
-  </si>
-  <si>
-    <t>A_L21</t>
-  </si>
-  <si>
-    <t>C_L30</t>
-  </si>
-  <si>
-    <t>C_L28</t>
-  </si>
-  <si>
-    <t>B_L03</t>
-  </si>
-  <si>
-    <t>C_L18</t>
-  </si>
-  <si>
-    <t>C_L23</t>
-  </si>
-  <si>
-    <t>B_L05</t>
-  </si>
-  <si>
-    <t>C_L21</t>
-  </si>
-  <si>
-    <t>B_L12</t>
-  </si>
-  <si>
-    <t>A_L18</t>
-  </si>
-  <si>
-    <t>C_L05</t>
-  </si>
-  <si>
-    <t>B_L20</t>
-  </si>
-  <si>
-    <t>A_L09</t>
-  </si>
-  <si>
-    <t>B_L19</t>
-  </si>
-  <si>
-    <t>B_L04</t>
-  </si>
-  <si>
-    <t>B_L08</t>
-  </si>
-  <si>
-    <t>B_L25</t>
-  </si>
-  <si>
-    <t>B_L16</t>
-  </si>
-  <si>
-    <t>A_L07</t>
-  </si>
-  <si>
-    <t>C_L17</t>
-  </si>
-  <si>
-    <t>C_L01</t>
-  </si>
-  <si>
-    <t>A_L02</t>
-  </si>
-  <si>
-    <t>C_L11</t>
-  </si>
-  <si>
-    <t>C_L14</t>
-  </si>
-  <si>
-    <t>A_L03</t>
-  </si>
-  <si>
-    <t>A_L25</t>
-  </si>
-  <si>
-    <t>B_L01</t>
-  </si>
-  <si>
-    <t>A_L17</t>
-  </si>
-  <si>
-    <t>B_L15</t>
-  </si>
-  <si>
-    <t>B_L21</t>
-  </si>
-  <si>
-    <t>A_L23</t>
-  </si>
-  <si>
-    <t>B_L14</t>
-  </si>
-  <si>
-    <t>C_L27</t>
-  </si>
-  <si>
-    <t>A_L12</t>
-  </si>
-  <si>
-    <t>B_L18</t>
-  </si>
-  <si>
-    <t>A_L22</t>
-  </si>
-  <si>
-    <t>A_L24</t>
-  </si>
-  <si>
-    <t>A_L01</t>
-  </si>
-  <si>
-    <t>C_L24</t>
-  </si>
-  <si>
-    <t>C_L07</t>
-  </si>
-  <si>
-    <t>A_L04</t>
-  </si>
-  <si>
-    <t>A_L28</t>
   </si>
   <si>
     <t>A</t>
@@ -771,31 +771,31 @@
         <v>1</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H2">
         <v>2</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J2">
         <v>4</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O2">
         <v>6</v>
@@ -804,19 +804,19 @@
         <v>52</v>
       </c>
       <c r="Q2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R2">
         <v>3</v>
       </c>
       <c r="S2">
-        <v>6.6</v>
+        <v>8.9</v>
       </c>
       <c r="T2">
         <v>5</v>
       </c>
       <c r="U2">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="V2">
         <v>3</v>
@@ -842,22 +842,22 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3">
         <v>2</v>
       </c>
       <c r="I3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M3">
         <v>7</v>
@@ -869,25 +869,25 @@
         <v>6</v>
       </c>
       <c r="P3">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="Q3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R3">
         <v>3</v>
       </c>
       <c r="S3">
-        <v>7.9</v>
+        <v>6.4</v>
       </c>
       <c r="T3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U3">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="V3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -901,61 +901,61 @@
         <v>101</v>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4">
         <v>3</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K4">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M4">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O4">
         <v>6</v>
       </c>
       <c r="P4">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="Q4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S4">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="T4">
         <v>5</v>
       </c>
       <c r="U4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V4">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -969,55 +969,55 @@
         <v>102</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5">
         <v>5</v>
       </c>
       <c r="J5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O5">
         <v>6</v>
       </c>
       <c r="P5">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="Q5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S5">
         <v>3.9</v>
       </c>
       <c r="T5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U5">
         <v>11</v>
@@ -1037,58 +1037,58 @@
         <v>102</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6">
         <v>5</v>
       </c>
       <c r="J6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O6">
         <v>6</v>
       </c>
       <c r="P6">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="Q6">
         <v>1</v>
       </c>
       <c r="R6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S6">
-        <v>7.9</v>
+        <v>4.4</v>
       </c>
       <c r="T6">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U6">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="V6">
         <v>4</v>
@@ -1114,52 +1114,52 @@
         <v>1</v>
       </c>
       <c r="G7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M7">
         <v>5</v>
       </c>
       <c r="N7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O7">
         <v>6</v>
       </c>
       <c r="P7">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="Q7">
         <v>2</v>
       </c>
       <c r="R7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S7">
-        <v>4</v>
+        <v>6.6</v>
       </c>
       <c r="T7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U7">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="V7">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -1176,31 +1176,31 @@
         <v>6</v>
       </c>
       <c r="E8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I8">
         <v>1</v>
       </c>
       <c r="J8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L8">
         <v>1</v>
       </c>
       <c r="M8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N8">
         <v>1</v>
@@ -1209,25 +1209,25 @@
         <v>6</v>
       </c>
       <c r="P8">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="Q8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R8">
         <v>4</v>
       </c>
       <c r="S8">
-        <v>10.5</v>
+        <v>2.4</v>
       </c>
       <c r="T8">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V8">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -1241,58 +1241,58 @@
         <v>101</v>
       </c>
       <c r="D9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E9">
         <v>2</v>
       </c>
       <c r="F9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I9">
         <v>3</v>
       </c>
       <c r="J9">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L9">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M9">
         <v>4</v>
       </c>
       <c r="N9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O9">
         <v>6</v>
       </c>
       <c r="P9">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="Q9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R9">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S9">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U9">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="V9">
         <v>3</v>
@@ -1312,7 +1312,7 @@
         <v>3</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F10">
         <v>1</v>
@@ -1321,22 +1321,22 @@
         <v>2</v>
       </c>
       <c r="H10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N10">
         <v>5</v>
@@ -1345,7 +1345,7 @@
         <v>6</v>
       </c>
       <c r="P10">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="Q10">
         <v>2</v>
@@ -1354,16 +1354,16 @@
         <v>3</v>
       </c>
       <c r="S10">
-        <v>12.9</v>
+        <v>5.9</v>
       </c>
       <c r="T10">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U10">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="V10">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1377,46 +1377,46 @@
         <v>102</v>
       </c>
       <c r="D11">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E11">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I11">
         <v>5</v>
       </c>
       <c r="J11">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K11">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N11">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O11">
         <v>6</v>
       </c>
       <c r="P11">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="Q11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R11">
         <v>4</v>
@@ -1425,10 +1425,10 @@
         <v>4.8</v>
       </c>
       <c r="T11">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U11">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="V11">
         <v>3</v>
@@ -1445,34 +1445,34 @@
         <v>102</v>
       </c>
       <c r="D12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K12">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L12">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N12">
         <v>4</v>
@@ -1481,25 +1481,25 @@
         <v>6</v>
       </c>
       <c r="P12">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="Q12">
         <v>1</v>
       </c>
       <c r="R12">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S12">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="T12">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="U12">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="V12">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1513,55 +1513,55 @@
         <v>103</v>
       </c>
       <c r="D13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13">
         <v>4</v>
       </c>
       <c r="F13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I13">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K13">
         <v>6</v>
       </c>
       <c r="L13">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M13">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O13">
         <v>6</v>
       </c>
       <c r="P13">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="Q13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R13">
         <v>3</v>
       </c>
       <c r="S13">
-        <v>8.4</v>
+        <v>5</v>
       </c>
       <c r="T13">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U13">
         <v>10</v>
@@ -1581,43 +1581,43 @@
         <v>103</v>
       </c>
       <c r="D14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H14">
         <v>4</v>
       </c>
       <c r="I14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J14">
         <v>3</v>
       </c>
       <c r="K14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O14">
         <v>6</v>
       </c>
       <c r="P14">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="Q14">
         <v>1</v>
@@ -1626,13 +1626,13 @@
         <v>3</v>
       </c>
       <c r="S14">
-        <v>11</v>
+        <v>2.7</v>
       </c>
       <c r="T14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U14">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="V14">
         <v>3</v>
@@ -1655,13 +1655,13 @@
         <v>1</v>
       </c>
       <c r="F15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G15">
         <v>1</v>
       </c>
       <c r="H15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I15">
         <v>5</v>
@@ -1673,34 +1673,31 @@
         <v>5</v>
       </c>
       <c r="L15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M15">
         <v>6</v>
       </c>
       <c r="N15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O15">
         <v>6</v>
       </c>
       <c r="P15">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="Q15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S15">
-        <v>4.2</v>
-      </c>
-      <c r="T15">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="U15">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="V15">
         <v>3</v>
@@ -1717,61 +1714,61 @@
         <v>102</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K16">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L16">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N16">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O16">
         <v>6</v>
       </c>
       <c r="P16">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R16">
         <v>3</v>
       </c>
       <c r="S16">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="T16">
         <v>3</v>
       </c>
       <c r="U16">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="V16">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -1785,61 +1782,61 @@
         <v>102</v>
       </c>
       <c r="D17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E17">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F17">
         <v>3</v>
       </c>
       <c r="G17">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H17">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I17">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J17">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K17">
         <v>5</v>
       </c>
       <c r="L17">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M17">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N17">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O17">
         <v>6</v>
       </c>
       <c r="P17">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="Q17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S17">
-        <v>1.2</v>
+        <v>6.5</v>
       </c>
       <c r="T17">
         <v>5</v>
       </c>
       <c r="U17">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="V17">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -1853,25 +1850,25 @@
         <v>101</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G18">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I18">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K18">
         <v>6</v>
@@ -1880,31 +1877,31 @@
         <v>4</v>
       </c>
       <c r="M18">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N18">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O18">
         <v>6</v>
       </c>
       <c r="P18">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="Q18">
         <v>2</v>
       </c>
       <c r="R18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S18">
-        <v>6</v>
+        <v>12.7</v>
       </c>
       <c r="T18">
         <v>4</v>
       </c>
       <c r="U18">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="V18">
         <v>4</v>
@@ -1924,22 +1921,22 @@
         <v>5</v>
       </c>
       <c r="E19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G19">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I19">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J19">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K19">
         <v>5</v>
@@ -1948,7 +1945,7 @@
         <v>3</v>
       </c>
       <c r="M19">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N19">
         <v>6</v>
@@ -1957,22 +1954,22 @@
         <v>6</v>
       </c>
       <c r="P19">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="Q19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R19">
         <v>4</v>
       </c>
       <c r="S19">
-        <v>8.9</v>
+        <v>5.9</v>
       </c>
       <c r="T19">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U19">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="V19">
         <v>3</v>
@@ -1989,43 +1986,43 @@
         <v>101</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E20">
         <v>3</v>
       </c>
       <c r="F20">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G20">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I20">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J20">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K20">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M20">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N20">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O20">
         <v>6</v>
       </c>
       <c r="P20">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="Q20">
         <v>1</v>
@@ -2034,16 +2031,16 @@
         <v>4</v>
       </c>
       <c r="S20">
-        <v>6.8</v>
+        <v>2.2</v>
       </c>
       <c r="T20">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U20">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="V20">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -2060,58 +2057,58 @@
         <v>2</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G21">
         <v>3</v>
       </c>
       <c r="H21">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I21">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J21">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L21">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M21">
         <v>6</v>
       </c>
       <c r="N21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O21">
         <v>6</v>
       </c>
       <c r="P21">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="Q21">
         <v>1</v>
       </c>
       <c r="R21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S21">
-        <v>15.1</v>
+        <v>4.9</v>
       </c>
       <c r="T21">
         <v>7</v>
       </c>
       <c r="U21">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="V21">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -2128,25 +2125,25 @@
         <v>1</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K22">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L22">
         <v>3</v>
@@ -2155,31 +2152,31 @@
         <v>4</v>
       </c>
       <c r="N22">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O22">
         <v>6</v>
       </c>
       <c r="P22">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S22">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="T22">
+        <v>5</v>
+      </c>
+      <c r="U22">
         <v>8</v>
       </c>
-      <c r="U22">
-        <v>17</v>
-      </c>
       <c r="V22">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -2193,25 +2190,25 @@
         <v>103</v>
       </c>
       <c r="D23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G23">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H23">
         <v>4</v>
       </c>
       <c r="I23">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J23">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K23">
         <v>5</v>
@@ -2220,34 +2217,34 @@
         <v>5</v>
       </c>
       <c r="M23">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N23">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O23">
         <v>6</v>
       </c>
       <c r="P23">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="Q23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R23">
         <v>3</v>
       </c>
       <c r="S23">
-        <v>4</v>
+        <v>12.9</v>
       </c>
       <c r="T23">
         <v>5</v>
       </c>
       <c r="U23">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V23">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -2261,61 +2258,61 @@
         <v>103</v>
       </c>
       <c r="D24">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G24">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I24">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J24">
         <v>7</v>
       </c>
       <c r="K24">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N24">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O24">
         <v>6</v>
       </c>
       <c r="P24">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="Q24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R24">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S24">
-        <v>3.2</v>
+        <v>1.9</v>
       </c>
       <c r="T24">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U24">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="V24">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -2329,58 +2326,58 @@
         <v>101</v>
       </c>
       <c r="D25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F25">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G25">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H25">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I25">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J25">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K25">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L25">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M25">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N25">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O25">
         <v>6</v>
       </c>
       <c r="P25">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="Q25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R25">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S25">
-        <v>9</v>
+        <v>6.5</v>
       </c>
       <c r="T25">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U25">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="V25">
         <v>3</v>
@@ -2400,10 +2397,10 @@
         <v>1</v>
       </c>
       <c r="E26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -2412,46 +2409,46 @@
         <v>1</v>
       </c>
       <c r="I26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J26">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L26">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M26">
         <v>4</v>
       </c>
       <c r="N26">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O26">
         <v>6</v>
       </c>
       <c r="P26">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="Q26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R26">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S26">
-        <v>5.1</v>
+        <v>3.3</v>
       </c>
       <c r="T26">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U26">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="V26">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -2465,22 +2462,22 @@
         <v>103</v>
       </c>
       <c r="D27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F27">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G27">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J27">
         <v>5</v>
@@ -2489,7 +2486,7 @@
         <v>4</v>
       </c>
       <c r="L27">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M27">
         <v>4</v>
@@ -2501,25 +2498,25 @@
         <v>6</v>
       </c>
       <c r="P27">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Q27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S27">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="T27">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U27">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="V27">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -2533,19 +2530,19 @@
         <v>101</v>
       </c>
       <c r="D28">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E28">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G28">
         <v>5</v>
       </c>
       <c r="H28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I28">
         <v>6</v>
@@ -2554,40 +2551,40 @@
         <v>6</v>
       </c>
       <c r="K28">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L28">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M28">
         <v>4</v>
       </c>
       <c r="N28">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O28">
         <v>6</v>
       </c>
       <c r="P28">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="Q28">
         <v>1</v>
       </c>
       <c r="R28">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S28">
-        <v>8.4</v>
+        <v>2.3</v>
       </c>
       <c r="T28">
         <v>6</v>
       </c>
       <c r="U28">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="V28">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -2601,34 +2598,34 @@
         <v>102</v>
       </c>
       <c r="D29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E29">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H29">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J29">
         <v>4</v>
       </c>
       <c r="K29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L29">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M29">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N29">
         <v>5</v>
@@ -2637,25 +2634,25 @@
         <v>6</v>
       </c>
       <c r="P29">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="Q29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R29">
         <v>3</v>
       </c>
       <c r="S29">
-        <v>4.8</v>
+        <v>2.6</v>
       </c>
       <c r="T29">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U29">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="V29">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30" spans="1:22">
@@ -2669,43 +2666,43 @@
         <v>101</v>
       </c>
       <c r="D30">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E30">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F30">
         <v>4</v>
       </c>
       <c r="G30">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H30">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I30">
         <v>4</v>
       </c>
       <c r="J30">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K30">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L30">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M30">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N30">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O30">
         <v>6</v>
       </c>
       <c r="P30">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="Q30">
         <v>1</v>
@@ -2714,16 +2711,16 @@
         <v>3</v>
       </c>
       <c r="S30">
-        <v>5.7</v>
+        <v>2.1</v>
       </c>
       <c r="T30">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U30">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V30">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31" spans="1:22">
@@ -2737,61 +2734,61 @@
         <v>103</v>
       </c>
       <c r="D31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E31">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F31">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H31">
         <v>1</v>
       </c>
       <c r="I31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J31">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K31">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L31">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M31">
         <v>7</v>
       </c>
       <c r="N31">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O31">
         <v>6</v>
       </c>
       <c r="P31">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="Q31">
         <v>2</v>
       </c>
       <c r="R31">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S31">
-        <v>2.2</v>
+        <v>7.9</v>
       </c>
       <c r="T31">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U31">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="V31">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:22">
@@ -2808,7 +2805,7 @@
         <v>1</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F32">
         <v>1</v>
@@ -2817,46 +2814,46 @@
         <v>1</v>
       </c>
       <c r="H32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J32">
         <v>7</v>
       </c>
       <c r="K32">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M32">
         <v>7</v>
       </c>
       <c r="N32">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O32">
         <v>6</v>
       </c>
       <c r="P32">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="Q32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R32">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S32">
-        <v>3.3</v>
+        <v>4.9</v>
       </c>
       <c r="T32">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U32">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="V32">
         <v>3</v>
@@ -2876,25 +2873,25 @@
         <v>2</v>
       </c>
       <c r="E33">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F33">
         <v>2</v>
       </c>
       <c r="G33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J33">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K33">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L33">
         <v>6</v>
@@ -2903,28 +2900,28 @@
         <v>5</v>
       </c>
       <c r="N33">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O33">
         <v>6</v>
       </c>
       <c r="P33">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="Q33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R33">
         <v>4</v>
       </c>
       <c r="S33">
-        <v>5.1</v>
+        <v>11</v>
       </c>
       <c r="T33">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U33">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="V33">
         <v>3</v>
@@ -2944,55 +2941,55 @@
         <v>2</v>
       </c>
       <c r="E34">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F34">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G34">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H34">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I34">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J34">
         <v>3</v>
       </c>
       <c r="K34">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L34">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M34">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N34">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O34">
         <v>6</v>
       </c>
       <c r="P34">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="Q34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R34">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S34">
-        <v>1.7</v>
+        <v>16</v>
       </c>
       <c r="T34">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U34">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="V34">
         <v>4</v>
@@ -3009,61 +3006,61 @@
         <v>103</v>
       </c>
       <c r="D35">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E35">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F35">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G35">
         <v>3</v>
       </c>
       <c r="H35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I35">
         <v>4</v>
       </c>
       <c r="J35">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K35">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L35">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M35">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N35">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O35">
         <v>6</v>
       </c>
       <c r="P35">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="Q35">
         <v>1</v>
       </c>
       <c r="R35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S35">
-        <v>1.7</v>
+        <v>4.3</v>
       </c>
       <c r="T35">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U35">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="V35">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:22">
@@ -3077,58 +3074,58 @@
         <v>102</v>
       </c>
       <c r="D36">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F36">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G36">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I36">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J36">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K36">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L36">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N36">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O36">
         <v>6</v>
       </c>
       <c r="P36">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="Q36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S36">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="T36">
         <v>5</v>
       </c>
       <c r="U36">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="V36">
         <v>3</v>
@@ -3145,61 +3142,61 @@
         <v>102</v>
       </c>
       <c r="D37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H37">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I37">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J37">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K37">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L37">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N37">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O37">
         <v>6</v>
       </c>
       <c r="P37">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="Q37">
         <v>2</v>
       </c>
       <c r="R37">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S37">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="T37">
         <v>5</v>
       </c>
       <c r="U37">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="V37">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:22">
@@ -3213,34 +3210,34 @@
         <v>103</v>
       </c>
       <c r="D38">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E38">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F38">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G38">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H38">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J38">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K38">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L38">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N38">
         <v>5</v>
@@ -3249,22 +3246,22 @@
         <v>6</v>
       </c>
       <c r="P38">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="Q38">
         <v>1</v>
       </c>
       <c r="R38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S38">
-        <v>2.6</v>
+        <v>4.4</v>
       </c>
       <c r="T38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U38">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V38">
         <v>4</v>
@@ -3281,16 +3278,16 @@
         <v>101</v>
       </c>
       <c r="D39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E39">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H39">
         <v>2</v>
@@ -3302,16 +3299,16 @@
         <v>6</v>
       </c>
       <c r="K39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L39">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M39">
         <v>5</v>
       </c>
       <c r="N39">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O39">
         <v>6</v>
@@ -3320,19 +3317,19 @@
         <v>38</v>
       </c>
       <c r="Q39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R39">
         <v>3</v>
       </c>
       <c r="S39">
-        <v>2.4</v>
+        <v>8.1</v>
       </c>
       <c r="T39">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U39">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="V39">
         <v>3</v>
@@ -3349,61 +3346,61 @@
         <v>103</v>
       </c>
       <c r="D40">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E40">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F40">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G40">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I40">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J40">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K40">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M40">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N40">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O40">
         <v>6</v>
       </c>
       <c r="P40">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q40">
         <v>1</v>
       </c>
       <c r="R40">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S40">
-        <v>13.7</v>
+        <v>6.8</v>
       </c>
       <c r="T40">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U40">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="V40">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41" spans="1:22">
@@ -3420,13 +3417,13 @@
         <v>1</v>
       </c>
       <c r="E41">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F41">
         <v>1</v>
       </c>
       <c r="G41">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H41">
         <v>1</v>
@@ -3435,10 +3432,10 @@
         <v>5</v>
       </c>
       <c r="J41">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K41">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L41">
         <v>6</v>
@@ -3447,31 +3444,31 @@
         <v>5</v>
       </c>
       <c r="N41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O41">
         <v>6</v>
       </c>
       <c r="P41">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="Q41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R41">
         <v>3</v>
       </c>
       <c r="S41">
-        <v>2.6</v>
+        <v>7.5</v>
       </c>
       <c r="T41">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U41">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="V41">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42" spans="1:22">
@@ -3485,10 +3482,10 @@
         <v>102</v>
       </c>
       <c r="D42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F42">
         <v>3</v>
@@ -3500,46 +3497,46 @@
         <v>2</v>
       </c>
       <c r="I42">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J42">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K42">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L42">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M42">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N42">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O42">
         <v>6</v>
       </c>
       <c r="P42">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="Q42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R42">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S42">
-        <v>1.3</v>
+        <v>4.7</v>
       </c>
       <c r="T42">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U42">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="V42">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43" spans="1:22">
@@ -3556,19 +3553,19 @@
         <v>2</v>
       </c>
       <c r="E43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F43">
         <v>1</v>
       </c>
       <c r="G43">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I43">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J43">
         <v>7</v>
@@ -3577,37 +3574,37 @@
         <v>7</v>
       </c>
       <c r="L43">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M43">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N43">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O43">
         <v>6</v>
       </c>
       <c r="P43">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="Q43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R43">
         <v>3</v>
       </c>
       <c r="S43">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="T43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U43">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="V43">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44" spans="1:22">
@@ -3621,16 +3618,16 @@
         <v>103</v>
       </c>
       <c r="D44">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E44">
         <v>4</v>
       </c>
       <c r="F44">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G44">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H44">
         <v>3</v>
@@ -3639,43 +3636,40 @@
         <v>5</v>
       </c>
       <c r="J44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K44">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L44">
         <v>6</v>
       </c>
       <c r="M44">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N44">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O44">
         <v>6</v>
       </c>
-      <c r="P44">
-        <v>32</v>
-      </c>
       <c r="Q44">
         <v>1</v>
       </c>
       <c r="R44">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S44">
-        <v>5</v>
+        <v>2.9</v>
       </c>
       <c r="T44">
         <v>5</v>
       </c>
       <c r="U44">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V44">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:22">
@@ -3689,25 +3683,25 @@
         <v>102</v>
       </c>
       <c r="D45">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E45">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H45">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I45">
         <v>5</v>
       </c>
       <c r="J45">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K45">
         <v>7</v>
@@ -3719,31 +3713,31 @@
         <v>7</v>
       </c>
       <c r="N45">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O45">
         <v>6</v>
       </c>
       <c r="P45">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q45">
         <v>2</v>
       </c>
       <c r="R45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S45">
-        <v>5.3</v>
+        <v>10.2</v>
       </c>
       <c r="T45">
         <v>6</v>
       </c>
       <c r="U45">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="V45">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46" spans="1:22">
@@ -3757,34 +3751,34 @@
         <v>103</v>
       </c>
       <c r="D46">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E46">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F46">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G46">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H46">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I46">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J46">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K46">
         <v>5</v>
       </c>
       <c r="L46">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M46">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N46">
         <v>5</v>
@@ -3793,19 +3787,19 @@
         <v>6</v>
       </c>
       <c r="P46">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="Q46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R46">
         <v>4</v>
       </c>
-      <c r="S46">
-        <v>7</v>
+      <c r="T46">
+        <v>5</v>
       </c>
       <c r="U46">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="V46">
         <v>3</v>
@@ -3822,37 +3816,37 @@
         <v>102</v>
       </c>
       <c r="D47">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E47">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F47">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H47">
         <v>1</v>
       </c>
       <c r="I47">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J47">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K47">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L47">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M47">
         <v>4</v>
       </c>
       <c r="N47">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O47">
         <v>6</v>
@@ -3867,13 +3861,13 @@
         <v>3</v>
       </c>
       <c r="S47">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="T47">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U47">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="V47">
         <v>3</v>
@@ -3893,55 +3887,55 @@
         <v>1</v>
       </c>
       <c r="E48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F48">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G48">
         <v>1</v>
       </c>
       <c r="H48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I48">
         <v>5</v>
       </c>
       <c r="J48">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K48">
         <v>7</v>
       </c>
       <c r="L48">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M48">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N48">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O48">
         <v>6</v>
       </c>
       <c r="P48">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="Q48">
         <v>2</v>
       </c>
       <c r="R48">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S48">
-        <v>2.9</v>
+        <v>4.4</v>
       </c>
       <c r="T48">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U48">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="V48">
         <v>4</v>
@@ -3958,58 +3952,58 @@
         <v>103</v>
       </c>
       <c r="D49">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E49">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G49">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I49">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J49">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K49">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L49">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M49">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N49">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O49">
         <v>6</v>
       </c>
       <c r="P49">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="Q49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S49">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="T49">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="U49">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V49">
         <v>4</v>
@@ -4026,43 +4020,43 @@
         <v>102</v>
       </c>
       <c r="D50">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G50">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H50">
         <v>2</v>
       </c>
       <c r="I50">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J50">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K50">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L50">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M50">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N50">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O50">
         <v>6</v>
       </c>
       <c r="P50">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="Q50">
         <v>1</v>
@@ -4071,16 +4065,16 @@
         <v>3</v>
       </c>
       <c r="S50">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="T50">
         <v>4</v>
       </c>
       <c r="U50">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V50">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51" spans="1:22">
@@ -4094,58 +4088,58 @@
         <v>101</v>
       </c>
       <c r="D51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G51">
         <v>2</v>
       </c>
       <c r="H51">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I51">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J51">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K51">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L51">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M51">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N51">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O51">
         <v>6</v>
       </c>
       <c r="P51">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="Q51">
         <v>1</v>
       </c>
       <c r="R51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S51">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="T51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U51">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="V51">
         <v>4</v>
@@ -4162,28 +4156,28 @@
         <v>102</v>
       </c>
       <c r="D52">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E52">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F52">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G52">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H52">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I52">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J52">
         <v>5</v>
       </c>
       <c r="K52">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L52">
         <v>5</v>
@@ -4192,31 +4186,31 @@
         <v>5</v>
       </c>
       <c r="N52">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O52">
         <v>6</v>
       </c>
       <c r="P52">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="Q52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R52">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S52">
-        <v>4.1</v>
+        <v>2.2</v>
       </c>
       <c r="T52">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U52">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="V52">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53" spans="1:22">
@@ -4230,58 +4224,58 @@
         <v>102</v>
       </c>
       <c r="D53">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E53">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F53">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G53">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H53">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I53">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J53">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K53">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L53">
         <v>4</v>
       </c>
       <c r="M53">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N53">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O53">
         <v>6</v>
       </c>
       <c r="P53">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="Q53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R53">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S53">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="T53">
         <v>4</v>
       </c>
       <c r="U53">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="V53">
         <v>4</v>
@@ -4298,61 +4292,61 @@
         <v>102</v>
       </c>
       <c r="D54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E54">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G54">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H54">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I54">
         <v>6</v>
       </c>
       <c r="J54">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K54">
         <v>6</v>
       </c>
       <c r="L54">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M54">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N54">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O54">
         <v>6</v>
       </c>
       <c r="P54">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="Q54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R54">
         <v>3</v>
       </c>
       <c r="S54">
-        <v>6</v>
+        <v>2.6</v>
       </c>
       <c r="T54">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U54">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="V54">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55" spans="1:22">
@@ -4369,55 +4363,55 @@
         <v>1</v>
       </c>
       <c r="E55">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F55">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G55">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H55">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I55">
         <v>4</v>
       </c>
       <c r="J55">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K55">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L55">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M55">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N55">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O55">
         <v>6</v>
       </c>
       <c r="P55">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="Q55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R55">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S55">
-        <v>8.5</v>
+        <v>4.3</v>
       </c>
       <c r="T55">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U55">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="V55">
         <v>4</v>
@@ -4437,55 +4431,58 @@
         <v>1</v>
       </c>
       <c r="E56">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G56">
         <v>1</v>
       </c>
       <c r="H56">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I56">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J56">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K56">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L56">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M56">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N56">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O56">
         <v>6</v>
       </c>
+      <c r="P56">
+        <v>41</v>
+      </c>
       <c r="Q56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R56">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S56">
-        <v>5</v>
+        <v>2.6</v>
       </c>
       <c r="T56">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U56">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="V56">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:22">
@@ -4499,61 +4496,61 @@
         <v>101</v>
       </c>
       <c r="D57">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E57">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F57">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H57">
         <v>4</v>
       </c>
       <c r="I57">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J57">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K57">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L57">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M57">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N57">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O57">
         <v>6</v>
       </c>
       <c r="P57">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="Q57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R57">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S57">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="T57">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U57">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="V57">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="58" spans="1:22">
@@ -4567,61 +4564,61 @@
         <v>103</v>
       </c>
       <c r="D58">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G58">
         <v>1</v>
       </c>
       <c r="H58">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I58">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J58">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K58">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L58">
         <v>6</v>
       </c>
       <c r="M58">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N58">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O58">
         <v>6</v>
       </c>
       <c r="P58">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="Q58">
         <v>1</v>
       </c>
       <c r="R58">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S58">
-        <v>3.7</v>
+        <v>7</v>
       </c>
       <c r="T58">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U58">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="V58">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59" spans="1:22">
@@ -4635,58 +4632,58 @@
         <v>103</v>
       </c>
       <c r="D59">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F59">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G59">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H59">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I59">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J59">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K59">
         <v>5</v>
       </c>
       <c r="L59">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M59">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N59">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O59">
         <v>6</v>
       </c>
       <c r="P59">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="Q59">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R59">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S59">
-        <v>2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="T59">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U59">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="V59">
         <v>3</v>
@@ -4706,55 +4703,55 @@
         <v>2</v>
       </c>
       <c r="E60">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F60">
         <v>4</v>
       </c>
       <c r="G60">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H60">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I60">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J60">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K60">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L60">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M60">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N60">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O60">
         <v>6</v>
       </c>
       <c r="P60">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="Q60">
         <v>1</v>
       </c>
       <c r="R60">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S60">
-        <v>5.9</v>
+        <v>4.1</v>
       </c>
       <c r="T60">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U60">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="V60">
         <v>3</v>
@@ -4771,61 +4768,61 @@
         <v>103</v>
       </c>
       <c r="D61">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E61">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F61">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G61">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H61">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I61">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J61">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K61">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L61">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M61">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N61">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O61">
         <v>6</v>
       </c>
       <c r="P61">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="Q61">
         <v>1</v>
       </c>
       <c r="R61">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S61">
-        <v>7.7</v>
+        <v>5.7</v>
       </c>
       <c r="T61">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="U61">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="V61">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62" spans="1:22">
@@ -4839,34 +4836,34 @@
         <v>103</v>
       </c>
       <c r="D62">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E62">
         <v>1</v>
       </c>
       <c r="F62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G62">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H62">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I62">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J62">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K62">
         <v>6</v>
       </c>
       <c r="L62">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M62">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N62">
         <v>4</v>
@@ -4884,16 +4881,16 @@
         <v>4</v>
       </c>
       <c r="S62">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="T62">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U62">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="V62">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63" spans="1:22">
@@ -4907,16 +4904,16 @@
         <v>101</v>
       </c>
       <c r="D63">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E63">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F63">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H63">
         <v>3</v>
@@ -4925,43 +4922,43 @@
         <v>1</v>
       </c>
       <c r="J63">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K63">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L63">
         <v>2</v>
       </c>
       <c r="M63">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O63">
         <v>6</v>
       </c>
       <c r="P63">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Q63">
         <v>1</v>
       </c>
       <c r="R63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S63">
-        <v>3.1</v>
+        <v>8.5</v>
       </c>
       <c r="T63">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U63">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="V63">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:22">
@@ -4975,58 +4972,58 @@
         <v>101</v>
       </c>
       <c r="D64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F64">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G64">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H64">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I64">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J64">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K64">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L64">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M64">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="N64">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O64">
         <v>6</v>
       </c>
       <c r="P64">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="Q64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R64">
         <v>3</v>
       </c>
       <c r="S64">
-        <v>6.8</v>
+        <v>2.8</v>
       </c>
       <c r="T64">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U64">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V64">
         <v>4</v>
@@ -5040,37 +5037,37 @@
         <v>85</v>
       </c>
       <c r="C65" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D65">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E65">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F65">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G65">
         <v>3</v>
       </c>
       <c r="H65">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I65">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J65">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K65">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L65">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M65">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N65">
         <v>5</v>
@@ -5079,25 +5076,25 @@
         <v>6</v>
       </c>
       <c r="P65">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q65">
         <v>1</v>
       </c>
       <c r="R65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S65">
-        <v>2.2</v>
+        <v>3.7</v>
       </c>
       <c r="T65">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="U65">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V65">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66" spans="1:22">
@@ -5111,61 +5108,61 @@
         <v>101</v>
       </c>
       <c r="D66">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E66">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F66">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G66">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H66">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I66">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J66">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K66">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L66">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M66">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N66">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O66">
         <v>6</v>
       </c>
       <c r="P66">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Q66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R66">
         <v>3</v>
       </c>
       <c r="S66">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="T66">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U66">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="V66">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67" spans="1:22">
@@ -5179,43 +5176,43 @@
         <v>102</v>
       </c>
       <c r="D67">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E67">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F67">
         <v>4</v>
       </c>
       <c r="G67">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H67">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I67">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J67">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K67">
         <v>4</v>
       </c>
       <c r="L67">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M67">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N67">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O67">
         <v>6</v>
       </c>
       <c r="P67">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="Q67">
         <v>2</v>
@@ -5224,16 +5221,16 @@
         <v>3</v>
       </c>
       <c r="S67">
-        <v>7.4</v>
+        <v>5</v>
       </c>
       <c r="T67">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U67">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V67">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68" spans="1:22">
@@ -5247,61 +5244,61 @@
         <v>102</v>
       </c>
       <c r="D68">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E68">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F68">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G68">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H68">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I68">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J68">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K68">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L68">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M68">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N68">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O68">
         <v>6</v>
       </c>
       <c r="P68">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="Q68">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R68">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S68">
-        <v>6.6</v>
+        <v>5.3</v>
       </c>
       <c r="T68">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U68">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="V68">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69" spans="1:22">
@@ -5315,16 +5312,16 @@
         <v>101</v>
       </c>
       <c r="D69">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E69">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F69">
         <v>1</v>
       </c>
       <c r="G69">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H69">
         <v>1</v>
@@ -5333,25 +5330,25 @@
         <v>6</v>
       </c>
       <c r="J69">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K69">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L69">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M69">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N69">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O69">
         <v>6</v>
       </c>
       <c r="P69">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="Q69">
         <v>1</v>
@@ -5360,16 +5357,16 @@
         <v>4</v>
       </c>
       <c r="S69">
-        <v>7.5</v>
+        <v>2.1</v>
       </c>
       <c r="T69">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U69">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="V69">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:22">
@@ -5383,37 +5380,37 @@
         <v>102</v>
       </c>
       <c r="D70">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E70">
         <v>1</v>
       </c>
       <c r="F70">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H70">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I70">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J70">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K70">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L70">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M70">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N70">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O70">
         <v>6</v>
@@ -5425,16 +5422,16 @@
         <v>1</v>
       </c>
       <c r="R70">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S70">
-        <v>13.9</v>
+        <v>10.3</v>
       </c>
       <c r="T70">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U70">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="V70">
         <v>4</v>
@@ -5454,10 +5451,10 @@
         <v>1</v>
       </c>
       <c r="E71">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F71">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G71">
         <v>1</v>
@@ -5466,46 +5463,46 @@
         <v>1</v>
       </c>
       <c r="I71">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J71">
         <v>7</v>
       </c>
       <c r="K71">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L71">
         <v>7</v>
       </c>
       <c r="M71">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N71">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O71">
         <v>6</v>
       </c>
       <c r="P71">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="Q71">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R71">
         <v>3</v>
       </c>
       <c r="S71">
-        <v>4.4</v>
+        <v>8</v>
       </c>
       <c r="T71">
         <v>5</v>
       </c>
       <c r="U71">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="V71">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72" spans="1:22">
@@ -5522,58 +5519,58 @@
         <v>1</v>
       </c>
       <c r="E72">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F72">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G72">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H72">
         <v>1</v>
       </c>
       <c r="I72">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J72">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K72">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L72">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M72">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N72">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O72">
         <v>6</v>
       </c>
       <c r="P72">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="Q72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R72">
         <v>3</v>
       </c>
       <c r="S72">
-        <v>2.9</v>
+        <v>10</v>
       </c>
       <c r="T72">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U72">
         <v>10</v>
       </c>
       <c r="V72">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73" spans="1:22">
@@ -5587,58 +5584,61 @@
         <v>102</v>
       </c>
       <c r="D73">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E73">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F73">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G73">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H73">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I73">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J73">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K73">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L73">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M73">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N73">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O73">
         <v>6</v>
       </c>
       <c r="P73">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="Q73">
         <v>1</v>
       </c>
       <c r="R73">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="S73">
+        <v>1.1</v>
       </c>
       <c r="T73">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U73">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="V73">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74" spans="1:22">
@@ -5652,28 +5652,28 @@
         <v>101</v>
       </c>
       <c r="D74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E74">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F74">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G74">
         <v>2</v>
       </c>
       <c r="H74">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I74">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J74">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L74">
         <v>5</v>
@@ -5682,31 +5682,31 @@
         <v>5</v>
       </c>
       <c r="N74">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O74">
         <v>6</v>
       </c>
       <c r="P74">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="Q74">
         <v>2</v>
       </c>
       <c r="R74">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S74">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U74">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="V74">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75" spans="1:22">
@@ -5723,55 +5723,55 @@
         <v>2</v>
       </c>
       <c r="E75">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F75">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G75">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H75">
         <v>3</v>
       </c>
       <c r="I75">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J75">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K75">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L75">
         <v>5</v>
       </c>
       <c r="M75">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N75">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O75">
         <v>6</v>
       </c>
       <c r="P75">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="Q75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S75">
-        <v>11</v>
+        <v>3.6</v>
       </c>
       <c r="T75">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U75">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="V75">
         <v>4</v>
@@ -5788,7 +5788,7 @@
         <v>101</v>
       </c>
       <c r="D76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E76">
         <v>2</v>
@@ -5800,31 +5800,31 @@
         <v>4</v>
       </c>
       <c r="H76">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I76">
         <v>1</v>
       </c>
       <c r="J76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K76">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L76">
         <v>5</v>
       </c>
       <c r="M76">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O76">
         <v>6</v>
       </c>
       <c r="P76">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="Q76">
         <v>1</v>
@@ -5833,16 +5833,16 @@
         <v>2</v>
       </c>
       <c r="S76">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="T76">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U76">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V76">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="77" spans="1:22">
@@ -5856,58 +5856,58 @@
         <v>103</v>
       </c>
       <c r="D77">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E77">
         <v>4</v>
       </c>
       <c r="F77">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G77">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H77">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I77">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J77">
         <v>3</v>
       </c>
       <c r="K77">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L77">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M77">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N77">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O77">
         <v>6</v>
       </c>
       <c r="P77">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="Q77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R77">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S77">
-        <v>1.4</v>
+        <v>8.4</v>
       </c>
       <c r="T77">
         <v>6</v>
       </c>
       <c r="U77">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V77">
         <v>4</v>
@@ -5924,13 +5924,13 @@
         <v>103</v>
       </c>
       <c r="D78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F78">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G78">
         <v>2</v>
@@ -5939,28 +5939,28 @@
         <v>1</v>
       </c>
       <c r="I78">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J78">
         <v>4</v>
       </c>
       <c r="K78">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L78">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M78">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N78">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O78">
         <v>6</v>
       </c>
       <c r="P78">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="Q78">
         <v>2</v>
@@ -5969,16 +5969,16 @@
         <v>3</v>
       </c>
       <c r="S78">
-        <v>4.7</v>
+        <v>15.7</v>
       </c>
       <c r="T78">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U78">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="V78">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79" spans="1:22">
@@ -5995,31 +5995,31 @@
         <v>1</v>
       </c>
       <c r="E79">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F79">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G79">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I79">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J79">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K79">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L79">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M79">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N79">
         <v>7</v>
@@ -6028,7 +6028,7 @@
         <v>6</v>
       </c>
       <c r="P79">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="Q79">
         <v>1</v>
@@ -6037,16 +6037,16 @@
         <v>3</v>
       </c>
       <c r="S79">
-        <v>4.9</v>
+        <v>2.8</v>
       </c>
       <c r="T79">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U79">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="V79">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80" spans="1:22">
@@ -6063,7 +6063,7 @@
         <v>1</v>
       </c>
       <c r="E80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F80">
         <v>1</v>
@@ -6075,43 +6075,43 @@
         <v>1</v>
       </c>
       <c r="I80">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J80">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K80">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L80">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M80">
         <v>7</v>
       </c>
       <c r="N80">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O80">
         <v>6</v>
       </c>
       <c r="P80">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="Q80">
         <v>1</v>
       </c>
       <c r="R80">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S80">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="T80">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U80">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="V80">
         <v>3</v>

--- a/data/T3_leader_cleaned.xlsx
+++ b/data/T3_leader_cleaned.xlsx
@@ -82,232 +82,232 @@
     <t>LeaderJobLevel</t>
   </si>
   <si>
+    <t>A_L14</t>
+  </si>
+  <si>
+    <t>A_L20</t>
+  </si>
+  <si>
+    <t>A_L07</t>
+  </si>
+  <si>
+    <t>B_L10</t>
+  </si>
+  <si>
+    <t>B_L06</t>
+  </si>
+  <si>
+    <t>C_L20</t>
+  </si>
+  <si>
+    <t>C_L26</t>
+  </si>
+  <si>
+    <t>A_L11</t>
+  </si>
+  <si>
+    <t>A_L10</t>
+  </si>
+  <si>
+    <t>B_L26</t>
+  </si>
+  <si>
+    <t>B_L23</t>
+  </si>
+  <si>
+    <t>C_L12</t>
+  </si>
+  <si>
+    <t>C_L02</t>
+  </si>
+  <si>
+    <t>C_L03</t>
+  </si>
+  <si>
+    <t>B_L08</t>
+  </si>
+  <si>
+    <t>B_L09</t>
+  </si>
+  <si>
+    <t>A_L26</t>
+  </si>
+  <si>
+    <t>C_L07</t>
+  </si>
+  <si>
+    <t>A_L15</t>
+  </si>
+  <si>
+    <t>C_L09</t>
+  </si>
+  <si>
+    <t>B_L05</t>
+  </si>
+  <si>
+    <t>C_L14</t>
+  </si>
+  <si>
+    <t>C_L22</t>
+  </si>
+  <si>
+    <t>A_L28</t>
+  </si>
+  <si>
+    <t>C_L19</t>
+  </si>
+  <si>
+    <t>C_L08</t>
+  </si>
+  <si>
+    <t>A_L18</t>
+  </si>
+  <si>
+    <t>B_L01</t>
+  </si>
+  <si>
+    <t>A_L05</t>
+  </si>
+  <si>
+    <t>C_L25</t>
+  </si>
+  <si>
     <t>A_L13</t>
   </si>
   <si>
-    <t>A_L18</t>
-  </si>
-  <si>
-    <t>A_L07</t>
+    <t>C_L29</t>
+  </si>
+  <si>
+    <t>B_L29</t>
+  </si>
+  <si>
+    <t>C_L11</t>
+  </si>
+  <si>
+    <t>B_L27</t>
+  </si>
+  <si>
+    <t>B_L30</t>
+  </si>
+  <si>
+    <t>C_L05</t>
+  </si>
+  <si>
+    <t>A_L21</t>
+  </si>
+  <si>
+    <t>C_L30</t>
+  </si>
+  <si>
+    <t>C_L28</t>
+  </si>
+  <si>
+    <t>B_L02</t>
+  </si>
+  <si>
+    <t>C_L17</t>
+  </si>
+  <si>
+    <t>C_L23</t>
+  </si>
+  <si>
+    <t>B_L04</t>
+  </si>
+  <si>
+    <t>C_L21</t>
   </si>
   <si>
     <t>B_L11</t>
   </si>
   <si>
+    <t>A_L17</t>
+  </si>
+  <si>
+    <t>C_L04</t>
+  </si>
+  <si>
+    <t>B_L21</t>
+  </si>
+  <si>
+    <t>A_L09</t>
+  </si>
+  <si>
+    <t>B_L20</t>
+  </si>
+  <si>
+    <t>B_L03</t>
+  </si>
+  <si>
     <t>B_L07</t>
   </si>
   <si>
-    <t>C_L19</t>
-  </si>
-  <si>
-    <t>C_L26</t>
-  </si>
-  <si>
-    <t>A_L10</t>
-  </si>
-  <si>
-    <t>A_L09</t>
-  </si>
-  <si>
-    <t>B_L26</t>
-  </si>
-  <si>
-    <t>B_L24</t>
-  </si>
-  <si>
-    <t>C_L12</t>
-  </si>
-  <si>
-    <t>C_L02</t>
-  </si>
-  <si>
-    <t>C_L03</t>
-  </si>
-  <si>
-    <t>B_L09</t>
-  </si>
-  <si>
-    <t>B_L10</t>
+    <t>B_L25</t>
+  </si>
+  <si>
+    <t>B_L18</t>
+  </si>
+  <si>
+    <t>A_L06</t>
+  </si>
+  <si>
+    <t>C_L16</t>
+  </si>
+  <si>
+    <t>C_L01</t>
+  </si>
+  <si>
+    <t>A_L02</t>
+  </si>
+  <si>
+    <t>C_L10</t>
+  </si>
+  <si>
+    <t>C_L13</t>
+  </si>
+  <si>
+    <t>A_L03</t>
   </si>
   <si>
     <t>A_L25</t>
   </si>
   <si>
-    <t>C_L07</t>
-  </si>
-  <si>
-    <t>A_L14</t>
-  </si>
-  <si>
-    <t>C_L09</t>
-  </si>
-  <si>
-    <t>B_L06</t>
-  </si>
-  <si>
-    <t>C_L14</t>
-  </si>
-  <si>
-    <t>C_L21</t>
-  </si>
-  <si>
-    <t>A_L28</t>
-  </si>
-  <si>
-    <t>C_L18</t>
-  </si>
-  <si>
-    <t>C_L08</t>
-  </si>
-  <si>
-    <t>A_L17</t>
-  </si>
-  <si>
-    <t>B_L01</t>
-  </si>
-  <si>
-    <t>A_L05</t>
-  </si>
-  <si>
-    <t>C_L25</t>
+    <t>A_L29</t>
+  </si>
+  <si>
+    <t>A_L16</t>
+  </si>
+  <si>
+    <t>B_L15</t>
+  </si>
+  <si>
+    <t>B_L22</t>
+  </si>
+  <si>
+    <t>A_L23</t>
+  </si>
+  <si>
+    <t>B_L14</t>
+  </si>
+  <si>
+    <t>C_L27</t>
   </si>
   <si>
     <t>A_L12</t>
   </si>
   <si>
-    <t>C_L29</t>
-  </si>
-  <si>
-    <t>B_L29</t>
-  </si>
-  <si>
-    <t>C_L11</t>
-  </si>
-  <si>
-    <t>B_L27</t>
-  </si>
-  <si>
-    <t>B_L30</t>
-  </si>
-  <si>
-    <t>C_L05</t>
-  </si>
-  <si>
-    <t>A_L19</t>
-  </si>
-  <si>
-    <t>C_L30</t>
-  </si>
-  <si>
-    <t>C_L28</t>
-  </si>
-  <si>
-    <t>B_L02</t>
-  </si>
-  <si>
-    <t>C_L17</t>
-  </si>
-  <si>
-    <t>C_L22</t>
-  </si>
-  <si>
-    <t>B_L05</t>
-  </si>
-  <si>
-    <t>C_L20</t>
-  </si>
-  <si>
-    <t>B_L12</t>
-  </si>
-  <si>
-    <t>A_L16</t>
-  </si>
-  <si>
-    <t>C_L04</t>
-  </si>
-  <si>
-    <t>B_L21</t>
-  </si>
-  <si>
-    <t>A_L08</t>
-  </si>
-  <si>
     <t>B_L19</t>
   </si>
   <si>
-    <t>B_L04</t>
-  </si>
-  <si>
-    <t>B_L08</t>
-  </si>
-  <si>
-    <t>B_L25</t>
-  </si>
-  <si>
-    <t>B_L16</t>
-  </si>
-  <si>
-    <t>A_L06</t>
-  </si>
-  <si>
-    <t>C_L16</t>
-  </si>
-  <si>
-    <t>C_L01</t>
-  </si>
-  <si>
-    <t>A_L02</t>
-  </si>
-  <si>
-    <t>C_L10</t>
-  </si>
-  <si>
-    <t>C_L13</t>
-  </si>
-  <si>
-    <t>A_L03</t>
+    <t>A_L22</t>
   </si>
   <si>
     <t>A_L24</t>
   </si>
   <si>
-    <t>A_L29</t>
-  </si>
-  <si>
-    <t>A_L15</t>
-  </si>
-  <si>
-    <t>B_L15</t>
-  </si>
-  <si>
-    <t>B_L23</t>
-  </si>
-  <si>
-    <t>A_L21</t>
-  </si>
-  <si>
-    <t>B_L14</t>
-  </si>
-  <si>
-    <t>C_L27</t>
-  </si>
-  <si>
-    <t>A_L11</t>
-  </si>
-  <si>
-    <t>B_L18</t>
-  </si>
-  <si>
-    <t>A_L20</t>
-  </si>
-  <si>
-    <t>A_L23</t>
-  </si>
-  <si>
     <t>A_L01</t>
   </si>
   <si>
-    <t>C_L23</t>
+    <t>C_L24</t>
   </si>
   <si>
     <t>C_L06</t>
@@ -316,7 +316,7 @@
     <t>A_L04</t>
   </si>
   <si>
-    <t>A_L26</t>
+    <t>A_L27</t>
   </si>
   <si>
     <t>A</t>
@@ -765,61 +765,61 @@
         <v>101</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I2">
         <v>6</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K2">
         <v>5</v>
       </c>
       <c r="L2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M2">
         <v>5</v>
       </c>
       <c r="N2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O2">
         <v>6</v>
       </c>
       <c r="P2">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="Q2">
         <v>1</v>
       </c>
       <c r="R2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S2">
-        <v>8.9</v>
+        <v>6.7</v>
       </c>
       <c r="T2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="V2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -833,13 +833,13 @@
         <v>101</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -848,16 +848,16 @@
         <v>2</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M3">
         <v>7</v>
@@ -869,25 +869,25 @@
         <v>6</v>
       </c>
       <c r="P3">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q3">
         <v>2</v>
       </c>
       <c r="R3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S3">
-        <v>6.4</v>
+        <v>3.7</v>
       </c>
       <c r="T3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U3">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="V3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -901,58 +901,58 @@
         <v>101</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I4">
         <v>4</v>
       </c>
       <c r="J4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K4">
         <v>4</v>
       </c>
       <c r="L4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O4">
         <v>6</v>
       </c>
       <c r="P4">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="Q4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R4">
         <v>3</v>
       </c>
       <c r="S4">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="T4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U4">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="V4">
         <v>4</v>
@@ -969,58 +969,58 @@
         <v>102</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K5">
         <v>3</v>
       </c>
       <c r="L5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O5">
         <v>6</v>
       </c>
       <c r="P5">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="Q5">
         <v>2</v>
       </c>
       <c r="R5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S5">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="T5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U5">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="V5">
         <v>3</v>
@@ -1037,61 +1037,61 @@
         <v>102</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6">
         <v>2</v>
       </c>
       <c r="I6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L6">
         <v>5</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O6">
         <v>6</v>
       </c>
       <c r="P6">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="Q6">
         <v>1</v>
       </c>
       <c r="R6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S6">
-        <v>4.4</v>
+        <v>6.1</v>
       </c>
       <c r="T6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U6">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="V6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -1114,34 +1114,34 @@
         <v>1</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I7">
         <v>4</v>
       </c>
       <c r="J7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K7">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O7">
         <v>6</v>
       </c>
       <c r="P7">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="Q7">
         <v>2</v>
@@ -1150,16 +1150,16 @@
         <v>3</v>
       </c>
       <c r="S7">
-        <v>6.6</v>
+        <v>2.8</v>
       </c>
       <c r="T7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U7">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="V7">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -1173,61 +1173,61 @@
         <v>103</v>
       </c>
       <c r="D8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M8">
         <v>1</v>
       </c>
       <c r="N8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O8">
         <v>6</v>
       </c>
       <c r="P8">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="Q8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S8">
-        <v>2.4</v>
+        <v>4.7</v>
       </c>
       <c r="T8">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V8">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -1241,37 +1241,37 @@
         <v>101</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9">
         <v>2</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I9">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M9">
         <v>4</v>
       </c>
       <c r="N9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O9">
         <v>6</v>
@@ -1280,22 +1280,22 @@
         <v>31</v>
       </c>
       <c r="Q9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S9">
-        <v>3</v>
+        <v>5.6</v>
       </c>
       <c r="T9">
         <v>5</v>
       </c>
       <c r="U9">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="V9">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1309,16 +1309,16 @@
         <v>101</v>
       </c>
       <c r="D10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H10">
         <v>4</v>
@@ -1327,43 +1327,43 @@
         <v>5</v>
       </c>
       <c r="J10">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O10">
         <v>6</v>
       </c>
       <c r="P10">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="Q10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S10">
-        <v>5.9</v>
+        <v>4.5</v>
       </c>
       <c r="T10">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U10">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="V10">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1377,7 +1377,7 @@
         <v>102</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -1386,52 +1386,52 @@
         <v>1</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I11">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K11">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N11">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O11">
         <v>6</v>
       </c>
       <c r="P11">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S11">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="T11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U11">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="V11">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1445,34 +1445,34 @@
         <v>102</v>
       </c>
       <c r="D12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E12">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F12">
         <v>4</v>
       </c>
       <c r="G12">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12">
         <v>5</v>
       </c>
       <c r="J12">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K12">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N12">
         <v>4</v>
@@ -1481,25 +1481,25 @@
         <v>6</v>
       </c>
       <c r="P12">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="Q12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S12">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="T12">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="U12">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="V12">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1513,61 +1513,61 @@
         <v>103</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H13">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L13">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M13">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N13">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O13">
         <v>6</v>
       </c>
       <c r="P13">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="Q13">
         <v>1</v>
       </c>
       <c r="R13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S13">
-        <v>5</v>
+        <v>2.3</v>
       </c>
       <c r="T13">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U13">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="V13">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -1581,25 +1581,25 @@
         <v>103</v>
       </c>
       <c r="D14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E14">
         <v>5</v>
       </c>
       <c r="F14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G14">
         <v>4</v>
       </c>
       <c r="H14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I14">
         <v>2</v>
       </c>
       <c r="J14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K14">
         <v>1</v>
@@ -1611,13 +1611,13 @@
         <v>2</v>
       </c>
       <c r="N14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O14">
         <v>6</v>
       </c>
       <c r="P14">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Q14">
         <v>1</v>
@@ -1626,16 +1626,16 @@
         <v>3</v>
       </c>
       <c r="S14">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="T14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U14">
         <v>10</v>
       </c>
       <c r="V14">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1649,34 +1649,34 @@
         <v>103</v>
       </c>
       <c r="D15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N15">
         <v>5</v>
@@ -1685,22 +1685,22 @@
         <v>6</v>
       </c>
       <c r="P15">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q15">
         <v>1</v>
       </c>
       <c r="R15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S15">
-        <v>5.8</v>
+        <v>2.6</v>
       </c>
       <c r="U15">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="V15">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -1714,19 +1714,19 @@
         <v>102</v>
       </c>
       <c r="D16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G16">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H16">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I16">
         <v>5</v>
@@ -1735,22 +1735,22 @@
         <v>7</v>
       </c>
       <c r="K16">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O16">
         <v>6</v>
       </c>
       <c r="P16">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="Q16">
         <v>2</v>
@@ -1759,16 +1759,16 @@
         <v>3</v>
       </c>
       <c r="S16">
-        <v>5.6</v>
+        <v>13.8</v>
       </c>
       <c r="T16">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U16">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="V16">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -1782,58 +1782,58 @@
         <v>102</v>
       </c>
       <c r="D17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E17">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G17">
         <v>4</v>
       </c>
       <c r="H17">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I17">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J17">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K17">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L17">
         <v>4</v>
       </c>
       <c r="M17">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N17">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O17">
         <v>6</v>
       </c>
       <c r="P17">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="Q17">
         <v>1</v>
       </c>
       <c r="R17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S17">
-        <v>6.5</v>
+        <v>4.9</v>
       </c>
       <c r="T17">
         <v>5</v>
       </c>
       <c r="U17">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="V17">
         <v>3</v>
@@ -1850,34 +1850,34 @@
         <v>101</v>
       </c>
       <c r="D18">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F18">
         <v>3</v>
       </c>
       <c r="G18">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I18">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J18">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K18">
         <v>6</v>
       </c>
       <c r="L18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M18">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N18">
         <v>4</v>
@@ -1886,25 +1886,25 @@
         <v>6</v>
       </c>
       <c r="P18">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="Q18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R18">
         <v>4</v>
       </c>
       <c r="S18">
-        <v>12.7</v>
+        <v>3.8</v>
       </c>
       <c r="T18">
         <v>4</v>
       </c>
       <c r="U18">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="V18">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -1918,34 +1918,34 @@
         <v>103</v>
       </c>
       <c r="D19">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E19">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F19">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G19">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J19">
         <v>3</v>
       </c>
       <c r="K19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L19">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M19">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N19">
         <v>6</v>
@@ -1954,25 +1954,25 @@
         <v>6</v>
       </c>
       <c r="P19">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="Q19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S19">
-        <v>5.9</v>
+        <v>4.9</v>
       </c>
       <c r="T19">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U19">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="V19">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -1989,58 +1989,58 @@
         <v>3</v>
       </c>
       <c r="E20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F20">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G20">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H20">
         <v>5</v>
       </c>
       <c r="I20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J20">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L20">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M20">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N20">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O20">
         <v>6</v>
       </c>
       <c r="P20">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="Q20">
         <v>1</v>
       </c>
       <c r="R20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S20">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="T20">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U20">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="V20">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -2054,61 +2054,61 @@
         <v>103</v>
       </c>
       <c r="D21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E21">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F21">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G21">
         <v>3</v>
       </c>
       <c r="H21">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I21">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J21">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K21">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L21">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M21">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N21">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O21">
         <v>6</v>
       </c>
       <c r="P21">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="Q21">
         <v>1</v>
       </c>
       <c r="R21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S21">
-        <v>4.9</v>
+        <v>2.2</v>
       </c>
       <c r="T21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U21">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="V21">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -2125,10 +2125,10 @@
         <v>1</v>
       </c>
       <c r="E22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F22">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -2137,46 +2137,46 @@
         <v>2</v>
       </c>
       <c r="I22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J22">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K22">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L22">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M22">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N22">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O22">
         <v>6</v>
       </c>
       <c r="P22">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="Q22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R22">
         <v>4</v>
       </c>
       <c r="S22">
-        <v>4.1</v>
+        <v>2.6</v>
       </c>
       <c r="T22">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U22">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="V22">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -2190,22 +2190,22 @@
         <v>103</v>
       </c>
       <c r="D23">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F23">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H23">
         <v>4</v>
       </c>
       <c r="I23">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J23">
         <v>2</v>
@@ -2214,19 +2214,19 @@
         <v>5</v>
       </c>
       <c r="L23">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M23">
         <v>5</v>
       </c>
       <c r="N23">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O23">
         <v>6</v>
       </c>
       <c r="P23">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="Q23">
         <v>1</v>
@@ -2235,16 +2235,16 @@
         <v>3</v>
       </c>
       <c r="S23">
-        <v>12.9</v>
+        <v>8.1</v>
       </c>
       <c r="T23">
         <v>5</v>
       </c>
       <c r="U23">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="V23">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -2258,22 +2258,22 @@
         <v>103</v>
       </c>
       <c r="D24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F24">
         <v>3</v>
       </c>
       <c r="G24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H24">
         <v>2</v>
       </c>
       <c r="I24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J24">
         <v>7</v>
@@ -2282,37 +2282,34 @@
         <v>4</v>
       </c>
       <c r="L24">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M24">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N24">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O24">
         <v>6</v>
       </c>
       <c r="P24">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="Q24">
         <v>1</v>
       </c>
       <c r="R24">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S24">
-        <v>1.9</v>
-      </c>
-      <c r="T24">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="U24">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="V24">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -2335,7 +2332,7 @@
         <v>1</v>
       </c>
       <c r="G25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H25">
         <v>1</v>
@@ -2344,13 +2341,13 @@
         <v>6</v>
       </c>
       <c r="J25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K25">
         <v>7</v>
       </c>
       <c r="L25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M25">
         <v>6</v>
@@ -2362,25 +2359,25 @@
         <v>6</v>
       </c>
       <c r="P25">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="Q25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R25">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S25">
-        <v>6.5</v>
+        <v>7.7</v>
       </c>
       <c r="T25">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U25">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="V25">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -2397,55 +2394,55 @@
         <v>1</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F26">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G26">
         <v>1</v>
       </c>
       <c r="H26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J26">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K26">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L26">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M26">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N26">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O26">
         <v>6</v>
       </c>
       <c r="P26">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="Q26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R26">
         <v>4</v>
       </c>
       <c r="S26">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="T26">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U26">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="V26">
         <v>4</v>
@@ -2465,28 +2462,28 @@
         <v>2</v>
       </c>
       <c r="E27">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F27">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G27">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I27">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J27">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K27">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L27">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M27">
         <v>4</v>
@@ -2498,25 +2495,25 @@
         <v>6</v>
       </c>
       <c r="P27">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Q27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R27">
         <v>3</v>
       </c>
       <c r="S27">
-        <v>3.1</v>
+        <v>8.9</v>
       </c>
       <c r="T27">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="U27">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V27">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -2530,19 +2527,19 @@
         <v>101</v>
       </c>
       <c r="D28">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E28">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G28">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I28">
         <v>6</v>
@@ -2551,40 +2548,40 @@
         <v>6</v>
       </c>
       <c r="K28">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L28">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M28">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O28">
         <v>6</v>
       </c>
       <c r="P28">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="Q28">
         <v>1</v>
       </c>
       <c r="R28">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S28">
-        <v>2.3</v>
+        <v>5</v>
       </c>
       <c r="T28">
         <v>6</v>
       </c>
       <c r="U28">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="V28">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -2598,31 +2595,31 @@
         <v>102</v>
       </c>
       <c r="D29">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I29">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J29">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L29">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M29">
         <v>6</v>
@@ -2634,25 +2631,25 @@
         <v>6</v>
       </c>
       <c r="P29">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="Q29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R29">
         <v>3</v>
       </c>
       <c r="S29">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="T29">
         <v>6</v>
       </c>
       <c r="U29">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="V29">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:22">
@@ -2669,55 +2666,55 @@
         <v>3</v>
       </c>
       <c r="E30">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F30">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G30">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H30">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K30">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M30">
         <v>3</v>
       </c>
       <c r="N30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O30">
         <v>6</v>
       </c>
       <c r="P30">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="Q30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S30">
-        <v>2.1</v>
+        <v>8.4</v>
       </c>
       <c r="T30">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U30">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="V30">
         <v>4</v>
@@ -2737,34 +2734,34 @@
         <v>1</v>
       </c>
       <c r="E31">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F31">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G31">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I31">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J31">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K31">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M31">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N31">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O31">
         <v>6</v>
@@ -2773,19 +2770,19 @@
         <v>37</v>
       </c>
       <c r="Q31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S31">
-        <v>7.9</v>
+        <v>2.6</v>
       </c>
       <c r="T31">
         <v>4</v>
       </c>
       <c r="U31">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="V31">
         <v>4</v>
@@ -2802,58 +2799,58 @@
         <v>101</v>
       </c>
       <c r="D32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E32">
         <v>1</v>
       </c>
       <c r="F32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G32">
         <v>1</v>
       </c>
       <c r="H32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I32">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J32">
         <v>7</v>
       </c>
       <c r="K32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L32">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M32">
         <v>7</v>
       </c>
       <c r="N32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O32">
         <v>6</v>
       </c>
       <c r="P32">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="Q32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R32">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S32">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="T32">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U32">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="V32">
         <v>3</v>
@@ -2873,31 +2870,31 @@
         <v>2</v>
       </c>
       <c r="E33">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N33">
         <v>5</v>
@@ -2906,25 +2903,25 @@
         <v>6</v>
       </c>
       <c r="P33">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="Q33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R33">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S33">
-        <v>11</v>
+        <v>4.1</v>
       </c>
       <c r="T33">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U33">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="V33">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34" spans="1:22">
@@ -2944,37 +2941,37 @@
         <v>5</v>
       </c>
       <c r="F34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G34">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H34">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I34">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J34">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K34">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L34">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M34">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N34">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O34">
         <v>6</v>
       </c>
       <c r="P34">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="Q34">
         <v>1</v>
@@ -2983,16 +2980,16 @@
         <v>4</v>
       </c>
       <c r="S34">
-        <v>16</v>
+        <v>2.8</v>
       </c>
       <c r="T34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U34">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V34">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35" spans="1:22">
@@ -3006,43 +3003,43 @@
         <v>103</v>
       </c>
       <c r="D35">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E35">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F35">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I35">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J35">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K35">
         <v>4</v>
       </c>
       <c r="L35">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M35">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N35">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O35">
         <v>6</v>
       </c>
       <c r="P35">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="Q35">
         <v>1</v>
@@ -3051,13 +3048,13 @@
         <v>3</v>
       </c>
       <c r="S35">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T35">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U35">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="V35">
         <v>3</v>
@@ -3074,58 +3071,58 @@
         <v>102</v>
       </c>
       <c r="D36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E36">
         <v>1</v>
       </c>
       <c r="F36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H36">
         <v>3</v>
       </c>
       <c r="I36">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J36">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L36">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M36">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O36">
         <v>6</v>
       </c>
       <c r="P36">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="Q36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R36">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S36">
-        <v>2.9</v>
+        <v>8.5</v>
       </c>
       <c r="T36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U36">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="V36">
         <v>3</v>
@@ -3142,61 +3139,61 @@
         <v>102</v>
       </c>
       <c r="D37">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E37">
         <v>2</v>
       </c>
       <c r="F37">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G37">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H37">
         <v>4</v>
       </c>
       <c r="I37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J37">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K37">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L37">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N37">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O37">
         <v>6</v>
       </c>
       <c r="P37">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="Q37">
         <v>2</v>
       </c>
       <c r="R37">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S37">
-        <v>5.5</v>
+        <v>2.1</v>
       </c>
       <c r="T37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U37">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="V37">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38" spans="1:22">
@@ -3210,58 +3207,58 @@
         <v>103</v>
       </c>
       <c r="D38">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E38">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G38">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H38">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J38">
         <v>5</v>
       </c>
       <c r="K38">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M38">
         <v>7</v>
       </c>
       <c r="N38">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O38">
         <v>6</v>
       </c>
       <c r="P38">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="Q38">
         <v>1</v>
       </c>
       <c r="R38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S38">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="T38">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U38">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="V38">
         <v>4</v>
@@ -3278,43 +3275,43 @@
         <v>101</v>
       </c>
       <c r="D39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F39">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G39">
         <v>2</v>
       </c>
       <c r="H39">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J39">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K39">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L39">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N39">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O39">
         <v>6</v>
       </c>
       <c r="P39">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="Q39">
         <v>2</v>
@@ -3323,16 +3320,16 @@
         <v>3</v>
       </c>
       <c r="S39">
-        <v>8.1</v>
+        <v>2.8</v>
       </c>
       <c r="T39">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U39">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="V39">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40" spans="1:22">
@@ -3349,55 +3346,55 @@
         <v>3</v>
       </c>
       <c r="E40">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F40">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G40">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H40">
         <v>4</v>
       </c>
       <c r="I40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K40">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L40">
         <v>4</v>
       </c>
       <c r="M40">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N40">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O40">
         <v>6</v>
       </c>
       <c r="P40">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="Q40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R40">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S40">
-        <v>6.8</v>
+        <v>4.4</v>
       </c>
       <c r="T40">
         <v>5</v>
       </c>
       <c r="U40">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="V40">
         <v>3</v>
@@ -3414,61 +3411,61 @@
         <v>103</v>
       </c>
       <c r="D41">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F41">
         <v>1</v>
       </c>
       <c r="G41">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H41">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I41">
         <v>5</v>
       </c>
       <c r="J41">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L41">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M41">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O41">
         <v>6</v>
       </c>
       <c r="P41">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="Q41">
         <v>1</v>
       </c>
       <c r="R41">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S41">
-        <v>7.5</v>
+        <v>10.2</v>
       </c>
       <c r="T41">
         <v>7</v>
       </c>
       <c r="U41">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="V41">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42" spans="1:22">
@@ -3488,55 +3485,55 @@
         <v>1</v>
       </c>
       <c r="F42">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G42">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H42">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I42">
         <v>6</v>
       </c>
       <c r="J42">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K42">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L42">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M42">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N42">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O42">
         <v>6</v>
       </c>
       <c r="P42">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="Q42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R42">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S42">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="T42">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U42">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="V42">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:22">
@@ -3550,19 +3547,19 @@
         <v>103</v>
       </c>
       <c r="D43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F43">
         <v>1</v>
       </c>
       <c r="G43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H43">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I43">
         <v>6</v>
@@ -3571,22 +3568,22 @@
         <v>7</v>
       </c>
       <c r="K43">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M43">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N43">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O43">
         <v>6</v>
       </c>
       <c r="P43">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="Q43">
         <v>1</v>
@@ -3595,13 +3592,13 @@
         <v>3</v>
       </c>
       <c r="S43">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="T43">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U43">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V43">
         <v>3</v>
@@ -3621,55 +3618,58 @@
         <v>2</v>
       </c>
       <c r="E44">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F44">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G44">
         <v>2</v>
       </c>
       <c r="H44">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J44">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K44">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L44">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M44">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N44">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O44">
         <v>6</v>
       </c>
+      <c r="P44">
+        <v>55</v>
+      </c>
       <c r="Q44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R44">
         <v>5</v>
       </c>
       <c r="S44">
-        <v>2.9</v>
+        <v>6.5</v>
       </c>
       <c r="T44">
         <v>5</v>
       </c>
       <c r="U44">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="V44">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45" spans="1:22">
@@ -3683,61 +3683,61 @@
         <v>102</v>
       </c>
       <c r="D45">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H45">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I45">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J45">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K45">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L45">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M45">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N45">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O45">
         <v>6</v>
       </c>
       <c r="P45">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q45">
         <v>2</v>
       </c>
       <c r="R45">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S45">
-        <v>10.2</v>
+        <v>5.7</v>
       </c>
       <c r="T45">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U45">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="V45">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46" spans="1:22">
@@ -3754,34 +3754,34 @@
         <v>2</v>
       </c>
       <c r="E46">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F46">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G46">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H46">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I46">
         <v>5</v>
       </c>
       <c r="J46">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K46">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L46">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M46">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N46">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O46">
         <v>6</v>
@@ -3790,16 +3790,19 @@
         <v>34</v>
       </c>
       <c r="Q46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R46">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="S46">
+        <v>12</v>
       </c>
       <c r="T46">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U46">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="V46">
         <v>3</v>
@@ -3816,19 +3819,19 @@
         <v>102</v>
       </c>
       <c r="D47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E47">
         <v>4</v>
       </c>
       <c r="F47">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H47">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I47">
         <v>4</v>
@@ -3837,13 +3840,13 @@
         <v>4</v>
       </c>
       <c r="K47">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L47">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M47">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N47">
         <v>5</v>
@@ -3852,22 +3855,22 @@
         <v>6</v>
       </c>
       <c r="P47">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="Q47">
         <v>1</v>
       </c>
       <c r="R47">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S47">
-        <v>5.1</v>
+        <v>10.6</v>
       </c>
       <c r="T47">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U47">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="V47">
         <v>3</v>
@@ -3884,37 +3887,37 @@
         <v>101</v>
       </c>
       <c r="D48">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E48">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F48">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G48">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I48">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J48">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K48">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L48">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M48">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N48">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O48">
         <v>6</v>
@@ -3929,16 +3932,16 @@
         <v>4</v>
       </c>
       <c r="S48">
-        <v>4.4</v>
+        <v>6.7</v>
       </c>
       <c r="T48">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U48">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V48">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:22">
@@ -3952,58 +3955,58 @@
         <v>103</v>
       </c>
       <c r="D49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E49">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F49">
         <v>1</v>
       </c>
       <c r="G49">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H49">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I49">
         <v>5</v>
       </c>
       <c r="J49">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K49">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L49">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M49">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N49">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O49">
         <v>6</v>
       </c>
       <c r="P49">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="Q49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R49">
         <v>4</v>
       </c>
       <c r="S49">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="T49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U49">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="V49">
         <v>4</v>
@@ -4020,61 +4023,61 @@
         <v>102</v>
       </c>
       <c r="D50">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F50">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G50">
         <v>1</v>
       </c>
       <c r="H50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I50">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J50">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K50">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L50">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M50">
         <v>4</v>
       </c>
       <c r="N50">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O50">
         <v>6</v>
       </c>
       <c r="P50">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="Q50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R50">
         <v>3</v>
       </c>
       <c r="S50">
-        <v>3.5</v>
+        <v>6.2</v>
       </c>
       <c r="T50">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U50">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="V50">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51" spans="1:22">
@@ -4094,55 +4097,55 @@
         <v>2</v>
       </c>
       <c r="F51">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G51">
         <v>2</v>
       </c>
       <c r="H51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I51">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J51">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K51">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L51">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M51">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N51">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O51">
         <v>6</v>
       </c>
       <c r="P51">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="Q51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R51">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S51">
-        <v>2.6</v>
+        <v>4.5</v>
       </c>
       <c r="T51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U51">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="V51">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52" spans="1:22">
@@ -4156,58 +4159,58 @@
         <v>102</v>
       </c>
       <c r="D52">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E52">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F52">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G52">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H52">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I52">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J52">
         <v>5</v>
       </c>
       <c r="K52">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L52">
         <v>5</v>
       </c>
       <c r="M52">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N52">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O52">
         <v>6</v>
       </c>
       <c r="P52">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="Q52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R52">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S52">
-        <v>2.2</v>
+        <v>9.6</v>
       </c>
       <c r="T52">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U52">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="V52">
         <v>3</v>
@@ -4224,34 +4227,34 @@
         <v>102</v>
       </c>
       <c r="D53">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E53">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F53">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G53">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H53">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I53">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J53">
         <v>4</v>
       </c>
       <c r="K53">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L53">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M53">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N53">
         <v>5</v>
@@ -4260,7 +4263,7 @@
         <v>6</v>
       </c>
       <c r="P53">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="Q53">
         <v>1</v>
@@ -4269,13 +4272,13 @@
         <v>3</v>
       </c>
       <c r="S53">
-        <v>3</v>
+        <v>10.3</v>
       </c>
       <c r="T53">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U53">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="V53">
         <v>4</v>
@@ -4292,61 +4295,61 @@
         <v>102</v>
       </c>
       <c r="D54">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E54">
         <v>4</v>
       </c>
       <c r="F54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G54">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I54">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J54">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K54">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L54">
         <v>7</v>
       </c>
       <c r="M54">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N54">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O54">
         <v>6</v>
       </c>
       <c r="P54">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="Q54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R54">
         <v>3</v>
       </c>
       <c r="S54">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
       <c r="T54">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U54">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="V54">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55" spans="1:22">
@@ -4360,43 +4363,43 @@
         <v>102</v>
       </c>
       <c r="D55">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E55">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F55">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G55">
         <v>4</v>
       </c>
       <c r="H55">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I55">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J55">
         <v>4</v>
       </c>
       <c r="K55">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L55">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M55">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N55">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O55">
         <v>6</v>
       </c>
       <c r="P55">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="Q55">
         <v>1</v>
@@ -4405,13 +4408,13 @@
         <v>3</v>
       </c>
       <c r="S55">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="T55">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U55">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="V55">
         <v>4</v>
@@ -4428,61 +4431,61 @@
         <v>102</v>
       </c>
       <c r="D56">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E56">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G56">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H56">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I56">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J56">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K56">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L56">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M56">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N56">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O56">
         <v>6</v>
       </c>
       <c r="P56">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="Q56">
         <v>1</v>
       </c>
       <c r="R56">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S56">
-        <v>2.6</v>
+        <v>6.6</v>
       </c>
       <c r="T56">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U56">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="V56">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57" spans="1:22">
@@ -4496,22 +4499,22 @@
         <v>101</v>
       </c>
       <c r="D57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E57">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F57">
         <v>1</v>
       </c>
       <c r="G57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H57">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I57">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J57">
         <v>7</v>
@@ -4520,37 +4523,37 @@
         <v>7</v>
       </c>
       <c r="L57">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M57">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N57">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O57">
         <v>6</v>
       </c>
       <c r="P57">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="Q57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S57">
-        <v>3.9</v>
+        <v>7</v>
       </c>
       <c r="T57">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U57">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="V57">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58" spans="1:22">
@@ -4567,58 +4570,58 @@
         <v>3</v>
       </c>
       <c r="E58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F58">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H58">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I58">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J58">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K58">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L58">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M58">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N58">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O58">
         <v>6</v>
       </c>
       <c r="P58">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="Q58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R58">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S58">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T58">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U58">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="V58">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59" spans="1:22">
@@ -4635,31 +4638,31 @@
         <v>1</v>
       </c>
       <c r="E59">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F59">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G59">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H59">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I59">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J59">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K59">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L59">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M59">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N59">
         <v>5</v>
@@ -4668,22 +4671,22 @@
         <v>6</v>
       </c>
       <c r="P59">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="Q59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R59">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S59">
-        <v>9.800000000000001</v>
+        <v>3.9</v>
       </c>
       <c r="T59">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U59">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="V59">
         <v>3</v>
@@ -4700,58 +4703,58 @@
         <v>101</v>
       </c>
       <c r="D60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E60">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F60">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G60">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H60">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I60">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J60">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K60">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L60">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M60">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N60">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O60">
         <v>6</v>
       </c>
       <c r="P60">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="Q60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R60">
         <v>3</v>
       </c>
       <c r="S60">
-        <v>4.1</v>
+        <v>9.4</v>
       </c>
       <c r="T60">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U60">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="V60">
         <v>3</v>
@@ -4771,55 +4774,55 @@
         <v>1</v>
       </c>
       <c r="E61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F61">
         <v>3</v>
       </c>
       <c r="G61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H61">
         <v>2</v>
       </c>
       <c r="I61">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J61">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K61">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L61">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M61">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N61">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O61">
         <v>6</v>
       </c>
       <c r="P61">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Q61">
         <v>1</v>
       </c>
       <c r="R61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S61">
-        <v>5.7</v>
+        <v>2.2</v>
       </c>
       <c r="T61">
         <v>4</v>
       </c>
       <c r="U61">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V61">
         <v>3</v>
@@ -4836,61 +4839,61 @@
         <v>103</v>
       </c>
       <c r="D62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E62">
         <v>1</v>
       </c>
       <c r="F62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G62">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I62">
         <v>5</v>
       </c>
       <c r="J62">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K62">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L62">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M62">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="N62">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O62">
         <v>6</v>
       </c>
       <c r="P62">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="Q62">
         <v>1</v>
       </c>
       <c r="R62">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S62">
-        <v>2.4</v>
+        <v>6.4</v>
       </c>
       <c r="T62">
         <v>6</v>
       </c>
       <c r="U62">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="V62">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63" spans="1:22">
@@ -4904,61 +4907,61 @@
         <v>101</v>
       </c>
       <c r="D63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E63">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F63">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G63">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H63">
         <v>3</v>
       </c>
       <c r="I63">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J63">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K63">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M63">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O63">
         <v>6</v>
       </c>
       <c r="P63">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="Q63">
         <v>1</v>
       </c>
       <c r="R63">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S63">
-        <v>8.5</v>
+        <v>3.6</v>
       </c>
       <c r="T63">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U63">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="V63">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64" spans="1:22">
@@ -4972,58 +4975,55 @@
         <v>101</v>
       </c>
       <c r="D64">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E64">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F64">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H64">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I64">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J64">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K64">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L64">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M64">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N64">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O64">
         <v>6</v>
       </c>
-      <c r="P64">
-        <v>32</v>
-      </c>
       <c r="Q64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R64">
         <v>3</v>
       </c>
       <c r="S64">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="T64">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U64">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="V64">
         <v>4</v>
@@ -5040,61 +5040,61 @@
         <v>101</v>
       </c>
       <c r="D65">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E65">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F65">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G65">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H65">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J65">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K65">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L65">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N65">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O65">
         <v>6</v>
       </c>
       <c r="P65">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Q65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R65">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S65">
-        <v>3.7</v>
+        <v>7.9</v>
       </c>
       <c r="T65">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U65">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="V65">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66" spans="1:22">
@@ -5108,61 +5108,61 @@
         <v>101</v>
       </c>
       <c r="D66">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E66">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F66">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G66">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H66">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I66">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J66">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K66">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L66">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M66">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N66">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O66">
         <v>6</v>
       </c>
       <c r="P66">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="Q66">
         <v>1</v>
       </c>
       <c r="R66">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S66">
-        <v>2.2</v>
+        <v>7.5</v>
       </c>
       <c r="T66">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U66">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="V66">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67" spans="1:22">
@@ -5176,61 +5176,61 @@
         <v>102</v>
       </c>
       <c r="D67">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E67">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F67">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G67">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H67">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I67">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J67">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K67">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L67">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M67">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N67">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O67">
         <v>6</v>
       </c>
       <c r="P67">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="Q67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R67">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S67">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="T67">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U67">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="V67">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68" spans="1:22">
@@ -5244,58 +5244,58 @@
         <v>102</v>
       </c>
       <c r="D68">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E68">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F68">
         <v>4</v>
       </c>
       <c r="G68">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H68">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I68">
         <v>5</v>
       </c>
       <c r="J68">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K68">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L68">
         <v>5</v>
       </c>
       <c r="M68">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N68">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O68">
         <v>6</v>
       </c>
       <c r="P68">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="Q68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R68">
         <v>3</v>
       </c>
       <c r="S68">
-        <v>5.3</v>
+        <v>4.2</v>
       </c>
       <c r="T68">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U68">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="V68">
         <v>3</v>
@@ -5312,43 +5312,43 @@
         <v>101</v>
       </c>
       <c r="D69">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F69">
         <v>1</v>
       </c>
       <c r="G69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I69">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J69">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K69">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L69">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M69">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N69">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O69">
         <v>6</v>
       </c>
       <c r="P69">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="Q69">
         <v>1</v>
@@ -5357,16 +5357,16 @@
         <v>4</v>
       </c>
       <c r="S69">
-        <v>2.1</v>
+        <v>7.5</v>
       </c>
       <c r="T69">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U69">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="V69">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70" spans="1:22">
@@ -5380,61 +5380,61 @@
         <v>102</v>
       </c>
       <c r="D70">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E70">
         <v>1</v>
       </c>
       <c r="F70">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H70">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I70">
         <v>5</v>
       </c>
       <c r="J70">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K70">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L70">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M70">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N70">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O70">
         <v>6</v>
       </c>
       <c r="P70">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="Q70">
         <v>1</v>
       </c>
       <c r="R70">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S70">
-        <v>10.3</v>
+        <v>12</v>
       </c>
       <c r="T70">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U70">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="V70">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:22">
@@ -5448,25 +5448,25 @@
         <v>103</v>
       </c>
       <c r="D71">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E71">
         <v>1</v>
       </c>
       <c r="F71">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G71">
         <v>1</v>
       </c>
       <c r="H71">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J71">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K71">
         <v>6</v>
@@ -5475,34 +5475,34 @@
         <v>7</v>
       </c>
       <c r="M71">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N71">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O71">
         <v>6</v>
       </c>
       <c r="P71">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q71">
         <v>2</v>
       </c>
       <c r="R71">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S71">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T71">
         <v>5</v>
       </c>
       <c r="U71">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="V71">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72" spans="1:22">
@@ -5519,58 +5519,58 @@
         <v>1</v>
       </c>
       <c r="E72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F72">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H72">
         <v>1</v>
       </c>
       <c r="I72">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J72">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K72">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L72">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M72">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N72">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O72">
         <v>6</v>
       </c>
       <c r="P72">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q72">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R72">
         <v>3</v>
       </c>
       <c r="S72">
-        <v>10</v>
+        <v>3.4</v>
       </c>
       <c r="T72">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U72">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="V72">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73" spans="1:22">
@@ -5584,58 +5584,58 @@
         <v>102</v>
       </c>
       <c r="D73">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E73">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F73">
         <v>1</v>
       </c>
       <c r="G73">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H73">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I73">
         <v>5</v>
       </c>
       <c r="J73">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K73">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L73">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M73">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N73">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O73">
         <v>6</v>
       </c>
       <c r="P73">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="Q73">
         <v>1</v>
       </c>
       <c r="R73">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S73">
-        <v>1.1</v>
+        <v>7.6</v>
       </c>
       <c r="T73">
         <v>5</v>
       </c>
       <c r="U73">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="V73">
         <v>3</v>
@@ -5652,13 +5652,13 @@
         <v>101</v>
       </c>
       <c r="D74">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G74">
         <v>2</v>
@@ -5670,13 +5670,13 @@
         <v>4</v>
       </c>
       <c r="J74">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K74">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L74">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M74">
         <v>5</v>
@@ -5688,25 +5688,25 @@
         <v>6</v>
       </c>
       <c r="P74">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="Q74">
         <v>2</v>
       </c>
       <c r="R74">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S74">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="T74">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U74">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V74">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75" spans="1:22">
@@ -5720,58 +5720,58 @@
         <v>101</v>
       </c>
       <c r="D75">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E75">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G75">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I75">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J75">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K75">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L75">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M75">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N75">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O75">
         <v>6</v>
       </c>
       <c r="P75">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="Q75">
         <v>2</v>
       </c>
       <c r="R75">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S75">
-        <v>3.6</v>
+        <v>5.1</v>
       </c>
       <c r="T75">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U75">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="V75">
         <v>4</v>
@@ -5788,61 +5788,61 @@
         <v>101</v>
       </c>
       <c r="D76">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F76">
         <v>3</v>
       </c>
       <c r="G76">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H76">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I76">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J76">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K76">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L76">
         <v>5</v>
       </c>
       <c r="M76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N76">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O76">
         <v>6</v>
       </c>
       <c r="P76">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="Q76">
         <v>1</v>
       </c>
       <c r="R76">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S76">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="T76">
         <v>5</v>
       </c>
       <c r="U76">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="V76">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77" spans="1:22">
@@ -5856,7 +5856,7 @@
         <v>103</v>
       </c>
       <c r="D77">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E77">
         <v>4</v>
@@ -5865,49 +5865,49 @@
         <v>4</v>
       </c>
       <c r="G77">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H77">
         <v>2</v>
       </c>
       <c r="I77">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J77">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K77">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L77">
         <v>5</v>
       </c>
       <c r="M77">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N77">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O77">
         <v>6</v>
       </c>
       <c r="P77">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="Q77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>8.4</v>
+        <v>3.7</v>
       </c>
       <c r="T77">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U77">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="V77">
         <v>4</v>
@@ -5933,13 +5933,13 @@
         <v>1</v>
       </c>
       <c r="G78">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H78">
         <v>1</v>
       </c>
       <c r="I78">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J78">
         <v>4</v>
@@ -5960,25 +5960,25 @@
         <v>6</v>
       </c>
       <c r="P78">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="Q78">
         <v>2</v>
       </c>
       <c r="R78">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S78">
-        <v>15.7</v>
+        <v>10</v>
       </c>
       <c r="T78">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U78">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="V78">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79" spans="1:22">
@@ -5995,19 +5995,19 @@
         <v>1</v>
       </c>
       <c r="E79">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F79">
         <v>1</v>
       </c>
       <c r="G79">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I79">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J79">
         <v>7</v>
@@ -6028,25 +6028,25 @@
         <v>6</v>
       </c>
       <c r="P79">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="Q79">
         <v>1</v>
       </c>
       <c r="R79">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S79">
-        <v>2.8</v>
+        <v>9.1</v>
       </c>
       <c r="T79">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U79">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="V79">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80" spans="1:22">
@@ -6060,58 +6060,58 @@
         <v>101</v>
       </c>
       <c r="D80">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E80">
         <v>1</v>
       </c>
       <c r="F80">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G80">
         <v>1</v>
       </c>
       <c r="H80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I80">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J80">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K80">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L80">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M80">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N80">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O80">
         <v>6</v>
       </c>
       <c r="P80">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="Q80">
         <v>1</v>
       </c>
       <c r="R80">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S80">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="T80">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U80">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="V80">
         <v>3</v>

--- a/data/T3_leader_cleaned.xlsx
+++ b/data/T3_leader_cleaned.xlsx
@@ -82,241 +82,241 @@
     <t>LeaderJobLevel</t>
   </si>
   <si>
+    <t>A_L13</t>
+  </si>
+  <si>
+    <t>A_L18</t>
+  </si>
+  <si>
+    <t>A_L07</t>
+  </si>
+  <si>
+    <t>B_L09</t>
+  </si>
+  <si>
+    <t>B_L05</t>
+  </si>
+  <si>
+    <t>C_L20</t>
+  </si>
+  <si>
+    <t>C_L26</t>
+  </si>
+  <si>
+    <t>A_L10</t>
+  </si>
+  <si>
+    <t>A_L09</t>
+  </si>
+  <si>
+    <t>B_L23</t>
+  </si>
+  <si>
+    <t>B_L21</t>
+  </si>
+  <si>
+    <t>C_L13</t>
+  </si>
+  <si>
+    <t>B_L29</t>
+  </si>
+  <si>
+    <t>C_L01</t>
+  </si>
+  <si>
+    <t>B_L07</t>
+  </si>
+  <si>
+    <t>B_L08</t>
+  </si>
+  <si>
+    <t>A_L25</t>
+  </si>
+  <si>
+    <t>C_L06</t>
+  </si>
+  <si>
     <t>A_L14</t>
   </si>
   <si>
+    <t>C_L10</t>
+  </si>
+  <si>
+    <t>B_L04</t>
+  </si>
+  <si>
+    <t>C_L16</t>
+  </si>
+  <si>
+    <t>C_L22</t>
+  </si>
+  <si>
+    <t>A_L27</t>
+  </si>
+  <si>
+    <t>C_L19</t>
+  </si>
+  <si>
+    <t>C_L07</t>
+  </si>
+  <si>
+    <t>A_L17</t>
+  </si>
+  <si>
+    <t>A_L29</t>
+  </si>
+  <si>
+    <t>B_L06</t>
+  </si>
+  <si>
+    <t>A_L05</t>
+  </si>
+  <si>
+    <t>C_L25</t>
+  </si>
+  <si>
+    <t>A_L12</t>
+  </si>
+  <si>
+    <t>C_L29</t>
+  </si>
+  <si>
+    <t>B_L25</t>
+  </si>
+  <si>
+    <t>C_L12</t>
+  </si>
+  <si>
+    <t>B_L24</t>
+  </si>
+  <si>
+    <t>B_L26</t>
+  </si>
+  <si>
+    <t>C_L04</t>
+  </si>
+  <si>
+    <t>A_L19</t>
+  </si>
+  <si>
+    <t>C_L30</t>
+  </si>
+  <si>
+    <t>C_L28</t>
+  </si>
+  <si>
+    <t>B_L01</t>
+  </si>
+  <si>
+    <t>C_L18</t>
+  </si>
+  <si>
+    <t>C_L23</t>
+  </si>
+  <si>
+    <t>B_L03</t>
+  </si>
+  <si>
+    <t>C_L21</t>
+  </si>
+  <si>
+    <t>B_L10</t>
+  </si>
+  <si>
+    <t>A_L16</t>
+  </si>
+  <si>
+    <t>C_L03</t>
+  </si>
+  <si>
+    <t>B_L18</t>
+  </si>
+  <si>
+    <t>A_L08</t>
+  </si>
+  <si>
+    <t>B_L16</t>
+  </si>
+  <si>
+    <t>B_L02</t>
+  </si>
+  <si>
+    <t>B_L22</t>
+  </si>
+  <si>
+    <t>B_L14</t>
+  </si>
+  <si>
+    <t>A_L06</t>
+  </si>
+  <si>
+    <t>C_L17</t>
+  </si>
+  <si>
+    <t>B_L27</t>
+  </si>
+  <si>
+    <t>A_L02</t>
+  </si>
+  <si>
+    <t>C_L11</t>
+  </si>
+  <si>
+    <t>C_L14</t>
+  </si>
+  <si>
+    <t>A_L03</t>
+  </si>
+  <si>
+    <t>A_L24</t>
+  </si>
+  <si>
+    <t>A_L28</t>
+  </si>
+  <si>
+    <t>A_L15</t>
+  </si>
+  <si>
+    <t>B_L12</t>
+  </si>
+  <si>
+    <t>B_L19</t>
+  </si>
+  <si>
+    <t>A_L22</t>
+  </si>
+  <si>
+    <t>B_L11</t>
+  </si>
+  <si>
+    <t>C_L27</t>
+  </si>
+  <si>
+    <t>A_L11</t>
+  </si>
+  <si>
+    <t>B_L15</t>
+  </si>
+  <si>
     <t>A_L20</t>
   </si>
   <si>
-    <t>A_L07</t>
-  </si>
-  <si>
-    <t>B_L10</t>
-  </si>
-  <si>
-    <t>B_L06</t>
-  </si>
-  <si>
-    <t>C_L20</t>
-  </si>
-  <si>
-    <t>C_L26</t>
-  </si>
-  <si>
-    <t>A_L11</t>
-  </si>
-  <si>
-    <t>A_L10</t>
-  </si>
-  <si>
-    <t>B_L26</t>
-  </si>
-  <si>
-    <t>B_L23</t>
-  </si>
-  <si>
-    <t>C_L12</t>
-  </si>
-  <si>
-    <t>C_L02</t>
-  </si>
-  <si>
-    <t>C_L03</t>
-  </si>
-  <si>
-    <t>B_L08</t>
-  </si>
-  <si>
-    <t>B_L09</t>
+    <t>A_L23</t>
+  </si>
+  <si>
+    <t>A_L01</t>
+  </si>
+  <si>
+    <t>C_L24</t>
+  </si>
+  <si>
+    <t>C_L05</t>
+  </si>
+  <si>
+    <t>A_L04</t>
   </si>
   <si>
     <t>A_L26</t>
-  </si>
-  <si>
-    <t>C_L07</t>
-  </si>
-  <si>
-    <t>A_L15</t>
-  </si>
-  <si>
-    <t>C_L09</t>
-  </si>
-  <si>
-    <t>B_L05</t>
-  </si>
-  <si>
-    <t>C_L14</t>
-  </si>
-  <si>
-    <t>C_L22</t>
-  </si>
-  <si>
-    <t>A_L28</t>
-  </si>
-  <si>
-    <t>C_L19</t>
-  </si>
-  <si>
-    <t>C_L08</t>
-  </si>
-  <si>
-    <t>A_L18</t>
-  </si>
-  <si>
-    <t>B_L01</t>
-  </si>
-  <si>
-    <t>A_L05</t>
-  </si>
-  <si>
-    <t>C_L25</t>
-  </si>
-  <si>
-    <t>A_L13</t>
-  </si>
-  <si>
-    <t>C_L29</t>
-  </si>
-  <si>
-    <t>B_L29</t>
-  </si>
-  <si>
-    <t>C_L11</t>
-  </si>
-  <si>
-    <t>B_L27</t>
-  </si>
-  <si>
-    <t>B_L30</t>
-  </si>
-  <si>
-    <t>C_L05</t>
-  </si>
-  <si>
-    <t>A_L21</t>
-  </si>
-  <si>
-    <t>C_L30</t>
-  </si>
-  <si>
-    <t>C_L28</t>
-  </si>
-  <si>
-    <t>B_L02</t>
-  </si>
-  <si>
-    <t>C_L17</t>
-  </si>
-  <si>
-    <t>C_L23</t>
-  </si>
-  <si>
-    <t>B_L04</t>
-  </si>
-  <si>
-    <t>C_L21</t>
-  </si>
-  <si>
-    <t>B_L11</t>
-  </si>
-  <si>
-    <t>A_L17</t>
-  </si>
-  <si>
-    <t>C_L04</t>
-  </si>
-  <si>
-    <t>B_L21</t>
-  </si>
-  <si>
-    <t>A_L09</t>
-  </si>
-  <si>
-    <t>B_L20</t>
-  </si>
-  <si>
-    <t>B_L03</t>
-  </si>
-  <si>
-    <t>B_L07</t>
-  </si>
-  <si>
-    <t>B_L25</t>
-  </si>
-  <si>
-    <t>B_L18</t>
-  </si>
-  <si>
-    <t>A_L06</t>
-  </si>
-  <si>
-    <t>C_L16</t>
-  </si>
-  <si>
-    <t>C_L01</t>
-  </si>
-  <si>
-    <t>A_L02</t>
-  </si>
-  <si>
-    <t>C_L10</t>
-  </si>
-  <si>
-    <t>C_L13</t>
-  </si>
-  <si>
-    <t>A_L03</t>
-  </si>
-  <si>
-    <t>A_L25</t>
-  </si>
-  <si>
-    <t>A_L29</t>
-  </si>
-  <si>
-    <t>A_L16</t>
-  </si>
-  <si>
-    <t>B_L15</t>
-  </si>
-  <si>
-    <t>B_L22</t>
-  </si>
-  <si>
-    <t>A_L23</t>
-  </si>
-  <si>
-    <t>B_L14</t>
-  </si>
-  <si>
-    <t>C_L27</t>
-  </si>
-  <si>
-    <t>A_L12</t>
-  </si>
-  <si>
-    <t>B_L19</t>
-  </si>
-  <si>
-    <t>A_L22</t>
-  </si>
-  <si>
-    <t>A_L24</t>
-  </si>
-  <si>
-    <t>A_L01</t>
-  </si>
-  <si>
-    <t>C_L24</t>
-  </si>
-  <si>
-    <t>C_L06</t>
-  </si>
-  <si>
-    <t>A_L04</t>
-  </si>
-  <si>
-    <t>A_L27</t>
   </si>
   <si>
     <t>A</t>
@@ -765,61 +765,61 @@
         <v>101</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J2">
         <v>5</v>
       </c>
       <c r="K2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M2">
         <v>5</v>
       </c>
       <c r="N2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O2">
         <v>6</v>
       </c>
       <c r="P2">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="Q2">
         <v>1</v>
       </c>
       <c r="R2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S2">
-        <v>6.7</v>
+        <v>6</v>
       </c>
       <c r="T2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -833,61 +833,61 @@
         <v>101</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="N3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O3">
         <v>6</v>
       </c>
       <c r="P3">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="Q3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S3">
-        <v>3.7</v>
+        <v>11.5</v>
       </c>
       <c r="T3">
         <v>3</v>
       </c>
       <c r="U3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -901,61 +901,61 @@
         <v>101</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4">
         <v>3</v>
       </c>
       <c r="H4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O4">
         <v>6</v>
       </c>
       <c r="P4">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="Q4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R4">
         <v>3</v>
       </c>
       <c r="S4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U4">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="V4">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -972,58 +972,58 @@
         <v>3</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G5">
         <v>3</v>
       </c>
       <c r="H5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J5">
         <v>4</v>
       </c>
       <c r="K5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O5">
         <v>6</v>
       </c>
       <c r="P5">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="Q5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S5">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="T5">
         <v>6</v>
       </c>
       <c r="U5">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="V5">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -1037,37 +1037,37 @@
         <v>102</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6">
         <v>1</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O6">
         <v>6</v>
@@ -1079,16 +1079,16 @@
         <v>1</v>
       </c>
       <c r="R6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S6">
-        <v>6.1</v>
+        <v>2.4</v>
       </c>
       <c r="T6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U6">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V6">
         <v>3</v>
@@ -1105,61 +1105,61 @@
         <v>103</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7">
         <v>2</v>
       </c>
       <c r="H7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I7">
         <v>4</v>
       </c>
       <c r="J7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K7">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L7">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M7">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N7">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O7">
         <v>6</v>
       </c>
       <c r="P7">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="Q7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R7">
         <v>3</v>
       </c>
       <c r="S7">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="T7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U7">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="V7">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -1173,7 +1173,7 @@
         <v>103</v>
       </c>
       <c r="D8">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E8">
         <v>5</v>
@@ -1182,25 +1182,25 @@
         <v>4</v>
       </c>
       <c r="G8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H8">
         <v>6</v>
       </c>
       <c r="I8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N8">
         <v>3</v>
@@ -1209,25 +1209,25 @@
         <v>6</v>
       </c>
       <c r="P8">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="Q8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R8">
         <v>3</v>
       </c>
       <c r="S8">
-        <v>4.7</v>
+        <v>9</v>
       </c>
       <c r="T8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U8">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="V8">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -1241,31 +1241,31 @@
         <v>101</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H9">
         <v>3</v>
       </c>
       <c r="I9">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L9">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M9">
         <v>4</v>
@@ -1277,7 +1277,7 @@
         <v>6</v>
       </c>
       <c r="P9">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="Q9">
         <v>1</v>
@@ -1286,16 +1286,16 @@
         <v>4</v>
       </c>
       <c r="S9">
-        <v>5.6</v>
+        <v>2.7</v>
       </c>
       <c r="T9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U9">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="V9">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1312,58 +1312,55 @@
         <v>4</v>
       </c>
       <c r="E10">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F10">
         <v>3</v>
       </c>
       <c r="G10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N10">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O10">
         <v>6</v>
       </c>
-      <c r="P10">
-        <v>43</v>
-      </c>
       <c r="Q10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S10">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="T10">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U10">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="V10">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1383,55 +1380,55 @@
         <v>2</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G11">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K11">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M11">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N11">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O11">
         <v>6</v>
       </c>
       <c r="P11">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="Q11">
         <v>1</v>
       </c>
       <c r="R11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S11">
-        <v>4.1</v>
+        <v>6.4</v>
       </c>
       <c r="T11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U11">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="V11">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1445,31 +1442,31 @@
         <v>102</v>
       </c>
       <c r="D12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G12">
         <v>3</v>
       </c>
       <c r="H12">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I12">
         <v>5</v>
       </c>
       <c r="J12">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K12">
         <v>4</v>
       </c>
       <c r="L12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M12">
         <v>3</v>
@@ -1481,22 +1478,22 @@
         <v>6</v>
       </c>
       <c r="P12">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="Q12">
         <v>2</v>
       </c>
       <c r="R12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S12">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="T12">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U12">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="V12">
         <v>3</v>
@@ -1525,49 +1522,49 @@
         <v>2</v>
       </c>
       <c r="H13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I13">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J13">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K13">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M13">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O13">
         <v>6</v>
       </c>
       <c r="P13">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="Q13">
         <v>1</v>
       </c>
       <c r="R13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S13">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="T13">
         <v>6</v>
       </c>
       <c r="U13">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="V13">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -1578,64 +1575,64 @@
         <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K14">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L14">
         <v>3</v>
       </c>
       <c r="M14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O14">
         <v>6</v>
       </c>
       <c r="P14">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="Q14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R14">
         <v>3</v>
       </c>
       <c r="S14">
-        <v>3.4</v>
+        <v>5.7</v>
       </c>
       <c r="T14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U14">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V14">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1649,28 +1646,28 @@
         <v>103</v>
       </c>
       <c r="D15">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L15">
         <v>5</v>
@@ -1679,28 +1676,31 @@
         <v>5</v>
       </c>
       <c r="N15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O15">
         <v>6</v>
       </c>
       <c r="P15">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="Q15">
         <v>1</v>
       </c>
       <c r="R15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S15">
-        <v>2.6</v>
+        <v>7.4</v>
+      </c>
+      <c r="T15">
+        <v>6</v>
       </c>
       <c r="U15">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="V15">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -1714,25 +1714,25 @@
         <v>102</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F16">
         <v>2</v>
       </c>
       <c r="G16">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J16">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K16">
         <v>6</v>
@@ -1741,31 +1741,31 @@
         <v>4</v>
       </c>
       <c r="M16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O16">
         <v>6</v>
       </c>
       <c r="P16">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="Q16">
         <v>2</v>
       </c>
       <c r="R16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S16">
-        <v>13.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="T16">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U16">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="V16">
         <v>4</v>
@@ -1785,55 +1785,55 @@
         <v>3</v>
       </c>
       <c r="E17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G17">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H17">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I17">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J17">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O17">
         <v>6</v>
       </c>
       <c r="P17">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="Q17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S17">
-        <v>4.9</v>
+        <v>6.3</v>
       </c>
       <c r="T17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U17">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="V17">
         <v>3</v>
@@ -1850,34 +1850,34 @@
         <v>101</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F18">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G18">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H18">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I18">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J18">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K18">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L18">
         <v>5</v>
       </c>
       <c r="M18">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N18">
         <v>4</v>
@@ -1886,7 +1886,7 @@
         <v>6</v>
       </c>
       <c r="P18">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="Q18">
         <v>1</v>
@@ -1895,16 +1895,16 @@
         <v>4</v>
       </c>
       <c r="S18">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="T18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U18">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="V18">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -1918,7 +1918,7 @@
         <v>103</v>
       </c>
       <c r="D19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E19">
         <v>2</v>
@@ -1927,25 +1927,25 @@
         <v>1</v>
       </c>
       <c r="G19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K19">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L19">
         <v>5</v>
       </c>
       <c r="M19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N19">
         <v>6</v>
@@ -1957,19 +1957,19 @@
         <v>45</v>
       </c>
       <c r="Q19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S19">
-        <v>4.9</v>
+        <v>8</v>
       </c>
       <c r="T19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U19">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="V19">
         <v>4</v>
@@ -1986,58 +1986,58 @@
         <v>101</v>
       </c>
       <c r="D20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E20">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F20">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H20">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J20">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K20">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L20">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M20">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N20">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O20">
         <v>6</v>
       </c>
       <c r="P20">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="Q20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S20">
-        <v>1.2</v>
+        <v>5.6</v>
       </c>
       <c r="T20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U20">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="V20">
         <v>3</v>
@@ -2063,52 +2063,52 @@
         <v>1</v>
       </c>
       <c r="G21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H21">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I21">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J21">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K21">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L21">
         <v>2</v>
       </c>
       <c r="M21">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N21">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O21">
         <v>6</v>
       </c>
       <c r="P21">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="Q21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R21">
         <v>3</v>
       </c>
       <c r="S21">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="T21">
         <v>6</v>
       </c>
       <c r="U21">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="V21">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -2122,34 +2122,34 @@
         <v>102</v>
       </c>
       <c r="D22">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22">
         <v>1</v>
       </c>
       <c r="H22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I22">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J22">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K22">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L22">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M22">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N22">
         <v>6</v>
@@ -2158,22 +2158,22 @@
         <v>6</v>
       </c>
       <c r="P22">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="Q22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R22">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S22">
-        <v>2.6</v>
+        <v>5.5</v>
       </c>
       <c r="T22">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U22">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="V22">
         <v>3</v>
@@ -2190,61 +2190,61 @@
         <v>103</v>
       </c>
       <c r="D23">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E23">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F23">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J23">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L23">
         <v>4</v>
       </c>
       <c r="M23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N23">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O23">
         <v>6</v>
       </c>
       <c r="P23">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="Q23">
         <v>1</v>
       </c>
       <c r="R23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S23">
-        <v>8.1</v>
+        <v>4.4</v>
       </c>
       <c r="T23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U23">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="V23">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -2258,22 +2258,22 @@
         <v>103</v>
       </c>
       <c r="D24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F24">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G24">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H24">
         <v>2</v>
       </c>
       <c r="I24">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J24">
         <v>7</v>
@@ -2282,13 +2282,13 @@
         <v>4</v>
       </c>
       <c r="L24">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N24">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O24">
         <v>6</v>
@@ -2303,13 +2303,16 @@
         <v>3</v>
       </c>
       <c r="S24">
-        <v>5.4</v>
+        <v>1.5</v>
+      </c>
+      <c r="T24">
+        <v>7</v>
       </c>
       <c r="U24">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="V24">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -2326,10 +2329,10 @@
         <v>1</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G25">
         <v>2</v>
@@ -2338,46 +2341,46 @@
         <v>1</v>
       </c>
       <c r="I25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J25">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K25">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L25">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M25">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N25">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O25">
         <v>6</v>
       </c>
       <c r="P25">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="Q25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R25">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S25">
-        <v>7.7</v>
+        <v>11.9</v>
       </c>
       <c r="T25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U25">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="V25">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -2391,7 +2394,7 @@
         <v>103</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E26">
         <v>1</v>
@@ -2403,22 +2406,22 @@
         <v>1</v>
       </c>
       <c r="H26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I26">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J26">
         <v>5</v>
       </c>
       <c r="K26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M26">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N26">
         <v>6</v>
@@ -2427,22 +2430,22 @@
         <v>6</v>
       </c>
       <c r="P26">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="Q26">
         <v>1</v>
       </c>
       <c r="R26">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S26">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="T26">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U26">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="V26">
         <v>4</v>
@@ -2459,58 +2462,58 @@
         <v>103</v>
       </c>
       <c r="D27">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G27">
         <v>5</v>
       </c>
       <c r="H27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K27">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L27">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M27">
         <v>4</v>
       </c>
       <c r="N27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O27">
         <v>6</v>
       </c>
       <c r="P27">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="Q27">
         <v>1</v>
       </c>
       <c r="R27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S27">
-        <v>8.9</v>
+        <v>3.8</v>
       </c>
       <c r="T27">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U27">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="V27">
         <v>4</v>
@@ -2527,61 +2530,61 @@
         <v>101</v>
       </c>
       <c r="D28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F28">
         <v>1</v>
       </c>
       <c r="G28">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K28">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N28">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O28">
         <v>6</v>
       </c>
       <c r="P28">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R28">
         <v>3</v>
       </c>
       <c r="S28">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T28">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U28">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="V28">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -2592,64 +2595,64 @@
         <v>49</v>
       </c>
       <c r="C29" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D29">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E29">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H29">
         <v>3</v>
       </c>
       <c r="I29">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J29">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K29">
         <v>5</v>
       </c>
       <c r="L29">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M29">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N29">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O29">
         <v>6</v>
       </c>
       <c r="P29">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="Q29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R29">
         <v>3</v>
       </c>
       <c r="S29">
-        <v>3.8</v>
+        <v>5.2</v>
       </c>
       <c r="T29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U29">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="V29">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30" spans="1:22">
@@ -2660,37 +2663,37 @@
         <v>50</v>
       </c>
       <c r="C30" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D30">
         <v>3</v>
       </c>
       <c r="E30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G30">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H30">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K30">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L30">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M30">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N30">
         <v>5</v>
@@ -2699,25 +2702,25 @@
         <v>6</v>
       </c>
       <c r="P30">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="Q30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R30">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S30">
-        <v>8.4</v>
+        <v>6.5</v>
       </c>
       <c r="T30">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="U30">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="V30">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:22">
@@ -2728,28 +2731,28 @@
         <v>51</v>
       </c>
       <c r="C31" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D31">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I31">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J31">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K31">
         <v>5</v>
@@ -2758,34 +2761,34 @@
         <v>4</v>
       </c>
       <c r="M31">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N31">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O31">
         <v>6</v>
       </c>
       <c r="P31">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="Q31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R31">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S31">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="T31">
         <v>4</v>
       </c>
       <c r="U31">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V31">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:22">
@@ -2796,19 +2799,19 @@
         <v>52</v>
       </c>
       <c r="C32" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D32">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F32">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H32">
         <v>2</v>
@@ -2817,40 +2820,40 @@
         <v>5</v>
       </c>
       <c r="J32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K32">
         <v>6</v>
       </c>
       <c r="L32">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M32">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O32">
         <v>6</v>
       </c>
       <c r="P32">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="Q32">
         <v>1</v>
       </c>
       <c r="R32">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S32">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="T32">
         <v>5</v>
       </c>
       <c r="U32">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="V32">
         <v>3</v>
@@ -2864,7 +2867,7 @@
         <v>53</v>
       </c>
       <c r="C33" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D33">
         <v>2</v>
@@ -2873,52 +2876,52 @@
         <v>1</v>
       </c>
       <c r="F33">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H33">
         <v>1</v>
       </c>
       <c r="I33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L33">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N33">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O33">
         <v>6</v>
       </c>
       <c r="P33">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Q33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R33">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S33">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="T33">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="V33">
         <v>4</v>
@@ -2932,61 +2935,61 @@
         <v>54</v>
       </c>
       <c r="C34" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E34">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G34">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H34">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I34">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J34">
         <v>4</v>
       </c>
       <c r="K34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L34">
         <v>4</v>
       </c>
       <c r="M34">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O34">
         <v>6</v>
       </c>
       <c r="P34">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Q34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R34">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S34">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="T34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U34">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="V34">
         <v>3</v>
@@ -3000,40 +3003,40 @@
         <v>55</v>
       </c>
       <c r="C35" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D35">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E35">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F35">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G35">
         <v>2</v>
       </c>
       <c r="H35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I35">
         <v>5</v>
       </c>
       <c r="J35">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K35">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L35">
         <v>3</v>
       </c>
       <c r="M35">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N35">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O35">
         <v>6</v>
@@ -3048,16 +3051,16 @@
         <v>3</v>
       </c>
       <c r="S35">
-        <v>4.4</v>
+        <v>1.8</v>
       </c>
       <c r="T35">
         <v>6</v>
       </c>
       <c r="U35">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="V35">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:22">
@@ -3068,64 +3071,64 @@
         <v>56</v>
       </c>
       <c r="C36" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E36">
         <v>1</v>
       </c>
       <c r="F36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G36">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H36">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I36">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J36">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K36">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L36">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M36">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N36">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O36">
         <v>6</v>
       </c>
       <c r="P36">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S36">
-        <v>8.5</v>
+        <v>2.6</v>
       </c>
       <c r="T36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U36">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="V36">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37" spans="1:22">
@@ -3139,61 +3142,61 @@
         <v>102</v>
       </c>
       <c r="D37">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F37">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G37">
         <v>4</v>
       </c>
       <c r="H37">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I37">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J37">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K37">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L37">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O37">
         <v>6</v>
       </c>
       <c r="P37">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="Q37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R37">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S37">
-        <v>2.1</v>
+        <v>3.6</v>
       </c>
       <c r="T37">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U37">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V37">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38" spans="1:22">
@@ -3204,61 +3207,61 @@
         <v>58</v>
       </c>
       <c r="C38" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D38">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F38">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G38">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I38">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J38">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K38">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L38">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M38">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N38">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O38">
         <v>6</v>
       </c>
       <c r="P38">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="Q38">
         <v>1</v>
       </c>
       <c r="R38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S38">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="T38">
         <v>5</v>
       </c>
       <c r="U38">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="V38">
         <v>4</v>
@@ -3272,64 +3275,64 @@
         <v>59</v>
       </c>
       <c r="C39" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D39">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F39">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H39">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I39">
         <v>6</v>
       </c>
       <c r="J39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K39">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L39">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M39">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N39">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O39">
         <v>6</v>
       </c>
       <c r="P39">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="Q39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R39">
         <v>3</v>
       </c>
       <c r="S39">
-        <v>2.8</v>
+        <v>6.3</v>
       </c>
       <c r="T39">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U39">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="V39">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40" spans="1:22">
@@ -3340,10 +3343,10 @@
         <v>60</v>
       </c>
       <c r="C40" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E40">
         <v>3</v>
@@ -3355,46 +3358,46 @@
         <v>1</v>
       </c>
       <c r="H40">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I40">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J40">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K40">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L40">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M40">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N40">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O40">
         <v>6</v>
       </c>
       <c r="P40">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="Q40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S40">
-        <v>4.4</v>
+        <v>1.8</v>
       </c>
       <c r="T40">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U40">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="V40">
         <v>3</v>
@@ -3411,34 +3414,34 @@
         <v>103</v>
       </c>
       <c r="D41">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E41">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F41">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G41">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H41">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I41">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J41">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L41">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M41">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N41">
         <v>6</v>
@@ -3447,19 +3450,19 @@
         <v>6</v>
       </c>
       <c r="P41">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="Q41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R41">
         <v>5</v>
       </c>
       <c r="S41">
-        <v>10.2</v>
+        <v>2.9</v>
       </c>
       <c r="T41">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U41">
         <v>13</v>
@@ -3476,7 +3479,7 @@
         <v>62</v>
       </c>
       <c r="C42" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D42">
         <v>1</v>
@@ -3488,28 +3491,28 @@
         <v>2</v>
       </c>
       <c r="G42">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H42">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J42">
         <v>4</v>
       </c>
       <c r="K42">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L42">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M42">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N42">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O42">
         <v>6</v>
@@ -3524,16 +3527,16 @@
         <v>4</v>
       </c>
       <c r="S42">
-        <v>5.9</v>
+        <v>3.3</v>
       </c>
       <c r="T42">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U42">
         <v>14</v>
       </c>
       <c r="V42">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43" spans="1:22">
@@ -3544,13 +3547,13 @@
         <v>63</v>
       </c>
       <c r="C43" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D43">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F43">
         <v>1</v>
@@ -3559,7 +3562,7 @@
         <v>1</v>
       </c>
       <c r="H43">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I43">
         <v>6</v>
@@ -3568,40 +3571,40 @@
         <v>7</v>
       </c>
       <c r="K43">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L43">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M43">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N43">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O43">
         <v>6</v>
       </c>
       <c r="P43">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="Q43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R43">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S43">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="T43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U43">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="V43">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44" spans="1:22">
@@ -3615,22 +3618,22 @@
         <v>103</v>
       </c>
       <c r="D44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F44">
         <v>1</v>
       </c>
       <c r="G44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H44">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I44">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J44">
         <v>4</v>
@@ -3639,37 +3642,37 @@
         <v>3</v>
       </c>
       <c r="L44">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M44">
         <v>4</v>
       </c>
       <c r="N44">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O44">
         <v>6</v>
       </c>
       <c r="P44">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="Q44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R44">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S44">
-        <v>6.5</v>
+        <v>7.9</v>
       </c>
       <c r="T44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U44">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V44">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45" spans="1:22">
@@ -3680,31 +3683,31 @@
         <v>65</v>
       </c>
       <c r="C45" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D45">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E45">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F45">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H45">
         <v>1</v>
       </c>
       <c r="I45">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J45">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K45">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L45">
         <v>6</v>
@@ -3713,28 +3716,28 @@
         <v>6</v>
       </c>
       <c r="N45">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O45">
         <v>6</v>
       </c>
       <c r="P45">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="Q45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R45">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S45">
-        <v>5.7</v>
+        <v>2.6</v>
       </c>
       <c r="T45">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U45">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="V45">
         <v>3</v>
@@ -3748,64 +3751,64 @@
         <v>66</v>
       </c>
       <c r="C46" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G46">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H46">
         <v>3</v>
       </c>
       <c r="I46">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J46">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K46">
         <v>3</v>
       </c>
       <c r="L46">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M46">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O46">
         <v>6</v>
       </c>
       <c r="P46">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="Q46">
         <v>2</v>
       </c>
       <c r="R46">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S46">
-        <v>12</v>
+        <v>6.4</v>
       </c>
       <c r="T46">
         <v>6</v>
       </c>
       <c r="U46">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="V46">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:22">
@@ -3816,64 +3819,64 @@
         <v>67</v>
       </c>
       <c r="C47" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E47">
         <v>4</v>
       </c>
       <c r="F47">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G47">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H47">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I47">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J47">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K47">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L47">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M47">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N47">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O47">
         <v>6</v>
       </c>
       <c r="P47">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q47">
         <v>1</v>
       </c>
       <c r="R47">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S47">
-        <v>10.6</v>
+        <v>5.7</v>
       </c>
       <c r="T47">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U47">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="V47">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48" spans="1:22">
@@ -3884,37 +3887,37 @@
         <v>68</v>
       </c>
       <c r="C48" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D48">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E48">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F48">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I48">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J48">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K48">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L48">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M48">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N48">
         <v>6</v>
@@ -3923,25 +3926,25 @@
         <v>6</v>
       </c>
       <c r="P48">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="Q48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R48">
         <v>4</v>
       </c>
       <c r="S48">
-        <v>6.7</v>
+        <v>3.6</v>
       </c>
       <c r="T48">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U48">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V48">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49" spans="1:22">
@@ -3952,13 +3955,13 @@
         <v>69</v>
       </c>
       <c r="C49" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D49">
         <v>1</v>
       </c>
       <c r="E49">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F49">
         <v>1</v>
@@ -3967,25 +3970,25 @@
         <v>1</v>
       </c>
       <c r="H49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I49">
         <v>5</v>
       </c>
       <c r="J49">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K49">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L49">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M49">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N49">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O49">
         <v>6</v>
@@ -3994,19 +3997,19 @@
         <v>43</v>
       </c>
       <c r="Q49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R49">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S49">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="T49">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U49">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="V49">
         <v>4</v>
@@ -4020,7 +4023,7 @@
         <v>70</v>
       </c>
       <c r="C50" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D50">
         <v>1</v>
@@ -4029,37 +4032,37 @@
         <v>1</v>
       </c>
       <c r="F50">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I50">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J50">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K50">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L50">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M50">
         <v>4</v>
       </c>
       <c r="N50">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O50">
         <v>6</v>
       </c>
       <c r="P50">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="Q50">
         <v>2</v>
@@ -4068,16 +4071,16 @@
         <v>3</v>
       </c>
       <c r="S50">
-        <v>6.2</v>
+        <v>2.2</v>
       </c>
       <c r="T50">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U50">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="V50">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51" spans="1:22">
@@ -4088,46 +4091,46 @@
         <v>71</v>
       </c>
       <c r="C51" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D51">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E51">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G51">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H51">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I51">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J51">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M51">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N51">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O51">
         <v>6</v>
       </c>
       <c r="P51">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="Q51">
         <v>2</v>
@@ -4136,10 +4139,10 @@
         <v>3</v>
       </c>
       <c r="S51">
-        <v>4.5</v>
+        <v>7.2</v>
       </c>
       <c r="T51">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U51">
         <v>9</v>
@@ -4156,10 +4159,10 @@
         <v>72</v>
       </c>
       <c r="C52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D52">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E52">
         <v>2</v>
@@ -4168,16 +4171,16 @@
         <v>2</v>
       </c>
       <c r="G52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H52">
         <v>1</v>
       </c>
       <c r="I52">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J52">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K52">
         <v>6</v>
@@ -4186,34 +4189,34 @@
         <v>5</v>
       </c>
       <c r="M52">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N52">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O52">
         <v>6</v>
       </c>
       <c r="P52">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="Q52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R52">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S52">
-        <v>9.6</v>
+        <v>6.8</v>
       </c>
       <c r="T52">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U52">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="V52">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53" spans="1:22">
@@ -4227,43 +4230,43 @@
         <v>102</v>
       </c>
       <c r="D53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E53">
         <v>1</v>
       </c>
       <c r="F53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G53">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I53">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J53">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K53">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L53">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M53">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N53">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O53">
         <v>6</v>
       </c>
       <c r="P53">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="Q53">
         <v>1</v>
@@ -4272,16 +4275,16 @@
         <v>3</v>
       </c>
       <c r="S53">
-        <v>10.3</v>
+        <v>5</v>
       </c>
       <c r="T53">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U53">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="V53">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54" spans="1:22">
@@ -4295,58 +4298,58 @@
         <v>102</v>
       </c>
       <c r="D54">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E54">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F54">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G54">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H54">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I54">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J54">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K54">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L54">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M54">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N54">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O54">
         <v>6</v>
       </c>
       <c r="P54">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="Q54">
         <v>1</v>
       </c>
       <c r="R54">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S54">
-        <v>3.9</v>
+        <v>7.3</v>
       </c>
       <c r="T54">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U54">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="V54">
         <v>3</v>
@@ -4363,58 +4366,58 @@
         <v>102</v>
       </c>
       <c r="D55">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E55">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F55">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G55">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H55">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I55">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J55">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K55">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L55">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M55">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N55">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O55">
         <v>6</v>
       </c>
       <c r="P55">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="Q55">
         <v>1</v>
       </c>
       <c r="R55">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S55">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="T55">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U55">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="V55">
         <v>4</v>
@@ -4431,58 +4434,58 @@
         <v>102</v>
       </c>
       <c r="D56">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E56">
         <v>2</v>
       </c>
       <c r="F56">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G56">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I56">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J56">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K56">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L56">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M56">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N56">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O56">
         <v>6</v>
       </c>
       <c r="P56">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="Q56">
         <v>1</v>
       </c>
       <c r="R56">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S56">
-        <v>6.6</v>
+        <v>11.5</v>
       </c>
       <c r="T56">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="U56">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="V56">
         <v>4</v>
@@ -4502,19 +4505,19 @@
         <v>2</v>
       </c>
       <c r="E57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G57">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I57">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J57">
         <v>7</v>
@@ -4535,25 +4538,25 @@
         <v>6</v>
       </c>
       <c r="P57">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="Q57">
         <v>1</v>
       </c>
       <c r="R57">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S57">
-        <v>7</v>
+        <v>2.3</v>
       </c>
       <c r="T57">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="U57">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="V57">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="58" spans="1:22">
@@ -4570,10 +4573,10 @@
         <v>3</v>
       </c>
       <c r="E58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F58">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G58">
         <v>2</v>
@@ -4582,43 +4585,43 @@
         <v>2</v>
       </c>
       <c r="I58">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J58">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K58">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L58">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M58">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N58">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O58">
         <v>6</v>
       </c>
       <c r="P58">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q58">
         <v>2</v>
       </c>
       <c r="R58">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S58">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="T58">
         <v>6</v>
       </c>
       <c r="U58">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="V58">
         <v>4</v>
@@ -4632,46 +4635,46 @@
         <v>79</v>
       </c>
       <c r="C59" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D59">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E59">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F59">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G59">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H59">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I59">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J59">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K59">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L59">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M59">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N59">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O59">
         <v>6</v>
       </c>
       <c r="P59">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="Q59">
         <v>1</v>
@@ -4679,14 +4682,11 @@
       <c r="R59">
         <v>3</v>
       </c>
-      <c r="S59">
-        <v>3.9</v>
-      </c>
       <c r="T59">
         <v>4</v>
       </c>
       <c r="U59">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="V59">
         <v>3</v>
@@ -4703,58 +4703,58 @@
         <v>101</v>
       </c>
       <c r="D60">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E60">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F60">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G60">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H60">
         <v>1</v>
       </c>
       <c r="I60">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J60">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K60">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L60">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M60">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N60">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O60">
         <v>6</v>
       </c>
       <c r="P60">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="Q60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R60">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S60">
-        <v>9.4</v>
+        <v>10.6</v>
       </c>
       <c r="T60">
         <v>4</v>
       </c>
       <c r="U60">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="V60">
         <v>3</v>
@@ -4771,58 +4771,58 @@
         <v>103</v>
       </c>
       <c r="D61">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E61">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G61">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H61">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I61">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J61">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K61">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L61">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M61">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N61">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O61">
         <v>6</v>
       </c>
       <c r="P61">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="Q61">
         <v>1</v>
       </c>
       <c r="R61">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S61">
-        <v>2.2</v>
+        <v>5.6</v>
       </c>
       <c r="T61">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U61">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="V61">
         <v>3</v>
@@ -4839,34 +4839,34 @@
         <v>103</v>
       </c>
       <c r="D62">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E62">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F62">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G62">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H62">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I62">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J62">
         <v>7</v>
       </c>
       <c r="K62">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L62">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M62">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N62">
         <v>7</v>
@@ -4875,25 +4875,25 @@
         <v>6</v>
       </c>
       <c r="P62">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q62">
         <v>1</v>
       </c>
       <c r="R62">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S62">
-        <v>6.4</v>
+        <v>9.9</v>
       </c>
       <c r="T62">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U62">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="V62">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63" spans="1:22">
@@ -4907,61 +4907,61 @@
         <v>101</v>
       </c>
       <c r="D63">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E63">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F63">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G63">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H63">
         <v>3</v>
       </c>
       <c r="I63">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J63">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K63">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L63">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M63">
         <v>4</v>
       </c>
       <c r="N63">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O63">
         <v>6</v>
       </c>
       <c r="P63">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="Q63">
         <v>1</v>
       </c>
       <c r="R63">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S63">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="T63">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U63">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="V63">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64" spans="1:22">
@@ -4975,58 +4975,61 @@
         <v>101</v>
       </c>
       <c r="D64">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E64">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F64">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H64">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I64">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J64">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K64">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L64">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M64">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N64">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O64">
         <v>6</v>
       </c>
+      <c r="P64">
+        <v>37</v>
+      </c>
       <c r="Q64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R64">
         <v>3</v>
       </c>
       <c r="S64">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="T64">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="U64">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="V64">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65" spans="1:22">
@@ -5040,61 +5043,61 @@
         <v>101</v>
       </c>
       <c r="D65">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E65">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F65">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H65">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I65">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J65">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K65">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L65">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M65">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N65">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O65">
         <v>6</v>
       </c>
       <c r="P65">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="Q65">
         <v>2</v>
       </c>
       <c r="R65">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S65">
-        <v>7.9</v>
+        <v>6.4</v>
       </c>
       <c r="T65">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U65">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="V65">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66" spans="1:22">
@@ -5108,58 +5111,58 @@
         <v>101</v>
       </c>
       <c r="D66">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E66">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F66">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G66">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H66">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I66">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J66">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K66">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L66">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M66">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N66">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O66">
         <v>6</v>
       </c>
       <c r="P66">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="Q66">
         <v>1</v>
       </c>
       <c r="R66">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S66">
-        <v>7.5</v>
+        <v>5.1</v>
       </c>
       <c r="T66">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U66">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="V66">
         <v>3</v>
@@ -5179,22 +5182,22 @@
         <v>1</v>
       </c>
       <c r="E67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F67">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G67">
         <v>3</v>
       </c>
       <c r="H67">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I67">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J67">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K67">
         <v>5</v>
@@ -5206,31 +5209,31 @@
         <v>3</v>
       </c>
       <c r="N67">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O67">
         <v>6</v>
       </c>
       <c r="P67">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="Q67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R67">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S67">
-        <v>3.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="T67">
         <v>6</v>
       </c>
       <c r="U67">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="V67">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68" spans="1:22">
@@ -5247,31 +5250,31 @@
         <v>2</v>
       </c>
       <c r="E68">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F68">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G68">
         <v>2</v>
       </c>
       <c r="H68">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I68">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J68">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K68">
         <v>6</v>
       </c>
       <c r="L68">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M68">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="N68">
         <v>5</v>
@@ -5280,22 +5283,22 @@
         <v>6</v>
       </c>
       <c r="P68">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Q68">
         <v>1</v>
       </c>
       <c r="R68">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S68">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="T68">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U68">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="V68">
         <v>3</v>
@@ -5312,43 +5315,43 @@
         <v>101</v>
       </c>
       <c r="D69">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E69">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G69">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H69">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I69">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J69">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K69">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L69">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M69">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N69">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O69">
         <v>6</v>
       </c>
       <c r="P69">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="Q69">
         <v>1</v>
@@ -5357,16 +5360,16 @@
         <v>4</v>
       </c>
       <c r="S69">
-        <v>7.5</v>
+        <v>3.4</v>
       </c>
       <c r="T69">
         <v>3</v>
       </c>
       <c r="U69">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="V69">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:22">
@@ -5383,25 +5386,25 @@
         <v>2</v>
       </c>
       <c r="E70">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F70">
         <v>1</v>
       </c>
       <c r="G70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H70">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I70">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J70">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K70">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L70">
         <v>5</v>
@@ -5410,31 +5413,31 @@
         <v>5</v>
       </c>
       <c r="N70">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O70">
         <v>6</v>
       </c>
       <c r="P70">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="Q70">
         <v>1</v>
       </c>
       <c r="R70">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S70">
-        <v>12</v>
+        <v>4.6</v>
       </c>
       <c r="T70">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U70">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="V70">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71" spans="1:22">
@@ -5448,10 +5451,10 @@
         <v>103</v>
       </c>
       <c r="D71">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E71">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F71">
         <v>1</v>
@@ -5460,49 +5463,49 @@
         <v>1</v>
       </c>
       <c r="H71">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I71">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J71">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K71">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L71">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M71">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N71">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O71">
         <v>6</v>
       </c>
       <c r="P71">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Q71">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R71">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S71">
-        <v>3</v>
+        <v>5.8</v>
       </c>
       <c r="T71">
         <v>5</v>
       </c>
       <c r="U71">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="V71">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72" spans="1:22">
@@ -5516,34 +5519,34 @@
         <v>101</v>
       </c>
       <c r="D72">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E72">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F72">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G72">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H72">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I72">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J72">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K72">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L72">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M72">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N72">
         <v>7</v>
@@ -5552,7 +5555,7 @@
         <v>6</v>
       </c>
       <c r="P72">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="Q72">
         <v>2</v>
@@ -5561,16 +5564,16 @@
         <v>3</v>
       </c>
       <c r="S72">
-        <v>3.4</v>
+        <v>6.9</v>
       </c>
       <c r="T72">
         <v>5</v>
       </c>
       <c r="U72">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V72">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73" spans="1:22">
@@ -5584,61 +5587,61 @@
         <v>102</v>
       </c>
       <c r="D73">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E73">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F73">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G73">
         <v>2</v>
       </c>
       <c r="H73">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I73">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J73">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K73">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L73">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M73">
         <v>7</v>
       </c>
       <c r="N73">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O73">
         <v>6</v>
       </c>
       <c r="P73">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="Q73">
         <v>1</v>
       </c>
       <c r="R73">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S73">
-        <v>7.6</v>
+        <v>6.5</v>
       </c>
       <c r="T73">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U73">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="V73">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74" spans="1:22">
@@ -5652,58 +5655,58 @@
         <v>101</v>
       </c>
       <c r="D74">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H74">
         <v>2</v>
       </c>
       <c r="I74">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J74">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K74">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L74">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M74">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N74">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O74">
         <v>6</v>
       </c>
       <c r="P74">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="Q74">
         <v>2</v>
       </c>
       <c r="R74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S74">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="T74">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U74">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="V74">
         <v>4</v>
@@ -5720,61 +5723,61 @@
         <v>101</v>
       </c>
       <c r="D75">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G75">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I75">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J75">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K75">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L75">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M75">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N75">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O75">
         <v>6</v>
       </c>
       <c r="P75">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="Q75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R75">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S75">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="T75">
         <v>5</v>
       </c>
       <c r="U75">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="V75">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76" spans="1:22">
@@ -5791,55 +5794,55 @@
         <v>4</v>
       </c>
       <c r="E76">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F76">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G76">
         <v>2</v>
       </c>
       <c r="H76">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I76">
         <v>4</v>
       </c>
       <c r="J76">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K76">
         <v>3</v>
       </c>
       <c r="L76">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M76">
         <v>3</v>
       </c>
       <c r="N76">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O76">
         <v>6</v>
       </c>
       <c r="P76">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q76">
         <v>1</v>
       </c>
       <c r="R76">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S76">
-        <v>5.1</v>
+        <v>18</v>
       </c>
       <c r="T76">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U76">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="V76">
         <v>3</v>
@@ -5856,34 +5859,34 @@
         <v>103</v>
       </c>
       <c r="D77">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E77">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F77">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G77">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H77">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I77">
         <v>3</v>
       </c>
       <c r="J77">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K77">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L77">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M77">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N77">
         <v>3</v>
@@ -5892,7 +5895,7 @@
         <v>6</v>
       </c>
       <c r="P77">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="Q77">
         <v>1</v>
@@ -5901,16 +5904,16 @@
         <v>3</v>
       </c>
       <c r="S77">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="T77">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U77">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V77">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78" spans="1:22">
@@ -5924,28 +5927,28 @@
         <v>103</v>
       </c>
       <c r="D78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F78">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G78">
         <v>3</v>
       </c>
       <c r="H78">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I78">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J78">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K78">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L78">
         <v>6</v>
@@ -5954,31 +5957,31 @@
         <v>6</v>
       </c>
       <c r="N78">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O78">
         <v>6</v>
       </c>
       <c r="P78">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="Q78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R78">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S78">
-        <v>10</v>
+        <v>3.1</v>
       </c>
       <c r="T78">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U78">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="V78">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79" spans="1:22">
@@ -5992,16 +5995,16 @@
         <v>101</v>
       </c>
       <c r="D79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E79">
         <v>3</v>
       </c>
       <c r="F79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G79">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H79">
         <v>1</v>
@@ -6010,43 +6013,43 @@
         <v>5</v>
       </c>
       <c r="J79">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K79">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L79">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M79">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N79">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O79">
         <v>6</v>
       </c>
       <c r="P79">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="Q79">
         <v>1</v>
       </c>
       <c r="R79">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S79">
-        <v>9.1</v>
+        <v>8.4</v>
       </c>
       <c r="T79">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U79">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="V79">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80" spans="1:22">
@@ -6060,52 +6063,49 @@
         <v>101</v>
       </c>
       <c r="D80">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F80">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G80">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H80">
         <v>2</v>
       </c>
       <c r="I80">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J80">
         <v>5</v>
       </c>
       <c r="K80">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L80">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M80">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N80">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O80">
         <v>6</v>
       </c>
       <c r="P80">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="Q80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R80">
-        <v>2</v>
-      </c>
-      <c r="S80">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="T80">
         <v>5</v>
@@ -6114,7 +6114,7 @@
         <v>22</v>
       </c>
       <c r="V80">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/data/T3_leader_cleaned.xlsx
+++ b/data/T3_leader_cleaned.xlsx
@@ -85,238 +85,238 @@
     <t>A_L13</t>
   </si>
   <si>
+    <t>A_L19</t>
+  </si>
+  <si>
+    <t>A_L07</t>
+  </si>
+  <si>
+    <t>B_L10</t>
+  </si>
+  <si>
+    <t>B_L06</t>
+  </si>
+  <si>
+    <t>C_L19</t>
+  </si>
+  <si>
+    <t>C_L25</t>
+  </si>
+  <si>
+    <t>A_L10</t>
+  </si>
+  <si>
+    <t>A_L09</t>
+  </si>
+  <si>
+    <t>B_L24</t>
+  </si>
+  <si>
+    <t>B_L22</t>
+  </si>
+  <si>
+    <t>C_L10</t>
+  </si>
+  <si>
+    <t>B_L30</t>
+  </si>
+  <si>
+    <t>C_L01</t>
+  </si>
+  <si>
+    <t>B_L08</t>
+  </si>
+  <si>
+    <t>B_L09</t>
+  </si>
+  <si>
+    <t>A_L26</t>
+  </si>
+  <si>
+    <t>C_L05</t>
+  </si>
+  <si>
+    <t>A_L14</t>
+  </si>
+  <si>
+    <t>C_L07</t>
+  </si>
+  <si>
+    <t>B_L05</t>
+  </si>
+  <si>
+    <t>C_L12</t>
+  </si>
+  <si>
+    <t>C_L21</t>
+  </si>
+  <si>
+    <t>A_L28</t>
+  </si>
+  <si>
+    <t>C_L18</t>
+  </si>
+  <si>
+    <t>C_L06</t>
+  </si>
+  <si>
     <t>A_L18</t>
   </si>
   <si>
-    <t>A_L07</t>
-  </si>
-  <si>
-    <t>B_L09</t>
-  </si>
-  <si>
-    <t>B_L05</t>
+    <t>B_L01</t>
+  </si>
+  <si>
+    <t>A_L05</t>
+  </si>
+  <si>
+    <t>C_L24</t>
+  </si>
+  <si>
+    <t>A_L12</t>
+  </si>
+  <si>
+    <t>C_L29</t>
+  </si>
+  <si>
+    <t>B_L26</t>
+  </si>
+  <si>
+    <t>C_L09</t>
+  </si>
+  <si>
+    <t>B_L25</t>
+  </si>
+  <si>
+    <t>B_L27</t>
+  </si>
+  <si>
+    <t>C_L03</t>
+  </si>
+  <si>
+    <t>A_L20</t>
+  </si>
+  <si>
+    <t>C_L30</t>
+  </si>
+  <si>
+    <t>C_L27</t>
+  </si>
+  <si>
+    <t>B_L02</t>
+  </si>
+  <si>
+    <t>C_L17</t>
+  </si>
+  <si>
+    <t>C_L22</t>
+  </si>
+  <si>
+    <t>B_L04</t>
   </si>
   <si>
     <t>C_L20</t>
   </si>
   <si>
+    <t>B_L11</t>
+  </si>
+  <si>
+    <t>A_L17</t>
+  </si>
+  <si>
+    <t>C_L02</t>
+  </si>
+  <si>
+    <t>B_L20</t>
+  </si>
+  <si>
+    <t>A_L08</t>
+  </si>
+  <si>
+    <t>B_L19</t>
+  </si>
+  <si>
+    <t>B_L03</t>
+  </si>
+  <si>
+    <t>B_L07</t>
+  </si>
+  <si>
+    <t>B_L23</t>
+  </si>
+  <si>
+    <t>B_L16</t>
+  </si>
+  <si>
+    <t>A_L06</t>
+  </si>
+  <si>
+    <t>C_L14</t>
+  </si>
+  <si>
+    <t>B_L29</t>
+  </si>
+  <si>
+    <t>A_L02</t>
+  </si>
+  <si>
+    <t>C_L08</t>
+  </si>
+  <si>
+    <t>C_L11</t>
+  </si>
+  <si>
+    <t>A_L03</t>
+  </si>
+  <si>
+    <t>A_L25</t>
+  </si>
+  <si>
+    <t>A_L29</t>
+  </si>
+  <si>
+    <t>A_L15</t>
+  </si>
+  <si>
+    <t>B_L15</t>
+  </si>
+  <si>
+    <t>B_L21</t>
+  </si>
+  <si>
+    <t>A_L23</t>
+  </si>
+  <si>
+    <t>B_L14</t>
+  </si>
+  <si>
     <t>C_L26</t>
   </si>
   <si>
-    <t>A_L10</t>
-  </si>
-  <si>
-    <t>A_L09</t>
-  </si>
-  <si>
-    <t>B_L23</t>
-  </si>
-  <si>
-    <t>B_L21</t>
-  </si>
-  <si>
-    <t>C_L13</t>
-  </si>
-  <si>
-    <t>B_L29</t>
-  </si>
-  <si>
-    <t>C_L01</t>
-  </si>
-  <si>
-    <t>B_L07</t>
-  </si>
-  <si>
-    <t>B_L08</t>
-  </si>
-  <si>
-    <t>A_L25</t>
-  </si>
-  <si>
-    <t>C_L06</t>
-  </si>
-  <si>
-    <t>A_L14</t>
-  </si>
-  <si>
-    <t>C_L10</t>
-  </si>
-  <si>
-    <t>B_L04</t>
-  </si>
-  <si>
-    <t>C_L16</t>
-  </si>
-  <si>
-    <t>C_L22</t>
+    <t>A_L11</t>
+  </si>
+  <si>
+    <t>B_L18</t>
+  </si>
+  <si>
+    <t>A_L22</t>
+  </si>
+  <si>
+    <t>A_L24</t>
+  </si>
+  <si>
+    <t>A_L01</t>
+  </si>
+  <si>
+    <t>C_L23</t>
+  </si>
+  <si>
+    <t>C_L04</t>
+  </si>
+  <si>
+    <t>A_L04</t>
   </si>
   <si>
     <t>A_L27</t>
-  </si>
-  <si>
-    <t>C_L19</t>
-  </si>
-  <si>
-    <t>C_L07</t>
-  </si>
-  <si>
-    <t>A_L17</t>
-  </si>
-  <si>
-    <t>A_L29</t>
-  </si>
-  <si>
-    <t>B_L06</t>
-  </si>
-  <si>
-    <t>A_L05</t>
-  </si>
-  <si>
-    <t>C_L25</t>
-  </si>
-  <si>
-    <t>A_L12</t>
-  </si>
-  <si>
-    <t>C_L29</t>
-  </si>
-  <si>
-    <t>B_L25</t>
-  </si>
-  <si>
-    <t>C_L12</t>
-  </si>
-  <si>
-    <t>B_L24</t>
-  </si>
-  <si>
-    <t>B_L26</t>
-  </si>
-  <si>
-    <t>C_L04</t>
-  </si>
-  <si>
-    <t>A_L19</t>
-  </si>
-  <si>
-    <t>C_L30</t>
-  </si>
-  <si>
-    <t>C_L28</t>
-  </si>
-  <si>
-    <t>B_L01</t>
-  </si>
-  <si>
-    <t>C_L18</t>
-  </si>
-  <si>
-    <t>C_L23</t>
-  </si>
-  <si>
-    <t>B_L03</t>
-  </si>
-  <si>
-    <t>C_L21</t>
-  </si>
-  <si>
-    <t>B_L10</t>
-  </si>
-  <si>
-    <t>A_L16</t>
-  </si>
-  <si>
-    <t>C_L03</t>
-  </si>
-  <si>
-    <t>B_L18</t>
-  </si>
-  <si>
-    <t>A_L08</t>
-  </si>
-  <si>
-    <t>B_L16</t>
-  </si>
-  <si>
-    <t>B_L02</t>
-  </si>
-  <si>
-    <t>B_L22</t>
-  </si>
-  <si>
-    <t>B_L14</t>
-  </si>
-  <si>
-    <t>A_L06</t>
-  </si>
-  <si>
-    <t>C_L17</t>
-  </si>
-  <si>
-    <t>B_L27</t>
-  </si>
-  <si>
-    <t>A_L02</t>
-  </si>
-  <si>
-    <t>C_L11</t>
-  </si>
-  <si>
-    <t>C_L14</t>
-  </si>
-  <si>
-    <t>A_L03</t>
-  </si>
-  <si>
-    <t>A_L24</t>
-  </si>
-  <si>
-    <t>A_L28</t>
-  </si>
-  <si>
-    <t>A_L15</t>
-  </si>
-  <si>
-    <t>B_L12</t>
-  </si>
-  <si>
-    <t>B_L19</t>
-  </si>
-  <si>
-    <t>A_L22</t>
-  </si>
-  <si>
-    <t>B_L11</t>
-  </si>
-  <si>
-    <t>C_L27</t>
-  </si>
-  <si>
-    <t>A_L11</t>
-  </si>
-  <si>
-    <t>B_L15</t>
-  </si>
-  <si>
-    <t>A_L20</t>
-  </si>
-  <si>
-    <t>A_L23</t>
-  </si>
-  <si>
-    <t>A_L01</t>
-  </si>
-  <si>
-    <t>C_L24</t>
-  </si>
-  <si>
-    <t>C_L05</t>
-  </si>
-  <si>
-    <t>A_L04</t>
-  </si>
-  <si>
-    <t>A_L26</t>
   </si>
   <si>
     <t>A</t>
@@ -765,58 +765,58 @@
         <v>101</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G2">
         <v>1</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M2">
         <v>5</v>
       </c>
       <c r="N2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O2">
         <v>6</v>
       </c>
       <c r="P2">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="Q2">
         <v>1</v>
       </c>
       <c r="R2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S2">
-        <v>6</v>
+        <v>8.9</v>
       </c>
       <c r="T2">
         <v>5</v>
       </c>
       <c r="U2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="V2">
         <v>3</v>
@@ -836,7 +836,7 @@
         <v>2</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <v>2</v>
@@ -845,49 +845,49 @@
         <v>2</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O3">
         <v>6</v>
       </c>
       <c r="P3">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="Q3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S3">
-        <v>11.5</v>
+        <v>6.4</v>
       </c>
       <c r="T3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -901,34 +901,34 @@
         <v>101</v>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N4">
         <v>3</v>
@@ -937,7 +937,7 @@
         <v>6</v>
       </c>
       <c r="P4">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="Q4">
         <v>1</v>
@@ -946,16 +946,16 @@
         <v>3</v>
       </c>
       <c r="S4">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="T4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U4">
         <v>20</v>
       </c>
       <c r="V4">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -969,61 +969,61 @@
         <v>102</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J5">
         <v>4</v>
       </c>
       <c r="K5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O5">
         <v>6</v>
       </c>
       <c r="P5">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="Q5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S5">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="T5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U5">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="V5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -1037,61 +1037,61 @@
         <v>102</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J6">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O6">
         <v>6</v>
       </c>
       <c r="P6">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="Q6">
         <v>1</v>
       </c>
       <c r="R6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S6">
-        <v>2.4</v>
+        <v>4.4</v>
       </c>
       <c r="T6">
         <v>8</v>
       </c>
       <c r="U6">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="V6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -1105,16 +1105,16 @@
         <v>103</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H7">
         <v>2</v>
@@ -1126,37 +1126,37 @@
         <v>5</v>
       </c>
       <c r="K7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O7">
         <v>6</v>
       </c>
       <c r="P7">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R7">
         <v>3</v>
       </c>
       <c r="S7">
-        <v>3.7</v>
+        <v>6.6</v>
       </c>
       <c r="T7">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U7">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="V7">
         <v>4</v>
@@ -1173,58 +1173,58 @@
         <v>103</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G8">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H8">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I8">
         <v>4</v>
       </c>
       <c r="J8">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O8">
         <v>6</v>
       </c>
       <c r="P8">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="Q8">
         <v>2</v>
       </c>
       <c r="R8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S8">
-        <v>9</v>
+        <v>2.4</v>
       </c>
       <c r="T8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U8">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="V8">
         <v>4</v>
@@ -1241,61 +1241,61 @@
         <v>101</v>
       </c>
       <c r="D9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I9">
         <v>3</v>
       </c>
       <c r="J9">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K9">
         <v>3</v>
       </c>
       <c r="L9">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M9">
         <v>4</v>
       </c>
       <c r="N9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O9">
         <v>6</v>
       </c>
       <c r="P9">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="Q9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S9">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="T9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U9">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="V9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1309,28 +1309,28 @@
         <v>101</v>
       </c>
       <c r="D10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G10">
         <v>2</v>
       </c>
       <c r="H10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I10">
         <v>6</v>
       </c>
       <c r="J10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L10">
         <v>4</v>
@@ -1339,25 +1339,28 @@
         <v>5</v>
       </c>
       <c r="N10">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O10">
         <v>6</v>
       </c>
+      <c r="P10">
+        <v>49</v>
+      </c>
       <c r="Q10">
         <v>2</v>
       </c>
       <c r="R10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S10">
-        <v>2.6</v>
+        <v>5.9</v>
       </c>
       <c r="T10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U10">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="V10">
         <v>4</v>
@@ -1374,34 +1377,34 @@
         <v>102</v>
       </c>
       <c r="D11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E11">
         <v>2</v>
       </c>
       <c r="F11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H11">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J11">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K11">
         <v>4</v>
       </c>
       <c r="L11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N11">
         <v>4</v>
@@ -1410,25 +1413,25 @@
         <v>6</v>
       </c>
       <c r="P11">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="Q11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S11">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="T11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U11">
         <v>21</v>
       </c>
       <c r="V11">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1442,46 +1445,46 @@
         <v>102</v>
       </c>
       <c r="D12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H12">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K12">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O12">
         <v>6</v>
       </c>
       <c r="P12">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="Q12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R12">
         <v>2</v>
@@ -1490,13 +1493,13 @@
         <v>2.9</v>
       </c>
       <c r="T12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U12">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="V12">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1510,61 +1513,61 @@
         <v>103</v>
       </c>
       <c r="D13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="F13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I13">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J13">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K13">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L13">
         <v>4</v>
       </c>
       <c r="M13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O13">
         <v>6</v>
       </c>
       <c r="P13">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q13">
         <v>1</v>
       </c>
       <c r="R13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S13">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="T13">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U13">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="V13">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -1578,19 +1581,19 @@
         <v>102</v>
       </c>
       <c r="D14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E14">
         <v>4</v>
       </c>
       <c r="F14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G14">
         <v>3</v>
       </c>
       <c r="H14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I14">
         <v>3</v>
@@ -1599,10 +1602,10 @@
         <v>5</v>
       </c>
       <c r="K14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M14">
         <v>3</v>
@@ -1617,22 +1620,22 @@
         <v>47</v>
       </c>
       <c r="Q14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R14">
         <v>3</v>
       </c>
       <c r="S14">
-        <v>5.7</v>
+        <v>2.7</v>
       </c>
       <c r="T14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U14">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="V14">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1646,43 +1649,43 @@
         <v>103</v>
       </c>
       <c r="D15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G15">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H15">
         <v>1</v>
       </c>
       <c r="I15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M15">
         <v>5</v>
       </c>
       <c r="N15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O15">
         <v>6</v>
       </c>
       <c r="P15">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="Q15">
         <v>1</v>
@@ -1691,16 +1694,13 @@
         <v>3</v>
       </c>
       <c r="S15">
-        <v>7.4</v>
-      </c>
-      <c r="T15">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="U15">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="V15">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -1714,31 +1714,31 @@
         <v>102</v>
       </c>
       <c r="D16">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K16">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M16">
         <v>6</v>
@@ -1750,25 +1750,25 @@
         <v>6</v>
       </c>
       <c r="P16">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="Q16">
         <v>2</v>
       </c>
       <c r="R16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S16">
-        <v>9.199999999999999</v>
+        <v>5.6</v>
       </c>
       <c r="T16">
         <v>3</v>
       </c>
       <c r="U16">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="V16">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -1785,55 +1785,55 @@
         <v>3</v>
       </c>
       <c r="E17">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L17">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N17">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O17">
         <v>6</v>
       </c>
       <c r="P17">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="Q17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R17">
         <v>3</v>
       </c>
       <c r="S17">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="T17">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U17">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="V17">
         <v>3</v>
@@ -1850,58 +1850,58 @@
         <v>101</v>
       </c>
       <c r="D18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E18">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F18">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G18">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H18">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I18">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J18">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K18">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M18">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N18">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O18">
         <v>6</v>
       </c>
       <c r="P18">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="Q18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R18">
         <v>4</v>
       </c>
       <c r="S18">
-        <v>3.6</v>
+        <v>12.7</v>
       </c>
       <c r="T18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U18">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V18">
         <v>4</v>
@@ -1924,13 +1924,13 @@
         <v>2</v>
       </c>
       <c r="F19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I19">
         <v>7</v>
@@ -1945,16 +1945,16 @@
         <v>5</v>
       </c>
       <c r="M19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O19">
         <v>6</v>
       </c>
       <c r="P19">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="Q19">
         <v>2</v>
@@ -1963,16 +1963,16 @@
         <v>4</v>
       </c>
       <c r="S19">
+        <v>5.9</v>
+      </c>
+      <c r="T19">
         <v>8</v>
       </c>
-      <c r="T19">
-        <v>4</v>
-      </c>
       <c r="U19">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="V19">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -1989,58 +1989,58 @@
         <v>2</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G20">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I20">
         <v>4</v>
       </c>
       <c r="J20">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K20">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L20">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M20">
         <v>5</v>
       </c>
       <c r="N20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O20">
         <v>6</v>
       </c>
       <c r="P20">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="Q20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R20">
         <v>4</v>
       </c>
       <c r="S20">
-        <v>5.6</v>
+        <v>2.2</v>
       </c>
       <c r="T20">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U20">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="V20">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -2054,58 +2054,58 @@
         <v>103</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G21">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H21">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I21">
         <v>5</v>
       </c>
       <c r="J21">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K21">
         <v>5</v>
       </c>
       <c r="L21">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N21">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O21">
         <v>6</v>
       </c>
       <c r="P21">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S21">
-        <v>1.4</v>
+        <v>4.9</v>
       </c>
       <c r="T21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U21">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="V21">
         <v>4</v>
@@ -2122,7 +2122,7 @@
         <v>102</v>
       </c>
       <c r="D22">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -2134,10 +2134,10 @@
         <v>1</v>
       </c>
       <c r="H22">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I22">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J22">
         <v>5</v>
@@ -2149,7 +2149,7 @@
         <v>5</v>
       </c>
       <c r="M22">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N22">
         <v>6</v>
@@ -2158,25 +2158,25 @@
         <v>6</v>
       </c>
       <c r="P22">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="Q22">
         <v>2</v>
       </c>
       <c r="R22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S22">
-        <v>5.5</v>
+        <v>4.1</v>
       </c>
       <c r="T22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U22">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="V22">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -2190,34 +2190,34 @@
         <v>103</v>
       </c>
       <c r="D23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E23">
         <v>1</v>
       </c>
       <c r="F23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I23">
         <v>5</v>
       </c>
       <c r="J23">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K23">
         <v>7</v>
       </c>
       <c r="L23">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N23">
         <v>7</v>
@@ -2226,22 +2226,22 @@
         <v>6</v>
       </c>
       <c r="P23">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="Q23">
         <v>1</v>
       </c>
       <c r="R23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S23">
-        <v>4.4</v>
+        <v>12.9</v>
       </c>
       <c r="T23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U23">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="V23">
         <v>3</v>
@@ -2261,19 +2261,19 @@
         <v>2</v>
       </c>
       <c r="E24">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F24">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H24">
         <v>2</v>
       </c>
       <c r="I24">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J24">
         <v>7</v>
@@ -2282,37 +2282,37 @@
         <v>4</v>
       </c>
       <c r="L24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M24">
         <v>5</v>
       </c>
       <c r="N24">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O24">
         <v>6</v>
       </c>
       <c r="P24">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="Q24">
         <v>1</v>
       </c>
       <c r="R24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S24">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="T24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U24">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="V24">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -2329,40 +2329,40 @@
         <v>1</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H25">
         <v>1</v>
       </c>
       <c r="I25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J25">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K25">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L25">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M25">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N25">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O25">
         <v>6</v>
       </c>
       <c r="P25">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="Q25">
         <v>1</v>
@@ -2371,13 +2371,13 @@
         <v>3</v>
       </c>
       <c r="S25">
-        <v>11.9</v>
+        <v>6.5</v>
       </c>
       <c r="T25">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="U25">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="V25">
         <v>3</v>
@@ -2394,13 +2394,13 @@
         <v>103</v>
       </c>
       <c r="D26">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -2412,40 +2412,40 @@
         <v>5</v>
       </c>
       <c r="J26">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L26">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N26">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O26">
         <v>6</v>
       </c>
       <c r="P26">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="Q26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R26">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S26">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="T26">
         <v>5</v>
       </c>
       <c r="U26">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="V26">
         <v>4</v>
@@ -2462,61 +2462,61 @@
         <v>103</v>
       </c>
       <c r="D27">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E27">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F27">
         <v>3</v>
       </c>
       <c r="G27">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I27">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J27">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K27">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L27">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M27">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N27">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O27">
         <v>6</v>
       </c>
       <c r="P27">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="Q27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S27">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="T27">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U27">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="V27">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -2530,13 +2530,13 @@
         <v>101</v>
       </c>
       <c r="D28">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E28">
         <v>3</v>
       </c>
       <c r="F28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28">
         <v>4</v>
@@ -2545,43 +2545,43 @@
         <v>2</v>
       </c>
       <c r="I28">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J28">
         <v>7</v>
       </c>
       <c r="K28">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L28">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M28">
         <v>6</v>
       </c>
       <c r="N28">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O28">
         <v>6</v>
       </c>
       <c r="P28">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="Q28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R28">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S28">
-        <v>11</v>
+        <v>2.3</v>
       </c>
       <c r="T28">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U28">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="V28">
         <v>3</v>
@@ -2595,46 +2595,46 @@
         <v>49</v>
       </c>
       <c r="C29" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E29">
         <v>1</v>
       </c>
       <c r="F29">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J29">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L29">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M29">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N29">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O29">
         <v>6</v>
       </c>
       <c r="P29">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="Q29">
         <v>2</v>
@@ -2643,13 +2643,13 @@
         <v>3</v>
       </c>
       <c r="S29">
-        <v>5.2</v>
+        <v>2.6</v>
       </c>
       <c r="T29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U29">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="V29">
         <v>4</v>
@@ -2663,7 +2663,7 @@
         <v>50</v>
       </c>
       <c r="C30" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D30">
         <v>3</v>
@@ -2675,52 +2675,52 @@
         <v>4</v>
       </c>
       <c r="G30">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H30">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J30">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L30">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M30">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N30">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O30">
         <v>6</v>
       </c>
       <c r="P30">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q30">
         <v>1</v>
       </c>
       <c r="R30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S30">
-        <v>6.5</v>
+        <v>2.1</v>
       </c>
       <c r="T30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U30">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="V30">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31" spans="1:22">
@@ -2731,46 +2731,46 @@
         <v>51</v>
       </c>
       <c r="C31" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D31">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E31">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F31">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G31">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H31">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I31">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J31">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K31">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L31">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O31">
         <v>6</v>
       </c>
       <c r="P31">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="Q31">
         <v>2</v>
@@ -2779,16 +2779,16 @@
         <v>3</v>
       </c>
       <c r="S31">
-        <v>3.8</v>
+        <v>7.9</v>
       </c>
       <c r="T31">
         <v>4</v>
       </c>
       <c r="U31">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="V31">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:22">
@@ -2799,61 +2799,61 @@
         <v>52</v>
       </c>
       <c r="C32" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D32">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E32">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F32">
         <v>1</v>
       </c>
       <c r="G32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I32">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L32">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M32">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N32">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O32">
         <v>6</v>
       </c>
       <c r="P32">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="Q32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R32">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S32">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="T32">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U32">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V32">
         <v>3</v>
@@ -2867,46 +2867,46 @@
         <v>53</v>
       </c>
       <c r="C33" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D33">
         <v>2</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F33">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I33">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J33">
         <v>6</v>
       </c>
       <c r="K33">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M33">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N33">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O33">
         <v>6</v>
       </c>
       <c r="P33">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q33">
         <v>1</v>
@@ -2915,16 +2915,16 @@
         <v>4</v>
       </c>
       <c r="S33">
-        <v>3.3</v>
+        <v>11</v>
       </c>
       <c r="T33">
         <v>4</v>
       </c>
       <c r="U33">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="V33">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:22">
@@ -2935,16 +2935,16 @@
         <v>54</v>
       </c>
       <c r="C34" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D34">
         <v>1</v>
       </c>
       <c r="E34">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G34">
         <v>1</v>
@@ -2953,7 +2953,7 @@
         <v>1</v>
       </c>
       <c r="I34">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J34">
         <v>4</v>
@@ -2968,31 +2968,31 @@
         <v>4</v>
       </c>
       <c r="N34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O34">
         <v>6</v>
       </c>
       <c r="P34">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="Q34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R34">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S34">
-        <v>2.2</v>
+        <v>16</v>
       </c>
       <c r="T34">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U34">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="V34">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35" spans="1:22">
@@ -3003,46 +3003,46 @@
         <v>55</v>
       </c>
       <c r="C35" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D35">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E35">
         <v>5</v>
       </c>
       <c r="F35">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H35">
         <v>3</v>
       </c>
       <c r="I35">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J35">
         <v>5</v>
       </c>
       <c r="K35">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M35">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N35">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O35">
         <v>6</v>
       </c>
       <c r="P35">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="Q35">
         <v>1</v>
@@ -3051,16 +3051,16 @@
         <v>3</v>
       </c>
       <c r="S35">
-        <v>1.8</v>
+        <v>4.3</v>
       </c>
       <c r="T35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U35">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V35">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:22">
@@ -3071,10 +3071,10 @@
         <v>56</v>
       </c>
       <c r="C36" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D36">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E36">
         <v>1</v>
@@ -3086,49 +3086,49 @@
         <v>1</v>
       </c>
       <c r="H36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I36">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J36">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L36">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M36">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N36">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O36">
         <v>6</v>
       </c>
       <c r="P36">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="Q36">
         <v>1</v>
       </c>
       <c r="R36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S36">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="T36">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U36">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="V36">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:22">
@@ -3142,7 +3142,7 @@
         <v>102</v>
       </c>
       <c r="D37">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E37">
         <v>1</v>
@@ -3151,52 +3151,52 @@
         <v>1</v>
       </c>
       <c r="G37">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I37">
         <v>4</v>
       </c>
       <c r="J37">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K37">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L37">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O37">
         <v>6</v>
       </c>
       <c r="P37">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="Q37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R37">
         <v>4</v>
       </c>
       <c r="S37">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="T37">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U37">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="V37">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:22">
@@ -3207,46 +3207,46 @@
         <v>58</v>
       </c>
       <c r="C38" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D38">
         <v>4</v>
       </c>
       <c r="E38">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F38">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I38">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J38">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K38">
         <v>4</v>
       </c>
       <c r="L38">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M38">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N38">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O38">
         <v>6</v>
       </c>
       <c r="P38">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="Q38">
         <v>1</v>
@@ -3255,13 +3255,13 @@
         <v>3</v>
       </c>
       <c r="S38">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="T38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U38">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="V38">
         <v>4</v>
@@ -3275,10 +3275,10 @@
         <v>59</v>
       </c>
       <c r="C39" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D39">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E39">
         <v>1</v>
@@ -3296,19 +3296,19 @@
         <v>6</v>
       </c>
       <c r="J39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K39">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L39">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M39">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N39">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O39">
         <v>6</v>
@@ -3317,19 +3317,19 @@
         <v>38</v>
       </c>
       <c r="Q39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R39">
         <v>3</v>
       </c>
       <c r="S39">
-        <v>6.3</v>
+        <v>8.1</v>
       </c>
       <c r="T39">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="U39">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="V39">
         <v>3</v>
@@ -3343,61 +3343,61 @@
         <v>60</v>
       </c>
       <c r="C40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F40">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G40">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H40">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I40">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J40">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K40">
         <v>3</v>
       </c>
       <c r="L40">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M40">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N40">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O40">
         <v>6</v>
       </c>
       <c r="P40">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="Q40">
         <v>1</v>
       </c>
       <c r="R40">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S40">
-        <v>1.8</v>
+        <v>6.8</v>
       </c>
       <c r="T40">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U40">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="V40">
         <v>3</v>
@@ -3414,31 +3414,31 @@
         <v>103</v>
       </c>
       <c r="D41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E41">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F41">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G41">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H41">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I41">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J41">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K41">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L41">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M41">
         <v>6</v>
@@ -3450,25 +3450,25 @@
         <v>6</v>
       </c>
       <c r="P41">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="Q41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R41">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S41">
-        <v>2.9</v>
+        <v>7.5</v>
       </c>
       <c r="T41">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U41">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="V41">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42" spans="1:22">
@@ -3479,7 +3479,7 @@
         <v>62</v>
       </c>
       <c r="C42" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D42">
         <v>1</v>
@@ -3488,7 +3488,7 @@
         <v>1</v>
       </c>
       <c r="F42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G42">
         <v>3</v>
@@ -3497,46 +3497,46 @@
         <v>2</v>
       </c>
       <c r="I42">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J42">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K42">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M42">
         <v>7</v>
       </c>
       <c r="N42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O42">
         <v>6</v>
       </c>
       <c r="P42">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="Q42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R42">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S42">
-        <v>3.3</v>
+        <v>4.7</v>
       </c>
       <c r="T42">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U42">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V42">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43" spans="1:22">
@@ -3547,10 +3547,10 @@
         <v>63</v>
       </c>
       <c r="C43" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D43">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E43">
         <v>1</v>
@@ -3559,7 +3559,7 @@
         <v>1</v>
       </c>
       <c r="G43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H43">
         <v>1</v>
@@ -3574,7 +3574,7 @@
         <v>7</v>
       </c>
       <c r="L43">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M43">
         <v>7</v>
@@ -3586,25 +3586,25 @@
         <v>6</v>
       </c>
       <c r="P43">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R43">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S43">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="T43">
         <v>6</v>
       </c>
       <c r="U43">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="V43">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44" spans="1:22">
@@ -3618,61 +3618,58 @@
         <v>103</v>
       </c>
       <c r="D44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E44">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F44">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H44">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I44">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J44">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K44">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L44">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M44">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N44">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O44">
         <v>6</v>
       </c>
-      <c r="P44">
-        <v>39</v>
-      </c>
       <c r="Q44">
         <v>1</v>
       </c>
       <c r="R44">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S44">
-        <v>7.9</v>
+        <v>2.9</v>
       </c>
       <c r="T44">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U44">
         <v>13</v>
       </c>
       <c r="V44">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:22">
@@ -3683,64 +3680,64 @@
         <v>65</v>
       </c>
       <c r="C45" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F45">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G45">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H45">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I45">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J45">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K45">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L45">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M45">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N45">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O45">
         <v>6</v>
       </c>
       <c r="P45">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="Q45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R45">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S45">
-        <v>2.6</v>
+        <v>10.2</v>
       </c>
       <c r="T45">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U45">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="V45">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46" spans="1:22">
@@ -3751,64 +3748,61 @@
         <v>66</v>
       </c>
       <c r="C46" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G46">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H46">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I46">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J46">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K46">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L46">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M46">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N46">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O46">
         <v>6</v>
       </c>
       <c r="P46">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="Q46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R46">
-        <v>3</v>
-      </c>
-      <c r="S46">
-        <v>6.4</v>
+        <v>4</v>
       </c>
       <c r="T46">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U46">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="V46">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47" spans="1:22">
@@ -3819,7 +3813,7 @@
         <v>67</v>
       </c>
       <c r="C47" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D47">
         <v>3</v>
@@ -3831,52 +3825,52 @@
         <v>4</v>
       </c>
       <c r="G47">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H47">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I47">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J47">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K47">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M47">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N47">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O47">
         <v>6</v>
       </c>
       <c r="P47">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="Q47">
         <v>1</v>
       </c>
       <c r="R47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S47">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="T47">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U47">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V47">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48" spans="1:22">
@@ -3887,22 +3881,22 @@
         <v>68</v>
       </c>
       <c r="C48" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E48">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I48">
         <v>4</v>
@@ -3911,40 +3905,40 @@
         <v>3</v>
       </c>
       <c r="K48">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L48">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M48">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="N48">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O48">
         <v>6</v>
       </c>
       <c r="P48">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="Q48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R48">
         <v>4</v>
       </c>
       <c r="S48">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="T48">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U48">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="V48">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49" spans="1:22">
@@ -3955,61 +3949,61 @@
         <v>69</v>
       </c>
       <c r="C49" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D49">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E49">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F49">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G49">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H49">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I49">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J49">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K49">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L49">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M49">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N49">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O49">
         <v>6</v>
       </c>
       <c r="P49">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="Q49">
         <v>2</v>
       </c>
       <c r="R49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S49">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="T49">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="U49">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="V49">
         <v>4</v>
@@ -4023,64 +4017,64 @@
         <v>70</v>
       </c>
       <c r="C50" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F50">
         <v>1</v>
       </c>
       <c r="G50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I50">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J50">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K50">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L50">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M50">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N50">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O50">
         <v>6</v>
       </c>
       <c r="P50">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="Q50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R50">
         <v>3</v>
       </c>
       <c r="S50">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="T50">
         <v>4</v>
       </c>
       <c r="U50">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="V50">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51" spans="1:22">
@@ -4091,37 +4085,37 @@
         <v>71</v>
       </c>
       <c r="C51" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D51">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E51">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F51">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G51">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H51">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I51">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J51">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K51">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L51">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M51">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N51">
         <v>5</v>
@@ -4130,25 +4124,25 @@
         <v>6</v>
       </c>
       <c r="P51">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="Q51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S51">
-        <v>7.2</v>
+        <v>2.6</v>
       </c>
       <c r="T51">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="U51">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="V51">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52" spans="1:22">
@@ -4159,64 +4153,64 @@
         <v>72</v>
       </c>
       <c r="C52" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D52">
         <v>3</v>
       </c>
       <c r="E52">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F52">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G52">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H52">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I52">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J52">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K52">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L52">
         <v>5</v>
       </c>
       <c r="M52">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N52">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O52">
         <v>6</v>
       </c>
       <c r="P52">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="Q52">
         <v>2</v>
       </c>
       <c r="R52">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S52">
-        <v>6.8</v>
+        <v>2.2</v>
       </c>
       <c r="T52">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U52">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="V52">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53" spans="1:22">
@@ -4230,43 +4224,43 @@
         <v>102</v>
       </c>
       <c r="D53">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E53">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F53">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G53">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H53">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I53">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J53">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K53">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L53">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M53">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N53">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O53">
         <v>6</v>
       </c>
       <c r="P53">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Q53">
         <v>1</v>
@@ -4275,16 +4269,16 @@
         <v>3</v>
       </c>
       <c r="S53">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T53">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U53">
         <v>14</v>
       </c>
       <c r="V53">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54" spans="1:22">
@@ -4301,34 +4295,34 @@
         <v>1</v>
       </c>
       <c r="E54">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G54">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H54">
         <v>3</v>
       </c>
       <c r="I54">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J54">
         <v>7</v>
       </c>
       <c r="K54">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L54">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M54">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N54">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O54">
         <v>6</v>
@@ -4337,22 +4331,22 @@
         <v>30</v>
       </c>
       <c r="Q54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R54">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S54">
-        <v>7.3</v>
+        <v>2.6</v>
       </c>
       <c r="T54">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U54">
         <v>21</v>
       </c>
       <c r="V54">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55" spans="1:22">
@@ -4366,58 +4360,58 @@
         <v>102</v>
       </c>
       <c r="D55">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E55">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F55">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G55">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H55">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I55">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J55">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K55">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L55">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M55">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="N55">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O55">
         <v>6</v>
       </c>
       <c r="P55">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="Q55">
         <v>1</v>
       </c>
       <c r="R55">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S55">
-        <v>2.4</v>
+        <v>4.3</v>
       </c>
       <c r="T55">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U55">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="V55">
         <v>4</v>
@@ -4434,31 +4428,31 @@
         <v>102</v>
       </c>
       <c r="D56">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E56">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G56">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I56">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J56">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K56">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L56">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M56">
         <v>4</v>
@@ -4470,25 +4464,25 @@
         <v>6</v>
       </c>
       <c r="P56">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="Q56">
         <v>1</v>
       </c>
       <c r="R56">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S56">
-        <v>11.5</v>
+        <v>2.6</v>
       </c>
       <c r="T56">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="U56">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="V56">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:22">
@@ -4502,19 +4496,19 @@
         <v>101</v>
       </c>
       <c r="D57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G57">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H57">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I57">
         <v>6</v>
@@ -4526,34 +4520,34 @@
         <v>7</v>
       </c>
       <c r="L57">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M57">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N57">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O57">
         <v>6</v>
       </c>
       <c r="P57">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Q57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R57">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S57">
-        <v>2.3</v>
+        <v>3.9</v>
       </c>
       <c r="T57">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U57">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="V57">
         <v>4</v>
@@ -4570,34 +4564,34 @@
         <v>103</v>
       </c>
       <c r="D58">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E58">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F58">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G58">
         <v>2</v>
       </c>
       <c r="H58">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I58">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J58">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K58">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L58">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M58">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N58">
         <v>6</v>
@@ -4606,25 +4600,25 @@
         <v>6</v>
       </c>
       <c r="P58">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="Q58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R58">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S58">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="T58">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U58">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="V58">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59" spans="1:22">
@@ -4638,55 +4632,58 @@
         <v>102</v>
       </c>
       <c r="D59">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E59">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F59">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H59">
         <v>1</v>
       </c>
       <c r="I59">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J59">
         <v>5</v>
       </c>
       <c r="K59">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L59">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M59">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N59">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O59">
         <v>6</v>
       </c>
       <c r="P59">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="Q59">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R59">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="S59">
+        <v>9.800000000000001</v>
       </c>
       <c r="T59">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U59">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V59">
         <v>3</v>
@@ -4703,10 +4700,10 @@
         <v>101</v>
       </c>
       <c r="D60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E60">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F60">
         <v>4</v>
@@ -4715,43 +4712,43 @@
         <v>3</v>
       </c>
       <c r="H60">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I60">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J60">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K60">
         <v>5</v>
       </c>
       <c r="L60">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M60">
         <v>2</v>
       </c>
       <c r="N60">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O60">
         <v>6</v>
       </c>
       <c r="P60">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="Q60">
         <v>1</v>
       </c>
       <c r="R60">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S60">
-        <v>10.6</v>
+        <v>4.1</v>
       </c>
       <c r="T60">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U60">
         <v>14</v>
@@ -4771,43 +4768,43 @@
         <v>103</v>
       </c>
       <c r="D61">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E61">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F61">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H61">
         <v>3</v>
       </c>
       <c r="I61">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J61">
         <v>4</v>
       </c>
       <c r="K61">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L61">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M61">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N61">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O61">
         <v>6</v>
       </c>
       <c r="P61">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Q61">
         <v>1</v>
@@ -4816,13 +4813,13 @@
         <v>3</v>
       </c>
       <c r="S61">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="T61">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U61">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="V61">
         <v>3</v>
@@ -4839,43 +4836,43 @@
         <v>103</v>
       </c>
       <c r="D62">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F62">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G62">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H62">
         <v>4</v>
       </c>
       <c r="I62">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J62">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K62">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L62">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M62">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N62">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O62">
         <v>6</v>
       </c>
       <c r="P62">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="Q62">
         <v>1</v>
@@ -4884,10 +4881,10 @@
         <v>4</v>
       </c>
       <c r="S62">
-        <v>9.9</v>
+        <v>2.4</v>
       </c>
       <c r="T62">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U62">
         <v>22</v>
@@ -4907,16 +4904,16 @@
         <v>101</v>
       </c>
       <c r="D63">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F63">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G63">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H63">
         <v>3</v>
@@ -4925,7 +4922,7 @@
         <v>1</v>
       </c>
       <c r="J63">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K63">
         <v>2</v>
@@ -4934,10 +4931,10 @@
         <v>3</v>
       </c>
       <c r="M63">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N63">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O63">
         <v>6</v>
@@ -4949,19 +4946,19 @@
         <v>1</v>
       </c>
       <c r="R63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S63">
-        <v>3.4</v>
+        <v>8.5</v>
       </c>
       <c r="T63">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U63">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="V63">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:22">
@@ -4975,28 +4972,28 @@
         <v>101</v>
       </c>
       <c r="D64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E64">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F64">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G64">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H64">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I64">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J64">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K64">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L64">
         <v>6</v>
@@ -5005,13 +5002,13 @@
         <v>6</v>
       </c>
       <c r="N64">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O64">
         <v>6</v>
       </c>
       <c r="P64">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="Q64">
         <v>1</v>
@@ -5020,16 +5017,16 @@
         <v>3</v>
       </c>
       <c r="S64">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="T64">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U64">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="V64">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65" spans="1:22">
@@ -5043,58 +5040,58 @@
         <v>101</v>
       </c>
       <c r="D65">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E65">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F65">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H65">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I65">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J65">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K65">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L65">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M65">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N65">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O65">
         <v>6</v>
       </c>
       <c r="P65">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="Q65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R65">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S65">
-        <v>6.4</v>
+        <v>3.7</v>
       </c>
       <c r="T65">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U65">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="V65">
         <v>4</v>
@@ -5111,28 +5108,28 @@
         <v>101</v>
       </c>
       <c r="D66">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E66">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F66">
         <v>5</v>
       </c>
       <c r="G66">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H66">
         <v>3</v>
       </c>
       <c r="I66">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K66">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L66">
         <v>2</v>
@@ -5141,31 +5138,31 @@
         <v>2</v>
       </c>
       <c r="N66">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O66">
         <v>6</v>
       </c>
       <c r="P66">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="Q66">
         <v>1</v>
       </c>
       <c r="R66">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S66">
-        <v>5.1</v>
+        <v>2.2</v>
       </c>
       <c r="T66">
         <v>5</v>
       </c>
       <c r="U66">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="V66">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67" spans="1:22">
@@ -5179,43 +5176,43 @@
         <v>102</v>
       </c>
       <c r="D67">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E67">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F67">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G67">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H67">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I67">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J67">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K67">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L67">
         <v>5</v>
       </c>
       <c r="M67">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N67">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O67">
         <v>6</v>
       </c>
       <c r="P67">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="Q67">
         <v>2</v>
@@ -5224,13 +5221,13 @@
         <v>3</v>
       </c>
       <c r="S67">
-        <v>9.199999999999999</v>
+        <v>5</v>
       </c>
       <c r="T67">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U67">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="V67">
         <v>3</v>
@@ -5250,16 +5247,16 @@
         <v>2</v>
       </c>
       <c r="E68">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F68">
         <v>2</v>
       </c>
       <c r="G68">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H68">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I68">
         <v>6</v>
@@ -5268,37 +5265,37 @@
         <v>7</v>
       </c>
       <c r="K68">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L68">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M68">
         <v>7</v>
       </c>
       <c r="N68">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O68">
         <v>6</v>
       </c>
       <c r="P68">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="Q68">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R68">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S68">
-        <v>2.8</v>
+        <v>5.3</v>
       </c>
       <c r="T68">
         <v>5</v>
       </c>
       <c r="U68">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="V68">
         <v>3</v>
@@ -5315,43 +5312,43 @@
         <v>101</v>
       </c>
       <c r="D69">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E69">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F69">
         <v>2</v>
       </c>
       <c r="G69">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H69">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I69">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J69">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K69">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L69">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M69">
         <v>6</v>
       </c>
       <c r="N69">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O69">
         <v>6</v>
       </c>
       <c r="P69">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="Q69">
         <v>1</v>
@@ -5360,13 +5357,13 @@
         <v>4</v>
       </c>
       <c r="S69">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="T69">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U69">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="V69">
         <v>2</v>
@@ -5383,13 +5380,13 @@
         <v>102</v>
       </c>
       <c r="D70">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E70">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F70">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G70">
         <v>2</v>
@@ -5398,28 +5395,28 @@
         <v>3</v>
       </c>
       <c r="I70">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J70">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K70">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L70">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M70">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N70">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O70">
         <v>6</v>
       </c>
       <c r="P70">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="Q70">
         <v>1</v>
@@ -5428,16 +5425,16 @@
         <v>3</v>
       </c>
       <c r="S70">
-        <v>4.6</v>
+        <v>10.3</v>
       </c>
       <c r="T70">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U70">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="V70">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="71" spans="1:22">
@@ -5451,37 +5448,37 @@
         <v>103</v>
       </c>
       <c r="D71">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E71">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F71">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G71">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H71">
         <v>1</v>
       </c>
       <c r="I71">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J71">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K71">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L71">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M71">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N71">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O71">
         <v>6</v>
@@ -5490,22 +5487,22 @@
         <v>39</v>
       </c>
       <c r="Q71">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R71">
         <v>3</v>
       </c>
       <c r="S71">
-        <v>5.8</v>
+        <v>8</v>
       </c>
       <c r="T71">
         <v>5</v>
       </c>
       <c r="U71">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="V71">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72" spans="1:22">
@@ -5519,28 +5516,28 @@
         <v>101</v>
       </c>
       <c r="D72">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E72">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F72">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G72">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H72">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I72">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J72">
         <v>5</v>
       </c>
       <c r="K72">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L72">
         <v>5</v>
@@ -5549,28 +5546,28 @@
         <v>5</v>
       </c>
       <c r="N72">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O72">
         <v>6</v>
       </c>
       <c r="P72">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="Q72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R72">
         <v>3</v>
       </c>
       <c r="S72">
-        <v>6.9</v>
+        <v>10</v>
       </c>
       <c r="T72">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U72">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="V72">
         <v>3</v>
@@ -5587,61 +5584,61 @@
         <v>102</v>
       </c>
       <c r="D73">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E73">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F73">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G73">
         <v>2</v>
       </c>
       <c r="H73">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I73">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J73">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K73">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L73">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M73">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="N73">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O73">
         <v>6</v>
       </c>
       <c r="P73">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q73">
         <v>1</v>
       </c>
       <c r="R73">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S73">
-        <v>6.5</v>
+        <v>1.1</v>
       </c>
       <c r="T73">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U73">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="V73">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74" spans="1:22">
@@ -5655,31 +5652,31 @@
         <v>101</v>
       </c>
       <c r="D74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F74">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G74">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H74">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I74">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J74">
         <v>5</v>
       </c>
       <c r="K74">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L74">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M74">
         <v>4</v>
@@ -5691,7 +5688,7 @@
         <v>6</v>
       </c>
       <c r="P74">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="Q74">
         <v>2</v>
@@ -5700,16 +5697,16 @@
         <v>3</v>
       </c>
       <c r="S74">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="T74">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U74">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="V74">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75" spans="1:22">
@@ -5723,61 +5720,61 @@
         <v>101</v>
       </c>
       <c r="D75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E75">
         <v>2</v>
       </c>
       <c r="F75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G75">
         <v>2</v>
       </c>
       <c r="H75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I75">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J75">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K75">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L75">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M75">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N75">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O75">
         <v>6</v>
       </c>
       <c r="P75">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="Q75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R75">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S75">
-        <v>5.2</v>
+        <v>3.6</v>
       </c>
       <c r="T75">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U75">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="V75">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76" spans="1:22">
@@ -5791,43 +5788,43 @@
         <v>101</v>
       </c>
       <c r="D76">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E76">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F76">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H76">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I76">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K76">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L76">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O76">
         <v>6</v>
       </c>
       <c r="P76">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="Q76">
         <v>1</v>
@@ -5836,16 +5833,16 @@
         <v>2</v>
       </c>
       <c r="S76">
-        <v>18</v>
+        <v>4.9</v>
       </c>
       <c r="T76">
+        <v>5</v>
+      </c>
+      <c r="U76">
         <v>8</v>
       </c>
-      <c r="U76">
-        <v>18</v>
-      </c>
       <c r="V76">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="77" spans="1:22">
@@ -5862,58 +5859,58 @@
         <v>5</v>
       </c>
       <c r="E77">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F77">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G77">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H77">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I77">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J77">
         <v>3</v>
       </c>
       <c r="K77">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L77">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M77">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N77">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O77">
         <v>6</v>
       </c>
       <c r="P77">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="Q77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>3.1</v>
+        <v>8.4</v>
       </c>
       <c r="T77">
         <v>6</v>
       </c>
       <c r="U77">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V77">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78" spans="1:22">
@@ -5927,61 +5924,61 @@
         <v>103</v>
       </c>
       <c r="D78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F78">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G78">
         <v>3</v>
       </c>
       <c r="H78">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I78">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J78">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K78">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L78">
         <v>6</v>
       </c>
       <c r="M78">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N78">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O78">
         <v>6</v>
       </c>
       <c r="P78">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="Q78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R78">
         <v>3</v>
       </c>
       <c r="S78">
-        <v>3.1</v>
+        <v>15.7</v>
       </c>
       <c r="T78">
         <v>7</v>
       </c>
       <c r="U78">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="V78">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79" spans="1:22">
@@ -5995,43 +5992,43 @@
         <v>101</v>
       </c>
       <c r="D79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E79">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G79">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I79">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J79">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K79">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L79">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M79">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N79">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O79">
         <v>6</v>
       </c>
       <c r="P79">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="Q79">
         <v>1</v>
@@ -6040,16 +6037,16 @@
         <v>3</v>
       </c>
       <c r="S79">
-        <v>8.4</v>
+        <v>2.8</v>
       </c>
       <c r="T79">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U79">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="V79">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80" spans="1:22">
@@ -6063,58 +6060,61 @@
         <v>101</v>
       </c>
       <c r="D80">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F80">
         <v>2</v>
       </c>
       <c r="G80">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H80">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I80">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J80">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K80">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L80">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M80">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N80">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O80">
         <v>6</v>
       </c>
       <c r="P80">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="Q80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R80">
         <v>4</v>
       </c>
+      <c r="S80">
+        <v>5.4</v>
+      </c>
       <c r="T80">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U80">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="V80">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/data/T3_leader_cleaned.xlsx
+++ b/data/T3_leader_cleaned.xlsx
@@ -97,220 +97,220 @@
     <t>B_L06</t>
   </si>
   <si>
+    <t>C_L18</t>
+  </si>
+  <si>
+    <t>C_L24</t>
+  </si>
+  <si>
+    <t>A_L10</t>
+  </si>
+  <si>
+    <t>A_L09</t>
+  </si>
+  <si>
+    <t>B_L23</t>
+  </si>
+  <si>
+    <t>B_L21</t>
+  </si>
+  <si>
+    <t>C_L09</t>
+  </si>
+  <si>
+    <t>B_L29</t>
+  </si>
+  <si>
+    <t>B_L30</t>
+  </si>
+  <si>
+    <t>B_L08</t>
+  </si>
+  <si>
+    <t>B_L09</t>
+  </si>
+  <si>
+    <t>A_L26</t>
+  </si>
+  <si>
+    <t>C_L04</t>
+  </si>
+  <si>
+    <t>A_L14</t>
+  </si>
+  <si>
+    <t>C_L06</t>
+  </si>
+  <si>
+    <t>B_L05</t>
+  </si>
+  <si>
+    <t>C_L13</t>
+  </si>
+  <si>
+    <t>C_L20</t>
+  </si>
+  <si>
+    <t>A_L28</t>
+  </si>
+  <si>
+    <t>C_L17</t>
+  </si>
+  <si>
+    <t>C_L05</t>
+  </si>
+  <si>
+    <t>A_L17</t>
+  </si>
+  <si>
+    <t>B_L01</t>
+  </si>
+  <si>
+    <t>A_L05</t>
+  </si>
+  <si>
+    <t>C_L23</t>
+  </si>
+  <si>
+    <t>A_L12</t>
+  </si>
+  <si>
+    <t>C_L28</t>
+  </si>
+  <si>
+    <t>B_L25</t>
+  </si>
+  <si>
+    <t>C_L08</t>
+  </si>
+  <si>
+    <t>B_L24</t>
+  </si>
+  <si>
+    <t>B_L26</t>
+  </si>
+  <si>
+    <t>C_L02</t>
+  </si>
+  <si>
+    <t>A_L20</t>
+  </si>
+  <si>
+    <t>C_L30</t>
+  </si>
+  <si>
+    <t>C_L27</t>
+  </si>
+  <si>
+    <t>B_L02</t>
+  </si>
+  <si>
+    <t>C_L16</t>
+  </si>
+  <si>
+    <t>C_L21</t>
+  </si>
+  <si>
+    <t>B_L04</t>
+  </si>
+  <si>
     <t>C_L19</t>
   </si>
   <si>
-    <t>C_L25</t>
-  </si>
-  <si>
-    <t>A_L10</t>
-  </si>
-  <si>
-    <t>A_L09</t>
-  </si>
-  <si>
-    <t>B_L24</t>
+    <t>B_L11</t>
+  </si>
+  <si>
+    <t>A_L16</t>
+  </si>
+  <si>
+    <t>C_L01</t>
+  </si>
+  <si>
+    <t>B_L19</t>
+  </si>
+  <si>
+    <t>A_L08</t>
+  </si>
+  <si>
+    <t>B_L18</t>
+  </si>
+  <si>
+    <t>B_L03</t>
+  </si>
+  <si>
+    <t>B_L07</t>
   </si>
   <si>
     <t>B_L22</t>
   </si>
   <si>
-    <t>C_L10</t>
-  </si>
-  <si>
-    <t>B_L30</t>
-  </si>
-  <si>
-    <t>C_L01</t>
-  </si>
-  <si>
-    <t>B_L08</t>
-  </si>
-  <si>
-    <t>B_L09</t>
-  </si>
-  <si>
-    <t>A_L26</t>
-  </si>
-  <si>
-    <t>C_L05</t>
-  </si>
-  <si>
-    <t>A_L14</t>
+    <t>B_L15</t>
+  </si>
+  <si>
+    <t>A_L06</t>
+  </si>
+  <si>
+    <t>C_L14</t>
+  </si>
+  <si>
+    <t>B_L27</t>
+  </si>
+  <si>
+    <t>A_L02</t>
   </si>
   <si>
     <t>C_L07</t>
   </si>
   <si>
-    <t>B_L05</t>
-  </si>
-  <si>
     <t>C_L12</t>
   </si>
   <si>
-    <t>C_L21</t>
-  </si>
-  <si>
-    <t>A_L28</t>
-  </si>
-  <si>
-    <t>C_L18</t>
-  </si>
-  <si>
-    <t>C_L06</t>
-  </si>
-  <si>
-    <t>A_L18</t>
-  </si>
-  <si>
-    <t>B_L01</t>
-  </si>
-  <si>
-    <t>A_L05</t>
-  </si>
-  <si>
-    <t>C_L24</t>
-  </si>
-  <si>
-    <t>A_L12</t>
-  </si>
-  <si>
-    <t>C_L29</t>
-  </si>
-  <si>
-    <t>B_L26</t>
-  </si>
-  <si>
-    <t>C_L09</t>
-  </si>
-  <si>
-    <t>B_L25</t>
-  </si>
-  <si>
-    <t>B_L27</t>
+    <t>A_L03</t>
+  </si>
+  <si>
+    <t>A_L25</t>
+  </si>
+  <si>
+    <t>A_L29</t>
+  </si>
+  <si>
+    <t>A_L15</t>
+  </si>
+  <si>
+    <t>B_L14</t>
+  </si>
+  <si>
+    <t>B_L20</t>
+  </si>
+  <si>
+    <t>A_L23</t>
+  </si>
+  <si>
+    <t>B_L12</t>
+  </si>
+  <si>
+    <t>C_L26</t>
+  </si>
+  <si>
+    <t>A_L11</t>
+  </si>
+  <si>
+    <t>B_L16</t>
+  </si>
+  <si>
+    <t>A_L22</t>
+  </si>
+  <si>
+    <t>A_L24</t>
+  </si>
+  <si>
+    <t>A_L01</t>
+  </si>
+  <si>
+    <t>C_L22</t>
   </si>
   <si>
     <t>C_L03</t>
-  </si>
-  <si>
-    <t>A_L20</t>
-  </si>
-  <si>
-    <t>C_L30</t>
-  </si>
-  <si>
-    <t>C_L27</t>
-  </si>
-  <si>
-    <t>B_L02</t>
-  </si>
-  <si>
-    <t>C_L17</t>
-  </si>
-  <si>
-    <t>C_L22</t>
-  </si>
-  <si>
-    <t>B_L04</t>
-  </si>
-  <si>
-    <t>C_L20</t>
-  </si>
-  <si>
-    <t>B_L11</t>
-  </si>
-  <si>
-    <t>A_L17</t>
-  </si>
-  <si>
-    <t>C_L02</t>
-  </si>
-  <si>
-    <t>B_L20</t>
-  </si>
-  <si>
-    <t>A_L08</t>
-  </si>
-  <si>
-    <t>B_L19</t>
-  </si>
-  <si>
-    <t>B_L03</t>
-  </si>
-  <si>
-    <t>B_L07</t>
-  </si>
-  <si>
-    <t>B_L23</t>
-  </si>
-  <si>
-    <t>B_L16</t>
-  </si>
-  <si>
-    <t>A_L06</t>
-  </si>
-  <si>
-    <t>C_L14</t>
-  </si>
-  <si>
-    <t>B_L29</t>
-  </si>
-  <si>
-    <t>A_L02</t>
-  </si>
-  <si>
-    <t>C_L08</t>
-  </si>
-  <si>
-    <t>C_L11</t>
-  </si>
-  <si>
-    <t>A_L03</t>
-  </si>
-  <si>
-    <t>A_L25</t>
-  </si>
-  <si>
-    <t>A_L29</t>
-  </si>
-  <si>
-    <t>A_L15</t>
-  </si>
-  <si>
-    <t>B_L15</t>
-  </si>
-  <si>
-    <t>B_L21</t>
-  </si>
-  <si>
-    <t>A_L23</t>
-  </si>
-  <si>
-    <t>B_L14</t>
-  </si>
-  <si>
-    <t>C_L26</t>
-  </si>
-  <si>
-    <t>A_L11</t>
-  </si>
-  <si>
-    <t>B_L18</t>
-  </si>
-  <si>
-    <t>A_L22</t>
-  </si>
-  <si>
-    <t>A_L24</t>
-  </si>
-  <si>
-    <t>A_L01</t>
-  </si>
-  <si>
-    <t>C_L23</t>
-  </si>
-  <si>
-    <t>C_L04</t>
   </si>
   <si>
     <t>A_L04</t>
@@ -768,13 +768,13 @@
         <v>2</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2">
         <v>4</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2">
         <v>2</v>
@@ -783,16 +783,16 @@
         <v>7</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N2">
         <v>4</v>
@@ -801,25 +801,25 @@
         <v>6</v>
       </c>
       <c r="P2">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="Q2">
         <v>1</v>
       </c>
       <c r="R2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S2">
-        <v>8.9</v>
+        <v>6.7</v>
       </c>
       <c r="T2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="V2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -833,13 +833,13 @@
         <v>101</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -848,19 +848,19 @@
         <v>3</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N3">
         <v>7</v>
@@ -869,25 +869,25 @@
         <v>6</v>
       </c>
       <c r="P3">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q3">
         <v>2</v>
       </c>
       <c r="R3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S3">
-        <v>6.4</v>
+        <v>3.7</v>
       </c>
       <c r="T3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U3">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="V3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -901,58 +901,58 @@
         <v>101</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I4">
         <v>4</v>
       </c>
       <c r="J4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K4">
         <v>4</v>
       </c>
       <c r="L4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O4">
         <v>6</v>
       </c>
       <c r="P4">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="Q4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R4">
         <v>3</v>
       </c>
       <c r="S4">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="T4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U4">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="V4">
         <v>4</v>
@@ -969,58 +969,58 @@
         <v>102</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J5">
         <v>4</v>
       </c>
       <c r="K5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O5">
         <v>6</v>
       </c>
       <c r="P5">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="Q5">
         <v>2</v>
       </c>
       <c r="R5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S5">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="T5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U5">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="V5">
         <v>3</v>
@@ -1037,61 +1037,61 @@
         <v>102</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6">
         <v>2</v>
       </c>
       <c r="I6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L6">
         <v>5</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O6">
         <v>6</v>
       </c>
       <c r="P6">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="Q6">
         <v>1</v>
       </c>
       <c r="R6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S6">
-        <v>4.4</v>
+        <v>6.1</v>
       </c>
       <c r="T6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U6">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="V6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -1114,34 +1114,34 @@
         <v>1</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I7">
         <v>4</v>
       </c>
       <c r="J7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K7">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O7">
         <v>6</v>
       </c>
       <c r="P7">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="Q7">
         <v>2</v>
@@ -1150,16 +1150,16 @@
         <v>3</v>
       </c>
       <c r="S7">
-        <v>6.6</v>
+        <v>2.8</v>
       </c>
       <c r="T7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U7">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="V7">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -1173,61 +1173,61 @@
         <v>103</v>
       </c>
       <c r="D8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F8">
         <v>3</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J8">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O8">
         <v>6</v>
       </c>
       <c r="P8">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="Q8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S8">
-        <v>2.4</v>
+        <v>4.7</v>
       </c>
       <c r="T8">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V8">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -1241,37 +1241,37 @@
         <v>101</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9">
         <v>2</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O9">
         <v>6</v>
@@ -1280,22 +1280,22 @@
         <v>31</v>
       </c>
       <c r="Q9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S9">
-        <v>3</v>
+        <v>5.6</v>
       </c>
       <c r="T9">
         <v>5</v>
       </c>
       <c r="U9">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="V9">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1309,61 +1309,61 @@
         <v>101</v>
       </c>
       <c r="D10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G10">
         <v>2</v>
       </c>
       <c r="H10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J10">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L10">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O10">
         <v>6</v>
       </c>
       <c r="P10">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="Q10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S10">
-        <v>5.9</v>
+        <v>4.5</v>
       </c>
       <c r="T10">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U10">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="V10">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1377,28 +1377,28 @@
         <v>102</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F11">
         <v>1</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H11">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I11">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L11">
         <v>3</v>
@@ -1407,31 +1407,31 @@
         <v>5</v>
       </c>
       <c r="N11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O11">
         <v>6</v>
       </c>
       <c r="P11">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S11">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="T11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U11">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="V11">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1445,16 +1445,16 @@
         <v>102</v>
       </c>
       <c r="D12">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F12">
         <v>3</v>
       </c>
       <c r="G12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -1463,16 +1463,16 @@
         <v>6</v>
       </c>
       <c r="J12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L12">
         <v>4</v>
       </c>
       <c r="M12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N12">
         <v>5</v>
@@ -1481,25 +1481,25 @@
         <v>6</v>
       </c>
       <c r="P12">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="Q12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S12">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="T12">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="U12">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="V12">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1513,61 +1513,61 @@
         <v>103</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I13">
         <v>5</v>
       </c>
       <c r="J13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K13">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M13">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N13">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O13">
         <v>6</v>
       </c>
       <c r="P13">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="Q13">
         <v>1</v>
       </c>
       <c r="R13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S13">
-        <v>5</v>
+        <v>2.3</v>
       </c>
       <c r="T13">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U13">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="V13">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -1581,28 +1581,28 @@
         <v>102</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E14">
         <v>4</v>
       </c>
       <c r="F14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G14">
         <v>3</v>
       </c>
       <c r="H14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I14">
         <v>3</v>
       </c>
       <c r="J14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L14">
         <v>4</v>
@@ -1611,13 +1611,13 @@
         <v>3</v>
       </c>
       <c r="N14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O14">
         <v>6</v>
       </c>
       <c r="P14">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Q14">
         <v>1</v>
@@ -1626,16 +1626,16 @@
         <v>3</v>
       </c>
       <c r="S14">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="T14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U14">
         <v>10</v>
       </c>
       <c r="V14">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1646,37 +1646,37 @@
         <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G15">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L15">
         <v>3</v>
       </c>
       <c r="M15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N15">
         <v>4</v>
@@ -1685,22 +1685,22 @@
         <v>6</v>
       </c>
       <c r="P15">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q15">
         <v>1</v>
       </c>
       <c r="R15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S15">
-        <v>5.8</v>
+        <v>2.6</v>
       </c>
       <c r="U15">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="V15">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -1717,16 +1717,16 @@
         <v>1</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G16">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H16">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I16">
         <v>5</v>
@@ -1735,22 +1735,22 @@
         <v>7</v>
       </c>
       <c r="K16">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O16">
         <v>6</v>
       </c>
       <c r="P16">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="Q16">
         <v>2</v>
@@ -1759,16 +1759,16 @@
         <v>3</v>
       </c>
       <c r="S16">
-        <v>5.6</v>
+        <v>13.8</v>
       </c>
       <c r="T16">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U16">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="V16">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -1785,55 +1785,55 @@
         <v>3</v>
       </c>
       <c r="E17">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F17">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I17">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J17">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K17">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L17">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M17">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N17">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O17">
         <v>6</v>
       </c>
       <c r="P17">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="Q17">
         <v>1</v>
       </c>
       <c r="R17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S17">
-        <v>6.5</v>
+        <v>4.9</v>
       </c>
       <c r="T17">
         <v>5</v>
       </c>
       <c r="U17">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="V17">
         <v>3</v>
@@ -1850,13 +1850,13 @@
         <v>101</v>
       </c>
       <c r="D18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E18">
         <v>1</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1865,46 +1865,46 @@
         <v>1</v>
       </c>
       <c r="I18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J18">
         <v>6</v>
       </c>
       <c r="K18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L18">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M18">
         <v>5</v>
       </c>
       <c r="N18">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O18">
         <v>6</v>
       </c>
       <c r="P18">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="Q18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R18">
         <v>4</v>
       </c>
       <c r="S18">
-        <v>12.7</v>
+        <v>3.8</v>
       </c>
       <c r="T18">
         <v>4</v>
       </c>
       <c r="U18">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="V18">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -1918,34 +1918,34 @@
         <v>103</v>
       </c>
       <c r="D19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G19">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I19">
         <v>7</v>
       </c>
       <c r="J19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N19">
         <v>7</v>
@@ -1954,25 +1954,25 @@
         <v>6</v>
       </c>
       <c r="P19">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="Q19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S19">
-        <v>5.9</v>
+        <v>4.9</v>
       </c>
       <c r="T19">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U19">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="V19">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -1986,61 +1986,61 @@
         <v>101</v>
       </c>
       <c r="D20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F20">
         <v>3</v>
       </c>
       <c r="G20">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H20">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J20">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K20">
         <v>3</v>
       </c>
       <c r="L20">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M20">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O20">
         <v>6</v>
       </c>
       <c r="P20">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="Q20">
         <v>1</v>
       </c>
       <c r="R20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S20">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="T20">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U20">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="V20">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -2054,61 +2054,61 @@
         <v>103</v>
       </c>
       <c r="D21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E21">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F21">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H21">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K21">
         <v>5</v>
       </c>
       <c r="L21">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M21">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N21">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O21">
         <v>6</v>
       </c>
       <c r="P21">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="Q21">
         <v>1</v>
       </c>
       <c r="R21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S21">
-        <v>4.9</v>
+        <v>2.2</v>
       </c>
       <c r="T21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U21">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="V21">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -2125,28 +2125,28 @@
         <v>1</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G22">
         <v>1</v>
       </c>
       <c r="H22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I22">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J22">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K22">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L22">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M22">
         <v>5</v>
@@ -2158,25 +2158,25 @@
         <v>6</v>
       </c>
       <c r="P22">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="Q22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R22">
         <v>4</v>
       </c>
       <c r="S22">
-        <v>4.1</v>
+        <v>2.6</v>
       </c>
       <c r="T22">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U22">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="V22">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -2190,43 +2190,43 @@
         <v>103</v>
       </c>
       <c r="D23">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F23">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H23">
         <v>3</v>
       </c>
       <c r="I23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N23">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O23">
         <v>6</v>
       </c>
       <c r="P23">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="Q23">
         <v>1</v>
@@ -2235,16 +2235,16 @@
         <v>3</v>
       </c>
       <c r="S23">
-        <v>12.9</v>
+        <v>8.1</v>
       </c>
       <c r="T23">
         <v>5</v>
       </c>
       <c r="U23">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="V23">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -2258,61 +2258,58 @@
         <v>103</v>
       </c>
       <c r="D24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H24">
         <v>2</v>
       </c>
       <c r="I24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J24">
         <v>7</v>
       </c>
       <c r="K24">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L24">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M24">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N24">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O24">
         <v>6</v>
       </c>
       <c r="P24">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="Q24">
         <v>1</v>
       </c>
       <c r="R24">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S24">
-        <v>1.9</v>
-      </c>
-      <c r="T24">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="U24">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="V24">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -2335,7 +2332,7 @@
         <v>1</v>
       </c>
       <c r="G25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H25">
         <v>1</v>
@@ -2344,13 +2341,13 @@
         <v>6</v>
       </c>
       <c r="J25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K25">
         <v>7</v>
       </c>
       <c r="L25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M25">
         <v>6</v>
@@ -2362,25 +2359,25 @@
         <v>6</v>
       </c>
       <c r="P25">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="Q25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R25">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S25">
-        <v>6.5</v>
+        <v>7.7</v>
       </c>
       <c r="T25">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U25">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="V25">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -2397,55 +2394,55 @@
         <v>1</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G26">
         <v>1</v>
       </c>
       <c r="H26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J26">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K26">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L26">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M26">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N26">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O26">
         <v>6</v>
       </c>
       <c r="P26">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="Q26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R26">
         <v>4</v>
       </c>
       <c r="S26">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="T26">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U26">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="V26">
         <v>4</v>
@@ -2465,58 +2462,58 @@
         <v>1</v>
       </c>
       <c r="E27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F27">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G27">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I27">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J27">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L27">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M27">
         <v>5</v>
       </c>
       <c r="N27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O27">
         <v>6</v>
       </c>
       <c r="P27">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Q27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R27">
         <v>3</v>
       </c>
       <c r="S27">
-        <v>3.1</v>
+        <v>8.9</v>
       </c>
       <c r="T27">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="U27">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V27">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -2530,61 +2527,61 @@
         <v>101</v>
       </c>
       <c r="D28">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G28">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H28">
         <v>2</v>
       </c>
       <c r="I28">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J28">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K28">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L28">
         <v>5</v>
       </c>
       <c r="M28">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O28">
         <v>6</v>
       </c>
       <c r="P28">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="Q28">
         <v>1</v>
       </c>
       <c r="R28">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S28">
-        <v>2.3</v>
+        <v>5</v>
       </c>
       <c r="T28">
         <v>6</v>
       </c>
       <c r="U28">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="V28">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -2598,31 +2595,31 @@
         <v>102</v>
       </c>
       <c r="D29">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I29">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J29">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L29">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M29">
         <v>6</v>
@@ -2634,25 +2631,25 @@
         <v>6</v>
       </c>
       <c r="P29">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="Q29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R29">
         <v>3</v>
       </c>
       <c r="S29">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="T29">
         <v>6</v>
       </c>
       <c r="U29">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="V29">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:22">
@@ -2669,55 +2666,55 @@
         <v>3</v>
       </c>
       <c r="E30">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F30">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G30">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H30">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I30">
         <v>5</v>
       </c>
       <c r="J30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K30">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M30">
         <v>3</v>
       </c>
       <c r="N30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O30">
         <v>6</v>
       </c>
       <c r="P30">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="Q30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S30">
-        <v>2.1</v>
+        <v>8.4</v>
       </c>
       <c r="T30">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U30">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="V30">
         <v>4</v>
@@ -2737,34 +2734,34 @@
         <v>2</v>
       </c>
       <c r="E31">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F31">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G31">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I31">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K31">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M31">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N31">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O31">
         <v>6</v>
@@ -2773,19 +2770,19 @@
         <v>37</v>
       </c>
       <c r="Q31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S31">
-        <v>7.9</v>
+        <v>2.6</v>
       </c>
       <c r="T31">
         <v>4</v>
       </c>
       <c r="U31">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="V31">
         <v>4</v>
@@ -2808,7 +2805,7 @@
         <v>1</v>
       </c>
       <c r="F32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -2826,7 +2823,7 @@
         <v>7</v>
       </c>
       <c r="L32">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M32">
         <v>7</v>
@@ -2838,22 +2835,22 @@
         <v>6</v>
       </c>
       <c r="P32">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="Q32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R32">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S32">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="T32">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U32">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="V32">
         <v>3</v>
@@ -2873,31 +2870,31 @@
         <v>2</v>
       </c>
       <c r="E33">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G33">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I33">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K33">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N33">
         <v>5</v>
@@ -2906,25 +2903,25 @@
         <v>6</v>
       </c>
       <c r="P33">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="Q33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R33">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S33">
-        <v>11</v>
+        <v>4.1</v>
       </c>
       <c r="T33">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U33">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="V33">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34" spans="1:22">
@@ -2941,40 +2938,40 @@
         <v>1</v>
       </c>
       <c r="E34">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G34">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H34">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J34">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K34">
         <v>7</v>
       </c>
       <c r="L34">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M34">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O34">
         <v>6</v>
       </c>
       <c r="P34">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="Q34">
         <v>1</v>
@@ -2983,16 +2980,16 @@
         <v>4</v>
       </c>
       <c r="S34">
-        <v>16</v>
+        <v>2.8</v>
       </c>
       <c r="T34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U34">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V34">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35" spans="1:22">
@@ -3006,43 +3003,43 @@
         <v>103</v>
       </c>
       <c r="D35">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E35">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F35">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I35">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J35">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K35">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L35">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M35">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N35">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O35">
         <v>6</v>
       </c>
       <c r="P35">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="Q35">
         <v>1</v>
@@ -3051,13 +3048,13 @@
         <v>3</v>
       </c>
       <c r="S35">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T35">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U35">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="V35">
         <v>3</v>
@@ -3074,34 +3071,34 @@
         <v>102</v>
       </c>
       <c r="D36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E36">
         <v>1</v>
       </c>
       <c r="F36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G36">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H36">
         <v>3</v>
       </c>
       <c r="I36">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J36">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L36">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M36">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N36">
         <v>3</v>
@@ -3110,22 +3107,22 @@
         <v>6</v>
       </c>
       <c r="P36">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="Q36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R36">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S36">
-        <v>2.9</v>
+        <v>8.5</v>
       </c>
       <c r="T36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U36">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="V36">
         <v>3</v>
@@ -3142,61 +3139,61 @@
         <v>102</v>
       </c>
       <c r="D37">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F37">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H37">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I37">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J37">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L37">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M37">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N37">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O37">
         <v>6</v>
       </c>
       <c r="P37">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="Q37">
         <v>2</v>
       </c>
       <c r="R37">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S37">
-        <v>5.5</v>
+        <v>2.1</v>
       </c>
       <c r="T37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U37">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="V37">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38" spans="1:22">
@@ -3213,55 +3210,55 @@
         <v>4</v>
       </c>
       <c r="E38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F38">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G38">
         <v>3</v>
       </c>
       <c r="H38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I38">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J38">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K38">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L38">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M38">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N38">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O38">
         <v>6</v>
       </c>
       <c r="P38">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="Q38">
         <v>1</v>
       </c>
       <c r="R38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S38">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="T38">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U38">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="V38">
         <v>4</v>
@@ -3284,37 +3281,37 @@
         <v>1</v>
       </c>
       <c r="F39">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H39">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I39">
         <v>6</v>
       </c>
       <c r="J39">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K39">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L39">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O39">
         <v>6</v>
       </c>
       <c r="P39">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="Q39">
         <v>2</v>
@@ -3323,16 +3320,16 @@
         <v>3</v>
       </c>
       <c r="S39">
-        <v>8.1</v>
+        <v>2.8</v>
       </c>
       <c r="T39">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U39">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="V39">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40" spans="1:22">
@@ -3349,25 +3346,25 @@
         <v>3</v>
       </c>
       <c r="E40">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F40">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G40">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H40">
         <v>4</v>
       </c>
       <c r="I40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K40">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L40">
         <v>4</v>
@@ -3376,28 +3373,28 @@
         <v>5</v>
       </c>
       <c r="N40">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O40">
         <v>6</v>
       </c>
       <c r="P40">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="Q40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R40">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S40">
-        <v>6.8</v>
+        <v>4.4</v>
       </c>
       <c r="T40">
         <v>5</v>
       </c>
       <c r="U40">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="V40">
         <v>3</v>
@@ -3414,7 +3411,7 @@
         <v>103</v>
       </c>
       <c r="D41">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E41">
         <v>1</v>
@@ -3426,7 +3423,7 @@
         <v>2</v>
       </c>
       <c r="H41">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I41">
         <v>6</v>
@@ -3435,40 +3432,40 @@
         <v>5</v>
       </c>
       <c r="K41">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L41">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M41">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N41">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O41">
         <v>6</v>
       </c>
       <c r="P41">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="Q41">
         <v>1</v>
       </c>
       <c r="R41">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S41">
-        <v>7.5</v>
+        <v>10.2</v>
       </c>
       <c r="T41">
         <v>7</v>
       </c>
       <c r="U41">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="V41">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42" spans="1:22">
@@ -3488,55 +3485,55 @@
         <v>1</v>
       </c>
       <c r="F42">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G42">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H42">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I42">
         <v>6</v>
       </c>
       <c r="J42">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K42">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L42">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M42">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N42">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O42">
         <v>6</v>
       </c>
       <c r="P42">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="Q42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R42">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S42">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="T42">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U42">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="V42">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:22">
@@ -3553,40 +3550,40 @@
         <v>2</v>
       </c>
       <c r="E43">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H43">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I43">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J43">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K43">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L43">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M43">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N43">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O43">
         <v>6</v>
       </c>
       <c r="P43">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="Q43">
         <v>1</v>
@@ -3595,13 +3592,13 @@
         <v>3</v>
       </c>
       <c r="S43">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="T43">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U43">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V43">
         <v>3</v>
@@ -3621,10 +3618,10 @@
         <v>2</v>
       </c>
       <c r="E44">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F44">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G44">
         <v>2</v>
@@ -3633,43 +3630,46 @@
         <v>3</v>
       </c>
       <c r="I44">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J44">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K44">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L44">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M44">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N44">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O44">
         <v>6</v>
       </c>
+      <c r="P44">
+        <v>55</v>
+      </c>
       <c r="Q44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R44">
         <v>5</v>
       </c>
       <c r="S44">
-        <v>2.9</v>
+        <v>6.5</v>
       </c>
       <c r="T44">
         <v>5</v>
       </c>
       <c r="U44">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="V44">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45" spans="1:22">
@@ -3683,7 +3683,7 @@
         <v>102</v>
       </c>
       <c r="D45">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E45">
         <v>4</v>
@@ -3695,49 +3695,49 @@
         <v>2</v>
       </c>
       <c r="H45">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I45">
         <v>4</v>
       </c>
       <c r="J45">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K45">
         <v>6</v>
       </c>
       <c r="L45">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M45">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N45">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O45">
         <v>6</v>
       </c>
       <c r="P45">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q45">
         <v>2</v>
       </c>
       <c r="R45">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S45">
-        <v>10.2</v>
+        <v>5.7</v>
       </c>
       <c r="T45">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U45">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="V45">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46" spans="1:22">
@@ -3751,34 +3751,34 @@
         <v>103</v>
       </c>
       <c r="D46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E46">
         <v>1</v>
       </c>
       <c r="F46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G46">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I46">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J46">
         <v>5</v>
       </c>
       <c r="K46">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L46">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M46">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N46">
         <v>5</v>
@@ -3790,16 +3790,19 @@
         <v>34</v>
       </c>
       <c r="Q46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R46">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="S46">
+        <v>12</v>
       </c>
       <c r="T46">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U46">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="V46">
         <v>3</v>
@@ -3816,34 +3819,34 @@
         <v>102</v>
       </c>
       <c r="D47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E47">
         <v>4</v>
       </c>
       <c r="F47">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G47">
         <v>3</v>
       </c>
       <c r="H47">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I47">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J47">
         <v>4</v>
       </c>
       <c r="K47">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L47">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M47">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N47">
         <v>5</v>
@@ -3852,22 +3855,22 @@
         <v>6</v>
       </c>
       <c r="P47">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="Q47">
         <v>1</v>
       </c>
       <c r="R47">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S47">
-        <v>5.1</v>
+        <v>10.6</v>
       </c>
       <c r="T47">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U47">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="V47">
         <v>3</v>
@@ -3887,28 +3890,28 @@
         <v>2</v>
       </c>
       <c r="E48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I48">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J48">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K48">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L48">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M48">
         <v>7</v>
@@ -3929,16 +3932,16 @@
         <v>4</v>
       </c>
       <c r="S48">
-        <v>4.4</v>
+        <v>6.7</v>
       </c>
       <c r="T48">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U48">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V48">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:22">
@@ -3952,58 +3955,58 @@
         <v>103</v>
       </c>
       <c r="D49">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E49">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F49">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G49">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H49">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J49">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K49">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L49">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M49">
         <v>4</v>
       </c>
       <c r="N49">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O49">
         <v>6</v>
       </c>
       <c r="P49">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="Q49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R49">
         <v>4</v>
       </c>
       <c r="S49">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="T49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U49">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="V49">
         <v>4</v>
@@ -4020,13 +4023,13 @@
         <v>102</v>
       </c>
       <c r="D50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G50">
         <v>1</v>
@@ -4038,43 +4041,43 @@
         <v>4</v>
       </c>
       <c r="J50">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K50">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L50">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M50">
         <v>5</v>
       </c>
       <c r="N50">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O50">
         <v>6</v>
       </c>
       <c r="P50">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="Q50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R50">
         <v>3</v>
       </c>
       <c r="S50">
-        <v>3.5</v>
+        <v>6.2</v>
       </c>
       <c r="T50">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U50">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="V50">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51" spans="1:22">
@@ -4091,58 +4094,58 @@
         <v>1</v>
       </c>
       <c r="E51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I51">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J51">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K51">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L51">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M51">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O51">
         <v>6</v>
       </c>
       <c r="P51">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="Q51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R51">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S51">
-        <v>2.6</v>
+        <v>4.5</v>
       </c>
       <c r="T51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U51">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="V51">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52" spans="1:22">
@@ -4159,55 +4162,55 @@
         <v>3</v>
       </c>
       <c r="E52">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F52">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G52">
         <v>3</v>
       </c>
       <c r="H52">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I52">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J52">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K52">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L52">
         <v>5</v>
       </c>
       <c r="M52">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N52">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O52">
         <v>6</v>
       </c>
       <c r="P52">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="Q52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R52">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S52">
-        <v>2.2</v>
+        <v>9.6</v>
       </c>
       <c r="T52">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U52">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="V52">
         <v>3</v>
@@ -4224,34 +4227,34 @@
         <v>102</v>
       </c>
       <c r="D53">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E53">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F53">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G53">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H53">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I53">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J53">
         <v>4</v>
       </c>
       <c r="K53">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L53">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M53">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N53">
         <v>5</v>
@@ -4260,7 +4263,7 @@
         <v>6</v>
       </c>
       <c r="P53">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="Q53">
         <v>1</v>
@@ -4269,13 +4272,13 @@
         <v>3</v>
       </c>
       <c r="S53">
-        <v>3</v>
+        <v>10.3</v>
       </c>
       <c r="T53">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U53">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="V53">
         <v>4</v>
@@ -4292,61 +4295,61 @@
         <v>102</v>
       </c>
       <c r="D54">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E54">
         <v>4</v>
       </c>
       <c r="F54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G54">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I54">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J54">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K54">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L54">
         <v>7</v>
       </c>
       <c r="M54">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N54">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O54">
         <v>6</v>
       </c>
       <c r="P54">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="Q54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R54">
         <v>3</v>
       </c>
       <c r="S54">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
       <c r="T54">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U54">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="V54">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55" spans="1:22">
@@ -4363,40 +4366,40 @@
         <v>3</v>
       </c>
       <c r="E55">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F55">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G55">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H55">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I55">
         <v>2</v>
       </c>
       <c r="J55">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K55">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M55">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N55">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O55">
         <v>6</v>
       </c>
       <c r="P55">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="Q55">
         <v>1</v>
@@ -4405,13 +4408,13 @@
         <v>3</v>
       </c>
       <c r="S55">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="T55">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U55">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="V55">
         <v>4</v>
@@ -4428,61 +4431,61 @@
         <v>102</v>
       </c>
       <c r="D56">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E56">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G56">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I56">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J56">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K56">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L56">
         <v>6</v>
       </c>
       <c r="M56">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N56">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O56">
         <v>6</v>
       </c>
       <c r="P56">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="Q56">
         <v>1</v>
       </c>
       <c r="R56">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S56">
-        <v>2.6</v>
+        <v>6.6</v>
       </c>
       <c r="T56">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U56">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="V56">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57" spans="1:22">
@@ -4496,10 +4499,10 @@
         <v>101</v>
       </c>
       <c r="D57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E57">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F57">
         <v>1</v>
@@ -4508,10 +4511,10 @@
         <v>1</v>
       </c>
       <c r="H57">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I57">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J57">
         <v>7</v>
@@ -4520,37 +4523,37 @@
         <v>7</v>
       </c>
       <c r="L57">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M57">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N57">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O57">
         <v>6</v>
       </c>
       <c r="P57">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="Q57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S57">
-        <v>3.9</v>
+        <v>7</v>
       </c>
       <c r="T57">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U57">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="V57">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58" spans="1:22">
@@ -4567,58 +4570,58 @@
         <v>4</v>
       </c>
       <c r="E58">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F58">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G58">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H58">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I58">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J58">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K58">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L58">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M58">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N58">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O58">
         <v>6</v>
       </c>
       <c r="P58">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="Q58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R58">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S58">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T58">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U58">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="V58">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59" spans="1:22">
@@ -4632,58 +4635,58 @@
         <v>102</v>
       </c>
       <c r="D59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E59">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F59">
         <v>3</v>
       </c>
       <c r="G59">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H59">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I59">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J59">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K59">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L59">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M59">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="N59">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O59">
         <v>6</v>
       </c>
       <c r="P59">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="Q59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R59">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S59">
-        <v>9.800000000000001</v>
+        <v>3.9</v>
       </c>
       <c r="T59">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U59">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="V59">
         <v>3</v>
@@ -4700,58 +4703,58 @@
         <v>101</v>
       </c>
       <c r="D60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E60">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F60">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G60">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H60">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I60">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J60">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K60">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L60">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M60">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N60">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O60">
         <v>6</v>
       </c>
       <c r="P60">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="Q60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R60">
         <v>3</v>
       </c>
       <c r="S60">
-        <v>4.1</v>
+        <v>9.4</v>
       </c>
       <c r="T60">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U60">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="V60">
         <v>3</v>
@@ -4771,55 +4774,55 @@
         <v>2</v>
       </c>
       <c r="E61">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F61">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G61">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H61">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I61">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J61">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K61">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L61">
         <v>4</v>
       </c>
       <c r="M61">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N61">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O61">
         <v>6</v>
       </c>
       <c r="P61">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Q61">
         <v>1</v>
       </c>
       <c r="R61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S61">
-        <v>5.7</v>
+        <v>2.2</v>
       </c>
       <c r="T61">
         <v>4</v>
       </c>
       <c r="U61">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V61">
         <v>3</v>
@@ -4839,58 +4842,58 @@
         <v>2</v>
       </c>
       <c r="E62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G62">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H62">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I62">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J62">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K62">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L62">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M62">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="N62">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O62">
         <v>6</v>
       </c>
       <c r="P62">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="Q62">
         <v>1</v>
       </c>
       <c r="R62">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S62">
-        <v>2.4</v>
+        <v>6.4</v>
       </c>
       <c r="T62">
         <v>6</v>
       </c>
       <c r="U62">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="V62">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63" spans="1:22">
@@ -4904,61 +4907,61 @@
         <v>101</v>
       </c>
       <c r="D63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E63">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F63">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G63">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H63">
         <v>3</v>
       </c>
       <c r="I63">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J63">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K63">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L63">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M63">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O63">
         <v>6</v>
       </c>
       <c r="P63">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="Q63">
         <v>1</v>
       </c>
       <c r="R63">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S63">
-        <v>8.5</v>
+        <v>3.6</v>
       </c>
       <c r="T63">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U63">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="V63">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64" spans="1:22">
@@ -4972,19 +4975,19 @@
         <v>101</v>
       </c>
       <c r="D64">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E64">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F64">
         <v>4</v>
       </c>
       <c r="G64">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H64">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I64">
         <v>4</v>
@@ -4993,37 +4996,34 @@
         <v>4</v>
       </c>
       <c r="K64">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L64">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M64">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N64">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O64">
         <v>6</v>
       </c>
-      <c r="P64">
-        <v>32</v>
-      </c>
       <c r="Q64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R64">
         <v>3</v>
       </c>
       <c r="S64">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="T64">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U64">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="V64">
         <v>4</v>
@@ -5040,61 +5040,61 @@
         <v>101</v>
       </c>
       <c r="D65">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E65">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F65">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G65">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H65">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J65">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K65">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L65">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M65">
         <v>4</v>
       </c>
       <c r="N65">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O65">
         <v>6</v>
       </c>
       <c r="P65">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Q65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R65">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S65">
-        <v>3.7</v>
+        <v>7.9</v>
       </c>
       <c r="T65">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U65">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="V65">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66" spans="1:22">
@@ -5108,61 +5108,61 @@
         <v>101</v>
       </c>
       <c r="D66">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E66">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F66">
         <v>5</v>
       </c>
       <c r="G66">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H66">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I66">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J66">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L66">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M66">
         <v>2</v>
       </c>
       <c r="N66">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O66">
         <v>6</v>
       </c>
       <c r="P66">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="Q66">
         <v>1</v>
       </c>
       <c r="R66">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S66">
-        <v>2.2</v>
+        <v>7.5</v>
       </c>
       <c r="T66">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U66">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="V66">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67" spans="1:22">
@@ -5176,61 +5176,61 @@
         <v>102</v>
       </c>
       <c r="D67">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E67">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F67">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G67">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H67">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I67">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J67">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K67">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L67">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M67">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N67">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O67">
         <v>6</v>
       </c>
       <c r="P67">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="Q67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R67">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S67">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="T67">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U67">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="V67">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68" spans="1:22">
@@ -5247,55 +5247,55 @@
         <v>2</v>
       </c>
       <c r="E68">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F68">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G68">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H68">
         <v>2</v>
       </c>
       <c r="I68">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J68">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K68">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L68">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M68">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N68">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O68">
         <v>6</v>
       </c>
       <c r="P68">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="Q68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R68">
         <v>3</v>
       </c>
       <c r="S68">
-        <v>5.3</v>
+        <v>4.2</v>
       </c>
       <c r="T68">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U68">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="V68">
         <v>3</v>
@@ -5312,43 +5312,43 @@
         <v>101</v>
       </c>
       <c r="D69">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E69">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I69">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J69">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K69">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L69">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M69">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N69">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O69">
         <v>6</v>
       </c>
       <c r="P69">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="Q69">
         <v>1</v>
@@ -5357,16 +5357,16 @@
         <v>4</v>
       </c>
       <c r="S69">
-        <v>2.1</v>
+        <v>7.5</v>
       </c>
       <c r="T69">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U69">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="V69">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70" spans="1:22">
@@ -5380,61 +5380,61 @@
         <v>102</v>
       </c>
       <c r="D70">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E70">
         <v>1</v>
       </c>
       <c r="F70">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H70">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I70">
         <v>5</v>
       </c>
       <c r="J70">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K70">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L70">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M70">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N70">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O70">
         <v>6</v>
       </c>
       <c r="P70">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="Q70">
         <v>1</v>
       </c>
       <c r="R70">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S70">
-        <v>10.3</v>
+        <v>12</v>
       </c>
       <c r="T70">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U70">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="V70">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:22">
@@ -5448,25 +5448,25 @@
         <v>103</v>
       </c>
       <c r="D71">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E71">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F71">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H71">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I71">
         <v>1</v>
       </c>
       <c r="J71">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K71">
         <v>2</v>
@@ -5475,34 +5475,34 @@
         <v>3</v>
       </c>
       <c r="M71">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N71">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O71">
         <v>6</v>
       </c>
       <c r="P71">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q71">
         <v>2</v>
       </c>
       <c r="R71">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S71">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T71">
         <v>5</v>
       </c>
       <c r="U71">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="V71">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72" spans="1:22">
@@ -5519,58 +5519,58 @@
         <v>1</v>
       </c>
       <c r="E72">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F72">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G72">
         <v>2</v>
       </c>
       <c r="H72">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I72">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J72">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K72">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L72">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M72">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N72">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O72">
         <v>6</v>
       </c>
       <c r="P72">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q72">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R72">
         <v>3</v>
       </c>
       <c r="S72">
-        <v>10</v>
+        <v>3.4</v>
       </c>
       <c r="T72">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U72">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="V72">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73" spans="1:22">
@@ -5584,10 +5584,10 @@
         <v>102</v>
       </c>
       <c r="D73">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F73">
         <v>1</v>
@@ -5599,43 +5599,43 @@
         <v>2</v>
       </c>
       <c r="I73">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J73">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K73">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L73">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M73">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N73">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O73">
         <v>6</v>
       </c>
       <c r="P73">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="Q73">
         <v>1</v>
       </c>
       <c r="R73">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S73">
-        <v>1.1</v>
+        <v>7.6</v>
       </c>
       <c r="T73">
         <v>5</v>
       </c>
       <c r="U73">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="V73">
         <v>3</v>
@@ -5652,61 +5652,61 @@
         <v>101</v>
       </c>
       <c r="D74">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E74">
         <v>2</v>
       </c>
       <c r="F74">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G74">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H74">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I74">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J74">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K74">
         <v>2</v>
       </c>
       <c r="L74">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M74">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N74">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O74">
         <v>6</v>
       </c>
       <c r="P74">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="Q74">
         <v>2</v>
       </c>
       <c r="R74">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S74">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="T74">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U74">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V74">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75" spans="1:22">
@@ -5720,31 +5720,31 @@
         <v>101</v>
       </c>
       <c r="D75">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F75">
         <v>2</v>
       </c>
       <c r="G75">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H75">
         <v>2</v>
       </c>
       <c r="I75">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J75">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K75">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L75">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M75">
         <v>6</v>
@@ -5756,22 +5756,22 @@
         <v>6</v>
       </c>
       <c r="P75">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="Q75">
         <v>2</v>
       </c>
       <c r="R75">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S75">
-        <v>3.6</v>
+        <v>5.1</v>
       </c>
       <c r="T75">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U75">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="V75">
         <v>4</v>
@@ -5788,61 +5788,61 @@
         <v>101</v>
       </c>
       <c r="D76">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F76">
         <v>3</v>
       </c>
       <c r="G76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H76">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I76">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J76">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K76">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L76">
         <v>5</v>
       </c>
       <c r="M76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N76">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O76">
         <v>6</v>
       </c>
       <c r="P76">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="Q76">
         <v>1</v>
       </c>
       <c r="R76">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S76">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="T76">
         <v>5</v>
       </c>
       <c r="U76">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="V76">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77" spans="1:22">
@@ -5856,34 +5856,34 @@
         <v>103</v>
       </c>
       <c r="D77">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E77">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F77">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G77">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I77">
         <v>5</v>
       </c>
       <c r="J77">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K77">
         <v>4</v>
       </c>
       <c r="L77">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M77">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N77">
         <v>5</v>
@@ -5892,22 +5892,22 @@
         <v>6</v>
       </c>
       <c r="P77">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="Q77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>8.4</v>
+        <v>3.7</v>
       </c>
       <c r="T77">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U77">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="V77">
         <v>4</v>
@@ -5933,13 +5933,13 @@
         <v>1</v>
       </c>
       <c r="G78">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H78">
         <v>1</v>
       </c>
       <c r="I78">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J78">
         <v>4</v>
@@ -5951,7 +5951,7 @@
         <v>6</v>
       </c>
       <c r="M78">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N78">
         <v>6</v>
@@ -5960,25 +5960,25 @@
         <v>6</v>
       </c>
       <c r="P78">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="Q78">
         <v>2</v>
       </c>
       <c r="R78">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S78">
-        <v>15.7</v>
+        <v>10</v>
       </c>
       <c r="T78">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U78">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="V78">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79" spans="1:22">
@@ -5995,7 +5995,7 @@
         <v>1</v>
       </c>
       <c r="E79">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F79">
         <v>1</v>
@@ -6004,10 +6004,10 @@
         <v>4</v>
       </c>
       <c r="H79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I79">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J79">
         <v>7</v>
@@ -6028,25 +6028,25 @@
         <v>6</v>
       </c>
       <c r="P79">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="Q79">
         <v>1</v>
       </c>
       <c r="R79">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S79">
-        <v>2.8</v>
+        <v>9.1</v>
       </c>
       <c r="T79">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U79">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="V79">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80" spans="1:22">
@@ -6060,31 +6060,31 @@
         <v>101</v>
       </c>
       <c r="D80">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E80">
         <v>1</v>
       </c>
       <c r="F80">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H80">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I80">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J80">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K80">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L80">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M80">
         <v>5</v>
@@ -6096,22 +6096,22 @@
         <v>6</v>
       </c>
       <c r="P80">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="Q80">
         <v>1</v>
       </c>
       <c r="R80">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S80">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="T80">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U80">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="V80">
         <v>3</v>

--- a/data/T3_leader_cleaned.xlsx
+++ b/data/T3_leader_cleaned.xlsx
@@ -765,37 +765,37 @@
         <v>101</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O2">
         <v>6</v>
@@ -833,37 +833,37 @@
         <v>101</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E3">
         <v>2</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G3">
         <v>2</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3">
         <v>6</v>
       </c>
       <c r="J3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M3">
         <v>6</v>
       </c>
       <c r="N3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O3">
         <v>6</v>
@@ -904,34 +904,34 @@
         <v>4</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O4">
         <v>6</v>
@@ -969,37 +969,37 @@
         <v>102</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L5">
         <v>5</v>
       </c>
       <c r="M5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O5">
         <v>6</v>
@@ -1037,37 +1037,37 @@
         <v>102</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6">
         <v>2</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O6">
         <v>6</v>
@@ -1105,37 +1105,37 @@
         <v>103</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E7">
         <v>2</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7">
         <v>2</v>
       </c>
       <c r="H7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I7">
         <v>4</v>
       </c>
       <c r="J7">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O7">
         <v>6</v>
@@ -1173,37 +1173,37 @@
         <v>103</v>
       </c>
       <c r="D8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H8">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O8">
         <v>6</v>
@@ -1241,19 +1241,19 @@
         <v>101</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I9">
         <v>4</v>
@@ -1265,13 +1265,13 @@
         <v>4</v>
       </c>
       <c r="L9">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O9">
         <v>6</v>
@@ -1309,10 +1309,10 @@
         <v>101</v>
       </c>
       <c r="D10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F10">
         <v>3</v>
@@ -1324,16 +1324,16 @@
         <v>3</v>
       </c>
       <c r="I10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K10">
         <v>4</v>
       </c>
       <c r="L10">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M10">
         <v>4</v>
@@ -1377,31 +1377,31 @@
         <v>102</v>
       </c>
       <c r="D11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E11">
         <v>4</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G11">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H11">
         <v>4</v>
       </c>
       <c r="I11">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J11">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K11">
         <v>5</v>
       </c>
       <c r="L11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M11">
         <v>5</v>
@@ -1445,10 +1445,10 @@
         <v>102</v>
       </c>
       <c r="D12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F12">
         <v>3</v>
@@ -1457,19 +1457,19 @@
         <v>2</v>
       </c>
       <c r="H12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I12">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M12">
         <v>5</v>
@@ -1516,16 +1516,16 @@
         <v>3</v>
       </c>
       <c r="E13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F13">
         <v>3</v>
       </c>
       <c r="G13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I13">
         <v>5</v>
@@ -1534,16 +1534,16 @@
         <v>4</v>
       </c>
       <c r="K13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L13">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M13">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N13">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O13">
         <v>6</v>
@@ -1581,37 +1581,37 @@
         <v>102</v>
       </c>
       <c r="D14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F14">
         <v>2</v>
       </c>
       <c r="G14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H14">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M14">
         <v>3</v>
       </c>
       <c r="N14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O14">
         <v>6</v>
@@ -1649,31 +1649,31 @@
         <v>102</v>
       </c>
       <c r="D15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E15">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F15">
         <v>3</v>
       </c>
       <c r="G15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M15">
         <v>4</v>
@@ -1714,28 +1714,28 @@
         <v>102</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F16">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I16">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J16">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K16">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L16">
         <v>4</v>
@@ -1785,34 +1785,34 @@
         <v>3</v>
       </c>
       <c r="E17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G17">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I17">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J17">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K17">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M17">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N17">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O17">
         <v>6</v>
@@ -1850,37 +1850,37 @@
         <v>101</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I18">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N18">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O18">
         <v>6</v>
@@ -1918,22 +1918,22 @@
         <v>103</v>
       </c>
       <c r="D19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H19">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J19">
         <v>5</v>
@@ -1942,13 +1942,13 @@
         <v>6</v>
       </c>
       <c r="L19">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M19">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N19">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O19">
         <v>6</v>
@@ -1986,37 +1986,37 @@
         <v>101</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20">
         <v>2</v>
       </c>
       <c r="F20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G20">
         <v>2</v>
       </c>
       <c r="H20">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K20">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L20">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M20">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N20">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O20">
         <v>6</v>
@@ -2054,34 +2054,34 @@
         <v>103</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I21">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K21">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L21">
         <v>4</v>
       </c>
       <c r="M21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N21">
         <v>5</v>
@@ -2122,34 +2122,34 @@
         <v>102</v>
       </c>
       <c r="D22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22">
         <v>2</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I22">
         <v>5</v>
       </c>
       <c r="J22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K22">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N22">
         <v>6</v>
@@ -2190,13 +2190,13 @@
         <v>103</v>
       </c>
       <c r="D23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E23">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F23">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G23">
         <v>2</v>
@@ -2205,13 +2205,13 @@
         <v>3</v>
       </c>
       <c r="I23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J23">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L23">
         <v>5</v>
@@ -2261,34 +2261,34 @@
         <v>3</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F24">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G24">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I24">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J24">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L24">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N24">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O24">
         <v>6</v>
@@ -2323,37 +2323,37 @@
         <v>101</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G25">
         <v>2</v>
       </c>
       <c r="H25">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J25">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O25">
         <v>6</v>
@@ -2391,19 +2391,19 @@
         <v>103</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I26">
         <v>4</v>
@@ -2412,16 +2412,16 @@
         <v>5</v>
       </c>
       <c r="K26">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L26">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M26">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N26">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O26">
         <v>6</v>
@@ -2459,31 +2459,31 @@
         <v>103</v>
       </c>
       <c r="D27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J27">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L27">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M27">
         <v>5</v>
@@ -2530,16 +2530,16 @@
         <v>2</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I28">
         <v>5</v>
@@ -2548,13 +2548,13 @@
         <v>5</v>
       </c>
       <c r="K28">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L28">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M28">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N28">
         <v>5</v>
@@ -2595,37 +2595,37 @@
         <v>102</v>
       </c>
       <c r="D29">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E29">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I29">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J29">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K29">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L29">
         <v>4</v>
       </c>
       <c r="M29">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N29">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O29">
         <v>6</v>
@@ -2663,22 +2663,22 @@
         <v>101</v>
       </c>
       <c r="D30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F30">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H30">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I30">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J30">
         <v>4</v>
@@ -2687,13 +2687,13 @@
         <v>4</v>
       </c>
       <c r="L30">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M30">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N30">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O30">
         <v>6</v>
@@ -2731,37 +2731,37 @@
         <v>103</v>
       </c>
       <c r="D31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F31">
         <v>3</v>
       </c>
       <c r="G31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J31">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K31">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M31">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O31">
         <v>6</v>
@@ -2799,37 +2799,37 @@
         <v>101</v>
       </c>
       <c r="D32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F32">
         <v>2</v>
       </c>
       <c r="G32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L32">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O32">
         <v>6</v>
@@ -2870,34 +2870,34 @@
         <v>2</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I33">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J33">
         <v>5</v>
       </c>
       <c r="K33">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L33">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M33">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N33">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O33">
         <v>6</v>
@@ -2935,37 +2935,37 @@
         <v>102</v>
       </c>
       <c r="D34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E34">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J34">
         <v>5</v>
       </c>
       <c r="K34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M34">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N34">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O34">
         <v>6</v>
@@ -3003,37 +3003,37 @@
         <v>103</v>
       </c>
       <c r="D35">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E35">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G35">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H35">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I35">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J35">
         <v>4</v>
       </c>
       <c r="K35">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M35">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N35">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O35">
         <v>6</v>
@@ -3071,37 +3071,37 @@
         <v>102</v>
       </c>
       <c r="D36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F36">
         <v>2</v>
       </c>
       <c r="G36">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I36">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J36">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K36">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L36">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M36">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N36">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O36">
         <v>6</v>
@@ -3139,37 +3139,37 @@
         <v>102</v>
       </c>
       <c r="D37">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F37">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H37">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I37">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J37">
         <v>5</v>
       </c>
       <c r="K37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L37">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N37">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O37">
         <v>6</v>
@@ -3207,37 +3207,37 @@
         <v>103</v>
       </c>
       <c r="D38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E38">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G38">
         <v>3</v>
       </c>
       <c r="H38">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I38">
         <v>3</v>
       </c>
       <c r="J38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K38">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L38">
         <v>3</v>
       </c>
       <c r="M38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N38">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O38">
         <v>6</v>
@@ -3275,10 +3275,10 @@
         <v>101</v>
       </c>
       <c r="D39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F39">
         <v>3</v>
@@ -3290,22 +3290,22 @@
         <v>3</v>
       </c>
       <c r="I39">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J39">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K39">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L39">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M39">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N39">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O39">
         <v>6</v>
@@ -3343,37 +3343,37 @@
         <v>103</v>
       </c>
       <c r="D40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H40">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K40">
         <v>5</v>
       </c>
       <c r="L40">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M40">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N40">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O40">
         <v>6</v>
@@ -3411,37 +3411,37 @@
         <v>103</v>
       </c>
       <c r="D41">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G41">
         <v>2</v>
       </c>
       <c r="H41">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I41">
         <v>6</v>
       </c>
       <c r="J41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L41">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M41">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N41">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O41">
         <v>6</v>
@@ -3479,37 +3479,37 @@
         <v>102</v>
       </c>
       <c r="D42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F42">
         <v>2</v>
       </c>
       <c r="G42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H42">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I42">
         <v>6</v>
       </c>
       <c r="J42">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K42">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L42">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M42">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N42">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O42">
         <v>6</v>
@@ -3550,34 +3550,34 @@
         <v>2</v>
       </c>
       <c r="E43">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F43">
         <v>2</v>
       </c>
       <c r="G43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H43">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I43">
         <v>5</v>
       </c>
       <c r="J43">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K43">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L43">
         <v>5</v>
       </c>
       <c r="M43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N43">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O43">
         <v>6</v>
@@ -3615,34 +3615,34 @@
         <v>103</v>
       </c>
       <c r="D44">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E44">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F44">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G44">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H44">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I44">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J44">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K44">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L44">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M44">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N44">
         <v>3</v>
@@ -3683,37 +3683,37 @@
         <v>102</v>
       </c>
       <c r="D45">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E45">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F45">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G45">
         <v>2</v>
       </c>
       <c r="H45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I45">
         <v>4</v>
       </c>
       <c r="J45">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K45">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L45">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M45">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N45">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O45">
         <v>6</v>
@@ -3751,37 +3751,37 @@
         <v>103</v>
       </c>
       <c r="D46">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E46">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G46">
         <v>3</v>
       </c>
       <c r="H46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I46">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J46">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K46">
         <v>4</v>
       </c>
       <c r="L46">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M46">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N46">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O46">
         <v>6</v>
@@ -3822,31 +3822,31 @@
         <v>2</v>
       </c>
       <c r="E47">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H47">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I47">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J47">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K47">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L47">
         <v>5</v>
       </c>
       <c r="M47">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N47">
         <v>5</v>
@@ -3887,37 +3887,37 @@
         <v>101</v>
       </c>
       <c r="D48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G48">
         <v>2</v>
       </c>
       <c r="H48">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I48">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J48">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K48">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L48">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M48">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N48">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O48">
         <v>6</v>
@@ -3955,19 +3955,19 @@
         <v>103</v>
       </c>
       <c r="D49">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F49">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G49">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H49">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I49">
         <v>4</v>
@@ -3976,16 +3976,16 @@
         <v>4</v>
       </c>
       <c r="K49">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L49">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M49">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N49">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O49">
         <v>6</v>
@@ -4023,37 +4023,37 @@
         <v>102</v>
       </c>
       <c r="D50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F50">
         <v>2</v>
       </c>
       <c r="G50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I50">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J50">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K50">
         <v>6</v>
       </c>
       <c r="L50">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M50">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N50">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O50">
         <v>6</v>
@@ -4091,37 +4091,37 @@
         <v>101</v>
       </c>
       <c r="D51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F51">
         <v>2</v>
       </c>
       <c r="G51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I51">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J51">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K51">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L51">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N51">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O51">
         <v>6</v>
@@ -4165,16 +4165,16 @@
         <v>2</v>
       </c>
       <c r="F52">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G52">
         <v>3</v>
       </c>
       <c r="H52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I52">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J52">
         <v>4</v>
@@ -4183,13 +4183,13 @@
         <v>5</v>
       </c>
       <c r="L52">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M52">
         <v>4</v>
       </c>
       <c r="N52">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O52">
         <v>6</v>
@@ -4227,16 +4227,16 @@
         <v>102</v>
       </c>
       <c r="D53">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E53">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F53">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G53">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H53">
         <v>2</v>
@@ -4248,16 +4248,16 @@
         <v>4</v>
       </c>
       <c r="K53">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L53">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M53">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N53">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O53">
         <v>6</v>
@@ -4295,37 +4295,37 @@
         <v>102</v>
       </c>
       <c r="D54">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E54">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F54">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G54">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H54">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I54">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J54">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K54">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L54">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M54">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N54">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O54">
         <v>6</v>
@@ -4363,37 +4363,37 @@
         <v>102</v>
       </c>
       <c r="D55">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E55">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F55">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G55">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H55">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I55">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J55">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K55">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L55">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M55">
         <v>6</v>
       </c>
       <c r="N55">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O55">
         <v>6</v>
@@ -4431,37 +4431,37 @@
         <v>102</v>
       </c>
       <c r="D56">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E56">
         <v>2</v>
       </c>
       <c r="F56">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G56">
         <v>3</v>
       </c>
       <c r="H56">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I56">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J56">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K56">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L56">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M56">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N56">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O56">
         <v>6</v>
@@ -4502,7 +4502,7 @@
         <v>2</v>
       </c>
       <c r="E57">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F57">
         <v>1</v>
@@ -4511,25 +4511,25 @@
         <v>1</v>
       </c>
       <c r="H57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I57">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J57">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K57">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L57">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M57">
         <v>6</v>
       </c>
       <c r="N57">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O57">
         <v>6</v>
@@ -4567,37 +4567,37 @@
         <v>103</v>
       </c>
       <c r="D58">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F58">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G58">
         <v>3</v>
       </c>
       <c r="H58">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I58">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J58">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K58">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L58">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M58">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N58">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O58">
         <v>6</v>
@@ -4635,10 +4635,10 @@
         <v>102</v>
       </c>
       <c r="D59">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E59">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F59">
         <v>3</v>
@@ -4650,19 +4650,19 @@
         <v>3</v>
       </c>
       <c r="I59">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J59">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K59">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L59">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M59">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N59">
         <v>5</v>
@@ -4703,37 +4703,37 @@
         <v>101</v>
       </c>
       <c r="D60">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E60">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F60">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G60">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H60">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I60">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J60">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K60">
         <v>3</v>
       </c>
       <c r="L60">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M60">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N60">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O60">
         <v>6</v>
@@ -4771,37 +4771,37 @@
         <v>103</v>
       </c>
       <c r="D61">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E61">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F61">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G61">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H61">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I61">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J61">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K61">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L61">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M61">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N61">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O61">
         <v>6</v>
@@ -4842,34 +4842,34 @@
         <v>2</v>
       </c>
       <c r="E62">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F62">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H62">
         <v>2</v>
       </c>
       <c r="I62">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J62">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K62">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L62">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M62">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N62">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O62">
         <v>6</v>
@@ -4907,13 +4907,13 @@
         <v>101</v>
       </c>
       <c r="D63">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E63">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F63">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G63">
         <v>4</v>
@@ -4922,22 +4922,22 @@
         <v>3</v>
       </c>
       <c r="I63">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J63">
         <v>4</v>
       </c>
       <c r="K63">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L63">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M63">
         <v>4</v>
       </c>
       <c r="N63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O63">
         <v>6</v>
@@ -4975,34 +4975,34 @@
         <v>101</v>
       </c>
       <c r="D64">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E64">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F64">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G64">
         <v>2</v>
       </c>
       <c r="H64">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I64">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J64">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K64">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L64">
         <v>5</v>
       </c>
       <c r="M64">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N64">
         <v>5</v>
@@ -5040,37 +5040,37 @@
         <v>101</v>
       </c>
       <c r="D65">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E65">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F65">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G65">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H65">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I65">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J65">
         <v>5</v>
       </c>
       <c r="K65">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L65">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M65">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N65">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O65">
         <v>6</v>
@@ -5108,37 +5108,37 @@
         <v>101</v>
       </c>
       <c r="D66">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E66">
         <v>4</v>
       </c>
       <c r="F66">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G66">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H66">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I66">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J66">
         <v>4</v>
       </c>
       <c r="K66">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L66">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M66">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N66">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O66">
         <v>6</v>
@@ -5179,22 +5179,22 @@
         <v>1</v>
       </c>
       <c r="E67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H67">
         <v>2</v>
       </c>
       <c r="I67">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J67">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K67">
         <v>5</v>
@@ -5203,10 +5203,10 @@
         <v>6</v>
       </c>
       <c r="M67">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N67">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O67">
         <v>6</v>
@@ -5244,37 +5244,37 @@
         <v>102</v>
       </c>
       <c r="D68">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E68">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F68">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G68">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H68">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I68">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J68">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K68">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L68">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M68">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N68">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O68">
         <v>6</v>
@@ -5312,34 +5312,34 @@
         <v>101</v>
       </c>
       <c r="D69">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E69">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F69">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G69">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H69">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I69">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J69">
         <v>4</v>
       </c>
       <c r="K69">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L69">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M69">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N69">
         <v>4</v>
@@ -5380,34 +5380,34 @@
         <v>102</v>
       </c>
       <c r="D70">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F70">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G70">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H70">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I70">
         <v>5</v>
       </c>
       <c r="J70">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K70">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L70">
         <v>5</v>
       </c>
       <c r="M70">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N70">
         <v>5</v>
@@ -5448,37 +5448,37 @@
         <v>103</v>
       </c>
       <c r="D71">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E71">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F71">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G71">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H71">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I71">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J71">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K71">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L71">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M71">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N71">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O71">
         <v>6</v>
@@ -5516,34 +5516,34 @@
         <v>101</v>
       </c>
       <c r="D72">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E72">
         <v>3</v>
       </c>
       <c r="F72">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G72">
         <v>2</v>
       </c>
       <c r="H72">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I72">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J72">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K72">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L72">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M72">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N72">
         <v>4</v>
@@ -5584,37 +5584,37 @@
         <v>102</v>
       </c>
       <c r="D73">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G73">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H73">
         <v>2</v>
       </c>
       <c r="I73">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J73">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K73">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L73">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M73">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N73">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O73">
         <v>6</v>
@@ -5652,37 +5652,37 @@
         <v>101</v>
       </c>
       <c r="D74">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F74">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I74">
         <v>4</v>
       </c>
       <c r="J74">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K74">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L74">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M74">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N74">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O74">
         <v>6</v>
@@ -5720,37 +5720,37 @@
         <v>101</v>
       </c>
       <c r="D75">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F75">
         <v>2</v>
       </c>
       <c r="G75">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H75">
         <v>2</v>
       </c>
       <c r="I75">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J75">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K75">
         <v>5</v>
       </c>
       <c r="L75">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M75">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N75">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O75">
         <v>6</v>
@@ -5788,13 +5788,13 @@
         <v>101</v>
       </c>
       <c r="D76">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E76">
         <v>3</v>
       </c>
       <c r="F76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G76">
         <v>2</v>
@@ -5803,22 +5803,22 @@
         <v>2</v>
       </c>
       <c r="I76">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J76">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K76">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L76">
         <v>5</v>
       </c>
       <c r="M76">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N76">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O76">
         <v>6</v>
@@ -5856,7 +5856,7 @@
         <v>103</v>
       </c>
       <c r="D77">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E77">
         <v>2</v>
@@ -5865,25 +5865,25 @@
         <v>3</v>
       </c>
       <c r="G77">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H77">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I77">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J77">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K77">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L77">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M77">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N77">
         <v>5</v>
@@ -5924,37 +5924,37 @@
         <v>103</v>
       </c>
       <c r="D78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E78">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G78">
         <v>2</v>
       </c>
       <c r="H78">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I78">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J78">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K78">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L78">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M78">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N78">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O78">
         <v>6</v>
@@ -5992,37 +5992,37 @@
         <v>101</v>
       </c>
       <c r="D79">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E79">
         <v>3</v>
       </c>
       <c r="F79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G79">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H79">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I79">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J79">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K79">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L79">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M79">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N79">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O79">
         <v>6</v>
@@ -6063,34 +6063,34 @@
         <v>4</v>
       </c>
       <c r="E80">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F80">
         <v>3</v>
       </c>
       <c r="G80">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H80">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I80">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J80">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K80">
         <v>4</v>
       </c>
       <c r="L80">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M80">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N80">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O80">
         <v>6</v>

--- a/data/T3_leader_cleaned.xlsx
+++ b/data/T3_leader_cleaned.xlsx
@@ -765,22 +765,22 @@
         <v>101</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E2">
         <v>3</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J2">
         <v>4</v>
@@ -789,13 +789,13 @@
         <v>3</v>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M2">
         <v>3</v>
       </c>
       <c r="N2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O2">
         <v>6</v>
@@ -836,34 +836,34 @@
         <v>2</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H3">
         <v>2</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O3">
         <v>6</v>
@@ -904,7 +904,7 @@
         <v>4</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4">
         <v>4</v>
@@ -916,22 +916,22 @@
         <v>4</v>
       </c>
       <c r="I4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K4">
         <v>5</v>
       </c>
       <c r="L4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O4">
         <v>6</v>
@@ -972,25 +972,25 @@
         <v>2</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I5">
         <v>5</v>
       </c>
       <c r="J5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L5">
         <v>5</v>
@@ -1037,13 +1037,13 @@
         <v>102</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6">
         <v>3</v>
@@ -1055,19 +1055,19 @@
         <v>4</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M6">
         <v>4</v>
       </c>
       <c r="N6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O6">
         <v>6</v>
@@ -1108,34 +1108,34 @@
         <v>3</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G7">
         <v>2</v>
       </c>
       <c r="H7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O7">
         <v>6</v>
@@ -1173,10 +1173,10 @@
         <v>103</v>
       </c>
       <c r="D8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F8">
         <v>4</v>
@@ -1185,25 +1185,25 @@
         <v>4</v>
       </c>
       <c r="H8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J8">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O8">
         <v>6</v>
@@ -1241,34 +1241,34 @@
         <v>101</v>
       </c>
       <c r="D9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M9">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N9">
         <v>4</v>
@@ -1309,37 +1309,37 @@
         <v>101</v>
       </c>
       <c r="D10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G10">
         <v>2</v>
       </c>
       <c r="H10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O10">
         <v>6</v>
@@ -1386,7 +1386,7 @@
         <v>3</v>
       </c>
       <c r="G11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H11">
         <v>4</v>
@@ -1398,13 +1398,13 @@
         <v>5</v>
       </c>
       <c r="K11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L11">
         <v>5</v>
       </c>
       <c r="M11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N11">
         <v>5</v>
@@ -1451,31 +1451,31 @@
         <v>3</v>
       </c>
       <c r="F12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H12">
         <v>3</v>
       </c>
       <c r="I12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J12">
         <v>5</v>
       </c>
       <c r="K12">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O12">
         <v>6</v>
@@ -1513,37 +1513,37 @@
         <v>103</v>
       </c>
       <c r="D13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J13">
         <v>4</v>
       </c>
       <c r="K13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M13">
         <v>4</v>
       </c>
       <c r="N13">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O13">
         <v>6</v>
@@ -1581,37 +1581,37 @@
         <v>102</v>
       </c>
       <c r="D14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O14">
         <v>6</v>
@@ -1658,10 +1658,10 @@
         <v>3</v>
       </c>
       <c r="G15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I15">
         <v>4</v>
@@ -1670,7 +1670,7 @@
         <v>4</v>
       </c>
       <c r="K15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L15">
         <v>4</v>
@@ -1714,37 +1714,37 @@
         <v>102</v>
       </c>
       <c r="D16">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F16">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I16">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J16">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K16">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L16">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N16">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O16">
         <v>6</v>
@@ -1785,34 +1785,34 @@
         <v>3</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F17">
         <v>3</v>
       </c>
       <c r="G17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I17">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J17">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K17">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L17">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M17">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N17">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O17">
         <v>6</v>
@@ -1850,19 +1850,19 @@
         <v>101</v>
       </c>
       <c r="D18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I18">
         <v>5</v>
@@ -1874,13 +1874,13 @@
         <v>5</v>
       </c>
       <c r="L18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O18">
         <v>6</v>
@@ -1918,28 +1918,28 @@
         <v>103</v>
       </c>
       <c r="D19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G19">
         <v>3</v>
       </c>
       <c r="H19">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I19">
         <v>6</v>
       </c>
       <c r="J19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L19">
         <v>5</v>
@@ -1948,7 +1948,7 @@
         <v>5</v>
       </c>
       <c r="N19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O19">
         <v>6</v>
@@ -1998,25 +1998,25 @@
         <v>2</v>
       </c>
       <c r="H20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J20">
         <v>5</v>
       </c>
       <c r="K20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L20">
         <v>5</v>
       </c>
       <c r="M20">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N20">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O20">
         <v>6</v>
@@ -2054,7 +2054,7 @@
         <v>103</v>
       </c>
       <c r="D21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E21">
         <v>2</v>
@@ -2069,22 +2069,22 @@
         <v>3</v>
       </c>
       <c r="I21">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J21">
         <v>5</v>
       </c>
       <c r="K21">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L21">
         <v>4</v>
       </c>
       <c r="M21">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N21">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O21">
         <v>6</v>
@@ -2122,7 +2122,7 @@
         <v>102</v>
       </c>
       <c r="D22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E22">
         <v>2</v>
@@ -2134,25 +2134,25 @@
         <v>2</v>
       </c>
       <c r="H22">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I22">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J22">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K22">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L22">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M22">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N22">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O22">
         <v>6</v>
@@ -2193,7 +2193,7 @@
         <v>2</v>
       </c>
       <c r="E23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F23">
         <v>2</v>
@@ -2202,7 +2202,7 @@
         <v>2</v>
       </c>
       <c r="H23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I23">
         <v>6</v>
@@ -2214,7 +2214,7 @@
         <v>5</v>
       </c>
       <c r="L23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M23">
         <v>6</v>
@@ -2261,13 +2261,13 @@
         <v>3</v>
       </c>
       <c r="E24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F24">
         <v>3</v>
       </c>
       <c r="G24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H24">
         <v>3</v>
@@ -2276,13 +2276,13 @@
         <v>5</v>
       </c>
       <c r="J24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M24">
         <v>5</v>
@@ -2329,31 +2329,31 @@
         <v>2</v>
       </c>
       <c r="F25">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G25">
         <v>2</v>
       </c>
       <c r="H25">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I25">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J25">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L25">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M25">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N25">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O25">
         <v>6</v>
@@ -2391,37 +2391,37 @@
         <v>103</v>
       </c>
       <c r="D26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F26">
         <v>2</v>
       </c>
       <c r="G26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I26">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K26">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L26">
         <v>4</v>
       </c>
       <c r="M26">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N26">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O26">
         <v>6</v>
@@ -2474,16 +2474,16 @@
         <v>2</v>
       </c>
       <c r="I27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J27">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K27">
         <v>5</v>
       </c>
       <c r="L27">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M27">
         <v>5</v>
@@ -2527,13 +2527,13 @@
         <v>101</v>
       </c>
       <c r="D28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G28">
         <v>3</v>
@@ -2542,22 +2542,22 @@
         <v>3</v>
       </c>
       <c r="I28">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J28">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K28">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L28">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M28">
         <v>5</v>
       </c>
       <c r="N28">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O28">
         <v>6</v>
@@ -2604,25 +2604,25 @@
         <v>2</v>
       </c>
       <c r="G29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I29">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J29">
         <v>4</v>
       </c>
       <c r="K29">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L29">
         <v>4</v>
       </c>
       <c r="M29">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N29">
         <v>4</v>
@@ -2669,7 +2669,7 @@
         <v>2</v>
       </c>
       <c r="F30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G30">
         <v>2</v>
@@ -2678,22 +2678,22 @@
         <v>2</v>
       </c>
       <c r="I30">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J30">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K30">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N30">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O30">
         <v>6</v>
@@ -2731,16 +2731,16 @@
         <v>103</v>
       </c>
       <c r="D31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E31">
         <v>3</v>
       </c>
       <c r="F31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G31">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H31">
         <v>2</v>
@@ -2749,19 +2749,19 @@
         <v>4</v>
       </c>
       <c r="J31">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K31">
         <v>4</v>
       </c>
       <c r="L31">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N31">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O31">
         <v>6</v>
@@ -2799,37 +2799,37 @@
         <v>101</v>
       </c>
       <c r="D32">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F32">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G32">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I32">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J32">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K32">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L32">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N32">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O32">
         <v>6</v>
@@ -2867,37 +2867,37 @@
         <v>103</v>
       </c>
       <c r="D33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E33">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G33">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I33">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J33">
         <v>5</v>
       </c>
       <c r="K33">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L33">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M33">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N33">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O33">
         <v>6</v>
@@ -2938,7 +2938,7 @@
         <v>2</v>
       </c>
       <c r="E34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34">
         <v>2</v>
@@ -2950,16 +2950,16 @@
         <v>2</v>
       </c>
       <c r="I34">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J34">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K34">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L34">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M34">
         <v>5</v>
@@ -3006,7 +3006,7 @@
         <v>4</v>
       </c>
       <c r="E35">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F35">
         <v>3</v>
@@ -3015,7 +3015,7 @@
         <v>4</v>
       </c>
       <c r="H35">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I35">
         <v>4</v>
@@ -3071,31 +3071,31 @@
         <v>102</v>
       </c>
       <c r="D36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F36">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K36">
         <v>5</v>
       </c>
       <c r="L36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M36">
         <v>5</v>
@@ -3139,22 +3139,22 @@
         <v>102</v>
       </c>
       <c r="D37">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E37">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H37">
         <v>3</v>
       </c>
       <c r="I37">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J37">
         <v>5</v>
@@ -3163,10 +3163,10 @@
         <v>5</v>
       </c>
       <c r="L37">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M37">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N37">
         <v>4</v>
@@ -3207,28 +3207,28 @@
         <v>103</v>
       </c>
       <c r="D38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G38">
         <v>3</v>
       </c>
       <c r="H38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I38">
         <v>3</v>
       </c>
       <c r="J38">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L38">
         <v>3</v>
@@ -3237,7 +3237,7 @@
         <v>3</v>
       </c>
       <c r="N38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O38">
         <v>6</v>
@@ -3278,19 +3278,19 @@
         <v>2</v>
       </c>
       <c r="E39">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G39">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H39">
         <v>3</v>
       </c>
       <c r="I39">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J39">
         <v>5</v>
@@ -3299,13 +3299,13 @@
         <v>6</v>
       </c>
       <c r="L39">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M39">
         <v>5</v>
       </c>
       <c r="N39">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O39">
         <v>6</v>
@@ -3343,22 +3343,22 @@
         <v>103</v>
       </c>
       <c r="D40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E40">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F40">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G40">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I40">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J40">
         <v>5</v>
@@ -3370,10 +3370,10 @@
         <v>5</v>
       </c>
       <c r="M40">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N40">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O40">
         <v>6</v>
@@ -3411,13 +3411,13 @@
         <v>103</v>
       </c>
       <c r="D41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E41">
         <v>2</v>
       </c>
       <c r="F41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G41">
         <v>2</v>
@@ -3426,22 +3426,22 @@
         <v>2</v>
       </c>
       <c r="I41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M41">
         <v>6</v>
       </c>
       <c r="N41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O41">
         <v>6</v>
@@ -3479,25 +3479,25 @@
         <v>102</v>
       </c>
       <c r="D42">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G42">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H42">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I42">
         <v>6</v>
       </c>
       <c r="J42">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K42">
         <v>5</v>
@@ -3506,7 +3506,7 @@
         <v>5</v>
       </c>
       <c r="M42">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N42">
         <v>5</v>
@@ -3559,19 +3559,19 @@
         <v>2</v>
       </c>
       <c r="H43">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M43">
         <v>6</v>
@@ -3615,37 +3615,37 @@
         <v>103</v>
       </c>
       <c r="D44">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E44">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F44">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G44">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H44">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I44">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J44">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K44">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L44">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M44">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N44">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O44">
         <v>6</v>
@@ -3692,7 +3692,7 @@
         <v>2</v>
       </c>
       <c r="G45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H45">
         <v>2</v>
@@ -3701,7 +3701,7 @@
         <v>4</v>
       </c>
       <c r="J45">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K45">
         <v>4</v>
@@ -3710,10 +3710,10 @@
         <v>4</v>
       </c>
       <c r="M45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N45">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O45">
         <v>6</v>
@@ -3754,7 +3754,7 @@
         <v>3</v>
       </c>
       <c r="E46">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F46">
         <v>3</v>
@@ -3763,25 +3763,25 @@
         <v>3</v>
       </c>
       <c r="H46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I46">
         <v>4</v>
       </c>
       <c r="J46">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K46">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L46">
         <v>4</v>
       </c>
       <c r="M46">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N46">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O46">
         <v>6</v>
@@ -3819,10 +3819,10 @@
         <v>102</v>
       </c>
       <c r="D47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F47">
         <v>3</v>
@@ -3831,25 +3831,25 @@
         <v>2</v>
       </c>
       <c r="H47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I47">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J47">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K47">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L47">
         <v>5</v>
       </c>
       <c r="M47">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N47">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O47">
         <v>6</v>
@@ -3887,19 +3887,19 @@
         <v>101</v>
       </c>
       <c r="D48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H48">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I48">
         <v>5</v>
@@ -3911,7 +3911,7 @@
         <v>5</v>
       </c>
       <c r="L48">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M48">
         <v>5</v>
@@ -3955,37 +3955,37 @@
         <v>103</v>
       </c>
       <c r="D49">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F49">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G49">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H49">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I49">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J49">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K49">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L49">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M49">
         <v>5</v>
       </c>
       <c r="N49">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O49">
         <v>6</v>
@@ -4026,34 +4026,34 @@
         <v>2</v>
       </c>
       <c r="E50">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F50">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G50">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H50">
         <v>2</v>
       </c>
       <c r="I50">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J50">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K50">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L50">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M50">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N50">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O50">
         <v>6</v>
@@ -4094,13 +4094,13 @@
         <v>2</v>
       </c>
       <c r="E51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G51">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H51">
         <v>2</v>
@@ -4112,7 +4112,7 @@
         <v>6</v>
       </c>
       <c r="K51">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L51">
         <v>6</v>
@@ -4159,16 +4159,16 @@
         <v>102</v>
       </c>
       <c r="D52">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E52">
         <v>2</v>
       </c>
       <c r="F52">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G52">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H52">
         <v>2</v>
@@ -4180,7 +4180,7 @@
         <v>4</v>
       </c>
       <c r="K52">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L52">
         <v>4</v>
@@ -4189,7 +4189,7 @@
         <v>4</v>
       </c>
       <c r="N52">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O52">
         <v>6</v>
@@ -4227,37 +4227,37 @@
         <v>102</v>
       </c>
       <c r="D53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E53">
         <v>3</v>
       </c>
       <c r="F53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G53">
         <v>2</v>
       </c>
       <c r="H53">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I53">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J53">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K53">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L53">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M53">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N53">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O53">
         <v>6</v>
@@ -4304,28 +4304,28 @@
         <v>3</v>
       </c>
       <c r="G54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H54">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I54">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J54">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K54">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L54">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M54">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N54">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O54">
         <v>6</v>
@@ -4366,7 +4366,7 @@
         <v>2</v>
       </c>
       <c r="E55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F55">
         <v>2</v>
@@ -4375,25 +4375,25 @@
         <v>2</v>
       </c>
       <c r="H55">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I55">
         <v>6</v>
       </c>
       <c r="J55">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K55">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L55">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M55">
         <v>6</v>
       </c>
       <c r="N55">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O55">
         <v>6</v>
@@ -4431,31 +4431,31 @@
         <v>102</v>
       </c>
       <c r="D56">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E56">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F56">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G56">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H56">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I56">
         <v>5</v>
       </c>
       <c r="J56">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K56">
         <v>4</v>
       </c>
       <c r="L56">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M56">
         <v>4</v>
@@ -4502,16 +4502,16 @@
         <v>2</v>
       </c>
       <c r="E57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I57">
         <v>6</v>
@@ -4570,7 +4570,7 @@
         <v>3</v>
       </c>
       <c r="E58">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F58">
         <v>2</v>
@@ -4579,25 +4579,25 @@
         <v>3</v>
       </c>
       <c r="H58">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I58">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J58">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K58">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L58">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M58">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N58">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O58">
         <v>6</v>
@@ -4635,37 +4635,37 @@
         <v>102</v>
       </c>
       <c r="D59">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E59">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F59">
         <v>3</v>
       </c>
       <c r="G59">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H59">
         <v>3</v>
       </c>
       <c r="I59">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J59">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K59">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L59">
         <v>4</v>
       </c>
       <c r="M59">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N59">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O59">
         <v>6</v>
@@ -4703,37 +4703,37 @@
         <v>101</v>
       </c>
       <c r="D60">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E60">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F60">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G60">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I60">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J60">
         <v>4</v>
       </c>
       <c r="K60">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L60">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M60">
         <v>4</v>
       </c>
       <c r="N60">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O60">
         <v>6</v>
@@ -4780,22 +4780,22 @@
         <v>3</v>
       </c>
       <c r="G61">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H61">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I61">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J61">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K61">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L61">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M61">
         <v>4</v>
@@ -4842,10 +4842,10 @@
         <v>2</v>
       </c>
       <c r="E62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G62">
         <v>2</v>
@@ -4854,22 +4854,22 @@
         <v>2</v>
       </c>
       <c r="I62">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J62">
         <v>4</v>
       </c>
       <c r="K62">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L62">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M62">
         <v>4</v>
       </c>
       <c r="N62">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O62">
         <v>6</v>
@@ -4907,13 +4907,13 @@
         <v>101</v>
       </c>
       <c r="D63">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E63">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F63">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G63">
         <v>4</v>
@@ -4925,19 +4925,19 @@
         <v>4</v>
       </c>
       <c r="J63">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K63">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L63">
         <v>5</v>
       </c>
       <c r="M63">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N63">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O63">
         <v>6</v>
@@ -4975,7 +4975,7 @@
         <v>101</v>
       </c>
       <c r="D64">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E64">
         <v>2</v>
@@ -4984,16 +4984,16 @@
         <v>2</v>
       </c>
       <c r="G64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H64">
         <v>3</v>
       </c>
       <c r="I64">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J64">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K64">
         <v>5</v>
@@ -5002,10 +5002,10 @@
         <v>5</v>
       </c>
       <c r="M64">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N64">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O64">
         <v>6</v>
@@ -5040,25 +5040,25 @@
         <v>101</v>
       </c>
       <c r="D65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I65">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J65">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K65">
         <v>5</v>
@@ -5067,10 +5067,10 @@
         <v>5</v>
       </c>
       <c r="M65">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N65">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O65">
         <v>6</v>
@@ -5108,22 +5108,22 @@
         <v>101</v>
       </c>
       <c r="D66">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E66">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F66">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G66">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H66">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I66">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J66">
         <v>4</v>
@@ -5138,7 +5138,7 @@
         <v>4</v>
       </c>
       <c r="N66">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O66">
         <v>6</v>
@@ -5176,25 +5176,25 @@
         <v>102</v>
       </c>
       <c r="D67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E67">
         <v>2</v>
       </c>
       <c r="F67">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H67">
         <v>2</v>
       </c>
       <c r="I67">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J67">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K67">
         <v>5</v>
@@ -5203,10 +5203,10 @@
         <v>6</v>
       </c>
       <c r="M67">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N67">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O67">
         <v>6</v>
@@ -5247,16 +5247,16 @@
         <v>3</v>
       </c>
       <c r="E68">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F68">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G68">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H68">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I68">
         <v>4</v>
@@ -5271,7 +5271,7 @@
         <v>4</v>
       </c>
       <c r="M68">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N68">
         <v>4</v>
@@ -5312,37 +5312,37 @@
         <v>101</v>
       </c>
       <c r="D69">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E69">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F69">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G69">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H69">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I69">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J69">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K69">
         <v>4</v>
       </c>
       <c r="L69">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M69">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N69">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O69">
         <v>6</v>
@@ -5380,25 +5380,25 @@
         <v>102</v>
       </c>
       <c r="D70">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E70">
         <v>2</v>
       </c>
       <c r="F70">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G70">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H70">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I70">
         <v>5</v>
       </c>
       <c r="J70">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K70">
         <v>5</v>
@@ -5410,7 +5410,7 @@
         <v>5</v>
       </c>
       <c r="N70">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O70">
         <v>6</v>
@@ -5448,13 +5448,13 @@
         <v>103</v>
       </c>
       <c r="D71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E71">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G71">
         <v>2</v>
@@ -5463,22 +5463,22 @@
         <v>2</v>
       </c>
       <c r="I71">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J71">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K71">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L71">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M71">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N71">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O71">
         <v>6</v>
@@ -5522,25 +5522,25 @@
         <v>3</v>
       </c>
       <c r="F72">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G72">
         <v>2</v>
       </c>
       <c r="H72">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I72">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J72">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K72">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L72">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M72">
         <v>5</v>
@@ -5593,28 +5593,28 @@
         <v>2</v>
       </c>
       <c r="G73">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H73">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I73">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J73">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K73">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L73">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M73">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N73">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O73">
         <v>6</v>
@@ -5661,7 +5661,7 @@
         <v>4</v>
       </c>
       <c r="G74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H74">
         <v>3</v>
@@ -5670,7 +5670,7 @@
         <v>4</v>
       </c>
       <c r="J74">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K74">
         <v>4</v>
@@ -5682,7 +5682,7 @@
         <v>4</v>
       </c>
       <c r="N74">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O74">
         <v>6</v>
@@ -5720,37 +5720,37 @@
         <v>101</v>
       </c>
       <c r="D75">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E75">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F75">
         <v>2</v>
       </c>
       <c r="G75">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H75">
         <v>2</v>
       </c>
       <c r="I75">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J75">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K75">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L75">
         <v>6</v>
       </c>
       <c r="M75">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N75">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O75">
         <v>6</v>
@@ -5797,28 +5797,28 @@
         <v>2</v>
       </c>
       <c r="G76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H76">
         <v>2</v>
       </c>
       <c r="I76">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J76">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K76">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L76">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M76">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N76">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O76">
         <v>6</v>
@@ -5859,34 +5859,34 @@
         <v>4</v>
       </c>
       <c r="E77">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F77">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G77">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H77">
         <v>4</v>
       </c>
       <c r="I77">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J77">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K77">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L77">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M77">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N77">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O77">
         <v>6</v>
@@ -5927,7 +5927,7 @@
         <v>2</v>
       </c>
       <c r="E78">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F78">
         <v>2</v>
@@ -5936,25 +5936,25 @@
         <v>2</v>
       </c>
       <c r="H78">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I78">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J78">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K78">
         <v>6</v>
       </c>
       <c r="L78">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M78">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N78">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O78">
         <v>6</v>
@@ -5998,16 +5998,16 @@
         <v>3</v>
       </c>
       <c r="F79">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G79">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H79">
         <v>3</v>
       </c>
       <c r="I79">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J79">
         <v>4</v>
@@ -6019,7 +6019,7 @@
         <v>4</v>
       </c>
       <c r="M79">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N79">
         <v>4</v>
@@ -6060,7 +6060,7 @@
         <v>101</v>
       </c>
       <c r="D80">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E80">
         <v>3</v>
@@ -6072,19 +6072,19 @@
         <v>3</v>
       </c>
       <c r="H80">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I80">
         <v>4</v>
       </c>
       <c r="J80">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K80">
         <v>4</v>
       </c>
       <c r="L80">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M80">
         <v>4</v>

--- a/data/T3_leader_cleaned.xlsx
+++ b/data/T3_leader_cleaned.xlsx
@@ -955,7 +955,7 @@
         <v>16</v>
       </c>
       <c r="V4">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -1023,7 +1023,7 @@
         <v>29</v>
       </c>
       <c r="V5">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -1091,7 +1091,7 @@
         <v>14</v>
       </c>
       <c r="V6">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -1159,7 +1159,7 @@
         <v>17</v>
       </c>
       <c r="V7">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -1227,7 +1227,7 @@
         <v>7</v>
       </c>
       <c r="V8">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -1295,7 +1295,7 @@
         <v>20</v>
       </c>
       <c r="V9">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1363,7 +1363,7 @@
         <v>14</v>
       </c>
       <c r="V10">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1431,7 +1431,7 @@
         <v>16</v>
       </c>
       <c r="V11">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1499,7 +1499,7 @@
         <v>13</v>
       </c>
       <c r="V12">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1567,7 +1567,7 @@
         <v>12</v>
       </c>
       <c r="V13">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -1635,7 +1635,7 @@
         <v>10</v>
       </c>
       <c r="V14">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1700,7 +1700,7 @@
         <v>17</v>
       </c>
       <c r="V15">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -1768,7 +1768,7 @@
         <v>11</v>
       </c>
       <c r="V16">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -1836,7 +1836,7 @@
         <v>22</v>
       </c>
       <c r="V17">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -1904,7 +1904,7 @@
         <v>22</v>
       </c>
       <c r="V18">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -2040,7 +2040,7 @@
         <v>29</v>
       </c>
       <c r="V20">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -2108,7 +2108,7 @@
         <v>8</v>
       </c>
       <c r="V21">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -2176,7 +2176,7 @@
         <v>19</v>
       </c>
       <c r="V22">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -2244,7 +2244,7 @@
         <v>10</v>
       </c>
       <c r="V23">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -2309,7 +2309,7 @@
         <v>17</v>
       </c>
       <c r="V24">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -2513,7 +2513,7 @@
         <v>20</v>
       </c>
       <c r="V27">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -2581,7 +2581,7 @@
         <v>20</v>
       </c>
       <c r="V28">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -2649,7 +2649,7 @@
         <v>8</v>
       </c>
       <c r="V29">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:22">
@@ -2853,7 +2853,7 @@
         <v>9</v>
       </c>
       <c r="V32">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33" spans="1:22">
@@ -2989,7 +2989,7 @@
         <v>5</v>
       </c>
       <c r="V34">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35" spans="1:22">
@@ -3057,7 +3057,7 @@
         <v>17</v>
       </c>
       <c r="V35">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36" spans="1:22">
@@ -3125,7 +3125,7 @@
         <v>14</v>
       </c>
       <c r="V36">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37" spans="1:22">
@@ -3193,7 +3193,7 @@
         <v>8</v>
       </c>
       <c r="V37">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:22">
@@ -3261,7 +3261,7 @@
         <v>8</v>
       </c>
       <c r="V38">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39" spans="1:22">
@@ -3397,7 +3397,7 @@
         <v>15</v>
       </c>
       <c r="V40">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41" spans="1:22">
@@ -3465,7 +3465,7 @@
         <v>13</v>
       </c>
       <c r="V41">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:22">
@@ -3533,7 +3533,7 @@
         <v>14</v>
       </c>
       <c r="V42">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:22">
@@ -3601,7 +3601,7 @@
         <v>13</v>
       </c>
       <c r="V43">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44" spans="1:22">
@@ -3737,7 +3737,7 @@
         <v>21</v>
       </c>
       <c r="V45">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46" spans="1:22">
@@ -3805,7 +3805,7 @@
         <v>6</v>
       </c>
       <c r="V46">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:22">
@@ -3873,7 +3873,7 @@
         <v>16</v>
       </c>
       <c r="V47">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48" spans="1:22">
@@ -4009,7 +4009,7 @@
         <v>5</v>
       </c>
       <c r="V49">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50" spans="1:22">
@@ -4077,7 +4077,7 @@
         <v>16</v>
       </c>
       <c r="V50">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51" spans="1:22">
@@ -4145,7 +4145,7 @@
         <v>9</v>
       </c>
       <c r="V51">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52" spans="1:22">
@@ -4213,7 +4213,7 @@
         <v>24</v>
       </c>
       <c r="V52">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53" spans="1:22">
@@ -4281,7 +4281,7 @@
         <v>17</v>
       </c>
       <c r="V53">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:22">
@@ -4349,7 +4349,7 @@
         <v>17</v>
       </c>
       <c r="V54">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55" spans="1:22">
@@ -4485,7 +4485,7 @@
         <v>26</v>
       </c>
       <c r="V56">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:22">
@@ -4689,7 +4689,7 @@
         <v>14</v>
       </c>
       <c r="V59">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60" spans="1:22">
@@ -4757,7 +4757,7 @@
         <v>19</v>
       </c>
       <c r="V60">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61" spans="1:22">
@@ -4825,7 +4825,7 @@
         <v>10</v>
       </c>
       <c r="V61">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="62" spans="1:22">
@@ -4893,7 +4893,7 @@
         <v>13</v>
       </c>
       <c r="V62">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63" spans="1:22">
@@ -4961,7 +4961,7 @@
         <v>24</v>
       </c>
       <c r="V63">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:22">
@@ -5026,7 +5026,7 @@
         <v>16</v>
       </c>
       <c r="V64">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65" spans="1:22">
@@ -5094,7 +5094,7 @@
         <v>7</v>
       </c>
       <c r="V65">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66" spans="1:22">
@@ -5162,7 +5162,7 @@
         <v>20</v>
       </c>
       <c r="V66">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67" spans="1:22">
@@ -5366,7 +5366,7 @@
         <v>15</v>
       </c>
       <c r="V69">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:22">
@@ -5434,7 +5434,7 @@
         <v>10</v>
       </c>
       <c r="V70">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="71" spans="1:22">
@@ -5570,7 +5570,7 @@
         <v>19</v>
       </c>
       <c r="V72">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:22">
@@ -5706,7 +5706,7 @@
         <v>5</v>
       </c>
       <c r="V74">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75" spans="1:22">
@@ -5842,7 +5842,7 @@
         <v>15</v>
       </c>
       <c r="V76">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="77" spans="1:22">
@@ -5910,7 +5910,7 @@
         <v>11</v>
       </c>
       <c r="V77">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78" spans="1:22">
@@ -6046,7 +6046,7 @@
         <v>10</v>
       </c>
       <c r="V79">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80" spans="1:22">
@@ -6114,7 +6114,7 @@
         <v>22</v>
       </c>
       <c r="V80">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/data/T3_leader_cleaned.xlsx
+++ b/data/T3_leader_cleaned.xlsx
@@ -774,7 +774,7 @@
         <v>2</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H2">
         <v>2</v>
@@ -786,13 +786,13 @@
         <v>4</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L2">
         <v>3</v>
       </c>
       <c r="M2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N2">
         <v>4</v>
@@ -842,7 +842,7 @@
         <v>2</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H3">
         <v>2</v>
@@ -854,7 +854,7 @@
         <v>5</v>
       </c>
       <c r="K3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L3">
         <v>4</v>
@@ -901,7 +901,7 @@
         <v>101</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E4">
         <v>4</v>
@@ -990,13 +990,13 @@
         <v>4</v>
       </c>
       <c r="K5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N5">
         <v>5</v>
@@ -1058,10 +1058,10 @@
         <v>3</v>
       </c>
       <c r="K6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M6">
         <v>4</v>
@@ -1120,10 +1120,10 @@
         <v>3</v>
       </c>
       <c r="I7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K7">
         <v>5</v>
@@ -1188,10 +1188,10 @@
         <v>4</v>
       </c>
       <c r="I8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K8">
         <v>5</v>
@@ -1531,7 +1531,7 @@
         <v>4</v>
       </c>
       <c r="J13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K13">
         <v>4</v>
@@ -1593,7 +1593,7 @@
         <v>3</v>
       </c>
       <c r="H14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I14">
         <v>5</v>
@@ -1735,7 +1735,7 @@
         <v>7</v>
       </c>
       <c r="K16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L16">
         <v>6</v>
@@ -1797,7 +1797,7 @@
         <v>3</v>
       </c>
       <c r="I17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J17">
         <v>2</v>
@@ -1880,7 +1880,7 @@
         <v>5</v>
       </c>
       <c r="N18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O18">
         <v>6</v>
@@ -1933,7 +1933,7 @@
         <v>2</v>
       </c>
       <c r="I19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J19">
         <v>4</v>
@@ -1942,7 +1942,7 @@
         <v>5</v>
       </c>
       <c r="L19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M19">
         <v>5</v>
@@ -2010,7 +2010,7 @@
         <v>5</v>
       </c>
       <c r="L20">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M20">
         <v>4</v>
@@ -2075,7 +2075,7 @@
         <v>5</v>
       </c>
       <c r="K21">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L21">
         <v>4</v>
@@ -2122,7 +2122,7 @@
         <v>102</v>
       </c>
       <c r="D22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E22">
         <v>2</v>
@@ -2140,7 +2140,7 @@
         <v>4</v>
       </c>
       <c r="J22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K22">
         <v>4</v>
@@ -2190,7 +2190,7 @@
         <v>103</v>
       </c>
       <c r="D23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E23">
         <v>2</v>
@@ -2205,16 +2205,16 @@
         <v>2</v>
       </c>
       <c r="I23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K23">
         <v>5</v>
       </c>
       <c r="L23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M23">
         <v>6</v>
@@ -2285,7 +2285,7 @@
         <v>5</v>
       </c>
       <c r="M24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N24">
         <v>5</v>
@@ -2338,7 +2338,7 @@
         <v>2</v>
       </c>
       <c r="I25">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J25">
         <v>4</v>
@@ -2394,7 +2394,7 @@
         <v>2</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F26">
         <v>2</v>
@@ -2409,13 +2409,13 @@
         <v>5</v>
       </c>
       <c r="J26">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K26">
         <v>5</v>
       </c>
       <c r="L26">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M26">
         <v>5</v>
@@ -2477,7 +2477,7 @@
         <v>5</v>
       </c>
       <c r="J27">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K27">
         <v>5</v>
@@ -2486,7 +2486,7 @@
         <v>4</v>
       </c>
       <c r="M27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N27">
         <v>5</v>
@@ -2527,13 +2527,13 @@
         <v>101</v>
       </c>
       <c r="D28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E28">
         <v>3</v>
       </c>
       <c r="F28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G28">
         <v>3</v>
@@ -2607,7 +2607,7 @@
         <v>2</v>
       </c>
       <c r="H29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I29">
         <v>5</v>
@@ -2734,7 +2734,7 @@
         <v>4</v>
       </c>
       <c r="E31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F31">
         <v>4</v>
@@ -2743,25 +2743,25 @@
         <v>4</v>
       </c>
       <c r="H31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I31">
         <v>4</v>
       </c>
       <c r="J31">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K31">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L31">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M31">
         <v>4</v>
       </c>
       <c r="N31">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O31">
         <v>6</v>
@@ -2799,13 +2799,13 @@
         <v>101</v>
       </c>
       <c r="D32">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E32">
         <v>3</v>
       </c>
       <c r="F32">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G32">
         <v>4</v>
@@ -2820,10 +2820,10 @@
         <v>4</v>
       </c>
       <c r="K32">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L32">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M32">
         <v>5</v>
@@ -2867,7 +2867,7 @@
         <v>103</v>
       </c>
       <c r="D33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33">
         <v>3</v>
@@ -3006,13 +3006,13 @@
         <v>4</v>
       </c>
       <c r="E35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F35">
         <v>3</v>
       </c>
       <c r="G35">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H35">
         <v>3</v>
@@ -3077,13 +3077,13 @@
         <v>3</v>
       </c>
       <c r="F36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G36">
         <v>3</v>
       </c>
       <c r="H36">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I36">
         <v>4</v>
@@ -3098,7 +3098,7 @@
         <v>4</v>
       </c>
       <c r="M36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N36">
         <v>5</v>
@@ -3142,7 +3142,7 @@
         <v>4</v>
       </c>
       <c r="E37">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F37">
         <v>3</v>
@@ -3154,7 +3154,7 @@
         <v>3</v>
       </c>
       <c r="I37">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J37">
         <v>5</v>
@@ -3169,7 +3169,7 @@
         <v>4</v>
       </c>
       <c r="N37">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O37">
         <v>6</v>
@@ -3207,13 +3207,13 @@
         <v>103</v>
       </c>
       <c r="D38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E38">
         <v>3</v>
       </c>
       <c r="F38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G38">
         <v>3</v>
@@ -3222,7 +3222,7 @@
         <v>3</v>
       </c>
       <c r="I38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J38">
         <v>4</v>
@@ -3231,10 +3231,10 @@
         <v>4</v>
       </c>
       <c r="L38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N38">
         <v>4</v>
@@ -3284,7 +3284,7 @@
         <v>2</v>
       </c>
       <c r="G39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H39">
         <v>3</v>
@@ -3358,7 +3358,7 @@
         <v>3</v>
       </c>
       <c r="I40">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J40">
         <v>5</v>
@@ -3577,7 +3577,7 @@
         <v>6</v>
       </c>
       <c r="N43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O43">
         <v>6</v>
@@ -3689,13 +3689,13 @@
         <v>2</v>
       </c>
       <c r="F45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G45">
         <v>3</v>
       </c>
       <c r="H45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I45">
         <v>4</v>
@@ -3772,13 +3772,13 @@
         <v>5</v>
       </c>
       <c r="K46">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L46">
         <v>4</v>
       </c>
       <c r="M46">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N46">
         <v>5</v>
@@ -3905,7 +3905,7 @@
         <v>5</v>
       </c>
       <c r="J48">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K48">
         <v>5</v>
@@ -3917,7 +3917,7 @@
         <v>5</v>
       </c>
       <c r="N48">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O48">
         <v>6</v>
@@ -3955,7 +3955,7 @@
         <v>103</v>
       </c>
       <c r="D49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49">
         <v>1</v>
@@ -4053,7 +4053,7 @@
         <v>3</v>
       </c>
       <c r="N50">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O50">
         <v>6</v>
@@ -4112,13 +4112,13 @@
         <v>6</v>
       </c>
       <c r="K51">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L51">
         <v>6</v>
       </c>
       <c r="M51">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N51">
         <v>6</v>
@@ -4245,7 +4245,7 @@
         <v>5</v>
       </c>
       <c r="J53">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K53">
         <v>5</v>
@@ -4298,7 +4298,7 @@
         <v>3</v>
       </c>
       <c r="E54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F54">
         <v>3</v>
@@ -4440,13 +4440,13 @@
         <v>4</v>
       </c>
       <c r="G56">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H56">
         <v>4</v>
       </c>
       <c r="I56">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J56">
         <v>4</v>
@@ -4573,7 +4573,7 @@
         <v>3</v>
       </c>
       <c r="F58">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G58">
         <v>3</v>
@@ -4662,7 +4662,7 @@
         <v>4</v>
       </c>
       <c r="M59">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N59">
         <v>4</v>
@@ -4869,7 +4869,7 @@
         <v>4</v>
       </c>
       <c r="N62">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O62">
         <v>6</v>
@@ -4981,10 +4981,10 @@
         <v>2</v>
       </c>
       <c r="F64">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H64">
         <v>3</v>
@@ -5043,7 +5043,7 @@
         <v>3</v>
       </c>
       <c r="E65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F65">
         <v>3</v>
@@ -5055,7 +5055,7 @@
         <v>2</v>
       </c>
       <c r="I65">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J65">
         <v>6</v>
@@ -5197,7 +5197,7 @@
         <v>6</v>
       </c>
       <c r="K67">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L67">
         <v>6</v>
@@ -5268,7 +5268,7 @@
         <v>4</v>
       </c>
       <c r="L68">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M68">
         <v>4</v>
@@ -5315,7 +5315,7 @@
         <v>4</v>
       </c>
       <c r="E69">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F69">
         <v>5</v>
@@ -5339,7 +5339,7 @@
         <v>5</v>
       </c>
       <c r="M69">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N69">
         <v>5</v>
@@ -5469,13 +5469,13 @@
         <v>5</v>
       </c>
       <c r="K71">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L71">
         <v>6</v>
       </c>
       <c r="M71">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N71">
         <v>6</v>
@@ -5516,10 +5516,10 @@
         <v>101</v>
       </c>
       <c r="D72">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E72">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F72">
         <v>3</v>
@@ -5540,10 +5540,10 @@
         <v>4</v>
       </c>
       <c r="L72">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M72">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N72">
         <v>4</v>
@@ -5587,7 +5587,7 @@
         <v>2</v>
       </c>
       <c r="E73">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73">
         <v>2</v>
@@ -5611,7 +5611,7 @@
         <v>